--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E6CBC2-893A-A542-A2B4-91669771821F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1D6BC9-C315-0743-8471-111929B8AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39640" yWindow="500" windowWidth="38100" windowHeight="20800" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -5829,7 +5829,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="436">
+  <cellXfs count="434">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6736,16 +6736,96 @@
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="20" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6759,133 +6839,48 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6894,13 +6889,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6908,27 +6900,44 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6936,46 +6945,33 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -7742,88 +7738,88 @@
       <c r="CD2" s="296"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="365"/>
-      <c r="B3" s="362"/>
-      <c r="C3" s="362"/>
-      <c r="D3" s="362"/>
-      <c r="E3" s="362"/>
-      <c r="F3" s="362"/>
-      <c r="G3" s="362"/>
-      <c r="H3" s="362"/>
-      <c r="I3" s="362"/>
-      <c r="J3" s="362"/>
-      <c r="K3" s="362"/>
-      <c r="L3" s="362"/>
-      <c r="M3" s="362"/>
-      <c r="N3" s="362"/>
-      <c r="O3" s="362"/>
-      <c r="P3" s="362"/>
-      <c r="Q3" s="362"/>
-      <c r="R3" s="362"/>
-      <c r="S3" s="362"/>
-      <c r="T3" s="362"/>
-      <c r="U3" s="362"/>
-      <c r="V3" s="362"/>
-      <c r="W3" s="362"/>
-      <c r="X3" s="362"/>
-      <c r="Y3" s="362"/>
-      <c r="Z3" s="362"/>
-      <c r="AA3" s="362"/>
-      <c r="AB3" s="362"/>
-      <c r="AC3" s="362"/>
-      <c r="AD3" s="362"/>
-      <c r="AE3" s="362"/>
-      <c r="AF3" s="362"/>
-      <c r="AG3" s="362"/>
-      <c r="AH3" s="362"/>
-      <c r="AI3" s="362"/>
-      <c r="AJ3" s="362"/>
-      <c r="AK3" s="362"/>
-      <c r="AL3" s="362"/>
-      <c r="AM3" s="362"/>
-      <c r="AN3" s="362"/>
-      <c r="AO3" s="362"/>
-      <c r="AP3" s="362"/>
-      <c r="AQ3" s="362"/>
-      <c r="AR3" s="362"/>
-      <c r="AS3" s="362"/>
-      <c r="AT3" s="362"/>
-      <c r="AU3" s="362"/>
-      <c r="AV3" s="362"/>
-      <c r="AW3" s="362"/>
-      <c r="AX3" s="362"/>
-      <c r="AY3" s="362"/>
-      <c r="AZ3" s="362"/>
-      <c r="BA3" s="362"/>
-      <c r="BB3" s="362"/>
-      <c r="BC3" s="362"/>
-      <c r="BD3" s="362"/>
-      <c r="BE3" s="362"/>
-      <c r="BF3" s="362"/>
-      <c r="BG3" s="362"/>
-      <c r="BH3" s="362"/>
-      <c r="BI3" s="362"/>
-      <c r="BJ3" s="362"/>
-      <c r="BK3" s="362"/>
-      <c r="BL3" s="362"/>
-      <c r="BM3" s="362"/>
-      <c r="BN3" s="362"/>
-      <c r="BO3" s="362"/>
-      <c r="BP3" s="362"/>
-      <c r="BQ3" s="362"/>
-      <c r="BR3" s="362"/>
-      <c r="BS3" s="362"/>
-      <c r="BT3" s="362"/>
-      <c r="BU3" s="362"/>
+      <c r="A3" s="361"/>
+      <c r="B3" s="360"/>
+      <c r="C3" s="360"/>
+      <c r="D3" s="360"/>
+      <c r="E3" s="360"/>
+      <c r="F3" s="360"/>
+      <c r="G3" s="360"/>
+      <c r="H3" s="360"/>
+      <c r="I3" s="360"/>
+      <c r="J3" s="360"/>
+      <c r="K3" s="360"/>
+      <c r="L3" s="360"/>
+      <c r="M3" s="360"/>
+      <c r="N3" s="360"/>
+      <c r="O3" s="360"/>
+      <c r="P3" s="360"/>
+      <c r="Q3" s="360"/>
+      <c r="R3" s="360"/>
+      <c r="S3" s="360"/>
+      <c r="T3" s="360"/>
+      <c r="U3" s="360"/>
+      <c r="V3" s="360"/>
+      <c r="W3" s="360"/>
+      <c r="X3" s="360"/>
+      <c r="Y3" s="360"/>
+      <c r="Z3" s="360"/>
+      <c r="AA3" s="360"/>
+      <c r="AB3" s="360"/>
+      <c r="AC3" s="360"/>
+      <c r="AD3" s="360"/>
+      <c r="AE3" s="360"/>
+      <c r="AF3" s="360"/>
+      <c r="AG3" s="360"/>
+      <c r="AH3" s="360"/>
+      <c r="AI3" s="360"/>
+      <c r="AJ3" s="360"/>
+      <c r="AK3" s="360"/>
+      <c r="AL3" s="360"/>
+      <c r="AM3" s="360"/>
+      <c r="AN3" s="360"/>
+      <c r="AO3" s="360"/>
+      <c r="AP3" s="360"/>
+      <c r="AQ3" s="360"/>
+      <c r="AR3" s="360"/>
+      <c r="AS3" s="360"/>
+      <c r="AT3" s="360"/>
+      <c r="AU3" s="360"/>
+      <c r="AV3" s="360"/>
+      <c r="AW3" s="360"/>
+      <c r="AX3" s="360"/>
+      <c r="AY3" s="360"/>
+      <c r="AZ3" s="360"/>
+      <c r="BA3" s="360"/>
+      <c r="BB3" s="360"/>
+      <c r="BC3" s="360"/>
+      <c r="BD3" s="360"/>
+      <c r="BE3" s="360"/>
+      <c r="BF3" s="360"/>
+      <c r="BG3" s="360"/>
+      <c r="BH3" s="360"/>
+      <c r="BI3" s="360"/>
+      <c r="BJ3" s="360"/>
+      <c r="BK3" s="360"/>
+      <c r="BL3" s="360"/>
+      <c r="BM3" s="360"/>
+      <c r="BN3" s="360"/>
+      <c r="BO3" s="360"/>
+      <c r="BP3" s="360"/>
+      <c r="BQ3" s="360"/>
+      <c r="BR3" s="360"/>
+      <c r="BS3" s="360"/>
+      <c r="BT3" s="360"/>
+      <c r="BU3" s="360"/>
       <c r="BV3" s="298"/>
-      <c r="BW3" s="361" t="s">
+      <c r="BW3" s="359" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="362"/>
-      <c r="BY3" s="362"/>
-      <c r="BZ3" s="362"/>
-      <c r="CA3" s="362"/>
-      <c r="CB3" s="362"/>
+      <c r="BX3" s="360"/>
+      <c r="BY3" s="360"/>
+      <c r="BZ3" s="360"/>
+      <c r="CA3" s="360"/>
+      <c r="CB3" s="360"/>
       <c r="CC3" s="300"/>
       <c r="CD3" s="300"/>
     </row>
@@ -7901,12 +7897,12 @@
       <c r="BT4" s="301"/>
       <c r="BU4" s="301"/>
       <c r="BV4" s="301"/>
-      <c r="BW4" s="362"/>
-      <c r="BX4" s="362"/>
-      <c r="BY4" s="362"/>
-      <c r="BZ4" s="362"/>
-      <c r="CA4" s="362"/>
-      <c r="CB4" s="362"/>
+      <c r="BW4" s="360"/>
+      <c r="BX4" s="360"/>
+      <c r="BY4" s="360"/>
+      <c r="BZ4" s="360"/>
+      <c r="CA4" s="360"/>
+      <c r="CB4" s="360"/>
       <c r="CC4" s="300"/>
       <c r="CD4" s="300"/>
     </row>
@@ -7984,12 +7980,12 @@
       <c r="BT5" s="301"/>
       <c r="BU5" s="301"/>
       <c r="BV5" s="301"/>
-      <c r="BW5" s="362"/>
-      <c r="BX5" s="362"/>
-      <c r="BY5" s="362"/>
-      <c r="BZ5" s="362"/>
-      <c r="CA5" s="362"/>
-      <c r="CB5" s="362"/>
+      <c r="BW5" s="360"/>
+      <c r="BX5" s="360"/>
+      <c r="BY5" s="360"/>
+      <c r="BZ5" s="360"/>
+      <c r="CA5" s="360"/>
+      <c r="CB5" s="360"/>
       <c r="CC5" s="300"/>
       <c r="CD5" s="300"/>
     </row>
@@ -8065,12 +8061,12 @@
       <c r="BT6" s="303"/>
       <c r="BU6" s="303"/>
       <c r="BV6" s="303"/>
-      <c r="BW6" s="362"/>
-      <c r="BX6" s="362"/>
-      <c r="BY6" s="362"/>
-      <c r="BZ6" s="362"/>
-      <c r="CA6" s="362"/>
-      <c r="CB6" s="362"/>
+      <c r="BW6" s="360"/>
+      <c r="BX6" s="360"/>
+      <c r="BY6" s="360"/>
+      <c r="BZ6" s="360"/>
+      <c r="CA6" s="360"/>
+      <c r="CB6" s="360"/>
       <c r="CC6" s="300"/>
       <c r="CD6" s="300"/>
     </row>
@@ -8142,7 +8138,7 @@
         <v>158</v>
       </c>
       <c r="AM7" s="303" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AN7" s="303" t="s">
         <v>158</v>
@@ -8210,356 +8206,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="333" t="s">
+      <c r="A8" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="367" t="s">
+      <c r="B8" s="363" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="345" t="s">
+      <c r="C8" s="333" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="349" t="s">
+      <c r="D8" s="351" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="349" t="s">
+      <c r="E8" s="351" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="345" t="s">
+      <c r="F8" s="333" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="368" t="s">
+      <c r="G8" s="352" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="354" t="s">
+      <c r="H8" s="330" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="354" t="s">
+      <c r="I8" s="330" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="354" t="s">
+      <c r="J8" s="330" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="355" t="s">
+      <c r="K8" s="364" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="356"/>
-      <c r="M8" s="356"/>
-      <c r="N8" s="356"/>
-      <c r="O8" s="356"/>
-      <c r="P8" s="356"/>
-      <c r="Q8" s="356"/>
-      <c r="R8" s="356"/>
-      <c r="S8" s="356"/>
-      <c r="T8" s="356"/>
-      <c r="U8" s="356"/>
-      <c r="V8" s="356"/>
-      <c r="W8" s="356"/>
-      <c r="X8" s="356"/>
-      <c r="Y8" s="360" t="s">
+      <c r="L8" s="365"/>
+      <c r="M8" s="365"/>
+      <c r="N8" s="365"/>
+      <c r="O8" s="365"/>
+      <c r="P8" s="365"/>
+      <c r="Q8" s="365"/>
+      <c r="R8" s="365"/>
+      <c r="S8" s="365"/>
+      <c r="T8" s="365"/>
+      <c r="U8" s="365"/>
+      <c r="V8" s="365"/>
+      <c r="W8" s="365"/>
+      <c r="X8" s="365"/>
+      <c r="Y8" s="368" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="356"/>
-      <c r="AA8" s="356"/>
-      <c r="AB8" s="356"/>
-      <c r="AC8" s="356"/>
-      <c r="AD8" s="356"/>
-      <c r="AE8" s="356"/>
-      <c r="AF8" s="356"/>
-      <c r="AG8" s="356"/>
-      <c r="AH8" s="356"/>
-      <c r="AI8" s="356"/>
-      <c r="AJ8" s="356"/>
-      <c r="AK8" s="356"/>
-      <c r="AL8" s="356"/>
-      <c r="AM8" s="356"/>
-      <c r="AN8" s="356"/>
-      <c r="AO8" s="358"/>
-      <c r="AP8" s="354" t="s">
+      <c r="Z8" s="365"/>
+      <c r="AA8" s="365"/>
+      <c r="AB8" s="365"/>
+      <c r="AC8" s="365"/>
+      <c r="AD8" s="365"/>
+      <c r="AE8" s="365"/>
+      <c r="AF8" s="365"/>
+      <c r="AG8" s="365"/>
+      <c r="AH8" s="365"/>
+      <c r="AI8" s="365"/>
+      <c r="AJ8" s="365"/>
+      <c r="AK8" s="365"/>
+      <c r="AL8" s="365"/>
+      <c r="AM8" s="365"/>
+      <c r="AN8" s="365"/>
+      <c r="AO8" s="367"/>
+      <c r="AP8" s="330" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="354" t="s">
+      <c r="AQ8" s="330" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="354" t="s">
+      <c r="AR8" s="330" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="354" t="s">
+      <c r="AS8" s="330" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="354" t="s">
+      <c r="AT8" s="330" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="354" t="s">
+      <c r="AU8" s="330" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="345" t="s">
+      <c r="AV8" s="333" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="359" t="s">
+      <c r="AW8" s="342" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="359" t="s">
+      <c r="AX8" s="342" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="357" t="s">
+      <c r="AY8" s="366" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="356"/>
-      <c r="BA8" s="356"/>
-      <c r="BB8" s="356"/>
-      <c r="BC8" s="356"/>
-      <c r="BD8" s="356"/>
-      <c r="BE8" s="356"/>
-      <c r="BF8" s="356"/>
-      <c r="BG8" s="356"/>
-      <c r="BH8" s="356"/>
-      <c r="BI8" s="356"/>
-      <c r="BJ8" s="356"/>
-      <c r="BK8" s="356"/>
-      <c r="BL8" s="356"/>
-      <c r="BM8" s="356"/>
-      <c r="BN8" s="356"/>
-      <c r="BO8" s="356"/>
-      <c r="BP8" s="356"/>
-      <c r="BQ8" s="358"/>
-      <c r="BR8" s="376" t="s">
+      <c r="AZ8" s="365"/>
+      <c r="BA8" s="365"/>
+      <c r="BB8" s="365"/>
+      <c r="BC8" s="365"/>
+      <c r="BD8" s="365"/>
+      <c r="BE8" s="365"/>
+      <c r="BF8" s="365"/>
+      <c r="BG8" s="365"/>
+      <c r="BH8" s="365"/>
+      <c r="BI8" s="365"/>
+      <c r="BJ8" s="365"/>
+      <c r="BK8" s="365"/>
+      <c r="BL8" s="365"/>
+      <c r="BM8" s="365"/>
+      <c r="BN8" s="365"/>
+      <c r="BO8" s="365"/>
+      <c r="BP8" s="365"/>
+      <c r="BQ8" s="367"/>
+      <c r="BR8" s="343" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="373"/>
-      <c r="BT8" s="345" t="s">
+      <c r="BS8" s="344"/>
+      <c r="BT8" s="333" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="369" t="s">
+      <c r="BU8" s="339" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="22"/>
-      <c r="BW8" s="346" t="s">
+      <c r="BW8" s="379" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="336" t="s">
+      <c r="BX8" s="370" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="337"/>
-      <c r="BZ8" s="337"/>
-      <c r="CA8" s="338"/>
-      <c r="CB8" s="377" t="s">
+      <c r="BY8" s="371"/>
+      <c r="BZ8" s="371"/>
+      <c r="CA8" s="372"/>
+      <c r="CB8" s="345" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="363" t="s">
+      <c r="CC8" s="337" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="363" t="s">
+      <c r="CD8" s="337" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="334"/>
-      <c r="B9" s="331"/>
-      <c r="C9" s="331"/>
-      <c r="D9" s="331"/>
-      <c r="E9" s="331"/>
-      <c r="F9" s="331"/>
-      <c r="G9" s="331"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="352" t="s">
+      <c r="A9" s="331"/>
+      <c r="B9" s="334"/>
+      <c r="C9" s="334"/>
+      <c r="D9" s="334"/>
+      <c r="E9" s="334"/>
+      <c r="F9" s="334"/>
+      <c r="G9" s="334"/>
+      <c r="H9" s="331"/>
+      <c r="I9" s="331"/>
+      <c r="J9" s="331"/>
+      <c r="K9" s="350" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="352" t="s">
+      <c r="L9" s="350" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="352" t="s">
+      <c r="M9" s="350" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="352" t="s">
+      <c r="N9" s="350" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="352" t="s">
+      <c r="O9" s="350" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="352" t="s">
+      <c r="P9" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="352" t="s">
+      <c r="Q9" s="350" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="352" t="s">
+      <c r="R9" s="350" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="352" t="s">
+      <c r="S9" s="350" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="352" t="s">
+      <c r="T9" s="350" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="352" t="s">
+      <c r="U9" s="350" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="372" t="s">
+      <c r="V9" s="355" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="373"/>
-      <c r="X9" s="352" t="s">
+      <c r="W9" s="344"/>
+      <c r="X9" s="350" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="330" t="s">
+      <c r="Y9" s="336" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="330" t="s">
+      <c r="Z9" s="336" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="330" t="s">
+      <c r="AA9" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="330" t="s">
+      <c r="AB9" s="336" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="330" t="s">
+      <c r="AC9" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="330" t="s">
+      <c r="AD9" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="330" t="s">
+      <c r="AE9" s="336" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="330" t="s">
+      <c r="AF9" s="336" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="330" t="s">
+      <c r="AG9" s="336" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="330" t="s">
+      <c r="AH9" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="330" t="s">
+      <c r="AI9" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="330" t="s">
+      <c r="AJ9" s="336" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="369" t="s">
+      <c r="AK9" s="339" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="345" t="s">
+      <c r="AL9" s="333" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="330" t="s">
+      <c r="AM9" s="336" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="345" t="s">
+      <c r="AN9" s="333" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="345" t="s">
+      <c r="AO9" s="333" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="334"/>
-      <c r="AQ9" s="334"/>
-      <c r="AR9" s="334"/>
-      <c r="AS9" s="334"/>
-      <c r="AT9" s="334"/>
-      <c r="AU9" s="334"/>
-      <c r="AV9" s="331"/>
-      <c r="AW9" s="334"/>
-      <c r="AX9" s="334"/>
-      <c r="AY9" s="379" t="s">
+      <c r="AP9" s="331"/>
+      <c r="AQ9" s="331"/>
+      <c r="AR9" s="331"/>
+      <c r="AS9" s="331"/>
+      <c r="AT9" s="331"/>
+      <c r="AU9" s="331"/>
+      <c r="AV9" s="334"/>
+      <c r="AW9" s="331"/>
+      <c r="AX9" s="331"/>
+      <c r="AY9" s="347" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="380"/>
-      <c r="BA9" s="380"/>
-      <c r="BB9" s="380"/>
-      <c r="BC9" s="380"/>
-      <c r="BD9" s="380"/>
-      <c r="BE9" s="380"/>
-      <c r="BF9" s="380"/>
-      <c r="BG9" s="380"/>
-      <c r="BH9" s="380"/>
-      <c r="BI9" s="380"/>
-      <c r="BJ9" s="380"/>
-      <c r="BK9" s="380"/>
-      <c r="BL9" s="381"/>
-      <c r="BM9" s="379" t="s">
+      <c r="AZ9" s="348"/>
+      <c r="BA9" s="348"/>
+      <c r="BB9" s="348"/>
+      <c r="BC9" s="348"/>
+      <c r="BD9" s="348"/>
+      <c r="BE9" s="348"/>
+      <c r="BF9" s="348"/>
+      <c r="BG9" s="348"/>
+      <c r="BH9" s="348"/>
+      <c r="BI9" s="348"/>
+      <c r="BJ9" s="348"/>
+      <c r="BK9" s="348"/>
+      <c r="BL9" s="349"/>
+      <c r="BM9" s="347" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="380"/>
-      <c r="BO9" s="380"/>
-      <c r="BP9" s="380"/>
-      <c r="BQ9" s="381"/>
+      <c r="BN9" s="348"/>
+      <c r="BO9" s="348"/>
+      <c r="BP9" s="348"/>
+      <c r="BQ9" s="349"/>
       <c r="BR9" s="353" t="s">
         <v>65</v>
       </c>
       <c r="BS9" s="353" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="331"/>
-      <c r="BU9" s="370"/>
+      <c r="BT9" s="334"/>
+      <c r="BU9" s="340"/>
       <c r="BV9" s="22"/>
-      <c r="BW9" s="347"/>
-      <c r="BX9" s="339"/>
-      <c r="BY9" s="340"/>
-      <c r="BZ9" s="340"/>
-      <c r="CA9" s="341"/>
-      <c r="CB9" s="331"/>
-      <c r="CC9" s="334"/>
-      <c r="CD9" s="334"/>
+      <c r="BW9" s="380"/>
+      <c r="BX9" s="373"/>
+      <c r="BY9" s="374"/>
+      <c r="BZ9" s="374"/>
+      <c r="CA9" s="375"/>
+      <c r="CB9" s="334"/>
+      <c r="CC9" s="331"/>
+      <c r="CD9" s="331"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="307" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="334"/>
-      <c r="B10" s="331"/>
-      <c r="C10" s="331"/>
-      <c r="D10" s="331"/>
-      <c r="E10" s="331"/>
-      <c r="F10" s="331"/>
-      <c r="G10" s="331"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
-      <c r="N10" s="334"/>
-      <c r="O10" s="334"/>
-      <c r="P10" s="334"/>
-      <c r="Q10" s="334"/>
-      <c r="R10" s="334"/>
-      <c r="S10" s="334"/>
-      <c r="T10" s="334"/>
-      <c r="U10" s="334"/>
-      <c r="V10" s="374"/>
-      <c r="W10" s="375"/>
-      <c r="X10" s="334"/>
-      <c r="Y10" s="331"/>
-      <c r="Z10" s="331"/>
-      <c r="AA10" s="331"/>
-      <c r="AB10" s="331"/>
-      <c r="AC10" s="331"/>
-      <c r="AD10" s="331"/>
-      <c r="AE10" s="331"/>
-      <c r="AF10" s="331"/>
-      <c r="AG10" s="331"/>
-      <c r="AH10" s="331"/>
-      <c r="AI10" s="331"/>
-      <c r="AJ10" s="331"/>
-      <c r="AK10" s="370"/>
-      <c r="AL10" s="331"/>
-      <c r="AM10" s="331"/>
-      <c r="AN10" s="331"/>
-      <c r="AO10" s="331"/>
-      <c r="AP10" s="334"/>
-      <c r="AQ10" s="334"/>
-      <c r="AR10" s="334"/>
-      <c r="AS10" s="334"/>
-      <c r="AT10" s="334"/>
-      <c r="AU10" s="334"/>
-      <c r="AV10" s="331"/>
-      <c r="AW10" s="334"/>
-      <c r="AX10" s="334"/>
+      <c r="A10" s="331"/>
+      <c r="B10" s="334"/>
+      <c r="C10" s="334"/>
+      <c r="D10" s="334"/>
+      <c r="E10" s="334"/>
+      <c r="F10" s="334"/>
+      <c r="G10" s="334"/>
+      <c r="H10" s="331"/>
+      <c r="I10" s="331"/>
+      <c r="J10" s="331"/>
+      <c r="K10" s="331"/>
+      <c r="L10" s="331"/>
+      <c r="M10" s="331"/>
+      <c r="N10" s="331"/>
+      <c r="O10" s="331"/>
+      <c r="P10" s="331"/>
+      <c r="Q10" s="331"/>
+      <c r="R10" s="331"/>
+      <c r="S10" s="331"/>
+      <c r="T10" s="331"/>
+      <c r="U10" s="331"/>
+      <c r="V10" s="356"/>
+      <c r="W10" s="357"/>
+      <c r="X10" s="331"/>
+      <c r="Y10" s="334"/>
+      <c r="Z10" s="334"/>
+      <c r="AA10" s="334"/>
+      <c r="AB10" s="334"/>
+      <c r="AC10" s="334"/>
+      <c r="AD10" s="334"/>
+      <c r="AE10" s="334"/>
+      <c r="AF10" s="334"/>
+      <c r="AG10" s="334"/>
+      <c r="AH10" s="334"/>
+      <c r="AI10" s="334"/>
+      <c r="AJ10" s="334"/>
+      <c r="AK10" s="340"/>
+      <c r="AL10" s="334"/>
+      <c r="AM10" s="334"/>
+      <c r="AN10" s="334"/>
+      <c r="AO10" s="334"/>
+      <c r="AP10" s="331"/>
+      <c r="AQ10" s="331"/>
+      <c r="AR10" s="331"/>
+      <c r="AS10" s="331"/>
+      <c r="AT10" s="331"/>
+      <c r="AU10" s="331"/>
+      <c r="AV10" s="334"/>
+      <c r="AW10" s="331"/>
+      <c r="AX10" s="331"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8569,67 +8565,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="366" t="s">
+      <c r="BB10" s="362" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="351" t="s">
+      <c r="BC10" s="354" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="351" t="s">
+      <c r="BD10" s="354" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="350" t="s">
+      <c r="BE10" s="358" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="350" t="s">
+      <c r="BF10" s="358" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="351" t="s">
+      <c r="BG10" s="354" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="351" t="s">
+      <c r="BH10" s="354" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="350" t="s">
+      <c r="BI10" s="358" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="350" t="s">
+      <c r="BJ10" s="358" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="350" t="s">
+      <c r="BK10" s="358" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="345" t="s">
+      <c r="BL10" s="333" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="351" t="s">
+      <c r="BM10" s="354" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="359" t="s">
+      <c r="BN10" s="342" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="351" t="s">
+      <c r="BO10" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="359" t="s">
+      <c r="BP10" s="342" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="359" t="s">
+      <c r="BQ10" s="342" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="334"/>
-      <c r="BS10" s="334"/>
-      <c r="BT10" s="331"/>
-      <c r="BU10" s="370"/>
+      <c r="BR10" s="331"/>
+      <c r="BS10" s="331"/>
+      <c r="BT10" s="334"/>
+      <c r="BU10" s="340"/>
       <c r="BV10" s="22"/>
-      <c r="BW10" s="347"/>
-      <c r="BX10" s="342"/>
-      <c r="BY10" s="343"/>
-      <c r="BZ10" s="343"/>
-      <c r="CA10" s="344"/>
-      <c r="CB10" s="331"/>
-      <c r="CC10" s="334"/>
-      <c r="CD10" s="334"/>
+      <c r="BW10" s="380"/>
+      <c r="BX10" s="376"/>
+      <c r="BY10" s="377"/>
+      <c r="BZ10" s="377"/>
+      <c r="CA10" s="378"/>
+      <c r="CB10" s="334"/>
+      <c r="CC10" s="331"/>
+      <c r="CD10" s="331"/>
       <c r="CE10" s="321" t="s">
         <v>3</v>
       </c>
@@ -8637,60 +8633,60 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="307" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="335"/>
-      <c r="B11" s="332"/>
-      <c r="C11" s="332"/>
-      <c r="D11" s="332"/>
-      <c r="E11" s="332"/>
-      <c r="F11" s="332"/>
-      <c r="G11" s="332"/>
-      <c r="H11" s="335"/>
-      <c r="I11" s="335"/>
-      <c r="J11" s="335"/>
-      <c r="K11" s="335"/>
-      <c r="L11" s="335"/>
-      <c r="M11" s="335"/>
-      <c r="N11" s="335"/>
-      <c r="O11" s="335"/>
-      <c r="P11" s="335"/>
-      <c r="Q11" s="335"/>
-      <c r="R11" s="335"/>
-      <c r="S11" s="335"/>
-      <c r="T11" s="335"/>
-      <c r="U11" s="335"/>
+      <c r="A11" s="332"/>
+      <c r="B11" s="335"/>
+      <c r="C11" s="335"/>
+      <c r="D11" s="335"/>
+      <c r="E11" s="335"/>
+      <c r="F11" s="335"/>
+      <c r="G11" s="335"/>
+      <c r="H11" s="332"/>
+      <c r="I11" s="332"/>
+      <c r="J11" s="332"/>
+      <c r="K11" s="332"/>
+      <c r="L11" s="332"/>
+      <c r="M11" s="332"/>
+      <c r="N11" s="332"/>
+      <c r="O11" s="332"/>
+      <c r="P11" s="332"/>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
       <c r="V11" s="269" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="269" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="335"/>
-      <c r="Y11" s="332"/>
-      <c r="Z11" s="332"/>
-      <c r="AA11" s="332"/>
-      <c r="AB11" s="332"/>
-      <c r="AC11" s="332"/>
-      <c r="AD11" s="332"/>
-      <c r="AE11" s="332"/>
-      <c r="AF11" s="332"/>
-      <c r="AG11" s="332"/>
-      <c r="AH11" s="332"/>
-      <c r="AI11" s="332"/>
-      <c r="AJ11" s="332"/>
-      <c r="AK11" s="371"/>
-      <c r="AL11" s="332"/>
-      <c r="AM11" s="332"/>
-      <c r="AN11" s="332"/>
-      <c r="AO11" s="332"/>
-      <c r="AP11" s="335"/>
-      <c r="AQ11" s="335"/>
-      <c r="AR11" s="335"/>
-      <c r="AS11" s="335"/>
-      <c r="AT11" s="335"/>
-      <c r="AU11" s="335"/>
-      <c r="AV11" s="332"/>
-      <c r="AW11" s="335"/>
-      <c r="AX11" s="335"/>
+      <c r="X11" s="332"/>
+      <c r="Y11" s="335"/>
+      <c r="Z11" s="335"/>
+      <c r="AA11" s="335"/>
+      <c r="AB11" s="335"/>
+      <c r="AC11" s="335"/>
+      <c r="AD11" s="335"/>
+      <c r="AE11" s="335"/>
+      <c r="AF11" s="335"/>
+      <c r="AG11" s="335"/>
+      <c r="AH11" s="335"/>
+      <c r="AI11" s="335"/>
+      <c r="AJ11" s="335"/>
+      <c r="AK11" s="341"/>
+      <c r="AL11" s="335"/>
+      <c r="AM11" s="335"/>
+      <c r="AN11" s="335"/>
+      <c r="AO11" s="335"/>
+      <c r="AP11" s="332"/>
+      <c r="AQ11" s="332"/>
+      <c r="AR11" s="332"/>
+      <c r="AS11" s="332"/>
+      <c r="AT11" s="332"/>
+      <c r="AU11" s="332"/>
+      <c r="AV11" s="335"/>
+      <c r="AW11" s="332"/>
+      <c r="AX11" s="332"/>
       <c r="AY11" s="322" t="s">
         <v>88</v>
       </c>
@@ -8700,28 +8696,28 @@
       <c r="BA11" s="322" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="332"/>
-      <c r="BC11" s="335"/>
-      <c r="BD11" s="335"/>
-      <c r="BE11" s="332"/>
-      <c r="BF11" s="332"/>
-      <c r="BG11" s="335"/>
-      <c r="BH11" s="335"/>
-      <c r="BI11" s="332"/>
-      <c r="BJ11" s="332"/>
-      <c r="BK11" s="332"/>
-      <c r="BL11" s="332"/>
-      <c r="BM11" s="335"/>
-      <c r="BN11" s="335"/>
-      <c r="BO11" s="335"/>
-      <c r="BP11" s="335"/>
-      <c r="BQ11" s="335"/>
-      <c r="BR11" s="335"/>
-      <c r="BS11" s="335"/>
-      <c r="BT11" s="332"/>
-      <c r="BU11" s="371"/>
+      <c r="BB11" s="335"/>
+      <c r="BC11" s="332"/>
+      <c r="BD11" s="332"/>
+      <c r="BE11" s="335"/>
+      <c r="BF11" s="335"/>
+      <c r="BG11" s="332"/>
+      <c r="BH11" s="332"/>
+      <c r="BI11" s="335"/>
+      <c r="BJ11" s="335"/>
+      <c r="BK11" s="335"/>
+      <c r="BL11" s="335"/>
+      <c r="BM11" s="332"/>
+      <c r="BN11" s="332"/>
+      <c r="BO11" s="332"/>
+      <c r="BP11" s="332"/>
+      <c r="BQ11" s="332"/>
+      <c r="BR11" s="332"/>
+      <c r="BS11" s="332"/>
+      <c r="BT11" s="335"/>
+      <c r="BU11" s="341"/>
       <c r="BV11" s="22"/>
-      <c r="BW11" s="348"/>
+      <c r="BW11" s="381"/>
       <c r="BX11" s="270" t="s">
         <v>91</v>
       </c>
@@ -8734,9 +8730,9 @@
       <c r="CA11" s="271" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="378"/>
-      <c r="CC11" s="364"/>
-      <c r="CD11" s="364"/>
+      <c r="CB11" s="346"/>
+      <c r="CC11" s="338"/>
+      <c r="CD11" s="338"/>
       <c r="CE11" s="320">
         <v>26</v>
       </c>
@@ -9570,7 +9566,7 @@
       <c r="BQ15" s="280"/>
       <c r="BR15" s="280"/>
       <c r="BS15" s="280"/>
-      <c r="BT15" s="435">
+      <c r="BT15" s="263">
         <v>25846153.846153852</v>
       </c>
       <c r="BU15" s="282">
@@ -9779,7 +9775,7 @@
         <f t="shared" si="26"/>
         <v>84800</v>
       </c>
-      <c r="BF16" s="434">
+      <c r="BF16" s="250">
         <f t="shared" ref="BF16:BF21" si="34">AM16+IF(E16="CT",IF(AR16&gt;=730000,730000,AR16),0)+IF(((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16)&gt;0,((AV16-AM16-IF(AR16&gt;=730000,730000,AR16)-AS16)*15%-AS16),0)</f>
         <v>7925769.230769231</v>
       </c>
@@ -9791,7 +9787,7 @@
       <c r="BI16" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ16" s="434">
+      <c r="BJ16" s="250">
         <f t="shared" ref="BJ16:BJ21" si="35">IF(E16="CT",15500000,0)</f>
         <v>15500000</v>
       </c>
@@ -10023,7 +10019,7 @@
         <f t="shared" si="26"/>
         <v>78200</v>
       </c>
-      <c r="BF17" s="434">
+      <c r="BF17" s="250">
         <f t="shared" si="34"/>
         <v>6862307.692307692</v>
       </c>
@@ -10035,7 +10031,7 @@
       <c r="BI17" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ17" s="434">
+      <c r="BJ17" s="250">
         <f t="shared" si="35"/>
         <v>15500000</v>
       </c>
@@ -10267,7 +10263,7 @@
         <f t="shared" si="26"/>
         <v>69900</v>
       </c>
-      <c r="BF18" s="434">
+      <c r="BF18" s="250">
         <f t="shared" si="34"/>
         <v>4645961.538461538</v>
       </c>
@@ -10279,7 +10275,7 @@
       <c r="BI18" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ18" s="434">
+      <c r="BJ18" s="250">
         <f t="shared" si="35"/>
         <v>15500000</v>
       </c>
@@ -10511,7 +10507,7 @@
         <f t="shared" si="26"/>
         <v>48500</v>
       </c>
-      <c r="BF19" s="434">
+      <c r="BF19" s="250">
         <f t="shared" si="34"/>
         <v>2303461.5384615385</v>
       </c>
@@ -10523,7 +10519,7 @@
       <c r="BI19" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ19" s="434">
+      <c r="BJ19" s="250">
         <f t="shared" si="35"/>
         <v>15500000</v>
       </c>
@@ -10755,7 +10751,7 @@
         <f t="shared" si="26"/>
         <v>63400</v>
       </c>
-      <c r="BF20" s="434">
+      <c r="BF20" s="250">
         <f t="shared" si="34"/>
         <v>3622500</v>
       </c>
@@ -10767,7 +10763,7 @@
       <c r="BI20" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ20" s="434">
+      <c r="BJ20" s="250">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
@@ -11001,7 +10997,7 @@
         <f t="shared" si="26"/>
         <v>63400</v>
       </c>
-      <c r="BF21" s="434">
+      <c r="BF21" s="250">
         <f t="shared" si="34"/>
         <v>3924038.4615384615</v>
       </c>
@@ -11013,7 +11009,7 @@
       <c r="BI21" s="280">
         <v>6200000</v>
       </c>
-      <c r="BJ21" s="434">
+      <c r="BJ21" s="250">
         <f t="shared" si="35"/>
         <v>15500000</v>
       </c>
@@ -11210,6 +11206,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="AV8:AV11"/>
     <mergeCell ref="F8:F11"/>
@@ -11226,72 +11288,6 @@
     <mergeCell ref="AY9:BL9"/>
     <mergeCell ref="AN9:AN11"/>
     <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11500,87 +11496,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="415"/>
-      <c r="B3" s="403"/>
-      <c r="C3" s="403"/>
-      <c r="D3" s="403"/>
-      <c r="E3" s="403"/>
-      <c r="F3" s="403"/>
-      <c r="G3" s="403"/>
-      <c r="H3" s="403"/>
-      <c r="I3" s="403"/>
-      <c r="J3" s="403"/>
-      <c r="K3" s="403"/>
-      <c r="L3" s="403"/>
-      <c r="M3" s="403"/>
-      <c r="N3" s="403"/>
-      <c r="O3" s="403"/>
-      <c r="P3" s="403"/>
-      <c r="Q3" s="403"/>
-      <c r="R3" s="403"/>
-      <c r="S3" s="403"/>
-      <c r="T3" s="403"/>
-      <c r="U3" s="403"/>
-      <c r="V3" s="403"/>
-      <c r="W3" s="403"/>
-      <c r="X3" s="403"/>
-      <c r="Y3" s="403"/>
-      <c r="Z3" s="403"/>
-      <c r="AA3" s="403"/>
-      <c r="AB3" s="403"/>
-      <c r="AC3" s="403"/>
-      <c r="AD3" s="403"/>
-      <c r="AE3" s="403"/>
-      <c r="AF3" s="403"/>
-      <c r="AG3" s="403"/>
-      <c r="AH3" s="403"/>
-      <c r="AI3" s="403"/>
-      <c r="AJ3" s="403"/>
-      <c r="AK3" s="403"/>
-      <c r="AL3" s="403"/>
-      <c r="AM3" s="403"/>
-      <c r="AN3" s="403"/>
-      <c r="AO3" s="403"/>
-      <c r="AP3" s="403"/>
-      <c r="AQ3" s="403"/>
-      <c r="AR3" s="403"/>
-      <c r="AS3" s="403"/>
-      <c r="AT3" s="403"/>
-      <c r="AU3" s="403"/>
-      <c r="AV3" s="403"/>
-      <c r="AW3" s="403"/>
-      <c r="AX3" s="403"/>
-      <c r="AY3" s="403"/>
-      <c r="AZ3" s="403"/>
-      <c r="BA3" s="403"/>
-      <c r="BB3" s="403"/>
-      <c r="BC3" s="403"/>
-      <c r="BD3" s="403"/>
-      <c r="BE3" s="403"/>
-      <c r="BF3" s="403"/>
-      <c r="BG3" s="403"/>
-      <c r="BH3" s="403"/>
-      <c r="BI3" s="403"/>
-      <c r="BJ3" s="403"/>
-      <c r="BK3" s="403"/>
-      <c r="BL3" s="403"/>
-      <c r="BM3" s="403"/>
-      <c r="BN3" s="403"/>
-      <c r="BO3" s="403"/>
-      <c r="BP3" s="403"/>
-      <c r="BQ3" s="403"/>
-      <c r="BR3" s="403"/>
-      <c r="BS3" s="403"/>
-      <c r="BT3" s="403"/>
-      <c r="BU3" s="403"/>
-      <c r="BW3" s="402" t="s">
+      <c r="A3" s="411"/>
+      <c r="B3" s="402"/>
+      <c r="C3" s="402"/>
+      <c r="D3" s="402"/>
+      <c r="E3" s="402"/>
+      <c r="F3" s="402"/>
+      <c r="G3" s="402"/>
+      <c r="H3" s="402"/>
+      <c r="I3" s="402"/>
+      <c r="J3" s="402"/>
+      <c r="K3" s="402"/>
+      <c r="L3" s="402"/>
+      <c r="M3" s="402"/>
+      <c r="N3" s="402"/>
+      <c r="O3" s="402"/>
+      <c r="P3" s="402"/>
+      <c r="Q3" s="402"/>
+      <c r="R3" s="402"/>
+      <c r="S3" s="402"/>
+      <c r="T3" s="402"/>
+      <c r="U3" s="402"/>
+      <c r="V3" s="402"/>
+      <c r="W3" s="402"/>
+      <c r="X3" s="402"/>
+      <c r="Y3" s="402"/>
+      <c r="Z3" s="402"/>
+      <c r="AA3" s="402"/>
+      <c r="AB3" s="402"/>
+      <c r="AC3" s="402"/>
+      <c r="AD3" s="402"/>
+      <c r="AE3" s="402"/>
+      <c r="AF3" s="402"/>
+      <c r="AG3" s="402"/>
+      <c r="AH3" s="402"/>
+      <c r="AI3" s="402"/>
+      <c r="AJ3" s="402"/>
+      <c r="AK3" s="402"/>
+      <c r="AL3" s="402"/>
+      <c r="AM3" s="402"/>
+      <c r="AN3" s="402"/>
+      <c r="AO3" s="402"/>
+      <c r="AP3" s="402"/>
+      <c r="AQ3" s="402"/>
+      <c r="AR3" s="402"/>
+      <c r="AS3" s="402"/>
+      <c r="AT3" s="402"/>
+      <c r="AU3" s="402"/>
+      <c r="AV3" s="402"/>
+      <c r="AW3" s="402"/>
+      <c r="AX3" s="402"/>
+      <c r="AY3" s="402"/>
+      <c r="AZ3" s="402"/>
+      <c r="BA3" s="402"/>
+      <c r="BB3" s="402"/>
+      <c r="BC3" s="402"/>
+      <c r="BD3" s="402"/>
+      <c r="BE3" s="402"/>
+      <c r="BF3" s="402"/>
+      <c r="BG3" s="402"/>
+      <c r="BH3" s="402"/>
+      <c r="BI3" s="402"/>
+      <c r="BJ3" s="402"/>
+      <c r="BK3" s="402"/>
+      <c r="BL3" s="402"/>
+      <c r="BM3" s="402"/>
+      <c r="BN3" s="402"/>
+      <c r="BO3" s="402"/>
+      <c r="BP3" s="402"/>
+      <c r="BQ3" s="402"/>
+      <c r="BR3" s="402"/>
+      <c r="BS3" s="402"/>
+      <c r="BT3" s="402"/>
+      <c r="BU3" s="402"/>
+      <c r="BW3" s="401" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="403"/>
-      <c r="BY3" s="403"/>
-      <c r="BZ3" s="403"/>
-      <c r="CA3" s="403"/>
-      <c r="CB3" s="403"/>
+      <c r="BX3" s="402"/>
+      <c r="BY3" s="402"/>
+      <c r="BZ3" s="402"/>
+      <c r="CA3" s="402"/>
+      <c r="CB3" s="402"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11663,155 +11659,155 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="403"/>
-      <c r="BX4" s="403"/>
-      <c r="BY4" s="403"/>
-      <c r="BZ4" s="403"/>
-      <c r="CA4" s="403"/>
-      <c r="CB4" s="403"/>
+      <c r="BW4" s="402"/>
+      <c r="BX4" s="402"/>
+      <c r="BY4" s="402"/>
+      <c r="BZ4" s="402"/>
+      <c r="CA4" s="402"/>
+      <c r="CB4" s="402"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="391" t="s">
+      <c r="A5" s="414" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="401" t="s">
+      <c r="B5" s="413" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="389" t="s">
+      <c r="C5" s="387" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="397" t="s">
+      <c r="D5" s="412" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="397" t="s">
+      <c r="E5" s="412" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="389" t="s">
+      <c r="F5" s="387" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="389" t="s">
+      <c r="G5" s="387" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="345" t="s">
+      <c r="H5" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="345" t="s">
+      <c r="I5" s="333" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="389" t="s">
+      <c r="J5" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="395" t="s">
+      <c r="K5" s="416" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="386"/>
-      <c r="M5" s="386"/>
-      <c r="N5" s="386"/>
-      <c r="O5" s="386"/>
-      <c r="P5" s="386"/>
-      <c r="Q5" s="386"/>
-      <c r="R5" s="386"/>
-      <c r="S5" s="386"/>
-      <c r="T5" s="386"/>
-      <c r="U5" s="386"/>
-      <c r="V5" s="386"/>
-      <c r="W5" s="386"/>
-      <c r="X5" s="386"/>
-      <c r="Y5" s="389" t="s">
+      <c r="L5" s="398"/>
+      <c r="M5" s="398"/>
+      <c r="N5" s="398"/>
+      <c r="O5" s="398"/>
+      <c r="P5" s="398"/>
+      <c r="Q5" s="398"/>
+      <c r="R5" s="398"/>
+      <c r="S5" s="398"/>
+      <c r="T5" s="398"/>
+      <c r="U5" s="398"/>
+      <c r="V5" s="398"/>
+      <c r="W5" s="398"/>
+      <c r="X5" s="398"/>
+      <c r="Y5" s="387" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="386"/>
-      <c r="AA5" s="386"/>
-      <c r="AB5" s="386"/>
-      <c r="AC5" s="386"/>
-      <c r="AD5" s="386"/>
-      <c r="AE5" s="386"/>
-      <c r="AF5" s="386"/>
-      <c r="AG5" s="386"/>
-      <c r="AH5" s="386"/>
-      <c r="AI5" s="386"/>
-      <c r="AJ5" s="386"/>
-      <c r="AK5" s="386"/>
-      <c r="AL5" s="386"/>
-      <c r="AM5" s="386"/>
-      <c r="AN5" s="386"/>
-      <c r="AO5" s="387"/>
-      <c r="AP5" s="389" t="s">
+      <c r="Z5" s="398"/>
+      <c r="AA5" s="398"/>
+      <c r="AB5" s="398"/>
+      <c r="AC5" s="398"/>
+      <c r="AD5" s="398"/>
+      <c r="AE5" s="398"/>
+      <c r="AF5" s="398"/>
+      <c r="AG5" s="398"/>
+      <c r="AH5" s="398"/>
+      <c r="AI5" s="398"/>
+      <c r="AJ5" s="398"/>
+      <c r="AK5" s="398"/>
+      <c r="AL5" s="398"/>
+      <c r="AM5" s="398"/>
+      <c r="AN5" s="398"/>
+      <c r="AO5" s="399"/>
+      <c r="AP5" s="387" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="389" t="s">
+      <c r="AQ5" s="387" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="389" t="s">
+      <c r="AR5" s="387" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="389" t="s">
+      <c r="AS5" s="387" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="389" t="s">
+      <c r="AT5" s="387" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="389" t="s">
+      <c r="AU5" s="387" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="389" t="s">
+      <c r="AV5" s="387" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="389" t="s">
+      <c r="AW5" s="387" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="389" t="s">
+      <c r="AX5" s="387" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="385" t="s">
+      <c r="AY5" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="386"/>
-      <c r="BA5" s="386"/>
-      <c r="BB5" s="386"/>
-      <c r="BC5" s="386"/>
-      <c r="BD5" s="386"/>
-      <c r="BE5" s="386"/>
-      <c r="BF5" s="386"/>
-      <c r="BG5" s="386"/>
-      <c r="BH5" s="386"/>
-      <c r="BI5" s="386"/>
-      <c r="BJ5" s="386"/>
-      <c r="BK5" s="386"/>
-      <c r="BL5" s="386"/>
-      <c r="BM5" s="386"/>
-      <c r="BN5" s="386"/>
-      <c r="BO5" s="386"/>
-      <c r="BP5" s="386"/>
-      <c r="BQ5" s="387"/>
-      <c r="BR5" s="406" t="s">
+      <c r="AZ5" s="398"/>
+      <c r="BA5" s="398"/>
+      <c r="BB5" s="398"/>
+      <c r="BC5" s="398"/>
+      <c r="BD5" s="398"/>
+      <c r="BE5" s="398"/>
+      <c r="BF5" s="398"/>
+      <c r="BG5" s="398"/>
+      <c r="BH5" s="398"/>
+      <c r="BI5" s="398"/>
+      <c r="BJ5" s="398"/>
+      <c r="BK5" s="398"/>
+      <c r="BL5" s="398"/>
+      <c r="BM5" s="398"/>
+      <c r="BN5" s="398"/>
+      <c r="BO5" s="398"/>
+      <c r="BP5" s="398"/>
+      <c r="BQ5" s="399"/>
+      <c r="BR5" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="399"/>
-      <c r="BT5" s="385" t="s">
+      <c r="BS5" s="404"/>
+      <c r="BT5" s="397" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="417" t="s">
+      <c r="BU5" s="391" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="418" t="s">
+      <c r="BW5" s="394" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="407" t="s">
+      <c r="BX5" s="405" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="408"/>
-      <c r="BZ5" s="408"/>
-      <c r="CA5" s="399"/>
-      <c r="CB5" s="419" t="s">
+      <c r="BY5" s="406"/>
+      <c r="BZ5" s="406"/>
+      <c r="CA5" s="404"/>
+      <c r="CB5" s="400" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="404" t="s">
+      <c r="CC5" s="382" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="404" t="s">
+      <c r="CD5" s="382" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
@@ -11828,95 +11824,95 @@
       <c r="H6" s="383"/>
       <c r="I6" s="383"/>
       <c r="J6" s="383"/>
-      <c r="K6" s="390" t="s">
+      <c r="K6" s="388" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="390" t="s">
+      <c r="L6" s="388" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="390" t="s">
+      <c r="M6" s="388" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="390" t="s">
+      <c r="N6" s="388" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="390" t="s">
+      <c r="O6" s="388" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="390" t="s">
+      <c r="P6" s="388" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="390" t="s">
+      <c r="Q6" s="388" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="390" t="s">
+      <c r="R6" s="388" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="390" t="s">
+      <c r="S6" s="388" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="390" t="s">
+      <c r="T6" s="388" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="390" t="s">
+      <c r="U6" s="388" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="398" t="s">
+      <c r="V6" s="418" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="399"/>
-      <c r="X6" s="390" t="s">
+      <c r="W6" s="404"/>
+      <c r="X6" s="388" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="389" t="s">
+      <c r="Y6" s="387" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="389" t="s">
+      <c r="Z6" s="387" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="389" t="s">
+      <c r="AA6" s="387" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="389" t="s">
+      <c r="AB6" s="387" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="345" t="s">
+      <c r="AC6" s="333" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="345" t="s">
+      <c r="AD6" s="333" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="345" t="s">
+      <c r="AE6" s="333" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="345" t="s">
+      <c r="AF6" s="333" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="389" t="s">
+      <c r="AG6" s="387" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="345" t="s">
+      <c r="AH6" s="333" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="345" t="s">
+      <c r="AI6" s="333" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="389" t="s">
+      <c r="AJ6" s="387" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="392" t="s">
+      <c r="AK6" s="415" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="389" t="s">
+      <c r="AL6" s="387" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="389" t="s">
+      <c r="AM6" s="387" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="396" t="s">
+      <c r="AN6" s="417" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="389" t="s">
+      <c r="AO6" s="387" t="s">
         <v>63</v>
       </c>
       <c r="AP6" s="383"/>
@@ -11928,42 +11924,42 @@
       <c r="AV6" s="383"/>
       <c r="AW6" s="383"/>
       <c r="AX6" s="383"/>
-      <c r="AY6" s="385" t="s">
+      <c r="AY6" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="386"/>
-      <c r="BA6" s="386"/>
-      <c r="BB6" s="386"/>
-      <c r="BC6" s="386"/>
-      <c r="BD6" s="386"/>
-      <c r="BE6" s="386"/>
-      <c r="BF6" s="386"/>
-      <c r="BG6" s="386"/>
-      <c r="BH6" s="386"/>
-      <c r="BI6" s="386"/>
-      <c r="BJ6" s="386"/>
-      <c r="BK6" s="386"/>
-      <c r="BL6" s="387"/>
-      <c r="BM6" s="385" t="s">
+      <c r="AZ6" s="398"/>
+      <c r="BA6" s="398"/>
+      <c r="BB6" s="398"/>
+      <c r="BC6" s="398"/>
+      <c r="BD6" s="398"/>
+      <c r="BE6" s="398"/>
+      <c r="BF6" s="398"/>
+      <c r="BG6" s="398"/>
+      <c r="BH6" s="398"/>
+      <c r="BI6" s="398"/>
+      <c r="BJ6" s="398"/>
+      <c r="BK6" s="398"/>
+      <c r="BL6" s="399"/>
+      <c r="BM6" s="397" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="386"/>
-      <c r="BO6" s="386"/>
-      <c r="BP6" s="386"/>
-      <c r="BQ6" s="387"/>
-      <c r="BR6" s="382" t="s">
+      <c r="BN6" s="398"/>
+      <c r="BO6" s="398"/>
+      <c r="BP6" s="398"/>
+      <c r="BQ6" s="399"/>
+      <c r="BR6" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="382" t="s">
+      <c r="BS6" s="385" t="s">
         <v>66</v>
       </c>
       <c r="BT6" s="383"/>
-      <c r="BU6" s="393"/>
-      <c r="BW6" s="410"/>
-      <c r="BX6" s="393"/>
-      <c r="BY6" s="409"/>
-      <c r="BZ6" s="409"/>
-      <c r="CA6" s="410"/>
+      <c r="BU6" s="392"/>
+      <c r="BW6" s="395"/>
+      <c r="BX6" s="392"/>
+      <c r="BY6" s="407"/>
+      <c r="BZ6" s="407"/>
+      <c r="CA6" s="395"/>
       <c r="CB6" s="383"/>
       <c r="CC6" s="383"/>
       <c r="CD6" s="383"/>
@@ -11992,8 +11988,8 @@
       <c r="S7" s="383"/>
       <c r="T7" s="383"/>
       <c r="U7" s="383"/>
-      <c r="V7" s="394"/>
-      <c r="W7" s="400"/>
+      <c r="V7" s="393"/>
+      <c r="W7" s="419"/>
       <c r="X7" s="383"/>
       <c r="Y7" s="383"/>
       <c r="Z7" s="383"/>
@@ -12007,7 +12003,7 @@
       <c r="AH7" s="383"/>
       <c r="AI7" s="383"/>
       <c r="AJ7" s="383"/>
-      <c r="AK7" s="393"/>
+      <c r="AK7" s="392"/>
       <c r="AL7" s="383"/>
       <c r="AM7" s="383"/>
       <c r="AN7" s="383"/>
@@ -12030,63 +12026,63 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="385" t="s">
+      <c r="BB7" s="397" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="388" t="s">
+      <c r="BC7" s="389" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="388" t="s">
+      <c r="BD7" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="414" t="s">
+      <c r="BE7" s="410" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="388" t="s">
+      <c r="BF7" s="389" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="388" t="s">
+      <c r="BG7" s="389" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="388" t="s">
+      <c r="BH7" s="389" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="388" t="s">
+      <c r="BI7" s="389" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="388" t="s">
+      <c r="BJ7" s="389" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="388" t="s">
+      <c r="BK7" s="389" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="416" t="s">
+      <c r="BL7" s="390" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="388" t="s">
+      <c r="BM7" s="389" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="385" t="s">
+      <c r="BN7" s="397" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="388" t="s">
+      <c r="BO7" s="389" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="385" t="s">
+      <c r="BP7" s="397" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="385" t="s">
+      <c r="BQ7" s="397" t="s">
         <v>85</v>
       </c>
       <c r="BR7" s="383"/>
       <c r="BS7" s="383"/>
       <c r="BT7" s="383"/>
-      <c r="BU7" s="393"/>
-      <c r="BW7" s="410"/>
-      <c r="BX7" s="411"/>
-      <c r="BY7" s="412"/>
-      <c r="BZ7" s="412"/>
-      <c r="CA7" s="413"/>
+      <c r="BU7" s="392"/>
+      <c r="BW7" s="395"/>
+      <c r="BX7" s="408"/>
+      <c r="BY7" s="409"/>
+      <c r="BZ7" s="409"/>
+      <c r="CA7" s="396"/>
       <c r="CB7" s="383"/>
       <c r="CC7" s="383"/>
       <c r="CD7" s="383"/>
@@ -12094,60 +12090,60 @@
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="384"/>
-      <c r="B8" s="384"/>
-      <c r="C8" s="384"/>
-      <c r="D8" s="384"/>
-      <c r="E8" s="384"/>
-      <c r="F8" s="384"/>
-      <c r="G8" s="384"/>
-      <c r="H8" s="384"/>
-      <c r="I8" s="384"/>
-      <c r="J8" s="384"/>
-      <c r="K8" s="384"/>
-      <c r="L8" s="384"/>
-      <c r="M8" s="384"/>
-      <c r="N8" s="384"/>
-      <c r="O8" s="384"/>
-      <c r="P8" s="384"/>
-      <c r="Q8" s="384"/>
-      <c r="R8" s="384"/>
-      <c r="S8" s="384"/>
-      <c r="T8" s="384"/>
-      <c r="U8" s="384"/>
+      <c r="A8" s="386"/>
+      <c r="B8" s="386"/>
+      <c r="C8" s="386"/>
+      <c r="D8" s="386"/>
+      <c r="E8" s="386"/>
+      <c r="F8" s="386"/>
+      <c r="G8" s="386"/>
+      <c r="H8" s="386"/>
+      <c r="I8" s="386"/>
+      <c r="J8" s="386"/>
+      <c r="K8" s="386"/>
+      <c r="L8" s="386"/>
+      <c r="M8" s="386"/>
+      <c r="N8" s="386"/>
+      <c r="O8" s="386"/>
+      <c r="P8" s="386"/>
+      <c r="Q8" s="386"/>
+      <c r="R8" s="386"/>
+      <c r="S8" s="386"/>
+      <c r="T8" s="386"/>
+      <c r="U8" s="386"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="384"/>
-      <c r="Y8" s="384"/>
-      <c r="Z8" s="384"/>
-      <c r="AA8" s="384"/>
-      <c r="AB8" s="384"/>
-      <c r="AC8" s="384"/>
-      <c r="AD8" s="384"/>
-      <c r="AE8" s="384"/>
-      <c r="AF8" s="384"/>
-      <c r="AG8" s="384"/>
-      <c r="AH8" s="384"/>
-      <c r="AI8" s="384"/>
-      <c r="AJ8" s="384"/>
-      <c r="AK8" s="394"/>
-      <c r="AL8" s="384"/>
-      <c r="AM8" s="384"/>
-      <c r="AN8" s="384"/>
-      <c r="AO8" s="384"/>
-      <c r="AP8" s="384"/>
-      <c r="AQ8" s="384"/>
-      <c r="AR8" s="384"/>
-      <c r="AS8" s="384"/>
-      <c r="AT8" s="384"/>
-      <c r="AU8" s="384"/>
-      <c r="AV8" s="384"/>
-      <c r="AW8" s="384"/>
-      <c r="AX8" s="384"/>
+      <c r="X8" s="386"/>
+      <c r="Y8" s="386"/>
+      <c r="Z8" s="386"/>
+      <c r="AA8" s="386"/>
+      <c r="AB8" s="386"/>
+      <c r="AC8" s="386"/>
+      <c r="AD8" s="386"/>
+      <c r="AE8" s="386"/>
+      <c r="AF8" s="386"/>
+      <c r="AG8" s="386"/>
+      <c r="AH8" s="386"/>
+      <c r="AI8" s="386"/>
+      <c r="AJ8" s="386"/>
+      <c r="AK8" s="393"/>
+      <c r="AL8" s="386"/>
+      <c r="AM8" s="386"/>
+      <c r="AN8" s="386"/>
+      <c r="AO8" s="386"/>
+      <c r="AP8" s="386"/>
+      <c r="AQ8" s="386"/>
+      <c r="AR8" s="386"/>
+      <c r="AS8" s="386"/>
+      <c r="AT8" s="386"/>
+      <c r="AU8" s="386"/>
+      <c r="AV8" s="386"/>
+      <c r="AW8" s="386"/>
+      <c r="AX8" s="386"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12157,27 +12153,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="384"/>
-      <c r="BC8" s="384"/>
-      <c r="BD8" s="384"/>
-      <c r="BE8" s="384"/>
-      <c r="BF8" s="384"/>
-      <c r="BG8" s="384"/>
-      <c r="BH8" s="384"/>
-      <c r="BI8" s="384"/>
-      <c r="BJ8" s="384"/>
-      <c r="BK8" s="384"/>
-      <c r="BL8" s="384"/>
-      <c r="BM8" s="384"/>
-      <c r="BN8" s="384"/>
-      <c r="BO8" s="384"/>
-      <c r="BP8" s="384"/>
-      <c r="BQ8" s="384"/>
-      <c r="BR8" s="384"/>
-      <c r="BS8" s="384"/>
-      <c r="BT8" s="384"/>
-      <c r="BU8" s="394"/>
-      <c r="BW8" s="413"/>
+      <c r="BB8" s="386"/>
+      <c r="BC8" s="386"/>
+      <c r="BD8" s="386"/>
+      <c r="BE8" s="386"/>
+      <c r="BF8" s="386"/>
+      <c r="BG8" s="386"/>
+      <c r="BH8" s="386"/>
+      <c r="BI8" s="386"/>
+      <c r="BJ8" s="386"/>
+      <c r="BK8" s="386"/>
+      <c r="BL8" s="386"/>
+      <c r="BM8" s="386"/>
+      <c r="BN8" s="386"/>
+      <c r="BO8" s="386"/>
+      <c r="BP8" s="386"/>
+      <c r="BQ8" s="386"/>
+      <c r="BR8" s="386"/>
+      <c r="BS8" s="386"/>
+      <c r="BT8" s="386"/>
+      <c r="BU8" s="393"/>
+      <c r="BW8" s="396"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12190,9 +12186,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="405"/>
-      <c r="CC8" s="405"/>
-      <c r="CD8" s="405"/>
+      <c r="CB8" s="384"/>
+      <c r="CC8" s="384"/>
+      <c r="CD8" s="384"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14650,6 +14646,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="CD5:CD8"/>
     <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="AT5:AT8"/>
@@ -14666,72 +14728,6 @@
     <mergeCell ref="AY5:BQ5"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -14959,88 +14955,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="430"/>
-      <c r="B3" s="429"/>
-      <c r="C3" s="429"/>
-      <c r="D3" s="429"/>
-      <c r="E3" s="429"/>
-      <c r="F3" s="429"/>
-      <c r="G3" s="429"/>
-      <c r="H3" s="429"/>
-      <c r="I3" s="429"/>
-      <c r="J3" s="429"/>
-      <c r="K3" s="429"/>
-      <c r="L3" s="429"/>
-      <c r="M3" s="429"/>
-      <c r="N3" s="429"/>
-      <c r="O3" s="429"/>
-      <c r="P3" s="429"/>
-      <c r="Q3" s="429"/>
-      <c r="R3" s="429"/>
-      <c r="S3" s="429"/>
-      <c r="T3" s="429"/>
-      <c r="U3" s="429"/>
-      <c r="V3" s="429"/>
-      <c r="W3" s="429"/>
-      <c r="X3" s="429"/>
-      <c r="Y3" s="429"/>
-      <c r="Z3" s="429"/>
-      <c r="AA3" s="429"/>
-      <c r="AB3" s="429"/>
-      <c r="AC3" s="429"/>
-      <c r="AD3" s="429"/>
-      <c r="AE3" s="429"/>
-      <c r="AF3" s="429"/>
-      <c r="AG3" s="429"/>
-      <c r="AH3" s="429"/>
-      <c r="AI3" s="429"/>
-      <c r="AJ3" s="429"/>
-      <c r="AK3" s="429"/>
-      <c r="AL3" s="429"/>
-      <c r="AM3" s="429"/>
-      <c r="AN3" s="429"/>
-      <c r="AO3" s="429"/>
-      <c r="AP3" s="429"/>
-      <c r="AQ3" s="429"/>
-      <c r="AR3" s="429"/>
-      <c r="AS3" s="429"/>
-      <c r="AT3" s="429"/>
-      <c r="AU3" s="429"/>
-      <c r="AV3" s="429"/>
-      <c r="AW3" s="429"/>
-      <c r="AX3" s="429"/>
-      <c r="AY3" s="429"/>
-      <c r="AZ3" s="429"/>
-      <c r="BA3" s="429"/>
-      <c r="BB3" s="429"/>
-      <c r="BC3" s="429"/>
-      <c r="BD3" s="429"/>
-      <c r="BE3" s="429"/>
-      <c r="BF3" s="429"/>
-      <c r="BG3" s="429"/>
-      <c r="BH3" s="429"/>
-      <c r="BI3" s="429"/>
-      <c r="BJ3" s="429"/>
-      <c r="BK3" s="429"/>
-      <c r="BL3" s="429"/>
-      <c r="BM3" s="429"/>
-      <c r="BN3" s="429"/>
-      <c r="BO3" s="429"/>
-      <c r="BP3" s="429"/>
-      <c r="BQ3" s="429"/>
-      <c r="BR3" s="429"/>
-      <c r="BS3" s="429"/>
-      <c r="BT3" s="429"/>
-      <c r="BU3" s="429"/>
+      <c r="A3" s="429"/>
+      <c r="B3" s="428"/>
+      <c r="C3" s="428"/>
+      <c r="D3" s="428"/>
+      <c r="E3" s="428"/>
+      <c r="F3" s="428"/>
+      <c r="G3" s="428"/>
+      <c r="H3" s="428"/>
+      <c r="I3" s="428"/>
+      <c r="J3" s="428"/>
+      <c r="K3" s="428"/>
+      <c r="L3" s="428"/>
+      <c r="M3" s="428"/>
+      <c r="N3" s="428"/>
+      <c r="O3" s="428"/>
+      <c r="P3" s="428"/>
+      <c r="Q3" s="428"/>
+      <c r="R3" s="428"/>
+      <c r="S3" s="428"/>
+      <c r="T3" s="428"/>
+      <c r="U3" s="428"/>
+      <c r="V3" s="428"/>
+      <c r="W3" s="428"/>
+      <c r="X3" s="428"/>
+      <c r="Y3" s="428"/>
+      <c r="Z3" s="428"/>
+      <c r="AA3" s="428"/>
+      <c r="AB3" s="428"/>
+      <c r="AC3" s="428"/>
+      <c r="AD3" s="428"/>
+      <c r="AE3" s="428"/>
+      <c r="AF3" s="428"/>
+      <c r="AG3" s="428"/>
+      <c r="AH3" s="428"/>
+      <c r="AI3" s="428"/>
+      <c r="AJ3" s="428"/>
+      <c r="AK3" s="428"/>
+      <c r="AL3" s="428"/>
+      <c r="AM3" s="428"/>
+      <c r="AN3" s="428"/>
+      <c r="AO3" s="428"/>
+      <c r="AP3" s="428"/>
+      <c r="AQ3" s="428"/>
+      <c r="AR3" s="428"/>
+      <c r="AS3" s="428"/>
+      <c r="AT3" s="428"/>
+      <c r="AU3" s="428"/>
+      <c r="AV3" s="428"/>
+      <c r="AW3" s="428"/>
+      <c r="AX3" s="428"/>
+      <c r="AY3" s="428"/>
+      <c r="AZ3" s="428"/>
+      <c r="BA3" s="428"/>
+      <c r="BB3" s="428"/>
+      <c r="BC3" s="428"/>
+      <c r="BD3" s="428"/>
+      <c r="BE3" s="428"/>
+      <c r="BF3" s="428"/>
+      <c r="BG3" s="428"/>
+      <c r="BH3" s="428"/>
+      <c r="BI3" s="428"/>
+      <c r="BJ3" s="428"/>
+      <c r="BK3" s="428"/>
+      <c r="BL3" s="428"/>
+      <c r="BM3" s="428"/>
+      <c r="BN3" s="428"/>
+      <c r="BO3" s="428"/>
+      <c r="BP3" s="428"/>
+      <c r="BQ3" s="428"/>
+      <c r="BR3" s="428"/>
+      <c r="BS3" s="428"/>
+      <c r="BT3" s="428"/>
+      <c r="BU3" s="428"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="428" t="s">
+      <c r="BW3" s="427" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="429"/>
-      <c r="BY3" s="429"/>
-      <c r="BZ3" s="429"/>
-      <c r="CA3" s="429"/>
-      <c r="CB3" s="429"/>
+      <c r="BX3" s="428"/>
+      <c r="BY3" s="428"/>
+      <c r="BZ3" s="428"/>
+      <c r="CA3" s="428"/>
+      <c r="CB3" s="428"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15124,12 +15120,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="429"/>
-      <c r="BX4" s="429"/>
-      <c r="BY4" s="429"/>
-      <c r="BZ4" s="429"/>
-      <c r="CA4" s="429"/>
-      <c r="CB4" s="429"/>
+      <c r="BW4" s="428"/>
+      <c r="BX4" s="428"/>
+      <c r="BY4" s="428"/>
+      <c r="BZ4" s="428"/>
+      <c r="CA4" s="428"/>
+      <c r="CB4" s="428"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15207,12 +15203,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="362"/>
-      <c r="BX5" s="362"/>
-      <c r="BY5" s="362"/>
-      <c r="BZ5" s="362"/>
-      <c r="CA5" s="362"/>
-      <c r="CB5" s="362"/>
+      <c r="BW5" s="360"/>
+      <c r="BX5" s="360"/>
+      <c r="BY5" s="360"/>
+      <c r="BZ5" s="360"/>
+      <c r="CA5" s="360"/>
+      <c r="CB5" s="360"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15290,12 +15286,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="362"/>
-      <c r="BX6" s="362"/>
-      <c r="BY6" s="362"/>
-      <c r="BZ6" s="362"/>
-      <c r="CA6" s="362"/>
-      <c r="CB6" s="362"/>
+      <c r="BW6" s="360"/>
+      <c r="BX6" s="360"/>
+      <c r="BY6" s="360"/>
+      <c r="BZ6" s="360"/>
+      <c r="CA6" s="360"/>
+      <c r="CB6" s="360"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15383,148 +15379,148 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="391" t="s">
+      <c r="A8" s="414" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="401" t="s">
+      <c r="B8" s="413" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="389" t="s">
+      <c r="C8" s="387" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="397" t="s">
+      <c r="D8" s="412" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="397" t="s">
+      <c r="E8" s="412" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="426" t="s">
+      <c r="F8" s="431" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="423" t="s">
+      <c r="G8" s="421" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="368" t="s">
+      <c r="H8" s="352" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="368" t="s">
+      <c r="I8" s="352" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="423" t="s">
+      <c r="J8" s="421" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="427" t="s">
+      <c r="K8" s="432" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="386"/>
-      <c r="M8" s="386"/>
-      <c r="N8" s="386"/>
-      <c r="O8" s="386"/>
-      <c r="P8" s="386"/>
-      <c r="Q8" s="386"/>
-      <c r="R8" s="386"/>
-      <c r="S8" s="386"/>
-      <c r="T8" s="386"/>
-      <c r="U8" s="386"/>
-      <c r="V8" s="386"/>
-      <c r="W8" s="386"/>
-      <c r="X8" s="386"/>
-      <c r="Y8" s="423" t="s">
+      <c r="L8" s="398"/>
+      <c r="M8" s="398"/>
+      <c r="N8" s="398"/>
+      <c r="O8" s="398"/>
+      <c r="P8" s="398"/>
+      <c r="Q8" s="398"/>
+      <c r="R8" s="398"/>
+      <c r="S8" s="398"/>
+      <c r="T8" s="398"/>
+      <c r="U8" s="398"/>
+      <c r="V8" s="398"/>
+      <c r="W8" s="398"/>
+      <c r="X8" s="398"/>
+      <c r="Y8" s="421" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="386"/>
-      <c r="AA8" s="386"/>
-      <c r="AB8" s="386"/>
-      <c r="AC8" s="386"/>
-      <c r="AD8" s="386"/>
-      <c r="AE8" s="386"/>
-      <c r="AF8" s="386"/>
-      <c r="AG8" s="386"/>
-      <c r="AH8" s="386"/>
-      <c r="AI8" s="386"/>
-      <c r="AJ8" s="386"/>
-      <c r="AK8" s="386"/>
-      <c r="AL8" s="386"/>
-      <c r="AM8" s="386"/>
-      <c r="AN8" s="386"/>
-      <c r="AO8" s="387"/>
-      <c r="AP8" s="423" t="s">
+      <c r="Z8" s="398"/>
+      <c r="AA8" s="398"/>
+      <c r="AB8" s="398"/>
+      <c r="AC8" s="398"/>
+      <c r="AD8" s="398"/>
+      <c r="AE8" s="398"/>
+      <c r="AF8" s="398"/>
+      <c r="AG8" s="398"/>
+      <c r="AH8" s="398"/>
+      <c r="AI8" s="398"/>
+      <c r="AJ8" s="398"/>
+      <c r="AK8" s="398"/>
+      <c r="AL8" s="398"/>
+      <c r="AM8" s="398"/>
+      <c r="AN8" s="398"/>
+      <c r="AO8" s="399"/>
+      <c r="AP8" s="421" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="423" t="s">
+      <c r="AQ8" s="421" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="423" t="s">
+      <c r="AR8" s="421" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="423" t="s">
+      <c r="AS8" s="421" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="423" t="s">
+      <c r="AT8" s="421" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="423" t="s">
+      <c r="AU8" s="421" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="389" t="s">
+      <c r="AV8" s="387" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="389" t="s">
+      <c r="AW8" s="387" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="389" t="s">
+      <c r="AX8" s="387" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="385" t="s">
+      <c r="AY8" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="386"/>
-      <c r="BA8" s="386"/>
-      <c r="BB8" s="386"/>
-      <c r="BC8" s="386"/>
-      <c r="BD8" s="386"/>
-      <c r="BE8" s="386"/>
-      <c r="BF8" s="386"/>
-      <c r="BG8" s="386"/>
-      <c r="BH8" s="386"/>
-      <c r="BI8" s="386"/>
-      <c r="BJ8" s="386"/>
-      <c r="BK8" s="386"/>
-      <c r="BL8" s="386"/>
-      <c r="BM8" s="386"/>
-      <c r="BN8" s="386"/>
-      <c r="BO8" s="386"/>
-      <c r="BP8" s="387"/>
-      <c r="BQ8" s="406" t="s">
+      <c r="AZ8" s="398"/>
+      <c r="BA8" s="398"/>
+      <c r="BB8" s="398"/>
+      <c r="BC8" s="398"/>
+      <c r="BD8" s="398"/>
+      <c r="BE8" s="398"/>
+      <c r="BF8" s="398"/>
+      <c r="BG8" s="398"/>
+      <c r="BH8" s="398"/>
+      <c r="BI8" s="398"/>
+      <c r="BJ8" s="398"/>
+      <c r="BK8" s="398"/>
+      <c r="BL8" s="398"/>
+      <c r="BM8" s="398"/>
+      <c r="BN8" s="398"/>
+      <c r="BO8" s="398"/>
+      <c r="BP8" s="399"/>
+      <c r="BQ8" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="399"/>
-      <c r="BS8" s="385" t="s">
+      <c r="BR8" s="404"/>
+      <c r="BS8" s="397" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="385" t="s">
+      <c r="BT8" s="397" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="417" t="s">
+      <c r="BU8" s="391" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="418" t="s">
+      <c r="BW8" s="394" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="407" t="s">
+      <c r="BX8" s="405" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="408"/>
-      <c r="BZ8" s="408"/>
-      <c r="CA8" s="399"/>
-      <c r="CB8" s="419" t="s">
+      <c r="BY8" s="406"/>
+      <c r="BZ8" s="406"/>
+      <c r="CA8" s="404"/>
+      <c r="CB8" s="400" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="404" t="s">
+      <c r="CC8" s="382" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="404" t="s">
+      <c r="CD8" s="382" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
@@ -15541,95 +15537,95 @@
       <c r="H9" s="383"/>
       <c r="I9" s="383"/>
       <c r="J9" s="383"/>
-      <c r="K9" s="420" t="s">
+      <c r="K9" s="423" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="420" t="s">
+      <c r="L9" s="423" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="420" t="s">
+      <c r="M9" s="423" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="420" t="s">
+      <c r="N9" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="420" t="s">
+      <c r="O9" s="423" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="420" t="s">
+      <c r="P9" s="423" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="420" t="s">
+      <c r="Q9" s="423" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="420" t="s">
+      <c r="R9" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="420" t="s">
+      <c r="S9" s="423" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="420" t="s">
+      <c r="T9" s="423" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="420" t="s">
+      <c r="U9" s="423" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="432" t="s">
+      <c r="V9" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="399"/>
-      <c r="X9" s="420" t="s">
+      <c r="W9" s="404"/>
+      <c r="X9" s="423" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="422" t="s">
+      <c r="Y9" s="420" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="422" t="s">
+      <c r="Z9" s="420" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="422" t="s">
+      <c r="AA9" s="420" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="422" t="s">
+      <c r="AB9" s="420" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="330" t="s">
+      <c r="AC9" s="336" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="330" t="s">
+      <c r="AD9" s="336" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="330" t="s">
+      <c r="AE9" s="336" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="330" t="s">
+      <c r="AF9" s="336" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="422" t="s">
+      <c r="AG9" s="420" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="330" t="s">
+      <c r="AH9" s="336" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="330" t="s">
+      <c r="AI9" s="336" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="422" t="s">
+      <c r="AJ9" s="420" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="392" t="s">
+      <c r="AK9" s="415" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="389" t="s">
+      <c r="AL9" s="387" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="422" t="s">
+      <c r="AM9" s="420" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="396" t="s">
+      <c r="AN9" s="417" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="389" t="s">
+      <c r="AO9" s="387" t="s">
         <v>63</v>
       </c>
       <c r="AP9" s="383"/>
@@ -15641,43 +15637,43 @@
       <c r="AV9" s="383"/>
       <c r="AW9" s="383"/>
       <c r="AX9" s="383"/>
-      <c r="AY9" s="385" t="s">
+      <c r="AY9" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="386"/>
-      <c r="BA9" s="386"/>
-      <c r="BB9" s="386"/>
-      <c r="BC9" s="386"/>
-      <c r="BD9" s="386"/>
-      <c r="BE9" s="386"/>
-      <c r="BF9" s="386"/>
-      <c r="BG9" s="386"/>
-      <c r="BH9" s="386"/>
-      <c r="BI9" s="386"/>
-      <c r="BJ9" s="387"/>
-      <c r="BK9" s="385" t="s">
+      <c r="AZ9" s="398"/>
+      <c r="BA9" s="398"/>
+      <c r="BB9" s="398"/>
+      <c r="BC9" s="398"/>
+      <c r="BD9" s="398"/>
+      <c r="BE9" s="398"/>
+      <c r="BF9" s="398"/>
+      <c r="BG9" s="398"/>
+      <c r="BH9" s="398"/>
+      <c r="BI9" s="398"/>
+      <c r="BJ9" s="399"/>
+      <c r="BK9" s="397" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="386"/>
-      <c r="BM9" s="386"/>
-      <c r="BN9" s="386"/>
-      <c r="BO9" s="386"/>
-      <c r="BP9" s="387"/>
-      <c r="BQ9" s="382" t="s">
+      <c r="BL9" s="398"/>
+      <c r="BM9" s="398"/>
+      <c r="BN9" s="398"/>
+      <c r="BO9" s="398"/>
+      <c r="BP9" s="399"/>
+      <c r="BQ9" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="382" t="s">
+      <c r="BR9" s="385" t="s">
         <v>66</v>
       </c>
       <c r="BS9" s="383"/>
       <c r="BT9" s="383"/>
-      <c r="BU9" s="393"/>
+      <c r="BU9" s="392"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="410"/>
-      <c r="BX9" s="393"/>
-      <c r="BY9" s="424"/>
-      <c r="BZ9" s="424"/>
-      <c r="CA9" s="410"/>
+      <c r="BW9" s="395"/>
+      <c r="BX9" s="392"/>
+      <c r="BY9" s="433"/>
+      <c r="BZ9" s="433"/>
+      <c r="CA9" s="395"/>
       <c r="CB9" s="383"/>
       <c r="CC9" s="383"/>
       <c r="CD9" s="383"/>
@@ -15706,8 +15702,8 @@
       <c r="S10" s="383"/>
       <c r="T10" s="383"/>
       <c r="U10" s="383"/>
-      <c r="V10" s="394"/>
-      <c r="W10" s="400"/>
+      <c r="V10" s="393"/>
+      <c r="W10" s="419"/>
       <c r="X10" s="383"/>
       <c r="Y10" s="383"/>
       <c r="Z10" s="383"/>
@@ -15721,7 +15717,7 @@
       <c r="AH10" s="383"/>
       <c r="AI10" s="383"/>
       <c r="AJ10" s="383"/>
-      <c r="AK10" s="393"/>
+      <c r="AK10" s="392"/>
       <c r="AL10" s="383"/>
       <c r="AM10" s="383"/>
       <c r="AN10" s="383"/>
@@ -15744,40 +15740,40 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="431" t="s">
+      <c r="BB10" s="430" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="421" t="s">
+      <c r="BC10" s="424" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="421" t="s">
+      <c r="BD10" s="424" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="421" t="s">
+      <c r="BE10" s="424" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="421" t="s">
+      <c r="BF10" s="424" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="421" t="s">
+      <c r="BG10" s="424" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="421" t="s">
+      <c r="BH10" s="424" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="421" t="s">
+      <c r="BI10" s="424" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="433" t="s">
+      <c r="BJ10" s="422" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="421" t="s">
+      <c r="BK10" s="424" t="s">
         <v>81</v>
       </c>
       <c r="BL10" s="425" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="421" t="s">
+      <c r="BM10" s="424" t="s">
         <v>83</v>
       </c>
       <c r="BN10" s="425" t="s">
@@ -15786,20 +15782,20 @@
       <c r="BO10" s="425" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="385" t="s">
+      <c r="BP10" s="397" t="s">
         <v>85</v>
       </c>
       <c r="BQ10" s="383"/>
       <c r="BR10" s="383"/>
       <c r="BS10" s="383"/>
       <c r="BT10" s="383"/>
-      <c r="BU10" s="393"/>
+      <c r="BU10" s="392"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="410"/>
-      <c r="BX10" s="411"/>
-      <c r="BY10" s="412"/>
-      <c r="BZ10" s="412"/>
-      <c r="CA10" s="413"/>
+      <c r="BW10" s="395"/>
+      <c r="BX10" s="408"/>
+      <c r="BY10" s="409"/>
+      <c r="BZ10" s="409"/>
+      <c r="CA10" s="396"/>
       <c r="CB10" s="383"/>
       <c r="CC10" s="383"/>
       <c r="CD10" s="383"/>
@@ -15807,60 +15803,60 @@
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="384"/>
-      <c r="B11" s="384"/>
-      <c r="C11" s="384"/>
-      <c r="D11" s="384"/>
-      <c r="E11" s="384"/>
-      <c r="F11" s="384"/>
-      <c r="G11" s="384"/>
-      <c r="H11" s="384"/>
-      <c r="I11" s="384"/>
-      <c r="J11" s="384"/>
-      <c r="K11" s="384"/>
-      <c r="L11" s="384"/>
-      <c r="M11" s="384"/>
-      <c r="N11" s="384"/>
-      <c r="O11" s="384"/>
-      <c r="P11" s="384"/>
-      <c r="Q11" s="384"/>
-      <c r="R11" s="384"/>
-      <c r="S11" s="384"/>
-      <c r="T11" s="384"/>
-      <c r="U11" s="384"/>
+      <c r="A11" s="386"/>
+      <c r="B11" s="386"/>
+      <c r="C11" s="386"/>
+      <c r="D11" s="386"/>
+      <c r="E11" s="386"/>
+      <c r="F11" s="386"/>
+      <c r="G11" s="386"/>
+      <c r="H11" s="386"/>
+      <c r="I11" s="386"/>
+      <c r="J11" s="386"/>
+      <c r="K11" s="386"/>
+      <c r="L11" s="386"/>
+      <c r="M11" s="386"/>
+      <c r="N11" s="386"/>
+      <c r="O11" s="386"/>
+      <c r="P11" s="386"/>
+      <c r="Q11" s="386"/>
+      <c r="R11" s="386"/>
+      <c r="S11" s="386"/>
+      <c r="T11" s="386"/>
+      <c r="U11" s="386"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="384"/>
-      <c r="Y11" s="384"/>
-      <c r="Z11" s="384"/>
-      <c r="AA11" s="384"/>
-      <c r="AB11" s="384"/>
-      <c r="AC11" s="384"/>
-      <c r="AD11" s="384"/>
-      <c r="AE11" s="384"/>
-      <c r="AF11" s="384"/>
-      <c r="AG11" s="384"/>
-      <c r="AH11" s="384"/>
-      <c r="AI11" s="384"/>
-      <c r="AJ11" s="384"/>
-      <c r="AK11" s="394"/>
-      <c r="AL11" s="384"/>
-      <c r="AM11" s="384"/>
-      <c r="AN11" s="384"/>
-      <c r="AO11" s="384"/>
-      <c r="AP11" s="384"/>
-      <c r="AQ11" s="384"/>
-      <c r="AR11" s="384"/>
-      <c r="AS11" s="384"/>
-      <c r="AT11" s="384"/>
-      <c r="AU11" s="384"/>
-      <c r="AV11" s="384"/>
-      <c r="AW11" s="384"/>
-      <c r="AX11" s="384"/>
+      <c r="X11" s="386"/>
+      <c r="Y11" s="386"/>
+      <c r="Z11" s="386"/>
+      <c r="AA11" s="386"/>
+      <c r="AB11" s="386"/>
+      <c r="AC11" s="386"/>
+      <c r="AD11" s="386"/>
+      <c r="AE11" s="386"/>
+      <c r="AF11" s="386"/>
+      <c r="AG11" s="386"/>
+      <c r="AH11" s="386"/>
+      <c r="AI11" s="386"/>
+      <c r="AJ11" s="386"/>
+      <c r="AK11" s="393"/>
+      <c r="AL11" s="386"/>
+      <c r="AM11" s="386"/>
+      <c r="AN11" s="386"/>
+      <c r="AO11" s="386"/>
+      <c r="AP11" s="386"/>
+      <c r="AQ11" s="386"/>
+      <c r="AR11" s="386"/>
+      <c r="AS11" s="386"/>
+      <c r="AT11" s="386"/>
+      <c r="AU11" s="386"/>
+      <c r="AV11" s="386"/>
+      <c r="AW11" s="386"/>
+      <c r="AX11" s="386"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15870,28 +15866,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="384"/>
-      <c r="BC11" s="384"/>
-      <c r="BD11" s="384"/>
-      <c r="BE11" s="384"/>
-      <c r="BF11" s="384"/>
-      <c r="BG11" s="384"/>
-      <c r="BH11" s="384"/>
-      <c r="BI11" s="384"/>
-      <c r="BJ11" s="384"/>
-      <c r="BK11" s="384"/>
-      <c r="BL11" s="384"/>
-      <c r="BM11" s="384"/>
-      <c r="BN11" s="384"/>
-      <c r="BO11" s="384"/>
-      <c r="BP11" s="384"/>
-      <c r="BQ11" s="384"/>
-      <c r="BR11" s="384"/>
-      <c r="BS11" s="384"/>
-      <c r="BT11" s="384"/>
-      <c r="BU11" s="394"/>
+      <c r="BB11" s="386"/>
+      <c r="BC11" s="386"/>
+      <c r="BD11" s="386"/>
+      <c r="BE11" s="386"/>
+      <c r="BF11" s="386"/>
+      <c r="BG11" s="386"/>
+      <c r="BH11" s="386"/>
+      <c r="BI11" s="386"/>
+      <c r="BJ11" s="386"/>
+      <c r="BK11" s="386"/>
+      <c r="BL11" s="386"/>
+      <c r="BM11" s="386"/>
+      <c r="BN11" s="386"/>
+      <c r="BO11" s="386"/>
+      <c r="BP11" s="386"/>
+      <c r="BQ11" s="386"/>
+      <c r="BR11" s="386"/>
+      <c r="BS11" s="386"/>
+      <c r="BT11" s="386"/>
+      <c r="BU11" s="393"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="413"/>
+      <c r="BW11" s="396"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15904,9 +15900,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="405"/>
-      <c r="CC11" s="405"/>
-      <c r="CD11" s="405"/>
+      <c r="CB11" s="384"/>
+      <c r="CC11" s="384"/>
+      <c r="CD11" s="384"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18307,14 +18303,64 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="G8:G11"/>
     <mergeCell ref="BS8:BS11"/>
@@ -18331,64 +18377,14 @@
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18618,87 +18614,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="415"/>
-      <c r="B3" s="403"/>
-      <c r="C3" s="403"/>
-      <c r="D3" s="403"/>
-      <c r="E3" s="403"/>
-      <c r="F3" s="403"/>
-      <c r="G3" s="403"/>
-      <c r="H3" s="403"/>
-      <c r="I3" s="403"/>
-      <c r="J3" s="403"/>
-      <c r="K3" s="403"/>
-      <c r="L3" s="403"/>
-      <c r="M3" s="403"/>
-      <c r="N3" s="403"/>
-      <c r="O3" s="403"/>
-      <c r="P3" s="403"/>
-      <c r="Q3" s="403"/>
-      <c r="R3" s="403"/>
-      <c r="S3" s="403"/>
-      <c r="T3" s="403"/>
-      <c r="U3" s="403"/>
-      <c r="V3" s="403"/>
-      <c r="W3" s="403"/>
-      <c r="X3" s="403"/>
-      <c r="Y3" s="403"/>
-      <c r="Z3" s="403"/>
-      <c r="AA3" s="403"/>
-      <c r="AB3" s="403"/>
-      <c r="AC3" s="403"/>
-      <c r="AD3" s="403"/>
-      <c r="AE3" s="403"/>
-      <c r="AF3" s="403"/>
-      <c r="AG3" s="403"/>
-      <c r="AH3" s="403"/>
-      <c r="AI3" s="403"/>
-      <c r="AJ3" s="403"/>
-      <c r="AK3" s="403"/>
-      <c r="AL3" s="403"/>
-      <c r="AM3" s="403"/>
-      <c r="AN3" s="403"/>
-      <c r="AO3" s="403"/>
-      <c r="AP3" s="403"/>
-      <c r="AQ3" s="403"/>
-      <c r="AR3" s="403"/>
-      <c r="AS3" s="403"/>
-      <c r="AT3" s="403"/>
-      <c r="AU3" s="403"/>
-      <c r="AV3" s="403"/>
-      <c r="AW3" s="403"/>
-      <c r="AX3" s="403"/>
-      <c r="AY3" s="403"/>
-      <c r="AZ3" s="403"/>
-      <c r="BA3" s="403"/>
-      <c r="BB3" s="403"/>
-      <c r="BC3" s="403"/>
-      <c r="BD3" s="403"/>
-      <c r="BE3" s="403"/>
-      <c r="BF3" s="403"/>
-      <c r="BG3" s="403"/>
-      <c r="BH3" s="403"/>
-      <c r="BI3" s="403"/>
-      <c r="BJ3" s="403"/>
-      <c r="BK3" s="403"/>
-      <c r="BL3" s="403"/>
-      <c r="BM3" s="403"/>
-      <c r="BN3" s="403"/>
-      <c r="BO3" s="403"/>
-      <c r="BP3" s="403"/>
-      <c r="BQ3" s="403"/>
-      <c r="BR3" s="403"/>
-      <c r="BS3" s="403"/>
-      <c r="BT3" s="403"/>
-      <c r="BU3" s="403"/>
-      <c r="BW3" s="402" t="s">
+      <c r="A3" s="411"/>
+      <c r="B3" s="402"/>
+      <c r="C3" s="402"/>
+      <c r="D3" s="402"/>
+      <c r="E3" s="402"/>
+      <c r="F3" s="402"/>
+      <c r="G3" s="402"/>
+      <c r="H3" s="402"/>
+      <c r="I3" s="402"/>
+      <c r="J3" s="402"/>
+      <c r="K3" s="402"/>
+      <c r="L3" s="402"/>
+      <c r="M3" s="402"/>
+      <c r="N3" s="402"/>
+      <c r="O3" s="402"/>
+      <c r="P3" s="402"/>
+      <c r="Q3" s="402"/>
+      <c r="R3" s="402"/>
+      <c r="S3" s="402"/>
+      <c r="T3" s="402"/>
+      <c r="U3" s="402"/>
+      <c r="V3" s="402"/>
+      <c r="W3" s="402"/>
+      <c r="X3" s="402"/>
+      <c r="Y3" s="402"/>
+      <c r="Z3" s="402"/>
+      <c r="AA3" s="402"/>
+      <c r="AB3" s="402"/>
+      <c r="AC3" s="402"/>
+      <c r="AD3" s="402"/>
+      <c r="AE3" s="402"/>
+      <c r="AF3" s="402"/>
+      <c r="AG3" s="402"/>
+      <c r="AH3" s="402"/>
+      <c r="AI3" s="402"/>
+      <c r="AJ3" s="402"/>
+      <c r="AK3" s="402"/>
+      <c r="AL3" s="402"/>
+      <c r="AM3" s="402"/>
+      <c r="AN3" s="402"/>
+      <c r="AO3" s="402"/>
+      <c r="AP3" s="402"/>
+      <c r="AQ3" s="402"/>
+      <c r="AR3" s="402"/>
+      <c r="AS3" s="402"/>
+      <c r="AT3" s="402"/>
+      <c r="AU3" s="402"/>
+      <c r="AV3" s="402"/>
+      <c r="AW3" s="402"/>
+      <c r="AX3" s="402"/>
+      <c r="AY3" s="402"/>
+      <c r="AZ3" s="402"/>
+      <c r="BA3" s="402"/>
+      <c r="BB3" s="402"/>
+      <c r="BC3" s="402"/>
+      <c r="BD3" s="402"/>
+      <c r="BE3" s="402"/>
+      <c r="BF3" s="402"/>
+      <c r="BG3" s="402"/>
+      <c r="BH3" s="402"/>
+      <c r="BI3" s="402"/>
+      <c r="BJ3" s="402"/>
+      <c r="BK3" s="402"/>
+      <c r="BL3" s="402"/>
+      <c r="BM3" s="402"/>
+      <c r="BN3" s="402"/>
+      <c r="BO3" s="402"/>
+      <c r="BP3" s="402"/>
+      <c r="BQ3" s="402"/>
+      <c r="BR3" s="402"/>
+      <c r="BS3" s="402"/>
+      <c r="BT3" s="402"/>
+      <c r="BU3" s="402"/>
+      <c r="BW3" s="401" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="403"/>
-      <c r="BY3" s="403"/>
-      <c r="BZ3" s="403"/>
-      <c r="CA3" s="403"/>
-      <c r="CB3" s="403"/>
+      <c r="BX3" s="402"/>
+      <c r="BY3" s="402"/>
+      <c r="BZ3" s="402"/>
+      <c r="CA3" s="402"/>
+      <c r="CB3" s="402"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18781,157 +18777,157 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="403"/>
-      <c r="BX4" s="403"/>
-      <c r="BY4" s="403"/>
-      <c r="BZ4" s="403"/>
-      <c r="CA4" s="403"/>
-      <c r="CB4" s="403"/>
+      <c r="BW4" s="402"/>
+      <c r="BX4" s="402"/>
+      <c r="BY4" s="402"/>
+      <c r="BZ4" s="402"/>
+      <c r="CA4" s="402"/>
+      <c r="CB4" s="402"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="391" t="s">
+      <c r="A5" s="414" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="401" t="s">
+      <c r="B5" s="413" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="389" t="s">
+      <c r="C5" s="387" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="397" t="s">
+      <c r="D5" s="412" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="397" t="s">
+      <c r="E5" s="412" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="426" t="s">
+      <c r="F5" s="431" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="389" t="s">
+      <c r="G5" s="387" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="345" t="s">
+      <c r="H5" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="345" t="s">
+      <c r="I5" s="333" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="389" t="s">
+      <c r="J5" s="387" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="395" t="s">
+      <c r="K5" s="416" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="386"/>
-      <c r="M5" s="386"/>
-      <c r="N5" s="386"/>
-      <c r="O5" s="386"/>
-      <c r="P5" s="386"/>
-      <c r="Q5" s="386"/>
-      <c r="R5" s="386"/>
-      <c r="S5" s="386"/>
-      <c r="T5" s="386"/>
-      <c r="U5" s="386"/>
-      <c r="V5" s="386"/>
-      <c r="W5" s="386"/>
-      <c r="X5" s="386"/>
-      <c r="Y5" s="389" t="s">
+      <c r="L5" s="398"/>
+      <c r="M5" s="398"/>
+      <c r="N5" s="398"/>
+      <c r="O5" s="398"/>
+      <c r="P5" s="398"/>
+      <c r="Q5" s="398"/>
+      <c r="R5" s="398"/>
+      <c r="S5" s="398"/>
+      <c r="T5" s="398"/>
+      <c r="U5" s="398"/>
+      <c r="V5" s="398"/>
+      <c r="W5" s="398"/>
+      <c r="X5" s="398"/>
+      <c r="Y5" s="387" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="386"/>
-      <c r="AA5" s="386"/>
-      <c r="AB5" s="386"/>
-      <c r="AC5" s="386"/>
-      <c r="AD5" s="386"/>
-      <c r="AE5" s="386"/>
-      <c r="AF5" s="386"/>
-      <c r="AG5" s="386"/>
-      <c r="AH5" s="386"/>
-      <c r="AI5" s="386"/>
-      <c r="AJ5" s="386"/>
-      <c r="AK5" s="386"/>
-      <c r="AL5" s="386"/>
-      <c r="AM5" s="386"/>
-      <c r="AN5" s="386"/>
-      <c r="AO5" s="387"/>
-      <c r="AP5" s="389" t="s">
+      <c r="Z5" s="398"/>
+      <c r="AA5" s="398"/>
+      <c r="AB5" s="398"/>
+      <c r="AC5" s="398"/>
+      <c r="AD5" s="398"/>
+      <c r="AE5" s="398"/>
+      <c r="AF5" s="398"/>
+      <c r="AG5" s="398"/>
+      <c r="AH5" s="398"/>
+      <c r="AI5" s="398"/>
+      <c r="AJ5" s="398"/>
+      <c r="AK5" s="398"/>
+      <c r="AL5" s="398"/>
+      <c r="AM5" s="398"/>
+      <c r="AN5" s="398"/>
+      <c r="AO5" s="399"/>
+      <c r="AP5" s="387" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="389" t="s">
+      <c r="AQ5" s="387" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="389" t="s">
+      <c r="AR5" s="387" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="389" t="s">
+      <c r="AS5" s="387" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="389" t="s">
+      <c r="AT5" s="387" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="389" t="s">
+      <c r="AU5" s="387" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="389" t="s">
+      <c r="AV5" s="387" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="389" t="s">
+      <c r="AW5" s="387" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="389" t="s">
+      <c r="AX5" s="387" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="385" t="s">
+      <c r="AY5" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="386"/>
-      <c r="BA5" s="386"/>
-      <c r="BB5" s="386"/>
-      <c r="BC5" s="386"/>
-      <c r="BD5" s="386"/>
-      <c r="BE5" s="386"/>
-      <c r="BF5" s="386"/>
-      <c r="BG5" s="386"/>
-      <c r="BH5" s="386"/>
-      <c r="BI5" s="386"/>
-      <c r="BJ5" s="386"/>
-      <c r="BK5" s="386"/>
-      <c r="BL5" s="386"/>
-      <c r="BM5" s="386"/>
-      <c r="BN5" s="386"/>
-      <c r="BO5" s="386"/>
-      <c r="BP5" s="387"/>
-      <c r="BQ5" s="406" t="s">
+      <c r="AZ5" s="398"/>
+      <c r="BA5" s="398"/>
+      <c r="BB5" s="398"/>
+      <c r="BC5" s="398"/>
+      <c r="BD5" s="398"/>
+      <c r="BE5" s="398"/>
+      <c r="BF5" s="398"/>
+      <c r="BG5" s="398"/>
+      <c r="BH5" s="398"/>
+      <c r="BI5" s="398"/>
+      <c r="BJ5" s="398"/>
+      <c r="BK5" s="398"/>
+      <c r="BL5" s="398"/>
+      <c r="BM5" s="398"/>
+      <c r="BN5" s="398"/>
+      <c r="BO5" s="398"/>
+      <c r="BP5" s="399"/>
+      <c r="BQ5" s="403" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="399"/>
-      <c r="BS5" s="385" t="s">
+      <c r="BR5" s="404"/>
+      <c r="BS5" s="397" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="385" t="s">
+      <c r="BT5" s="397" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="417" t="s">
+      <c r="BU5" s="391" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="418" t="s">
+      <c r="BW5" s="394" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="407" t="s">
+      <c r="BX5" s="405" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="408"/>
-      <c r="BZ5" s="408"/>
-      <c r="CA5" s="399"/>
-      <c r="CB5" s="419" t="s">
+      <c r="BY5" s="406"/>
+      <c r="BZ5" s="406"/>
+      <c r="CA5" s="404"/>
+      <c r="CB5" s="400" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="404" t="s">
+      <c r="CC5" s="382" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="404" t="s">
+      <c r="CD5" s="382" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
@@ -18948,95 +18944,95 @@
       <c r="H6" s="383"/>
       <c r="I6" s="383"/>
       <c r="J6" s="383"/>
-      <c r="K6" s="390" t="s">
+      <c r="K6" s="388" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="390" t="s">
+      <c r="L6" s="388" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="390" t="s">
+      <c r="M6" s="388" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="390" t="s">
+      <c r="N6" s="388" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="390" t="s">
+      <c r="O6" s="388" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="390" t="s">
+      <c r="P6" s="388" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="390" t="s">
+      <c r="Q6" s="388" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="390" t="s">
+      <c r="R6" s="388" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="390" t="s">
+      <c r="S6" s="388" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="390" t="s">
+      <c r="T6" s="388" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="390" t="s">
+      <c r="U6" s="388" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="398" t="s">
+      <c r="V6" s="418" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="399"/>
-      <c r="X6" s="390" t="s">
+      <c r="W6" s="404"/>
+      <c r="X6" s="388" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="389" t="s">
+      <c r="Y6" s="387" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="389" t="s">
+      <c r="Z6" s="387" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="389" t="s">
+      <c r="AA6" s="387" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="389" t="s">
+      <c r="AB6" s="387" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="345" t="s">
+      <c r="AC6" s="333" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="345" t="s">
+      <c r="AD6" s="333" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="345" t="s">
+      <c r="AE6" s="333" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="345" t="s">
+      <c r="AF6" s="333" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="389" t="s">
+      <c r="AG6" s="387" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="345" t="s">
+      <c r="AH6" s="333" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="345" t="s">
+      <c r="AI6" s="333" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="389" t="s">
+      <c r="AJ6" s="387" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="392" t="s">
+      <c r="AK6" s="415" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="389" t="s">
+      <c r="AL6" s="387" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="389" t="s">
+      <c r="AM6" s="387" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="396" t="s">
+      <c r="AN6" s="417" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="389" t="s">
+      <c r="AO6" s="387" t="s">
         <v>63</v>
       </c>
       <c r="AP6" s="383"/>
@@ -19048,42 +19044,42 @@
       <c r="AV6" s="383"/>
       <c r="AW6" s="383"/>
       <c r="AX6" s="383"/>
-      <c r="AY6" s="385" t="s">
+      <c r="AY6" s="397" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="386"/>
-      <c r="BA6" s="386"/>
-      <c r="BB6" s="386"/>
-      <c r="BC6" s="386"/>
-      <c r="BD6" s="386"/>
-      <c r="BE6" s="386"/>
-      <c r="BF6" s="386"/>
-      <c r="BG6" s="386"/>
-      <c r="BH6" s="386"/>
-      <c r="BI6" s="386"/>
-      <c r="BJ6" s="387"/>
-      <c r="BK6" s="385" t="s">
+      <c r="AZ6" s="398"/>
+      <c r="BA6" s="398"/>
+      <c r="BB6" s="398"/>
+      <c r="BC6" s="398"/>
+      <c r="BD6" s="398"/>
+      <c r="BE6" s="398"/>
+      <c r="BF6" s="398"/>
+      <c r="BG6" s="398"/>
+      <c r="BH6" s="398"/>
+      <c r="BI6" s="398"/>
+      <c r="BJ6" s="399"/>
+      <c r="BK6" s="397" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="386"/>
-      <c r="BM6" s="386"/>
-      <c r="BN6" s="386"/>
-      <c r="BO6" s="386"/>
-      <c r="BP6" s="387"/>
-      <c r="BQ6" s="382" t="s">
+      <c r="BL6" s="398"/>
+      <c r="BM6" s="398"/>
+      <c r="BN6" s="398"/>
+      <c r="BO6" s="398"/>
+      <c r="BP6" s="399"/>
+      <c r="BQ6" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="382" t="s">
+      <c r="BR6" s="385" t="s">
         <v>66</v>
       </c>
       <c r="BS6" s="383"/>
       <c r="BT6" s="383"/>
-      <c r="BU6" s="393"/>
-      <c r="BW6" s="410"/>
-      <c r="BX6" s="393"/>
-      <c r="BY6" s="409"/>
-      <c r="BZ6" s="409"/>
-      <c r="CA6" s="410"/>
+      <c r="BU6" s="392"/>
+      <c r="BW6" s="395"/>
+      <c r="BX6" s="392"/>
+      <c r="BY6" s="407"/>
+      <c r="BZ6" s="407"/>
+      <c r="CA6" s="395"/>
       <c r="CB6" s="383"/>
       <c r="CC6" s="383"/>
       <c r="CD6" s="383"/>
@@ -19112,8 +19108,8 @@
       <c r="S7" s="383"/>
       <c r="T7" s="383"/>
       <c r="U7" s="383"/>
-      <c r="V7" s="394"/>
-      <c r="W7" s="400"/>
+      <c r="V7" s="393"/>
+      <c r="W7" s="419"/>
       <c r="X7" s="383"/>
       <c r="Y7" s="383"/>
       <c r="Z7" s="383"/>
@@ -19127,7 +19123,7 @@
       <c r="AH7" s="383"/>
       <c r="AI7" s="383"/>
       <c r="AJ7" s="383"/>
-      <c r="AK7" s="393"/>
+      <c r="AK7" s="392"/>
       <c r="AL7" s="383"/>
       <c r="AM7" s="383"/>
       <c r="AN7" s="383"/>
@@ -19150,61 +19146,61 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="385" t="s">
+      <c r="BB7" s="397" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="388" t="s">
+      <c r="BC7" s="389" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="388" t="s">
+      <c r="BD7" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="388" t="s">
+      <c r="BE7" s="389" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="388" t="s">
+      <c r="BF7" s="389" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="388" t="s">
+      <c r="BG7" s="389" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="388" t="s">
+      <c r="BH7" s="389" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="388" t="s">
+      <c r="BI7" s="389" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="416" t="s">
+      <c r="BJ7" s="390" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="388" t="s">
+      <c r="BK7" s="389" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="385" t="s">
+      <c r="BL7" s="397" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="388" t="s">
+      <c r="BM7" s="389" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="385" t="s">
+      <c r="BN7" s="397" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="385" t="s">
+      <c r="BO7" s="397" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="385" t="s">
+      <c r="BP7" s="397" t="s">
         <v>85</v>
       </c>
       <c r="BQ7" s="383"/>
       <c r="BR7" s="383"/>
       <c r="BS7" s="383"/>
       <c r="BT7" s="383"/>
-      <c r="BU7" s="393"/>
-      <c r="BW7" s="410"/>
-      <c r="BX7" s="411"/>
-      <c r="BY7" s="412"/>
-      <c r="BZ7" s="412"/>
-      <c r="CA7" s="413"/>
+      <c r="BU7" s="392"/>
+      <c r="BW7" s="395"/>
+      <c r="BX7" s="408"/>
+      <c r="BY7" s="409"/>
+      <c r="BZ7" s="409"/>
+      <c r="CA7" s="396"/>
       <c r="CB7" s="383"/>
       <c r="CC7" s="383"/>
       <c r="CD7" s="383"/>
@@ -19212,60 +19208,60 @@
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="384"/>
-      <c r="B8" s="384"/>
-      <c r="C8" s="384"/>
-      <c r="D8" s="384"/>
-      <c r="E8" s="384"/>
-      <c r="F8" s="384"/>
-      <c r="G8" s="384"/>
-      <c r="H8" s="384"/>
-      <c r="I8" s="384"/>
-      <c r="J8" s="384"/>
-      <c r="K8" s="384"/>
-      <c r="L8" s="384"/>
-      <c r="M8" s="384"/>
-      <c r="N8" s="384"/>
-      <c r="O8" s="384"/>
-      <c r="P8" s="384"/>
-      <c r="Q8" s="384"/>
-      <c r="R8" s="384"/>
-      <c r="S8" s="384"/>
-      <c r="T8" s="384"/>
-      <c r="U8" s="384"/>
+      <c r="A8" s="386"/>
+      <c r="B8" s="386"/>
+      <c r="C8" s="386"/>
+      <c r="D8" s="386"/>
+      <c r="E8" s="386"/>
+      <c r="F8" s="386"/>
+      <c r="G8" s="386"/>
+      <c r="H8" s="386"/>
+      <c r="I8" s="386"/>
+      <c r="J8" s="386"/>
+      <c r="K8" s="386"/>
+      <c r="L8" s="386"/>
+      <c r="M8" s="386"/>
+      <c r="N8" s="386"/>
+      <c r="O8" s="386"/>
+      <c r="P8" s="386"/>
+      <c r="Q8" s="386"/>
+      <c r="R8" s="386"/>
+      <c r="S8" s="386"/>
+      <c r="T8" s="386"/>
+      <c r="U8" s="386"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="384"/>
-      <c r="Y8" s="384"/>
-      <c r="Z8" s="384"/>
-      <c r="AA8" s="384"/>
-      <c r="AB8" s="384"/>
-      <c r="AC8" s="384"/>
-      <c r="AD8" s="384"/>
-      <c r="AE8" s="384"/>
-      <c r="AF8" s="384"/>
-      <c r="AG8" s="384"/>
-      <c r="AH8" s="384"/>
-      <c r="AI8" s="384"/>
-      <c r="AJ8" s="384"/>
-      <c r="AK8" s="394"/>
-      <c r="AL8" s="384"/>
-      <c r="AM8" s="384"/>
-      <c r="AN8" s="384"/>
-      <c r="AO8" s="384"/>
-      <c r="AP8" s="384"/>
-      <c r="AQ8" s="384"/>
-      <c r="AR8" s="384"/>
-      <c r="AS8" s="384"/>
-      <c r="AT8" s="384"/>
-      <c r="AU8" s="384"/>
-      <c r="AV8" s="384"/>
-      <c r="AW8" s="384"/>
-      <c r="AX8" s="384"/>
+      <c r="X8" s="386"/>
+      <c r="Y8" s="386"/>
+      <c r="Z8" s="386"/>
+      <c r="AA8" s="386"/>
+      <c r="AB8" s="386"/>
+      <c r="AC8" s="386"/>
+      <c r="AD8" s="386"/>
+      <c r="AE8" s="386"/>
+      <c r="AF8" s="386"/>
+      <c r="AG8" s="386"/>
+      <c r="AH8" s="386"/>
+      <c r="AI8" s="386"/>
+      <c r="AJ8" s="386"/>
+      <c r="AK8" s="393"/>
+      <c r="AL8" s="386"/>
+      <c r="AM8" s="386"/>
+      <c r="AN8" s="386"/>
+      <c r="AO8" s="386"/>
+      <c r="AP8" s="386"/>
+      <c r="AQ8" s="386"/>
+      <c r="AR8" s="386"/>
+      <c r="AS8" s="386"/>
+      <c r="AT8" s="386"/>
+      <c r="AU8" s="386"/>
+      <c r="AV8" s="386"/>
+      <c r="AW8" s="386"/>
+      <c r="AX8" s="386"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19275,27 +19271,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="384"/>
-      <c r="BC8" s="384"/>
-      <c r="BD8" s="384"/>
-      <c r="BE8" s="384"/>
-      <c r="BF8" s="384"/>
-      <c r="BG8" s="384"/>
-      <c r="BH8" s="384"/>
-      <c r="BI8" s="384"/>
-      <c r="BJ8" s="384"/>
-      <c r="BK8" s="384"/>
-      <c r="BL8" s="384"/>
-      <c r="BM8" s="384"/>
-      <c r="BN8" s="384"/>
-      <c r="BO8" s="384"/>
-      <c r="BP8" s="384"/>
-      <c r="BQ8" s="384"/>
-      <c r="BR8" s="384"/>
-      <c r="BS8" s="384"/>
-      <c r="BT8" s="384"/>
-      <c r="BU8" s="394"/>
-      <c r="BW8" s="413"/>
+      <c r="BB8" s="386"/>
+      <c r="BC8" s="386"/>
+      <c r="BD8" s="386"/>
+      <c r="BE8" s="386"/>
+      <c r="BF8" s="386"/>
+      <c r="BG8" s="386"/>
+      <c r="BH8" s="386"/>
+      <c r="BI8" s="386"/>
+      <c r="BJ8" s="386"/>
+      <c r="BK8" s="386"/>
+      <c r="BL8" s="386"/>
+      <c r="BM8" s="386"/>
+      <c r="BN8" s="386"/>
+      <c r="BO8" s="386"/>
+      <c r="BP8" s="386"/>
+      <c r="BQ8" s="386"/>
+      <c r="BR8" s="386"/>
+      <c r="BS8" s="386"/>
+      <c r="BT8" s="386"/>
+      <c r="BU8" s="393"/>
+      <c r="BW8" s="396"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19308,9 +19304,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="405"/>
-      <c r="CC8" s="405"/>
-      <c r="CD8" s="405"/>
+      <c r="CB8" s="384"/>
+      <c r="CC8" s="384"/>
+      <c r="CD8" s="384"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21317,20 +21313,56 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="CC5:CC8"/>
     <mergeCell ref="H5:H8"/>
@@ -21347,58 +21379,22 @@
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="C5:C8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
     <mergeCell ref="AU5:AU8"/>
     <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1D6BC9-C315-0743-8471-111929B8AD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD10DCA-FDC3-2E45-A02C-24FC378319AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5061,7 +5061,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="73">
+  <fonts count="77">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5515,6 +5515,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -5829,7 +5858,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="434">
+  <cellXfs count="444">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6562,12 +6591,6 @@
     <xf numFmtId="0" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="6" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6736,96 +6759,6 @@
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="20" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6839,60 +6772,146 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6900,78 +6919,110 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="76" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="49" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -7573,989 +7624,989 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" s="240" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
-      <c r="A1" s="284" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
-      <c r="I1" s="288"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="289"/>
-      <c r="N1" s="289"/>
-      <c r="O1" s="289"/>
-      <c r="P1" s="289"/>
-      <c r="Q1" s="289"/>
-      <c r="R1" s="289"/>
-      <c r="S1" s="289"/>
-      <c r="T1" s="289"/>
-      <c r="U1" s="289"/>
-      <c r="V1" s="289"/>
-      <c r="W1" s="289"/>
-      <c r="X1" s="289"/>
-      <c r="Y1" s="290"/>
-      <c r="Z1" s="290"/>
-      <c r="AA1" s="290"/>
-      <c r="AB1" s="290"/>
-      <c r="AC1" s="290"/>
-      <c r="AD1" s="290"/>
-      <c r="AE1" s="290"/>
-      <c r="AF1" s="290"/>
-      <c r="AG1" s="290"/>
-      <c r="AH1" s="290"/>
-      <c r="AI1" s="290"/>
-      <c r="AJ1" s="290"/>
-      <c r="AK1" s="290"/>
-      <c r="AL1" s="290"/>
-      <c r="AM1" s="290"/>
-      <c r="AN1" s="290"/>
-      <c r="AO1" s="290"/>
-      <c r="AP1" s="290"/>
-      <c r="AQ1" s="290"/>
-      <c r="AR1" s="290"/>
-      <c r="AS1" s="290"/>
-      <c r="AT1" s="290"/>
-      <c r="AU1" s="290"/>
-      <c r="AV1" s="290"/>
-      <c r="AW1" s="290"/>
-      <c r="AX1" s="290"/>
-      <c r="AY1" s="290"/>
-      <c r="AZ1" s="290"/>
-      <c r="BA1" s="290"/>
-      <c r="BB1" s="290"/>
-      <c r="BC1" s="290"/>
-      <c r="BD1" s="291"/>
-      <c r="BE1" s="290"/>
-      <c r="BF1" s="291"/>
-      <c r="BG1" s="290"/>
-      <c r="BH1" s="290"/>
-      <c r="BI1" s="290"/>
-      <c r="BJ1" s="290"/>
-      <c r="BK1" s="290"/>
-      <c r="BL1" s="290"/>
-      <c r="BM1" s="290"/>
-      <c r="BN1" s="290"/>
-      <c r="BO1" s="290"/>
-      <c r="BP1" s="292"/>
-      <c r="BQ1" s="290"/>
-      <c r="BR1" s="290"/>
-      <c r="BS1" s="290"/>
-      <c r="BU1" s="290"/>
-      <c r="BV1" s="290"/>
-      <c r="BW1" s="293"/>
-      <c r="BX1" s="293"/>
-      <c r="BY1" s="293"/>
-      <c r="BZ1" s="293"/>
-      <c r="CA1" s="293"/>
-      <c r="CB1" s="294"/>
-      <c r="CC1" s="294"/>
-      <c r="CD1" s="294"/>
+      <c r="A1" s="282" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="283"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="I1" s="286"/>
+      <c r="K1" s="287"/>
+      <c r="L1" s="287"/>
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="288"/>
+      <c r="AI1" s="288"/>
+      <c r="AJ1" s="288"/>
+      <c r="AK1" s="288"/>
+      <c r="AL1" s="288"/>
+      <c r="AM1" s="288"/>
+      <c r="AN1" s="288"/>
+      <c r="AO1" s="288"/>
+      <c r="AP1" s="288"/>
+      <c r="AQ1" s="288"/>
+      <c r="AR1" s="288"/>
+      <c r="AS1" s="288"/>
+      <c r="AT1" s="288"/>
+      <c r="AU1" s="288"/>
+      <c r="AV1" s="288"/>
+      <c r="AW1" s="288"/>
+      <c r="AX1" s="288"/>
+      <c r="AY1" s="288"/>
+      <c r="AZ1" s="288"/>
+      <c r="BA1" s="288"/>
+      <c r="BB1" s="288"/>
+      <c r="BC1" s="288"/>
+      <c r="BD1" s="289"/>
+      <c r="BE1" s="288"/>
+      <c r="BF1" s="289"/>
+      <c r="BG1" s="288"/>
+      <c r="BH1" s="288"/>
+      <c r="BI1" s="288"/>
+      <c r="BJ1" s="288"/>
+      <c r="BK1" s="288"/>
+      <c r="BL1" s="288"/>
+      <c r="BM1" s="288"/>
+      <c r="BN1" s="288"/>
+      <c r="BO1" s="288"/>
+      <c r="BP1" s="290"/>
+      <c r="BQ1" s="288"/>
+      <c r="BR1" s="288"/>
+      <c r="BS1" s="288"/>
+      <c r="BU1" s="288"/>
+      <c r="BV1" s="288"/>
+      <c r="BW1" s="291"/>
+      <c r="BX1" s="291"/>
+      <c r="BY1" s="291"/>
+      <c r="BZ1" s="291"/>
+      <c r="CA1" s="291"/>
+      <c r="CB1" s="292"/>
+      <c r="CC1" s="292"/>
+      <c r="CD1" s="292"/>
     </row>
     <row r="2" spans="1:87" s="240" customFormat="1" ht="19.25" customHeight="1" outlineLevel="1">
-      <c r="A2" s="295" t="s">
+      <c r="A2" s="293" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="285"/>
-      <c r="C2" s="296"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
-      <c r="F2" s="287"/>
-      <c r="I2" s="288"/>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="289"/>
-      <c r="N2" s="289"/>
-      <c r="O2" s="289"/>
-      <c r="P2" s="289"/>
-      <c r="Q2" s="289"/>
-      <c r="R2" s="289"/>
-      <c r="S2" s="289"/>
-      <c r="T2" s="289"/>
-      <c r="U2" s="289"/>
-      <c r="V2" s="289"/>
-      <c r="W2" s="289"/>
-      <c r="X2" s="289"/>
-      <c r="Y2" s="290"/>
-      <c r="Z2" s="290"/>
-      <c r="AA2" s="290"/>
-      <c r="AB2" s="290"/>
-      <c r="AC2" s="290"/>
-      <c r="AD2" s="290"/>
-      <c r="AE2" s="290"/>
-      <c r="AF2" s="290"/>
-      <c r="AG2" s="290"/>
-      <c r="AH2" s="290"/>
-      <c r="AI2" s="290"/>
-      <c r="AJ2" s="290"/>
-      <c r="AK2" s="290"/>
-      <c r="AL2" s="290"/>
-      <c r="AM2" s="290"/>
-      <c r="AN2" s="290"/>
-      <c r="AO2" s="290"/>
-      <c r="AP2" s="290"/>
-      <c r="AQ2" s="290"/>
-      <c r="AR2" s="290"/>
-      <c r="AS2" s="290"/>
-      <c r="AT2" s="290"/>
-      <c r="AU2" s="290"/>
-      <c r="AV2" s="290"/>
-      <c r="AW2" s="290"/>
-      <c r="AX2" s="290"/>
-      <c r="AY2" s="290"/>
-      <c r="AZ2" s="290"/>
-      <c r="BA2" s="290"/>
-      <c r="BB2" s="290"/>
-      <c r="BC2" s="290"/>
-      <c r="BD2" s="291"/>
-      <c r="BE2" s="290"/>
-      <c r="BF2" s="290"/>
-      <c r="BG2" s="290"/>
-      <c r="BH2" s="290"/>
-      <c r="BI2" s="290"/>
-      <c r="BJ2" s="290"/>
-      <c r="BK2" s="290"/>
-      <c r="BL2" s="290"/>
-      <c r="BM2" s="290"/>
-      <c r="BN2" s="290"/>
-      <c r="BO2" s="290"/>
-      <c r="BP2" s="290"/>
-      <c r="BQ2" s="290"/>
-      <c r="BR2" s="290"/>
-      <c r="BS2" s="290"/>
-      <c r="BT2" s="290"/>
-      <c r="BU2" s="290"/>
-      <c r="BV2" s="290"/>
-      <c r="BW2" s="297"/>
-      <c r="BX2" s="297"/>
-      <c r="BY2" s="297"/>
-      <c r="BZ2" s="297"/>
-      <c r="CA2" s="297"/>
-      <c r="CB2" s="296"/>
-      <c r="CC2" s="296"/>
-      <c r="CD2" s="296"/>
+      <c r="B2" s="283"/>
+      <c r="C2" s="294"/>
+      <c r="D2" s="285"/>
+      <c r="E2" s="285"/>
+      <c r="F2" s="285"/>
+      <c r="I2" s="286"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
+      <c r="P2" s="287"/>
+      <c r="Q2" s="287"/>
+      <c r="R2" s="287"/>
+      <c r="S2" s="287"/>
+      <c r="T2" s="287"/>
+      <c r="U2" s="287"/>
+      <c r="V2" s="287"/>
+      <c r="W2" s="287"/>
+      <c r="X2" s="287"/>
+      <c r="Y2" s="288"/>
+      <c r="Z2" s="288"/>
+      <c r="AA2" s="288"/>
+      <c r="AB2" s="288"/>
+      <c r="AC2" s="288"/>
+      <c r="AD2" s="288"/>
+      <c r="AE2" s="288"/>
+      <c r="AF2" s="288"/>
+      <c r="AG2" s="288"/>
+      <c r="AH2" s="288"/>
+      <c r="AI2" s="288"/>
+      <c r="AJ2" s="288"/>
+      <c r="AK2" s="288"/>
+      <c r="AL2" s="288"/>
+      <c r="AM2" s="288"/>
+      <c r="AN2" s="288"/>
+      <c r="AO2" s="288"/>
+      <c r="AP2" s="288"/>
+      <c r="AQ2" s="288"/>
+      <c r="AR2" s="288"/>
+      <c r="AS2" s="288"/>
+      <c r="AT2" s="288"/>
+      <c r="AU2" s="288"/>
+      <c r="AV2" s="288"/>
+      <c r="AW2" s="288"/>
+      <c r="AX2" s="288"/>
+      <c r="AY2" s="288"/>
+      <c r="AZ2" s="288"/>
+      <c r="BA2" s="288"/>
+      <c r="BB2" s="288"/>
+      <c r="BC2" s="288"/>
+      <c r="BD2" s="289"/>
+      <c r="BE2" s="288"/>
+      <c r="BF2" s="288"/>
+      <c r="BG2" s="288"/>
+      <c r="BH2" s="288"/>
+      <c r="BI2" s="288"/>
+      <c r="BJ2" s="288"/>
+      <c r="BK2" s="288"/>
+      <c r="BL2" s="288"/>
+      <c r="BM2" s="288"/>
+      <c r="BN2" s="288"/>
+      <c r="BO2" s="288"/>
+      <c r="BP2" s="288"/>
+      <c r="BQ2" s="288"/>
+      <c r="BR2" s="288"/>
+      <c r="BS2" s="288"/>
+      <c r="BT2" s="288"/>
+      <c r="BU2" s="288"/>
+      <c r="BV2" s="288"/>
+      <c r="BW2" s="295"/>
+      <c r="BX2" s="295"/>
+      <c r="BY2" s="295"/>
+      <c r="BZ2" s="295"/>
+      <c r="CA2" s="295"/>
+      <c r="CB2" s="294"/>
+      <c r="CC2" s="294"/>
+      <c r="CD2" s="294"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="361"/>
-      <c r="B3" s="360"/>
-      <c r="C3" s="360"/>
-      <c r="D3" s="360"/>
-      <c r="E3" s="360"/>
-      <c r="F3" s="360"/>
-      <c r="G3" s="360"/>
-      <c r="H3" s="360"/>
-      <c r="I3" s="360"/>
-      <c r="J3" s="360"/>
-      <c r="K3" s="360"/>
-      <c r="L3" s="360"/>
-      <c r="M3" s="360"/>
-      <c r="N3" s="360"/>
-      <c r="O3" s="360"/>
-      <c r="P3" s="360"/>
-      <c r="Q3" s="360"/>
-      <c r="R3" s="360"/>
-      <c r="S3" s="360"/>
-      <c r="T3" s="360"/>
-      <c r="U3" s="360"/>
-      <c r="V3" s="360"/>
-      <c r="W3" s="360"/>
-      <c r="X3" s="360"/>
-      <c r="Y3" s="360"/>
-      <c r="Z3" s="360"/>
-      <c r="AA3" s="360"/>
-      <c r="AB3" s="360"/>
-      <c r="AC3" s="360"/>
-      <c r="AD3" s="360"/>
-      <c r="AE3" s="360"/>
-      <c r="AF3" s="360"/>
-      <c r="AG3" s="360"/>
-      <c r="AH3" s="360"/>
-      <c r="AI3" s="360"/>
-      <c r="AJ3" s="360"/>
-      <c r="AK3" s="360"/>
-      <c r="AL3" s="360"/>
-      <c r="AM3" s="360"/>
-      <c r="AN3" s="360"/>
-      <c r="AO3" s="360"/>
-      <c r="AP3" s="360"/>
-      <c r="AQ3" s="360"/>
-      <c r="AR3" s="360"/>
-      <c r="AS3" s="360"/>
-      <c r="AT3" s="360"/>
-      <c r="AU3" s="360"/>
-      <c r="AV3" s="360"/>
-      <c r="AW3" s="360"/>
-      <c r="AX3" s="360"/>
-      <c r="AY3" s="360"/>
-      <c r="AZ3" s="360"/>
-      <c r="BA3" s="360"/>
-      <c r="BB3" s="360"/>
-      <c r="BC3" s="360"/>
-      <c r="BD3" s="360"/>
-      <c r="BE3" s="360"/>
-      <c r="BF3" s="360"/>
-      <c r="BG3" s="360"/>
-      <c r="BH3" s="360"/>
-      <c r="BI3" s="360"/>
-      <c r="BJ3" s="360"/>
-      <c r="BK3" s="360"/>
-      <c r="BL3" s="360"/>
-      <c r="BM3" s="360"/>
-      <c r="BN3" s="360"/>
-      <c r="BO3" s="360"/>
-      <c r="BP3" s="360"/>
-      <c r="BQ3" s="360"/>
-      <c r="BR3" s="360"/>
-      <c r="BS3" s="360"/>
-      <c r="BT3" s="360"/>
-      <c r="BU3" s="360"/>
-      <c r="BV3" s="298"/>
-      <c r="BW3" s="359" t="s">
+      <c r="A3" s="352"/>
+      <c r="B3" s="351"/>
+      <c r="C3" s="351"/>
+      <c r="D3" s="351"/>
+      <c r="E3" s="351"/>
+      <c r="F3" s="351"/>
+      <c r="G3" s="351"/>
+      <c r="H3" s="351"/>
+      <c r="I3" s="351"/>
+      <c r="J3" s="351"/>
+      <c r="K3" s="351"/>
+      <c r="L3" s="351"/>
+      <c r="M3" s="351"/>
+      <c r="N3" s="351"/>
+      <c r="O3" s="351"/>
+      <c r="P3" s="351"/>
+      <c r="Q3" s="351"/>
+      <c r="R3" s="351"/>
+      <c r="S3" s="351"/>
+      <c r="T3" s="351"/>
+      <c r="U3" s="351"/>
+      <c r="V3" s="351"/>
+      <c r="W3" s="351"/>
+      <c r="X3" s="351"/>
+      <c r="Y3" s="351"/>
+      <c r="Z3" s="351"/>
+      <c r="AA3" s="351"/>
+      <c r="AB3" s="351"/>
+      <c r="AC3" s="351"/>
+      <c r="AD3" s="351"/>
+      <c r="AE3" s="351"/>
+      <c r="AF3" s="351"/>
+      <c r="AG3" s="351"/>
+      <c r="AH3" s="351"/>
+      <c r="AI3" s="351"/>
+      <c r="AJ3" s="351"/>
+      <c r="AK3" s="351"/>
+      <c r="AL3" s="351"/>
+      <c r="AM3" s="351"/>
+      <c r="AN3" s="351"/>
+      <c r="AO3" s="351"/>
+      <c r="AP3" s="351"/>
+      <c r="AQ3" s="351"/>
+      <c r="AR3" s="351"/>
+      <c r="AS3" s="351"/>
+      <c r="AT3" s="351"/>
+      <c r="AU3" s="351"/>
+      <c r="AV3" s="351"/>
+      <c r="AW3" s="351"/>
+      <c r="AX3" s="351"/>
+      <c r="AY3" s="351"/>
+      <c r="AZ3" s="351"/>
+      <c r="BA3" s="351"/>
+      <c r="BB3" s="351"/>
+      <c r="BC3" s="351"/>
+      <c r="BD3" s="351"/>
+      <c r="BE3" s="351"/>
+      <c r="BF3" s="351"/>
+      <c r="BG3" s="351"/>
+      <c r="BH3" s="351"/>
+      <c r="BI3" s="351"/>
+      <c r="BJ3" s="351"/>
+      <c r="BK3" s="351"/>
+      <c r="BL3" s="351"/>
+      <c r="BM3" s="351"/>
+      <c r="BN3" s="351"/>
+      <c r="BO3" s="351"/>
+      <c r="BP3" s="351"/>
+      <c r="BQ3" s="351"/>
+      <c r="BR3" s="351"/>
+      <c r="BS3" s="351"/>
+      <c r="BT3" s="351"/>
+      <c r="BU3" s="351"/>
+      <c r="BV3" s="296"/>
+      <c r="BW3" s="350" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="360"/>
-      <c r="BY3" s="360"/>
-      <c r="BZ3" s="360"/>
-      <c r="CA3" s="360"/>
-      <c r="CB3" s="360"/>
-      <c r="CC3" s="300"/>
-      <c r="CD3" s="300"/>
+      <c r="BX3" s="351"/>
+      <c r="BY3" s="351"/>
+      <c r="BZ3" s="351"/>
+      <c r="CA3" s="351"/>
+      <c r="CB3" s="351"/>
+      <c r="CC3" s="298"/>
+      <c r="CD3" s="298"/>
     </row>
     <row r="4" spans="1:87" s="14" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
-      <c r="A4" s="301"/>
-      <c r="B4" s="301"/>
-      <c r="C4" s="301"/>
-      <c r="D4" s="301"/>
-      <c r="E4" s="301"/>
-      <c r="F4" s="301"/>
-      <c r="G4" s="301"/>
-      <c r="H4" s="301"/>
-      <c r="I4" s="288"/>
-      <c r="K4" s="301"/>
-      <c r="L4" s="301"/>
-      <c r="M4" s="301"/>
-      <c r="N4" s="301"/>
-      <c r="O4" s="301"/>
-      <c r="P4" s="301"/>
-      <c r="Q4" s="301"/>
-      <c r="R4" s="301"/>
-      <c r="S4" s="301"/>
-      <c r="T4" s="301"/>
-      <c r="U4" s="301"/>
-      <c r="V4" s="302"/>
-      <c r="W4" s="302"/>
-      <c r="X4" s="302"/>
-      <c r="Y4" s="302"/>
-      <c r="Z4" s="302"/>
-      <c r="AA4" s="302"/>
-      <c r="AB4" s="302"/>
-      <c r="AC4" s="302"/>
-      <c r="AD4" s="302"/>
-      <c r="AE4" s="302"/>
-      <c r="AF4" s="302"/>
-      <c r="AG4" s="302"/>
-      <c r="AH4" s="302"/>
-      <c r="AI4" s="302"/>
-      <c r="AJ4" s="302"/>
-      <c r="AK4" s="302"/>
-      <c r="AL4" s="302"/>
-      <c r="AM4" s="301"/>
-      <c r="AN4" s="301"/>
-      <c r="AO4" s="301"/>
-      <c r="AP4" s="301"/>
-      <c r="AQ4" s="301"/>
-      <c r="AR4" s="301"/>
-      <c r="AS4" s="301"/>
-      <c r="AT4" s="301"/>
-      <c r="AU4" s="301"/>
-      <c r="AV4" s="301"/>
-      <c r="AW4" s="301"/>
-      <c r="AX4" s="301"/>
-      <c r="AY4" s="301"/>
-      <c r="AZ4" s="301"/>
-      <c r="BA4" s="301"/>
-      <c r="BB4" s="301"/>
-      <c r="BC4" s="301"/>
-      <c r="BD4" s="301"/>
-      <c r="BE4" s="301"/>
-      <c r="BF4" s="301"/>
-      <c r="BG4" s="301"/>
-      <c r="BH4" s="301"/>
-      <c r="BI4" s="301"/>
-      <c r="BJ4" s="301"/>
-      <c r="BK4" s="301"/>
-      <c r="BL4" s="301"/>
-      <c r="BM4" s="301"/>
-      <c r="BN4" s="301"/>
-      <c r="BO4" s="301"/>
-      <c r="BP4" s="301"/>
-      <c r="BQ4" s="301"/>
-      <c r="BR4" s="301"/>
-      <c r="BS4" s="301"/>
-      <c r="BT4" s="301"/>
-      <c r="BU4" s="301"/>
-      <c r="BV4" s="301"/>
-      <c r="BW4" s="360"/>
-      <c r="BX4" s="360"/>
-      <c r="BY4" s="360"/>
-      <c r="BZ4" s="360"/>
-      <c r="CA4" s="360"/>
-      <c r="CB4" s="360"/>
-      <c r="CC4" s="300"/>
-      <c r="CD4" s="300"/>
+      <c r="A4" s="299"/>
+      <c r="B4" s="299"/>
+      <c r="C4" s="299"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
+      <c r="G4" s="299"/>
+      <c r="H4" s="299"/>
+      <c r="I4" s="286"/>
+      <c r="K4" s="299"/>
+      <c r="L4" s="299"/>
+      <c r="M4" s="299"/>
+      <c r="N4" s="299"/>
+      <c r="O4" s="299"/>
+      <c r="P4" s="299"/>
+      <c r="Q4" s="299"/>
+      <c r="R4" s="299"/>
+      <c r="S4" s="299"/>
+      <c r="T4" s="299"/>
+      <c r="U4" s="299"/>
+      <c r="V4" s="300"/>
+      <c r="W4" s="300"/>
+      <c r="X4" s="300"/>
+      <c r="Y4" s="300"/>
+      <c r="Z4" s="300"/>
+      <c r="AA4" s="300"/>
+      <c r="AB4" s="300"/>
+      <c r="AC4" s="300"/>
+      <c r="AD4" s="300"/>
+      <c r="AE4" s="300"/>
+      <c r="AF4" s="300"/>
+      <c r="AG4" s="300"/>
+      <c r="AH4" s="300"/>
+      <c r="AI4" s="300"/>
+      <c r="AJ4" s="300"/>
+      <c r="AK4" s="300"/>
+      <c r="AL4" s="300"/>
+      <c r="AM4" s="299"/>
+      <c r="AN4" s="299"/>
+      <c r="AO4" s="299"/>
+      <c r="AP4" s="299"/>
+      <c r="AQ4" s="299"/>
+      <c r="AR4" s="299"/>
+      <c r="AS4" s="299"/>
+      <c r="AT4" s="299"/>
+      <c r="AU4" s="299"/>
+      <c r="AV4" s="299"/>
+      <c r="AW4" s="299"/>
+      <c r="AX4" s="299"/>
+      <c r="AY4" s="299"/>
+      <c r="AZ4" s="299"/>
+      <c r="BA4" s="299"/>
+      <c r="BB4" s="299"/>
+      <c r="BC4" s="299"/>
+      <c r="BD4" s="299"/>
+      <c r="BE4" s="299"/>
+      <c r="BF4" s="299"/>
+      <c r="BG4" s="299"/>
+      <c r="BH4" s="299"/>
+      <c r="BI4" s="299"/>
+      <c r="BJ4" s="299"/>
+      <c r="BK4" s="299"/>
+      <c r="BL4" s="299"/>
+      <c r="BM4" s="299"/>
+      <c r="BN4" s="299"/>
+      <c r="BO4" s="299"/>
+      <c r="BP4" s="299"/>
+      <c r="BQ4" s="299"/>
+      <c r="BR4" s="299"/>
+      <c r="BS4" s="299"/>
+      <c r="BT4" s="299"/>
+      <c r="BU4" s="299"/>
+      <c r="BV4" s="299"/>
+      <c r="BW4" s="351"/>
+      <c r="BX4" s="351"/>
+      <c r="BY4" s="351"/>
+      <c r="BZ4" s="351"/>
+      <c r="CA4" s="351"/>
+      <c r="CB4" s="351"/>
+      <c r="CC4" s="298"/>
+      <c r="CD4" s="298"/>
     </row>
     <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
-      <c r="A5" s="301"/>
-      <c r="B5" s="301"/>
-      <c r="C5" s="301"/>
-      <c r="D5" s="301"/>
-      <c r="E5" s="301"/>
-      <c r="F5" s="301"/>
-      <c r="G5" s="301"/>
-      <c r="H5" s="301"/>
-      <c r="I5" s="288"/>
-      <c r="K5" s="301"/>
-      <c r="L5" s="301"/>
-      <c r="M5" s="301"/>
-      <c r="N5" s="301"/>
-      <c r="O5" s="301"/>
-      <c r="P5" s="301"/>
-      <c r="Q5" s="301"/>
-      <c r="R5" s="301"/>
-      <c r="S5" s="301"/>
-      <c r="T5" s="301"/>
-      <c r="U5" s="301"/>
-      <c r="V5" s="301"/>
-      <c r="W5" s="301"/>
-      <c r="X5" s="301"/>
-      <c r="Y5" s="301"/>
-      <c r="Z5" s="301"/>
-      <c r="AA5" s="301"/>
-      <c r="AB5" s="301"/>
-      <c r="AC5" s="301"/>
-      <c r="AD5" s="301"/>
-      <c r="AE5" s="301"/>
-      <c r="AF5" s="301"/>
-      <c r="AG5" s="301"/>
-      <c r="AH5" s="301"/>
-      <c r="AI5" s="301"/>
-      <c r="AJ5" s="301"/>
-      <c r="AK5" s="301"/>
-      <c r="AL5" s="301"/>
-      <c r="AM5" s="301"/>
-      <c r="AN5" s="301"/>
-      <c r="AO5" s="301"/>
-      <c r="AP5" s="301"/>
-      <c r="AQ5" s="301"/>
-      <c r="AR5" s="301"/>
-      <c r="AS5" s="301"/>
-      <c r="AT5" s="301"/>
-      <c r="AU5" s="301"/>
-      <c r="AV5" s="301"/>
-      <c r="AW5" s="301"/>
-      <c r="AX5" s="301"/>
-      <c r="AY5" s="301"/>
-      <c r="AZ5" s="301"/>
-      <c r="BA5" s="301"/>
-      <c r="BB5" s="301"/>
-      <c r="BC5" s="301"/>
-      <c r="BD5" s="301"/>
-      <c r="BE5" s="301"/>
-      <c r="BF5" s="301"/>
-      <c r="BG5" s="301"/>
-      <c r="BH5" s="301"/>
-      <c r="BI5" s="301"/>
-      <c r="BJ5" s="301"/>
-      <c r="BK5" s="301"/>
-      <c r="BL5" s="301"/>
-      <c r="BM5" s="301"/>
-      <c r="BN5" s="301"/>
-      <c r="BO5" s="301"/>
-      <c r="BP5" s="301"/>
-      <c r="BQ5" s="301"/>
-      <c r="BR5" s="301"/>
-      <c r="BS5" s="301"/>
-      <c r="BT5" s="301"/>
-      <c r="BU5" s="301"/>
-      <c r="BV5" s="301"/>
-      <c r="BW5" s="360"/>
-      <c r="BX5" s="360"/>
-      <c r="BY5" s="360"/>
-      <c r="BZ5" s="360"/>
-      <c r="CA5" s="360"/>
-      <c r="CB5" s="360"/>
-      <c r="CC5" s="300"/>
-      <c r="CD5" s="300"/>
+      <c r="A5" s="299"/>
+      <c r="B5" s="299"/>
+      <c r="C5" s="299"/>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
+      <c r="G5" s="299"/>
+      <c r="H5" s="299"/>
+      <c r="I5" s="286"/>
+      <c r="K5" s="299"/>
+      <c r="L5" s="299"/>
+      <c r="M5" s="299"/>
+      <c r="N5" s="299"/>
+      <c r="O5" s="299"/>
+      <c r="P5" s="299"/>
+      <c r="Q5" s="299"/>
+      <c r="R5" s="299"/>
+      <c r="S5" s="299"/>
+      <c r="T5" s="299"/>
+      <c r="U5" s="299"/>
+      <c r="V5" s="299"/>
+      <c r="W5" s="299"/>
+      <c r="X5" s="299"/>
+      <c r="Y5" s="299"/>
+      <c r="Z5" s="299"/>
+      <c r="AA5" s="299"/>
+      <c r="AB5" s="299"/>
+      <c r="AC5" s="299"/>
+      <c r="AD5" s="299"/>
+      <c r="AE5" s="299"/>
+      <c r="AF5" s="299"/>
+      <c r="AG5" s="299"/>
+      <c r="AH5" s="299"/>
+      <c r="AI5" s="299"/>
+      <c r="AJ5" s="299"/>
+      <c r="AK5" s="299"/>
+      <c r="AL5" s="299"/>
+      <c r="AM5" s="299"/>
+      <c r="AN5" s="299"/>
+      <c r="AO5" s="299"/>
+      <c r="AP5" s="299"/>
+      <c r="AQ5" s="299"/>
+      <c r="AR5" s="299"/>
+      <c r="AS5" s="299"/>
+      <c r="AT5" s="299"/>
+      <c r="AU5" s="299"/>
+      <c r="AV5" s="299"/>
+      <c r="AW5" s="299"/>
+      <c r="AX5" s="299"/>
+      <c r="AY5" s="299"/>
+      <c r="AZ5" s="299"/>
+      <c r="BA5" s="299"/>
+      <c r="BB5" s="299"/>
+      <c r="BC5" s="299"/>
+      <c r="BD5" s="299"/>
+      <c r="BE5" s="299"/>
+      <c r="BF5" s="299"/>
+      <c r="BG5" s="299"/>
+      <c r="BH5" s="299"/>
+      <c r="BI5" s="299"/>
+      <c r="BJ5" s="299"/>
+      <c r="BK5" s="299"/>
+      <c r="BL5" s="299"/>
+      <c r="BM5" s="299"/>
+      <c r="BN5" s="299"/>
+      <c r="BO5" s="299"/>
+      <c r="BP5" s="299"/>
+      <c r="BQ5" s="299"/>
+      <c r="BR5" s="299"/>
+      <c r="BS5" s="299"/>
+      <c r="BT5" s="299"/>
+      <c r="BU5" s="299"/>
+      <c r="BV5" s="299"/>
+      <c r="BW5" s="351"/>
+      <c r="BX5" s="351"/>
+      <c r="BY5" s="351"/>
+      <c r="BZ5" s="351"/>
+      <c r="CA5" s="351"/>
+      <c r="CB5" s="351"/>
+      <c r="CC5" s="298"/>
+      <c r="CD5" s="298"/>
     </row>
     <row r="6" spans="1:87" s="14" customFormat="1" ht="34" customHeight="1" outlineLevel="1">
-      <c r="A6" s="303"/>
-      <c r="D6" s="303"/>
-      <c r="E6" s="303"/>
-      <c r="F6" s="303"/>
-      <c r="G6" s="303"/>
-      <c r="H6" s="303"/>
-      <c r="I6" s="288"/>
-      <c r="K6" s="304"/>
-      <c r="L6" s="304"/>
-      <c r="M6" s="304"/>
-      <c r="N6" s="304"/>
-      <c r="O6" s="304"/>
-      <c r="P6" s="304"/>
-      <c r="Q6" s="304"/>
-      <c r="R6" s="304"/>
-      <c r="S6" s="304"/>
-      <c r="T6" s="304"/>
-      <c r="U6" s="304"/>
-      <c r="V6" s="304"/>
-      <c r="W6" s="304"/>
-      <c r="X6" s="304"/>
-      <c r="Y6" s="305"/>
-      <c r="Z6" s="305"/>
-      <c r="AA6" s="305"/>
-      <c r="AB6" s="305"/>
-      <c r="AC6" s="301"/>
-      <c r="AD6" s="303"/>
-      <c r="AE6" s="303"/>
-      <c r="AF6" s="303"/>
-      <c r="AG6" s="303"/>
-      <c r="AH6" s="303"/>
-      <c r="AI6" s="303"/>
-      <c r="AJ6" s="303"/>
-      <c r="AK6" s="303"/>
-      <c r="AL6" s="303"/>
-      <c r="AM6" s="303"/>
-      <c r="AN6" s="303"/>
-      <c r="AO6" s="303"/>
-      <c r="AP6" s="303"/>
-      <c r="AQ6" s="303"/>
-      <c r="AR6" s="303"/>
-      <c r="AS6" s="303"/>
-      <c r="AT6" s="303"/>
-      <c r="AU6" s="303"/>
-      <c r="AV6" s="303"/>
-      <c r="AW6" s="303"/>
-      <c r="AX6" s="303"/>
-      <c r="AY6" s="303"/>
-      <c r="AZ6" s="303"/>
-      <c r="BA6" s="303"/>
-      <c r="BB6" s="303"/>
-      <c r="BC6" s="303"/>
-      <c r="BD6" s="303"/>
-      <c r="BE6" s="303"/>
-      <c r="BF6" s="303"/>
-      <c r="BG6" s="303"/>
-      <c r="BH6" s="303"/>
-      <c r="BI6" s="303"/>
-      <c r="BJ6" s="303"/>
-      <c r="BK6" s="303"/>
-      <c r="BL6" s="303"/>
-      <c r="BM6" s="303"/>
-      <c r="BN6" s="303"/>
-      <c r="BO6" s="303"/>
-      <c r="BP6" s="303"/>
-      <c r="BQ6" s="303"/>
-      <c r="BR6" s="303"/>
-      <c r="BS6" s="303"/>
-      <c r="BT6" s="303"/>
-      <c r="BU6" s="303"/>
-      <c r="BV6" s="303"/>
-      <c r="BW6" s="360"/>
-      <c r="BX6" s="360"/>
-      <c r="BY6" s="360"/>
-      <c r="BZ6" s="360"/>
-      <c r="CA6" s="360"/>
-      <c r="CB6" s="360"/>
-      <c r="CC6" s="300"/>
-      <c r="CD6" s="300"/>
+      <c r="A6" s="301"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="301"/>
+      <c r="G6" s="301"/>
+      <c r="H6" s="301"/>
+      <c r="I6" s="286"/>
+      <c r="K6" s="302"/>
+      <c r="L6" s="302"/>
+      <c r="M6" s="302"/>
+      <c r="N6" s="302"/>
+      <c r="O6" s="302"/>
+      <c r="P6" s="302"/>
+      <c r="Q6" s="302"/>
+      <c r="R6" s="302"/>
+      <c r="S6" s="302"/>
+      <c r="T6" s="302"/>
+      <c r="U6" s="302"/>
+      <c r="V6" s="302"/>
+      <c r="W6" s="302"/>
+      <c r="X6" s="302"/>
+      <c r="Y6" s="303"/>
+      <c r="Z6" s="303"/>
+      <c r="AA6" s="303"/>
+      <c r="AB6" s="303"/>
+      <c r="AC6" s="299"/>
+      <c r="AD6" s="301"/>
+      <c r="AE6" s="301"/>
+      <c r="AF6" s="301"/>
+      <c r="AG6" s="301"/>
+      <c r="AH6" s="301"/>
+      <c r="AI6" s="301"/>
+      <c r="AJ6" s="301"/>
+      <c r="AK6" s="301"/>
+      <c r="AL6" s="301"/>
+      <c r="AM6" s="301"/>
+      <c r="AN6" s="301"/>
+      <c r="AO6" s="301"/>
+      <c r="AP6" s="301"/>
+      <c r="AQ6" s="301"/>
+      <c r="AR6" s="301"/>
+      <c r="AS6" s="301"/>
+      <c r="AT6" s="301"/>
+      <c r="AU6" s="301"/>
+      <c r="AV6" s="301"/>
+      <c r="AW6" s="301"/>
+      <c r="AX6" s="301"/>
+      <c r="AY6" s="301"/>
+      <c r="AZ6" s="301"/>
+      <c r="BA6" s="301"/>
+      <c r="BB6" s="301"/>
+      <c r="BC6" s="301"/>
+      <c r="BD6" s="301"/>
+      <c r="BE6" s="301"/>
+      <c r="BF6" s="301"/>
+      <c r="BG6" s="301"/>
+      <c r="BH6" s="301"/>
+      <c r="BI6" s="301"/>
+      <c r="BJ6" s="301"/>
+      <c r="BK6" s="301"/>
+      <c r="BL6" s="301"/>
+      <c r="BM6" s="301"/>
+      <c r="BN6" s="301"/>
+      <c r="BO6" s="301"/>
+      <c r="BP6" s="301"/>
+      <c r="BQ6" s="301"/>
+      <c r="BR6" s="301"/>
+      <c r="BS6" s="301"/>
+      <c r="BT6" s="301"/>
+      <c r="BU6" s="301"/>
+      <c r="BV6" s="301"/>
+      <c r="BW6" s="351"/>
+      <c r="BX6" s="351"/>
+      <c r="BY6" s="351"/>
+      <c r="BZ6" s="351"/>
+      <c r="CA6" s="351"/>
+      <c r="CB6" s="351"/>
+      <c r="CC6" s="298"/>
+      <c r="CD6" s="298"/>
     </row>
-    <row r="7" spans="1:87" s="323" customFormat="1" ht="31" outlineLevel="1">
-      <c r="B7" s="303" t="s">
+    <row r="7" spans="1:87" s="321" customFormat="1" ht="31" outlineLevel="1">
+      <c r="B7" s="301" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="303" t="s">
+      <c r="C7" s="301" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="324"/>
-      <c r="E7" s="324" t="s">
+      <c r="D7" s="322"/>
+      <c r="E7" s="322" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="325"/>
-      <c r="G7" s="324" t="s">
+      <c r="F7" s="323"/>
+      <c r="G7" s="322" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="324"/>
-      <c r="I7" s="326" t="s">
+      <c r="H7" s="322"/>
+      <c r="I7" s="324" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="323" t="s">
+      <c r="J7" s="321" t="s">
         <v>157</v>
       </c>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
-      <c r="O7" s="327"/>
-      <c r="Q7" s="327"/>
-      <c r="R7" s="327"/>
-      <c r="S7" s="327"/>
-      <c r="T7" s="327"/>
-      <c r="U7" s="328"/>
-      <c r="V7" s="327"/>
-      <c r="W7" s="327"/>
-      <c r="X7" s="327"/>
-      <c r="Y7" s="329" t="s">
+      <c r="K7" s="325"/>
+      <c r="L7" s="325"/>
+      <c r="M7" s="325"/>
+      <c r="N7" s="325"/>
+      <c r="O7" s="325"/>
+      <c r="Q7" s="325"/>
+      <c r="R7" s="325"/>
+      <c r="S7" s="325"/>
+      <c r="T7" s="325"/>
+      <c r="U7" s="326"/>
+      <c r="V7" s="325"/>
+      <c r="W7" s="325"/>
+      <c r="X7" s="325"/>
+      <c r="Y7" s="327" t="s">
         <v>158</v>
       </c>
-      <c r="Z7" s="329" t="s">
+      <c r="Z7" s="327" t="s">
         <v>158</v>
       </c>
-      <c r="AA7" s="329" t="s">
+      <c r="AA7" s="327" t="s">
         <v>158</v>
       </c>
-      <c r="AB7" s="329"/>
-      <c r="AC7" s="327" t="s">
+      <c r="AB7" s="327"/>
+      <c r="AC7" s="325" t="s">
         <v>158</v>
       </c>
-      <c r="AD7" s="303" t="s">
+      <c r="AD7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AE7" s="303" t="s">
+      <c r="AE7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AF7" s="303"/>
-      <c r="AG7" s="303"/>
-      <c r="AH7" s="303" t="s">
+      <c r="AF7" s="301"/>
+      <c r="AG7" s="301"/>
+      <c r="AH7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AI7" s="303" t="s">
+      <c r="AI7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AJ7" s="303"/>
-      <c r="AK7" s="303"/>
-      <c r="AL7" s="303" t="s">
+      <c r="AJ7" s="301"/>
+      <c r="AK7" s="301"/>
+      <c r="AL7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AM7" s="303" t="s">
+      <c r="AM7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AN7" s="303" t="s">
+      <c r="AN7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AO7" s="303" t="s">
+      <c r="AO7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AP7" s="303" t="s">
+      <c r="AP7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AQ7" s="303"/>
-      <c r="AR7" s="303" t="s">
+      <c r="AQ7" s="301"/>
+      <c r="AR7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AS7" s="303" t="s">
+      <c r="AS7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AT7" s="303" t="s">
+      <c r="AT7" s="301" t="s">
         <v>156</v>
       </c>
-      <c r="AU7" s="303" t="s">
+      <c r="AU7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AY7" s="324"/>
-      <c r="BA7" s="324"/>
-      <c r="BB7" s="324" t="s">
+      <c r="AY7" s="322"/>
+      <c r="BA7" s="322"/>
+      <c r="BB7" s="322" t="s">
         <v>160</v>
       </c>
-      <c r="BE7" s="324"/>
-      <c r="BF7" s="324"/>
-      <c r="BG7" s="324"/>
-      <c r="BH7" s="324"/>
-      <c r="BI7" s="324" t="s">
+      <c r="BE7" s="322"/>
+      <c r="BF7" s="322"/>
+      <c r="BG7" s="322"/>
+      <c r="BH7" s="322"/>
+      <c r="BI7" s="322" t="s">
         <v>160</v>
       </c>
-      <c r="BJ7" s="324"/>
-      <c r="BK7" s="324"/>
-      <c r="BL7" s="323" t="s">
+      <c r="BJ7" s="322"/>
+      <c r="BK7" s="322"/>
+      <c r="BL7" s="321" t="s">
         <v>160</v>
       </c>
-      <c r="BN7" s="324"/>
-      <c r="BP7" s="324"/>
-      <c r="BT7" s="324" t="s">
+      <c r="BN7" s="322"/>
+      <c r="BP7" s="322"/>
+      <c r="BT7" s="322" t="s">
         <v>161</v>
       </c>
-      <c r="BU7" s="323" t="s">
+      <c r="BU7" s="321" t="s">
         <v>161</v>
       </c>
-      <c r="BW7" s="299"/>
-      <c r="BX7" s="299" t="s">
+      <c r="BW7" s="297"/>
+      <c r="BX7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="BY7" s="299" t="s">
+      <c r="BY7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="BZ7" s="299"/>
-      <c r="CA7" s="299" t="s">
+      <c r="BZ7" s="297"/>
+      <c r="CA7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="CB7" s="328"/>
-      <c r="CC7" s="328"/>
-      <c r="CD7" s="328"/>
-      <c r="CE7" s="303" t="s">
+      <c r="CB7" s="326"/>
+      <c r="CC7" s="326"/>
+      <c r="CD7" s="326"/>
+      <c r="CE7" s="301" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="369" t="s">
+    <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="349" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="363" t="s">
+      <c r="B8" s="354" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="333" t="s">
+      <c r="C8" s="337" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="351" t="s">
+      <c r="D8" s="341" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="351" t="s">
+      <c r="E8" s="341" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="333" t="s">
+      <c r="F8" s="337" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="352" t="s">
+      <c r="G8" s="426" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="330" t="s">
+      <c r="H8" s="348" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="330" t="s">
+      <c r="I8" s="348" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="330" t="s">
+      <c r="J8" s="429" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="364" t="s">
+      <c r="K8" s="362" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="365"/>
-      <c r="M8" s="365"/>
-      <c r="N8" s="365"/>
-      <c r="O8" s="365"/>
-      <c r="P8" s="365"/>
-      <c r="Q8" s="365"/>
-      <c r="R8" s="365"/>
-      <c r="S8" s="365"/>
-      <c r="T8" s="365"/>
-      <c r="U8" s="365"/>
-      <c r="V8" s="365"/>
-      <c r="W8" s="365"/>
-      <c r="X8" s="365"/>
-      <c r="Y8" s="368" t="s">
+      <c r="L8" s="363"/>
+      <c r="M8" s="363"/>
+      <c r="N8" s="363"/>
+      <c r="O8" s="363"/>
+      <c r="P8" s="363"/>
+      <c r="Q8" s="363"/>
+      <c r="R8" s="363"/>
+      <c r="S8" s="363"/>
+      <c r="T8" s="363"/>
+      <c r="U8" s="363"/>
+      <c r="V8" s="363"/>
+      <c r="W8" s="363"/>
+      <c r="X8" s="363"/>
+      <c r="Y8" s="367" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="365"/>
-      <c r="AA8" s="365"/>
-      <c r="AB8" s="365"/>
-      <c r="AC8" s="365"/>
-      <c r="AD8" s="365"/>
-      <c r="AE8" s="365"/>
-      <c r="AF8" s="365"/>
-      <c r="AG8" s="365"/>
-      <c r="AH8" s="365"/>
-      <c r="AI8" s="365"/>
-      <c r="AJ8" s="365"/>
-      <c r="AK8" s="365"/>
-      <c r="AL8" s="365"/>
-      <c r="AM8" s="365"/>
-      <c r="AN8" s="365"/>
-      <c r="AO8" s="367"/>
-      <c r="AP8" s="330" t="s">
+      <c r="Z8" s="363"/>
+      <c r="AA8" s="363"/>
+      <c r="AB8" s="363"/>
+      <c r="AC8" s="363"/>
+      <c r="AD8" s="363"/>
+      <c r="AE8" s="363"/>
+      <c r="AF8" s="363"/>
+      <c r="AG8" s="363"/>
+      <c r="AH8" s="363"/>
+      <c r="AI8" s="363"/>
+      <c r="AJ8" s="363"/>
+      <c r="AK8" s="363"/>
+      <c r="AL8" s="363"/>
+      <c r="AM8" s="363"/>
+      <c r="AN8" s="363"/>
+      <c r="AO8" s="365"/>
+      <c r="AP8" s="429" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="330" t="s">
+      <c r="AQ8" s="429" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="330" t="s">
+      <c r="AR8" s="429" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="330" t="s">
+      <c r="AS8" s="429" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="330" t="s">
+      <c r="AT8" s="429" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="330" t="s">
+      <c r="AU8" s="429" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="333" t="s">
+      <c r="AV8" s="337" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="342" t="s">
+      <c r="AW8" s="434" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="342" t="s">
+      <c r="AX8" s="433" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="366" t="s">
+      <c r="AY8" s="364" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="365"/>
-      <c r="BA8" s="365"/>
-      <c r="BB8" s="365"/>
-      <c r="BC8" s="365"/>
-      <c r="BD8" s="365"/>
-      <c r="BE8" s="365"/>
-      <c r="BF8" s="365"/>
-      <c r="BG8" s="365"/>
-      <c r="BH8" s="365"/>
-      <c r="BI8" s="365"/>
-      <c r="BJ8" s="365"/>
-      <c r="BK8" s="365"/>
-      <c r="BL8" s="365"/>
-      <c r="BM8" s="365"/>
-      <c r="BN8" s="365"/>
-      <c r="BO8" s="365"/>
-      <c r="BP8" s="365"/>
-      <c r="BQ8" s="367"/>
-      <c r="BR8" s="343" t="s">
+      <c r="AZ8" s="363"/>
+      <c r="BA8" s="363"/>
+      <c r="BB8" s="363"/>
+      <c r="BC8" s="363"/>
+      <c r="BD8" s="363"/>
+      <c r="BE8" s="363"/>
+      <c r="BF8" s="363"/>
+      <c r="BG8" s="363"/>
+      <c r="BH8" s="363"/>
+      <c r="BI8" s="363"/>
+      <c r="BJ8" s="363"/>
+      <c r="BK8" s="363"/>
+      <c r="BL8" s="363"/>
+      <c r="BM8" s="363"/>
+      <c r="BN8" s="363"/>
+      <c r="BO8" s="363"/>
+      <c r="BP8" s="363"/>
+      <c r="BQ8" s="365"/>
+      <c r="BR8" s="368" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="344"/>
-      <c r="BT8" s="333" t="s">
+      <c r="BS8" s="359"/>
+      <c r="BT8" s="337" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="339" t="s">
+      <c r="BU8" s="355" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="22"/>
-      <c r="BW8" s="379" t="s">
+      <c r="BW8" s="437" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="370" t="s">
+      <c r="BX8" s="328" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="371"/>
-      <c r="BZ8" s="371"/>
-      <c r="CA8" s="372"/>
-      <c r="CB8" s="345" t="s">
+      <c r="BY8" s="329"/>
+      <c r="BZ8" s="329"/>
+      <c r="CA8" s="330"/>
+      <c r="CB8" s="369" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="337" t="s">
+      <c r="CC8" s="442" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="337" t="s">
+      <c r="CD8" s="442" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
-    <row r="9" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="331"/>
-      <c r="B9" s="334"/>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="331"/>
-      <c r="I9" s="331"/>
-      <c r="J9" s="331"/>
-      <c r="K9" s="350" t="s">
+    <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="346"/>
+      <c r="B9" s="338"/>
+      <c r="C9" s="338"/>
+      <c r="D9" s="338"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="338"/>
+      <c r="G9" s="427"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="430"/>
+      <c r="K9" s="345" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="350" t="s">
+      <c r="L9" s="345" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="350" t="s">
+      <c r="M9" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="350" t="s">
+      <c r="N9" s="345" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="350" t="s">
+      <c r="O9" s="345" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="350" t="s">
+      <c r="P9" s="345" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="350" t="s">
+      <c r="Q9" s="345" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="350" t="s">
+      <c r="R9" s="345" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="350" t="s">
+      <c r="S9" s="345" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="350" t="s">
+      <c r="T9" s="345" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="350" t="s">
+      <c r="U9" s="345" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="355" t="s">
+      <c r="V9" s="358" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="344"/>
-      <c r="X9" s="350" t="s">
+      <c r="W9" s="359"/>
+      <c r="X9" s="345" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="336" t="s">
+      <c r="Y9" s="340" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="336" t="s">
+      <c r="Z9" s="340" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="336" t="s">
+      <c r="AA9" s="340" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="336" t="s">
+      <c r="AB9" s="340" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="336" t="s">
+      <c r="AC9" s="340" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="336" t="s">
+      <c r="AD9" s="340" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="336" t="s">
+      <c r="AE9" s="340" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="336" t="s">
+      <c r="AF9" s="340" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="336" t="s">
+      <c r="AG9" s="340" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="336" t="s">
+      <c r="AH9" s="340" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="336" t="s">
+      <c r="AI9" s="340" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="336" t="s">
+      <c r="AJ9" s="432" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="339" t="s">
+      <c r="AK9" s="355" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="333" t="s">
+      <c r="AL9" s="433" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="336" t="s">
+      <c r="AM9" s="340" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="333" t="s">
+      <c r="AN9" s="337" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="333" t="s">
+      <c r="AO9" s="337" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="331"/>
-      <c r="AQ9" s="331"/>
-      <c r="AR9" s="331"/>
-      <c r="AS9" s="331"/>
-      <c r="AT9" s="331"/>
-      <c r="AU9" s="331"/>
-      <c r="AV9" s="334"/>
-      <c r="AW9" s="331"/>
-      <c r="AX9" s="331"/>
-      <c r="AY9" s="347" t="s">
+      <c r="AP9" s="430"/>
+      <c r="AQ9" s="430"/>
+      <c r="AR9" s="430"/>
+      <c r="AS9" s="430"/>
+      <c r="AT9" s="430"/>
+      <c r="AU9" s="430"/>
+      <c r="AV9" s="338"/>
+      <c r="AW9" s="430"/>
+      <c r="AX9" s="427"/>
+      <c r="AY9" s="371" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="348"/>
-      <c r="BA9" s="348"/>
-      <c r="BB9" s="348"/>
-      <c r="BC9" s="348"/>
-      <c r="BD9" s="348"/>
-      <c r="BE9" s="348"/>
-      <c r="BF9" s="348"/>
-      <c r="BG9" s="348"/>
-      <c r="BH9" s="348"/>
-      <c r="BI9" s="348"/>
-      <c r="BJ9" s="348"/>
-      <c r="BK9" s="348"/>
-      <c r="BL9" s="349"/>
-      <c r="BM9" s="347" t="s">
+      <c r="AZ9" s="372"/>
+      <c r="BA9" s="372"/>
+      <c r="BB9" s="372"/>
+      <c r="BC9" s="372"/>
+      <c r="BD9" s="372"/>
+      <c r="BE9" s="372"/>
+      <c r="BF9" s="372"/>
+      <c r="BG9" s="372"/>
+      <c r="BH9" s="372"/>
+      <c r="BI9" s="372"/>
+      <c r="BJ9" s="372"/>
+      <c r="BK9" s="372"/>
+      <c r="BL9" s="373"/>
+      <c r="BM9" s="371" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="348"/>
-      <c r="BO9" s="348"/>
-      <c r="BP9" s="348"/>
-      <c r="BQ9" s="349"/>
-      <c r="BR9" s="353" t="s">
+      <c r="BN9" s="372"/>
+      <c r="BO9" s="372"/>
+      <c r="BP9" s="372"/>
+      <c r="BQ9" s="373"/>
+      <c r="BR9" s="347" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="353" t="s">
+      <c r="BS9" s="347" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="334"/>
-      <c r="BU9" s="340"/>
+      <c r="BT9" s="338"/>
+      <c r="BU9" s="356"/>
       <c r="BV9" s="22"/>
-      <c r="BW9" s="380"/>
-      <c r="BX9" s="373"/>
-      <c r="BY9" s="374"/>
-      <c r="BZ9" s="374"/>
-      <c r="CA9" s="375"/>
-      <c r="CB9" s="334"/>
-      <c r="CC9" s="331"/>
-      <c r="CD9" s="331"/>
+      <c r="BW9" s="438"/>
+      <c r="BX9" s="331"/>
+      <c r="BY9" s="332"/>
+      <c r="BZ9" s="332"/>
+      <c r="CA9" s="333"/>
+      <c r="CB9" s="338"/>
+      <c r="CC9" s="430"/>
+      <c r="CD9" s="430"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
-    <row r="10" spans="1:87" s="307" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="331"/>
-      <c r="B10" s="334"/>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="331"/>
-      <c r="I10" s="331"/>
-      <c r="J10" s="331"/>
-      <c r="K10" s="331"/>
-      <c r="L10" s="331"/>
-      <c r="M10" s="331"/>
-      <c r="N10" s="331"/>
-      <c r="O10" s="331"/>
-      <c r="P10" s="331"/>
-      <c r="Q10" s="331"/>
-      <c r="R10" s="331"/>
-      <c r="S10" s="331"/>
-      <c r="T10" s="331"/>
-      <c r="U10" s="331"/>
-      <c r="V10" s="356"/>
-      <c r="W10" s="357"/>
-      <c r="X10" s="331"/>
-      <c r="Y10" s="334"/>
-      <c r="Z10" s="334"/>
-      <c r="AA10" s="334"/>
-      <c r="AB10" s="334"/>
-      <c r="AC10" s="334"/>
-      <c r="AD10" s="334"/>
-      <c r="AE10" s="334"/>
-      <c r="AF10" s="334"/>
-      <c r="AG10" s="334"/>
-      <c r="AH10" s="334"/>
-      <c r="AI10" s="334"/>
-      <c r="AJ10" s="334"/>
-      <c r="AK10" s="340"/>
-      <c r="AL10" s="334"/>
-      <c r="AM10" s="334"/>
-      <c r="AN10" s="334"/>
-      <c r="AO10" s="334"/>
-      <c r="AP10" s="331"/>
-      <c r="AQ10" s="331"/>
-      <c r="AR10" s="331"/>
-      <c r="AS10" s="331"/>
-      <c r="AT10" s="331"/>
-      <c r="AU10" s="331"/>
-      <c r="AV10" s="334"/>
-      <c r="AW10" s="331"/>
-      <c r="AX10" s="331"/>
+    <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="346"/>
+      <c r="B10" s="338"/>
+      <c r="C10" s="338"/>
+      <c r="D10" s="338"/>
+      <c r="E10" s="338"/>
+      <c r="F10" s="338"/>
+      <c r="G10" s="427"/>
+      <c r="H10" s="346"/>
+      <c r="I10" s="346"/>
+      <c r="J10" s="430"/>
+      <c r="K10" s="346"/>
+      <c r="L10" s="346"/>
+      <c r="M10" s="346"/>
+      <c r="N10" s="346"/>
+      <c r="O10" s="346"/>
+      <c r="P10" s="346"/>
+      <c r="Q10" s="346"/>
+      <c r="R10" s="346"/>
+      <c r="S10" s="346"/>
+      <c r="T10" s="346"/>
+      <c r="U10" s="346"/>
+      <c r="V10" s="360"/>
+      <c r="W10" s="361"/>
+      <c r="X10" s="346"/>
+      <c r="Y10" s="338"/>
+      <c r="Z10" s="338"/>
+      <c r="AA10" s="338"/>
+      <c r="AB10" s="338"/>
+      <c r="AC10" s="338"/>
+      <c r="AD10" s="338"/>
+      <c r="AE10" s="338"/>
+      <c r="AF10" s="338"/>
+      <c r="AG10" s="338"/>
+      <c r="AH10" s="338"/>
+      <c r="AI10" s="338"/>
+      <c r="AJ10" s="427"/>
+      <c r="AK10" s="356"/>
+      <c r="AL10" s="427"/>
+      <c r="AM10" s="338"/>
+      <c r="AN10" s="338"/>
+      <c r="AO10" s="338"/>
+      <c r="AP10" s="430"/>
+      <c r="AQ10" s="430"/>
+      <c r="AR10" s="430"/>
+      <c r="AS10" s="430"/>
+      <c r="AT10" s="430"/>
+      <c r="AU10" s="430"/>
+      <c r="AV10" s="338"/>
+      <c r="AW10" s="430"/>
+      <c r="AX10" s="427"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8565,578 +8616,578 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="362" t="s">
+      <c r="BB10" s="353" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="354" t="s">
+      <c r="BC10" s="435" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="354" t="s">
+      <c r="BD10" s="435" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="358" t="s">
+      <c r="BE10" s="342" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="358" t="s">
+      <c r="BF10" s="342" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="354" t="s">
+      <c r="BG10" s="343" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="354" t="s">
+      <c r="BH10" s="435" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="358" t="s">
+      <c r="BI10" s="436" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="358" t="s">
+      <c r="BJ10" s="342" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="358" t="s">
+      <c r="BK10" s="342" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="333" t="s">
+      <c r="BL10" s="337" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="354" t="s">
+      <c r="BM10" s="435" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="342" t="s">
+      <c r="BN10" s="434" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="354" t="s">
+      <c r="BO10" s="435" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="342" t="s">
+      <c r="BP10" s="434" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="342" t="s">
+      <c r="BQ10" s="434" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="331"/>
-      <c r="BS10" s="331"/>
-      <c r="BT10" s="334"/>
-      <c r="BU10" s="340"/>
+      <c r="BR10" s="346"/>
+      <c r="BS10" s="346"/>
+      <c r="BT10" s="338"/>
+      <c r="BU10" s="356"/>
       <c r="BV10" s="22"/>
-      <c r="BW10" s="380"/>
-      <c r="BX10" s="376"/>
-      <c r="BY10" s="377"/>
-      <c r="BZ10" s="377"/>
-      <c r="CA10" s="378"/>
-      <c r="CB10" s="334"/>
-      <c r="CC10" s="331"/>
-      <c r="CD10" s="331"/>
-      <c r="CE10" s="321" t="s">
+      <c r="BW10" s="438"/>
+      <c r="BX10" s="334"/>
+      <c r="BY10" s="335"/>
+      <c r="BZ10" s="335"/>
+      <c r="CA10" s="336"/>
+      <c r="CB10" s="338"/>
+      <c r="CC10" s="430"/>
+      <c r="CD10" s="430"/>
+      <c r="CE10" s="319" t="s">
         <v>3</v>
       </c>
       <c r="CH10" s="241"/>
       <c r="CI10" s="241"/>
     </row>
-    <row r="11" spans="1:87" s="307" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="332"/>
-      <c r="B11" s="335"/>
-      <c r="C11" s="335"/>
-      <c r="D11" s="335"/>
-      <c r="E11" s="335"/>
-      <c r="F11" s="335"/>
-      <c r="G11" s="335"/>
-      <c r="H11" s="332"/>
-      <c r="I11" s="332"/>
-      <c r="J11" s="332"/>
-      <c r="K11" s="332"/>
-      <c r="L11" s="332"/>
-      <c r="M11" s="332"/>
-      <c r="N11" s="332"/>
-      <c r="O11" s="332"/>
-      <c r="P11" s="332"/>
-      <c r="Q11" s="332"/>
-      <c r="R11" s="332"/>
-      <c r="S11" s="332"/>
-      <c r="T11" s="332"/>
-      <c r="U11" s="332"/>
+    <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="344"/>
+      <c r="B11" s="339"/>
+      <c r="C11" s="339"/>
+      <c r="D11" s="339"/>
+      <c r="E11" s="339"/>
+      <c r="F11" s="339"/>
+      <c r="G11" s="428"/>
+      <c r="H11" s="344"/>
+      <c r="I11" s="344"/>
+      <c r="J11" s="431"/>
+      <c r="K11" s="344"/>
+      <c r="L11" s="344"/>
+      <c r="M11" s="344"/>
+      <c r="N11" s="344"/>
+      <c r="O11" s="344"/>
+      <c r="P11" s="344"/>
+      <c r="Q11" s="344"/>
+      <c r="R11" s="344"/>
+      <c r="S11" s="344"/>
+      <c r="T11" s="344"/>
+      <c r="U11" s="344"/>
       <c r="V11" s="269" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="269" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="332"/>
-      <c r="Y11" s="335"/>
-      <c r="Z11" s="335"/>
-      <c r="AA11" s="335"/>
-      <c r="AB11" s="335"/>
-      <c r="AC11" s="335"/>
-      <c r="AD11" s="335"/>
-      <c r="AE11" s="335"/>
-      <c r="AF11" s="335"/>
-      <c r="AG11" s="335"/>
-      <c r="AH11" s="335"/>
-      <c r="AI11" s="335"/>
-      <c r="AJ11" s="335"/>
-      <c r="AK11" s="341"/>
-      <c r="AL11" s="335"/>
-      <c r="AM11" s="335"/>
-      <c r="AN11" s="335"/>
-      <c r="AO11" s="335"/>
-      <c r="AP11" s="332"/>
-      <c r="AQ11" s="332"/>
-      <c r="AR11" s="332"/>
-      <c r="AS11" s="332"/>
-      <c r="AT11" s="332"/>
-      <c r="AU11" s="332"/>
-      <c r="AV11" s="335"/>
-      <c r="AW11" s="332"/>
-      <c r="AX11" s="332"/>
-      <c r="AY11" s="322" t="s">
+      <c r="X11" s="344"/>
+      <c r="Y11" s="339"/>
+      <c r="Z11" s="339"/>
+      <c r="AA11" s="339"/>
+      <c r="AB11" s="339"/>
+      <c r="AC11" s="339"/>
+      <c r="AD11" s="339"/>
+      <c r="AE11" s="339"/>
+      <c r="AF11" s="339"/>
+      <c r="AG11" s="339"/>
+      <c r="AH11" s="339"/>
+      <c r="AI11" s="339"/>
+      <c r="AJ11" s="428"/>
+      <c r="AK11" s="357"/>
+      <c r="AL11" s="428"/>
+      <c r="AM11" s="339"/>
+      <c r="AN11" s="339"/>
+      <c r="AO11" s="339"/>
+      <c r="AP11" s="431"/>
+      <c r="AQ11" s="431"/>
+      <c r="AR11" s="431"/>
+      <c r="AS11" s="431"/>
+      <c r="AT11" s="431"/>
+      <c r="AU11" s="431"/>
+      <c r="AV11" s="339"/>
+      <c r="AW11" s="431"/>
+      <c r="AX11" s="428"/>
+      <c r="AY11" s="320" t="s">
         <v>88</v>
       </c>
-      <c r="AZ11" s="322" t="s">
+      <c r="AZ11" s="320" t="s">
         <v>89</v>
       </c>
-      <c r="BA11" s="322" t="s">
+      <c r="BA11" s="320" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="335"/>
-      <c r="BC11" s="332"/>
-      <c r="BD11" s="332"/>
-      <c r="BE11" s="335"/>
-      <c r="BF11" s="335"/>
-      <c r="BG11" s="332"/>
-      <c r="BH11" s="332"/>
-      <c r="BI11" s="335"/>
-      <c r="BJ11" s="335"/>
-      <c r="BK11" s="335"/>
-      <c r="BL11" s="335"/>
-      <c r="BM11" s="332"/>
-      <c r="BN11" s="332"/>
-      <c r="BO11" s="332"/>
-      <c r="BP11" s="332"/>
-      <c r="BQ11" s="332"/>
-      <c r="BR11" s="332"/>
-      <c r="BS11" s="332"/>
-      <c r="BT11" s="335"/>
-      <c r="BU11" s="341"/>
+      <c r="BB11" s="339"/>
+      <c r="BC11" s="431"/>
+      <c r="BD11" s="431"/>
+      <c r="BE11" s="339"/>
+      <c r="BF11" s="339"/>
+      <c r="BG11" s="344"/>
+      <c r="BH11" s="431"/>
+      <c r="BI11" s="428"/>
+      <c r="BJ11" s="339"/>
+      <c r="BK11" s="339"/>
+      <c r="BL11" s="339"/>
+      <c r="BM11" s="431"/>
+      <c r="BN11" s="431"/>
+      <c r="BO11" s="431"/>
+      <c r="BP11" s="431"/>
+      <c r="BQ11" s="431"/>
+      <c r="BR11" s="344"/>
+      <c r="BS11" s="344"/>
+      <c r="BT11" s="339"/>
+      <c r="BU11" s="357"/>
       <c r="BV11" s="22"/>
-      <c r="BW11" s="381"/>
-      <c r="BX11" s="270" t="s">
+      <c r="BW11" s="439"/>
+      <c r="BX11" s="440" t="s">
         <v>91</v>
       </c>
-      <c r="BY11" s="270" t="s">
+      <c r="BY11" s="440" t="s">
         <v>92</v>
       </c>
-      <c r="BZ11" s="270" t="s">
+      <c r="BZ11" s="440" t="s">
         <v>93</v>
       </c>
-      <c r="CA11" s="271" t="s">
+      <c r="CA11" s="441" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="346"/>
-      <c r="CC11" s="338"/>
-      <c r="CD11" s="338"/>
-      <c r="CE11" s="320">
+      <c r="CB11" s="370"/>
+      <c r="CC11" s="443"/>
+      <c r="CD11" s="443"/>
+      <c r="CE11" s="318">
         <v>26</v>
       </c>
-      <c r="CF11" s="308"/>
+      <c r="CF11" s="306"/>
       <c r="CH11" s="241"/>
       <c r="CI11" s="241"/>
     </row>
-    <row r="12" spans="1:87" s="313" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="309">
+    <row r="12" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="307">
         <v>1</v>
       </c>
-      <c r="B12" s="310">
+      <c r="B12" s="308">
         <f>A12+1</f>
         <v>2</v>
       </c>
-      <c r="C12" s="310">
+      <c r="C12" s="308">
         <f>B12+1</f>
         <v>3</v>
       </c>
-      <c r="D12" s="310">
+      <c r="D12" s="308">
         <f>C12+1</f>
         <v>4</v>
       </c>
-      <c r="E12" s="310"/>
-      <c r="F12" s="310">
+      <c r="E12" s="308"/>
+      <c r="F12" s="308">
         <f>D12+1</f>
         <v>5</v>
       </c>
-      <c r="G12" s="310">
+      <c r="G12" s="308">
         <f t="shared" ref="G12:AV12" si="0">F12+1</f>
         <v>6</v>
       </c>
-      <c r="H12" s="310">
+      <c r="H12" s="308">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I12" s="310">
+      <c r="I12" s="308">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J12" s="310">
+      <c r="J12" s="308">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K12" s="310">
+      <c r="K12" s="308">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="310">
+      <c r="L12" s="308">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="M12" s="310">
+      <c r="M12" s="308">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N12" s="310">
+      <c r="N12" s="308">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="O12" s="310">
+      <c r="O12" s="308">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="P12" s="310">
+      <c r="P12" s="308">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q12" s="310">
+      <c r="Q12" s="308">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="R12" s="310">
+      <c r="R12" s="308">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="S12" s="310">
+      <c r="S12" s="308">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T12" s="310">
+      <c r="T12" s="308">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U12" s="310">
+      <c r="U12" s="308">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V12" s="310">
+      <c r="V12" s="308">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W12" s="310">
+      <c r="W12" s="308">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X12" s="310">
+      <c r="X12" s="308">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y12" s="310">
+      <c r="Y12" s="308">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z12" s="310">
+      <c r="Z12" s="308">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA12" s="310">
+      <c r="AA12" s="308">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB12" s="310">
+      <c r="AB12" s="308">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC12" s="310">
+      <c r="AC12" s="308">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD12" s="310">
+      <c r="AD12" s="308">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE12" s="310">
+      <c r="AE12" s="308">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF12" s="310">
+      <c r="AF12" s="308">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG12" s="310">
+      <c r="AG12" s="308">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="AH12" s="310">
+      <c r="AH12" s="308">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="AI12" s="310">
+      <c r="AI12" s="308">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AJ12" s="310">
+      <c r="AJ12" s="308">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="AK12" s="310">
+      <c r="AK12" s="308">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="AL12" s="310">
+      <c r="AL12" s="308">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="AM12" s="310">
+      <c r="AM12" s="308">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="AN12" s="310">
+      <c r="AN12" s="308">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="AO12" s="310">
+      <c r="AO12" s="308">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="AP12" s="310">
+      <c r="AP12" s="308">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="AQ12" s="310">
+      <c r="AQ12" s="308">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="AR12" s="310">
+      <c r="AR12" s="308">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="AS12" s="310">
+      <c r="AS12" s="308">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="AT12" s="310">
+      <c r="AT12" s="308">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="AU12" s="310">
+      <c r="AU12" s="308">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="AV12" s="310">
+      <c r="AV12" s="308">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="AW12" s="310"/>
-      <c r="AX12" s="310"/>
-      <c r="AY12" s="310">
+      <c r="AW12" s="308"/>
+      <c r="AX12" s="308"/>
+      <c r="AY12" s="308">
         <f>AV12+1</f>
         <v>48</v>
       </c>
-      <c r="AZ12" s="310">
+      <c r="AZ12" s="308">
         <f t="shared" ref="AZ12:BE12" si="1">AY12+1</f>
         <v>49</v>
       </c>
-      <c r="BA12" s="310">
+      <c r="BA12" s="308">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="BB12" s="310">
+      <c r="BB12" s="308">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="BC12" s="310">
+      <c r="BC12" s="308">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="BD12" s="310">
+      <c r="BD12" s="308">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="BE12" s="310">
+      <c r="BE12" s="308">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="BF12" s="310"/>
-      <c r="BG12" s="310"/>
-      <c r="BH12" s="310"/>
-      <c r="BI12" s="310"/>
-      <c r="BJ12" s="310"/>
-      <c r="BK12" s="310"/>
-      <c r="BL12" s="310">
+      <c r="BF12" s="308"/>
+      <c r="BG12" s="308"/>
+      <c r="BH12" s="308"/>
+      <c r="BI12" s="308"/>
+      <c r="BJ12" s="308"/>
+      <c r="BK12" s="308"/>
+      <c r="BL12" s="308">
         <f>BE12+1</f>
         <v>55</v>
       </c>
-      <c r="BM12" s="310">
+      <c r="BM12" s="308">
         <f t="shared" ref="BM12:BU12" si="2">BL12+1</f>
         <v>56</v>
       </c>
-      <c r="BN12" s="310">
+      <c r="BN12" s="308">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="BO12" s="310">
+      <c r="BO12" s="308">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="BP12" s="310">
+      <c r="BP12" s="308">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="BQ12" s="310">
+      <c r="BQ12" s="308">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="BR12" s="310">
+      <c r="BR12" s="308">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="BS12" s="310">
+      <c r="BS12" s="308">
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="BT12" s="310">
+      <c r="BT12" s="308">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="BU12" s="310">
+      <c r="BU12" s="308">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="BV12" s="311"/>
-      <c r="BW12" s="312" t="s">
+      <c r="BV12" s="309"/>
+      <c r="BW12" s="310" t="s">
         <v>95</v>
       </c>
-      <c r="BX12" s="310">
+      <c r="BX12" s="308">
         <f t="shared" ref="BX12:CD12" si="3">BW12+1</f>
         <v>66</v>
       </c>
-      <c r="BY12" s="310">
+      <c r="BY12" s="308">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="BZ12" s="310">
+      <c r="BZ12" s="308">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="CA12" s="310">
+      <c r="CA12" s="308">
         <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="CB12" s="310">
+      <c r="CB12" s="308">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="CC12" s="310">
+      <c r="CC12" s="308">
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
-      <c r="CD12" s="310">
+      <c r="CD12" s="308">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="CG12" s="307"/>
+      <c r="CG12" s="305"/>
       <c r="CH12" s="241"/>
       <c r="CI12" s="241"/>
     </row>
-    <row r="13" spans="1:87" s="313" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="309" t="s">
+    <row r="13" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="309" t="s">
+      <c r="B13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="309" t="s">
+      <c r="C13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="310"/>
-      <c r="E13" s="310"/>
-      <c r="F13" s="310"/>
-      <c r="G13" s="309" t="s">
+      <c r="D13" s="308"/>
+      <c r="E13" s="308"/>
+      <c r="F13" s="308"/>
+      <c r="G13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="309" t="s">
+      <c r="H13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="309" t="s">
+      <c r="I13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="310"/>
-      <c r="K13" s="310"/>
-      <c r="L13" s="310"/>
-      <c r="M13" s="310"/>
-      <c r="N13" s="310"/>
-      <c r="O13" s="310"/>
-      <c r="P13" s="310"/>
-      <c r="Q13" s="310"/>
-      <c r="R13" s="310"/>
-      <c r="S13" s="310"/>
-      <c r="T13" s="310"/>
-      <c r="U13" s="310"/>
-      <c r="V13" s="310"/>
-      <c r="W13" s="310"/>
-      <c r="X13" s="310"/>
-      <c r="Y13" s="310"/>
-      <c r="Z13" s="310"/>
-      <c r="AA13" s="310"/>
-      <c r="AB13" s="310"/>
-      <c r="AC13" s="310"/>
-      <c r="AD13" s="310"/>
-      <c r="AE13" s="310"/>
-      <c r="AF13" s="310"/>
-      <c r="AG13" s="310"/>
-      <c r="AH13" s="310"/>
-      <c r="AI13" s="310"/>
-      <c r="AJ13" s="310"/>
-      <c r="AK13" s="310"/>
-      <c r="AL13" s="310"/>
-      <c r="AM13" s="310"/>
-      <c r="AN13" s="310"/>
-      <c r="AO13" s="310"/>
-      <c r="AP13" s="310"/>
-      <c r="AQ13" s="310"/>
-      <c r="AR13" s="310"/>
-      <c r="AS13" s="310"/>
-      <c r="AT13" s="310"/>
-      <c r="AU13" s="310"/>
-      <c r="AV13" s="310"/>
-      <c r="AW13" s="310"/>
-      <c r="AX13" s="310"/>
-      <c r="AY13" s="310"/>
-      <c r="AZ13" s="310"/>
-      <c r="BA13" s="310"/>
-      <c r="BB13" s="310"/>
-      <c r="BC13" s="310"/>
-      <c r="BD13" s="310"/>
-      <c r="BE13" s="310"/>
-      <c r="BF13" s="310"/>
-      <c r="BG13" s="310"/>
-      <c r="BH13" s="310"/>
-      <c r="BI13" s="310"/>
-      <c r="BJ13" s="310"/>
-      <c r="BK13" s="310"/>
-      <c r="BL13" s="310"/>
-      <c r="BM13" s="310"/>
-      <c r="BN13" s="310"/>
-      <c r="BO13" s="310"/>
-      <c r="BP13" s="310"/>
-      <c r="BQ13" s="310"/>
-      <c r="BR13" s="310"/>
-      <c r="BS13" s="310"/>
-      <c r="BT13" s="310"/>
-      <c r="BU13" s="314"/>
-      <c r="BV13" s="311"/>
-      <c r="BW13" s="312"/>
-      <c r="BX13" s="310"/>
-      <c r="BY13" s="310"/>
-      <c r="BZ13" s="310"/>
-      <c r="CA13" s="310"/>
-      <c r="CB13" s="310"/>
-      <c r="CC13" s="310"/>
-      <c r="CD13" s="310"/>
-      <c r="CG13" s="307"/>
+      <c r="J13" s="308"/>
+      <c r="K13" s="308"/>
+      <c r="L13" s="308"/>
+      <c r="M13" s="308"/>
+      <c r="N13" s="308"/>
+      <c r="O13" s="308"/>
+      <c r="P13" s="308"/>
+      <c r="Q13" s="308"/>
+      <c r="R13" s="308"/>
+      <c r="S13" s="308"/>
+      <c r="T13" s="308"/>
+      <c r="U13" s="308"/>
+      <c r="V13" s="308"/>
+      <c r="W13" s="308"/>
+      <c r="X13" s="308"/>
+      <c r="Y13" s="308"/>
+      <c r="Z13" s="308"/>
+      <c r="AA13" s="308"/>
+      <c r="AB13" s="308"/>
+      <c r="AC13" s="308"/>
+      <c r="AD13" s="308"/>
+      <c r="AE13" s="308"/>
+      <c r="AF13" s="308"/>
+      <c r="AG13" s="308"/>
+      <c r="AH13" s="308"/>
+      <c r="AI13" s="308"/>
+      <c r="AJ13" s="308"/>
+      <c r="AK13" s="308"/>
+      <c r="AL13" s="308"/>
+      <c r="AM13" s="308"/>
+      <c r="AN13" s="308"/>
+      <c r="AO13" s="308"/>
+      <c r="AP13" s="308"/>
+      <c r="AQ13" s="308"/>
+      <c r="AR13" s="308"/>
+      <c r="AS13" s="308"/>
+      <c r="AT13" s="308"/>
+      <c r="AU13" s="308"/>
+      <c r="AV13" s="308"/>
+      <c r="AW13" s="308"/>
+      <c r="AX13" s="308"/>
+      <c r="AY13" s="308"/>
+      <c r="AZ13" s="308"/>
+      <c r="BA13" s="308"/>
+      <c r="BB13" s="308"/>
+      <c r="BC13" s="308"/>
+      <c r="BD13" s="308"/>
+      <c r="BE13" s="308"/>
+      <c r="BF13" s="308"/>
+      <c r="BG13" s="308"/>
+      <c r="BH13" s="308"/>
+      <c r="BI13" s="308"/>
+      <c r="BJ13" s="308"/>
+      <c r="BK13" s="308"/>
+      <c r="BL13" s="308"/>
+      <c r="BM13" s="308"/>
+      <c r="BN13" s="308"/>
+      <c r="BO13" s="308"/>
+      <c r="BP13" s="308"/>
+      <c r="BQ13" s="308"/>
+      <c r="BR13" s="308"/>
+      <c r="BS13" s="308"/>
+      <c r="BT13" s="308"/>
+      <c r="BU13" s="312"/>
+      <c r="BV13" s="309"/>
+      <c r="BW13" s="310"/>
+      <c r="BX13" s="308"/>
+      <c r="BY13" s="308"/>
+      <c r="BZ13" s="308"/>
+      <c r="CA13" s="308"/>
+      <c r="CB13" s="308"/>
+      <c r="CC13" s="308"/>
+      <c r="CD13" s="308"/>
+      <c r="CG13" s="305"/>
       <c r="CH13" s="241"/>
       <c r="CI13" s="241"/>
     </row>
@@ -9160,56 +9211,56 @@
         <v>186060000</v>
       </c>
       <c r="J14" s="94"/>
-      <c r="K14" s="315">
+      <c r="K14" s="313">
         <f t="shared" ref="K14:S14" si="4">SUM(K15:K21)</f>
         <v>166</v>
       </c>
-      <c r="L14" s="315">
+      <c r="L14" s="313">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="M14" s="315">
+      <c r="M14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N14" s="315">
+      <c r="N14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="O14" s="315">
+      <c r="O14" s="313">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P14" s="315">
+      <c r="P14" s="313">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="Q14" s="315">
+      <c r="Q14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="R14" s="315">
+      <c r="R14" s="313">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S14" s="315">
+      <c r="S14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="T14" s="315"/>
-      <c r="U14" s="315">
+      <c r="T14" s="313"/>
+      <c r="U14" s="313">
         <f>SUM(U15:U21)</f>
         <v>2</v>
       </c>
-      <c r="V14" s="315">
+      <c r="V14" s="313">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="315">
+      <c r="W14" s="313">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="315">
+      <c r="X14" s="313">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -9342,7 +9393,7 @@
         <f>SUM(BT15:BT21)</f>
         <v>92038615.384615406</v>
       </c>
-      <c r="BU14" s="316">
+      <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
         <v>134901223.69230768</v>
       </c>
@@ -9357,243 +9408,243 @@
       <c r="CD14" s="243"/>
     </row>
     <row r="15" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="272">
+      <c r="A15" s="270">
         <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="273">
+      <c r="B15" s="271">
         <v>2405236</v>
       </c>
-      <c r="C15" s="274" t="s">
+      <c r="C15" s="272" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="275" t="s">
+      <c r="D15" s="273" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="276" t="s">
+      <c r="E15" s="274" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="276" t="s">
+      <c r="F15" s="274" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="277">
+      <c r="G15" s="275">
         <v>9520000</v>
       </c>
-      <c r="H15" s="277">
+      <c r="H15" s="275">
         <f t="shared" ref="H15:H21" si="7">+IF(OR(CC15="ĐT PCCC",CC15="ĐP PCCC"),780000,IF(CC15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="277">
+      <c r="I15" s="275">
         <f t="shared" ref="I15:I21" si="8">CB15-BZ15-G15-H15</f>
         <v>53480000</v>
       </c>
-      <c r="J15" s="278">
+      <c r="J15" s="276">
         <v>1</v>
       </c>
-      <c r="K15" s="279">
+      <c r="K15" s="277">
         <v>26</v>
       </c>
-      <c r="L15" s="279">
-        <v>0</v>
-      </c>
-      <c r="M15" s="279">
-        <v>0</v>
-      </c>
-      <c r="N15" s="279">
-        <v>0</v>
-      </c>
-      <c r="O15" s="279">
-        <v>0</v>
-      </c>
-      <c r="P15" s="279">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="279">
-        <v>0</v>
-      </c>
-      <c r="R15" s="279">
-        <v>0</v>
-      </c>
-      <c r="S15" s="279">
-        <v>0</v>
-      </c>
-      <c r="T15" s="279"/>
-      <c r="U15" s="279">
-        <v>0</v>
-      </c>
-      <c r="V15" s="279">
-        <v>0</v>
-      </c>
-      <c r="W15" s="279">
-        <v>0</v>
-      </c>
-      <c r="X15" s="279">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="277">
+      <c r="L15" s="277">
+        <v>0</v>
+      </c>
+      <c r="M15" s="277">
+        <v>0</v>
+      </c>
+      <c r="N15" s="277">
+        <v>0</v>
+      </c>
+      <c r="O15" s="277">
+        <v>0</v>
+      </c>
+      <c r="P15" s="277">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="277">
+        <v>0</v>
+      </c>
+      <c r="R15" s="277">
+        <v>0</v>
+      </c>
+      <c r="S15" s="277">
+        <v>0</v>
+      </c>
+      <c r="T15" s="277"/>
+      <c r="U15" s="277">
+        <v>0</v>
+      </c>
+      <c r="V15" s="277">
+        <v>0</v>
+      </c>
+      <c r="W15" s="277">
+        <v>0</v>
+      </c>
+      <c r="X15" s="277">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="275">
         <f t="shared" ref="Y15:Y21" si="9">G15*(K15+L15)/26</f>
         <v>9520000</v>
       </c>
-      <c r="Z15" s="277">
+      <c r="Z15" s="275">
         <f t="shared" ref="Z15:Z21" si="10">M15*G15/26</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="277">
+      <c r="AA15" s="275">
         <f t="shared" ref="AA15:AA21" si="11">G15*N15/26</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="277">
+      <c r="AB15" s="275">
         <f t="shared" ref="AB15:AB21" si="12">G15*O15/26</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="277">
+      <c r="AC15" s="275">
         <f t="shared" ref="AC15:AC21" si="13">G15*P15*150%/26</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="277">
+      <c r="AD15" s="275">
         <f t="shared" ref="AD15:AD21" si="14">G15*Q15/26*200%</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="277">
+      <c r="AE15" s="275">
         <f t="shared" ref="AE15:AE21" si="15">G15*R15/26*300%</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="277">
+      <c r="AF15" s="275">
         <f>ROUND((G15+H15)/26*S15*30%,0)</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="277">
+      <c r="AG15" s="275">
         <f t="shared" ref="AG15:AG21" si="16">T15*G15/26/8</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="277">
+      <c r="AH15" s="275">
         <f t="shared" ref="AH15:AH21" si="17">CB15/26*U15</f>
         <v>0</v>
       </c>
-      <c r="AI15" s="277">
+      <c r="AI15" s="275">
         <f t="shared" ref="AI15:AI21" si="18">G15*V15/26</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="277"/>
-      <c r="AK15" s="277">
+      <c r="AJ15" s="275"/>
+      <c r="AK15" s="275">
         <f t="shared" ref="AK15:AK21" si="19">BZ15*L15/26</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="277"/>
-      <c r="AM15" s="277">
+      <c r="AL15" s="275"/>
+      <c r="AM15" s="275">
         <f t="shared" ref="AM15:AM21" si="20">X15*CD15</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="277">
+      <c r="AN15" s="275">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="277">
+      <c r="AO15" s="275">
         <f t="shared" ref="AO15:AO21" si="21">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CE$11-K15-L15)/26+(H15+I15)*50%*M15/26+BW15*O15/26-AB15+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CE$11-K15-L15)/26-Y15)+(H15-H15*($CE$11-K15-L15)/26-AN15))</f>
         <v>53480000</v>
       </c>
-      <c r="AP15" s="277"/>
-      <c r="AQ15" s="277"/>
-      <c r="AR15" s="277">
+      <c r="AP15" s="275"/>
+      <c r="AQ15" s="275"/>
+      <c r="AR15" s="275">
         <v>1000000</v>
       </c>
-      <c r="AS15" s="277"/>
-      <c r="AT15" s="277"/>
-      <c r="AU15" s="277"/>
-      <c r="AV15" s="277">
+      <c r="AS15" s="275"/>
+      <c r="AT15" s="275"/>
+      <c r="AU15" s="275"/>
+      <c r="AV15" s="275">
         <f t="shared" ref="AV15:AV21" si="22">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>64000000</v>
       </c>
-      <c r="AW15" s="277"/>
-      <c r="AX15" s="277" t="str">
+      <c r="AW15" s="275"/>
+      <c r="AX15" s="275" t="str">
         <f t="shared" ref="AX15:AX21" si="23">IF(E15="CT","x",0)</f>
         <v>x</v>
       </c>
-      <c r="AY15" s="280">
+      <c r="AY15" s="278">
         <f t="shared" ref="AY15:BA21" si="24">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="280">
+      <c r="AZ15" s="278">
         <f t="shared" si="24"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="280">
+      <c r="BA15" s="278">
         <f t="shared" si="24"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="280">
+      <c r="BB15" s="278">
         <f t="shared" ref="BB15:BB21" si="25">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="280"/>
-      <c r="BD15" s="280"/>
-      <c r="BE15" s="280">
+      <c r="BC15" s="278"/>
+      <c r="BD15" s="278"/>
+      <c r="BE15" s="278">
         <f t="shared" ref="BE15:BE21" si="26">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="280">
+      <c r="BF15" s="278">
         <f>AM15+IF(E15="CT",IF(AR15&gt;=730000,730000,AR15),0)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
         <v>10220500</v>
       </c>
-      <c r="BG15" s="280">
+      <c r="BG15" s="278">
         <f t="shared" ref="BG15:BG21" si="27">AV15-BF15+AW15</f>
         <v>53779500</v>
       </c>
-      <c r="BH15" s="280">
+      <c r="BH15" s="278">
         <v>3</v>
       </c>
-      <c r="BI15" s="280">
+      <c r="BI15" s="278">
         <v>6200000</v>
       </c>
-      <c r="BJ15" s="280">
+      <c r="BJ15" s="278">
         <f>IF(E15="CT",15500000,0)</f>
         <v>15500000</v>
       </c>
-      <c r="BK15" s="280">
+      <c r="BK15" s="278">
         <f t="shared" ref="BK15:BK21" si="28">BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
         <v>18679900</v>
       </c>
-      <c r="BL15" s="281">
+      <c r="BL15" s="279">
         <f t="shared" ref="BL15:BL21" si="29">IF(E15="TV",BK15*10%,IF(BK15&gt;0,ROUND(IF(BK15&gt;=80000000,BK15*35%-9850000,IF(BK15&gt;=52000000,BK15*30%-5850000,IF(BK15&gt;=32000000,BK15*25%-3250000,IF(BK15&gt;=18000000,BK15*20%-1650000,IF(BK15&gt;=10000000,BK15*15%-750000,IF(BK15&gt;5000000,BK15*10%-250000,BK15*5%)))))),0),0))</f>
         <v>2085980</v>
       </c>
-      <c r="BM15" s="280"/>
-      <c r="BN15" s="280"/>
-      <c r="BO15" s="280">
-        <v>0</v>
-      </c>
-      <c r="BP15" s="280"/>
-      <c r="BQ15" s="280"/>
-      <c r="BR15" s="280"/>
-      <c r="BS15" s="280"/>
+      <c r="BM15" s="278"/>
+      <c r="BN15" s="278"/>
+      <c r="BO15" s="278">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="278"/>
+      <c r="BQ15" s="278"/>
+      <c r="BR15" s="278"/>
+      <c r="BS15" s="278"/>
       <c r="BT15" s="263">
         <v>25846153.846153852</v>
       </c>
-      <c r="BU15" s="282">
+      <c r="BU15" s="280">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
         <v>34973066.153846145</v>
       </c>
       <c r="BV15" s="252"/>
-      <c r="BW15" s="283">
+      <c r="BW15" s="281">
         <v>60000000</v>
       </c>
-      <c r="BX15" s="281">
-        <v>0</v>
-      </c>
-      <c r="BY15" s="281"/>
-      <c r="BZ15" s="281">
+      <c r="BX15" s="279">
+        <v>0</v>
+      </c>
+      <c r="BY15" s="279"/>
+      <c r="BZ15" s="279">
         <v>200000</v>
       </c>
-      <c r="CA15" s="281">
+      <c r="CA15" s="279">
         <f t="shared" ref="CA15:CA21" si="31">+BW15*5%</f>
         <v>3000000</v>
       </c>
-      <c r="CB15" s="281">
+      <c r="CB15" s="279">
         <f t="shared" ref="CB15:CB21" si="32">SUM(BW15:CA15)</f>
         <v>63200000</v>
       </c>
-      <c r="CC15" s="281"/>
-      <c r="CD15" s="281"/>
+      <c r="CC15" s="279"/>
+      <c r="CD15" s="279"/>
       <c r="CE15" s="253"/>
       <c r="CF15" s="254"/>
       <c r="CG15" s="254"/>
@@ -9784,7 +9835,7 @@
         <v>40832692.307692312</v>
       </c>
       <c r="BH16" s="250"/>
-      <c r="BI16" s="280">
+      <c r="BI16" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ16" s="250">
@@ -10028,7 +10079,7 @@
         <v>35713076.923076928</v>
       </c>
       <c r="BH17" s="250"/>
-      <c r="BI17" s="280">
+      <c r="BI17" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ17" s="250">
@@ -10272,7 +10323,7 @@
         <v>22247115.384615384</v>
       </c>
       <c r="BH18" s="250"/>
-      <c r="BI18" s="280">
+      <c r="BI18" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ18" s="250">
@@ -10516,7 +10567,7 @@
         <v>9879615.3846153859</v>
       </c>
       <c r="BH19" s="250"/>
-      <c r="BI19" s="280">
+      <c r="BI19" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ19" s="250">
@@ -10760,7 +10811,7 @@
         <v>21247500</v>
       </c>
       <c r="BH20" s="250"/>
-      <c r="BI20" s="280">
+      <c r="BI20" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ20" s="250">
@@ -11006,7 +11057,7 @@
         <v>19062884.615384616</v>
       </c>
       <c r="BH21" s="250"/>
-      <c r="BI21" s="280">
+      <c r="BI21" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ21" s="250">
@@ -11084,9 +11135,9 @@
       <c r="T22" s="40"/>
       <c r="U22" s="41"/>
       <c r="V22" s="41"/>
-      <c r="W22" s="317"/>
-      <c r="X22" s="317"/>
-      <c r="AC22" s="318"/>
+      <c r="W22" s="315"/>
+      <c r="X22" s="315"/>
+      <c r="AC22" s="316"/>
       <c r="BL22" s="45"/>
       <c r="BP22" s="45"/>
       <c r="BQ22" s="45"/>
@@ -11179,8 +11230,8 @@
       <c r="R24" s="53"/>
       <c r="U24" s="54"/>
       <c r="V24" s="54"/>
-      <c r="W24" s="319"/>
-      <c r="X24" s="319"/>
+      <c r="W24" s="317"/>
+      <c r="X24" s="317"/>
       <c r="AN24" s="58"/>
       <c r="AV24" s="49"/>
       <c r="AW24" s="49"/>
@@ -11206,6 +11257,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="BW8:BW11"/>
@@ -11222,72 +11339,6 @@
     <mergeCell ref="N9:N11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="BM9:BQ9"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11496,87 +11547,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="411"/>
-      <c r="B3" s="402"/>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
-      <c r="J3" s="402"/>
-      <c r="K3" s="402"/>
-      <c r="L3" s="402"/>
-      <c r="M3" s="402"/>
-      <c r="N3" s="402"/>
-      <c r="O3" s="402"/>
-      <c r="P3" s="402"/>
-      <c r="Q3" s="402"/>
-      <c r="R3" s="402"/>
-      <c r="S3" s="402"/>
-      <c r="T3" s="402"/>
-      <c r="U3" s="402"/>
-      <c r="V3" s="402"/>
-      <c r="W3" s="402"/>
-      <c r="X3" s="402"/>
-      <c r="Y3" s="402"/>
-      <c r="Z3" s="402"/>
-      <c r="AA3" s="402"/>
-      <c r="AB3" s="402"/>
-      <c r="AC3" s="402"/>
-      <c r="AD3" s="402"/>
-      <c r="AE3" s="402"/>
-      <c r="AF3" s="402"/>
-      <c r="AG3" s="402"/>
-      <c r="AH3" s="402"/>
-      <c r="AI3" s="402"/>
-      <c r="AJ3" s="402"/>
-      <c r="AK3" s="402"/>
-      <c r="AL3" s="402"/>
-      <c r="AM3" s="402"/>
-      <c r="AN3" s="402"/>
-      <c r="AO3" s="402"/>
-      <c r="AP3" s="402"/>
-      <c r="AQ3" s="402"/>
-      <c r="AR3" s="402"/>
-      <c r="AS3" s="402"/>
-      <c r="AT3" s="402"/>
-      <c r="AU3" s="402"/>
-      <c r="AV3" s="402"/>
-      <c r="AW3" s="402"/>
-      <c r="AX3" s="402"/>
-      <c r="AY3" s="402"/>
-      <c r="AZ3" s="402"/>
-      <c r="BA3" s="402"/>
-      <c r="BB3" s="402"/>
-      <c r="BC3" s="402"/>
-      <c r="BD3" s="402"/>
-      <c r="BE3" s="402"/>
-      <c r="BF3" s="402"/>
-      <c r="BG3" s="402"/>
-      <c r="BH3" s="402"/>
-      <c r="BI3" s="402"/>
-      <c r="BJ3" s="402"/>
-      <c r="BK3" s="402"/>
-      <c r="BL3" s="402"/>
-      <c r="BM3" s="402"/>
-      <c r="BN3" s="402"/>
-      <c r="BO3" s="402"/>
-      <c r="BP3" s="402"/>
-      <c r="BQ3" s="402"/>
-      <c r="BR3" s="402"/>
-      <c r="BS3" s="402"/>
-      <c r="BT3" s="402"/>
-      <c r="BU3" s="402"/>
-      <c r="BW3" s="401" t="s">
+      <c r="A3" s="407"/>
+      <c r="B3" s="395"/>
+      <c r="C3" s="395"/>
+      <c r="D3" s="395"/>
+      <c r="E3" s="395"/>
+      <c r="F3" s="395"/>
+      <c r="G3" s="395"/>
+      <c r="H3" s="395"/>
+      <c r="I3" s="395"/>
+      <c r="J3" s="395"/>
+      <c r="K3" s="395"/>
+      <c r="L3" s="395"/>
+      <c r="M3" s="395"/>
+      <c r="N3" s="395"/>
+      <c r="O3" s="395"/>
+      <c r="P3" s="395"/>
+      <c r="Q3" s="395"/>
+      <c r="R3" s="395"/>
+      <c r="S3" s="395"/>
+      <c r="T3" s="395"/>
+      <c r="U3" s="395"/>
+      <c r="V3" s="395"/>
+      <c r="W3" s="395"/>
+      <c r="X3" s="395"/>
+      <c r="Y3" s="395"/>
+      <c r="Z3" s="395"/>
+      <c r="AA3" s="395"/>
+      <c r="AB3" s="395"/>
+      <c r="AC3" s="395"/>
+      <c r="AD3" s="395"/>
+      <c r="AE3" s="395"/>
+      <c r="AF3" s="395"/>
+      <c r="AG3" s="395"/>
+      <c r="AH3" s="395"/>
+      <c r="AI3" s="395"/>
+      <c r="AJ3" s="395"/>
+      <c r="AK3" s="395"/>
+      <c r="AL3" s="395"/>
+      <c r="AM3" s="395"/>
+      <c r="AN3" s="395"/>
+      <c r="AO3" s="395"/>
+      <c r="AP3" s="395"/>
+      <c r="AQ3" s="395"/>
+      <c r="AR3" s="395"/>
+      <c r="AS3" s="395"/>
+      <c r="AT3" s="395"/>
+      <c r="AU3" s="395"/>
+      <c r="AV3" s="395"/>
+      <c r="AW3" s="395"/>
+      <c r="AX3" s="395"/>
+      <c r="AY3" s="395"/>
+      <c r="AZ3" s="395"/>
+      <c r="BA3" s="395"/>
+      <c r="BB3" s="395"/>
+      <c r="BC3" s="395"/>
+      <c r="BD3" s="395"/>
+      <c r="BE3" s="395"/>
+      <c r="BF3" s="395"/>
+      <c r="BG3" s="395"/>
+      <c r="BH3" s="395"/>
+      <c r="BI3" s="395"/>
+      <c r="BJ3" s="395"/>
+      <c r="BK3" s="395"/>
+      <c r="BL3" s="395"/>
+      <c r="BM3" s="395"/>
+      <c r="BN3" s="395"/>
+      <c r="BO3" s="395"/>
+      <c r="BP3" s="395"/>
+      <c r="BQ3" s="395"/>
+      <c r="BR3" s="395"/>
+      <c r="BS3" s="395"/>
+      <c r="BT3" s="395"/>
+      <c r="BU3" s="395"/>
+      <c r="BW3" s="394" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="402"/>
-      <c r="BY3" s="402"/>
-      <c r="BZ3" s="402"/>
-      <c r="CA3" s="402"/>
-      <c r="CB3" s="402"/>
+      <c r="BX3" s="395"/>
+      <c r="BY3" s="395"/>
+      <c r="BZ3" s="395"/>
+      <c r="CA3" s="395"/>
+      <c r="CB3" s="395"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11659,364 +11710,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="402"/>
-      <c r="BX4" s="402"/>
-      <c r="BY4" s="402"/>
-      <c r="BZ4" s="402"/>
-      <c r="CA4" s="402"/>
-      <c r="CB4" s="402"/>
+      <c r="BW4" s="395"/>
+      <c r="BX4" s="395"/>
+      <c r="BY4" s="395"/>
+      <c r="BZ4" s="395"/>
+      <c r="CA4" s="395"/>
+      <c r="CB4" s="395"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="414" t="s">
+      <c r="A5" s="382" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="413" t="s">
+      <c r="B5" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="387" t="s">
+      <c r="C5" s="381" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="412" t="s">
+      <c r="D5" s="388" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="412" t="s">
+      <c r="E5" s="388" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="387" t="s">
+      <c r="F5" s="381" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="387" t="s">
+      <c r="G5" s="381" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="333" t="s">
+      <c r="H5" s="337" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="333" t="s">
+      <c r="I5" s="337" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="387" t="s">
+      <c r="J5" s="381" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="416" t="s">
+      <c r="K5" s="386" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="398"/>
-      <c r="M5" s="398"/>
-      <c r="N5" s="398"/>
-      <c r="O5" s="398"/>
-      <c r="P5" s="398"/>
-      <c r="Q5" s="398"/>
-      <c r="R5" s="398"/>
-      <c r="S5" s="398"/>
-      <c r="T5" s="398"/>
-      <c r="U5" s="398"/>
-      <c r="V5" s="398"/>
-      <c r="W5" s="398"/>
-      <c r="X5" s="398"/>
-      <c r="Y5" s="387" t="s">
+      <c r="L5" s="378"/>
+      <c r="M5" s="378"/>
+      <c r="N5" s="378"/>
+      <c r="O5" s="378"/>
+      <c r="P5" s="378"/>
+      <c r="Q5" s="378"/>
+      <c r="R5" s="378"/>
+      <c r="S5" s="378"/>
+      <c r="T5" s="378"/>
+      <c r="U5" s="378"/>
+      <c r="V5" s="378"/>
+      <c r="W5" s="378"/>
+      <c r="X5" s="378"/>
+      <c r="Y5" s="381" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="398"/>
-      <c r="AA5" s="398"/>
-      <c r="AB5" s="398"/>
-      <c r="AC5" s="398"/>
-      <c r="AD5" s="398"/>
-      <c r="AE5" s="398"/>
-      <c r="AF5" s="398"/>
-      <c r="AG5" s="398"/>
-      <c r="AH5" s="398"/>
-      <c r="AI5" s="398"/>
-      <c r="AJ5" s="398"/>
-      <c r="AK5" s="398"/>
-      <c r="AL5" s="398"/>
-      <c r="AM5" s="398"/>
-      <c r="AN5" s="398"/>
-      <c r="AO5" s="399"/>
-      <c r="AP5" s="387" t="s">
+      <c r="Z5" s="378"/>
+      <c r="AA5" s="378"/>
+      <c r="AB5" s="378"/>
+      <c r="AC5" s="378"/>
+      <c r="AD5" s="378"/>
+      <c r="AE5" s="378"/>
+      <c r="AF5" s="378"/>
+      <c r="AG5" s="378"/>
+      <c r="AH5" s="378"/>
+      <c r="AI5" s="378"/>
+      <c r="AJ5" s="378"/>
+      <c r="AK5" s="378"/>
+      <c r="AL5" s="378"/>
+      <c r="AM5" s="378"/>
+      <c r="AN5" s="378"/>
+      <c r="AO5" s="379"/>
+      <c r="AP5" s="381" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="387" t="s">
+      <c r="AQ5" s="381" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="387" t="s">
+      <c r="AR5" s="381" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="387" t="s">
+      <c r="AS5" s="381" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="387" t="s">
+      <c r="AT5" s="381" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="387" t="s">
+      <c r="AU5" s="381" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="387" t="s">
+      <c r="AV5" s="381" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="387" t="s">
+      <c r="AW5" s="381" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="387" t="s">
+      <c r="AX5" s="381" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="397" t="s">
+      <c r="AY5" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="398"/>
-      <c r="BA5" s="398"/>
-      <c r="BB5" s="398"/>
-      <c r="BC5" s="398"/>
-      <c r="BD5" s="398"/>
-      <c r="BE5" s="398"/>
-      <c r="BF5" s="398"/>
-      <c r="BG5" s="398"/>
-      <c r="BH5" s="398"/>
-      <c r="BI5" s="398"/>
-      <c r="BJ5" s="398"/>
-      <c r="BK5" s="398"/>
-      <c r="BL5" s="398"/>
-      <c r="BM5" s="398"/>
-      <c r="BN5" s="398"/>
-      <c r="BO5" s="398"/>
-      <c r="BP5" s="398"/>
-      <c r="BQ5" s="399"/>
-      <c r="BR5" s="403" t="s">
+      <c r="AZ5" s="378"/>
+      <c r="BA5" s="378"/>
+      <c r="BB5" s="378"/>
+      <c r="BC5" s="378"/>
+      <c r="BD5" s="378"/>
+      <c r="BE5" s="378"/>
+      <c r="BF5" s="378"/>
+      <c r="BG5" s="378"/>
+      <c r="BH5" s="378"/>
+      <c r="BI5" s="378"/>
+      <c r="BJ5" s="378"/>
+      <c r="BK5" s="378"/>
+      <c r="BL5" s="378"/>
+      <c r="BM5" s="378"/>
+      <c r="BN5" s="378"/>
+      <c r="BO5" s="378"/>
+      <c r="BP5" s="378"/>
+      <c r="BQ5" s="379"/>
+      <c r="BR5" s="398" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="404"/>
-      <c r="BT5" s="397" t="s">
+      <c r="BS5" s="391"/>
+      <c r="BT5" s="377" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="391" t="s">
+      <c r="BU5" s="409" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="394" t="s">
+      <c r="BW5" s="410" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="405" t="s">
+      <c r="BX5" s="399" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="406"/>
-      <c r="BZ5" s="406"/>
-      <c r="CA5" s="404"/>
-      <c r="CB5" s="400" t="s">
+      <c r="BY5" s="400"/>
+      <c r="BZ5" s="400"/>
+      <c r="CA5" s="391"/>
+      <c r="CB5" s="411" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="382" t="s">
+      <c r="CC5" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="382" t="s">
+      <c r="CD5" s="396" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="383"/>
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
-      <c r="D6" s="383"/>
-      <c r="E6" s="383"/>
-      <c r="F6" s="383"/>
-      <c r="G6" s="383"/>
-      <c r="H6" s="383"/>
-      <c r="I6" s="383"/>
-      <c r="J6" s="383"/>
-      <c r="K6" s="388" t="s">
+      <c r="A6" s="375"/>
+      <c r="B6" s="375"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="375"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
+      <c r="G6" s="375"/>
+      <c r="H6" s="375"/>
+      <c r="I6" s="375"/>
+      <c r="J6" s="375"/>
+      <c r="K6" s="389" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="388" t="s">
+      <c r="L6" s="389" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="388" t="s">
+      <c r="M6" s="389" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="388" t="s">
+      <c r="N6" s="389" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="388" t="s">
+      <c r="O6" s="389" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="388" t="s">
+      <c r="P6" s="389" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="388" t="s">
+      <c r="Q6" s="389" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="388" t="s">
+      <c r="R6" s="389" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="388" t="s">
+      <c r="S6" s="389" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="388" t="s">
+      <c r="T6" s="389" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="388" t="s">
+      <c r="U6" s="389" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="418" t="s">
+      <c r="V6" s="390" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="404"/>
-      <c r="X6" s="388" t="s">
+      <c r="W6" s="391"/>
+      <c r="X6" s="389" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="387" t="s">
+      <c r="Y6" s="381" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="387" t="s">
+      <c r="Z6" s="381" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="387" t="s">
+      <c r="AA6" s="381" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="387" t="s">
+      <c r="AB6" s="381" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="333" t="s">
+      <c r="AC6" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="333" t="s">
+      <c r="AD6" s="337" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="337" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="333" t="s">
+      <c r="AF6" s="337" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="387" t="s">
+      <c r="AG6" s="381" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="333" t="s">
+      <c r="AH6" s="337" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="333" t="s">
+      <c r="AI6" s="337" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="387" t="s">
+      <c r="AJ6" s="381" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="415" t="s">
+      <c r="AK6" s="383" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="387" t="s">
+      <c r="AL6" s="381" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="387" t="s">
+      <c r="AM6" s="381" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="417" t="s">
+      <c r="AN6" s="387" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="387" t="s">
+      <c r="AO6" s="381" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="383"/>
-      <c r="AQ6" s="383"/>
-      <c r="AR6" s="383"/>
-      <c r="AS6" s="383"/>
-      <c r="AT6" s="383"/>
-      <c r="AU6" s="383"/>
-      <c r="AV6" s="383"/>
-      <c r="AW6" s="383"/>
-      <c r="AX6" s="383"/>
-      <c r="AY6" s="397" t="s">
+      <c r="AP6" s="375"/>
+      <c r="AQ6" s="375"/>
+      <c r="AR6" s="375"/>
+      <c r="AS6" s="375"/>
+      <c r="AT6" s="375"/>
+      <c r="AU6" s="375"/>
+      <c r="AV6" s="375"/>
+      <c r="AW6" s="375"/>
+      <c r="AX6" s="375"/>
+      <c r="AY6" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="398"/>
-      <c r="BA6" s="398"/>
-      <c r="BB6" s="398"/>
-      <c r="BC6" s="398"/>
-      <c r="BD6" s="398"/>
-      <c r="BE6" s="398"/>
-      <c r="BF6" s="398"/>
-      <c r="BG6" s="398"/>
-      <c r="BH6" s="398"/>
-      <c r="BI6" s="398"/>
-      <c r="BJ6" s="398"/>
-      <c r="BK6" s="398"/>
-      <c r="BL6" s="399"/>
-      <c r="BM6" s="397" t="s">
+      <c r="AZ6" s="378"/>
+      <c r="BA6" s="378"/>
+      <c r="BB6" s="378"/>
+      <c r="BC6" s="378"/>
+      <c r="BD6" s="378"/>
+      <c r="BE6" s="378"/>
+      <c r="BF6" s="378"/>
+      <c r="BG6" s="378"/>
+      <c r="BH6" s="378"/>
+      <c r="BI6" s="378"/>
+      <c r="BJ6" s="378"/>
+      <c r="BK6" s="378"/>
+      <c r="BL6" s="379"/>
+      <c r="BM6" s="377" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="398"/>
-      <c r="BO6" s="398"/>
-      <c r="BP6" s="398"/>
-      <c r="BQ6" s="399"/>
-      <c r="BR6" s="385" t="s">
+      <c r="BN6" s="378"/>
+      <c r="BO6" s="378"/>
+      <c r="BP6" s="378"/>
+      <c r="BQ6" s="379"/>
+      <c r="BR6" s="374" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="385" t="s">
+      <c r="BS6" s="374" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="383"/>
-      <c r="BU6" s="392"/>
-      <c r="BW6" s="395"/>
-      <c r="BX6" s="392"/>
-      <c r="BY6" s="407"/>
-      <c r="BZ6" s="407"/>
-      <c r="CA6" s="395"/>
-      <c r="CB6" s="383"/>
-      <c r="CC6" s="383"/>
-      <c r="CD6" s="383"/>
+      <c r="BT6" s="375"/>
+      <c r="BU6" s="384"/>
+      <c r="BW6" s="402"/>
+      <c r="BX6" s="384"/>
+      <c r="BY6" s="401"/>
+      <c r="BZ6" s="401"/>
+      <c r="CA6" s="402"/>
+      <c r="CB6" s="375"/>
+      <c r="CC6" s="375"/>
+      <c r="CD6" s="375"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="383"/>
-      <c r="B7" s="383"/>
-      <c r="C7" s="383"/>
-      <c r="D7" s="383"/>
-      <c r="E7" s="383"/>
-      <c r="F7" s="383"/>
-      <c r="G7" s="383"/>
-      <c r="H7" s="383"/>
-      <c r="I7" s="383"/>
-      <c r="J7" s="383"/>
-      <c r="K7" s="383"/>
-      <c r="L7" s="383"/>
-      <c r="M7" s="383"/>
-      <c r="N7" s="383"/>
-      <c r="O7" s="383"/>
-      <c r="P7" s="383"/>
-      <c r="Q7" s="383"/>
-      <c r="R7" s="383"/>
-      <c r="S7" s="383"/>
-      <c r="T7" s="383"/>
-      <c r="U7" s="383"/>
-      <c r="V7" s="393"/>
-      <c r="W7" s="419"/>
-      <c r="X7" s="383"/>
-      <c r="Y7" s="383"/>
-      <c r="Z7" s="383"/>
-      <c r="AA7" s="383"/>
-      <c r="AB7" s="383"/>
-      <c r="AC7" s="383"/>
-      <c r="AD7" s="383"/>
-      <c r="AE7" s="383"/>
-      <c r="AF7" s="383"/>
-      <c r="AG7" s="383"/>
-      <c r="AH7" s="383"/>
-      <c r="AI7" s="383"/>
-      <c r="AJ7" s="383"/>
-      <c r="AK7" s="392"/>
-      <c r="AL7" s="383"/>
-      <c r="AM7" s="383"/>
-      <c r="AN7" s="383"/>
-      <c r="AO7" s="383"/>
-      <c r="AP7" s="383"/>
-      <c r="AQ7" s="383"/>
-      <c r="AR7" s="383"/>
-      <c r="AS7" s="383"/>
-      <c r="AT7" s="383"/>
-      <c r="AU7" s="383"/>
-      <c r="AV7" s="383"/>
-      <c r="AW7" s="383"/>
-      <c r="AX7" s="383"/>
+      <c r="A7" s="375"/>
+      <c r="B7" s="375"/>
+      <c r="C7" s="375"/>
+      <c r="D7" s="375"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
+      <c r="G7" s="375"/>
+      <c r="H7" s="375"/>
+      <c r="I7" s="375"/>
+      <c r="J7" s="375"/>
+      <c r="K7" s="375"/>
+      <c r="L7" s="375"/>
+      <c r="M7" s="375"/>
+      <c r="N7" s="375"/>
+      <c r="O7" s="375"/>
+      <c r="P7" s="375"/>
+      <c r="Q7" s="375"/>
+      <c r="R7" s="375"/>
+      <c r="S7" s="375"/>
+      <c r="T7" s="375"/>
+      <c r="U7" s="375"/>
+      <c r="V7" s="385"/>
+      <c r="W7" s="392"/>
+      <c r="X7" s="375"/>
+      <c r="Y7" s="375"/>
+      <c r="Z7" s="375"/>
+      <c r="AA7" s="375"/>
+      <c r="AB7" s="375"/>
+      <c r="AC7" s="375"/>
+      <c r="AD7" s="375"/>
+      <c r="AE7" s="375"/>
+      <c r="AF7" s="375"/>
+      <c r="AG7" s="375"/>
+      <c r="AH7" s="375"/>
+      <c r="AI7" s="375"/>
+      <c r="AJ7" s="375"/>
+      <c r="AK7" s="384"/>
+      <c r="AL7" s="375"/>
+      <c r="AM7" s="375"/>
+      <c r="AN7" s="375"/>
+      <c r="AO7" s="375"/>
+      <c r="AP7" s="375"/>
+      <c r="AQ7" s="375"/>
+      <c r="AR7" s="375"/>
+      <c r="AS7" s="375"/>
+      <c r="AT7" s="375"/>
+      <c r="AU7" s="375"/>
+      <c r="AV7" s="375"/>
+      <c r="AW7" s="375"/>
+      <c r="AX7" s="375"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12026,124 +12077,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="397" t="s">
+      <c r="BB7" s="377" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="389" t="s">
+      <c r="BC7" s="380" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="389" t="s">
+      <c r="BD7" s="380" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="410" t="s">
+      <c r="BE7" s="406" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="389" t="s">
+      <c r="BF7" s="380" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="389" t="s">
+      <c r="BG7" s="380" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="389" t="s">
+      <c r="BH7" s="380" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="389" t="s">
+      <c r="BI7" s="380" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="389" t="s">
+      <c r="BJ7" s="380" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="389" t="s">
+      <c r="BK7" s="380" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="390" t="s">
+      <c r="BL7" s="408" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="389" t="s">
+      <c r="BM7" s="380" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="397" t="s">
+      <c r="BN7" s="377" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="389" t="s">
+      <c r="BO7" s="380" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="397" t="s">
+      <c r="BP7" s="377" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="397" t="s">
+      <c r="BQ7" s="377" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="383"/>
-      <c r="BS7" s="383"/>
-      <c r="BT7" s="383"/>
-      <c r="BU7" s="392"/>
-      <c r="BW7" s="395"/>
-      <c r="BX7" s="408"/>
-      <c r="BY7" s="409"/>
-      <c r="BZ7" s="409"/>
-      <c r="CA7" s="396"/>
-      <c r="CB7" s="383"/>
-      <c r="CC7" s="383"/>
-      <c r="CD7" s="383"/>
+      <c r="BR7" s="375"/>
+      <c r="BS7" s="375"/>
+      <c r="BT7" s="375"/>
+      <c r="BU7" s="384"/>
+      <c r="BW7" s="402"/>
+      <c r="BX7" s="403"/>
+      <c r="BY7" s="404"/>
+      <c r="BZ7" s="404"/>
+      <c r="CA7" s="405"/>
+      <c r="CB7" s="375"/>
+      <c r="CC7" s="375"/>
+      <c r="CD7" s="375"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="386"/>
-      <c r="B8" s="386"/>
-      <c r="C8" s="386"/>
-      <c r="D8" s="386"/>
-      <c r="E8" s="386"/>
-      <c r="F8" s="386"/>
-      <c r="G8" s="386"/>
-      <c r="H8" s="386"/>
-      <c r="I8" s="386"/>
-      <c r="J8" s="386"/>
-      <c r="K8" s="386"/>
-      <c r="L8" s="386"/>
-      <c r="M8" s="386"/>
-      <c r="N8" s="386"/>
-      <c r="O8" s="386"/>
-      <c r="P8" s="386"/>
-      <c r="Q8" s="386"/>
-      <c r="R8" s="386"/>
-      <c r="S8" s="386"/>
-      <c r="T8" s="386"/>
-      <c r="U8" s="386"/>
+      <c r="A8" s="376"/>
+      <c r="B8" s="376"/>
+      <c r="C8" s="376"/>
+      <c r="D8" s="376"/>
+      <c r="E8" s="376"/>
+      <c r="F8" s="376"/>
+      <c r="G8" s="376"/>
+      <c r="H8" s="376"/>
+      <c r="I8" s="376"/>
+      <c r="J8" s="376"/>
+      <c r="K8" s="376"/>
+      <c r="L8" s="376"/>
+      <c r="M8" s="376"/>
+      <c r="N8" s="376"/>
+      <c r="O8" s="376"/>
+      <c r="P8" s="376"/>
+      <c r="Q8" s="376"/>
+      <c r="R8" s="376"/>
+      <c r="S8" s="376"/>
+      <c r="T8" s="376"/>
+      <c r="U8" s="376"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="386"/>
-      <c r="Y8" s="386"/>
-      <c r="Z8" s="386"/>
-      <c r="AA8" s="386"/>
-      <c r="AB8" s="386"/>
-      <c r="AC8" s="386"/>
-      <c r="AD8" s="386"/>
-      <c r="AE8" s="386"/>
-      <c r="AF8" s="386"/>
-      <c r="AG8" s="386"/>
-      <c r="AH8" s="386"/>
-      <c r="AI8" s="386"/>
-      <c r="AJ8" s="386"/>
-      <c r="AK8" s="393"/>
-      <c r="AL8" s="386"/>
-      <c r="AM8" s="386"/>
-      <c r="AN8" s="386"/>
-      <c r="AO8" s="386"/>
-      <c r="AP8" s="386"/>
-      <c r="AQ8" s="386"/>
-      <c r="AR8" s="386"/>
-      <c r="AS8" s="386"/>
-      <c r="AT8" s="386"/>
-      <c r="AU8" s="386"/>
-      <c r="AV8" s="386"/>
-      <c r="AW8" s="386"/>
-      <c r="AX8" s="386"/>
+      <c r="X8" s="376"/>
+      <c r="Y8" s="376"/>
+      <c r="Z8" s="376"/>
+      <c r="AA8" s="376"/>
+      <c r="AB8" s="376"/>
+      <c r="AC8" s="376"/>
+      <c r="AD8" s="376"/>
+      <c r="AE8" s="376"/>
+      <c r="AF8" s="376"/>
+      <c r="AG8" s="376"/>
+      <c r="AH8" s="376"/>
+      <c r="AI8" s="376"/>
+      <c r="AJ8" s="376"/>
+      <c r="AK8" s="385"/>
+      <c r="AL8" s="376"/>
+      <c r="AM8" s="376"/>
+      <c r="AN8" s="376"/>
+      <c r="AO8" s="376"/>
+      <c r="AP8" s="376"/>
+      <c r="AQ8" s="376"/>
+      <c r="AR8" s="376"/>
+      <c r="AS8" s="376"/>
+      <c r="AT8" s="376"/>
+      <c r="AU8" s="376"/>
+      <c r="AV8" s="376"/>
+      <c r="AW8" s="376"/>
+      <c r="AX8" s="376"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12153,27 +12204,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="386"/>
-      <c r="BC8" s="386"/>
-      <c r="BD8" s="386"/>
-      <c r="BE8" s="386"/>
-      <c r="BF8" s="386"/>
-      <c r="BG8" s="386"/>
-      <c r="BH8" s="386"/>
-      <c r="BI8" s="386"/>
-      <c r="BJ8" s="386"/>
-      <c r="BK8" s="386"/>
-      <c r="BL8" s="386"/>
-      <c r="BM8" s="386"/>
-      <c r="BN8" s="386"/>
-      <c r="BO8" s="386"/>
-      <c r="BP8" s="386"/>
-      <c r="BQ8" s="386"/>
-      <c r="BR8" s="386"/>
-      <c r="BS8" s="386"/>
-      <c r="BT8" s="386"/>
-      <c r="BU8" s="393"/>
-      <c r="BW8" s="396"/>
+      <c r="BB8" s="376"/>
+      <c r="BC8" s="376"/>
+      <c r="BD8" s="376"/>
+      <c r="BE8" s="376"/>
+      <c r="BF8" s="376"/>
+      <c r="BG8" s="376"/>
+      <c r="BH8" s="376"/>
+      <c r="BI8" s="376"/>
+      <c r="BJ8" s="376"/>
+      <c r="BK8" s="376"/>
+      <c r="BL8" s="376"/>
+      <c r="BM8" s="376"/>
+      <c r="BN8" s="376"/>
+      <c r="BO8" s="376"/>
+      <c r="BP8" s="376"/>
+      <c r="BQ8" s="376"/>
+      <c r="BR8" s="376"/>
+      <c r="BS8" s="376"/>
+      <c r="BT8" s="376"/>
+      <c r="BU8" s="385"/>
+      <c r="BW8" s="405"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12186,9 +12237,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="384"/>
-      <c r="CC8" s="384"/>
-      <c r="CD8" s="384"/>
+      <c r="CB8" s="397"/>
+      <c r="CC8" s="397"/>
+      <c r="CD8" s="397"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14646,6 +14697,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="BS6:BS8"/>
     <mergeCell ref="BM6:BQ6"/>
     <mergeCell ref="AC6:AC8"/>
@@ -14662,72 +14779,6 @@
     <mergeCell ref="BD7:BD8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -14955,88 +15006,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="429"/>
-      <c r="B3" s="428"/>
-      <c r="C3" s="428"/>
-      <c r="D3" s="428"/>
-      <c r="E3" s="428"/>
-      <c r="F3" s="428"/>
-      <c r="G3" s="428"/>
-      <c r="H3" s="428"/>
-      <c r="I3" s="428"/>
-      <c r="J3" s="428"/>
-      <c r="K3" s="428"/>
-      <c r="L3" s="428"/>
-      <c r="M3" s="428"/>
-      <c r="N3" s="428"/>
-      <c r="O3" s="428"/>
-      <c r="P3" s="428"/>
-      <c r="Q3" s="428"/>
-      <c r="R3" s="428"/>
-      <c r="S3" s="428"/>
-      <c r="T3" s="428"/>
-      <c r="U3" s="428"/>
-      <c r="V3" s="428"/>
-      <c r="W3" s="428"/>
-      <c r="X3" s="428"/>
-      <c r="Y3" s="428"/>
-      <c r="Z3" s="428"/>
-      <c r="AA3" s="428"/>
-      <c r="AB3" s="428"/>
-      <c r="AC3" s="428"/>
-      <c r="AD3" s="428"/>
-      <c r="AE3" s="428"/>
-      <c r="AF3" s="428"/>
-      <c r="AG3" s="428"/>
-      <c r="AH3" s="428"/>
-      <c r="AI3" s="428"/>
-      <c r="AJ3" s="428"/>
-      <c r="AK3" s="428"/>
-      <c r="AL3" s="428"/>
-      <c r="AM3" s="428"/>
-      <c r="AN3" s="428"/>
-      <c r="AO3" s="428"/>
-      <c r="AP3" s="428"/>
-      <c r="AQ3" s="428"/>
-      <c r="AR3" s="428"/>
-      <c r="AS3" s="428"/>
-      <c r="AT3" s="428"/>
-      <c r="AU3" s="428"/>
-      <c r="AV3" s="428"/>
-      <c r="AW3" s="428"/>
-      <c r="AX3" s="428"/>
-      <c r="AY3" s="428"/>
-      <c r="AZ3" s="428"/>
-      <c r="BA3" s="428"/>
-      <c r="BB3" s="428"/>
-      <c r="BC3" s="428"/>
-      <c r="BD3" s="428"/>
-      <c r="BE3" s="428"/>
-      <c r="BF3" s="428"/>
-      <c r="BG3" s="428"/>
-      <c r="BH3" s="428"/>
-      <c r="BI3" s="428"/>
-      <c r="BJ3" s="428"/>
-      <c r="BK3" s="428"/>
-      <c r="BL3" s="428"/>
-      <c r="BM3" s="428"/>
-      <c r="BN3" s="428"/>
-      <c r="BO3" s="428"/>
-      <c r="BP3" s="428"/>
-      <c r="BQ3" s="428"/>
-      <c r="BR3" s="428"/>
-      <c r="BS3" s="428"/>
-      <c r="BT3" s="428"/>
-      <c r="BU3" s="428"/>
+      <c r="A3" s="422"/>
+      <c r="B3" s="421"/>
+      <c r="C3" s="421"/>
+      <c r="D3" s="421"/>
+      <c r="E3" s="421"/>
+      <c r="F3" s="421"/>
+      <c r="G3" s="421"/>
+      <c r="H3" s="421"/>
+      <c r="I3" s="421"/>
+      <c r="J3" s="421"/>
+      <c r="K3" s="421"/>
+      <c r="L3" s="421"/>
+      <c r="M3" s="421"/>
+      <c r="N3" s="421"/>
+      <c r="O3" s="421"/>
+      <c r="P3" s="421"/>
+      <c r="Q3" s="421"/>
+      <c r="R3" s="421"/>
+      <c r="S3" s="421"/>
+      <c r="T3" s="421"/>
+      <c r="U3" s="421"/>
+      <c r="V3" s="421"/>
+      <c r="W3" s="421"/>
+      <c r="X3" s="421"/>
+      <c r="Y3" s="421"/>
+      <c r="Z3" s="421"/>
+      <c r="AA3" s="421"/>
+      <c r="AB3" s="421"/>
+      <c r="AC3" s="421"/>
+      <c r="AD3" s="421"/>
+      <c r="AE3" s="421"/>
+      <c r="AF3" s="421"/>
+      <c r="AG3" s="421"/>
+      <c r="AH3" s="421"/>
+      <c r="AI3" s="421"/>
+      <c r="AJ3" s="421"/>
+      <c r="AK3" s="421"/>
+      <c r="AL3" s="421"/>
+      <c r="AM3" s="421"/>
+      <c r="AN3" s="421"/>
+      <c r="AO3" s="421"/>
+      <c r="AP3" s="421"/>
+      <c r="AQ3" s="421"/>
+      <c r="AR3" s="421"/>
+      <c r="AS3" s="421"/>
+      <c r="AT3" s="421"/>
+      <c r="AU3" s="421"/>
+      <c r="AV3" s="421"/>
+      <c r="AW3" s="421"/>
+      <c r="AX3" s="421"/>
+      <c r="AY3" s="421"/>
+      <c r="AZ3" s="421"/>
+      <c r="BA3" s="421"/>
+      <c r="BB3" s="421"/>
+      <c r="BC3" s="421"/>
+      <c r="BD3" s="421"/>
+      <c r="BE3" s="421"/>
+      <c r="BF3" s="421"/>
+      <c r="BG3" s="421"/>
+      <c r="BH3" s="421"/>
+      <c r="BI3" s="421"/>
+      <c r="BJ3" s="421"/>
+      <c r="BK3" s="421"/>
+      <c r="BL3" s="421"/>
+      <c r="BM3" s="421"/>
+      <c r="BN3" s="421"/>
+      <c r="BO3" s="421"/>
+      <c r="BP3" s="421"/>
+      <c r="BQ3" s="421"/>
+      <c r="BR3" s="421"/>
+      <c r="BS3" s="421"/>
+      <c r="BT3" s="421"/>
+      <c r="BU3" s="421"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="427" t="s">
+      <c r="BW3" s="420" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="428"/>
-      <c r="BY3" s="428"/>
-      <c r="BZ3" s="428"/>
-      <c r="CA3" s="428"/>
-      <c r="CB3" s="428"/>
+      <c r="BX3" s="421"/>
+      <c r="BY3" s="421"/>
+      <c r="BZ3" s="421"/>
+      <c r="CA3" s="421"/>
+      <c r="CB3" s="421"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15120,12 +15171,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="428"/>
-      <c r="BX4" s="428"/>
-      <c r="BY4" s="428"/>
-      <c r="BZ4" s="428"/>
-      <c r="CA4" s="428"/>
-      <c r="CB4" s="428"/>
+      <c r="BW4" s="421"/>
+      <c r="BX4" s="421"/>
+      <c r="BY4" s="421"/>
+      <c r="BZ4" s="421"/>
+      <c r="CA4" s="421"/>
+      <c r="CB4" s="421"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15203,12 +15254,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="360"/>
-      <c r="BX5" s="360"/>
-      <c r="BY5" s="360"/>
-      <c r="BZ5" s="360"/>
-      <c r="CA5" s="360"/>
-      <c r="CB5" s="360"/>
+      <c r="BW5" s="351"/>
+      <c r="BX5" s="351"/>
+      <c r="BY5" s="351"/>
+      <c r="BZ5" s="351"/>
+      <c r="CA5" s="351"/>
+      <c r="CB5" s="351"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15286,12 +15337,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="360"/>
-      <c r="BX6" s="360"/>
-      <c r="BY6" s="360"/>
-      <c r="BZ6" s="360"/>
-      <c r="CA6" s="360"/>
-      <c r="CB6" s="360"/>
+      <c r="BW6" s="351"/>
+      <c r="BX6" s="351"/>
+      <c r="BY6" s="351"/>
+      <c r="BZ6" s="351"/>
+      <c r="CA6" s="351"/>
+      <c r="CB6" s="351"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15379,358 +15430,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="414" t="s">
+      <c r="A8" s="382" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="413" t="s">
+      <c r="B8" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="387" t="s">
+      <c r="C8" s="381" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="412" t="s">
+      <c r="D8" s="388" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="412" t="s">
+      <c r="E8" s="388" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="431" t="s">
+      <c r="F8" s="418" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="421" t="s">
+      <c r="G8" s="415" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="352" t="s">
+      <c r="H8" s="366" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="352" t="s">
+      <c r="I8" s="366" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="421" t="s">
+      <c r="J8" s="415" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="432" t="s">
+      <c r="K8" s="419" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="398"/>
-      <c r="M8" s="398"/>
-      <c r="N8" s="398"/>
-      <c r="O8" s="398"/>
-      <c r="P8" s="398"/>
-      <c r="Q8" s="398"/>
-      <c r="R8" s="398"/>
-      <c r="S8" s="398"/>
-      <c r="T8" s="398"/>
-      <c r="U8" s="398"/>
-      <c r="V8" s="398"/>
-      <c r="W8" s="398"/>
-      <c r="X8" s="398"/>
-      <c r="Y8" s="421" t="s">
+      <c r="L8" s="378"/>
+      <c r="M8" s="378"/>
+      <c r="N8" s="378"/>
+      <c r="O8" s="378"/>
+      <c r="P8" s="378"/>
+      <c r="Q8" s="378"/>
+      <c r="R8" s="378"/>
+      <c r="S8" s="378"/>
+      <c r="T8" s="378"/>
+      <c r="U8" s="378"/>
+      <c r="V8" s="378"/>
+      <c r="W8" s="378"/>
+      <c r="X8" s="378"/>
+      <c r="Y8" s="415" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="398"/>
-      <c r="AA8" s="398"/>
-      <c r="AB8" s="398"/>
-      <c r="AC8" s="398"/>
-      <c r="AD8" s="398"/>
-      <c r="AE8" s="398"/>
-      <c r="AF8" s="398"/>
-      <c r="AG8" s="398"/>
-      <c r="AH8" s="398"/>
-      <c r="AI8" s="398"/>
-      <c r="AJ8" s="398"/>
-      <c r="AK8" s="398"/>
-      <c r="AL8" s="398"/>
-      <c r="AM8" s="398"/>
-      <c r="AN8" s="398"/>
-      <c r="AO8" s="399"/>
-      <c r="AP8" s="421" t="s">
+      <c r="Z8" s="378"/>
+      <c r="AA8" s="378"/>
+      <c r="AB8" s="378"/>
+      <c r="AC8" s="378"/>
+      <c r="AD8" s="378"/>
+      <c r="AE8" s="378"/>
+      <c r="AF8" s="378"/>
+      <c r="AG8" s="378"/>
+      <c r="AH8" s="378"/>
+      <c r="AI8" s="378"/>
+      <c r="AJ8" s="378"/>
+      <c r="AK8" s="378"/>
+      <c r="AL8" s="378"/>
+      <c r="AM8" s="378"/>
+      <c r="AN8" s="378"/>
+      <c r="AO8" s="379"/>
+      <c r="AP8" s="415" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="421" t="s">
+      <c r="AQ8" s="415" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="421" t="s">
+      <c r="AR8" s="415" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="421" t="s">
+      <c r="AS8" s="415" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="421" t="s">
+      <c r="AT8" s="415" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="421" t="s">
+      <c r="AU8" s="415" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="387" t="s">
+      <c r="AV8" s="381" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="387" t="s">
+      <c r="AW8" s="381" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="387" t="s">
+      <c r="AX8" s="381" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="397" t="s">
+      <c r="AY8" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="398"/>
-      <c r="BA8" s="398"/>
-      <c r="BB8" s="398"/>
-      <c r="BC8" s="398"/>
-      <c r="BD8" s="398"/>
-      <c r="BE8" s="398"/>
-      <c r="BF8" s="398"/>
-      <c r="BG8" s="398"/>
-      <c r="BH8" s="398"/>
-      <c r="BI8" s="398"/>
-      <c r="BJ8" s="398"/>
-      <c r="BK8" s="398"/>
-      <c r="BL8" s="398"/>
-      <c r="BM8" s="398"/>
-      <c r="BN8" s="398"/>
-      <c r="BO8" s="398"/>
-      <c r="BP8" s="399"/>
-      <c r="BQ8" s="403" t="s">
+      <c r="AZ8" s="378"/>
+      <c r="BA8" s="378"/>
+      <c r="BB8" s="378"/>
+      <c r="BC8" s="378"/>
+      <c r="BD8" s="378"/>
+      <c r="BE8" s="378"/>
+      <c r="BF8" s="378"/>
+      <c r="BG8" s="378"/>
+      <c r="BH8" s="378"/>
+      <c r="BI8" s="378"/>
+      <c r="BJ8" s="378"/>
+      <c r="BK8" s="378"/>
+      <c r="BL8" s="378"/>
+      <c r="BM8" s="378"/>
+      <c r="BN8" s="378"/>
+      <c r="BO8" s="378"/>
+      <c r="BP8" s="379"/>
+      <c r="BQ8" s="398" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="404"/>
-      <c r="BS8" s="397" t="s">
+      <c r="BR8" s="391"/>
+      <c r="BS8" s="377" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="397" t="s">
+      <c r="BT8" s="377" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="391" t="s">
+      <c r="BU8" s="409" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="394" t="s">
+      <c r="BW8" s="410" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="405" t="s">
+      <c r="BX8" s="399" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="406"/>
-      <c r="BZ8" s="406"/>
-      <c r="CA8" s="404"/>
-      <c r="CB8" s="400" t="s">
+      <c r="BY8" s="400"/>
+      <c r="BZ8" s="400"/>
+      <c r="CA8" s="391"/>
+      <c r="CB8" s="411" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="382" t="s">
+      <c r="CC8" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="382" t="s">
+      <c r="CD8" s="396" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="383"/>
-      <c r="B9" s="383"/>
-      <c r="C9" s="383"/>
-      <c r="D9" s="383"/>
-      <c r="E9" s="383"/>
-      <c r="F9" s="383"/>
-      <c r="G9" s="383"/>
-      <c r="H9" s="383"/>
-      <c r="I9" s="383"/>
-      <c r="J9" s="383"/>
-      <c r="K9" s="423" t="s">
+      <c r="A9" s="375"/>
+      <c r="B9" s="375"/>
+      <c r="C9" s="375"/>
+      <c r="D9" s="375"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
+      <c r="G9" s="375"/>
+      <c r="H9" s="375"/>
+      <c r="I9" s="375"/>
+      <c r="J9" s="375"/>
+      <c r="K9" s="412" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="423" t="s">
+      <c r="L9" s="412" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="423" t="s">
+      <c r="M9" s="412" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="423" t="s">
+      <c r="N9" s="412" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="423" t="s">
+      <c r="O9" s="412" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="423" t="s">
+      <c r="P9" s="412" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="423" t="s">
+      <c r="Q9" s="412" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="423" t="s">
+      <c r="R9" s="412" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="423" t="s">
+      <c r="S9" s="412" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="423" t="s">
+      <c r="T9" s="412" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="423" t="s">
+      <c r="U9" s="412" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="426" t="s">
+      <c r="V9" s="424" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="404"/>
-      <c r="X9" s="423" t="s">
+      <c r="W9" s="391"/>
+      <c r="X9" s="412" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="420" t="s">
+      <c r="Y9" s="414" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="420" t="s">
+      <c r="Z9" s="414" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="420" t="s">
+      <c r="AA9" s="414" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="420" t="s">
+      <c r="AB9" s="414" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="336" t="s">
+      <c r="AC9" s="340" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="336" t="s">
+      <c r="AD9" s="340" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="336" t="s">
+      <c r="AE9" s="340" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="336" t="s">
+      <c r="AF9" s="340" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="420" t="s">
+      <c r="AG9" s="414" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="336" t="s">
+      <c r="AH9" s="340" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="336" t="s">
+      <c r="AI9" s="340" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="420" t="s">
+      <c r="AJ9" s="414" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="415" t="s">
+      <c r="AK9" s="383" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="387" t="s">
+      <c r="AL9" s="381" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="420" t="s">
+      <c r="AM9" s="414" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="417" t="s">
+      <c r="AN9" s="387" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="387" t="s">
+      <c r="AO9" s="381" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="383"/>
-      <c r="AQ9" s="383"/>
-      <c r="AR9" s="383"/>
-      <c r="AS9" s="383"/>
-      <c r="AT9" s="383"/>
-      <c r="AU9" s="383"/>
-      <c r="AV9" s="383"/>
-      <c r="AW9" s="383"/>
-      <c r="AX9" s="383"/>
-      <c r="AY9" s="397" t="s">
+      <c r="AP9" s="375"/>
+      <c r="AQ9" s="375"/>
+      <c r="AR9" s="375"/>
+      <c r="AS9" s="375"/>
+      <c r="AT9" s="375"/>
+      <c r="AU9" s="375"/>
+      <c r="AV9" s="375"/>
+      <c r="AW9" s="375"/>
+      <c r="AX9" s="375"/>
+      <c r="AY9" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="398"/>
-      <c r="BA9" s="398"/>
-      <c r="BB9" s="398"/>
-      <c r="BC9" s="398"/>
-      <c r="BD9" s="398"/>
-      <c r="BE9" s="398"/>
-      <c r="BF9" s="398"/>
-      <c r="BG9" s="398"/>
-      <c r="BH9" s="398"/>
-      <c r="BI9" s="398"/>
-      <c r="BJ9" s="399"/>
-      <c r="BK9" s="397" t="s">
+      <c r="AZ9" s="378"/>
+      <c r="BA9" s="378"/>
+      <c r="BB9" s="378"/>
+      <c r="BC9" s="378"/>
+      <c r="BD9" s="378"/>
+      <c r="BE9" s="378"/>
+      <c r="BF9" s="378"/>
+      <c r="BG9" s="378"/>
+      <c r="BH9" s="378"/>
+      <c r="BI9" s="378"/>
+      <c r="BJ9" s="379"/>
+      <c r="BK9" s="377" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="398"/>
-      <c r="BM9" s="398"/>
-      <c r="BN9" s="398"/>
-      <c r="BO9" s="398"/>
-      <c r="BP9" s="399"/>
-      <c r="BQ9" s="385" t="s">
+      <c r="BL9" s="378"/>
+      <c r="BM9" s="378"/>
+      <c r="BN9" s="378"/>
+      <c r="BO9" s="378"/>
+      <c r="BP9" s="379"/>
+      <c r="BQ9" s="374" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="385" t="s">
+      <c r="BR9" s="374" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="383"/>
-      <c r="BT9" s="383"/>
-      <c r="BU9" s="392"/>
+      <c r="BS9" s="375"/>
+      <c r="BT9" s="375"/>
+      <c r="BU9" s="384"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="395"/>
-      <c r="BX9" s="392"/>
-      <c r="BY9" s="433"/>
-      <c r="BZ9" s="433"/>
-      <c r="CA9" s="395"/>
-      <c r="CB9" s="383"/>
-      <c r="CC9" s="383"/>
-      <c r="CD9" s="383"/>
+      <c r="BW9" s="402"/>
+      <c r="BX9" s="384"/>
+      <c r="BY9" s="416"/>
+      <c r="BZ9" s="416"/>
+      <c r="CA9" s="402"/>
+      <c r="CB9" s="375"/>
+      <c r="CC9" s="375"/>
+      <c r="CD9" s="375"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="383"/>
-      <c r="B10" s="383"/>
-      <c r="C10" s="383"/>
-      <c r="D10" s="383"/>
-      <c r="E10" s="383"/>
-      <c r="F10" s="383"/>
-      <c r="G10" s="383"/>
-      <c r="H10" s="383"/>
-      <c r="I10" s="383"/>
-      <c r="J10" s="383"/>
-      <c r="K10" s="383"/>
-      <c r="L10" s="383"/>
-      <c r="M10" s="383"/>
-      <c r="N10" s="383"/>
-      <c r="O10" s="383"/>
-      <c r="P10" s="383"/>
-      <c r="Q10" s="383"/>
-      <c r="R10" s="383"/>
-      <c r="S10" s="383"/>
-      <c r="T10" s="383"/>
-      <c r="U10" s="383"/>
-      <c r="V10" s="393"/>
-      <c r="W10" s="419"/>
-      <c r="X10" s="383"/>
-      <c r="Y10" s="383"/>
-      <c r="Z10" s="383"/>
-      <c r="AA10" s="383"/>
-      <c r="AB10" s="383"/>
-      <c r="AC10" s="383"/>
-      <c r="AD10" s="383"/>
-      <c r="AE10" s="383"/>
-      <c r="AF10" s="383"/>
-      <c r="AG10" s="383"/>
-      <c r="AH10" s="383"/>
-      <c r="AI10" s="383"/>
-      <c r="AJ10" s="383"/>
-      <c r="AK10" s="392"/>
-      <c r="AL10" s="383"/>
-      <c r="AM10" s="383"/>
-      <c r="AN10" s="383"/>
-      <c r="AO10" s="383"/>
-      <c r="AP10" s="383"/>
-      <c r="AQ10" s="383"/>
-      <c r="AR10" s="383"/>
-      <c r="AS10" s="383"/>
-      <c r="AT10" s="383"/>
-      <c r="AU10" s="383"/>
-      <c r="AV10" s="383"/>
-      <c r="AW10" s="383"/>
-      <c r="AX10" s="383"/>
+      <c r="A10" s="375"/>
+      <c r="B10" s="375"/>
+      <c r="C10" s="375"/>
+      <c r="D10" s="375"/>
+      <c r="E10" s="375"/>
+      <c r="F10" s="375"/>
+      <c r="G10" s="375"/>
+      <c r="H10" s="375"/>
+      <c r="I10" s="375"/>
+      <c r="J10" s="375"/>
+      <c r="K10" s="375"/>
+      <c r="L10" s="375"/>
+      <c r="M10" s="375"/>
+      <c r="N10" s="375"/>
+      <c r="O10" s="375"/>
+      <c r="P10" s="375"/>
+      <c r="Q10" s="375"/>
+      <c r="R10" s="375"/>
+      <c r="S10" s="375"/>
+      <c r="T10" s="375"/>
+      <c r="U10" s="375"/>
+      <c r="V10" s="385"/>
+      <c r="W10" s="392"/>
+      <c r="X10" s="375"/>
+      <c r="Y10" s="375"/>
+      <c r="Z10" s="375"/>
+      <c r="AA10" s="375"/>
+      <c r="AB10" s="375"/>
+      <c r="AC10" s="375"/>
+      <c r="AD10" s="375"/>
+      <c r="AE10" s="375"/>
+      <c r="AF10" s="375"/>
+      <c r="AG10" s="375"/>
+      <c r="AH10" s="375"/>
+      <c r="AI10" s="375"/>
+      <c r="AJ10" s="375"/>
+      <c r="AK10" s="384"/>
+      <c r="AL10" s="375"/>
+      <c r="AM10" s="375"/>
+      <c r="AN10" s="375"/>
+      <c r="AO10" s="375"/>
+      <c r="AP10" s="375"/>
+      <c r="AQ10" s="375"/>
+      <c r="AR10" s="375"/>
+      <c r="AS10" s="375"/>
+      <c r="AT10" s="375"/>
+      <c r="AU10" s="375"/>
+      <c r="AV10" s="375"/>
+      <c r="AW10" s="375"/>
+      <c r="AX10" s="375"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15740,123 +15791,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="430" t="s">
+      <c r="BB10" s="423" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="424" t="s">
+      <c r="BC10" s="413" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="424" t="s">
+      <c r="BD10" s="413" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="424" t="s">
+      <c r="BE10" s="413" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="424" t="s">
+      <c r="BF10" s="413" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="424" t="s">
+      <c r="BG10" s="413" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="424" t="s">
+      <c r="BH10" s="413" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="424" t="s">
+      <c r="BI10" s="413" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="422" t="s">
+      <c r="BJ10" s="425" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="424" t="s">
+      <c r="BK10" s="413" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="425" t="s">
+      <c r="BL10" s="417" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="424" t="s">
+      <c r="BM10" s="413" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="425" t="s">
+      <c r="BN10" s="417" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="425" t="s">
+      <c r="BO10" s="417" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="397" t="s">
+      <c r="BP10" s="377" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="383"/>
-      <c r="BR10" s="383"/>
-      <c r="BS10" s="383"/>
-      <c r="BT10" s="383"/>
-      <c r="BU10" s="392"/>
+      <c r="BQ10" s="375"/>
+      <c r="BR10" s="375"/>
+      <c r="BS10" s="375"/>
+      <c r="BT10" s="375"/>
+      <c r="BU10" s="384"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="395"/>
-      <c r="BX10" s="408"/>
-      <c r="BY10" s="409"/>
-      <c r="BZ10" s="409"/>
-      <c r="CA10" s="396"/>
-      <c r="CB10" s="383"/>
-      <c r="CC10" s="383"/>
-      <c r="CD10" s="383"/>
+      <c r="BW10" s="402"/>
+      <c r="BX10" s="403"/>
+      <c r="BY10" s="404"/>
+      <c r="BZ10" s="404"/>
+      <c r="CA10" s="405"/>
+      <c r="CB10" s="375"/>
+      <c r="CC10" s="375"/>
+      <c r="CD10" s="375"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="386"/>
-      <c r="B11" s="386"/>
-      <c r="C11" s="386"/>
-      <c r="D11" s="386"/>
-      <c r="E11" s="386"/>
-      <c r="F11" s="386"/>
-      <c r="G11" s="386"/>
-      <c r="H11" s="386"/>
-      <c r="I11" s="386"/>
-      <c r="J11" s="386"/>
-      <c r="K11" s="386"/>
-      <c r="L11" s="386"/>
-      <c r="M11" s="386"/>
-      <c r="N11" s="386"/>
-      <c r="O11" s="386"/>
-      <c r="P11" s="386"/>
-      <c r="Q11" s="386"/>
-      <c r="R11" s="386"/>
-      <c r="S11" s="386"/>
-      <c r="T11" s="386"/>
-      <c r="U11" s="386"/>
+      <c r="A11" s="376"/>
+      <c r="B11" s="376"/>
+      <c r="C11" s="376"/>
+      <c r="D11" s="376"/>
+      <c r="E11" s="376"/>
+      <c r="F11" s="376"/>
+      <c r="G11" s="376"/>
+      <c r="H11" s="376"/>
+      <c r="I11" s="376"/>
+      <c r="J11" s="376"/>
+      <c r="K11" s="376"/>
+      <c r="L11" s="376"/>
+      <c r="M11" s="376"/>
+      <c r="N11" s="376"/>
+      <c r="O11" s="376"/>
+      <c r="P11" s="376"/>
+      <c r="Q11" s="376"/>
+      <c r="R11" s="376"/>
+      <c r="S11" s="376"/>
+      <c r="T11" s="376"/>
+      <c r="U11" s="376"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="386"/>
-      <c r="Y11" s="386"/>
-      <c r="Z11" s="386"/>
-      <c r="AA11" s="386"/>
-      <c r="AB11" s="386"/>
-      <c r="AC11" s="386"/>
-      <c r="AD11" s="386"/>
-      <c r="AE11" s="386"/>
-      <c r="AF11" s="386"/>
-      <c r="AG11" s="386"/>
-      <c r="AH11" s="386"/>
-      <c r="AI11" s="386"/>
-      <c r="AJ11" s="386"/>
-      <c r="AK11" s="393"/>
-      <c r="AL11" s="386"/>
-      <c r="AM11" s="386"/>
-      <c r="AN11" s="386"/>
-      <c r="AO11" s="386"/>
-      <c r="AP11" s="386"/>
-      <c r="AQ11" s="386"/>
-      <c r="AR11" s="386"/>
-      <c r="AS11" s="386"/>
-      <c r="AT11" s="386"/>
-      <c r="AU11" s="386"/>
-      <c r="AV11" s="386"/>
-      <c r="AW11" s="386"/>
-      <c r="AX11" s="386"/>
+      <c r="X11" s="376"/>
+      <c r="Y11" s="376"/>
+      <c r="Z11" s="376"/>
+      <c r="AA11" s="376"/>
+      <c r="AB11" s="376"/>
+      <c r="AC11" s="376"/>
+      <c r="AD11" s="376"/>
+      <c r="AE11" s="376"/>
+      <c r="AF11" s="376"/>
+      <c r="AG11" s="376"/>
+      <c r="AH11" s="376"/>
+      <c r="AI11" s="376"/>
+      <c r="AJ11" s="376"/>
+      <c r="AK11" s="385"/>
+      <c r="AL11" s="376"/>
+      <c r="AM11" s="376"/>
+      <c r="AN11" s="376"/>
+      <c r="AO11" s="376"/>
+      <c r="AP11" s="376"/>
+      <c r="AQ11" s="376"/>
+      <c r="AR11" s="376"/>
+      <c r="AS11" s="376"/>
+      <c r="AT11" s="376"/>
+      <c r="AU11" s="376"/>
+      <c r="AV11" s="376"/>
+      <c r="AW11" s="376"/>
+      <c r="AX11" s="376"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15866,28 +15917,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="386"/>
-      <c r="BC11" s="386"/>
-      <c r="BD11" s="386"/>
-      <c r="BE11" s="386"/>
-      <c r="BF11" s="386"/>
-      <c r="BG11" s="386"/>
-      <c r="BH11" s="386"/>
-      <c r="BI11" s="386"/>
-      <c r="BJ11" s="386"/>
-      <c r="BK11" s="386"/>
-      <c r="BL11" s="386"/>
-      <c r="BM11" s="386"/>
-      <c r="BN11" s="386"/>
-      <c r="BO11" s="386"/>
-      <c r="BP11" s="386"/>
-      <c r="BQ11" s="386"/>
-      <c r="BR11" s="386"/>
-      <c r="BS11" s="386"/>
-      <c r="BT11" s="386"/>
-      <c r="BU11" s="393"/>
+      <c r="BB11" s="376"/>
+      <c r="BC11" s="376"/>
+      <c r="BD11" s="376"/>
+      <c r="BE11" s="376"/>
+      <c r="BF11" s="376"/>
+      <c r="BG11" s="376"/>
+      <c r="BH11" s="376"/>
+      <c r="BI11" s="376"/>
+      <c r="BJ11" s="376"/>
+      <c r="BK11" s="376"/>
+      <c r="BL11" s="376"/>
+      <c r="BM11" s="376"/>
+      <c r="BN11" s="376"/>
+      <c r="BO11" s="376"/>
+      <c r="BP11" s="376"/>
+      <c r="BQ11" s="376"/>
+      <c r="BR11" s="376"/>
+      <c r="BS11" s="376"/>
+      <c r="BT11" s="376"/>
+      <c r="BU11" s="385"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="396"/>
+      <c r="BW11" s="405"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15900,9 +15951,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="384"/>
-      <c r="CC11" s="384"/>
-      <c r="CD11" s="384"/>
+      <c r="CB11" s="397"/>
+      <c r="CC11" s="397"/>
+      <c r="CD11" s="397"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18303,16 +18354,62 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="BX8:CA10"/>
@@ -18329,62 +18426,16 @@
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18614,87 +18665,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="411"/>
-      <c r="B3" s="402"/>
-      <c r="C3" s="402"/>
-      <c r="D3" s="402"/>
-      <c r="E3" s="402"/>
-      <c r="F3" s="402"/>
-      <c r="G3" s="402"/>
-      <c r="H3" s="402"/>
-      <c r="I3" s="402"/>
-      <c r="J3" s="402"/>
-      <c r="K3" s="402"/>
-      <c r="L3" s="402"/>
-      <c r="M3" s="402"/>
-      <c r="N3" s="402"/>
-      <c r="O3" s="402"/>
-      <c r="P3" s="402"/>
-      <c r="Q3" s="402"/>
-      <c r="R3" s="402"/>
-      <c r="S3" s="402"/>
-      <c r="T3" s="402"/>
-      <c r="U3" s="402"/>
-      <c r="V3" s="402"/>
-      <c r="W3" s="402"/>
-      <c r="X3" s="402"/>
-      <c r="Y3" s="402"/>
-      <c r="Z3" s="402"/>
-      <c r="AA3" s="402"/>
-      <c r="AB3" s="402"/>
-      <c r="AC3" s="402"/>
-      <c r="AD3" s="402"/>
-      <c r="AE3" s="402"/>
-      <c r="AF3" s="402"/>
-      <c r="AG3" s="402"/>
-      <c r="AH3" s="402"/>
-      <c r="AI3" s="402"/>
-      <c r="AJ3" s="402"/>
-      <c r="AK3" s="402"/>
-      <c r="AL3" s="402"/>
-      <c r="AM3" s="402"/>
-      <c r="AN3" s="402"/>
-      <c r="AO3" s="402"/>
-      <c r="AP3" s="402"/>
-      <c r="AQ3" s="402"/>
-      <c r="AR3" s="402"/>
-      <c r="AS3" s="402"/>
-      <c r="AT3" s="402"/>
-      <c r="AU3" s="402"/>
-      <c r="AV3" s="402"/>
-      <c r="AW3" s="402"/>
-      <c r="AX3" s="402"/>
-      <c r="AY3" s="402"/>
-      <c r="AZ3" s="402"/>
-      <c r="BA3" s="402"/>
-      <c r="BB3" s="402"/>
-      <c r="BC3" s="402"/>
-      <c r="BD3" s="402"/>
-      <c r="BE3" s="402"/>
-      <c r="BF3" s="402"/>
-      <c r="BG3" s="402"/>
-      <c r="BH3" s="402"/>
-      <c r="BI3" s="402"/>
-      <c r="BJ3" s="402"/>
-      <c r="BK3" s="402"/>
-      <c r="BL3" s="402"/>
-      <c r="BM3" s="402"/>
-      <c r="BN3" s="402"/>
-      <c r="BO3" s="402"/>
-      <c r="BP3" s="402"/>
-      <c r="BQ3" s="402"/>
-      <c r="BR3" s="402"/>
-      <c r="BS3" s="402"/>
-      <c r="BT3" s="402"/>
-      <c r="BU3" s="402"/>
-      <c r="BW3" s="401" t="s">
+      <c r="A3" s="407"/>
+      <c r="B3" s="395"/>
+      <c r="C3" s="395"/>
+      <c r="D3" s="395"/>
+      <c r="E3" s="395"/>
+      <c r="F3" s="395"/>
+      <c r="G3" s="395"/>
+      <c r="H3" s="395"/>
+      <c r="I3" s="395"/>
+      <c r="J3" s="395"/>
+      <c r="K3" s="395"/>
+      <c r="L3" s="395"/>
+      <c r="M3" s="395"/>
+      <c r="N3" s="395"/>
+      <c r="O3" s="395"/>
+      <c r="P3" s="395"/>
+      <c r="Q3" s="395"/>
+      <c r="R3" s="395"/>
+      <c r="S3" s="395"/>
+      <c r="T3" s="395"/>
+      <c r="U3" s="395"/>
+      <c r="V3" s="395"/>
+      <c r="W3" s="395"/>
+      <c r="X3" s="395"/>
+      <c r="Y3" s="395"/>
+      <c r="Z3" s="395"/>
+      <c r="AA3" s="395"/>
+      <c r="AB3" s="395"/>
+      <c r="AC3" s="395"/>
+      <c r="AD3" s="395"/>
+      <c r="AE3" s="395"/>
+      <c r="AF3" s="395"/>
+      <c r="AG3" s="395"/>
+      <c r="AH3" s="395"/>
+      <c r="AI3" s="395"/>
+      <c r="AJ3" s="395"/>
+      <c r="AK3" s="395"/>
+      <c r="AL3" s="395"/>
+      <c r="AM3" s="395"/>
+      <c r="AN3" s="395"/>
+      <c r="AO3" s="395"/>
+      <c r="AP3" s="395"/>
+      <c r="AQ3" s="395"/>
+      <c r="AR3" s="395"/>
+      <c r="AS3" s="395"/>
+      <c r="AT3" s="395"/>
+      <c r="AU3" s="395"/>
+      <c r="AV3" s="395"/>
+      <c r="AW3" s="395"/>
+      <c r="AX3" s="395"/>
+      <c r="AY3" s="395"/>
+      <c r="AZ3" s="395"/>
+      <c r="BA3" s="395"/>
+      <c r="BB3" s="395"/>
+      <c r="BC3" s="395"/>
+      <c r="BD3" s="395"/>
+      <c r="BE3" s="395"/>
+      <c r="BF3" s="395"/>
+      <c r="BG3" s="395"/>
+      <c r="BH3" s="395"/>
+      <c r="BI3" s="395"/>
+      <c r="BJ3" s="395"/>
+      <c r="BK3" s="395"/>
+      <c r="BL3" s="395"/>
+      <c r="BM3" s="395"/>
+      <c r="BN3" s="395"/>
+      <c r="BO3" s="395"/>
+      <c r="BP3" s="395"/>
+      <c r="BQ3" s="395"/>
+      <c r="BR3" s="395"/>
+      <c r="BS3" s="395"/>
+      <c r="BT3" s="395"/>
+      <c r="BU3" s="395"/>
+      <c r="BW3" s="394" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="402"/>
-      <c r="BY3" s="402"/>
-      <c r="BZ3" s="402"/>
-      <c r="CA3" s="402"/>
-      <c r="CB3" s="402"/>
+      <c r="BX3" s="395"/>
+      <c r="BY3" s="395"/>
+      <c r="BZ3" s="395"/>
+      <c r="CA3" s="395"/>
+      <c r="CB3" s="395"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18777,366 +18828,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="402"/>
-      <c r="BX4" s="402"/>
-      <c r="BY4" s="402"/>
-      <c r="BZ4" s="402"/>
-      <c r="CA4" s="402"/>
-      <c r="CB4" s="402"/>
+      <c r="BW4" s="395"/>
+      <c r="BX4" s="395"/>
+      <c r="BY4" s="395"/>
+      <c r="BZ4" s="395"/>
+      <c r="CA4" s="395"/>
+      <c r="CB4" s="395"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="414" t="s">
+      <c r="A5" s="382" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="413" t="s">
+      <c r="B5" s="393" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="387" t="s">
+      <c r="C5" s="381" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="412" t="s">
+      <c r="D5" s="388" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="412" t="s">
+      <c r="E5" s="388" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="431" t="s">
+      <c r="F5" s="418" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="387" t="s">
+      <c r="G5" s="381" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="333" t="s">
+      <c r="H5" s="337" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="333" t="s">
+      <c r="I5" s="337" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="387" t="s">
+      <c r="J5" s="381" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="416" t="s">
+      <c r="K5" s="386" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="398"/>
-      <c r="M5" s="398"/>
-      <c r="N5" s="398"/>
-      <c r="O5" s="398"/>
-      <c r="P5" s="398"/>
-      <c r="Q5" s="398"/>
-      <c r="R5" s="398"/>
-      <c r="S5" s="398"/>
-      <c r="T5" s="398"/>
-      <c r="U5" s="398"/>
-      <c r="V5" s="398"/>
-      <c r="W5" s="398"/>
-      <c r="X5" s="398"/>
-      <c r="Y5" s="387" t="s">
+      <c r="L5" s="378"/>
+      <c r="M5" s="378"/>
+      <c r="N5" s="378"/>
+      <c r="O5" s="378"/>
+      <c r="P5" s="378"/>
+      <c r="Q5" s="378"/>
+      <c r="R5" s="378"/>
+      <c r="S5" s="378"/>
+      <c r="T5" s="378"/>
+      <c r="U5" s="378"/>
+      <c r="V5" s="378"/>
+      <c r="W5" s="378"/>
+      <c r="X5" s="378"/>
+      <c r="Y5" s="381" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="398"/>
-      <c r="AA5" s="398"/>
-      <c r="AB5" s="398"/>
-      <c r="AC5" s="398"/>
-      <c r="AD5" s="398"/>
-      <c r="AE5" s="398"/>
-      <c r="AF5" s="398"/>
-      <c r="AG5" s="398"/>
-      <c r="AH5" s="398"/>
-      <c r="AI5" s="398"/>
-      <c r="AJ5" s="398"/>
-      <c r="AK5" s="398"/>
-      <c r="AL5" s="398"/>
-      <c r="AM5" s="398"/>
-      <c r="AN5" s="398"/>
-      <c r="AO5" s="399"/>
-      <c r="AP5" s="387" t="s">
+      <c r="Z5" s="378"/>
+      <c r="AA5" s="378"/>
+      <c r="AB5" s="378"/>
+      <c r="AC5" s="378"/>
+      <c r="AD5" s="378"/>
+      <c r="AE5" s="378"/>
+      <c r="AF5" s="378"/>
+      <c r="AG5" s="378"/>
+      <c r="AH5" s="378"/>
+      <c r="AI5" s="378"/>
+      <c r="AJ5" s="378"/>
+      <c r="AK5" s="378"/>
+      <c r="AL5" s="378"/>
+      <c r="AM5" s="378"/>
+      <c r="AN5" s="378"/>
+      <c r="AO5" s="379"/>
+      <c r="AP5" s="381" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="387" t="s">
+      <c r="AQ5" s="381" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="387" t="s">
+      <c r="AR5" s="381" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="387" t="s">
+      <c r="AS5" s="381" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="387" t="s">
+      <c r="AT5" s="381" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="387" t="s">
+      <c r="AU5" s="381" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="387" t="s">
+      <c r="AV5" s="381" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="387" t="s">
+      <c r="AW5" s="381" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="387" t="s">
+      <c r="AX5" s="381" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="397" t="s">
+      <c r="AY5" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="398"/>
-      <c r="BA5" s="398"/>
-      <c r="BB5" s="398"/>
-      <c r="BC5" s="398"/>
-      <c r="BD5" s="398"/>
-      <c r="BE5" s="398"/>
-      <c r="BF5" s="398"/>
-      <c r="BG5" s="398"/>
-      <c r="BH5" s="398"/>
-      <c r="BI5" s="398"/>
-      <c r="BJ5" s="398"/>
-      <c r="BK5" s="398"/>
-      <c r="BL5" s="398"/>
-      <c r="BM5" s="398"/>
-      <c r="BN5" s="398"/>
-      <c r="BO5" s="398"/>
-      <c r="BP5" s="399"/>
-      <c r="BQ5" s="403" t="s">
+      <c r="AZ5" s="378"/>
+      <c r="BA5" s="378"/>
+      <c r="BB5" s="378"/>
+      <c r="BC5" s="378"/>
+      <c r="BD5" s="378"/>
+      <c r="BE5" s="378"/>
+      <c r="BF5" s="378"/>
+      <c r="BG5" s="378"/>
+      <c r="BH5" s="378"/>
+      <c r="BI5" s="378"/>
+      <c r="BJ5" s="378"/>
+      <c r="BK5" s="378"/>
+      <c r="BL5" s="378"/>
+      <c r="BM5" s="378"/>
+      <c r="BN5" s="378"/>
+      <c r="BO5" s="378"/>
+      <c r="BP5" s="379"/>
+      <c r="BQ5" s="398" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="404"/>
-      <c r="BS5" s="397" t="s">
+      <c r="BR5" s="391"/>
+      <c r="BS5" s="377" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="397" t="s">
+      <c r="BT5" s="377" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="391" t="s">
+      <c r="BU5" s="409" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="394" t="s">
+      <c r="BW5" s="410" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="405" t="s">
+      <c r="BX5" s="399" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="406"/>
-      <c r="BZ5" s="406"/>
-      <c r="CA5" s="404"/>
-      <c r="CB5" s="400" t="s">
+      <c r="BY5" s="400"/>
+      <c r="BZ5" s="400"/>
+      <c r="CA5" s="391"/>
+      <c r="CB5" s="411" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="382" t="s">
+      <c r="CC5" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="382" t="s">
+      <c r="CD5" s="396" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="383"/>
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
-      <c r="D6" s="383"/>
-      <c r="E6" s="383"/>
-      <c r="F6" s="383"/>
-      <c r="G6" s="383"/>
-      <c r="H6" s="383"/>
-      <c r="I6" s="383"/>
-      <c r="J6" s="383"/>
-      <c r="K6" s="388" t="s">
+      <c r="A6" s="375"/>
+      <c r="B6" s="375"/>
+      <c r="C6" s="375"/>
+      <c r="D6" s="375"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
+      <c r="G6" s="375"/>
+      <c r="H6" s="375"/>
+      <c r="I6" s="375"/>
+      <c r="J6" s="375"/>
+      <c r="K6" s="389" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="388" t="s">
+      <c r="L6" s="389" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="388" t="s">
+      <c r="M6" s="389" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="388" t="s">
+      <c r="N6" s="389" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="388" t="s">
+      <c r="O6" s="389" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="388" t="s">
+      <c r="P6" s="389" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="388" t="s">
+      <c r="Q6" s="389" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="388" t="s">
+      <c r="R6" s="389" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="388" t="s">
+      <c r="S6" s="389" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="388" t="s">
+      <c r="T6" s="389" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="388" t="s">
+      <c r="U6" s="389" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="418" t="s">
+      <c r="V6" s="390" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="404"/>
-      <c r="X6" s="388" t="s">
+      <c r="W6" s="391"/>
+      <c r="X6" s="389" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="387" t="s">
+      <c r="Y6" s="381" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="387" t="s">
+      <c r="Z6" s="381" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="387" t="s">
+      <c r="AA6" s="381" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="387" t="s">
+      <c r="AB6" s="381" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="333" t="s">
+      <c r="AC6" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="333" t="s">
+      <c r="AD6" s="337" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="333" t="s">
+      <c r="AE6" s="337" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="333" t="s">
+      <c r="AF6" s="337" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="387" t="s">
+      <c r="AG6" s="381" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="333" t="s">
+      <c r="AH6" s="337" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="333" t="s">
+      <c r="AI6" s="337" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="387" t="s">
+      <c r="AJ6" s="381" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="415" t="s">
+      <c r="AK6" s="383" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="387" t="s">
+      <c r="AL6" s="381" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="387" t="s">
+      <c r="AM6" s="381" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="417" t="s">
+      <c r="AN6" s="387" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="387" t="s">
+      <c r="AO6" s="381" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="383"/>
-      <c r="AQ6" s="383"/>
-      <c r="AR6" s="383"/>
-      <c r="AS6" s="383"/>
-      <c r="AT6" s="383"/>
-      <c r="AU6" s="383"/>
-      <c r="AV6" s="383"/>
-      <c r="AW6" s="383"/>
-      <c r="AX6" s="383"/>
-      <c r="AY6" s="397" t="s">
+      <c r="AP6" s="375"/>
+      <c r="AQ6" s="375"/>
+      <c r="AR6" s="375"/>
+      <c r="AS6" s="375"/>
+      <c r="AT6" s="375"/>
+      <c r="AU6" s="375"/>
+      <c r="AV6" s="375"/>
+      <c r="AW6" s="375"/>
+      <c r="AX6" s="375"/>
+      <c r="AY6" s="377" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="398"/>
-      <c r="BA6" s="398"/>
-      <c r="BB6" s="398"/>
-      <c r="BC6" s="398"/>
-      <c r="BD6" s="398"/>
-      <c r="BE6" s="398"/>
-      <c r="BF6" s="398"/>
-      <c r="BG6" s="398"/>
-      <c r="BH6" s="398"/>
-      <c r="BI6" s="398"/>
-      <c r="BJ6" s="399"/>
-      <c r="BK6" s="397" t="s">
+      <c r="AZ6" s="378"/>
+      <c r="BA6" s="378"/>
+      <c r="BB6" s="378"/>
+      <c r="BC6" s="378"/>
+      <c r="BD6" s="378"/>
+      <c r="BE6" s="378"/>
+      <c r="BF6" s="378"/>
+      <c r="BG6" s="378"/>
+      <c r="BH6" s="378"/>
+      <c r="BI6" s="378"/>
+      <c r="BJ6" s="379"/>
+      <c r="BK6" s="377" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="398"/>
-      <c r="BM6" s="398"/>
-      <c r="BN6" s="398"/>
-      <c r="BO6" s="398"/>
-      <c r="BP6" s="399"/>
-      <c r="BQ6" s="385" t="s">
+      <c r="BL6" s="378"/>
+      <c r="BM6" s="378"/>
+      <c r="BN6" s="378"/>
+      <c r="BO6" s="378"/>
+      <c r="BP6" s="379"/>
+      <c r="BQ6" s="374" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="385" t="s">
+      <c r="BR6" s="374" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="383"/>
-      <c r="BT6" s="383"/>
-      <c r="BU6" s="392"/>
-      <c r="BW6" s="395"/>
-      <c r="BX6" s="392"/>
-      <c r="BY6" s="407"/>
-      <c r="BZ6" s="407"/>
-      <c r="CA6" s="395"/>
-      <c r="CB6" s="383"/>
-      <c r="CC6" s="383"/>
-      <c r="CD6" s="383"/>
+      <c r="BS6" s="375"/>
+      <c r="BT6" s="375"/>
+      <c r="BU6" s="384"/>
+      <c r="BW6" s="402"/>
+      <c r="BX6" s="384"/>
+      <c r="BY6" s="401"/>
+      <c r="BZ6" s="401"/>
+      <c r="CA6" s="402"/>
+      <c r="CB6" s="375"/>
+      <c r="CC6" s="375"/>
+      <c r="CD6" s="375"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="383"/>
-      <c r="B7" s="383"/>
-      <c r="C7" s="383"/>
-      <c r="D7" s="383"/>
-      <c r="E7" s="383"/>
-      <c r="F7" s="383"/>
-      <c r="G7" s="383"/>
-      <c r="H7" s="383"/>
-      <c r="I7" s="383"/>
-      <c r="J7" s="383"/>
-      <c r="K7" s="383"/>
-      <c r="L7" s="383"/>
-      <c r="M7" s="383"/>
-      <c r="N7" s="383"/>
-      <c r="O7" s="383"/>
-      <c r="P7" s="383"/>
-      <c r="Q7" s="383"/>
-      <c r="R7" s="383"/>
-      <c r="S7" s="383"/>
-      <c r="T7" s="383"/>
-      <c r="U7" s="383"/>
-      <c r="V7" s="393"/>
-      <c r="W7" s="419"/>
-      <c r="X7" s="383"/>
-      <c r="Y7" s="383"/>
-      <c r="Z7" s="383"/>
-      <c r="AA7" s="383"/>
-      <c r="AB7" s="383"/>
-      <c r="AC7" s="383"/>
-      <c r="AD7" s="383"/>
-      <c r="AE7" s="383"/>
-      <c r="AF7" s="383"/>
-      <c r="AG7" s="383"/>
-      <c r="AH7" s="383"/>
-      <c r="AI7" s="383"/>
-      <c r="AJ7" s="383"/>
-      <c r="AK7" s="392"/>
-      <c r="AL7" s="383"/>
-      <c r="AM7" s="383"/>
-      <c r="AN7" s="383"/>
-      <c r="AO7" s="383"/>
-      <c r="AP7" s="383"/>
-      <c r="AQ7" s="383"/>
-      <c r="AR7" s="383"/>
-      <c r="AS7" s="383"/>
-      <c r="AT7" s="383"/>
-      <c r="AU7" s="383"/>
-      <c r="AV7" s="383"/>
-      <c r="AW7" s="383"/>
-      <c r="AX7" s="383"/>
+      <c r="A7" s="375"/>
+      <c r="B7" s="375"/>
+      <c r="C7" s="375"/>
+      <c r="D7" s="375"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
+      <c r="G7" s="375"/>
+      <c r="H7" s="375"/>
+      <c r="I7" s="375"/>
+      <c r="J7" s="375"/>
+      <c r="K7" s="375"/>
+      <c r="L7" s="375"/>
+      <c r="M7" s="375"/>
+      <c r="N7" s="375"/>
+      <c r="O7" s="375"/>
+      <c r="P7" s="375"/>
+      <c r="Q7" s="375"/>
+      <c r="R7" s="375"/>
+      <c r="S7" s="375"/>
+      <c r="T7" s="375"/>
+      <c r="U7" s="375"/>
+      <c r="V7" s="385"/>
+      <c r="W7" s="392"/>
+      <c r="X7" s="375"/>
+      <c r="Y7" s="375"/>
+      <c r="Z7" s="375"/>
+      <c r="AA7" s="375"/>
+      <c r="AB7" s="375"/>
+      <c r="AC7" s="375"/>
+      <c r="AD7" s="375"/>
+      <c r="AE7" s="375"/>
+      <c r="AF7" s="375"/>
+      <c r="AG7" s="375"/>
+      <c r="AH7" s="375"/>
+      <c r="AI7" s="375"/>
+      <c r="AJ7" s="375"/>
+      <c r="AK7" s="384"/>
+      <c r="AL7" s="375"/>
+      <c r="AM7" s="375"/>
+      <c r="AN7" s="375"/>
+      <c r="AO7" s="375"/>
+      <c r="AP7" s="375"/>
+      <c r="AQ7" s="375"/>
+      <c r="AR7" s="375"/>
+      <c r="AS7" s="375"/>
+      <c r="AT7" s="375"/>
+      <c r="AU7" s="375"/>
+      <c r="AV7" s="375"/>
+      <c r="AW7" s="375"/>
+      <c r="AX7" s="375"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19146,122 +19197,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="397" t="s">
+      <c r="BB7" s="377" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="389" t="s">
+      <c r="BC7" s="380" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="389" t="s">
+      <c r="BD7" s="380" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="389" t="s">
+      <c r="BE7" s="380" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="389" t="s">
+      <c r="BF7" s="380" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="389" t="s">
+      <c r="BG7" s="380" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="389" t="s">
+      <c r="BH7" s="380" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="389" t="s">
+      <c r="BI7" s="380" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="390" t="s">
+      <c r="BJ7" s="408" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="389" t="s">
+      <c r="BK7" s="380" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="397" t="s">
+      <c r="BL7" s="377" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="389" t="s">
+      <c r="BM7" s="380" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="397" t="s">
+      <c r="BN7" s="377" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="397" t="s">
+      <c r="BO7" s="377" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="397" t="s">
+      <c r="BP7" s="377" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="383"/>
-      <c r="BR7" s="383"/>
-      <c r="BS7" s="383"/>
-      <c r="BT7" s="383"/>
-      <c r="BU7" s="392"/>
-      <c r="BW7" s="395"/>
-      <c r="BX7" s="408"/>
-      <c r="BY7" s="409"/>
-      <c r="BZ7" s="409"/>
-      <c r="CA7" s="396"/>
-      <c r="CB7" s="383"/>
-      <c r="CC7" s="383"/>
-      <c r="CD7" s="383"/>
+      <c r="BQ7" s="375"/>
+      <c r="BR7" s="375"/>
+      <c r="BS7" s="375"/>
+      <c r="BT7" s="375"/>
+      <c r="BU7" s="384"/>
+      <c r="BW7" s="402"/>
+      <c r="BX7" s="403"/>
+      <c r="BY7" s="404"/>
+      <c r="BZ7" s="404"/>
+      <c r="CA7" s="405"/>
+      <c r="CB7" s="375"/>
+      <c r="CC7" s="375"/>
+      <c r="CD7" s="375"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="386"/>
-      <c r="B8" s="386"/>
-      <c r="C8" s="386"/>
-      <c r="D8" s="386"/>
-      <c r="E8" s="386"/>
-      <c r="F8" s="386"/>
-      <c r="G8" s="386"/>
-      <c r="H8" s="386"/>
-      <c r="I8" s="386"/>
-      <c r="J8" s="386"/>
-      <c r="K8" s="386"/>
-      <c r="L8" s="386"/>
-      <c r="M8" s="386"/>
-      <c r="N8" s="386"/>
-      <c r="O8" s="386"/>
-      <c r="P8" s="386"/>
-      <c r="Q8" s="386"/>
-      <c r="R8" s="386"/>
-      <c r="S8" s="386"/>
-      <c r="T8" s="386"/>
-      <c r="U8" s="386"/>
+      <c r="A8" s="376"/>
+      <c r="B8" s="376"/>
+      <c r="C8" s="376"/>
+      <c r="D8" s="376"/>
+      <c r="E8" s="376"/>
+      <c r="F8" s="376"/>
+      <c r="G8" s="376"/>
+      <c r="H8" s="376"/>
+      <c r="I8" s="376"/>
+      <c r="J8" s="376"/>
+      <c r="K8" s="376"/>
+      <c r="L8" s="376"/>
+      <c r="M8" s="376"/>
+      <c r="N8" s="376"/>
+      <c r="O8" s="376"/>
+      <c r="P8" s="376"/>
+      <c r="Q8" s="376"/>
+      <c r="R8" s="376"/>
+      <c r="S8" s="376"/>
+      <c r="T8" s="376"/>
+      <c r="U8" s="376"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="386"/>
-      <c r="Y8" s="386"/>
-      <c r="Z8" s="386"/>
-      <c r="AA8" s="386"/>
-      <c r="AB8" s="386"/>
-      <c r="AC8" s="386"/>
-      <c r="AD8" s="386"/>
-      <c r="AE8" s="386"/>
-      <c r="AF8" s="386"/>
-      <c r="AG8" s="386"/>
-      <c r="AH8" s="386"/>
-      <c r="AI8" s="386"/>
-      <c r="AJ8" s="386"/>
-      <c r="AK8" s="393"/>
-      <c r="AL8" s="386"/>
-      <c r="AM8" s="386"/>
-      <c r="AN8" s="386"/>
-      <c r="AO8" s="386"/>
-      <c r="AP8" s="386"/>
-      <c r="AQ8" s="386"/>
-      <c r="AR8" s="386"/>
-      <c r="AS8" s="386"/>
-      <c r="AT8" s="386"/>
-      <c r="AU8" s="386"/>
-      <c r="AV8" s="386"/>
-      <c r="AW8" s="386"/>
-      <c r="AX8" s="386"/>
+      <c r="X8" s="376"/>
+      <c r="Y8" s="376"/>
+      <c r="Z8" s="376"/>
+      <c r="AA8" s="376"/>
+      <c r="AB8" s="376"/>
+      <c r="AC8" s="376"/>
+      <c r="AD8" s="376"/>
+      <c r="AE8" s="376"/>
+      <c r="AF8" s="376"/>
+      <c r="AG8" s="376"/>
+      <c r="AH8" s="376"/>
+      <c r="AI8" s="376"/>
+      <c r="AJ8" s="376"/>
+      <c r="AK8" s="385"/>
+      <c r="AL8" s="376"/>
+      <c r="AM8" s="376"/>
+      <c r="AN8" s="376"/>
+      <c r="AO8" s="376"/>
+      <c r="AP8" s="376"/>
+      <c r="AQ8" s="376"/>
+      <c r="AR8" s="376"/>
+      <c r="AS8" s="376"/>
+      <c r="AT8" s="376"/>
+      <c r="AU8" s="376"/>
+      <c r="AV8" s="376"/>
+      <c r="AW8" s="376"/>
+      <c r="AX8" s="376"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19271,27 +19322,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="386"/>
-      <c r="BC8" s="386"/>
-      <c r="BD8" s="386"/>
-      <c r="BE8" s="386"/>
-      <c r="BF8" s="386"/>
-      <c r="BG8" s="386"/>
-      <c r="BH8" s="386"/>
-      <c r="BI8" s="386"/>
-      <c r="BJ8" s="386"/>
-      <c r="BK8" s="386"/>
-      <c r="BL8" s="386"/>
-      <c r="BM8" s="386"/>
-      <c r="BN8" s="386"/>
-      <c r="BO8" s="386"/>
-      <c r="BP8" s="386"/>
-      <c r="BQ8" s="386"/>
-      <c r="BR8" s="386"/>
-      <c r="BS8" s="386"/>
-      <c r="BT8" s="386"/>
-      <c r="BU8" s="393"/>
-      <c r="BW8" s="396"/>
+      <c r="BB8" s="376"/>
+      <c r="BC8" s="376"/>
+      <c r="BD8" s="376"/>
+      <c r="BE8" s="376"/>
+      <c r="BF8" s="376"/>
+      <c r="BG8" s="376"/>
+      <c r="BH8" s="376"/>
+      <c r="BI8" s="376"/>
+      <c r="BJ8" s="376"/>
+      <c r="BK8" s="376"/>
+      <c r="BL8" s="376"/>
+      <c r="BM8" s="376"/>
+      <c r="BN8" s="376"/>
+      <c r="BO8" s="376"/>
+      <c r="BP8" s="376"/>
+      <c r="BQ8" s="376"/>
+      <c r="BR8" s="376"/>
+      <c r="BS8" s="376"/>
+      <c r="BT8" s="376"/>
+      <c r="BU8" s="385"/>
+      <c r="BW8" s="405"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19304,9 +19355,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="384"/>
-      <c r="CC8" s="384"/>
-      <c r="CD8" s="384"/>
+      <c r="CB8" s="397"/>
+      <c r="CC8" s="397"/>
+      <c r="CD8" s="397"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21313,6 +21364,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="BT5:BT8"/>
     <mergeCell ref="AL6:AL8"/>
@@ -21329,72 +21446,6 @@
     <mergeCell ref="AA6:AA8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AK6:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD10DCA-FDC3-2E45-A02C-24FC378319AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D31779-62D9-9348-8C95-B77420D73C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5858,7 +5858,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="444">
+  <cellXfs count="447">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7023,6 +7023,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="46" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -8393,7 +8398,7 @@
       <c r="CB8" s="369" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="442" t="s">
+      <c r="CC8" s="444" t="s">
         <v>32</v>
       </c>
       <c r="CD8" s="442" t="s">
@@ -8551,7 +8556,7 @@
       <c r="BZ9" s="332"/>
       <c r="CA9" s="333"/>
       <c r="CB9" s="338"/>
-      <c r="CC9" s="430"/>
+      <c r="CC9" s="445"/>
       <c r="CD9" s="430"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
@@ -8675,7 +8680,7 @@
       <c r="BZ10" s="335"/>
       <c r="CA10" s="336"/>
       <c r="CB10" s="338"/>
-      <c r="CC10" s="430"/>
+      <c r="CC10" s="445"/>
       <c r="CD10" s="430"/>
       <c r="CE10" s="319" t="s">
         <v>3</v>
@@ -8782,7 +8787,7 @@
         <v>94</v>
       </c>
       <c r="CB11" s="370"/>
-      <c r="CC11" s="443"/>
+      <c r="CC11" s="446"/>
       <c r="CD11" s="443"/>
       <c r="CE11" s="318">
         <v>26</v>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D31779-62D9-9348-8C95-B77420D73C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D47A1FD-C281-734C-BA6F-541C12B0EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38440" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -7599,7 +7599,7 @@
   <cols>
     <col min="1" max="1" width="5.5" style="258" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="268" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" style="260" customWidth="1"/>
+    <col min="3" max="3" width="28" style="260" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" style="261" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="14.1640625" style="261" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="11.5" style="262" customWidth="1" outlineLevel="1"/>
@@ -8351,7 +8351,7 @@
       <c r="AW8" s="434" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="433" t="s">
+      <c r="AX8" s="337" t="s">
         <v>24</v>
       </c>
       <c r="AY8" s="364" t="s">
@@ -8517,7 +8517,7 @@
       <c r="AU9" s="430"/>
       <c r="AV9" s="338"/>
       <c r="AW9" s="430"/>
-      <c r="AX9" s="427"/>
+      <c r="AX9" s="338"/>
       <c r="AY9" s="371" t="s">
         <v>25</v>
       </c>
@@ -8611,7 +8611,7 @@
       <c r="AU10" s="430"/>
       <c r="AV10" s="338"/>
       <c r="AW10" s="430"/>
-      <c r="AX10" s="427"/>
+      <c r="AX10" s="338"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8742,7 +8742,7 @@
       <c r="AU11" s="431"/>
       <c r="AV11" s="339"/>
       <c r="AW11" s="431"/>
-      <c r="AX11" s="428"/>
+      <c r="AX11" s="339"/>
       <c r="AY11" s="320" t="s">
         <v>88</v>
       </c>
@@ -9205,7 +9205,7 @@
       <c r="F14" s="247"/>
       <c r="G14" s="94">
         <f>SUM(G15:G21)</f>
-        <v>50340000</v>
+        <v>53000010</v>
       </c>
       <c r="H14" s="94">
         <f>SUM(H15:H21)</f>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="I14" s="94">
         <f>SUM(I15:I21)</f>
-        <v>186060000</v>
+        <v>183399990</v>
       </c>
       <c r="J14" s="94"/>
       <c r="K14" s="313">
@@ -9271,18 +9271,18 @@
       </c>
       <c r="Y14" s="94">
         <f>SUM(Y15:Y21)</f>
-        <v>48340000</v>
+        <v>51000010</v>
       </c>
       <c r="Z14" s="94"/>
       <c r="AA14" s="94"/>
       <c r="AB14" s="94"/>
       <c r="AC14" s="94">
         <f>SUM(AC15:AC21)</f>
-        <v>1828846.1538461538</v>
+        <v>2596156.730769231</v>
       </c>
       <c r="AD14" s="94">
         <f>SUM(AD15:AD21)</f>
-        <v>975384.61538461538</v>
+        <v>1384616.923076923</v>
       </c>
       <c r="AE14" s="94"/>
       <c r="AF14" s="94">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AO14" s="94">
         <f t="shared" si="5"/>
-        <v>185063076.92307696</v>
+        <v>181303448.65384617</v>
       </c>
       <c r="AP14" s="94"/>
       <c r="AQ14" s="94"/>
@@ -9333,25 +9333,25 @@
       <c r="AU14" s="94"/>
       <c r="AV14" s="94">
         <f>SUM(AV15:AV21)</f>
-        <v>242266923.07692307</v>
+        <v>242343847.69230768</v>
       </c>
       <c r="AW14" s="94"/>
       <c r="AX14" s="94"/>
       <c r="AY14" s="94">
         <f>SUM(AY15:AY21)</f>
-        <v>3544000</v>
+        <v>3756801</v>
       </c>
       <c r="AZ14" s="94">
         <f>SUM(AZ15:AZ21)</f>
-        <v>664500</v>
+        <v>704400</v>
       </c>
       <c r="BA14" s="94">
         <f>SUM(BA15:BA21)</f>
-        <v>443000</v>
+        <v>469600</v>
       </c>
       <c r="BB14" s="94">
         <f>SUM(BB15:BB21)</f>
-        <v>4651500</v>
+        <v>4930801</v>
       </c>
       <c r="BC14" s="94">
         <f>SUM(BC15:BC21)</f>
@@ -9360,7 +9360,7 @@
       <c r="BD14" s="94"/>
       <c r="BE14" s="94">
         <f>SUM(BE15:BE21)</f>
-        <v>503400</v>
+        <v>530000.1</v>
       </c>
       <c r="BF14" s="94"/>
       <c r="BG14" s="94"/>
@@ -9370,7 +9370,7 @@
       <c r="BK14" s="94"/>
       <c r="BL14" s="94">
         <f t="shared" ref="BL14:BQ14" si="6">SUM(BL15:BL21)</f>
-        <v>10172184</v>
+        <v>10161488</v>
       </c>
       <c r="BM14" s="94">
         <f t="shared" si="6"/>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
-        <v>134901223.69230768</v>
+        <v>134682943.2076923</v>
       </c>
       <c r="BV14" s="252"/>
       <c r="BW14" s="242"/>
@@ -10899,7 +10899,7 @@
         <v>100</v>
       </c>
       <c r="G21" s="94">
-        <v>6340000</v>
+        <v>9000010</v>
       </c>
       <c r="H21" s="94">
         <f t="shared" si="7"/>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="I21" s="94">
         <f t="shared" si="8"/>
-        <v>11210000</v>
+        <v>8549990</v>
       </c>
       <c r="J21" s="92">
         <v>1</v>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="Y21" s="94">
         <f t="shared" si="9"/>
-        <v>6340000</v>
+        <v>9000010</v>
       </c>
       <c r="Z21" s="94">
         <f t="shared" si="10"/>
@@ -10970,11 +10970,11 @@
       </c>
       <c r="AC21" s="94">
         <f t="shared" si="13"/>
-        <v>1828846.1538461538</v>
+        <v>2596156.730769231</v>
       </c>
       <c r="AD21" s="94">
         <f t="shared" si="14"/>
-        <v>975384.61538461538</v>
+        <v>1384616.923076923</v>
       </c>
       <c r="AE21" s="94">
         <f t="shared" si="15"/>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AO21" s="94">
         <f t="shared" si="21"/>
-        <v>12982692.307692306</v>
+        <v>9223064.0384615362</v>
       </c>
       <c r="AP21" s="94"/>
       <c r="AQ21" s="94"/>
@@ -11024,7 +11024,7 @@
       <c r="AU21" s="94"/>
       <c r="AV21" s="94">
         <f t="shared" si="22"/>
-        <v>22986923.076923076</v>
+        <v>23063847.692307692</v>
       </c>
       <c r="AW21" s="94"/>
       <c r="AX21" s="94" t="str">
@@ -11033,33 +11033,33 @@
       </c>
       <c r="AY21" s="250">
         <f t="shared" si="24"/>
-        <v>531200</v>
+        <v>744001</v>
       </c>
       <c r="AZ21" s="250">
         <f t="shared" si="24"/>
-        <v>99600</v>
+        <v>139500</v>
       </c>
       <c r="BA21" s="250">
         <f t="shared" si="24"/>
-        <v>66400</v>
+        <v>93000</v>
       </c>
       <c r="BB21" s="250">
         <f t="shared" si="25"/>
-        <v>697200</v>
+        <v>976501</v>
       </c>
       <c r="BC21" s="250"/>
       <c r="BD21" s="250"/>
       <c r="BE21" s="250">
         <f t="shared" si="26"/>
-        <v>63400</v>
+        <v>90000.1</v>
       </c>
       <c r="BF21" s="250">
         <f t="shared" si="34"/>
-        <v>3924038.4615384615</v>
+        <v>3935577.1538461535</v>
       </c>
       <c r="BG21" s="250">
         <f t="shared" si="27"/>
-        <v>19062884.615384616</v>
+        <v>19128270.53846154</v>
       </c>
       <c r="BH21" s="250"/>
       <c r="BI21" s="278">
@@ -11071,11 +11071,11 @@
       </c>
       <c r="BK21" s="250">
         <f t="shared" si="28"/>
-        <v>2865684.615384616</v>
+        <v>2651769.5384615399</v>
       </c>
       <c r="BL21" s="243">
         <f t="shared" si="29"/>
-        <v>143284</v>
+        <v>132588</v>
       </c>
       <c r="BM21" s="250"/>
       <c r="BN21" s="250"/>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BU21" s="251">
         <f t="shared" si="30"/>
-        <v>12105192.923076922</v>
+        <v>11886912.438461537</v>
       </c>
       <c r="BV21" s="252"/>
       <c r="BW21" s="242">
@@ -14817,8 +14817,8 @@
   <cols>
     <col min="1" max="1" width="5.5" style="61" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="66" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="14.5" style="67" customWidth="1"/>
+    <col min="4" max="4" width="34" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="5.5" style="68" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="69" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="64" bestFit="1" customWidth="1"/>
@@ -15634,7 +15634,7 @@
         <v>46</v>
       </c>
       <c r="Y9" s="414" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="Z9" s="414" t="s">
         <v>48</v>
@@ -18473,8 +18473,8 @@
     <col min="1" max="1" width="5.5" style="215" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="216" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" style="217" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="218" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="218" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="9" style="218" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10" style="218" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="20.6640625" style="219" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="220" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="220" customWidth="1"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D47A1FD-C281-734C-BA6F-541C12B0EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37376625-FB59-714F-9AF7-96D89807F4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36860" yWindow="2620" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -9394,13 +9394,10 @@
       </c>
       <c r="BR14" s="94"/>
       <c r="BS14" s="94"/>
-      <c r="BT14" s="94">
-        <f>SUM(BT15:BT21)</f>
-        <v>92038615.384615406</v>
-      </c>
+      <c r="BT14" s="94"/>
       <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
-        <v>134682943.2076923</v>
+        <v>226721558.59230769</v>
       </c>
       <c r="BV14" s="252"/>
       <c r="BW14" s="242"/>
@@ -9622,12 +9619,10 @@
       <c r="BQ15" s="278"/>
       <c r="BR15" s="278"/>
       <c r="BS15" s="278"/>
-      <c r="BT15" s="263">
-        <v>25846153.846153852</v>
-      </c>
+      <c r="BT15" s="263"/>
       <c r="BU15" s="280">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
-        <v>34973066.153846145</v>
+        <v>60819220</v>
       </c>
       <c r="BV15" s="252"/>
       <c r="BW15" s="281">
@@ -9864,9 +9859,7 @@
       <c r="BQ16" s="250"/>
       <c r="BR16" s="250"/>
       <c r="BS16" s="250"/>
-      <c r="BT16" s="263">
-        <v>0</v>
-      </c>
+      <c r="BT16" s="263"/>
       <c r="BU16" s="251">
         <f t="shared" si="30"/>
         <v>44544803.538461544</v>
@@ -10108,12 +10101,10 @@
       <c r="BQ17" s="250"/>
       <c r="BR17" s="250"/>
       <c r="BS17" s="250"/>
-      <c r="BT17" s="263">
-        <v>25846153.846153852</v>
-      </c>
+      <c r="BT17" s="263"/>
       <c r="BU17" s="251">
         <f t="shared" si="30"/>
-        <v>13601535.769230764</v>
+        <v>39447689.615384616</v>
       </c>
       <c r="BV17" s="252"/>
       <c r="BW17" s="242">
@@ -10352,12 +10343,10 @@
       <c r="BQ18" s="250"/>
       <c r="BR18" s="250"/>
       <c r="BS18" s="250"/>
-      <c r="BT18" s="263">
-        <v>10195307.692307694</v>
-      </c>
+      <c r="BT18" s="263"/>
       <c r="BU18" s="251">
         <f t="shared" si="30"/>
-        <v>15542602.23076923</v>
+        <v>25737909.923076924</v>
       </c>
       <c r="BV18" s="252"/>
       <c r="BW18" s="242">
@@ -10596,12 +10585,10 @@
       <c r="BQ19" s="250"/>
       <c r="BR19" s="250"/>
       <c r="BS19" s="250"/>
-      <c r="BT19" s="263">
-        <v>9977846.153846154</v>
-      </c>
+      <c r="BT19" s="263"/>
       <c r="BU19" s="251">
         <f t="shared" si="30"/>
-        <v>1647480.7692307699</v>
+        <v>11625326.923076924</v>
       </c>
       <c r="BV19" s="252"/>
       <c r="BW19" s="242">
@@ -10840,12 +10827,10 @@
       <c r="BQ20" s="250"/>
       <c r="BR20" s="250"/>
       <c r="BS20" s="250"/>
-      <c r="BT20" s="263">
-        <v>10195307.692307694</v>
-      </c>
+      <c r="BT20" s="263"/>
       <c r="BU20" s="251">
         <f t="shared" si="30"/>
-        <v>12486542.307692306</v>
+        <v>22681850</v>
       </c>
       <c r="BV20" s="252"/>
       <c r="BW20" s="242">
@@ -11086,12 +11071,10 @@
       <c r="BQ21" s="250"/>
       <c r="BR21" s="250"/>
       <c r="BS21" s="250"/>
-      <c r="BT21" s="263">
-        <v>9977846.153846154</v>
-      </c>
+      <c r="BT21" s="263"/>
       <c r="BU21" s="251">
         <f t="shared" si="30"/>
-        <v>11886912.438461537</v>
+        <v>21864758.592307691</v>
       </c>
       <c r="BV21" s="252"/>
       <c r="BW21" s="242">

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37376625-FB59-714F-9AF7-96D89807F4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881B46FD-8C82-1C45-B312-83F059592A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36860" yWindow="2620" windowWidth="38360" windowHeight="20700" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38540" yWindow="660" windowWidth="38100" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -5858,7 +5858,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="447">
+  <cellXfs count="448">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6591,6 +6591,9 @@
     <xf numFmtId="0" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="6" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7016,9 +7019,6 @@
     <xf numFmtId="9" fontId="18" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="49" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7028,6 +7028,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -7629,773 +7630,773 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" s="240" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
-      <c r="A1" s="282" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
-      <c r="F1" s="285"/>
-      <c r="I1" s="286"/>
-      <c r="K1" s="287"/>
-      <c r="L1" s="287"/>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="288"/>
-      <c r="AI1" s="288"/>
-      <c r="AJ1" s="288"/>
-      <c r="AK1" s="288"/>
-      <c r="AL1" s="288"/>
-      <c r="AM1" s="288"/>
-      <c r="AN1" s="288"/>
-      <c r="AO1" s="288"/>
-      <c r="AP1" s="288"/>
-      <c r="AQ1" s="288"/>
-      <c r="AR1" s="288"/>
-      <c r="AS1" s="288"/>
-      <c r="AT1" s="288"/>
-      <c r="AU1" s="288"/>
-      <c r="AV1" s="288"/>
-      <c r="AW1" s="288"/>
-      <c r="AX1" s="288"/>
-      <c r="AY1" s="288"/>
-      <c r="AZ1" s="288"/>
-      <c r="BA1" s="288"/>
-      <c r="BB1" s="288"/>
-      <c r="BC1" s="288"/>
-      <c r="BD1" s="289"/>
-      <c r="BE1" s="288"/>
-      <c r="BF1" s="289"/>
-      <c r="BG1" s="288"/>
-      <c r="BH1" s="288"/>
-      <c r="BI1" s="288"/>
-      <c r="BJ1" s="288"/>
-      <c r="BK1" s="288"/>
-      <c r="BL1" s="288"/>
-      <c r="BM1" s="288"/>
-      <c r="BN1" s="288"/>
-      <c r="BO1" s="288"/>
-      <c r="BP1" s="290"/>
-      <c r="BQ1" s="288"/>
-      <c r="BR1" s="288"/>
-      <c r="BS1" s="288"/>
-      <c r="BU1" s="288"/>
-      <c r="BV1" s="288"/>
-      <c r="BW1" s="291"/>
-      <c r="BX1" s="291"/>
-      <c r="BY1" s="291"/>
-      <c r="BZ1" s="291"/>
-      <c r="CA1" s="291"/>
-      <c r="CB1" s="292"/>
-      <c r="CC1" s="292"/>
-      <c r="CD1" s="292"/>
+      <c r="A1" s="283" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="284"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="I1" s="287"/>
+      <c r="K1" s="288"/>
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
+      <c r="O1" s="288"/>
+      <c r="P1" s="288"/>
+      <c r="Q1" s="288"/>
+      <c r="R1" s="288"/>
+      <c r="S1" s="288"/>
+      <c r="T1" s="288"/>
+      <c r="U1" s="288"/>
+      <c r="V1" s="288"/>
+      <c r="W1" s="288"/>
+      <c r="X1" s="288"/>
+      <c r="Y1" s="289"/>
+      <c r="Z1" s="289"/>
+      <c r="AA1" s="289"/>
+      <c r="AB1" s="289"/>
+      <c r="AC1" s="289"/>
+      <c r="AD1" s="289"/>
+      <c r="AE1" s="289"/>
+      <c r="AF1" s="289"/>
+      <c r="AG1" s="289"/>
+      <c r="AH1" s="289"/>
+      <c r="AI1" s="289"/>
+      <c r="AJ1" s="289"/>
+      <c r="AK1" s="289"/>
+      <c r="AL1" s="289"/>
+      <c r="AM1" s="289"/>
+      <c r="AN1" s="289"/>
+      <c r="AO1" s="289"/>
+      <c r="AP1" s="289"/>
+      <c r="AQ1" s="289"/>
+      <c r="AR1" s="289"/>
+      <c r="AS1" s="289"/>
+      <c r="AT1" s="289"/>
+      <c r="AU1" s="289"/>
+      <c r="AV1" s="289"/>
+      <c r="AW1" s="289"/>
+      <c r="AX1" s="289"/>
+      <c r="AY1" s="289"/>
+      <c r="AZ1" s="289"/>
+      <c r="BA1" s="289"/>
+      <c r="BB1" s="289"/>
+      <c r="BC1" s="289"/>
+      <c r="BD1" s="290"/>
+      <c r="BE1" s="289"/>
+      <c r="BF1" s="290"/>
+      <c r="BG1" s="289"/>
+      <c r="BH1" s="289"/>
+      <c r="BI1" s="289"/>
+      <c r="BJ1" s="289"/>
+      <c r="BK1" s="289"/>
+      <c r="BL1" s="289"/>
+      <c r="BM1" s="289"/>
+      <c r="BN1" s="289"/>
+      <c r="BO1" s="289"/>
+      <c r="BP1" s="291"/>
+      <c r="BQ1" s="289"/>
+      <c r="BR1" s="289"/>
+      <c r="BS1" s="289"/>
+      <c r="BU1" s="289"/>
+      <c r="BV1" s="289"/>
+      <c r="BW1" s="292"/>
+      <c r="BX1" s="292"/>
+      <c r="BY1" s="292"/>
+      <c r="BZ1" s="292"/>
+      <c r="CA1" s="292"/>
+      <c r="CB1" s="293"/>
+      <c r="CC1" s="293"/>
+      <c r="CD1" s="293"/>
     </row>
     <row r="2" spans="1:87" s="240" customFormat="1" ht="19.25" customHeight="1" outlineLevel="1">
-      <c r="A2" s="293" t="s">
+      <c r="A2" s="294" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="283"/>
-      <c r="C2" s="294"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="I2" s="286"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="287"/>
-      <c r="Q2" s="287"/>
-      <c r="R2" s="287"/>
-      <c r="S2" s="287"/>
-      <c r="T2" s="287"/>
-      <c r="U2" s="287"/>
-      <c r="V2" s="287"/>
-      <c r="W2" s="287"/>
-      <c r="X2" s="287"/>
-      <c r="Y2" s="288"/>
-      <c r="Z2" s="288"/>
-      <c r="AA2" s="288"/>
-      <c r="AB2" s="288"/>
-      <c r="AC2" s="288"/>
-      <c r="AD2" s="288"/>
-      <c r="AE2" s="288"/>
-      <c r="AF2" s="288"/>
-      <c r="AG2" s="288"/>
-      <c r="AH2" s="288"/>
-      <c r="AI2" s="288"/>
-      <c r="AJ2" s="288"/>
-      <c r="AK2" s="288"/>
-      <c r="AL2" s="288"/>
-      <c r="AM2" s="288"/>
-      <c r="AN2" s="288"/>
-      <c r="AO2" s="288"/>
-      <c r="AP2" s="288"/>
-      <c r="AQ2" s="288"/>
-      <c r="AR2" s="288"/>
-      <c r="AS2" s="288"/>
-      <c r="AT2" s="288"/>
-      <c r="AU2" s="288"/>
-      <c r="AV2" s="288"/>
-      <c r="AW2" s="288"/>
-      <c r="AX2" s="288"/>
-      <c r="AY2" s="288"/>
-      <c r="AZ2" s="288"/>
-      <c r="BA2" s="288"/>
-      <c r="BB2" s="288"/>
-      <c r="BC2" s="288"/>
-      <c r="BD2" s="289"/>
-      <c r="BE2" s="288"/>
-      <c r="BF2" s="288"/>
-      <c r="BG2" s="288"/>
-      <c r="BH2" s="288"/>
-      <c r="BI2" s="288"/>
-      <c r="BJ2" s="288"/>
-      <c r="BK2" s="288"/>
-      <c r="BL2" s="288"/>
-      <c r="BM2" s="288"/>
-      <c r="BN2" s="288"/>
-      <c r="BO2" s="288"/>
-      <c r="BP2" s="288"/>
-      <c r="BQ2" s="288"/>
-      <c r="BR2" s="288"/>
-      <c r="BS2" s="288"/>
-      <c r="BT2" s="288"/>
-      <c r="BU2" s="288"/>
-      <c r="BV2" s="288"/>
-      <c r="BW2" s="295"/>
-      <c r="BX2" s="295"/>
-      <c r="BY2" s="295"/>
-      <c r="BZ2" s="295"/>
-      <c r="CA2" s="295"/>
-      <c r="CB2" s="294"/>
-      <c r="CC2" s="294"/>
-      <c r="CD2" s="294"/>
+      <c r="B2" s="284"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="I2" s="287"/>
+      <c r="K2" s="288"/>
+      <c r="L2" s="288"/>
+      <c r="M2" s="288"/>
+      <c r="N2" s="288"/>
+      <c r="O2" s="288"/>
+      <c r="P2" s="288"/>
+      <c r="Q2" s="288"/>
+      <c r="R2" s="288"/>
+      <c r="S2" s="288"/>
+      <c r="T2" s="288"/>
+      <c r="U2" s="288"/>
+      <c r="V2" s="288"/>
+      <c r="W2" s="288"/>
+      <c r="X2" s="288"/>
+      <c r="Y2" s="289"/>
+      <c r="Z2" s="289"/>
+      <c r="AA2" s="289"/>
+      <c r="AB2" s="289"/>
+      <c r="AC2" s="289"/>
+      <c r="AD2" s="289"/>
+      <c r="AE2" s="289"/>
+      <c r="AF2" s="289"/>
+      <c r="AG2" s="289"/>
+      <c r="AH2" s="289"/>
+      <c r="AI2" s="289"/>
+      <c r="AJ2" s="289"/>
+      <c r="AK2" s="289"/>
+      <c r="AL2" s="289"/>
+      <c r="AM2" s="289"/>
+      <c r="AN2" s="289"/>
+      <c r="AO2" s="289"/>
+      <c r="AP2" s="289"/>
+      <c r="AQ2" s="289"/>
+      <c r="AR2" s="289"/>
+      <c r="AS2" s="289"/>
+      <c r="AT2" s="289"/>
+      <c r="AU2" s="289"/>
+      <c r="AV2" s="289"/>
+      <c r="AW2" s="289"/>
+      <c r="AX2" s="289"/>
+      <c r="AY2" s="289"/>
+      <c r="AZ2" s="289"/>
+      <c r="BA2" s="289"/>
+      <c r="BB2" s="289"/>
+      <c r="BC2" s="289"/>
+      <c r="BD2" s="290"/>
+      <c r="BE2" s="289"/>
+      <c r="BF2" s="289"/>
+      <c r="BG2" s="289"/>
+      <c r="BH2" s="289"/>
+      <c r="BI2" s="289"/>
+      <c r="BJ2" s="289"/>
+      <c r="BK2" s="289"/>
+      <c r="BL2" s="289"/>
+      <c r="BM2" s="289"/>
+      <c r="BN2" s="289"/>
+      <c r="BO2" s="289"/>
+      <c r="BP2" s="289"/>
+      <c r="BQ2" s="289"/>
+      <c r="BR2" s="289"/>
+      <c r="BS2" s="289"/>
+      <c r="BT2" s="289"/>
+      <c r="BU2" s="289"/>
+      <c r="BV2" s="289"/>
+      <c r="BW2" s="296"/>
+      <c r="BX2" s="296"/>
+      <c r="BY2" s="296"/>
+      <c r="BZ2" s="296"/>
+      <c r="CA2" s="296"/>
+      <c r="CB2" s="295"/>
+      <c r="CC2" s="295"/>
+      <c r="CD2" s="295"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="352"/>
-      <c r="B3" s="351"/>
-      <c r="C3" s="351"/>
-      <c r="D3" s="351"/>
-      <c r="E3" s="351"/>
-      <c r="F3" s="351"/>
-      <c r="G3" s="351"/>
-      <c r="H3" s="351"/>
-      <c r="I3" s="351"/>
-      <c r="J3" s="351"/>
-      <c r="K3" s="351"/>
-      <c r="L3" s="351"/>
-      <c r="M3" s="351"/>
-      <c r="N3" s="351"/>
-      <c r="O3" s="351"/>
-      <c r="P3" s="351"/>
-      <c r="Q3" s="351"/>
-      <c r="R3" s="351"/>
-      <c r="S3" s="351"/>
-      <c r="T3" s="351"/>
-      <c r="U3" s="351"/>
-      <c r="V3" s="351"/>
-      <c r="W3" s="351"/>
-      <c r="X3" s="351"/>
-      <c r="Y3" s="351"/>
-      <c r="Z3" s="351"/>
-      <c r="AA3" s="351"/>
-      <c r="AB3" s="351"/>
-      <c r="AC3" s="351"/>
-      <c r="AD3" s="351"/>
-      <c r="AE3" s="351"/>
-      <c r="AF3" s="351"/>
-      <c r="AG3" s="351"/>
-      <c r="AH3" s="351"/>
-      <c r="AI3" s="351"/>
-      <c r="AJ3" s="351"/>
-      <c r="AK3" s="351"/>
-      <c r="AL3" s="351"/>
-      <c r="AM3" s="351"/>
-      <c r="AN3" s="351"/>
-      <c r="AO3" s="351"/>
-      <c r="AP3" s="351"/>
-      <c r="AQ3" s="351"/>
-      <c r="AR3" s="351"/>
-      <c r="AS3" s="351"/>
-      <c r="AT3" s="351"/>
-      <c r="AU3" s="351"/>
-      <c r="AV3" s="351"/>
-      <c r="AW3" s="351"/>
-      <c r="AX3" s="351"/>
-      <c r="AY3" s="351"/>
-      <c r="AZ3" s="351"/>
-      <c r="BA3" s="351"/>
-      <c r="BB3" s="351"/>
-      <c r="BC3" s="351"/>
-      <c r="BD3" s="351"/>
-      <c r="BE3" s="351"/>
-      <c r="BF3" s="351"/>
-      <c r="BG3" s="351"/>
-      <c r="BH3" s="351"/>
-      <c r="BI3" s="351"/>
-      <c r="BJ3" s="351"/>
-      <c r="BK3" s="351"/>
-      <c r="BL3" s="351"/>
-      <c r="BM3" s="351"/>
-      <c r="BN3" s="351"/>
-      <c r="BO3" s="351"/>
-      <c r="BP3" s="351"/>
-      <c r="BQ3" s="351"/>
-      <c r="BR3" s="351"/>
-      <c r="BS3" s="351"/>
-      <c r="BT3" s="351"/>
-      <c r="BU3" s="351"/>
-      <c r="BV3" s="296"/>
-      <c r="BW3" s="350" t="s">
+      <c r="A3" s="353"/>
+      <c r="B3" s="352"/>
+      <c r="C3" s="352"/>
+      <c r="D3" s="352"/>
+      <c r="E3" s="352"/>
+      <c r="F3" s="352"/>
+      <c r="G3" s="352"/>
+      <c r="H3" s="352"/>
+      <c r="I3" s="352"/>
+      <c r="J3" s="352"/>
+      <c r="K3" s="352"/>
+      <c r="L3" s="352"/>
+      <c r="M3" s="352"/>
+      <c r="N3" s="352"/>
+      <c r="O3" s="352"/>
+      <c r="P3" s="352"/>
+      <c r="Q3" s="352"/>
+      <c r="R3" s="352"/>
+      <c r="S3" s="352"/>
+      <c r="T3" s="352"/>
+      <c r="U3" s="352"/>
+      <c r="V3" s="352"/>
+      <c r="W3" s="352"/>
+      <c r="X3" s="352"/>
+      <c r="Y3" s="352"/>
+      <c r="Z3" s="352"/>
+      <c r="AA3" s="352"/>
+      <c r="AB3" s="352"/>
+      <c r="AC3" s="352"/>
+      <c r="AD3" s="352"/>
+      <c r="AE3" s="352"/>
+      <c r="AF3" s="352"/>
+      <c r="AG3" s="352"/>
+      <c r="AH3" s="352"/>
+      <c r="AI3" s="352"/>
+      <c r="AJ3" s="352"/>
+      <c r="AK3" s="352"/>
+      <c r="AL3" s="352"/>
+      <c r="AM3" s="352"/>
+      <c r="AN3" s="352"/>
+      <c r="AO3" s="352"/>
+      <c r="AP3" s="352"/>
+      <c r="AQ3" s="352"/>
+      <c r="AR3" s="352"/>
+      <c r="AS3" s="352"/>
+      <c r="AT3" s="352"/>
+      <c r="AU3" s="352"/>
+      <c r="AV3" s="352"/>
+      <c r="AW3" s="352"/>
+      <c r="AX3" s="352"/>
+      <c r="AY3" s="352"/>
+      <c r="AZ3" s="352"/>
+      <c r="BA3" s="352"/>
+      <c r="BB3" s="352"/>
+      <c r="BC3" s="352"/>
+      <c r="BD3" s="352"/>
+      <c r="BE3" s="352"/>
+      <c r="BF3" s="352"/>
+      <c r="BG3" s="352"/>
+      <c r="BH3" s="352"/>
+      <c r="BI3" s="352"/>
+      <c r="BJ3" s="352"/>
+      <c r="BK3" s="352"/>
+      <c r="BL3" s="352"/>
+      <c r="BM3" s="352"/>
+      <c r="BN3" s="352"/>
+      <c r="BO3" s="352"/>
+      <c r="BP3" s="352"/>
+      <c r="BQ3" s="352"/>
+      <c r="BR3" s="352"/>
+      <c r="BS3" s="352"/>
+      <c r="BT3" s="352"/>
+      <c r="BU3" s="352"/>
+      <c r="BV3" s="297"/>
+      <c r="BW3" s="351" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="351"/>
-      <c r="BY3" s="351"/>
-      <c r="BZ3" s="351"/>
-      <c r="CA3" s="351"/>
-      <c r="CB3" s="351"/>
-      <c r="CC3" s="298"/>
-      <c r="CD3" s="298"/>
+      <c r="BX3" s="352"/>
+      <c r="BY3" s="352"/>
+      <c r="BZ3" s="352"/>
+      <c r="CA3" s="352"/>
+      <c r="CB3" s="352"/>
+      <c r="CC3" s="299"/>
+      <c r="CD3" s="299"/>
     </row>
     <row r="4" spans="1:87" s="14" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
-      <c r="A4" s="299"/>
-      <c r="B4" s="299"/>
-      <c r="C4" s="299"/>
-      <c r="D4" s="299"/>
-      <c r="E4" s="299"/>
-      <c r="F4" s="299"/>
-      <c r="G4" s="299"/>
-      <c r="H4" s="299"/>
-      <c r="I4" s="286"/>
-      <c r="K4" s="299"/>
-      <c r="L4" s="299"/>
-      <c r="M4" s="299"/>
-      <c r="N4" s="299"/>
-      <c r="O4" s="299"/>
-      <c r="P4" s="299"/>
-      <c r="Q4" s="299"/>
-      <c r="R4" s="299"/>
-      <c r="S4" s="299"/>
-      <c r="T4" s="299"/>
-      <c r="U4" s="299"/>
-      <c r="V4" s="300"/>
-      <c r="W4" s="300"/>
-      <c r="X4" s="300"/>
-      <c r="Y4" s="300"/>
-      <c r="Z4" s="300"/>
-      <c r="AA4" s="300"/>
-      <c r="AB4" s="300"/>
-      <c r="AC4" s="300"/>
-      <c r="AD4" s="300"/>
-      <c r="AE4" s="300"/>
-      <c r="AF4" s="300"/>
-      <c r="AG4" s="300"/>
-      <c r="AH4" s="300"/>
-      <c r="AI4" s="300"/>
-      <c r="AJ4" s="300"/>
-      <c r="AK4" s="300"/>
-      <c r="AL4" s="300"/>
-      <c r="AM4" s="299"/>
-      <c r="AN4" s="299"/>
-      <c r="AO4" s="299"/>
-      <c r="AP4" s="299"/>
-      <c r="AQ4" s="299"/>
-      <c r="AR4" s="299"/>
-      <c r="AS4" s="299"/>
-      <c r="AT4" s="299"/>
-      <c r="AU4" s="299"/>
-      <c r="AV4" s="299"/>
-      <c r="AW4" s="299"/>
-      <c r="AX4" s="299"/>
-      <c r="AY4" s="299"/>
-      <c r="AZ4" s="299"/>
-      <c r="BA4" s="299"/>
-      <c r="BB4" s="299"/>
-      <c r="BC4" s="299"/>
-      <c r="BD4" s="299"/>
-      <c r="BE4" s="299"/>
-      <c r="BF4" s="299"/>
-      <c r="BG4" s="299"/>
-      <c r="BH4" s="299"/>
-      <c r="BI4" s="299"/>
-      <c r="BJ4" s="299"/>
-      <c r="BK4" s="299"/>
-      <c r="BL4" s="299"/>
-      <c r="BM4" s="299"/>
-      <c r="BN4" s="299"/>
-      <c r="BO4" s="299"/>
-      <c r="BP4" s="299"/>
-      <c r="BQ4" s="299"/>
-      <c r="BR4" s="299"/>
-      <c r="BS4" s="299"/>
-      <c r="BT4" s="299"/>
-      <c r="BU4" s="299"/>
-      <c r="BV4" s="299"/>
-      <c r="BW4" s="351"/>
-      <c r="BX4" s="351"/>
-      <c r="BY4" s="351"/>
-      <c r="BZ4" s="351"/>
-      <c r="CA4" s="351"/>
-      <c r="CB4" s="351"/>
-      <c r="CC4" s="298"/>
-      <c r="CD4" s="298"/>
+      <c r="A4" s="300"/>
+      <c r="B4" s="300"/>
+      <c r="C4" s="300"/>
+      <c r="D4" s="300"/>
+      <c r="E4" s="300"/>
+      <c r="F4" s="300"/>
+      <c r="G4" s="300"/>
+      <c r="H4" s="300"/>
+      <c r="I4" s="287"/>
+      <c r="K4" s="300"/>
+      <c r="L4" s="300"/>
+      <c r="M4" s="300"/>
+      <c r="N4" s="300"/>
+      <c r="O4" s="300"/>
+      <c r="P4" s="300"/>
+      <c r="Q4" s="300"/>
+      <c r="R4" s="300"/>
+      <c r="S4" s="300"/>
+      <c r="T4" s="300"/>
+      <c r="U4" s="300"/>
+      <c r="V4" s="301"/>
+      <c r="W4" s="301"/>
+      <c r="X4" s="301"/>
+      <c r="Y4" s="301"/>
+      <c r="Z4" s="301"/>
+      <c r="AA4" s="301"/>
+      <c r="AB4" s="301"/>
+      <c r="AC4" s="301"/>
+      <c r="AD4" s="301"/>
+      <c r="AE4" s="301"/>
+      <c r="AF4" s="301"/>
+      <c r="AG4" s="301"/>
+      <c r="AH4" s="301"/>
+      <c r="AI4" s="301"/>
+      <c r="AJ4" s="301"/>
+      <c r="AK4" s="301"/>
+      <c r="AL4" s="301"/>
+      <c r="AM4" s="300"/>
+      <c r="AN4" s="300"/>
+      <c r="AO4" s="300"/>
+      <c r="AP4" s="300"/>
+      <c r="AQ4" s="300"/>
+      <c r="AR4" s="300"/>
+      <c r="AS4" s="300"/>
+      <c r="AT4" s="300"/>
+      <c r="AU4" s="300"/>
+      <c r="AV4" s="300"/>
+      <c r="AW4" s="300"/>
+      <c r="AX4" s="300"/>
+      <c r="AY4" s="300"/>
+      <c r="AZ4" s="300"/>
+      <c r="BA4" s="300"/>
+      <c r="BB4" s="300"/>
+      <c r="BC4" s="300"/>
+      <c r="BD4" s="300"/>
+      <c r="BE4" s="300"/>
+      <c r="BF4" s="300"/>
+      <c r="BG4" s="300"/>
+      <c r="BH4" s="300"/>
+      <c r="BI4" s="300"/>
+      <c r="BJ4" s="300"/>
+      <c r="BK4" s="300"/>
+      <c r="BL4" s="300"/>
+      <c r="BM4" s="300"/>
+      <c r="BN4" s="300"/>
+      <c r="BO4" s="300"/>
+      <c r="BP4" s="300"/>
+      <c r="BQ4" s="300"/>
+      <c r="BR4" s="300"/>
+      <c r="BS4" s="300"/>
+      <c r="BT4" s="300"/>
+      <c r="BU4" s="300"/>
+      <c r="BV4" s="300"/>
+      <c r="BW4" s="352"/>
+      <c r="BX4" s="352"/>
+      <c r="BY4" s="352"/>
+      <c r="BZ4" s="352"/>
+      <c r="CA4" s="352"/>
+      <c r="CB4" s="352"/>
+      <c r="CC4" s="299"/>
+      <c r="CD4" s="299"/>
     </row>
     <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
-      <c r="A5" s="299"/>
-      <c r="B5" s="299"/>
-      <c r="C5" s="299"/>
-      <c r="D5" s="299"/>
-      <c r="E5" s="299"/>
-      <c r="F5" s="299"/>
-      <c r="G5" s="299"/>
-      <c r="H5" s="299"/>
-      <c r="I5" s="286"/>
-      <c r="K5" s="299"/>
-      <c r="L5" s="299"/>
-      <c r="M5" s="299"/>
-      <c r="N5" s="299"/>
-      <c r="O5" s="299"/>
-      <c r="P5" s="299"/>
-      <c r="Q5" s="299"/>
-      <c r="R5" s="299"/>
-      <c r="S5" s="299"/>
-      <c r="T5" s="299"/>
-      <c r="U5" s="299"/>
-      <c r="V5" s="299"/>
-      <c r="W5" s="299"/>
-      <c r="X5" s="299"/>
-      <c r="Y5" s="299"/>
-      <c r="Z5" s="299"/>
-      <c r="AA5" s="299"/>
-      <c r="AB5" s="299"/>
-      <c r="AC5" s="299"/>
-      <c r="AD5" s="299"/>
-      <c r="AE5" s="299"/>
-      <c r="AF5" s="299"/>
-      <c r="AG5" s="299"/>
-      <c r="AH5" s="299"/>
-      <c r="AI5" s="299"/>
-      <c r="AJ5" s="299"/>
-      <c r="AK5" s="299"/>
-      <c r="AL5" s="299"/>
-      <c r="AM5" s="299"/>
-      <c r="AN5" s="299"/>
-      <c r="AO5" s="299"/>
-      <c r="AP5" s="299"/>
-      <c r="AQ5" s="299"/>
-      <c r="AR5" s="299"/>
-      <c r="AS5" s="299"/>
-      <c r="AT5" s="299"/>
-      <c r="AU5" s="299"/>
-      <c r="AV5" s="299"/>
-      <c r="AW5" s="299"/>
-      <c r="AX5" s="299"/>
-      <c r="AY5" s="299"/>
-      <c r="AZ5" s="299"/>
-      <c r="BA5" s="299"/>
-      <c r="BB5" s="299"/>
-      <c r="BC5" s="299"/>
-      <c r="BD5" s="299"/>
-      <c r="BE5" s="299"/>
-      <c r="BF5" s="299"/>
-      <c r="BG5" s="299"/>
-      <c r="BH5" s="299"/>
-      <c r="BI5" s="299"/>
-      <c r="BJ5" s="299"/>
-      <c r="BK5" s="299"/>
-      <c r="BL5" s="299"/>
-      <c r="BM5" s="299"/>
-      <c r="BN5" s="299"/>
-      <c r="BO5" s="299"/>
-      <c r="BP5" s="299"/>
-      <c r="BQ5" s="299"/>
-      <c r="BR5" s="299"/>
-      <c r="BS5" s="299"/>
-      <c r="BT5" s="299"/>
-      <c r="BU5" s="299"/>
-      <c r="BV5" s="299"/>
-      <c r="BW5" s="351"/>
-      <c r="BX5" s="351"/>
-      <c r="BY5" s="351"/>
-      <c r="BZ5" s="351"/>
-      <c r="CA5" s="351"/>
-      <c r="CB5" s="351"/>
-      <c r="CC5" s="298"/>
-      <c r="CD5" s="298"/>
+      <c r="A5" s="300"/>
+      <c r="B5" s="300"/>
+      <c r="C5" s="300"/>
+      <c r="D5" s="300"/>
+      <c r="E5" s="300"/>
+      <c r="F5" s="300"/>
+      <c r="G5" s="300"/>
+      <c r="H5" s="300"/>
+      <c r="I5" s="287"/>
+      <c r="K5" s="300"/>
+      <c r="L5" s="300"/>
+      <c r="M5" s="300"/>
+      <c r="N5" s="300"/>
+      <c r="O5" s="300"/>
+      <c r="P5" s="300"/>
+      <c r="Q5" s="300"/>
+      <c r="R5" s="300"/>
+      <c r="S5" s="300"/>
+      <c r="T5" s="300"/>
+      <c r="U5" s="300"/>
+      <c r="V5" s="300"/>
+      <c r="W5" s="300"/>
+      <c r="X5" s="300"/>
+      <c r="Y5" s="300"/>
+      <c r="Z5" s="300"/>
+      <c r="AA5" s="300"/>
+      <c r="AB5" s="300"/>
+      <c r="AC5" s="300"/>
+      <c r="AD5" s="300"/>
+      <c r="AE5" s="300"/>
+      <c r="AF5" s="300"/>
+      <c r="AG5" s="300"/>
+      <c r="AH5" s="300"/>
+      <c r="AI5" s="300"/>
+      <c r="AJ5" s="300"/>
+      <c r="AK5" s="300"/>
+      <c r="AL5" s="300"/>
+      <c r="AM5" s="300"/>
+      <c r="AN5" s="300"/>
+      <c r="AO5" s="300"/>
+      <c r="AP5" s="300"/>
+      <c r="AQ5" s="300"/>
+      <c r="AR5" s="300"/>
+      <c r="AS5" s="300"/>
+      <c r="AT5" s="300"/>
+      <c r="AU5" s="300"/>
+      <c r="AV5" s="300"/>
+      <c r="AW5" s="300"/>
+      <c r="AX5" s="300"/>
+      <c r="AY5" s="300"/>
+      <c r="AZ5" s="300"/>
+      <c r="BA5" s="300"/>
+      <c r="BB5" s="300"/>
+      <c r="BC5" s="300"/>
+      <c r="BD5" s="300"/>
+      <c r="BE5" s="300"/>
+      <c r="BF5" s="300"/>
+      <c r="BG5" s="300"/>
+      <c r="BH5" s="300"/>
+      <c r="BI5" s="300"/>
+      <c r="BJ5" s="300"/>
+      <c r="BK5" s="300"/>
+      <c r="BL5" s="300"/>
+      <c r="BM5" s="300"/>
+      <c r="BN5" s="300"/>
+      <c r="BO5" s="300"/>
+      <c r="BP5" s="300"/>
+      <c r="BQ5" s="300"/>
+      <c r="BR5" s="300"/>
+      <c r="BS5" s="300"/>
+      <c r="BT5" s="300"/>
+      <c r="BU5" s="300"/>
+      <c r="BV5" s="300"/>
+      <c r="BW5" s="352"/>
+      <c r="BX5" s="352"/>
+      <c r="BY5" s="352"/>
+      <c r="BZ5" s="352"/>
+      <c r="CA5" s="352"/>
+      <c r="CB5" s="352"/>
+      <c r="CC5" s="299"/>
+      <c r="CD5" s="299"/>
     </row>
     <row r="6" spans="1:87" s="14" customFormat="1" ht="34" customHeight="1" outlineLevel="1">
-      <c r="A6" s="301"/>
-      <c r="D6" s="301"/>
-      <c r="E6" s="301"/>
-      <c r="F6" s="301"/>
-      <c r="G6" s="301"/>
-      <c r="H6" s="301"/>
-      <c r="I6" s="286"/>
-      <c r="K6" s="302"/>
-      <c r="L6" s="302"/>
-      <c r="M6" s="302"/>
-      <c r="N6" s="302"/>
-      <c r="O6" s="302"/>
-      <c r="P6" s="302"/>
-      <c r="Q6" s="302"/>
-      <c r="R6" s="302"/>
-      <c r="S6" s="302"/>
-      <c r="T6" s="302"/>
-      <c r="U6" s="302"/>
-      <c r="V6" s="302"/>
-      <c r="W6" s="302"/>
-      <c r="X6" s="302"/>
-      <c r="Y6" s="303"/>
-      <c r="Z6" s="303"/>
-      <c r="AA6" s="303"/>
-      <c r="AB6" s="303"/>
-      <c r="AC6" s="299"/>
-      <c r="AD6" s="301"/>
-      <c r="AE6" s="301"/>
-      <c r="AF6" s="301"/>
-      <c r="AG6" s="301"/>
-      <c r="AH6" s="301"/>
-      <c r="AI6" s="301"/>
-      <c r="AJ6" s="301"/>
-      <c r="AK6" s="301"/>
-      <c r="AL6" s="301"/>
-      <c r="AM6" s="301"/>
-      <c r="AN6" s="301"/>
-      <c r="AO6" s="301"/>
-      <c r="AP6" s="301"/>
-      <c r="AQ6" s="301"/>
-      <c r="AR6" s="301"/>
-      <c r="AS6" s="301"/>
-      <c r="AT6" s="301"/>
-      <c r="AU6" s="301"/>
-      <c r="AV6" s="301"/>
-      <c r="AW6" s="301"/>
-      <c r="AX6" s="301"/>
-      <c r="AY6" s="301"/>
-      <c r="AZ6" s="301"/>
-      <c r="BA6" s="301"/>
-      <c r="BB6" s="301"/>
-      <c r="BC6" s="301"/>
-      <c r="BD6" s="301"/>
-      <c r="BE6" s="301"/>
-      <c r="BF6" s="301"/>
-      <c r="BG6" s="301"/>
-      <c r="BH6" s="301"/>
-      <c r="BI6" s="301"/>
-      <c r="BJ6" s="301"/>
-      <c r="BK6" s="301"/>
-      <c r="BL6" s="301"/>
-      <c r="BM6" s="301"/>
-      <c r="BN6" s="301"/>
-      <c r="BO6" s="301"/>
-      <c r="BP6" s="301"/>
-      <c r="BQ6" s="301"/>
-      <c r="BR6" s="301"/>
-      <c r="BS6" s="301"/>
-      <c r="BT6" s="301"/>
-      <c r="BU6" s="301"/>
-      <c r="BV6" s="301"/>
-      <c r="BW6" s="351"/>
-      <c r="BX6" s="351"/>
-      <c r="BY6" s="351"/>
-      <c r="BZ6" s="351"/>
-      <c r="CA6" s="351"/>
-      <c r="CB6" s="351"/>
-      <c r="CC6" s="298"/>
-      <c r="CD6" s="298"/>
+      <c r="A6" s="302"/>
+      <c r="D6" s="302"/>
+      <c r="E6" s="302"/>
+      <c r="F6" s="302"/>
+      <c r="G6" s="302"/>
+      <c r="H6" s="302"/>
+      <c r="I6" s="287"/>
+      <c r="K6" s="303"/>
+      <c r="L6" s="303"/>
+      <c r="M6" s="303"/>
+      <c r="N6" s="303"/>
+      <c r="O6" s="303"/>
+      <c r="P6" s="303"/>
+      <c r="Q6" s="303"/>
+      <c r="R6" s="303"/>
+      <c r="S6" s="303"/>
+      <c r="T6" s="303"/>
+      <c r="U6" s="303"/>
+      <c r="V6" s="303"/>
+      <c r="W6" s="303"/>
+      <c r="X6" s="303"/>
+      <c r="Y6" s="304"/>
+      <c r="Z6" s="304"/>
+      <c r="AA6" s="304"/>
+      <c r="AB6" s="304"/>
+      <c r="AC6" s="300"/>
+      <c r="AD6" s="302"/>
+      <c r="AE6" s="302"/>
+      <c r="AF6" s="302"/>
+      <c r="AG6" s="302"/>
+      <c r="AH6" s="302"/>
+      <c r="AI6" s="302"/>
+      <c r="AJ6" s="302"/>
+      <c r="AK6" s="302"/>
+      <c r="AL6" s="302"/>
+      <c r="AM6" s="302"/>
+      <c r="AN6" s="302"/>
+      <c r="AO6" s="302"/>
+      <c r="AP6" s="302"/>
+      <c r="AQ6" s="302"/>
+      <c r="AR6" s="302"/>
+      <c r="AS6" s="302"/>
+      <c r="AT6" s="302"/>
+      <c r="AU6" s="302"/>
+      <c r="AV6" s="302"/>
+      <c r="AW6" s="302"/>
+      <c r="AX6" s="302"/>
+      <c r="AY6" s="302"/>
+      <c r="AZ6" s="302"/>
+      <c r="BA6" s="302"/>
+      <c r="BB6" s="302"/>
+      <c r="BC6" s="302"/>
+      <c r="BD6" s="302"/>
+      <c r="BE6" s="302"/>
+      <c r="BF6" s="302"/>
+      <c r="BG6" s="302"/>
+      <c r="BH6" s="302"/>
+      <c r="BI6" s="302"/>
+      <c r="BJ6" s="302"/>
+      <c r="BK6" s="302"/>
+      <c r="BL6" s="302"/>
+      <c r="BM6" s="302"/>
+      <c r="BN6" s="302"/>
+      <c r="BO6" s="302"/>
+      <c r="BP6" s="302"/>
+      <c r="BQ6" s="302"/>
+      <c r="BR6" s="302"/>
+      <c r="BS6" s="302"/>
+      <c r="BT6" s="302"/>
+      <c r="BU6" s="302"/>
+      <c r="BV6" s="302"/>
+      <c r="BW6" s="352"/>
+      <c r="BX6" s="352"/>
+      <c r="BY6" s="352"/>
+      <c r="BZ6" s="352"/>
+      <c r="CA6" s="352"/>
+      <c r="CB6" s="352"/>
+      <c r="CC6" s="299"/>
+      <c r="CD6" s="299"/>
     </row>
-    <row r="7" spans="1:87" s="321" customFormat="1" ht="31" outlineLevel="1">
-      <c r="B7" s="301" t="s">
+    <row r="7" spans="1:87" s="322" customFormat="1" ht="31" outlineLevel="1">
+      <c r="B7" s="302" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="301" t="s">
+      <c r="C7" s="302" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="322"/>
-      <c r="E7" s="322" t="s">
+      <c r="D7" s="323"/>
+      <c r="E7" s="323" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="323"/>
-      <c r="G7" s="322" t="s">
+      <c r="F7" s="324"/>
+      <c r="G7" s="323" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="322"/>
-      <c r="I7" s="324" t="s">
+      <c r="H7" s="323"/>
+      <c r="I7" s="325" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="321" t="s">
+      <c r="J7" s="322" t="s">
         <v>157</v>
       </c>
-      <c r="K7" s="325"/>
-      <c r="L7" s="325"/>
-      <c r="M7" s="325"/>
-      <c r="N7" s="325"/>
-      <c r="O7" s="325"/>
-      <c r="Q7" s="325"/>
-      <c r="R7" s="325"/>
-      <c r="S7" s="325"/>
-      <c r="T7" s="325"/>
-      <c r="U7" s="326"/>
-      <c r="V7" s="325"/>
-      <c r="W7" s="325"/>
-      <c r="X7" s="325"/>
-      <c r="Y7" s="327" t="s">
+      <c r="K7" s="326"/>
+      <c r="L7" s="326"/>
+      <c r="M7" s="326"/>
+      <c r="N7" s="326"/>
+      <c r="O7" s="326"/>
+      <c r="Q7" s="326"/>
+      <c r="R7" s="326"/>
+      <c r="S7" s="326"/>
+      <c r="T7" s="326"/>
+      <c r="U7" s="327"/>
+      <c r="V7" s="326"/>
+      <c r="W7" s="326"/>
+      <c r="X7" s="326"/>
+      <c r="Y7" s="328" t="s">
         <v>158</v>
       </c>
-      <c r="Z7" s="327" t="s">
+      <c r="Z7" s="328" t="s">
         <v>158</v>
       </c>
-      <c r="AA7" s="327" t="s">
+      <c r="AA7" s="328" t="s">
         <v>158</v>
       </c>
-      <c r="AB7" s="327"/>
-      <c r="AC7" s="325" t="s">
+      <c r="AB7" s="328"/>
+      <c r="AC7" s="326" t="s">
         <v>158</v>
       </c>
-      <c r="AD7" s="301" t="s">
+      <c r="AD7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AE7" s="301" t="s">
+      <c r="AE7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AF7" s="301"/>
-      <c r="AG7" s="301"/>
-      <c r="AH7" s="301" t="s">
+      <c r="AF7" s="302"/>
+      <c r="AG7" s="302"/>
+      <c r="AH7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AI7" s="301" t="s">
+      <c r="AI7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AJ7" s="301"/>
-      <c r="AK7" s="301"/>
-      <c r="AL7" s="301" t="s">
+      <c r="AJ7" s="302"/>
+      <c r="AK7" s="302"/>
+      <c r="AL7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AM7" s="301" t="s">
+      <c r="AM7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AN7" s="301" t="s">
+      <c r="AN7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AO7" s="301" t="s">
+      <c r="AO7" s="302" t="s">
         <v>158</v>
       </c>
-      <c r="AP7" s="301" t="s">
+      <c r="AP7" s="302" t="s">
         <v>159</v>
       </c>
-      <c r="AQ7" s="301"/>
-      <c r="AR7" s="301" t="s">
+      <c r="AQ7" s="302"/>
+      <c r="AR7" s="302" t="s">
         <v>159</v>
       </c>
-      <c r="AS7" s="301" t="s">
+      <c r="AS7" s="302" t="s">
         <v>159</v>
       </c>
-      <c r="AT7" s="301" t="s">
+      <c r="AT7" s="302" t="s">
         <v>156</v>
       </c>
-      <c r="AU7" s="301" t="s">
+      <c r="AU7" s="302" t="s">
         <v>159</v>
       </c>
-      <c r="AY7" s="322"/>
-      <c r="BA7" s="322"/>
-      <c r="BB7" s="322" t="s">
+      <c r="AY7" s="323"/>
+      <c r="BA7" s="323"/>
+      <c r="BB7" s="323" t="s">
         <v>160</v>
       </c>
-      <c r="BE7" s="322"/>
-      <c r="BF7" s="322"/>
-      <c r="BG7" s="322"/>
-      <c r="BH7" s="322"/>
-      <c r="BI7" s="322" t="s">
+      <c r="BE7" s="323"/>
+      <c r="BF7" s="323"/>
+      <c r="BG7" s="323"/>
+      <c r="BH7" s="323"/>
+      <c r="BI7" s="323" t="s">
         <v>160</v>
       </c>
-      <c r="BJ7" s="322"/>
-      <c r="BK7" s="322"/>
-      <c r="BL7" s="321" t="s">
+      <c r="BJ7" s="323"/>
+      <c r="BK7" s="323"/>
+      <c r="BL7" s="322" t="s">
         <v>160</v>
       </c>
-      <c r="BN7" s="322"/>
-      <c r="BP7" s="322"/>
-      <c r="BT7" s="322" t="s">
+      <c r="BN7" s="323"/>
+      <c r="BP7" s="323"/>
+      <c r="BT7" s="323" t="s">
         <v>161</v>
       </c>
-      <c r="BU7" s="321" t="s">
+      <c r="BU7" s="322" t="s">
         <v>161</v>
       </c>
-      <c r="BW7" s="297"/>
-      <c r="BX7" s="297" t="s">
+      <c r="BW7" s="298"/>
+      <c r="BX7" s="298" t="s">
         <v>156</v>
       </c>
-      <c r="BY7" s="297" t="s">
+      <c r="BY7" s="298" t="s">
         <v>156</v>
       </c>
-      <c r="BZ7" s="297"/>
-      <c r="CA7" s="297" t="s">
+      <c r="BZ7" s="298"/>
+      <c r="CA7" s="298" t="s">
         <v>156</v>
       </c>
-      <c r="CB7" s="326"/>
-      <c r="CC7" s="326"/>
-      <c r="CD7" s="326"/>
-      <c r="CE7" s="301" t="s">
+      <c r="CB7" s="327"/>
+      <c r="CC7" s="327"/>
+      <c r="CD7" s="327"/>
+      <c r="CE7" s="302" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="349" t="s">
+    <row r="8" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="350" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="354" t="s">
+      <c r="B8" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="337" t="s">
+      <c r="C8" s="338" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="341" t="s">
+      <c r="D8" s="342" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="341" t="s">
+      <c r="E8" s="342" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="337" t="s">
+      <c r="F8" s="338" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="426" t="s">
+      <c r="G8" s="427" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="348" t="s">
+      <c r="H8" s="349" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="348" t="s">
+      <c r="I8" s="349" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="429" t="s">
+      <c r="J8" s="430" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="362" t="s">
+      <c r="K8" s="363" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="363"/>
-      <c r="M8" s="363"/>
-      <c r="N8" s="363"/>
-      <c r="O8" s="363"/>
-      <c r="P8" s="363"/>
-      <c r="Q8" s="363"/>
-      <c r="R8" s="363"/>
-      <c r="S8" s="363"/>
-      <c r="T8" s="363"/>
-      <c r="U8" s="363"/>
-      <c r="V8" s="363"/>
-      <c r="W8" s="363"/>
-      <c r="X8" s="363"/>
-      <c r="Y8" s="367" t="s">
+      <c r="L8" s="364"/>
+      <c r="M8" s="364"/>
+      <c r="N8" s="364"/>
+      <c r="O8" s="364"/>
+      <c r="P8" s="364"/>
+      <c r="Q8" s="364"/>
+      <c r="R8" s="364"/>
+      <c r="S8" s="364"/>
+      <c r="T8" s="364"/>
+      <c r="U8" s="364"/>
+      <c r="V8" s="364"/>
+      <c r="W8" s="364"/>
+      <c r="X8" s="364"/>
+      <c r="Y8" s="368" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="363"/>
-      <c r="AA8" s="363"/>
-      <c r="AB8" s="363"/>
-      <c r="AC8" s="363"/>
-      <c r="AD8" s="363"/>
-      <c r="AE8" s="363"/>
-      <c r="AF8" s="363"/>
-      <c r="AG8" s="363"/>
-      <c r="AH8" s="363"/>
-      <c r="AI8" s="363"/>
-      <c r="AJ8" s="363"/>
-      <c r="AK8" s="363"/>
-      <c r="AL8" s="363"/>
-      <c r="AM8" s="363"/>
-      <c r="AN8" s="363"/>
-      <c r="AO8" s="365"/>
-      <c r="AP8" s="429" t="s">
+      <c r="Z8" s="364"/>
+      <c r="AA8" s="364"/>
+      <c r="AB8" s="364"/>
+      <c r="AC8" s="364"/>
+      <c r="AD8" s="364"/>
+      <c r="AE8" s="364"/>
+      <c r="AF8" s="364"/>
+      <c r="AG8" s="364"/>
+      <c r="AH8" s="364"/>
+      <c r="AI8" s="364"/>
+      <c r="AJ8" s="364"/>
+      <c r="AK8" s="364"/>
+      <c r="AL8" s="364"/>
+      <c r="AM8" s="364"/>
+      <c r="AN8" s="364"/>
+      <c r="AO8" s="366"/>
+      <c r="AP8" s="430" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="429" t="s">
+      <c r="AQ8" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="429" t="s">
+      <c r="AR8" s="430" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="429" t="s">
+      <c r="AS8" s="430" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="429" t="s">
+      <c r="AT8" s="430" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="429" t="s">
+      <c r="AU8" s="430" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="337" t="s">
+      <c r="AV8" s="338" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="434" t="s">
+      <c r="AW8" s="435" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="337" t="s">
+      <c r="AX8" s="338" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="364" t="s">
+      <c r="AY8" s="365" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="363"/>
-      <c r="BA8" s="363"/>
-      <c r="BB8" s="363"/>
-      <c r="BC8" s="363"/>
-      <c r="BD8" s="363"/>
-      <c r="BE8" s="363"/>
-      <c r="BF8" s="363"/>
-      <c r="BG8" s="363"/>
-      <c r="BH8" s="363"/>
-      <c r="BI8" s="363"/>
-      <c r="BJ8" s="363"/>
-      <c r="BK8" s="363"/>
-      <c r="BL8" s="363"/>
-      <c r="BM8" s="363"/>
-      <c r="BN8" s="363"/>
-      <c r="BO8" s="363"/>
-      <c r="BP8" s="363"/>
-      <c r="BQ8" s="365"/>
-      <c r="BR8" s="368" t="s">
+      <c r="AZ8" s="364"/>
+      <c r="BA8" s="364"/>
+      <c r="BB8" s="364"/>
+      <c r="BC8" s="364"/>
+      <c r="BD8" s="364"/>
+      <c r="BE8" s="364"/>
+      <c r="BF8" s="364"/>
+      <c r="BG8" s="364"/>
+      <c r="BH8" s="364"/>
+      <c r="BI8" s="364"/>
+      <c r="BJ8" s="364"/>
+      <c r="BK8" s="364"/>
+      <c r="BL8" s="364"/>
+      <c r="BM8" s="364"/>
+      <c r="BN8" s="364"/>
+      <c r="BO8" s="364"/>
+      <c r="BP8" s="364"/>
+      <c r="BQ8" s="366"/>
+      <c r="BR8" s="369" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="359"/>
-      <c r="BT8" s="337" t="s">
+      <c r="BS8" s="360"/>
+      <c r="BT8" s="338" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="355" t="s">
+      <c r="BU8" s="356" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="22"/>
-      <c r="BW8" s="437" t="s">
+      <c r="BW8" s="438" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="328" t="s">
+      <c r="BX8" s="329" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="329"/>
-      <c r="BZ8" s="329"/>
-      <c r="CA8" s="330"/>
-      <c r="CB8" s="369" t="s">
+      <c r="BY8" s="330"/>
+      <c r="BZ8" s="330"/>
+      <c r="CA8" s="331"/>
+      <c r="CB8" s="370" t="s">
         <v>31</v>
       </c>
       <c r="CC8" s="444" t="s">
@@ -8407,211 +8408,211 @@
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
-    <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="346"/>
-      <c r="B9" s="338"/>
-      <c r="C9" s="338"/>
-      <c r="D9" s="338"/>
-      <c r="E9" s="338"/>
-      <c r="F9" s="338"/>
-      <c r="G9" s="427"/>
-      <c r="H9" s="346"/>
-      <c r="I9" s="346"/>
-      <c r="J9" s="430"/>
-      <c r="K9" s="345" t="s">
+    <row r="9" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="347"/>
+      <c r="B9" s="339"/>
+      <c r="C9" s="339"/>
+      <c r="D9" s="339"/>
+      <c r="E9" s="339"/>
+      <c r="F9" s="339"/>
+      <c r="G9" s="428"/>
+      <c r="H9" s="347"/>
+      <c r="I9" s="347"/>
+      <c r="J9" s="431"/>
+      <c r="K9" s="346" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="345" t="s">
+      <c r="L9" s="346" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="345" t="s">
+      <c r="M9" s="346" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="345" t="s">
+      <c r="N9" s="346" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="345" t="s">
+      <c r="O9" s="346" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="345" t="s">
+      <c r="P9" s="346" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="345" t="s">
+      <c r="Q9" s="346" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="345" t="s">
+      <c r="R9" s="346" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="345" t="s">
+      <c r="S9" s="346" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="345" t="s">
+      <c r="T9" s="346" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="345" t="s">
+      <c r="U9" s="346" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="358" t="s">
+      <c r="V9" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="359"/>
-      <c r="X9" s="345" t="s">
+      <c r="W9" s="360"/>
+      <c r="X9" s="346" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="340" t="s">
+      <c r="Y9" s="341" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="340" t="s">
+      <c r="Z9" s="341" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="340" t="s">
+      <c r="AA9" s="341" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="340" t="s">
+      <c r="AB9" s="341" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="340" t="s">
+      <c r="AC9" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="340" t="s">
+      <c r="AD9" s="341" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="340" t="s">
+      <c r="AE9" s="341" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="340" t="s">
+      <c r="AF9" s="341" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="340" t="s">
+      <c r="AG9" s="341" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="340" t="s">
+      <c r="AH9" s="341" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="340" t="s">
+      <c r="AI9" s="341" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="432" t="s">
+      <c r="AJ9" s="433" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="355" t="s">
+      <c r="AK9" s="356" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="433" t="s">
+      <c r="AL9" s="434" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="340" t="s">
+      <c r="AM9" s="341" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="337" t="s">
+      <c r="AN9" s="338" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="337" t="s">
+      <c r="AO9" s="338" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="430"/>
-      <c r="AQ9" s="430"/>
-      <c r="AR9" s="430"/>
-      <c r="AS9" s="430"/>
-      <c r="AT9" s="430"/>
-      <c r="AU9" s="430"/>
-      <c r="AV9" s="338"/>
-      <c r="AW9" s="430"/>
-      <c r="AX9" s="338"/>
-      <c r="AY9" s="371" t="s">
+      <c r="AP9" s="431"/>
+      <c r="AQ9" s="431"/>
+      <c r="AR9" s="431"/>
+      <c r="AS9" s="431"/>
+      <c r="AT9" s="431"/>
+      <c r="AU9" s="431"/>
+      <c r="AV9" s="339"/>
+      <c r="AW9" s="431"/>
+      <c r="AX9" s="339"/>
+      <c r="AY9" s="372" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="372"/>
-      <c r="BA9" s="372"/>
-      <c r="BB9" s="372"/>
-      <c r="BC9" s="372"/>
-      <c r="BD9" s="372"/>
-      <c r="BE9" s="372"/>
-      <c r="BF9" s="372"/>
-      <c r="BG9" s="372"/>
-      <c r="BH9" s="372"/>
-      <c r="BI9" s="372"/>
-      <c r="BJ9" s="372"/>
-      <c r="BK9" s="372"/>
-      <c r="BL9" s="373"/>
-      <c r="BM9" s="371" t="s">
+      <c r="AZ9" s="373"/>
+      <c r="BA9" s="373"/>
+      <c r="BB9" s="373"/>
+      <c r="BC9" s="373"/>
+      <c r="BD9" s="373"/>
+      <c r="BE9" s="373"/>
+      <c r="BF9" s="373"/>
+      <c r="BG9" s="373"/>
+      <c r="BH9" s="373"/>
+      <c r="BI9" s="373"/>
+      <c r="BJ9" s="373"/>
+      <c r="BK9" s="373"/>
+      <c r="BL9" s="374"/>
+      <c r="BM9" s="372" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="372"/>
-      <c r="BO9" s="372"/>
-      <c r="BP9" s="372"/>
-      <c r="BQ9" s="373"/>
-      <c r="BR9" s="347" t="s">
+      <c r="BN9" s="373"/>
+      <c r="BO9" s="373"/>
+      <c r="BP9" s="373"/>
+      <c r="BQ9" s="374"/>
+      <c r="BR9" s="348" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="347" t="s">
+      <c r="BS9" s="348" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="338"/>
-      <c r="BU9" s="356"/>
+      <c r="BT9" s="339"/>
+      <c r="BU9" s="357"/>
       <c r="BV9" s="22"/>
-      <c r="BW9" s="438"/>
-      <c r="BX9" s="331"/>
-      <c r="BY9" s="332"/>
-      <c r="BZ9" s="332"/>
-      <c r="CA9" s="333"/>
-      <c r="CB9" s="338"/>
+      <c r="BW9" s="439"/>
+      <c r="BX9" s="332"/>
+      <c r="BY9" s="333"/>
+      <c r="BZ9" s="333"/>
+      <c r="CA9" s="334"/>
+      <c r="CB9" s="339"/>
       <c r="CC9" s="445"/>
-      <c r="CD9" s="430"/>
+      <c r="CD9" s="431"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
-    <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="346"/>
-      <c r="B10" s="338"/>
-      <c r="C10" s="338"/>
-      <c r="D10" s="338"/>
-      <c r="E10" s="338"/>
-      <c r="F10" s="338"/>
-      <c r="G10" s="427"/>
-      <c r="H10" s="346"/>
-      <c r="I10" s="346"/>
-      <c r="J10" s="430"/>
-      <c r="K10" s="346"/>
-      <c r="L10" s="346"/>
-      <c r="M10" s="346"/>
-      <c r="N10" s="346"/>
-      <c r="O10" s="346"/>
-      <c r="P10" s="346"/>
-      <c r="Q10" s="346"/>
-      <c r="R10" s="346"/>
-      <c r="S10" s="346"/>
-      <c r="T10" s="346"/>
-      <c r="U10" s="346"/>
-      <c r="V10" s="360"/>
-      <c r="W10" s="361"/>
-      <c r="X10" s="346"/>
-      <c r="Y10" s="338"/>
-      <c r="Z10" s="338"/>
-      <c r="AA10" s="338"/>
-      <c r="AB10" s="338"/>
-      <c r="AC10" s="338"/>
-      <c r="AD10" s="338"/>
-      <c r="AE10" s="338"/>
-      <c r="AF10" s="338"/>
-      <c r="AG10" s="338"/>
-      <c r="AH10" s="338"/>
-      <c r="AI10" s="338"/>
-      <c r="AJ10" s="427"/>
-      <c r="AK10" s="356"/>
-      <c r="AL10" s="427"/>
-      <c r="AM10" s="338"/>
-      <c r="AN10" s="338"/>
-      <c r="AO10" s="338"/>
-      <c r="AP10" s="430"/>
-      <c r="AQ10" s="430"/>
-      <c r="AR10" s="430"/>
-      <c r="AS10" s="430"/>
-      <c r="AT10" s="430"/>
-      <c r="AU10" s="430"/>
-      <c r="AV10" s="338"/>
-      <c r="AW10" s="430"/>
-      <c r="AX10" s="338"/>
+    <row r="10" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="347"/>
+      <c r="B10" s="339"/>
+      <c r="C10" s="339"/>
+      <c r="D10" s="339"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="339"/>
+      <c r="G10" s="428"/>
+      <c r="H10" s="347"/>
+      <c r="I10" s="347"/>
+      <c r="J10" s="431"/>
+      <c r="K10" s="347"/>
+      <c r="L10" s="347"/>
+      <c r="M10" s="347"/>
+      <c r="N10" s="347"/>
+      <c r="O10" s="347"/>
+      <c r="P10" s="347"/>
+      <c r="Q10" s="347"/>
+      <c r="R10" s="347"/>
+      <c r="S10" s="347"/>
+      <c r="T10" s="347"/>
+      <c r="U10" s="347"/>
+      <c r="V10" s="361"/>
+      <c r="W10" s="362"/>
+      <c r="X10" s="347"/>
+      <c r="Y10" s="339"/>
+      <c r="Z10" s="339"/>
+      <c r="AA10" s="339"/>
+      <c r="AB10" s="339"/>
+      <c r="AC10" s="339"/>
+      <c r="AD10" s="339"/>
+      <c r="AE10" s="339"/>
+      <c r="AF10" s="339"/>
+      <c r="AG10" s="339"/>
+      <c r="AH10" s="339"/>
+      <c r="AI10" s="339"/>
+      <c r="AJ10" s="428"/>
+      <c r="AK10" s="357"/>
+      <c r="AL10" s="428"/>
+      <c r="AM10" s="339"/>
+      <c r="AN10" s="339"/>
+      <c r="AO10" s="339"/>
+      <c r="AP10" s="431"/>
+      <c r="AQ10" s="431"/>
+      <c r="AR10" s="431"/>
+      <c r="AS10" s="431"/>
+      <c r="AT10" s="431"/>
+      <c r="AU10" s="431"/>
+      <c r="AV10" s="339"/>
+      <c r="AW10" s="431"/>
+      <c r="AX10" s="339"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8621,578 +8622,578 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="353" t="s">
+      <c r="BB10" s="354" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="435" t="s">
+      <c r="BC10" s="436" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="435" t="s">
+      <c r="BD10" s="436" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="342" t="s">
+      <c r="BE10" s="343" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="342" t="s">
+      <c r="BF10" s="343" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="343" t="s">
+      <c r="BG10" s="344" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="435" t="s">
+      <c r="BH10" s="436" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="436" t="s">
+      <c r="BI10" s="437" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="342" t="s">
+      <c r="BJ10" s="343" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="342" t="s">
+      <c r="BK10" s="343" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="337" t="s">
+      <c r="BL10" s="338" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="435" t="s">
+      <c r="BM10" s="436" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="434" t="s">
+      <c r="BN10" s="435" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="435" t="s">
+      <c r="BO10" s="436" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="434" t="s">
+      <c r="BP10" s="435" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="434" t="s">
+      <c r="BQ10" s="435" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="346"/>
-      <c r="BS10" s="346"/>
-      <c r="BT10" s="338"/>
-      <c r="BU10" s="356"/>
+      <c r="BR10" s="347"/>
+      <c r="BS10" s="347"/>
+      <c r="BT10" s="339"/>
+      <c r="BU10" s="357"/>
       <c r="BV10" s="22"/>
-      <c r="BW10" s="438"/>
-      <c r="BX10" s="334"/>
-      <c r="BY10" s="335"/>
-      <c r="BZ10" s="335"/>
-      <c r="CA10" s="336"/>
-      <c r="CB10" s="338"/>
+      <c r="BW10" s="439"/>
+      <c r="BX10" s="335"/>
+      <c r="BY10" s="336"/>
+      <c r="BZ10" s="336"/>
+      <c r="CA10" s="337"/>
+      <c r="CB10" s="339"/>
       <c r="CC10" s="445"/>
-      <c r="CD10" s="430"/>
-      <c r="CE10" s="319" t="s">
+      <c r="CD10" s="431"/>
+      <c r="CE10" s="320" t="s">
         <v>3</v>
       </c>
       <c r="CH10" s="241"/>
       <c r="CI10" s="241"/>
     </row>
-    <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="344"/>
-      <c r="B11" s="339"/>
-      <c r="C11" s="339"/>
-      <c r="D11" s="339"/>
-      <c r="E11" s="339"/>
-      <c r="F11" s="339"/>
-      <c r="G11" s="428"/>
-      <c r="H11" s="344"/>
-      <c r="I11" s="344"/>
-      <c r="J11" s="431"/>
-      <c r="K11" s="344"/>
-      <c r="L11" s="344"/>
-      <c r="M11" s="344"/>
-      <c r="N11" s="344"/>
-      <c r="O11" s="344"/>
-      <c r="P11" s="344"/>
-      <c r="Q11" s="344"/>
-      <c r="R11" s="344"/>
-      <c r="S11" s="344"/>
-      <c r="T11" s="344"/>
-      <c r="U11" s="344"/>
+    <row r="11" spans="1:87" s="306" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="345"/>
+      <c r="B11" s="340"/>
+      <c r="C11" s="340"/>
+      <c r="D11" s="340"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
+      <c r="G11" s="429"/>
+      <c r="H11" s="345"/>
+      <c r="I11" s="345"/>
+      <c r="J11" s="432"/>
+      <c r="K11" s="345"/>
+      <c r="L11" s="345"/>
+      <c r="M11" s="345"/>
+      <c r="N11" s="345"/>
+      <c r="O11" s="345"/>
+      <c r="P11" s="345"/>
+      <c r="Q11" s="345"/>
+      <c r="R11" s="345"/>
+      <c r="S11" s="345"/>
+      <c r="T11" s="345"/>
+      <c r="U11" s="345"/>
       <c r="V11" s="269" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="269" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="344"/>
-      <c r="Y11" s="339"/>
-      <c r="Z11" s="339"/>
-      <c r="AA11" s="339"/>
-      <c r="AB11" s="339"/>
-      <c r="AC11" s="339"/>
-      <c r="AD11" s="339"/>
-      <c r="AE11" s="339"/>
-      <c r="AF11" s="339"/>
-      <c r="AG11" s="339"/>
-      <c r="AH11" s="339"/>
-      <c r="AI11" s="339"/>
-      <c r="AJ11" s="428"/>
-      <c r="AK11" s="357"/>
-      <c r="AL11" s="428"/>
-      <c r="AM11" s="339"/>
-      <c r="AN11" s="339"/>
-      <c r="AO11" s="339"/>
-      <c r="AP11" s="431"/>
-      <c r="AQ11" s="431"/>
-      <c r="AR11" s="431"/>
-      <c r="AS11" s="431"/>
-      <c r="AT11" s="431"/>
-      <c r="AU11" s="431"/>
-      <c r="AV11" s="339"/>
-      <c r="AW11" s="431"/>
-      <c r="AX11" s="339"/>
-      <c r="AY11" s="320" t="s">
+      <c r="X11" s="345"/>
+      <c r="Y11" s="340"/>
+      <c r="Z11" s="340"/>
+      <c r="AA11" s="340"/>
+      <c r="AB11" s="340"/>
+      <c r="AC11" s="340"/>
+      <c r="AD11" s="340"/>
+      <c r="AE11" s="340"/>
+      <c r="AF11" s="340"/>
+      <c r="AG11" s="340"/>
+      <c r="AH11" s="340"/>
+      <c r="AI11" s="340"/>
+      <c r="AJ11" s="429"/>
+      <c r="AK11" s="358"/>
+      <c r="AL11" s="429"/>
+      <c r="AM11" s="340"/>
+      <c r="AN11" s="340"/>
+      <c r="AO11" s="340"/>
+      <c r="AP11" s="432"/>
+      <c r="AQ11" s="432"/>
+      <c r="AR11" s="432"/>
+      <c r="AS11" s="432"/>
+      <c r="AT11" s="432"/>
+      <c r="AU11" s="432"/>
+      <c r="AV11" s="340"/>
+      <c r="AW11" s="432"/>
+      <c r="AX11" s="340"/>
+      <c r="AY11" s="321" t="s">
         <v>88</v>
       </c>
-      <c r="AZ11" s="320" t="s">
+      <c r="AZ11" s="321" t="s">
         <v>89</v>
       </c>
-      <c r="BA11" s="320" t="s">
+      <c r="BA11" s="321" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="339"/>
-      <c r="BC11" s="431"/>
-      <c r="BD11" s="431"/>
-      <c r="BE11" s="339"/>
-      <c r="BF11" s="339"/>
-      <c r="BG11" s="344"/>
-      <c r="BH11" s="431"/>
-      <c r="BI11" s="428"/>
-      <c r="BJ11" s="339"/>
-      <c r="BK11" s="339"/>
-      <c r="BL11" s="339"/>
-      <c r="BM11" s="431"/>
-      <c r="BN11" s="431"/>
-      <c r="BO11" s="431"/>
-      <c r="BP11" s="431"/>
-      <c r="BQ11" s="431"/>
-      <c r="BR11" s="344"/>
-      <c r="BS11" s="344"/>
-      <c r="BT11" s="339"/>
-      <c r="BU11" s="357"/>
+      <c r="BB11" s="340"/>
+      <c r="BC11" s="432"/>
+      <c r="BD11" s="432"/>
+      <c r="BE11" s="340"/>
+      <c r="BF11" s="340"/>
+      <c r="BG11" s="345"/>
+      <c r="BH11" s="432"/>
+      <c r="BI11" s="429"/>
+      <c r="BJ11" s="340"/>
+      <c r="BK11" s="340"/>
+      <c r="BL11" s="340"/>
+      <c r="BM11" s="432"/>
+      <c r="BN11" s="432"/>
+      <c r="BO11" s="432"/>
+      <c r="BP11" s="432"/>
+      <c r="BQ11" s="432"/>
+      <c r="BR11" s="345"/>
+      <c r="BS11" s="345"/>
+      <c r="BT11" s="340"/>
+      <c r="BU11" s="358"/>
       <c r="BV11" s="22"/>
-      <c r="BW11" s="439"/>
-      <c r="BX11" s="440" t="s">
+      <c r="BW11" s="440"/>
+      <c r="BX11" s="441" t="s">
         <v>91</v>
       </c>
-      <c r="BY11" s="440" t="s">
+      <c r="BY11" s="441" t="s">
         <v>92</v>
       </c>
-      <c r="BZ11" s="440" t="s">
+      <c r="BZ11" s="441" t="s">
         <v>93</v>
       </c>
-      <c r="CA11" s="441" t="s">
+      <c r="CA11" s="270" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="370"/>
+      <c r="CB11" s="371"/>
       <c r="CC11" s="446"/>
       <c r="CD11" s="443"/>
-      <c r="CE11" s="318">
+      <c r="CE11" s="319">
         <v>26</v>
       </c>
-      <c r="CF11" s="306"/>
+      <c r="CF11" s="307"/>
       <c r="CH11" s="241"/>
       <c r="CI11" s="241"/>
     </row>
-    <row r="12" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="307">
+    <row r="12" spans="1:87" s="312" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="308">
         <v>1</v>
       </c>
-      <c r="B12" s="308">
+      <c r="B12" s="309">
         <f>A12+1</f>
         <v>2</v>
       </c>
-      <c r="C12" s="308">
+      <c r="C12" s="309">
         <f>B12+1</f>
         <v>3</v>
       </c>
-      <c r="D12" s="308">
+      <c r="D12" s="309">
         <f>C12+1</f>
         <v>4</v>
       </c>
-      <c r="E12" s="308"/>
-      <c r="F12" s="308">
+      <c r="E12" s="309"/>
+      <c r="F12" s="309">
         <f>D12+1</f>
         <v>5</v>
       </c>
-      <c r="G12" s="308">
+      <c r="G12" s="309">
         <f t="shared" ref="G12:AV12" si="0">F12+1</f>
         <v>6</v>
       </c>
-      <c r="H12" s="308">
+      <c r="H12" s="309">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I12" s="308">
+      <c r="I12" s="309">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J12" s="308">
+      <c r="J12" s="309">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K12" s="308">
+      <c r="K12" s="309">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="308">
+      <c r="L12" s="309">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="M12" s="308">
+      <c r="M12" s="309">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N12" s="308">
+      <c r="N12" s="309">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="O12" s="308">
+      <c r="O12" s="309">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="P12" s="308">
+      <c r="P12" s="309">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q12" s="308">
+      <c r="Q12" s="309">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="R12" s="308">
+      <c r="R12" s="309">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="S12" s="308">
+      <c r="S12" s="309">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T12" s="308">
+      <c r="T12" s="309">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U12" s="308">
+      <c r="U12" s="309">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V12" s="308">
+      <c r="V12" s="309">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W12" s="308">
+      <c r="W12" s="309">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X12" s="308">
+      <c r="X12" s="309">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y12" s="308">
+      <c r="Y12" s="309">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z12" s="308">
+      <c r="Z12" s="309">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA12" s="308">
+      <c r="AA12" s="309">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB12" s="308">
+      <c r="AB12" s="309">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC12" s="308">
+      <c r="AC12" s="309">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD12" s="308">
+      <c r="AD12" s="309">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE12" s="308">
+      <c r="AE12" s="309">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF12" s="308">
+      <c r="AF12" s="309">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG12" s="308">
+      <c r="AG12" s="309">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="AH12" s="308">
+      <c r="AH12" s="309">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="AI12" s="308">
+      <c r="AI12" s="309">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AJ12" s="308">
+      <c r="AJ12" s="309">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="AK12" s="308">
+      <c r="AK12" s="309">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="AL12" s="308">
+      <c r="AL12" s="309">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="AM12" s="308">
+      <c r="AM12" s="309">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="AN12" s="308">
+      <c r="AN12" s="309">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="AO12" s="308">
+      <c r="AO12" s="309">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="AP12" s="308">
+      <c r="AP12" s="309">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="AQ12" s="308">
+      <c r="AQ12" s="309">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="AR12" s="308">
+      <c r="AR12" s="309">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="AS12" s="308">
+      <c r="AS12" s="309">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="AT12" s="308">
+      <c r="AT12" s="309">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="AU12" s="308">
+      <c r="AU12" s="309">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="AV12" s="308">
+      <c r="AV12" s="309">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="AW12" s="308"/>
-      <c r="AX12" s="308"/>
-      <c r="AY12" s="308">
+      <c r="AW12" s="309"/>
+      <c r="AX12" s="309"/>
+      <c r="AY12" s="309">
         <f>AV12+1</f>
         <v>48</v>
       </c>
-      <c r="AZ12" s="308">
+      <c r="AZ12" s="309">
         <f t="shared" ref="AZ12:BE12" si="1">AY12+1</f>
         <v>49</v>
       </c>
-      <c r="BA12" s="308">
+      <c r="BA12" s="309">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="BB12" s="308">
+      <c r="BB12" s="309">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="BC12" s="308">
+      <c r="BC12" s="309">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="BD12" s="308">
+      <c r="BD12" s="309">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="BE12" s="308">
+      <c r="BE12" s="309">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="BF12" s="308"/>
-      <c r="BG12" s="308"/>
-      <c r="BH12" s="308"/>
-      <c r="BI12" s="308"/>
-      <c r="BJ12" s="308"/>
-      <c r="BK12" s="308"/>
-      <c r="BL12" s="308">
+      <c r="BF12" s="309"/>
+      <c r="BG12" s="309"/>
+      <c r="BH12" s="309"/>
+      <c r="BI12" s="309"/>
+      <c r="BJ12" s="309"/>
+      <c r="BK12" s="309"/>
+      <c r="BL12" s="309">
         <f>BE12+1</f>
         <v>55</v>
       </c>
-      <c r="BM12" s="308">
+      <c r="BM12" s="309">
         <f t="shared" ref="BM12:BU12" si="2">BL12+1</f>
         <v>56</v>
       </c>
-      <c r="BN12" s="308">
+      <c r="BN12" s="309">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="BO12" s="308">
+      <c r="BO12" s="309">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="BP12" s="308">
+      <c r="BP12" s="309">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="BQ12" s="308">
+      <c r="BQ12" s="309">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="BR12" s="308">
+      <c r="BR12" s="309">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="BS12" s="308">
+      <c r="BS12" s="309">
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="BT12" s="308">
+      <c r="BT12" s="309">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="BU12" s="308">
+      <c r="BU12" s="309">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="BV12" s="309"/>
-      <c r="BW12" s="310" t="s">
+      <c r="BV12" s="310"/>
+      <c r="BW12" s="311" t="s">
         <v>95</v>
       </c>
-      <c r="BX12" s="308">
+      <c r="BX12" s="309">
         <f t="shared" ref="BX12:CD12" si="3">BW12+1</f>
         <v>66</v>
       </c>
-      <c r="BY12" s="308">
+      <c r="BY12" s="309">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="BZ12" s="308">
+      <c r="BZ12" s="309">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="CA12" s="308">
+      <c r="CA12" s="309">
         <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="CB12" s="308">
+      <c r="CB12" s="309">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="CC12" s="308">
+      <c r="CC12" s="309">
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
-      <c r="CD12" s="308">
+      <c r="CD12" s="309">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="CG12" s="305"/>
+      <c r="CG12" s="306"/>
       <c r="CH12" s="241"/>
       <c r="CI12" s="241"/>
     </row>
-    <row r="13" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="307" t="s">
+    <row r="13" spans="1:87" s="312" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="307" t="s">
+      <c r="B13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="307" t="s">
+      <c r="C13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="308"/>
-      <c r="E13" s="308"/>
-      <c r="F13" s="308"/>
-      <c r="G13" s="307" t="s">
+      <c r="D13" s="309"/>
+      <c r="E13" s="309"/>
+      <c r="F13" s="309"/>
+      <c r="G13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="307" t="s">
+      <c r="H13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="307" t="s">
+      <c r="I13" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="308"/>
-      <c r="K13" s="308"/>
-      <c r="L13" s="308"/>
-      <c r="M13" s="308"/>
-      <c r="N13" s="308"/>
-      <c r="O13" s="308"/>
-      <c r="P13" s="308"/>
-      <c r="Q13" s="308"/>
-      <c r="R13" s="308"/>
-      <c r="S13" s="308"/>
-      <c r="T13" s="308"/>
-      <c r="U13" s="308"/>
-      <c r="V13" s="308"/>
-      <c r="W13" s="308"/>
-      <c r="X13" s="308"/>
-      <c r="Y13" s="308"/>
-      <c r="Z13" s="308"/>
-      <c r="AA13" s="308"/>
-      <c r="AB13" s="308"/>
-      <c r="AC13" s="308"/>
-      <c r="AD13" s="308"/>
-      <c r="AE13" s="308"/>
-      <c r="AF13" s="308"/>
-      <c r="AG13" s="308"/>
-      <c r="AH13" s="308"/>
-      <c r="AI13" s="308"/>
-      <c r="AJ13" s="308"/>
-      <c r="AK13" s="308"/>
-      <c r="AL13" s="308"/>
-      <c r="AM13" s="308"/>
-      <c r="AN13" s="308"/>
-      <c r="AO13" s="308"/>
-      <c r="AP13" s="308"/>
-      <c r="AQ13" s="308"/>
-      <c r="AR13" s="308"/>
-      <c r="AS13" s="308"/>
-      <c r="AT13" s="308"/>
-      <c r="AU13" s="308"/>
-      <c r="AV13" s="308"/>
-      <c r="AW13" s="308"/>
-      <c r="AX13" s="308"/>
-      <c r="AY13" s="308"/>
-      <c r="AZ13" s="308"/>
-      <c r="BA13" s="308"/>
-      <c r="BB13" s="308"/>
-      <c r="BC13" s="308"/>
-      <c r="BD13" s="308"/>
-      <c r="BE13" s="308"/>
-      <c r="BF13" s="308"/>
-      <c r="BG13" s="308"/>
-      <c r="BH13" s="308"/>
-      <c r="BI13" s="308"/>
-      <c r="BJ13" s="308"/>
-      <c r="BK13" s="308"/>
-      <c r="BL13" s="308"/>
-      <c r="BM13" s="308"/>
-      <c r="BN13" s="308"/>
-      <c r="BO13" s="308"/>
-      <c r="BP13" s="308"/>
-      <c r="BQ13" s="308"/>
-      <c r="BR13" s="308"/>
-      <c r="BS13" s="308"/>
-      <c r="BT13" s="308"/>
-      <c r="BU13" s="312"/>
-      <c r="BV13" s="309"/>
-      <c r="BW13" s="310"/>
-      <c r="BX13" s="308"/>
-      <c r="BY13" s="308"/>
-      <c r="BZ13" s="308"/>
-      <c r="CA13" s="308"/>
-      <c r="CB13" s="308"/>
-      <c r="CC13" s="308"/>
-      <c r="CD13" s="308"/>
-      <c r="CG13" s="305"/>
+      <c r="J13" s="309"/>
+      <c r="K13" s="309"/>
+      <c r="L13" s="309"/>
+      <c r="M13" s="309"/>
+      <c r="N13" s="309"/>
+      <c r="O13" s="309"/>
+      <c r="P13" s="309"/>
+      <c r="Q13" s="309"/>
+      <c r="R13" s="309"/>
+      <c r="S13" s="309"/>
+      <c r="T13" s="309"/>
+      <c r="U13" s="309"/>
+      <c r="V13" s="309"/>
+      <c r="W13" s="309"/>
+      <c r="X13" s="309"/>
+      <c r="Y13" s="309"/>
+      <c r="Z13" s="309"/>
+      <c r="AA13" s="309"/>
+      <c r="AB13" s="309"/>
+      <c r="AC13" s="309"/>
+      <c r="AD13" s="309"/>
+      <c r="AE13" s="309"/>
+      <c r="AF13" s="309"/>
+      <c r="AG13" s="309"/>
+      <c r="AH13" s="309"/>
+      <c r="AI13" s="309"/>
+      <c r="AJ13" s="309"/>
+      <c r="AK13" s="309"/>
+      <c r="AL13" s="309"/>
+      <c r="AM13" s="309"/>
+      <c r="AN13" s="309"/>
+      <c r="AO13" s="309"/>
+      <c r="AP13" s="309"/>
+      <c r="AQ13" s="309"/>
+      <c r="AR13" s="309"/>
+      <c r="AS13" s="309"/>
+      <c r="AT13" s="309"/>
+      <c r="AU13" s="309"/>
+      <c r="AV13" s="309"/>
+      <c r="AW13" s="309"/>
+      <c r="AX13" s="309"/>
+      <c r="AY13" s="309"/>
+      <c r="AZ13" s="309"/>
+      <c r="BA13" s="309"/>
+      <c r="BB13" s="309"/>
+      <c r="BC13" s="309"/>
+      <c r="BD13" s="309"/>
+      <c r="BE13" s="309"/>
+      <c r="BF13" s="309"/>
+      <c r="BG13" s="309"/>
+      <c r="BH13" s="309"/>
+      <c r="BI13" s="309"/>
+      <c r="BJ13" s="309"/>
+      <c r="BK13" s="309"/>
+      <c r="BL13" s="309"/>
+      <c r="BM13" s="309"/>
+      <c r="BN13" s="309"/>
+      <c r="BO13" s="309"/>
+      <c r="BP13" s="309"/>
+      <c r="BQ13" s="309"/>
+      <c r="BR13" s="309"/>
+      <c r="BS13" s="309"/>
+      <c r="BT13" s="309"/>
+      <c r="BU13" s="313"/>
+      <c r="BV13" s="310"/>
+      <c r="BW13" s="311"/>
+      <c r="BX13" s="309"/>
+      <c r="BY13" s="309"/>
+      <c r="BZ13" s="309"/>
+      <c r="CA13" s="309"/>
+      <c r="CB13" s="309"/>
+      <c r="CC13" s="309"/>
+      <c r="CD13" s="309"/>
+      <c r="CG13" s="306"/>
       <c r="CH13" s="241"/>
       <c r="CI13" s="241"/>
     </row>
@@ -9216,56 +9217,56 @@
         <v>183399990</v>
       </c>
       <c r="J14" s="94"/>
-      <c r="K14" s="313">
+      <c r="K14" s="314">
         <f t="shared" ref="K14:S14" si="4">SUM(K15:K21)</f>
         <v>166</v>
       </c>
-      <c r="L14" s="313">
+      <c r="L14" s="314">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="M14" s="313">
+      <c r="M14" s="314">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N14" s="313">
+      <c r="N14" s="314">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="O14" s="313">
+      <c r="O14" s="314">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P14" s="313">
+      <c r="P14" s="314">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="Q14" s="313">
+      <c r="Q14" s="314">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="R14" s="313">
+      <c r="R14" s="314">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S14" s="313">
+      <c r="S14" s="314">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="T14" s="313"/>
-      <c r="U14" s="313">
+      <c r="T14" s="314"/>
+      <c r="U14" s="314">
         <f>SUM(U15:U21)</f>
         <v>2</v>
       </c>
-      <c r="V14" s="313">
+      <c r="V14" s="314">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="313">
+      <c r="W14" s="314">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="313">
+      <c r="X14" s="314">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -9395,7 +9396,7 @@
       <c r="BR14" s="94"/>
       <c r="BS14" s="94"/>
       <c r="BT14" s="94"/>
-      <c r="BU14" s="314">
+      <c r="BU14" s="315">
         <f>SUM(BU15:BU21)</f>
         <v>226721558.59230769</v>
       </c>
@@ -9410,241 +9411,241 @@
       <c r="CD14" s="243"/>
     </row>
     <row r="15" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="270">
+      <c r="A15" s="271">
         <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="271">
+      <c r="B15" s="272">
         <v>2405236</v>
       </c>
-      <c r="C15" s="272" t="s">
+      <c r="C15" s="273" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="273" t="s">
+      <c r="D15" s="274" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="274" t="s">
+      <c r="E15" s="275" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="274" t="s">
+      <c r="F15" s="275" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="275">
+      <c r="G15" s="276">
         <v>9520000</v>
       </c>
-      <c r="H15" s="275">
+      <c r="H15" s="276">
         <f t="shared" ref="H15:H21" si="7">+IF(OR(CC15="ĐT PCCC",CC15="ĐP PCCC"),780000,IF(CC15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="275">
+      <c r="I15" s="276">
         <f t="shared" ref="I15:I21" si="8">CB15-BZ15-G15-H15</f>
         <v>53480000</v>
       </c>
-      <c r="J15" s="276">
+      <c r="J15" s="277">
         <v>1</v>
       </c>
-      <c r="K15" s="277">
+      <c r="K15" s="278">
         <v>26</v>
       </c>
-      <c r="L15" s="277">
-        <v>0</v>
-      </c>
-      <c r="M15" s="277">
-        <v>0</v>
-      </c>
-      <c r="N15" s="277">
-        <v>0</v>
-      </c>
-      <c r="O15" s="277">
-        <v>0</v>
-      </c>
-      <c r="P15" s="277">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="277">
-        <v>0</v>
-      </c>
-      <c r="R15" s="277">
-        <v>0</v>
-      </c>
-      <c r="S15" s="277">
-        <v>0</v>
-      </c>
-      <c r="T15" s="277"/>
-      <c r="U15" s="277">
-        <v>0</v>
-      </c>
-      <c r="V15" s="277">
-        <v>0</v>
-      </c>
-      <c r="W15" s="277">
-        <v>0</v>
-      </c>
-      <c r="X15" s="277">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="275">
+      <c r="L15" s="278">
+        <v>0</v>
+      </c>
+      <c r="M15" s="278">
+        <v>0</v>
+      </c>
+      <c r="N15" s="278">
+        <v>0</v>
+      </c>
+      <c r="O15" s="278">
+        <v>0</v>
+      </c>
+      <c r="P15" s="278">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="278">
+        <v>0</v>
+      </c>
+      <c r="R15" s="278">
+        <v>0</v>
+      </c>
+      <c r="S15" s="278">
+        <v>0</v>
+      </c>
+      <c r="T15" s="278"/>
+      <c r="U15" s="278">
+        <v>0</v>
+      </c>
+      <c r="V15" s="278">
+        <v>0</v>
+      </c>
+      <c r="W15" s="278">
+        <v>0</v>
+      </c>
+      <c r="X15" s="278">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="276">
         <f t="shared" ref="Y15:Y21" si="9">G15*(K15+L15)/26</f>
         <v>9520000</v>
       </c>
-      <c r="Z15" s="275">
+      <c r="Z15" s="276">
         <f t="shared" ref="Z15:Z21" si="10">M15*G15/26</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="275">
+      <c r="AA15" s="276">
         <f t="shared" ref="AA15:AA21" si="11">G15*N15/26</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="275">
+      <c r="AB15" s="276">
         <f t="shared" ref="AB15:AB21" si="12">G15*O15/26</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="275">
+      <c r="AC15" s="276">
         <f t="shared" ref="AC15:AC21" si="13">G15*P15*150%/26</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="275">
+      <c r="AD15" s="276">
         <f t="shared" ref="AD15:AD21" si="14">G15*Q15/26*200%</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="275">
+      <c r="AE15" s="276">
         <f t="shared" ref="AE15:AE21" si="15">G15*R15/26*300%</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="275">
+      <c r="AF15" s="276">
         <f>ROUND((G15+H15)/26*S15*30%,0)</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="275">
+      <c r="AG15" s="276">
         <f t="shared" ref="AG15:AG21" si="16">T15*G15/26/8</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="275">
+      <c r="AH15" s="276">
         <f t="shared" ref="AH15:AH21" si="17">CB15/26*U15</f>
         <v>0</v>
       </c>
-      <c r="AI15" s="275">
+      <c r="AI15" s="276">
         <f t="shared" ref="AI15:AI21" si="18">G15*V15/26</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="275"/>
-      <c r="AK15" s="275">
+      <c r="AJ15" s="276"/>
+      <c r="AK15" s="276">
         <f t="shared" ref="AK15:AK21" si="19">BZ15*L15/26</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="275"/>
-      <c r="AM15" s="275">
+      <c r="AL15" s="276"/>
+      <c r="AM15" s="276">
         <f t="shared" ref="AM15:AM21" si="20">X15*CD15</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="275">
+      <c r="AN15" s="276">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="275">
+      <c r="AO15" s="276">
         <f t="shared" ref="AO15:AO21" si="21">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CE$11-K15-L15)/26+(H15+I15)*50%*M15/26+BW15*O15/26-AB15+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CE$11-K15-L15)/26-Y15)+(H15-H15*($CE$11-K15-L15)/26-AN15))</f>
         <v>53480000</v>
       </c>
-      <c r="AP15" s="275"/>
-      <c r="AQ15" s="275"/>
-      <c r="AR15" s="275">
+      <c r="AP15" s="276"/>
+      <c r="AQ15" s="276"/>
+      <c r="AR15" s="276">
         <v>1000000</v>
       </c>
-      <c r="AS15" s="275"/>
-      <c r="AT15" s="275"/>
-      <c r="AU15" s="275"/>
-      <c r="AV15" s="275">
+      <c r="AS15" s="276"/>
+      <c r="AT15" s="276"/>
+      <c r="AU15" s="276"/>
+      <c r="AV15" s="276">
         <f t="shared" ref="AV15:AV21" si="22">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>64000000</v>
       </c>
-      <c r="AW15" s="275"/>
-      <c r="AX15" s="275" t="str">
+      <c r="AW15" s="276"/>
+      <c r="AX15" s="276" t="str">
         <f t="shared" ref="AX15:AX21" si="23">IF(E15="CT","x",0)</f>
         <v>x</v>
       </c>
-      <c r="AY15" s="278">
+      <c r="AY15" s="279">
         <f t="shared" ref="AY15:BA21" si="24">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="278">
+      <c r="AZ15" s="279">
         <f t="shared" si="24"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="278">
+      <c r="BA15" s="279">
         <f t="shared" si="24"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="278">
+      <c r="BB15" s="279">
         <f t="shared" ref="BB15:BB21" si="25">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="278"/>
-      <c r="BD15" s="278"/>
-      <c r="BE15" s="278">
+      <c r="BC15" s="279"/>
+      <c r="BD15" s="279"/>
+      <c r="BE15" s="279">
         <f t="shared" ref="BE15:BE21" si="26">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="278">
+      <c r="BF15" s="279">
         <f>AM15+IF(E15="CT",IF(AR15&gt;=730000,730000,AR15),0)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
         <v>10220500</v>
       </c>
-      <c r="BG15" s="278">
+      <c r="BG15" s="279">
         <f t="shared" ref="BG15:BG21" si="27">AV15-BF15+AW15</f>
         <v>53779500</v>
       </c>
-      <c r="BH15" s="278">
+      <c r="BH15" s="279">
         <v>3</v>
       </c>
-      <c r="BI15" s="278">
+      <c r="BI15" s="279">
         <v>6200000</v>
       </c>
-      <c r="BJ15" s="278">
+      <c r="BJ15" s="279">
         <f>IF(E15="CT",15500000,0)</f>
         <v>15500000</v>
       </c>
-      <c r="BK15" s="278">
+      <c r="BK15" s="279">
         <f t="shared" ref="BK15:BK21" si="28">BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
         <v>18679900</v>
       </c>
-      <c r="BL15" s="279">
+      <c r="BL15" s="280">
         <f t="shared" ref="BL15:BL21" si="29">IF(E15="TV",BK15*10%,IF(BK15&gt;0,ROUND(IF(BK15&gt;=80000000,BK15*35%-9850000,IF(BK15&gt;=52000000,BK15*30%-5850000,IF(BK15&gt;=32000000,BK15*25%-3250000,IF(BK15&gt;=18000000,BK15*20%-1650000,IF(BK15&gt;=10000000,BK15*15%-750000,IF(BK15&gt;5000000,BK15*10%-250000,BK15*5%)))))),0),0))</f>
         <v>2085980</v>
       </c>
-      <c r="BM15" s="278"/>
-      <c r="BN15" s="278"/>
-      <c r="BO15" s="278">
-        <v>0</v>
-      </c>
-      <c r="BP15" s="278"/>
-      <c r="BQ15" s="278"/>
-      <c r="BR15" s="278"/>
-      <c r="BS15" s="278"/>
-      <c r="BT15" s="263"/>
-      <c r="BU15" s="280">
+      <c r="BM15" s="279"/>
+      <c r="BN15" s="279"/>
+      <c r="BO15" s="279">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="279"/>
+      <c r="BQ15" s="279"/>
+      <c r="BR15" s="279"/>
+      <c r="BS15" s="279"/>
+      <c r="BT15" s="447"/>
+      <c r="BU15" s="281">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
         <v>60819220</v>
       </c>
       <c r="BV15" s="252"/>
-      <c r="BW15" s="281">
+      <c r="BW15" s="282">
         <v>60000000</v>
       </c>
-      <c r="BX15" s="279">
-        <v>0</v>
-      </c>
-      <c r="BY15" s="279"/>
-      <c r="BZ15" s="279">
+      <c r="BX15" s="280">
+        <v>0</v>
+      </c>
+      <c r="BY15" s="280"/>
+      <c r="BZ15" s="280">
         <v>200000</v>
       </c>
-      <c r="CA15" s="279">
+      <c r="CA15" s="280">
         <f t="shared" ref="CA15:CA21" si="31">+BW15*5%</f>
         <v>3000000</v>
       </c>
-      <c r="CB15" s="279">
+      <c r="CB15" s="280">
         <f t="shared" ref="CB15:CB21" si="32">SUM(BW15:CA15)</f>
         <v>63200000</v>
       </c>
-      <c r="CC15" s="279"/>
-      <c r="CD15" s="279"/>
+      <c r="CC15" s="280"/>
+      <c r="CD15" s="280"/>
       <c r="CE15" s="253"/>
       <c r="CF15" s="254"/>
       <c r="CG15" s="254"/>
@@ -9835,7 +9836,7 @@
         <v>40832692.307692312</v>
       </c>
       <c r="BH16" s="250"/>
-      <c r="BI16" s="278">
+      <c r="BI16" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ16" s="250">
@@ -10077,7 +10078,7 @@
         <v>35713076.923076928</v>
       </c>
       <c r="BH17" s="250"/>
-      <c r="BI17" s="278">
+      <c r="BI17" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ17" s="250">
@@ -10319,7 +10320,7 @@
         <v>22247115.384615384</v>
       </c>
       <c r="BH18" s="250"/>
-      <c r="BI18" s="278">
+      <c r="BI18" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ18" s="250">
@@ -10561,7 +10562,7 @@
         <v>9879615.3846153859</v>
       </c>
       <c r="BH19" s="250"/>
-      <c r="BI19" s="278">
+      <c r="BI19" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ19" s="250">
@@ -10803,7 +10804,7 @@
         <v>21247500</v>
       </c>
       <c r="BH20" s="250"/>
-      <c r="BI20" s="278">
+      <c r="BI20" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ20" s="250">
@@ -11047,7 +11048,7 @@
         <v>19128270.53846154</v>
       </c>
       <c r="BH21" s="250"/>
-      <c r="BI21" s="278">
+      <c r="BI21" s="279">
         <v>6200000</v>
       </c>
       <c r="BJ21" s="250">
@@ -11123,9 +11124,9 @@
       <c r="T22" s="40"/>
       <c r="U22" s="41"/>
       <c r="V22" s="41"/>
-      <c r="W22" s="315"/>
-      <c r="X22" s="315"/>
-      <c r="AC22" s="316"/>
+      <c r="W22" s="316"/>
+      <c r="X22" s="316"/>
+      <c r="AC22" s="317"/>
       <c r="BL22" s="45"/>
       <c r="BP22" s="45"/>
       <c r="BQ22" s="45"/>
@@ -11218,8 +11219,8 @@
       <c r="R24" s="53"/>
       <c r="U24" s="54"/>
       <c r="V24" s="54"/>
-      <c r="W24" s="317"/>
-      <c r="X24" s="317"/>
+      <c r="W24" s="318"/>
+      <c r="X24" s="318"/>
       <c r="AN24" s="58"/>
       <c r="AV24" s="49"/>
       <c r="AW24" s="49"/>
@@ -11535,87 +11536,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="407"/>
-      <c r="B3" s="395"/>
-      <c r="C3" s="395"/>
-      <c r="D3" s="395"/>
-      <c r="E3" s="395"/>
-      <c r="F3" s="395"/>
-      <c r="G3" s="395"/>
-      <c r="H3" s="395"/>
-      <c r="I3" s="395"/>
-      <c r="J3" s="395"/>
-      <c r="K3" s="395"/>
-      <c r="L3" s="395"/>
-      <c r="M3" s="395"/>
-      <c r="N3" s="395"/>
-      <c r="O3" s="395"/>
-      <c r="P3" s="395"/>
-      <c r="Q3" s="395"/>
-      <c r="R3" s="395"/>
-      <c r="S3" s="395"/>
-      <c r="T3" s="395"/>
-      <c r="U3" s="395"/>
-      <c r="V3" s="395"/>
-      <c r="W3" s="395"/>
-      <c r="X3" s="395"/>
-      <c r="Y3" s="395"/>
-      <c r="Z3" s="395"/>
-      <c r="AA3" s="395"/>
-      <c r="AB3" s="395"/>
-      <c r="AC3" s="395"/>
-      <c r="AD3" s="395"/>
-      <c r="AE3" s="395"/>
-      <c r="AF3" s="395"/>
-      <c r="AG3" s="395"/>
-      <c r="AH3" s="395"/>
-      <c r="AI3" s="395"/>
-      <c r="AJ3" s="395"/>
-      <c r="AK3" s="395"/>
-      <c r="AL3" s="395"/>
-      <c r="AM3" s="395"/>
-      <c r="AN3" s="395"/>
-      <c r="AO3" s="395"/>
-      <c r="AP3" s="395"/>
-      <c r="AQ3" s="395"/>
-      <c r="AR3" s="395"/>
-      <c r="AS3" s="395"/>
-      <c r="AT3" s="395"/>
-      <c r="AU3" s="395"/>
-      <c r="AV3" s="395"/>
-      <c r="AW3" s="395"/>
-      <c r="AX3" s="395"/>
-      <c r="AY3" s="395"/>
-      <c r="AZ3" s="395"/>
-      <c r="BA3" s="395"/>
-      <c r="BB3" s="395"/>
-      <c r="BC3" s="395"/>
-      <c r="BD3" s="395"/>
-      <c r="BE3" s="395"/>
-      <c r="BF3" s="395"/>
-      <c r="BG3" s="395"/>
-      <c r="BH3" s="395"/>
-      <c r="BI3" s="395"/>
-      <c r="BJ3" s="395"/>
-      <c r="BK3" s="395"/>
-      <c r="BL3" s="395"/>
-      <c r="BM3" s="395"/>
-      <c r="BN3" s="395"/>
-      <c r="BO3" s="395"/>
-      <c r="BP3" s="395"/>
-      <c r="BQ3" s="395"/>
-      <c r="BR3" s="395"/>
-      <c r="BS3" s="395"/>
-      <c r="BT3" s="395"/>
-      <c r="BU3" s="395"/>
-      <c r="BW3" s="394" t="s">
+      <c r="A3" s="408"/>
+      <c r="B3" s="396"/>
+      <c r="C3" s="396"/>
+      <c r="D3" s="396"/>
+      <c r="E3" s="396"/>
+      <c r="F3" s="396"/>
+      <c r="G3" s="396"/>
+      <c r="H3" s="396"/>
+      <c r="I3" s="396"/>
+      <c r="J3" s="396"/>
+      <c r="K3" s="396"/>
+      <c r="L3" s="396"/>
+      <c r="M3" s="396"/>
+      <c r="N3" s="396"/>
+      <c r="O3" s="396"/>
+      <c r="P3" s="396"/>
+      <c r="Q3" s="396"/>
+      <c r="R3" s="396"/>
+      <c r="S3" s="396"/>
+      <c r="T3" s="396"/>
+      <c r="U3" s="396"/>
+      <c r="V3" s="396"/>
+      <c r="W3" s="396"/>
+      <c r="X3" s="396"/>
+      <c r="Y3" s="396"/>
+      <c r="Z3" s="396"/>
+      <c r="AA3" s="396"/>
+      <c r="AB3" s="396"/>
+      <c r="AC3" s="396"/>
+      <c r="AD3" s="396"/>
+      <c r="AE3" s="396"/>
+      <c r="AF3" s="396"/>
+      <c r="AG3" s="396"/>
+      <c r="AH3" s="396"/>
+      <c r="AI3" s="396"/>
+      <c r="AJ3" s="396"/>
+      <c r="AK3" s="396"/>
+      <c r="AL3" s="396"/>
+      <c r="AM3" s="396"/>
+      <c r="AN3" s="396"/>
+      <c r="AO3" s="396"/>
+      <c r="AP3" s="396"/>
+      <c r="AQ3" s="396"/>
+      <c r="AR3" s="396"/>
+      <c r="AS3" s="396"/>
+      <c r="AT3" s="396"/>
+      <c r="AU3" s="396"/>
+      <c r="AV3" s="396"/>
+      <c r="AW3" s="396"/>
+      <c r="AX3" s="396"/>
+      <c r="AY3" s="396"/>
+      <c r="AZ3" s="396"/>
+      <c r="BA3" s="396"/>
+      <c r="BB3" s="396"/>
+      <c r="BC3" s="396"/>
+      <c r="BD3" s="396"/>
+      <c r="BE3" s="396"/>
+      <c r="BF3" s="396"/>
+      <c r="BG3" s="396"/>
+      <c r="BH3" s="396"/>
+      <c r="BI3" s="396"/>
+      <c r="BJ3" s="396"/>
+      <c r="BK3" s="396"/>
+      <c r="BL3" s="396"/>
+      <c r="BM3" s="396"/>
+      <c r="BN3" s="396"/>
+      <c r="BO3" s="396"/>
+      <c r="BP3" s="396"/>
+      <c r="BQ3" s="396"/>
+      <c r="BR3" s="396"/>
+      <c r="BS3" s="396"/>
+      <c r="BT3" s="396"/>
+      <c r="BU3" s="396"/>
+      <c r="BW3" s="395" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="395"/>
-      <c r="BY3" s="395"/>
-      <c r="BZ3" s="395"/>
-      <c r="CA3" s="395"/>
-      <c r="CB3" s="395"/>
+      <c r="BX3" s="396"/>
+      <c r="BY3" s="396"/>
+      <c r="BZ3" s="396"/>
+      <c r="CA3" s="396"/>
+      <c r="CB3" s="396"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11698,364 +11699,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="395"/>
-      <c r="BX4" s="395"/>
-      <c r="BY4" s="395"/>
-      <c r="BZ4" s="395"/>
-      <c r="CA4" s="395"/>
-      <c r="CB4" s="395"/>
+      <c r="BW4" s="396"/>
+      <c r="BX4" s="396"/>
+      <c r="BY4" s="396"/>
+      <c r="BZ4" s="396"/>
+      <c r="CA4" s="396"/>
+      <c r="CB4" s="396"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="382" t="s">
+      <c r="A5" s="383" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="393" t="s">
+      <c r="B5" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="381" t="s">
+      <c r="C5" s="382" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="388" t="s">
+      <c r="D5" s="389" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="388" t="s">
+      <c r="E5" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="381" t="s">
+      <c r="F5" s="382" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="381" t="s">
+      <c r="G5" s="382" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="337" t="s">
+      <c r="H5" s="338" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="337" t="s">
+      <c r="I5" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="381" t="s">
+      <c r="J5" s="382" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="386" t="s">
+      <c r="K5" s="387" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="378"/>
-      <c r="M5" s="378"/>
-      <c r="N5" s="378"/>
-      <c r="O5" s="378"/>
-      <c r="P5" s="378"/>
-      <c r="Q5" s="378"/>
-      <c r="R5" s="378"/>
-      <c r="S5" s="378"/>
-      <c r="T5" s="378"/>
-      <c r="U5" s="378"/>
-      <c r="V5" s="378"/>
-      <c r="W5" s="378"/>
-      <c r="X5" s="378"/>
-      <c r="Y5" s="381" t="s">
+      <c r="L5" s="379"/>
+      <c r="M5" s="379"/>
+      <c r="N5" s="379"/>
+      <c r="O5" s="379"/>
+      <c r="P5" s="379"/>
+      <c r="Q5" s="379"/>
+      <c r="R5" s="379"/>
+      <c r="S5" s="379"/>
+      <c r="T5" s="379"/>
+      <c r="U5" s="379"/>
+      <c r="V5" s="379"/>
+      <c r="W5" s="379"/>
+      <c r="X5" s="379"/>
+      <c r="Y5" s="382" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="378"/>
-      <c r="AA5" s="378"/>
-      <c r="AB5" s="378"/>
-      <c r="AC5" s="378"/>
-      <c r="AD5" s="378"/>
-      <c r="AE5" s="378"/>
-      <c r="AF5" s="378"/>
-      <c r="AG5" s="378"/>
-      <c r="AH5" s="378"/>
-      <c r="AI5" s="378"/>
-      <c r="AJ5" s="378"/>
-      <c r="AK5" s="378"/>
-      <c r="AL5" s="378"/>
-      <c r="AM5" s="378"/>
-      <c r="AN5" s="378"/>
-      <c r="AO5" s="379"/>
-      <c r="AP5" s="381" t="s">
+      <c r="Z5" s="379"/>
+      <c r="AA5" s="379"/>
+      <c r="AB5" s="379"/>
+      <c r="AC5" s="379"/>
+      <c r="AD5" s="379"/>
+      <c r="AE5" s="379"/>
+      <c r="AF5" s="379"/>
+      <c r="AG5" s="379"/>
+      <c r="AH5" s="379"/>
+      <c r="AI5" s="379"/>
+      <c r="AJ5" s="379"/>
+      <c r="AK5" s="379"/>
+      <c r="AL5" s="379"/>
+      <c r="AM5" s="379"/>
+      <c r="AN5" s="379"/>
+      <c r="AO5" s="380"/>
+      <c r="AP5" s="382" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="381" t="s">
+      <c r="AQ5" s="382" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="381" t="s">
+      <c r="AR5" s="382" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="381" t="s">
+      <c r="AS5" s="382" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="381" t="s">
+      <c r="AT5" s="382" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="381" t="s">
+      <c r="AU5" s="382" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="381" t="s">
+      <c r="AV5" s="382" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="381" t="s">
+      <c r="AW5" s="382" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="381" t="s">
+      <c r="AX5" s="382" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="377" t="s">
+      <c r="AY5" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="378"/>
-      <c r="BA5" s="378"/>
-      <c r="BB5" s="378"/>
-      <c r="BC5" s="378"/>
-      <c r="BD5" s="378"/>
-      <c r="BE5" s="378"/>
-      <c r="BF5" s="378"/>
-      <c r="BG5" s="378"/>
-      <c r="BH5" s="378"/>
-      <c r="BI5" s="378"/>
-      <c r="BJ5" s="378"/>
-      <c r="BK5" s="378"/>
-      <c r="BL5" s="378"/>
-      <c r="BM5" s="378"/>
-      <c r="BN5" s="378"/>
-      <c r="BO5" s="378"/>
-      <c r="BP5" s="378"/>
-      <c r="BQ5" s="379"/>
-      <c r="BR5" s="398" t="s">
+      <c r="AZ5" s="379"/>
+      <c r="BA5" s="379"/>
+      <c r="BB5" s="379"/>
+      <c r="BC5" s="379"/>
+      <c r="BD5" s="379"/>
+      <c r="BE5" s="379"/>
+      <c r="BF5" s="379"/>
+      <c r="BG5" s="379"/>
+      <c r="BH5" s="379"/>
+      <c r="BI5" s="379"/>
+      <c r="BJ5" s="379"/>
+      <c r="BK5" s="379"/>
+      <c r="BL5" s="379"/>
+      <c r="BM5" s="379"/>
+      <c r="BN5" s="379"/>
+      <c r="BO5" s="379"/>
+      <c r="BP5" s="379"/>
+      <c r="BQ5" s="380"/>
+      <c r="BR5" s="399" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="391"/>
-      <c r="BT5" s="377" t="s">
+      <c r="BS5" s="392"/>
+      <c r="BT5" s="378" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="409" t="s">
+      <c r="BU5" s="410" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="410" t="s">
+      <c r="BW5" s="411" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="399" t="s">
+      <c r="BX5" s="400" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="400"/>
-      <c r="BZ5" s="400"/>
-      <c r="CA5" s="391"/>
-      <c r="CB5" s="411" t="s">
+      <c r="BY5" s="401"/>
+      <c r="BZ5" s="401"/>
+      <c r="CA5" s="392"/>
+      <c r="CB5" s="412" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="396" t="s">
+      <c r="CC5" s="397" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="396" t="s">
+      <c r="CD5" s="397" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="375"/>
-      <c r="B6" s="375"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="375"/>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
-      <c r="G6" s="375"/>
-      <c r="H6" s="375"/>
-      <c r="I6" s="375"/>
-      <c r="J6" s="375"/>
-      <c r="K6" s="389" t="s">
+      <c r="A6" s="376"/>
+      <c r="B6" s="376"/>
+      <c r="C6" s="376"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="376"/>
+      <c r="F6" s="376"/>
+      <c r="G6" s="376"/>
+      <c r="H6" s="376"/>
+      <c r="I6" s="376"/>
+      <c r="J6" s="376"/>
+      <c r="K6" s="390" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="389" t="s">
+      <c r="L6" s="390" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="389" t="s">
+      <c r="M6" s="390" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="389" t="s">
+      <c r="N6" s="390" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="389" t="s">
+      <c r="O6" s="390" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="389" t="s">
+      <c r="P6" s="390" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="389" t="s">
+      <c r="Q6" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="389" t="s">
+      <c r="R6" s="390" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="389" t="s">
+      <c r="S6" s="390" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="389" t="s">
+      <c r="T6" s="390" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="389" t="s">
+      <c r="U6" s="390" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="390" t="s">
+      <c r="V6" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="391"/>
-      <c r="X6" s="389" t="s">
+      <c r="W6" s="392"/>
+      <c r="X6" s="390" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="381" t="s">
+      <c r="Y6" s="382" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="381" t="s">
+      <c r="Z6" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="381" t="s">
+      <c r="AA6" s="382" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="381" t="s">
+      <c r="AB6" s="382" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="337" t="s">
+      <c r="AC6" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="337" t="s">
+      <c r="AD6" s="338" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="337" t="s">
+      <c r="AE6" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="337" t="s">
+      <c r="AF6" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="381" t="s">
+      <c r="AG6" s="382" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="337" t="s">
+      <c r="AH6" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="337" t="s">
+      <c r="AI6" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="381" t="s">
+      <c r="AJ6" s="382" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="383" t="s">
+      <c r="AK6" s="384" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="381" t="s">
+      <c r="AL6" s="382" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="381" t="s">
+      <c r="AM6" s="382" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="387" t="s">
+      <c r="AN6" s="388" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="381" t="s">
+      <c r="AO6" s="382" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="375"/>
-      <c r="AQ6" s="375"/>
-      <c r="AR6" s="375"/>
-      <c r="AS6" s="375"/>
-      <c r="AT6" s="375"/>
-      <c r="AU6" s="375"/>
-      <c r="AV6" s="375"/>
-      <c r="AW6" s="375"/>
-      <c r="AX6" s="375"/>
-      <c r="AY6" s="377" t="s">
+      <c r="AP6" s="376"/>
+      <c r="AQ6" s="376"/>
+      <c r="AR6" s="376"/>
+      <c r="AS6" s="376"/>
+      <c r="AT6" s="376"/>
+      <c r="AU6" s="376"/>
+      <c r="AV6" s="376"/>
+      <c r="AW6" s="376"/>
+      <c r="AX6" s="376"/>
+      <c r="AY6" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="378"/>
-      <c r="BA6" s="378"/>
-      <c r="BB6" s="378"/>
-      <c r="BC6" s="378"/>
-      <c r="BD6" s="378"/>
-      <c r="BE6" s="378"/>
-      <c r="BF6" s="378"/>
-      <c r="BG6" s="378"/>
-      <c r="BH6" s="378"/>
-      <c r="BI6" s="378"/>
-      <c r="BJ6" s="378"/>
-      <c r="BK6" s="378"/>
-      <c r="BL6" s="379"/>
-      <c r="BM6" s="377" t="s">
+      <c r="AZ6" s="379"/>
+      <c r="BA6" s="379"/>
+      <c r="BB6" s="379"/>
+      <c r="BC6" s="379"/>
+      <c r="BD6" s="379"/>
+      <c r="BE6" s="379"/>
+      <c r="BF6" s="379"/>
+      <c r="BG6" s="379"/>
+      <c r="BH6" s="379"/>
+      <c r="BI6" s="379"/>
+      <c r="BJ6" s="379"/>
+      <c r="BK6" s="379"/>
+      <c r="BL6" s="380"/>
+      <c r="BM6" s="378" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="378"/>
-      <c r="BO6" s="378"/>
-      <c r="BP6" s="378"/>
-      <c r="BQ6" s="379"/>
-      <c r="BR6" s="374" t="s">
+      <c r="BN6" s="379"/>
+      <c r="BO6" s="379"/>
+      <c r="BP6" s="379"/>
+      <c r="BQ6" s="380"/>
+      <c r="BR6" s="375" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="374" t="s">
+      <c r="BS6" s="375" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="375"/>
-      <c r="BU6" s="384"/>
-      <c r="BW6" s="402"/>
-      <c r="BX6" s="384"/>
-      <c r="BY6" s="401"/>
-      <c r="BZ6" s="401"/>
-      <c r="CA6" s="402"/>
-      <c r="CB6" s="375"/>
-      <c r="CC6" s="375"/>
-      <c r="CD6" s="375"/>
+      <c r="BT6" s="376"/>
+      <c r="BU6" s="385"/>
+      <c r="BW6" s="403"/>
+      <c r="BX6" s="385"/>
+      <c r="BY6" s="402"/>
+      <c r="BZ6" s="402"/>
+      <c r="CA6" s="403"/>
+      <c r="CB6" s="376"/>
+      <c r="CC6" s="376"/>
+      <c r="CD6" s="376"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="375"/>
-      <c r="B7" s="375"/>
-      <c r="C7" s="375"/>
-      <c r="D7" s="375"/>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
-      <c r="G7" s="375"/>
-      <c r="H7" s="375"/>
-      <c r="I7" s="375"/>
-      <c r="J7" s="375"/>
-      <c r="K7" s="375"/>
-      <c r="L7" s="375"/>
-      <c r="M7" s="375"/>
-      <c r="N7" s="375"/>
-      <c r="O7" s="375"/>
-      <c r="P7" s="375"/>
-      <c r="Q7" s="375"/>
-      <c r="R7" s="375"/>
-      <c r="S7" s="375"/>
-      <c r="T7" s="375"/>
-      <c r="U7" s="375"/>
-      <c r="V7" s="385"/>
-      <c r="W7" s="392"/>
-      <c r="X7" s="375"/>
-      <c r="Y7" s="375"/>
-      <c r="Z7" s="375"/>
-      <c r="AA7" s="375"/>
-      <c r="AB7" s="375"/>
-      <c r="AC7" s="375"/>
-      <c r="AD7" s="375"/>
-      <c r="AE7" s="375"/>
-      <c r="AF7" s="375"/>
-      <c r="AG7" s="375"/>
-      <c r="AH7" s="375"/>
-      <c r="AI7" s="375"/>
-      <c r="AJ7" s="375"/>
-      <c r="AK7" s="384"/>
-      <c r="AL7" s="375"/>
-      <c r="AM7" s="375"/>
-      <c r="AN7" s="375"/>
-      <c r="AO7" s="375"/>
-      <c r="AP7" s="375"/>
-      <c r="AQ7" s="375"/>
-      <c r="AR7" s="375"/>
-      <c r="AS7" s="375"/>
-      <c r="AT7" s="375"/>
-      <c r="AU7" s="375"/>
-      <c r="AV7" s="375"/>
-      <c r="AW7" s="375"/>
-      <c r="AX7" s="375"/>
+      <c r="A7" s="376"/>
+      <c r="B7" s="376"/>
+      <c r="C7" s="376"/>
+      <c r="D7" s="376"/>
+      <c r="E7" s="376"/>
+      <c r="F7" s="376"/>
+      <c r="G7" s="376"/>
+      <c r="H7" s="376"/>
+      <c r="I7" s="376"/>
+      <c r="J7" s="376"/>
+      <c r="K7" s="376"/>
+      <c r="L7" s="376"/>
+      <c r="M7" s="376"/>
+      <c r="N7" s="376"/>
+      <c r="O7" s="376"/>
+      <c r="P7" s="376"/>
+      <c r="Q7" s="376"/>
+      <c r="R7" s="376"/>
+      <c r="S7" s="376"/>
+      <c r="T7" s="376"/>
+      <c r="U7" s="376"/>
+      <c r="V7" s="386"/>
+      <c r="W7" s="393"/>
+      <c r="X7" s="376"/>
+      <c r="Y7" s="376"/>
+      <c r="Z7" s="376"/>
+      <c r="AA7" s="376"/>
+      <c r="AB7" s="376"/>
+      <c r="AC7" s="376"/>
+      <c r="AD7" s="376"/>
+      <c r="AE7" s="376"/>
+      <c r="AF7" s="376"/>
+      <c r="AG7" s="376"/>
+      <c r="AH7" s="376"/>
+      <c r="AI7" s="376"/>
+      <c r="AJ7" s="376"/>
+      <c r="AK7" s="385"/>
+      <c r="AL7" s="376"/>
+      <c r="AM7" s="376"/>
+      <c r="AN7" s="376"/>
+      <c r="AO7" s="376"/>
+      <c r="AP7" s="376"/>
+      <c r="AQ7" s="376"/>
+      <c r="AR7" s="376"/>
+      <c r="AS7" s="376"/>
+      <c r="AT7" s="376"/>
+      <c r="AU7" s="376"/>
+      <c r="AV7" s="376"/>
+      <c r="AW7" s="376"/>
+      <c r="AX7" s="376"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12065,124 +12066,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="377" t="s">
+      <c r="BB7" s="378" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="380" t="s">
+      <c r="BC7" s="381" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="380" t="s">
+      <c r="BD7" s="381" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="406" t="s">
+      <c r="BE7" s="407" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="380" t="s">
+      <c r="BF7" s="381" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="380" t="s">
+      <c r="BG7" s="381" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="380" t="s">
+      <c r="BH7" s="381" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="380" t="s">
+      <c r="BI7" s="381" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="380" t="s">
+      <c r="BJ7" s="381" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="380" t="s">
+      <c r="BK7" s="381" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="408" t="s">
+      <c r="BL7" s="409" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="380" t="s">
+      <c r="BM7" s="381" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="377" t="s">
+      <c r="BN7" s="378" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="380" t="s">
+      <c r="BO7" s="381" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="377" t="s">
+      <c r="BP7" s="378" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="377" t="s">
+      <c r="BQ7" s="378" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="375"/>
-      <c r="BS7" s="375"/>
-      <c r="BT7" s="375"/>
-      <c r="BU7" s="384"/>
-      <c r="BW7" s="402"/>
-      <c r="BX7" s="403"/>
-      <c r="BY7" s="404"/>
-      <c r="BZ7" s="404"/>
-      <c r="CA7" s="405"/>
-      <c r="CB7" s="375"/>
-      <c r="CC7" s="375"/>
-      <c r="CD7" s="375"/>
+      <c r="BR7" s="376"/>
+      <c r="BS7" s="376"/>
+      <c r="BT7" s="376"/>
+      <c r="BU7" s="385"/>
+      <c r="BW7" s="403"/>
+      <c r="BX7" s="404"/>
+      <c r="BY7" s="405"/>
+      <c r="BZ7" s="405"/>
+      <c r="CA7" s="406"/>
+      <c r="CB7" s="376"/>
+      <c r="CC7" s="376"/>
+      <c r="CD7" s="376"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="376"/>
-      <c r="B8" s="376"/>
-      <c r="C8" s="376"/>
-      <c r="D8" s="376"/>
-      <c r="E8" s="376"/>
-      <c r="F8" s="376"/>
-      <c r="G8" s="376"/>
-      <c r="H8" s="376"/>
-      <c r="I8" s="376"/>
-      <c r="J8" s="376"/>
-      <c r="K8" s="376"/>
-      <c r="L8" s="376"/>
-      <c r="M8" s="376"/>
-      <c r="N8" s="376"/>
-      <c r="O8" s="376"/>
-      <c r="P8" s="376"/>
-      <c r="Q8" s="376"/>
-      <c r="R8" s="376"/>
-      <c r="S8" s="376"/>
-      <c r="T8" s="376"/>
-      <c r="U8" s="376"/>
+      <c r="A8" s="377"/>
+      <c r="B8" s="377"/>
+      <c r="C8" s="377"/>
+      <c r="D8" s="377"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
+      <c r="G8" s="377"/>
+      <c r="H8" s="377"/>
+      <c r="I8" s="377"/>
+      <c r="J8" s="377"/>
+      <c r="K8" s="377"/>
+      <c r="L8" s="377"/>
+      <c r="M8" s="377"/>
+      <c r="N8" s="377"/>
+      <c r="O8" s="377"/>
+      <c r="P8" s="377"/>
+      <c r="Q8" s="377"/>
+      <c r="R8" s="377"/>
+      <c r="S8" s="377"/>
+      <c r="T8" s="377"/>
+      <c r="U8" s="377"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="376"/>
-      <c r="Y8" s="376"/>
-      <c r="Z8" s="376"/>
-      <c r="AA8" s="376"/>
-      <c r="AB8" s="376"/>
-      <c r="AC8" s="376"/>
-      <c r="AD8" s="376"/>
-      <c r="AE8" s="376"/>
-      <c r="AF8" s="376"/>
-      <c r="AG8" s="376"/>
-      <c r="AH8" s="376"/>
-      <c r="AI8" s="376"/>
-      <c r="AJ8" s="376"/>
-      <c r="AK8" s="385"/>
-      <c r="AL8" s="376"/>
-      <c r="AM8" s="376"/>
-      <c r="AN8" s="376"/>
-      <c r="AO8" s="376"/>
-      <c r="AP8" s="376"/>
-      <c r="AQ8" s="376"/>
-      <c r="AR8" s="376"/>
-      <c r="AS8" s="376"/>
-      <c r="AT8" s="376"/>
-      <c r="AU8" s="376"/>
-      <c r="AV8" s="376"/>
-      <c r="AW8" s="376"/>
-      <c r="AX8" s="376"/>
+      <c r="X8" s="377"/>
+      <c r="Y8" s="377"/>
+      <c r="Z8" s="377"/>
+      <c r="AA8" s="377"/>
+      <c r="AB8" s="377"/>
+      <c r="AC8" s="377"/>
+      <c r="AD8" s="377"/>
+      <c r="AE8" s="377"/>
+      <c r="AF8" s="377"/>
+      <c r="AG8" s="377"/>
+      <c r="AH8" s="377"/>
+      <c r="AI8" s="377"/>
+      <c r="AJ8" s="377"/>
+      <c r="AK8" s="386"/>
+      <c r="AL8" s="377"/>
+      <c r="AM8" s="377"/>
+      <c r="AN8" s="377"/>
+      <c r="AO8" s="377"/>
+      <c r="AP8" s="377"/>
+      <c r="AQ8" s="377"/>
+      <c r="AR8" s="377"/>
+      <c r="AS8" s="377"/>
+      <c r="AT8" s="377"/>
+      <c r="AU8" s="377"/>
+      <c r="AV8" s="377"/>
+      <c r="AW8" s="377"/>
+      <c r="AX8" s="377"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12192,27 +12193,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="376"/>
-      <c r="BC8" s="376"/>
-      <c r="BD8" s="376"/>
-      <c r="BE8" s="376"/>
-      <c r="BF8" s="376"/>
-      <c r="BG8" s="376"/>
-      <c r="BH8" s="376"/>
-      <c r="BI8" s="376"/>
-      <c r="BJ8" s="376"/>
-      <c r="BK8" s="376"/>
-      <c r="BL8" s="376"/>
-      <c r="BM8" s="376"/>
-      <c r="BN8" s="376"/>
-      <c r="BO8" s="376"/>
-      <c r="BP8" s="376"/>
-      <c r="BQ8" s="376"/>
-      <c r="BR8" s="376"/>
-      <c r="BS8" s="376"/>
-      <c r="BT8" s="376"/>
-      <c r="BU8" s="385"/>
-      <c r="BW8" s="405"/>
+      <c r="BB8" s="377"/>
+      <c r="BC8" s="377"/>
+      <c r="BD8" s="377"/>
+      <c r="BE8" s="377"/>
+      <c r="BF8" s="377"/>
+      <c r="BG8" s="377"/>
+      <c r="BH8" s="377"/>
+      <c r="BI8" s="377"/>
+      <c r="BJ8" s="377"/>
+      <c r="BK8" s="377"/>
+      <c r="BL8" s="377"/>
+      <c r="BM8" s="377"/>
+      <c r="BN8" s="377"/>
+      <c r="BO8" s="377"/>
+      <c r="BP8" s="377"/>
+      <c r="BQ8" s="377"/>
+      <c r="BR8" s="377"/>
+      <c r="BS8" s="377"/>
+      <c r="BT8" s="377"/>
+      <c r="BU8" s="386"/>
+      <c r="BW8" s="406"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12225,9 +12226,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="397"/>
-      <c r="CC8" s="397"/>
-      <c r="CD8" s="397"/>
+      <c r="CB8" s="398"/>
+      <c r="CC8" s="398"/>
+      <c r="CD8" s="398"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14994,88 +14995,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="422"/>
-      <c r="B3" s="421"/>
-      <c r="C3" s="421"/>
-      <c r="D3" s="421"/>
-      <c r="E3" s="421"/>
-      <c r="F3" s="421"/>
-      <c r="G3" s="421"/>
-      <c r="H3" s="421"/>
-      <c r="I3" s="421"/>
-      <c r="J3" s="421"/>
-      <c r="K3" s="421"/>
-      <c r="L3" s="421"/>
-      <c r="M3" s="421"/>
-      <c r="N3" s="421"/>
-      <c r="O3" s="421"/>
-      <c r="P3" s="421"/>
-      <c r="Q3" s="421"/>
-      <c r="R3" s="421"/>
-      <c r="S3" s="421"/>
-      <c r="T3" s="421"/>
-      <c r="U3" s="421"/>
-      <c r="V3" s="421"/>
-      <c r="W3" s="421"/>
-      <c r="X3" s="421"/>
-      <c r="Y3" s="421"/>
-      <c r="Z3" s="421"/>
-      <c r="AA3" s="421"/>
-      <c r="AB3" s="421"/>
-      <c r="AC3" s="421"/>
-      <c r="AD3" s="421"/>
-      <c r="AE3" s="421"/>
-      <c r="AF3" s="421"/>
-      <c r="AG3" s="421"/>
-      <c r="AH3" s="421"/>
-      <c r="AI3" s="421"/>
-      <c r="AJ3" s="421"/>
-      <c r="AK3" s="421"/>
-      <c r="AL3" s="421"/>
-      <c r="AM3" s="421"/>
-      <c r="AN3" s="421"/>
-      <c r="AO3" s="421"/>
-      <c r="AP3" s="421"/>
-      <c r="AQ3" s="421"/>
-      <c r="AR3" s="421"/>
-      <c r="AS3" s="421"/>
-      <c r="AT3" s="421"/>
-      <c r="AU3" s="421"/>
-      <c r="AV3" s="421"/>
-      <c r="AW3" s="421"/>
-      <c r="AX3" s="421"/>
-      <c r="AY3" s="421"/>
-      <c r="AZ3" s="421"/>
-      <c r="BA3" s="421"/>
-      <c r="BB3" s="421"/>
-      <c r="BC3" s="421"/>
-      <c r="BD3" s="421"/>
-      <c r="BE3" s="421"/>
-      <c r="BF3" s="421"/>
-      <c r="BG3" s="421"/>
-      <c r="BH3" s="421"/>
-      <c r="BI3" s="421"/>
-      <c r="BJ3" s="421"/>
-      <c r="BK3" s="421"/>
-      <c r="BL3" s="421"/>
-      <c r="BM3" s="421"/>
-      <c r="BN3" s="421"/>
-      <c r="BO3" s="421"/>
-      <c r="BP3" s="421"/>
-      <c r="BQ3" s="421"/>
-      <c r="BR3" s="421"/>
-      <c r="BS3" s="421"/>
-      <c r="BT3" s="421"/>
-      <c r="BU3" s="421"/>
+      <c r="A3" s="423"/>
+      <c r="B3" s="422"/>
+      <c r="C3" s="422"/>
+      <c r="D3" s="422"/>
+      <c r="E3" s="422"/>
+      <c r="F3" s="422"/>
+      <c r="G3" s="422"/>
+      <c r="H3" s="422"/>
+      <c r="I3" s="422"/>
+      <c r="J3" s="422"/>
+      <c r="K3" s="422"/>
+      <c r="L3" s="422"/>
+      <c r="M3" s="422"/>
+      <c r="N3" s="422"/>
+      <c r="O3" s="422"/>
+      <c r="P3" s="422"/>
+      <c r="Q3" s="422"/>
+      <c r="R3" s="422"/>
+      <c r="S3" s="422"/>
+      <c r="T3" s="422"/>
+      <c r="U3" s="422"/>
+      <c r="V3" s="422"/>
+      <c r="W3" s="422"/>
+      <c r="X3" s="422"/>
+      <c r="Y3" s="422"/>
+      <c r="Z3" s="422"/>
+      <c r="AA3" s="422"/>
+      <c r="AB3" s="422"/>
+      <c r="AC3" s="422"/>
+      <c r="AD3" s="422"/>
+      <c r="AE3" s="422"/>
+      <c r="AF3" s="422"/>
+      <c r="AG3" s="422"/>
+      <c r="AH3" s="422"/>
+      <c r="AI3" s="422"/>
+      <c r="AJ3" s="422"/>
+      <c r="AK3" s="422"/>
+      <c r="AL3" s="422"/>
+      <c r="AM3" s="422"/>
+      <c r="AN3" s="422"/>
+      <c r="AO3" s="422"/>
+      <c r="AP3" s="422"/>
+      <c r="AQ3" s="422"/>
+      <c r="AR3" s="422"/>
+      <c r="AS3" s="422"/>
+      <c r="AT3" s="422"/>
+      <c r="AU3" s="422"/>
+      <c r="AV3" s="422"/>
+      <c r="AW3" s="422"/>
+      <c r="AX3" s="422"/>
+      <c r="AY3" s="422"/>
+      <c r="AZ3" s="422"/>
+      <c r="BA3" s="422"/>
+      <c r="BB3" s="422"/>
+      <c r="BC3" s="422"/>
+      <c r="BD3" s="422"/>
+      <c r="BE3" s="422"/>
+      <c r="BF3" s="422"/>
+      <c r="BG3" s="422"/>
+      <c r="BH3" s="422"/>
+      <c r="BI3" s="422"/>
+      <c r="BJ3" s="422"/>
+      <c r="BK3" s="422"/>
+      <c r="BL3" s="422"/>
+      <c r="BM3" s="422"/>
+      <c r="BN3" s="422"/>
+      <c r="BO3" s="422"/>
+      <c r="BP3" s="422"/>
+      <c r="BQ3" s="422"/>
+      <c r="BR3" s="422"/>
+      <c r="BS3" s="422"/>
+      <c r="BT3" s="422"/>
+      <c r="BU3" s="422"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="420" t="s">
+      <c r="BW3" s="421" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="421"/>
-      <c r="BY3" s="421"/>
-      <c r="BZ3" s="421"/>
-      <c r="CA3" s="421"/>
-      <c r="CB3" s="421"/>
+      <c r="BX3" s="422"/>
+      <c r="BY3" s="422"/>
+      <c r="BZ3" s="422"/>
+      <c r="CA3" s="422"/>
+      <c r="CB3" s="422"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15159,12 +15160,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="421"/>
-      <c r="BX4" s="421"/>
-      <c r="BY4" s="421"/>
-      <c r="BZ4" s="421"/>
-      <c r="CA4" s="421"/>
-      <c r="CB4" s="421"/>
+      <c r="BW4" s="422"/>
+      <c r="BX4" s="422"/>
+      <c r="BY4" s="422"/>
+      <c r="BZ4" s="422"/>
+      <c r="CA4" s="422"/>
+      <c r="CB4" s="422"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15242,12 +15243,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="351"/>
-      <c r="BX5" s="351"/>
-      <c r="BY5" s="351"/>
-      <c r="BZ5" s="351"/>
-      <c r="CA5" s="351"/>
-      <c r="CB5" s="351"/>
+      <c r="BW5" s="352"/>
+      <c r="BX5" s="352"/>
+      <c r="BY5" s="352"/>
+      <c r="BZ5" s="352"/>
+      <c r="CA5" s="352"/>
+      <c r="CB5" s="352"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15325,12 +15326,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="351"/>
-      <c r="BX6" s="351"/>
-      <c r="BY6" s="351"/>
-      <c r="BZ6" s="351"/>
-      <c r="CA6" s="351"/>
-      <c r="CB6" s="351"/>
+      <c r="BW6" s="352"/>
+      <c r="BX6" s="352"/>
+      <c r="BY6" s="352"/>
+      <c r="BZ6" s="352"/>
+      <c r="CA6" s="352"/>
+      <c r="CB6" s="352"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15418,358 +15419,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="382" t="s">
+      <c r="A8" s="383" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="393" t="s">
+      <c r="B8" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="381" t="s">
+      <c r="C8" s="382" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="388" t="s">
+      <c r="D8" s="389" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="388" t="s">
+      <c r="E8" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="418" t="s">
+      <c r="F8" s="419" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="415" t="s">
+      <c r="G8" s="416" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="366" t="s">
+      <c r="H8" s="367" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="366" t="s">
+      <c r="I8" s="367" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="415" t="s">
+      <c r="J8" s="416" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="419" t="s">
+      <c r="K8" s="420" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="378"/>
-      <c r="M8" s="378"/>
-      <c r="N8" s="378"/>
-      <c r="O8" s="378"/>
-      <c r="P8" s="378"/>
-      <c r="Q8" s="378"/>
-      <c r="R8" s="378"/>
-      <c r="S8" s="378"/>
-      <c r="T8" s="378"/>
-      <c r="U8" s="378"/>
-      <c r="V8" s="378"/>
-      <c r="W8" s="378"/>
-      <c r="X8" s="378"/>
-      <c r="Y8" s="415" t="s">
+      <c r="L8" s="379"/>
+      <c r="M8" s="379"/>
+      <c r="N8" s="379"/>
+      <c r="O8" s="379"/>
+      <c r="P8" s="379"/>
+      <c r="Q8" s="379"/>
+      <c r="R8" s="379"/>
+      <c r="S8" s="379"/>
+      <c r="T8" s="379"/>
+      <c r="U8" s="379"/>
+      <c r="V8" s="379"/>
+      <c r="W8" s="379"/>
+      <c r="X8" s="379"/>
+      <c r="Y8" s="416" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="378"/>
-      <c r="AA8" s="378"/>
-      <c r="AB8" s="378"/>
-      <c r="AC8" s="378"/>
-      <c r="AD8" s="378"/>
-      <c r="AE8" s="378"/>
-      <c r="AF8" s="378"/>
-      <c r="AG8" s="378"/>
-      <c r="AH8" s="378"/>
-      <c r="AI8" s="378"/>
-      <c r="AJ8" s="378"/>
-      <c r="AK8" s="378"/>
-      <c r="AL8" s="378"/>
-      <c r="AM8" s="378"/>
-      <c r="AN8" s="378"/>
-      <c r="AO8" s="379"/>
-      <c r="AP8" s="415" t="s">
+      <c r="Z8" s="379"/>
+      <c r="AA8" s="379"/>
+      <c r="AB8" s="379"/>
+      <c r="AC8" s="379"/>
+      <c r="AD8" s="379"/>
+      <c r="AE8" s="379"/>
+      <c r="AF8" s="379"/>
+      <c r="AG8" s="379"/>
+      <c r="AH8" s="379"/>
+      <c r="AI8" s="379"/>
+      <c r="AJ8" s="379"/>
+      <c r="AK8" s="379"/>
+      <c r="AL8" s="379"/>
+      <c r="AM8" s="379"/>
+      <c r="AN8" s="379"/>
+      <c r="AO8" s="380"/>
+      <c r="AP8" s="416" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="415" t="s">
+      <c r="AQ8" s="416" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="415" t="s">
+      <c r="AR8" s="416" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="415" t="s">
+      <c r="AS8" s="416" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="415" t="s">
+      <c r="AT8" s="416" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="415" t="s">
+      <c r="AU8" s="416" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="381" t="s">
+      <c r="AV8" s="382" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="381" t="s">
+      <c r="AW8" s="382" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="381" t="s">
+      <c r="AX8" s="382" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="377" t="s">
+      <c r="AY8" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="378"/>
-      <c r="BA8" s="378"/>
-      <c r="BB8" s="378"/>
-      <c r="BC8" s="378"/>
-      <c r="BD8" s="378"/>
-      <c r="BE8" s="378"/>
-      <c r="BF8" s="378"/>
-      <c r="BG8" s="378"/>
-      <c r="BH8" s="378"/>
-      <c r="BI8" s="378"/>
-      <c r="BJ8" s="378"/>
-      <c r="BK8" s="378"/>
-      <c r="BL8" s="378"/>
-      <c r="BM8" s="378"/>
-      <c r="BN8" s="378"/>
-      <c r="BO8" s="378"/>
-      <c r="BP8" s="379"/>
-      <c r="BQ8" s="398" t="s">
+      <c r="AZ8" s="379"/>
+      <c r="BA8" s="379"/>
+      <c r="BB8" s="379"/>
+      <c r="BC8" s="379"/>
+      <c r="BD8" s="379"/>
+      <c r="BE8" s="379"/>
+      <c r="BF8" s="379"/>
+      <c r="BG8" s="379"/>
+      <c r="BH8" s="379"/>
+      <c r="BI8" s="379"/>
+      <c r="BJ8" s="379"/>
+      <c r="BK8" s="379"/>
+      <c r="BL8" s="379"/>
+      <c r="BM8" s="379"/>
+      <c r="BN8" s="379"/>
+      <c r="BO8" s="379"/>
+      <c r="BP8" s="380"/>
+      <c r="BQ8" s="399" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="391"/>
-      <c r="BS8" s="377" t="s">
+      <c r="BR8" s="392"/>
+      <c r="BS8" s="378" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="377" t="s">
+      <c r="BT8" s="378" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="409" t="s">
+      <c r="BU8" s="410" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="410" t="s">
+      <c r="BW8" s="411" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="399" t="s">
+      <c r="BX8" s="400" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="400"/>
-      <c r="BZ8" s="400"/>
-      <c r="CA8" s="391"/>
-      <c r="CB8" s="411" t="s">
+      <c r="BY8" s="401"/>
+      <c r="BZ8" s="401"/>
+      <c r="CA8" s="392"/>
+      <c r="CB8" s="412" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="396" t="s">
+      <c r="CC8" s="397" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="396" t="s">
+      <c r="CD8" s="397" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="375"/>
-      <c r="B9" s="375"/>
-      <c r="C9" s="375"/>
-      <c r="D9" s="375"/>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
-      <c r="G9" s="375"/>
-      <c r="H9" s="375"/>
-      <c r="I9" s="375"/>
-      <c r="J9" s="375"/>
-      <c r="K9" s="412" t="s">
+      <c r="A9" s="376"/>
+      <c r="B9" s="376"/>
+      <c r="C9" s="376"/>
+      <c r="D9" s="376"/>
+      <c r="E9" s="376"/>
+      <c r="F9" s="376"/>
+      <c r="G9" s="376"/>
+      <c r="H9" s="376"/>
+      <c r="I9" s="376"/>
+      <c r="J9" s="376"/>
+      <c r="K9" s="413" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="412" t="s">
+      <c r="L9" s="413" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="412" t="s">
+      <c r="M9" s="413" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="412" t="s">
+      <c r="N9" s="413" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="412" t="s">
+      <c r="O9" s="413" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="412" t="s">
+      <c r="P9" s="413" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="412" t="s">
+      <c r="Q9" s="413" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="412" t="s">
+      <c r="R9" s="413" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="412" t="s">
+      <c r="S9" s="413" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="412" t="s">
+      <c r="T9" s="413" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="412" t="s">
+      <c r="U9" s="413" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="424" t="s">
+      <c r="V9" s="425" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="391"/>
-      <c r="X9" s="412" t="s">
+      <c r="W9" s="392"/>
+      <c r="X9" s="413" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="414" t="s">
+      <c r="Y9" s="415" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="414" t="s">
+      <c r="Z9" s="415" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="414" t="s">
+      <c r="AA9" s="415" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="414" t="s">
+      <c r="AB9" s="415" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="340" t="s">
+      <c r="AC9" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="340" t="s">
+      <c r="AD9" s="341" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="340" t="s">
+      <c r="AE9" s="341" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="340" t="s">
+      <c r="AF9" s="341" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="414" t="s">
+      <c r="AG9" s="415" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="340" t="s">
+      <c r="AH9" s="341" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="340" t="s">
+      <c r="AI9" s="341" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="414" t="s">
+      <c r="AJ9" s="415" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="383" t="s">
+      <c r="AK9" s="384" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="381" t="s">
+      <c r="AL9" s="382" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="414" t="s">
+      <c r="AM9" s="415" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="387" t="s">
+      <c r="AN9" s="388" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="381" t="s">
+      <c r="AO9" s="382" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="375"/>
-      <c r="AQ9" s="375"/>
-      <c r="AR9" s="375"/>
-      <c r="AS9" s="375"/>
-      <c r="AT9" s="375"/>
-      <c r="AU9" s="375"/>
-      <c r="AV9" s="375"/>
-      <c r="AW9" s="375"/>
-      <c r="AX9" s="375"/>
-      <c r="AY9" s="377" t="s">
+      <c r="AP9" s="376"/>
+      <c r="AQ9" s="376"/>
+      <c r="AR9" s="376"/>
+      <c r="AS9" s="376"/>
+      <c r="AT9" s="376"/>
+      <c r="AU9" s="376"/>
+      <c r="AV9" s="376"/>
+      <c r="AW9" s="376"/>
+      <c r="AX9" s="376"/>
+      <c r="AY9" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="378"/>
-      <c r="BA9" s="378"/>
-      <c r="BB9" s="378"/>
-      <c r="BC9" s="378"/>
-      <c r="BD9" s="378"/>
-      <c r="BE9" s="378"/>
-      <c r="BF9" s="378"/>
-      <c r="BG9" s="378"/>
-      <c r="BH9" s="378"/>
-      <c r="BI9" s="378"/>
-      <c r="BJ9" s="379"/>
-      <c r="BK9" s="377" t="s">
+      <c r="AZ9" s="379"/>
+      <c r="BA9" s="379"/>
+      <c r="BB9" s="379"/>
+      <c r="BC9" s="379"/>
+      <c r="BD9" s="379"/>
+      <c r="BE9" s="379"/>
+      <c r="BF9" s="379"/>
+      <c r="BG9" s="379"/>
+      <c r="BH9" s="379"/>
+      <c r="BI9" s="379"/>
+      <c r="BJ9" s="380"/>
+      <c r="BK9" s="378" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="378"/>
-      <c r="BM9" s="378"/>
-      <c r="BN9" s="378"/>
-      <c r="BO9" s="378"/>
-      <c r="BP9" s="379"/>
-      <c r="BQ9" s="374" t="s">
+      <c r="BL9" s="379"/>
+      <c r="BM9" s="379"/>
+      <c r="BN9" s="379"/>
+      <c r="BO9" s="379"/>
+      <c r="BP9" s="380"/>
+      <c r="BQ9" s="375" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="374" t="s">
+      <c r="BR9" s="375" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="375"/>
-      <c r="BT9" s="375"/>
-      <c r="BU9" s="384"/>
+      <c r="BS9" s="376"/>
+      <c r="BT9" s="376"/>
+      <c r="BU9" s="385"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="402"/>
-      <c r="BX9" s="384"/>
-      <c r="BY9" s="416"/>
-      <c r="BZ9" s="416"/>
-      <c r="CA9" s="402"/>
-      <c r="CB9" s="375"/>
-      <c r="CC9" s="375"/>
-      <c r="CD9" s="375"/>
+      <c r="BW9" s="403"/>
+      <c r="BX9" s="385"/>
+      <c r="BY9" s="417"/>
+      <c r="BZ9" s="417"/>
+      <c r="CA9" s="403"/>
+      <c r="CB9" s="376"/>
+      <c r="CC9" s="376"/>
+      <c r="CD9" s="376"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="375"/>
-      <c r="B10" s="375"/>
-      <c r="C10" s="375"/>
-      <c r="D10" s="375"/>
-      <c r="E10" s="375"/>
-      <c r="F10" s="375"/>
-      <c r="G10" s="375"/>
-      <c r="H10" s="375"/>
-      <c r="I10" s="375"/>
-      <c r="J10" s="375"/>
-      <c r="K10" s="375"/>
-      <c r="L10" s="375"/>
-      <c r="M10" s="375"/>
-      <c r="N10" s="375"/>
-      <c r="O10" s="375"/>
-      <c r="P10" s="375"/>
-      <c r="Q10" s="375"/>
-      <c r="R10" s="375"/>
-      <c r="S10" s="375"/>
-      <c r="T10" s="375"/>
-      <c r="U10" s="375"/>
-      <c r="V10" s="385"/>
-      <c r="W10" s="392"/>
-      <c r="X10" s="375"/>
-      <c r="Y10" s="375"/>
-      <c r="Z10" s="375"/>
-      <c r="AA10" s="375"/>
-      <c r="AB10" s="375"/>
-      <c r="AC10" s="375"/>
-      <c r="AD10" s="375"/>
-      <c r="AE10" s="375"/>
-      <c r="AF10" s="375"/>
-      <c r="AG10" s="375"/>
-      <c r="AH10" s="375"/>
-      <c r="AI10" s="375"/>
-      <c r="AJ10" s="375"/>
-      <c r="AK10" s="384"/>
-      <c r="AL10" s="375"/>
-      <c r="AM10" s="375"/>
-      <c r="AN10" s="375"/>
-      <c r="AO10" s="375"/>
-      <c r="AP10" s="375"/>
-      <c r="AQ10" s="375"/>
-      <c r="AR10" s="375"/>
-      <c r="AS10" s="375"/>
-      <c r="AT10" s="375"/>
-      <c r="AU10" s="375"/>
-      <c r="AV10" s="375"/>
-      <c r="AW10" s="375"/>
-      <c r="AX10" s="375"/>
+      <c r="A10" s="376"/>
+      <c r="B10" s="376"/>
+      <c r="C10" s="376"/>
+      <c r="D10" s="376"/>
+      <c r="E10" s="376"/>
+      <c r="F10" s="376"/>
+      <c r="G10" s="376"/>
+      <c r="H10" s="376"/>
+      <c r="I10" s="376"/>
+      <c r="J10" s="376"/>
+      <c r="K10" s="376"/>
+      <c r="L10" s="376"/>
+      <c r="M10" s="376"/>
+      <c r="N10" s="376"/>
+      <c r="O10" s="376"/>
+      <c r="P10" s="376"/>
+      <c r="Q10" s="376"/>
+      <c r="R10" s="376"/>
+      <c r="S10" s="376"/>
+      <c r="T10" s="376"/>
+      <c r="U10" s="376"/>
+      <c r="V10" s="386"/>
+      <c r="W10" s="393"/>
+      <c r="X10" s="376"/>
+      <c r="Y10" s="376"/>
+      <c r="Z10" s="376"/>
+      <c r="AA10" s="376"/>
+      <c r="AB10" s="376"/>
+      <c r="AC10" s="376"/>
+      <c r="AD10" s="376"/>
+      <c r="AE10" s="376"/>
+      <c r="AF10" s="376"/>
+      <c r="AG10" s="376"/>
+      <c r="AH10" s="376"/>
+      <c r="AI10" s="376"/>
+      <c r="AJ10" s="376"/>
+      <c r="AK10" s="385"/>
+      <c r="AL10" s="376"/>
+      <c r="AM10" s="376"/>
+      <c r="AN10" s="376"/>
+      <c r="AO10" s="376"/>
+      <c r="AP10" s="376"/>
+      <c r="AQ10" s="376"/>
+      <c r="AR10" s="376"/>
+      <c r="AS10" s="376"/>
+      <c r="AT10" s="376"/>
+      <c r="AU10" s="376"/>
+      <c r="AV10" s="376"/>
+      <c r="AW10" s="376"/>
+      <c r="AX10" s="376"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15779,123 +15780,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="423" t="s">
+      <c r="BB10" s="424" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="413" t="s">
+      <c r="BC10" s="414" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="413" t="s">
+      <c r="BD10" s="414" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="413" t="s">
+      <c r="BE10" s="414" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="413" t="s">
+      <c r="BF10" s="414" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="413" t="s">
+      <c r="BG10" s="414" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="413" t="s">
+      <c r="BH10" s="414" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="413" t="s">
+      <c r="BI10" s="414" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="425" t="s">
+      <c r="BJ10" s="426" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="413" t="s">
+      <c r="BK10" s="414" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="417" t="s">
+      <c r="BL10" s="418" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="413" t="s">
+      <c r="BM10" s="414" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="417" t="s">
+      <c r="BN10" s="418" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="417" t="s">
+      <c r="BO10" s="418" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="377" t="s">
+      <c r="BP10" s="378" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="375"/>
-      <c r="BR10" s="375"/>
-      <c r="BS10" s="375"/>
-      <c r="BT10" s="375"/>
-      <c r="BU10" s="384"/>
+      <c r="BQ10" s="376"/>
+      <c r="BR10" s="376"/>
+      <c r="BS10" s="376"/>
+      <c r="BT10" s="376"/>
+      <c r="BU10" s="385"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="402"/>
-      <c r="BX10" s="403"/>
-      <c r="BY10" s="404"/>
-      <c r="BZ10" s="404"/>
-      <c r="CA10" s="405"/>
-      <c r="CB10" s="375"/>
-      <c r="CC10" s="375"/>
-      <c r="CD10" s="375"/>
+      <c r="BW10" s="403"/>
+      <c r="BX10" s="404"/>
+      <c r="BY10" s="405"/>
+      <c r="BZ10" s="405"/>
+      <c r="CA10" s="406"/>
+      <c r="CB10" s="376"/>
+      <c r="CC10" s="376"/>
+      <c r="CD10" s="376"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="376"/>
-      <c r="B11" s="376"/>
-      <c r="C11" s="376"/>
-      <c r="D11" s="376"/>
-      <c r="E11" s="376"/>
-      <c r="F11" s="376"/>
-      <c r="G11" s="376"/>
-      <c r="H11" s="376"/>
-      <c r="I11" s="376"/>
-      <c r="J11" s="376"/>
-      <c r="K11" s="376"/>
-      <c r="L11" s="376"/>
-      <c r="M11" s="376"/>
-      <c r="N11" s="376"/>
-      <c r="O11" s="376"/>
-      <c r="P11" s="376"/>
-      <c r="Q11" s="376"/>
-      <c r="R11" s="376"/>
-      <c r="S11" s="376"/>
-      <c r="T11" s="376"/>
-      <c r="U11" s="376"/>
+      <c r="A11" s="377"/>
+      <c r="B11" s="377"/>
+      <c r="C11" s="377"/>
+      <c r="D11" s="377"/>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
+      <c r="G11" s="377"/>
+      <c r="H11" s="377"/>
+      <c r="I11" s="377"/>
+      <c r="J11" s="377"/>
+      <c r="K11" s="377"/>
+      <c r="L11" s="377"/>
+      <c r="M11" s="377"/>
+      <c r="N11" s="377"/>
+      <c r="O11" s="377"/>
+      <c r="P11" s="377"/>
+      <c r="Q11" s="377"/>
+      <c r="R11" s="377"/>
+      <c r="S11" s="377"/>
+      <c r="T11" s="377"/>
+      <c r="U11" s="377"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="376"/>
-      <c r="Y11" s="376"/>
-      <c r="Z11" s="376"/>
-      <c r="AA11" s="376"/>
-      <c r="AB11" s="376"/>
-      <c r="AC11" s="376"/>
-      <c r="AD11" s="376"/>
-      <c r="AE11" s="376"/>
-      <c r="AF11" s="376"/>
-      <c r="AG11" s="376"/>
-      <c r="AH11" s="376"/>
-      <c r="AI11" s="376"/>
-      <c r="AJ11" s="376"/>
-      <c r="AK11" s="385"/>
-      <c r="AL11" s="376"/>
-      <c r="AM11" s="376"/>
-      <c r="AN11" s="376"/>
-      <c r="AO11" s="376"/>
-      <c r="AP11" s="376"/>
-      <c r="AQ11" s="376"/>
-      <c r="AR11" s="376"/>
-      <c r="AS11" s="376"/>
-      <c r="AT11" s="376"/>
-      <c r="AU11" s="376"/>
-      <c r="AV11" s="376"/>
-      <c r="AW11" s="376"/>
-      <c r="AX11" s="376"/>
+      <c r="X11" s="377"/>
+      <c r="Y11" s="377"/>
+      <c r="Z11" s="377"/>
+      <c r="AA11" s="377"/>
+      <c r="AB11" s="377"/>
+      <c r="AC11" s="377"/>
+      <c r="AD11" s="377"/>
+      <c r="AE11" s="377"/>
+      <c r="AF11" s="377"/>
+      <c r="AG11" s="377"/>
+      <c r="AH11" s="377"/>
+      <c r="AI11" s="377"/>
+      <c r="AJ11" s="377"/>
+      <c r="AK11" s="386"/>
+      <c r="AL11" s="377"/>
+      <c r="AM11" s="377"/>
+      <c r="AN11" s="377"/>
+      <c r="AO11" s="377"/>
+      <c r="AP11" s="377"/>
+      <c r="AQ11" s="377"/>
+      <c r="AR11" s="377"/>
+      <c r="AS11" s="377"/>
+      <c r="AT11" s="377"/>
+      <c r="AU11" s="377"/>
+      <c r="AV11" s="377"/>
+      <c r="AW11" s="377"/>
+      <c r="AX11" s="377"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15905,28 +15906,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="376"/>
-      <c r="BC11" s="376"/>
-      <c r="BD11" s="376"/>
-      <c r="BE11" s="376"/>
-      <c r="BF11" s="376"/>
-      <c r="BG11" s="376"/>
-      <c r="BH11" s="376"/>
-      <c r="BI11" s="376"/>
-      <c r="BJ11" s="376"/>
-      <c r="BK11" s="376"/>
-      <c r="BL11" s="376"/>
-      <c r="BM11" s="376"/>
-      <c r="BN11" s="376"/>
-      <c r="BO11" s="376"/>
-      <c r="BP11" s="376"/>
-      <c r="BQ11" s="376"/>
-      <c r="BR11" s="376"/>
-      <c r="BS11" s="376"/>
-      <c r="BT11" s="376"/>
-      <c r="BU11" s="385"/>
+      <c r="BB11" s="377"/>
+      <c r="BC11" s="377"/>
+      <c r="BD11" s="377"/>
+      <c r="BE11" s="377"/>
+      <c r="BF11" s="377"/>
+      <c r="BG11" s="377"/>
+      <c r="BH11" s="377"/>
+      <c r="BI11" s="377"/>
+      <c r="BJ11" s="377"/>
+      <c r="BK11" s="377"/>
+      <c r="BL11" s="377"/>
+      <c r="BM11" s="377"/>
+      <c r="BN11" s="377"/>
+      <c r="BO11" s="377"/>
+      <c r="BP11" s="377"/>
+      <c r="BQ11" s="377"/>
+      <c r="BR11" s="377"/>
+      <c r="BS11" s="377"/>
+      <c r="BT11" s="377"/>
+      <c r="BU11" s="386"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="405"/>
+      <c r="BW11" s="406"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15939,9 +15940,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="397"/>
-      <c r="CC11" s="397"/>
-      <c r="CD11" s="397"/>
+      <c r="CB11" s="398"/>
+      <c r="CC11" s="398"/>
+      <c r="CD11" s="398"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18653,87 +18654,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="407"/>
-      <c r="B3" s="395"/>
-      <c r="C3" s="395"/>
-      <c r="D3" s="395"/>
-      <c r="E3" s="395"/>
-      <c r="F3" s="395"/>
-      <c r="G3" s="395"/>
-      <c r="H3" s="395"/>
-      <c r="I3" s="395"/>
-      <c r="J3" s="395"/>
-      <c r="K3" s="395"/>
-      <c r="L3" s="395"/>
-      <c r="M3" s="395"/>
-      <c r="N3" s="395"/>
-      <c r="O3" s="395"/>
-      <c r="P3" s="395"/>
-      <c r="Q3" s="395"/>
-      <c r="R3" s="395"/>
-      <c r="S3" s="395"/>
-      <c r="T3" s="395"/>
-      <c r="U3" s="395"/>
-      <c r="V3" s="395"/>
-      <c r="W3" s="395"/>
-      <c r="X3" s="395"/>
-      <c r="Y3" s="395"/>
-      <c r="Z3" s="395"/>
-      <c r="AA3" s="395"/>
-      <c r="AB3" s="395"/>
-      <c r="AC3" s="395"/>
-      <c r="AD3" s="395"/>
-      <c r="AE3" s="395"/>
-      <c r="AF3" s="395"/>
-      <c r="AG3" s="395"/>
-      <c r="AH3" s="395"/>
-      <c r="AI3" s="395"/>
-      <c r="AJ3" s="395"/>
-      <c r="AK3" s="395"/>
-      <c r="AL3" s="395"/>
-      <c r="AM3" s="395"/>
-      <c r="AN3" s="395"/>
-      <c r="AO3" s="395"/>
-      <c r="AP3" s="395"/>
-      <c r="AQ3" s="395"/>
-      <c r="AR3" s="395"/>
-      <c r="AS3" s="395"/>
-      <c r="AT3" s="395"/>
-      <c r="AU3" s="395"/>
-      <c r="AV3" s="395"/>
-      <c r="AW3" s="395"/>
-      <c r="AX3" s="395"/>
-      <c r="AY3" s="395"/>
-      <c r="AZ3" s="395"/>
-      <c r="BA3" s="395"/>
-      <c r="BB3" s="395"/>
-      <c r="BC3" s="395"/>
-      <c r="BD3" s="395"/>
-      <c r="BE3" s="395"/>
-      <c r="BF3" s="395"/>
-      <c r="BG3" s="395"/>
-      <c r="BH3" s="395"/>
-      <c r="BI3" s="395"/>
-      <c r="BJ3" s="395"/>
-      <c r="BK3" s="395"/>
-      <c r="BL3" s="395"/>
-      <c r="BM3" s="395"/>
-      <c r="BN3" s="395"/>
-      <c r="BO3" s="395"/>
-      <c r="BP3" s="395"/>
-      <c r="BQ3" s="395"/>
-      <c r="BR3" s="395"/>
-      <c r="BS3" s="395"/>
-      <c r="BT3" s="395"/>
-      <c r="BU3" s="395"/>
-      <c r="BW3" s="394" t="s">
+      <c r="A3" s="408"/>
+      <c r="B3" s="396"/>
+      <c r="C3" s="396"/>
+      <c r="D3" s="396"/>
+      <c r="E3" s="396"/>
+      <c r="F3" s="396"/>
+      <c r="G3" s="396"/>
+      <c r="H3" s="396"/>
+      <c r="I3" s="396"/>
+      <c r="J3" s="396"/>
+      <c r="K3" s="396"/>
+      <c r="L3" s="396"/>
+      <c r="M3" s="396"/>
+      <c r="N3" s="396"/>
+      <c r="O3" s="396"/>
+      <c r="P3" s="396"/>
+      <c r="Q3" s="396"/>
+      <c r="R3" s="396"/>
+      <c r="S3" s="396"/>
+      <c r="T3" s="396"/>
+      <c r="U3" s="396"/>
+      <c r="V3" s="396"/>
+      <c r="W3" s="396"/>
+      <c r="X3" s="396"/>
+      <c r="Y3" s="396"/>
+      <c r="Z3" s="396"/>
+      <c r="AA3" s="396"/>
+      <c r="AB3" s="396"/>
+      <c r="AC3" s="396"/>
+      <c r="AD3" s="396"/>
+      <c r="AE3" s="396"/>
+      <c r="AF3" s="396"/>
+      <c r="AG3" s="396"/>
+      <c r="AH3" s="396"/>
+      <c r="AI3" s="396"/>
+      <c r="AJ3" s="396"/>
+      <c r="AK3" s="396"/>
+      <c r="AL3" s="396"/>
+      <c r="AM3" s="396"/>
+      <c r="AN3" s="396"/>
+      <c r="AO3" s="396"/>
+      <c r="AP3" s="396"/>
+      <c r="AQ3" s="396"/>
+      <c r="AR3" s="396"/>
+      <c r="AS3" s="396"/>
+      <c r="AT3" s="396"/>
+      <c r="AU3" s="396"/>
+      <c r="AV3" s="396"/>
+      <c r="AW3" s="396"/>
+      <c r="AX3" s="396"/>
+      <c r="AY3" s="396"/>
+      <c r="AZ3" s="396"/>
+      <c r="BA3" s="396"/>
+      <c r="BB3" s="396"/>
+      <c r="BC3" s="396"/>
+      <c r="BD3" s="396"/>
+      <c r="BE3" s="396"/>
+      <c r="BF3" s="396"/>
+      <c r="BG3" s="396"/>
+      <c r="BH3" s="396"/>
+      <c r="BI3" s="396"/>
+      <c r="BJ3" s="396"/>
+      <c r="BK3" s="396"/>
+      <c r="BL3" s="396"/>
+      <c r="BM3" s="396"/>
+      <c r="BN3" s="396"/>
+      <c r="BO3" s="396"/>
+      <c r="BP3" s="396"/>
+      <c r="BQ3" s="396"/>
+      <c r="BR3" s="396"/>
+      <c r="BS3" s="396"/>
+      <c r="BT3" s="396"/>
+      <c r="BU3" s="396"/>
+      <c r="BW3" s="395" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="395"/>
-      <c r="BY3" s="395"/>
-      <c r="BZ3" s="395"/>
-      <c r="CA3" s="395"/>
-      <c r="CB3" s="395"/>
+      <c r="BX3" s="396"/>
+      <c r="BY3" s="396"/>
+      <c r="BZ3" s="396"/>
+      <c r="CA3" s="396"/>
+      <c r="CB3" s="396"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18816,366 +18817,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="395"/>
-      <c r="BX4" s="395"/>
-      <c r="BY4" s="395"/>
-      <c r="BZ4" s="395"/>
-      <c r="CA4" s="395"/>
-      <c r="CB4" s="395"/>
+      <c r="BW4" s="396"/>
+      <c r="BX4" s="396"/>
+      <c r="BY4" s="396"/>
+      <c r="BZ4" s="396"/>
+      <c r="CA4" s="396"/>
+      <c r="CB4" s="396"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="382" t="s">
+      <c r="A5" s="383" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="393" t="s">
+      <c r="B5" s="394" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="381" t="s">
+      <c r="C5" s="382" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="388" t="s">
+      <c r="D5" s="389" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="388" t="s">
+      <c r="E5" s="389" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="418" t="s">
+      <c r="F5" s="419" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="381" t="s">
+      <c r="G5" s="382" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="337" t="s">
+      <c r="H5" s="338" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="337" t="s">
+      <c r="I5" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="381" t="s">
+      <c r="J5" s="382" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="386" t="s">
+      <c r="K5" s="387" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="378"/>
-      <c r="M5" s="378"/>
-      <c r="N5" s="378"/>
-      <c r="O5" s="378"/>
-      <c r="P5" s="378"/>
-      <c r="Q5" s="378"/>
-      <c r="R5" s="378"/>
-      <c r="S5" s="378"/>
-      <c r="T5" s="378"/>
-      <c r="U5" s="378"/>
-      <c r="V5" s="378"/>
-      <c r="W5" s="378"/>
-      <c r="X5" s="378"/>
-      <c r="Y5" s="381" t="s">
+      <c r="L5" s="379"/>
+      <c r="M5" s="379"/>
+      <c r="N5" s="379"/>
+      <c r="O5" s="379"/>
+      <c r="P5" s="379"/>
+      <c r="Q5" s="379"/>
+      <c r="R5" s="379"/>
+      <c r="S5" s="379"/>
+      <c r="T5" s="379"/>
+      <c r="U5" s="379"/>
+      <c r="V5" s="379"/>
+      <c r="W5" s="379"/>
+      <c r="X5" s="379"/>
+      <c r="Y5" s="382" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="378"/>
-      <c r="AA5" s="378"/>
-      <c r="AB5" s="378"/>
-      <c r="AC5" s="378"/>
-      <c r="AD5" s="378"/>
-      <c r="AE5" s="378"/>
-      <c r="AF5" s="378"/>
-      <c r="AG5" s="378"/>
-      <c r="AH5" s="378"/>
-      <c r="AI5" s="378"/>
-      <c r="AJ5" s="378"/>
-      <c r="AK5" s="378"/>
-      <c r="AL5" s="378"/>
-      <c r="AM5" s="378"/>
-      <c r="AN5" s="378"/>
-      <c r="AO5" s="379"/>
-      <c r="AP5" s="381" t="s">
+      <c r="Z5" s="379"/>
+      <c r="AA5" s="379"/>
+      <c r="AB5" s="379"/>
+      <c r="AC5" s="379"/>
+      <c r="AD5" s="379"/>
+      <c r="AE5" s="379"/>
+      <c r="AF5" s="379"/>
+      <c r="AG5" s="379"/>
+      <c r="AH5" s="379"/>
+      <c r="AI5" s="379"/>
+      <c r="AJ5" s="379"/>
+      <c r="AK5" s="379"/>
+      <c r="AL5" s="379"/>
+      <c r="AM5" s="379"/>
+      <c r="AN5" s="379"/>
+      <c r="AO5" s="380"/>
+      <c r="AP5" s="382" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="381" t="s">
+      <c r="AQ5" s="382" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="381" t="s">
+      <c r="AR5" s="382" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="381" t="s">
+      <c r="AS5" s="382" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="381" t="s">
+      <c r="AT5" s="382" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="381" t="s">
+      <c r="AU5" s="382" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="381" t="s">
+      <c r="AV5" s="382" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="381" t="s">
+      <c r="AW5" s="382" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="381" t="s">
+      <c r="AX5" s="382" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="377" t="s">
+      <c r="AY5" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="378"/>
-      <c r="BA5" s="378"/>
-      <c r="BB5" s="378"/>
-      <c r="BC5" s="378"/>
-      <c r="BD5" s="378"/>
-      <c r="BE5" s="378"/>
-      <c r="BF5" s="378"/>
-      <c r="BG5" s="378"/>
-      <c r="BH5" s="378"/>
-      <c r="BI5" s="378"/>
-      <c r="BJ5" s="378"/>
-      <c r="BK5" s="378"/>
-      <c r="BL5" s="378"/>
-      <c r="BM5" s="378"/>
-      <c r="BN5" s="378"/>
-      <c r="BO5" s="378"/>
-      <c r="BP5" s="379"/>
-      <c r="BQ5" s="398" t="s">
+      <c r="AZ5" s="379"/>
+      <c r="BA5" s="379"/>
+      <c r="BB5" s="379"/>
+      <c r="BC5" s="379"/>
+      <c r="BD5" s="379"/>
+      <c r="BE5" s="379"/>
+      <c r="BF5" s="379"/>
+      <c r="BG5" s="379"/>
+      <c r="BH5" s="379"/>
+      <c r="BI5" s="379"/>
+      <c r="BJ5" s="379"/>
+      <c r="BK5" s="379"/>
+      <c r="BL5" s="379"/>
+      <c r="BM5" s="379"/>
+      <c r="BN5" s="379"/>
+      <c r="BO5" s="379"/>
+      <c r="BP5" s="380"/>
+      <c r="BQ5" s="399" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="391"/>
-      <c r="BS5" s="377" t="s">
+      <c r="BR5" s="392"/>
+      <c r="BS5" s="378" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="377" t="s">
+      <c r="BT5" s="378" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="409" t="s">
+      <c r="BU5" s="410" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="410" t="s">
+      <c r="BW5" s="411" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="399" t="s">
+      <c r="BX5" s="400" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="400"/>
-      <c r="BZ5" s="400"/>
-      <c r="CA5" s="391"/>
-      <c r="CB5" s="411" t="s">
+      <c r="BY5" s="401"/>
+      <c r="BZ5" s="401"/>
+      <c r="CA5" s="392"/>
+      <c r="CB5" s="412" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="396" t="s">
+      <c r="CC5" s="397" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="396" t="s">
+      <c r="CD5" s="397" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="375"/>
-      <c r="B6" s="375"/>
-      <c r="C6" s="375"/>
-      <c r="D6" s="375"/>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
-      <c r="G6" s="375"/>
-      <c r="H6" s="375"/>
-      <c r="I6" s="375"/>
-      <c r="J6" s="375"/>
-      <c r="K6" s="389" t="s">
+      <c r="A6" s="376"/>
+      <c r="B6" s="376"/>
+      <c r="C6" s="376"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="376"/>
+      <c r="F6" s="376"/>
+      <c r="G6" s="376"/>
+      <c r="H6" s="376"/>
+      <c r="I6" s="376"/>
+      <c r="J6" s="376"/>
+      <c r="K6" s="390" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="389" t="s">
+      <c r="L6" s="390" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="389" t="s">
+      <c r="M6" s="390" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="389" t="s">
+      <c r="N6" s="390" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="389" t="s">
+      <c r="O6" s="390" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="389" t="s">
+      <c r="P6" s="390" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="389" t="s">
+      <c r="Q6" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="389" t="s">
+      <c r="R6" s="390" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="389" t="s">
+      <c r="S6" s="390" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="389" t="s">
+      <c r="T6" s="390" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="389" t="s">
+      <c r="U6" s="390" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="390" t="s">
+      <c r="V6" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="391"/>
-      <c r="X6" s="389" t="s">
+      <c r="W6" s="392"/>
+      <c r="X6" s="390" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="381" t="s">
+      <c r="Y6" s="382" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="381" t="s">
+      <c r="Z6" s="382" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="381" t="s">
+      <c r="AA6" s="382" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="381" t="s">
+      <c r="AB6" s="382" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="337" t="s">
+      <c r="AC6" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="337" t="s">
+      <c r="AD6" s="338" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="337" t="s">
+      <c r="AE6" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="337" t="s">
+      <c r="AF6" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="381" t="s">
+      <c r="AG6" s="382" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="337" t="s">
+      <c r="AH6" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="337" t="s">
+      <c r="AI6" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="381" t="s">
+      <c r="AJ6" s="382" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="383" t="s">
+      <c r="AK6" s="384" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="381" t="s">
+      <c r="AL6" s="382" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="381" t="s">
+      <c r="AM6" s="382" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="387" t="s">
+      <c r="AN6" s="388" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="381" t="s">
+      <c r="AO6" s="382" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="375"/>
-      <c r="AQ6" s="375"/>
-      <c r="AR6" s="375"/>
-      <c r="AS6" s="375"/>
-      <c r="AT6" s="375"/>
-      <c r="AU6" s="375"/>
-      <c r="AV6" s="375"/>
-      <c r="AW6" s="375"/>
-      <c r="AX6" s="375"/>
-      <c r="AY6" s="377" t="s">
+      <c r="AP6" s="376"/>
+      <c r="AQ6" s="376"/>
+      <c r="AR6" s="376"/>
+      <c r="AS6" s="376"/>
+      <c r="AT6" s="376"/>
+      <c r="AU6" s="376"/>
+      <c r="AV6" s="376"/>
+      <c r="AW6" s="376"/>
+      <c r="AX6" s="376"/>
+      <c r="AY6" s="378" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="378"/>
-      <c r="BA6" s="378"/>
-      <c r="BB6" s="378"/>
-      <c r="BC6" s="378"/>
-      <c r="BD6" s="378"/>
-      <c r="BE6" s="378"/>
-      <c r="BF6" s="378"/>
-      <c r="BG6" s="378"/>
-      <c r="BH6" s="378"/>
-      <c r="BI6" s="378"/>
-      <c r="BJ6" s="379"/>
-      <c r="BK6" s="377" t="s">
+      <c r="AZ6" s="379"/>
+      <c r="BA6" s="379"/>
+      <c r="BB6" s="379"/>
+      <c r="BC6" s="379"/>
+      <c r="BD6" s="379"/>
+      <c r="BE6" s="379"/>
+      <c r="BF6" s="379"/>
+      <c r="BG6" s="379"/>
+      <c r="BH6" s="379"/>
+      <c r="BI6" s="379"/>
+      <c r="BJ6" s="380"/>
+      <c r="BK6" s="378" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="378"/>
-      <c r="BM6" s="378"/>
-      <c r="BN6" s="378"/>
-      <c r="BO6" s="378"/>
-      <c r="BP6" s="379"/>
-      <c r="BQ6" s="374" t="s">
+      <c r="BL6" s="379"/>
+      <c r="BM6" s="379"/>
+      <c r="BN6" s="379"/>
+      <c r="BO6" s="379"/>
+      <c r="BP6" s="380"/>
+      <c r="BQ6" s="375" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="374" t="s">
+      <c r="BR6" s="375" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="375"/>
-      <c r="BT6" s="375"/>
-      <c r="BU6" s="384"/>
-      <c r="BW6" s="402"/>
-      <c r="BX6" s="384"/>
-      <c r="BY6" s="401"/>
-      <c r="BZ6" s="401"/>
-      <c r="CA6" s="402"/>
-      <c r="CB6" s="375"/>
-      <c r="CC6" s="375"/>
-      <c r="CD6" s="375"/>
+      <c r="BS6" s="376"/>
+      <c r="BT6" s="376"/>
+      <c r="BU6" s="385"/>
+      <c r="BW6" s="403"/>
+      <c r="BX6" s="385"/>
+      <c r="BY6" s="402"/>
+      <c r="BZ6" s="402"/>
+      <c r="CA6" s="403"/>
+      <c r="CB6" s="376"/>
+      <c r="CC6" s="376"/>
+      <c r="CD6" s="376"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="375"/>
-      <c r="B7" s="375"/>
-      <c r="C7" s="375"/>
-      <c r="D7" s="375"/>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
-      <c r="G7" s="375"/>
-      <c r="H7" s="375"/>
-      <c r="I7" s="375"/>
-      <c r="J7" s="375"/>
-      <c r="K7" s="375"/>
-      <c r="L7" s="375"/>
-      <c r="M7" s="375"/>
-      <c r="N7" s="375"/>
-      <c r="O7" s="375"/>
-      <c r="P7" s="375"/>
-      <c r="Q7" s="375"/>
-      <c r="R7" s="375"/>
-      <c r="S7" s="375"/>
-      <c r="T7" s="375"/>
-      <c r="U7" s="375"/>
-      <c r="V7" s="385"/>
-      <c r="W7" s="392"/>
-      <c r="X7" s="375"/>
-      <c r="Y7" s="375"/>
-      <c r="Z7" s="375"/>
-      <c r="AA7" s="375"/>
-      <c r="AB7" s="375"/>
-      <c r="AC7" s="375"/>
-      <c r="AD7" s="375"/>
-      <c r="AE7" s="375"/>
-      <c r="AF7" s="375"/>
-      <c r="AG7" s="375"/>
-      <c r="AH7" s="375"/>
-      <c r="AI7" s="375"/>
-      <c r="AJ7" s="375"/>
-      <c r="AK7" s="384"/>
-      <c r="AL7" s="375"/>
-      <c r="AM7" s="375"/>
-      <c r="AN7" s="375"/>
-      <c r="AO7" s="375"/>
-      <c r="AP7" s="375"/>
-      <c r="AQ7" s="375"/>
-      <c r="AR7" s="375"/>
-      <c r="AS7" s="375"/>
-      <c r="AT7" s="375"/>
-      <c r="AU7" s="375"/>
-      <c r="AV7" s="375"/>
-      <c r="AW7" s="375"/>
-      <c r="AX7" s="375"/>
+      <c r="A7" s="376"/>
+      <c r="B7" s="376"/>
+      <c r="C7" s="376"/>
+      <c r="D7" s="376"/>
+      <c r="E7" s="376"/>
+      <c r="F7" s="376"/>
+      <c r="G7" s="376"/>
+      <c r="H7" s="376"/>
+      <c r="I7" s="376"/>
+      <c r="J7" s="376"/>
+      <c r="K7" s="376"/>
+      <c r="L7" s="376"/>
+      <c r="M7" s="376"/>
+      <c r="N7" s="376"/>
+      <c r="O7" s="376"/>
+      <c r="P7" s="376"/>
+      <c r="Q7" s="376"/>
+      <c r="R7" s="376"/>
+      <c r="S7" s="376"/>
+      <c r="T7" s="376"/>
+      <c r="U7" s="376"/>
+      <c r="V7" s="386"/>
+      <c r="W7" s="393"/>
+      <c r="X7" s="376"/>
+      <c r="Y7" s="376"/>
+      <c r="Z7" s="376"/>
+      <c r="AA7" s="376"/>
+      <c r="AB7" s="376"/>
+      <c r="AC7" s="376"/>
+      <c r="AD7" s="376"/>
+      <c r="AE7" s="376"/>
+      <c r="AF7" s="376"/>
+      <c r="AG7" s="376"/>
+      <c r="AH7" s="376"/>
+      <c r="AI7" s="376"/>
+      <c r="AJ7" s="376"/>
+      <c r="AK7" s="385"/>
+      <c r="AL7" s="376"/>
+      <c r="AM7" s="376"/>
+      <c r="AN7" s="376"/>
+      <c r="AO7" s="376"/>
+      <c r="AP7" s="376"/>
+      <c r="AQ7" s="376"/>
+      <c r="AR7" s="376"/>
+      <c r="AS7" s="376"/>
+      <c r="AT7" s="376"/>
+      <c r="AU7" s="376"/>
+      <c r="AV7" s="376"/>
+      <c r="AW7" s="376"/>
+      <c r="AX7" s="376"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19185,122 +19186,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="377" t="s">
+      <c r="BB7" s="378" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="380" t="s">
+      <c r="BC7" s="381" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="380" t="s">
+      <c r="BD7" s="381" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="380" t="s">
+      <c r="BE7" s="381" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="380" t="s">
+      <c r="BF7" s="381" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="380" t="s">
+      <c r="BG7" s="381" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="380" t="s">
+      <c r="BH7" s="381" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="380" t="s">
+      <c r="BI7" s="381" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="408" t="s">
+      <c r="BJ7" s="409" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="380" t="s">
+      <c r="BK7" s="381" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="377" t="s">
+      <c r="BL7" s="378" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="380" t="s">
+      <c r="BM7" s="381" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="377" t="s">
+      <c r="BN7" s="378" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="377" t="s">
+      <c r="BO7" s="378" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="377" t="s">
+      <c r="BP7" s="378" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="375"/>
-      <c r="BR7" s="375"/>
-      <c r="BS7" s="375"/>
-      <c r="BT7" s="375"/>
-      <c r="BU7" s="384"/>
-      <c r="BW7" s="402"/>
-      <c r="BX7" s="403"/>
-      <c r="BY7" s="404"/>
-      <c r="BZ7" s="404"/>
-      <c r="CA7" s="405"/>
-      <c r="CB7" s="375"/>
-      <c r="CC7" s="375"/>
-      <c r="CD7" s="375"/>
+      <c r="BQ7" s="376"/>
+      <c r="BR7" s="376"/>
+      <c r="BS7" s="376"/>
+      <c r="BT7" s="376"/>
+      <c r="BU7" s="385"/>
+      <c r="BW7" s="403"/>
+      <c r="BX7" s="404"/>
+      <c r="BY7" s="405"/>
+      <c r="BZ7" s="405"/>
+      <c r="CA7" s="406"/>
+      <c r="CB7" s="376"/>
+      <c r="CC7" s="376"/>
+      <c r="CD7" s="376"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="376"/>
-      <c r="B8" s="376"/>
-      <c r="C8" s="376"/>
-      <c r="D8" s="376"/>
-      <c r="E8" s="376"/>
-      <c r="F8" s="376"/>
-      <c r="G8" s="376"/>
-      <c r="H8" s="376"/>
-      <c r="I8" s="376"/>
-      <c r="J8" s="376"/>
-      <c r="K8" s="376"/>
-      <c r="L8" s="376"/>
-      <c r="M8" s="376"/>
-      <c r="N8" s="376"/>
-      <c r="O8" s="376"/>
-      <c r="P8" s="376"/>
-      <c r="Q8" s="376"/>
-      <c r="R8" s="376"/>
-      <c r="S8" s="376"/>
-      <c r="T8" s="376"/>
-      <c r="U8" s="376"/>
+      <c r="A8" s="377"/>
+      <c r="B8" s="377"/>
+      <c r="C8" s="377"/>
+      <c r="D8" s="377"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
+      <c r="G8" s="377"/>
+      <c r="H8" s="377"/>
+      <c r="I8" s="377"/>
+      <c r="J8" s="377"/>
+      <c r="K8" s="377"/>
+      <c r="L8" s="377"/>
+      <c r="M8" s="377"/>
+      <c r="N8" s="377"/>
+      <c r="O8" s="377"/>
+      <c r="P8" s="377"/>
+      <c r="Q8" s="377"/>
+      <c r="R8" s="377"/>
+      <c r="S8" s="377"/>
+      <c r="T8" s="377"/>
+      <c r="U8" s="377"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="376"/>
-      <c r="Y8" s="376"/>
-      <c r="Z8" s="376"/>
-      <c r="AA8" s="376"/>
-      <c r="AB8" s="376"/>
-      <c r="AC8" s="376"/>
-      <c r="AD8" s="376"/>
-      <c r="AE8" s="376"/>
-      <c r="AF8" s="376"/>
-      <c r="AG8" s="376"/>
-      <c r="AH8" s="376"/>
-      <c r="AI8" s="376"/>
-      <c r="AJ8" s="376"/>
-      <c r="AK8" s="385"/>
-      <c r="AL8" s="376"/>
-      <c r="AM8" s="376"/>
-      <c r="AN8" s="376"/>
-      <c r="AO8" s="376"/>
-      <c r="AP8" s="376"/>
-      <c r="AQ8" s="376"/>
-      <c r="AR8" s="376"/>
-      <c r="AS8" s="376"/>
-      <c r="AT8" s="376"/>
-      <c r="AU8" s="376"/>
-      <c r="AV8" s="376"/>
-      <c r="AW8" s="376"/>
-      <c r="AX8" s="376"/>
+      <c r="X8" s="377"/>
+      <c r="Y8" s="377"/>
+      <c r="Z8" s="377"/>
+      <c r="AA8" s="377"/>
+      <c r="AB8" s="377"/>
+      <c r="AC8" s="377"/>
+      <c r="AD8" s="377"/>
+      <c r="AE8" s="377"/>
+      <c r="AF8" s="377"/>
+      <c r="AG8" s="377"/>
+      <c r="AH8" s="377"/>
+      <c r="AI8" s="377"/>
+      <c r="AJ8" s="377"/>
+      <c r="AK8" s="386"/>
+      <c r="AL8" s="377"/>
+      <c r="AM8" s="377"/>
+      <c r="AN8" s="377"/>
+      <c r="AO8" s="377"/>
+      <c r="AP8" s="377"/>
+      <c r="AQ8" s="377"/>
+      <c r="AR8" s="377"/>
+      <c r="AS8" s="377"/>
+      <c r="AT8" s="377"/>
+      <c r="AU8" s="377"/>
+      <c r="AV8" s="377"/>
+      <c r="AW8" s="377"/>
+      <c r="AX8" s="377"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19310,27 +19311,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="376"/>
-      <c r="BC8" s="376"/>
-      <c r="BD8" s="376"/>
-      <c r="BE8" s="376"/>
-      <c r="BF8" s="376"/>
-      <c r="BG8" s="376"/>
-      <c r="BH8" s="376"/>
-      <c r="BI8" s="376"/>
-      <c r="BJ8" s="376"/>
-      <c r="BK8" s="376"/>
-      <c r="BL8" s="376"/>
-      <c r="BM8" s="376"/>
-      <c r="BN8" s="376"/>
-      <c r="BO8" s="376"/>
-      <c r="BP8" s="376"/>
-      <c r="BQ8" s="376"/>
-      <c r="BR8" s="376"/>
-      <c r="BS8" s="376"/>
-      <c r="BT8" s="376"/>
-      <c r="BU8" s="385"/>
-      <c r="BW8" s="405"/>
+      <c r="BB8" s="377"/>
+      <c r="BC8" s="377"/>
+      <c r="BD8" s="377"/>
+      <c r="BE8" s="377"/>
+      <c r="BF8" s="377"/>
+      <c r="BG8" s="377"/>
+      <c r="BH8" s="377"/>
+      <c r="BI8" s="377"/>
+      <c r="BJ8" s="377"/>
+      <c r="BK8" s="377"/>
+      <c r="BL8" s="377"/>
+      <c r="BM8" s="377"/>
+      <c r="BN8" s="377"/>
+      <c r="BO8" s="377"/>
+      <c r="BP8" s="377"/>
+      <c r="BQ8" s="377"/>
+      <c r="BR8" s="377"/>
+      <c r="BS8" s="377"/>
+      <c r="BT8" s="377"/>
+      <c r="BU8" s="386"/>
+      <c r="BW8" s="406"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19343,9 +19344,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="397"/>
-      <c r="CC8" s="397"/>
-      <c r="CD8" s="397"/>
+      <c r="CB8" s="398"/>
+      <c r="CC8" s="398"/>
+      <c r="CD8" s="398"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881B46FD-8C82-1C45-B312-83F059592A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46BFC66-376C-2D4E-82EA-624E9CAD1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38540" yWindow="660" windowWidth="38100" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4259,6 +4259,7 @@
     <definedName name="解_任_">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5061,7 +5062,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="78">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5544,6 +5545,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -5858,7 +5867,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="448">
+  <cellXfs count="445">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6762,6 +6771,112 @@
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="76" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="20" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6775,131 +6890,51 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6908,13 +6943,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6922,27 +6954,44 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6950,85 +6999,38 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="76" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="49" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="46" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="77" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="77" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -7795,88 +7797,88 @@
       <c r="CD2" s="295"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="353"/>
-      <c r="B3" s="352"/>
-      <c r="C3" s="352"/>
-      <c r="D3" s="352"/>
-      <c r="E3" s="352"/>
-      <c r="F3" s="352"/>
-      <c r="G3" s="352"/>
-      <c r="H3" s="352"/>
-      <c r="I3" s="352"/>
-      <c r="J3" s="352"/>
-      <c r="K3" s="352"/>
-      <c r="L3" s="352"/>
-      <c r="M3" s="352"/>
-      <c r="N3" s="352"/>
-      <c r="O3" s="352"/>
-      <c r="P3" s="352"/>
-      <c r="Q3" s="352"/>
-      <c r="R3" s="352"/>
-      <c r="S3" s="352"/>
-      <c r="T3" s="352"/>
-      <c r="U3" s="352"/>
-      <c r="V3" s="352"/>
-      <c r="W3" s="352"/>
-      <c r="X3" s="352"/>
-      <c r="Y3" s="352"/>
-      <c r="Z3" s="352"/>
-      <c r="AA3" s="352"/>
-      <c r="AB3" s="352"/>
-      <c r="AC3" s="352"/>
-      <c r="AD3" s="352"/>
-      <c r="AE3" s="352"/>
-      <c r="AF3" s="352"/>
-      <c r="AG3" s="352"/>
-      <c r="AH3" s="352"/>
-      <c r="AI3" s="352"/>
-      <c r="AJ3" s="352"/>
-      <c r="AK3" s="352"/>
-      <c r="AL3" s="352"/>
-      <c r="AM3" s="352"/>
-      <c r="AN3" s="352"/>
-      <c r="AO3" s="352"/>
-      <c r="AP3" s="352"/>
-      <c r="AQ3" s="352"/>
-      <c r="AR3" s="352"/>
-      <c r="AS3" s="352"/>
-      <c r="AT3" s="352"/>
-      <c r="AU3" s="352"/>
-      <c r="AV3" s="352"/>
-      <c r="AW3" s="352"/>
-      <c r="AX3" s="352"/>
-      <c r="AY3" s="352"/>
-      <c r="AZ3" s="352"/>
-      <c r="BA3" s="352"/>
-      <c r="BB3" s="352"/>
-      <c r="BC3" s="352"/>
-      <c r="BD3" s="352"/>
-      <c r="BE3" s="352"/>
-      <c r="BF3" s="352"/>
-      <c r="BG3" s="352"/>
-      <c r="BH3" s="352"/>
-      <c r="BI3" s="352"/>
-      <c r="BJ3" s="352"/>
-      <c r="BK3" s="352"/>
-      <c r="BL3" s="352"/>
-      <c r="BM3" s="352"/>
-      <c r="BN3" s="352"/>
-      <c r="BO3" s="352"/>
-      <c r="BP3" s="352"/>
-      <c r="BQ3" s="352"/>
-      <c r="BR3" s="352"/>
-      <c r="BS3" s="352"/>
-      <c r="BT3" s="352"/>
-      <c r="BU3" s="352"/>
+      <c r="A3" s="374"/>
+      <c r="B3" s="373"/>
+      <c r="C3" s="373"/>
+      <c r="D3" s="373"/>
+      <c r="E3" s="373"/>
+      <c r="F3" s="373"/>
+      <c r="G3" s="373"/>
+      <c r="H3" s="373"/>
+      <c r="I3" s="373"/>
+      <c r="J3" s="373"/>
+      <c r="K3" s="373"/>
+      <c r="L3" s="373"/>
+      <c r="M3" s="373"/>
+      <c r="N3" s="373"/>
+      <c r="O3" s="373"/>
+      <c r="P3" s="373"/>
+      <c r="Q3" s="373"/>
+      <c r="R3" s="373"/>
+      <c r="S3" s="373"/>
+      <c r="T3" s="373"/>
+      <c r="U3" s="373"/>
+      <c r="V3" s="373"/>
+      <c r="W3" s="373"/>
+      <c r="X3" s="373"/>
+      <c r="Y3" s="373"/>
+      <c r="Z3" s="373"/>
+      <c r="AA3" s="373"/>
+      <c r="AB3" s="373"/>
+      <c r="AC3" s="373"/>
+      <c r="AD3" s="373"/>
+      <c r="AE3" s="373"/>
+      <c r="AF3" s="373"/>
+      <c r="AG3" s="373"/>
+      <c r="AH3" s="373"/>
+      <c r="AI3" s="373"/>
+      <c r="AJ3" s="373"/>
+      <c r="AK3" s="373"/>
+      <c r="AL3" s="373"/>
+      <c r="AM3" s="373"/>
+      <c r="AN3" s="373"/>
+      <c r="AO3" s="373"/>
+      <c r="AP3" s="373"/>
+      <c r="AQ3" s="373"/>
+      <c r="AR3" s="373"/>
+      <c r="AS3" s="373"/>
+      <c r="AT3" s="373"/>
+      <c r="AU3" s="373"/>
+      <c r="AV3" s="373"/>
+      <c r="AW3" s="373"/>
+      <c r="AX3" s="373"/>
+      <c r="AY3" s="373"/>
+      <c r="AZ3" s="373"/>
+      <c r="BA3" s="373"/>
+      <c r="BB3" s="373"/>
+      <c r="BC3" s="373"/>
+      <c r="BD3" s="373"/>
+      <c r="BE3" s="373"/>
+      <c r="BF3" s="373"/>
+      <c r="BG3" s="373"/>
+      <c r="BH3" s="373"/>
+      <c r="BI3" s="373"/>
+      <c r="BJ3" s="373"/>
+      <c r="BK3" s="373"/>
+      <c r="BL3" s="373"/>
+      <c r="BM3" s="373"/>
+      <c r="BN3" s="373"/>
+      <c r="BO3" s="373"/>
+      <c r="BP3" s="373"/>
+      <c r="BQ3" s="373"/>
+      <c r="BR3" s="373"/>
+      <c r="BS3" s="373"/>
+      <c r="BT3" s="373"/>
+      <c r="BU3" s="373"/>
       <c r="BV3" s="297"/>
-      <c r="BW3" s="351" t="s">
+      <c r="BW3" s="372" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="352"/>
-      <c r="BY3" s="352"/>
-      <c r="BZ3" s="352"/>
-      <c r="CA3" s="352"/>
-      <c r="CB3" s="352"/>
+      <c r="BX3" s="373"/>
+      <c r="BY3" s="373"/>
+      <c r="BZ3" s="373"/>
+      <c r="CA3" s="373"/>
+      <c r="CB3" s="373"/>
       <c r="CC3" s="299"/>
       <c r="CD3" s="299"/>
     </row>
@@ -7954,12 +7956,12 @@
       <c r="BT4" s="300"/>
       <c r="BU4" s="300"/>
       <c r="BV4" s="300"/>
-      <c r="BW4" s="352"/>
-      <c r="BX4" s="352"/>
-      <c r="BY4" s="352"/>
-      <c r="BZ4" s="352"/>
-      <c r="CA4" s="352"/>
-      <c r="CB4" s="352"/>
+      <c r="BW4" s="373"/>
+      <c r="BX4" s="373"/>
+      <c r="BY4" s="373"/>
+      <c r="BZ4" s="373"/>
+      <c r="CA4" s="373"/>
+      <c r="CB4" s="373"/>
       <c r="CC4" s="299"/>
       <c r="CD4" s="299"/>
     </row>
@@ -8037,12 +8039,12 @@
       <c r="BT5" s="300"/>
       <c r="BU5" s="300"/>
       <c r="BV5" s="300"/>
-      <c r="BW5" s="352"/>
-      <c r="BX5" s="352"/>
-      <c r="BY5" s="352"/>
-      <c r="BZ5" s="352"/>
-      <c r="CA5" s="352"/>
-      <c r="CB5" s="352"/>
+      <c r="BW5" s="373"/>
+      <c r="BX5" s="373"/>
+      <c r="BY5" s="373"/>
+      <c r="BZ5" s="373"/>
+      <c r="CA5" s="373"/>
+      <c r="CB5" s="373"/>
       <c r="CC5" s="299"/>
       <c r="CD5" s="299"/>
     </row>
@@ -8118,12 +8120,12 @@
       <c r="BT6" s="302"/>
       <c r="BU6" s="302"/>
       <c r="BV6" s="302"/>
-      <c r="BW6" s="352"/>
-      <c r="BX6" s="352"/>
-      <c r="BY6" s="352"/>
-      <c r="BZ6" s="352"/>
-      <c r="CA6" s="352"/>
-      <c r="CB6" s="352"/>
+      <c r="BW6" s="373"/>
+      <c r="BX6" s="373"/>
+      <c r="BY6" s="373"/>
+      <c r="BZ6" s="373"/>
+      <c r="CA6" s="373"/>
+      <c r="CB6" s="373"/>
       <c r="CC6" s="299"/>
       <c r="CD6" s="299"/>
     </row>
@@ -8263,245 +8265,245 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="350" t="s">
+      <c r="A8" s="371" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="355" t="s">
+      <c r="B8" s="376" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="338" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="342" t="s">
+      <c r="D8" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="342" t="s">
+      <c r="E8" s="360" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="338" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="427" t="s">
+      <c r="G8" s="361" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="349" t="s">
+      <c r="H8" s="362" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="349" t="s">
+      <c r="I8" s="362" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="430" t="s">
+      <c r="J8" s="358" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="363" t="s">
+      <c r="K8" s="370" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="364"/>
-      <c r="M8" s="364"/>
-      <c r="N8" s="364"/>
-      <c r="O8" s="364"/>
-      <c r="P8" s="364"/>
-      <c r="Q8" s="364"/>
-      <c r="R8" s="364"/>
-      <c r="S8" s="364"/>
-      <c r="T8" s="364"/>
-      <c r="U8" s="364"/>
-      <c r="V8" s="364"/>
-      <c r="W8" s="364"/>
-      <c r="X8" s="364"/>
-      <c r="Y8" s="368" t="s">
+      <c r="L8" s="355"/>
+      <c r="M8" s="355"/>
+      <c r="N8" s="355"/>
+      <c r="O8" s="355"/>
+      <c r="P8" s="355"/>
+      <c r="Q8" s="355"/>
+      <c r="R8" s="355"/>
+      <c r="S8" s="355"/>
+      <c r="T8" s="355"/>
+      <c r="U8" s="355"/>
+      <c r="V8" s="355"/>
+      <c r="W8" s="355"/>
+      <c r="X8" s="355"/>
+      <c r="Y8" s="354" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="364"/>
-      <c r="AA8" s="364"/>
-      <c r="AB8" s="364"/>
-      <c r="AC8" s="364"/>
-      <c r="AD8" s="364"/>
-      <c r="AE8" s="364"/>
-      <c r="AF8" s="364"/>
-      <c r="AG8" s="364"/>
-      <c r="AH8" s="364"/>
-      <c r="AI8" s="364"/>
-      <c r="AJ8" s="364"/>
-      <c r="AK8" s="364"/>
-      <c r="AL8" s="364"/>
-      <c r="AM8" s="364"/>
-      <c r="AN8" s="364"/>
-      <c r="AO8" s="366"/>
-      <c r="AP8" s="430" t="s">
+      <c r="Z8" s="355"/>
+      <c r="AA8" s="355"/>
+      <c r="AB8" s="355"/>
+      <c r="AC8" s="355"/>
+      <c r="AD8" s="355"/>
+      <c r="AE8" s="355"/>
+      <c r="AF8" s="355"/>
+      <c r="AG8" s="355"/>
+      <c r="AH8" s="355"/>
+      <c r="AI8" s="355"/>
+      <c r="AJ8" s="355"/>
+      <c r="AK8" s="355"/>
+      <c r="AL8" s="355"/>
+      <c r="AM8" s="355"/>
+      <c r="AN8" s="355"/>
+      <c r="AO8" s="356"/>
+      <c r="AP8" s="358" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="430" t="s">
+      <c r="AQ8" s="358" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="430" t="s">
+      <c r="AR8" s="358" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="430" t="s">
+      <c r="AS8" s="358" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="430" t="s">
+      <c r="AT8" s="358" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="430" t="s">
+      <c r="AU8" s="358" t="s">
         <v>21</v>
       </c>
       <c r="AV8" s="338" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="435" t="s">
+      <c r="AW8" s="352" t="s">
         <v>23</v>
       </c>
       <c r="AX8" s="338" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="365" t="s">
+      <c r="AY8" s="363" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="364"/>
-      <c r="BA8" s="364"/>
-      <c r="BB8" s="364"/>
-      <c r="BC8" s="364"/>
-      <c r="BD8" s="364"/>
-      <c r="BE8" s="364"/>
-      <c r="BF8" s="364"/>
-      <c r="BG8" s="364"/>
-      <c r="BH8" s="364"/>
-      <c r="BI8" s="364"/>
-      <c r="BJ8" s="364"/>
-      <c r="BK8" s="364"/>
-      <c r="BL8" s="364"/>
-      <c r="BM8" s="364"/>
-      <c r="BN8" s="364"/>
-      <c r="BO8" s="364"/>
-      <c r="BP8" s="364"/>
-      <c r="BQ8" s="366"/>
-      <c r="BR8" s="369" t="s">
+      <c r="AZ8" s="355"/>
+      <c r="BA8" s="355"/>
+      <c r="BB8" s="355"/>
+      <c r="BC8" s="355"/>
+      <c r="BD8" s="355"/>
+      <c r="BE8" s="355"/>
+      <c r="BF8" s="355"/>
+      <c r="BG8" s="355"/>
+      <c r="BH8" s="355"/>
+      <c r="BI8" s="355"/>
+      <c r="BJ8" s="355"/>
+      <c r="BK8" s="355"/>
+      <c r="BL8" s="355"/>
+      <c r="BM8" s="355"/>
+      <c r="BN8" s="355"/>
+      <c r="BO8" s="355"/>
+      <c r="BP8" s="355"/>
+      <c r="BQ8" s="356"/>
+      <c r="BR8" s="339" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="360"/>
+      <c r="BS8" s="340"/>
       <c r="BT8" s="338" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="356" t="s">
+      <c r="BU8" s="335" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="22"/>
-      <c r="BW8" s="438" t="s">
+      <c r="BW8" s="386" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="329" t="s">
+      <c r="BX8" s="377" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="330"/>
-      <c r="BZ8" s="330"/>
-      <c r="CA8" s="331"/>
-      <c r="CB8" s="370" t="s">
+      <c r="BY8" s="378"/>
+      <c r="BZ8" s="378"/>
+      <c r="CA8" s="379"/>
+      <c r="CB8" s="341" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="444" t="s">
+      <c r="CC8" s="390" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="442" t="s">
+      <c r="CD8" s="390" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="347"/>
-      <c r="B9" s="339"/>
-      <c r="C9" s="339"/>
-      <c r="D9" s="339"/>
-      <c r="E9" s="339"/>
-      <c r="F9" s="339"/>
-      <c r="G9" s="428"/>
-      <c r="H9" s="347"/>
-      <c r="I9" s="347"/>
-      <c r="J9" s="431"/>
-      <c r="K9" s="346" t="s">
+      <c r="A9" s="350"/>
+      <c r="B9" s="333"/>
+      <c r="C9" s="333"/>
+      <c r="D9" s="333"/>
+      <c r="E9" s="333"/>
+      <c r="F9" s="333"/>
+      <c r="G9" s="344"/>
+      <c r="H9" s="350"/>
+      <c r="I9" s="350"/>
+      <c r="J9" s="331"/>
+      <c r="K9" s="349" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="346" t="s">
+      <c r="L9" s="349" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="346" t="s">
+      <c r="M9" s="349" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="346" t="s">
+      <c r="N9" s="349" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="346" t="s">
+      <c r="O9" s="349" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="346" t="s">
+      <c r="P9" s="349" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="346" t="s">
+      <c r="Q9" s="349" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="346" t="s">
+      <c r="R9" s="349" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="346" t="s">
+      <c r="S9" s="349" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="346" t="s">
+      <c r="T9" s="349" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="346" t="s">
+      <c r="U9" s="349" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="359" t="s">
+      <c r="V9" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="360"/>
-      <c r="X9" s="346" t="s">
+      <c r="W9" s="340"/>
+      <c r="X9" s="349" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="341" t="s">
+      <c r="Y9" s="332" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="341" t="s">
+      <c r="Z9" s="332" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="341" t="s">
+      <c r="AA9" s="332" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="341" t="s">
+      <c r="AB9" s="332" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="341" t="s">
+      <c r="AC9" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="341" t="s">
+      <c r="AD9" s="332" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="341" t="s">
+      <c r="AE9" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="341" t="s">
+      <c r="AF9" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="341" t="s">
+      <c r="AG9" s="332" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="341" t="s">
+      <c r="AH9" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="341" t="s">
+      <c r="AI9" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="433" t="s">
+      <c r="AJ9" s="359" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="356" t="s">
+      <c r="AK9" s="335" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="434" t="s">
+      <c r="AL9" s="343" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="341" t="s">
+      <c r="AM9" s="332" t="s">
         <v>61</v>
       </c>
       <c r="AN9" s="338" t="s">
@@ -8510,109 +8512,109 @@
       <c r="AO9" s="338" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="431"/>
-      <c r="AQ9" s="431"/>
-      <c r="AR9" s="431"/>
-      <c r="AS9" s="431"/>
-      <c r="AT9" s="431"/>
-      <c r="AU9" s="431"/>
-      <c r="AV9" s="339"/>
-      <c r="AW9" s="431"/>
-      <c r="AX9" s="339"/>
-      <c r="AY9" s="372" t="s">
+      <c r="AP9" s="331"/>
+      <c r="AQ9" s="331"/>
+      <c r="AR9" s="331"/>
+      <c r="AS9" s="331"/>
+      <c r="AT9" s="331"/>
+      <c r="AU9" s="331"/>
+      <c r="AV9" s="333"/>
+      <c r="AW9" s="331"/>
+      <c r="AX9" s="333"/>
+      <c r="AY9" s="346" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="373"/>
-      <c r="BA9" s="373"/>
-      <c r="BB9" s="373"/>
-      <c r="BC9" s="373"/>
-      <c r="BD9" s="373"/>
-      <c r="BE9" s="373"/>
-      <c r="BF9" s="373"/>
-      <c r="BG9" s="373"/>
-      <c r="BH9" s="373"/>
-      <c r="BI9" s="373"/>
-      <c r="BJ9" s="373"/>
-      <c r="BK9" s="373"/>
-      <c r="BL9" s="374"/>
-      <c r="BM9" s="372" t="s">
+      <c r="AZ9" s="347"/>
+      <c r="BA9" s="347"/>
+      <c r="BB9" s="347"/>
+      <c r="BC9" s="347"/>
+      <c r="BD9" s="347"/>
+      <c r="BE9" s="347"/>
+      <c r="BF9" s="347"/>
+      <c r="BG9" s="347"/>
+      <c r="BH9" s="347"/>
+      <c r="BI9" s="347"/>
+      <c r="BJ9" s="347"/>
+      <c r="BK9" s="347"/>
+      <c r="BL9" s="348"/>
+      <c r="BM9" s="346" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="373"/>
-      <c r="BO9" s="373"/>
-      <c r="BP9" s="373"/>
-      <c r="BQ9" s="374"/>
-      <c r="BR9" s="348" t="s">
+      <c r="BN9" s="347"/>
+      <c r="BO9" s="347"/>
+      <c r="BP9" s="347"/>
+      <c r="BQ9" s="348"/>
+      <c r="BR9" s="365" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="348" t="s">
+      <c r="BS9" s="365" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="339"/>
-      <c r="BU9" s="357"/>
+      <c r="BT9" s="333"/>
+      <c r="BU9" s="336"/>
       <c r="BV9" s="22"/>
-      <c r="BW9" s="439"/>
-      <c r="BX9" s="332"/>
-      <c r="BY9" s="333"/>
-      <c r="BZ9" s="333"/>
-      <c r="CA9" s="334"/>
-      <c r="CB9" s="339"/>
-      <c r="CC9" s="445"/>
-      <c r="CD9" s="431"/>
+      <c r="BW9" s="387"/>
+      <c r="BX9" s="380"/>
+      <c r="BY9" s="381"/>
+      <c r="BZ9" s="381"/>
+      <c r="CA9" s="382"/>
+      <c r="CB9" s="333"/>
+      <c r="CC9" s="443"/>
+      <c r="CD9" s="443"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="347"/>
-      <c r="B10" s="339"/>
-      <c r="C10" s="339"/>
-      <c r="D10" s="339"/>
-      <c r="E10" s="339"/>
-      <c r="F10" s="339"/>
-      <c r="G10" s="428"/>
-      <c r="H10" s="347"/>
-      <c r="I10" s="347"/>
-      <c r="J10" s="431"/>
-      <c r="K10" s="347"/>
-      <c r="L10" s="347"/>
-      <c r="M10" s="347"/>
-      <c r="N10" s="347"/>
-      <c r="O10" s="347"/>
-      <c r="P10" s="347"/>
-      <c r="Q10" s="347"/>
-      <c r="R10" s="347"/>
-      <c r="S10" s="347"/>
-      <c r="T10" s="347"/>
-      <c r="U10" s="347"/>
-      <c r="V10" s="361"/>
-      <c r="W10" s="362"/>
-      <c r="X10" s="347"/>
-      <c r="Y10" s="339"/>
-      <c r="Z10" s="339"/>
-      <c r="AA10" s="339"/>
-      <c r="AB10" s="339"/>
-      <c r="AC10" s="339"/>
-      <c r="AD10" s="339"/>
-      <c r="AE10" s="339"/>
-      <c r="AF10" s="339"/>
-      <c r="AG10" s="339"/>
-      <c r="AH10" s="339"/>
-      <c r="AI10" s="339"/>
-      <c r="AJ10" s="428"/>
-      <c r="AK10" s="357"/>
-      <c r="AL10" s="428"/>
-      <c r="AM10" s="339"/>
-      <c r="AN10" s="339"/>
-      <c r="AO10" s="339"/>
-      <c r="AP10" s="431"/>
-      <c r="AQ10" s="431"/>
-      <c r="AR10" s="431"/>
-      <c r="AS10" s="431"/>
-      <c r="AT10" s="431"/>
-      <c r="AU10" s="431"/>
-      <c r="AV10" s="339"/>
-      <c r="AW10" s="431"/>
-      <c r="AX10" s="339"/>
+      <c r="A10" s="350"/>
+      <c r="B10" s="333"/>
+      <c r="C10" s="333"/>
+      <c r="D10" s="333"/>
+      <c r="E10" s="333"/>
+      <c r="F10" s="333"/>
+      <c r="G10" s="344"/>
+      <c r="H10" s="350"/>
+      <c r="I10" s="350"/>
+      <c r="J10" s="331"/>
+      <c r="K10" s="350"/>
+      <c r="L10" s="350"/>
+      <c r="M10" s="350"/>
+      <c r="N10" s="350"/>
+      <c r="O10" s="350"/>
+      <c r="P10" s="350"/>
+      <c r="Q10" s="350"/>
+      <c r="R10" s="350"/>
+      <c r="S10" s="350"/>
+      <c r="T10" s="350"/>
+      <c r="U10" s="350"/>
+      <c r="V10" s="367"/>
+      <c r="W10" s="368"/>
+      <c r="X10" s="350"/>
+      <c r="Y10" s="333"/>
+      <c r="Z10" s="333"/>
+      <c r="AA10" s="333"/>
+      <c r="AB10" s="333"/>
+      <c r="AC10" s="333"/>
+      <c r="AD10" s="333"/>
+      <c r="AE10" s="333"/>
+      <c r="AF10" s="333"/>
+      <c r="AG10" s="333"/>
+      <c r="AH10" s="333"/>
+      <c r="AI10" s="333"/>
+      <c r="AJ10" s="344"/>
+      <c r="AK10" s="336"/>
+      <c r="AL10" s="344"/>
+      <c r="AM10" s="333"/>
+      <c r="AN10" s="333"/>
+      <c r="AO10" s="333"/>
+      <c r="AP10" s="331"/>
+      <c r="AQ10" s="331"/>
+      <c r="AR10" s="331"/>
+      <c r="AS10" s="331"/>
+      <c r="AT10" s="331"/>
+      <c r="AU10" s="331"/>
+      <c r="AV10" s="333"/>
+      <c r="AW10" s="331"/>
+      <c r="AX10" s="333"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8622,67 +8624,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="354" t="s">
+      <c r="BB10" s="375" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="436" t="s">
+      <c r="BC10" s="364" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="436" t="s">
+      <c r="BD10" s="364" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="343" t="s">
+      <c r="BE10" s="357" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="343" t="s">
+      <c r="BF10" s="357" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="344" t="s">
+      <c r="BG10" s="389" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="436" t="s">
+      <c r="BH10" s="364" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="437" t="s">
+      <c r="BI10" s="369" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="343" t="s">
+      <c r="BJ10" s="357" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="343" t="s">
+      <c r="BK10" s="357" t="s">
         <v>79</v>
       </c>
       <c r="BL10" s="338" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="436" t="s">
+      <c r="BM10" s="364" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="435" t="s">
+      <c r="BN10" s="352" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="436" t="s">
+      <c r="BO10" s="364" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="435" t="s">
+      <c r="BP10" s="352" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="435" t="s">
+      <c r="BQ10" s="352" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="347"/>
-      <c r="BS10" s="347"/>
-      <c r="BT10" s="339"/>
-      <c r="BU10" s="357"/>
+      <c r="BR10" s="350"/>
+      <c r="BS10" s="350"/>
+      <c r="BT10" s="333"/>
+      <c r="BU10" s="336"/>
       <c r="BV10" s="22"/>
-      <c r="BW10" s="439"/>
-      <c r="BX10" s="335"/>
-      <c r="BY10" s="336"/>
-      <c r="BZ10" s="336"/>
-      <c r="CA10" s="337"/>
-      <c r="CB10" s="339"/>
-      <c r="CC10" s="445"/>
-      <c r="CD10" s="431"/>
+      <c r="BW10" s="387"/>
+      <c r="BX10" s="383"/>
+      <c r="BY10" s="384"/>
+      <c r="BZ10" s="384"/>
+      <c r="CA10" s="385"/>
+      <c r="CB10" s="333"/>
+      <c r="CC10" s="443"/>
+      <c r="CD10" s="443"/>
       <c r="CE10" s="320" t="s">
         <v>3</v>
       </c>
@@ -8690,60 +8692,60 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="306" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="345"/>
-      <c r="B11" s="340"/>
-      <c r="C11" s="340"/>
-      <c r="D11" s="340"/>
-      <c r="E11" s="340"/>
-      <c r="F11" s="340"/>
-      <c r="G11" s="429"/>
-      <c r="H11" s="345"/>
-      <c r="I11" s="345"/>
-      <c r="J11" s="432"/>
-      <c r="K11" s="345"/>
-      <c r="L11" s="345"/>
-      <c r="M11" s="345"/>
-      <c r="N11" s="345"/>
-      <c r="O11" s="345"/>
-      <c r="P11" s="345"/>
-      <c r="Q11" s="345"/>
-      <c r="R11" s="345"/>
-      <c r="S11" s="345"/>
-      <c r="T11" s="345"/>
-      <c r="U11" s="345"/>
+      <c r="A11" s="351"/>
+      <c r="B11" s="334"/>
+      <c r="C11" s="334"/>
+      <c r="D11" s="334"/>
+      <c r="E11" s="334"/>
+      <c r="F11" s="334"/>
+      <c r="G11" s="345"/>
+      <c r="H11" s="351"/>
+      <c r="I11" s="351"/>
+      <c r="J11" s="353"/>
+      <c r="K11" s="351"/>
+      <c r="L11" s="351"/>
+      <c r="M11" s="351"/>
+      <c r="N11" s="351"/>
+      <c r="O11" s="351"/>
+      <c r="P11" s="351"/>
+      <c r="Q11" s="351"/>
+      <c r="R11" s="351"/>
+      <c r="S11" s="351"/>
+      <c r="T11" s="351"/>
+      <c r="U11" s="351"/>
       <c r="V11" s="269" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="269" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="345"/>
-      <c r="Y11" s="340"/>
-      <c r="Z11" s="340"/>
-      <c r="AA11" s="340"/>
-      <c r="AB11" s="340"/>
-      <c r="AC11" s="340"/>
-      <c r="AD11" s="340"/>
-      <c r="AE11" s="340"/>
-      <c r="AF11" s="340"/>
-      <c r="AG11" s="340"/>
-      <c r="AH11" s="340"/>
-      <c r="AI11" s="340"/>
-      <c r="AJ11" s="429"/>
-      <c r="AK11" s="358"/>
-      <c r="AL11" s="429"/>
-      <c r="AM11" s="340"/>
-      <c r="AN11" s="340"/>
-      <c r="AO11" s="340"/>
-      <c r="AP11" s="432"/>
-      <c r="AQ11" s="432"/>
-      <c r="AR11" s="432"/>
-      <c r="AS11" s="432"/>
-      <c r="AT11" s="432"/>
-      <c r="AU11" s="432"/>
-      <c r="AV11" s="340"/>
-      <c r="AW11" s="432"/>
-      <c r="AX11" s="340"/>
+      <c r="X11" s="351"/>
+      <c r="Y11" s="334"/>
+      <c r="Z11" s="334"/>
+      <c r="AA11" s="334"/>
+      <c r="AB11" s="334"/>
+      <c r="AC11" s="334"/>
+      <c r="AD11" s="334"/>
+      <c r="AE11" s="334"/>
+      <c r="AF11" s="334"/>
+      <c r="AG11" s="334"/>
+      <c r="AH11" s="334"/>
+      <c r="AI11" s="334"/>
+      <c r="AJ11" s="345"/>
+      <c r="AK11" s="337"/>
+      <c r="AL11" s="345"/>
+      <c r="AM11" s="334"/>
+      <c r="AN11" s="334"/>
+      <c r="AO11" s="334"/>
+      <c r="AP11" s="353"/>
+      <c r="AQ11" s="353"/>
+      <c r="AR11" s="353"/>
+      <c r="AS11" s="353"/>
+      <c r="AT11" s="353"/>
+      <c r="AU11" s="353"/>
+      <c r="AV11" s="334"/>
+      <c r="AW11" s="353"/>
+      <c r="AX11" s="334"/>
       <c r="AY11" s="321" t="s">
         <v>88</v>
       </c>
@@ -8753,43 +8755,43 @@
       <c r="BA11" s="321" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="340"/>
-      <c r="BC11" s="432"/>
-      <c r="BD11" s="432"/>
-      <c r="BE11" s="340"/>
-      <c r="BF11" s="340"/>
-      <c r="BG11" s="345"/>
-      <c r="BH11" s="432"/>
-      <c r="BI11" s="429"/>
-      <c r="BJ11" s="340"/>
-      <c r="BK11" s="340"/>
-      <c r="BL11" s="340"/>
-      <c r="BM11" s="432"/>
-      <c r="BN11" s="432"/>
-      <c r="BO11" s="432"/>
-      <c r="BP11" s="432"/>
-      <c r="BQ11" s="432"/>
-      <c r="BR11" s="345"/>
-      <c r="BS11" s="345"/>
-      <c r="BT11" s="340"/>
-      <c r="BU11" s="358"/>
+      <c r="BB11" s="334"/>
+      <c r="BC11" s="353"/>
+      <c r="BD11" s="353"/>
+      <c r="BE11" s="334"/>
+      <c r="BF11" s="334"/>
+      <c r="BG11" s="351"/>
+      <c r="BH11" s="353"/>
+      <c r="BI11" s="345"/>
+      <c r="BJ11" s="334"/>
+      <c r="BK11" s="334"/>
+      <c r="BL11" s="334"/>
+      <c r="BM11" s="353"/>
+      <c r="BN11" s="353"/>
+      <c r="BO11" s="353"/>
+      <c r="BP11" s="353"/>
+      <c r="BQ11" s="353"/>
+      <c r="BR11" s="351"/>
+      <c r="BS11" s="351"/>
+      <c r="BT11" s="334"/>
+      <c r="BU11" s="337"/>
       <c r="BV11" s="22"/>
-      <c r="BW11" s="440"/>
-      <c r="BX11" s="441" t="s">
+      <c r="BW11" s="388"/>
+      <c r="BX11" s="329" t="s">
         <v>91</v>
       </c>
-      <c r="BY11" s="441" t="s">
+      <c r="BY11" s="329" t="s">
         <v>92</v>
       </c>
-      <c r="BZ11" s="441" t="s">
+      <c r="BZ11" s="329" t="s">
         <v>93</v>
       </c>
       <c r="CA11" s="270" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="371"/>
-      <c r="CC11" s="446"/>
-      <c r="CD11" s="443"/>
+      <c r="CB11" s="342"/>
+      <c r="CC11" s="444"/>
+      <c r="CD11" s="444"/>
       <c r="CE11" s="319">
         <v>26</v>
       </c>
@@ -9620,7 +9622,7 @@
       <c r="BQ15" s="279"/>
       <c r="BR15" s="279"/>
       <c r="BS15" s="279"/>
-      <c r="BT15" s="447"/>
+      <c r="BT15" s="330"/>
       <c r="BU15" s="281">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
         <v>60819220</v>
@@ -11246,57 +11248,21 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="BW3:CB6"/>
     <mergeCell ref="CC8:CC11"/>
@@ -11313,21 +11279,57 @@
     <mergeCell ref="O9:O11"/>
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11536,87 +11538,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="408"/>
-      <c r="B3" s="396"/>
-      <c r="C3" s="396"/>
-      <c r="D3" s="396"/>
-      <c r="E3" s="396"/>
-      <c r="F3" s="396"/>
-      <c r="G3" s="396"/>
-      <c r="H3" s="396"/>
-      <c r="I3" s="396"/>
-      <c r="J3" s="396"/>
-      <c r="K3" s="396"/>
-      <c r="L3" s="396"/>
-      <c r="M3" s="396"/>
-      <c r="N3" s="396"/>
-      <c r="O3" s="396"/>
-      <c r="P3" s="396"/>
-      <c r="Q3" s="396"/>
-      <c r="R3" s="396"/>
-      <c r="S3" s="396"/>
-      <c r="T3" s="396"/>
-      <c r="U3" s="396"/>
-      <c r="V3" s="396"/>
-      <c r="W3" s="396"/>
-      <c r="X3" s="396"/>
-      <c r="Y3" s="396"/>
-      <c r="Z3" s="396"/>
-      <c r="AA3" s="396"/>
-      <c r="AB3" s="396"/>
-      <c r="AC3" s="396"/>
-      <c r="AD3" s="396"/>
-      <c r="AE3" s="396"/>
-      <c r="AF3" s="396"/>
-      <c r="AG3" s="396"/>
-      <c r="AH3" s="396"/>
-      <c r="AI3" s="396"/>
-      <c r="AJ3" s="396"/>
-      <c r="AK3" s="396"/>
-      <c r="AL3" s="396"/>
-      <c r="AM3" s="396"/>
-      <c r="AN3" s="396"/>
-      <c r="AO3" s="396"/>
-      <c r="AP3" s="396"/>
-      <c r="AQ3" s="396"/>
-      <c r="AR3" s="396"/>
-      <c r="AS3" s="396"/>
-      <c r="AT3" s="396"/>
-      <c r="AU3" s="396"/>
-      <c r="AV3" s="396"/>
-      <c r="AW3" s="396"/>
-      <c r="AX3" s="396"/>
-      <c r="AY3" s="396"/>
-      <c r="AZ3" s="396"/>
-      <c r="BA3" s="396"/>
-      <c r="BB3" s="396"/>
-      <c r="BC3" s="396"/>
-      <c r="BD3" s="396"/>
-      <c r="BE3" s="396"/>
-      <c r="BF3" s="396"/>
-      <c r="BG3" s="396"/>
-      <c r="BH3" s="396"/>
-      <c r="BI3" s="396"/>
-      <c r="BJ3" s="396"/>
-      <c r="BK3" s="396"/>
-      <c r="BL3" s="396"/>
-      <c r="BM3" s="396"/>
-      <c r="BN3" s="396"/>
-      <c r="BO3" s="396"/>
-      <c r="BP3" s="396"/>
-      <c r="BQ3" s="396"/>
-      <c r="BR3" s="396"/>
-      <c r="BS3" s="396"/>
-      <c r="BT3" s="396"/>
-      <c r="BU3" s="396"/>
-      <c r="BW3" s="395" t="s">
+      <c r="A3" s="419"/>
+      <c r="B3" s="410"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="410"/>
+      <c r="E3" s="410"/>
+      <c r="F3" s="410"/>
+      <c r="G3" s="410"/>
+      <c r="H3" s="410"/>
+      <c r="I3" s="410"/>
+      <c r="J3" s="410"/>
+      <c r="K3" s="410"/>
+      <c r="L3" s="410"/>
+      <c r="M3" s="410"/>
+      <c r="N3" s="410"/>
+      <c r="O3" s="410"/>
+      <c r="P3" s="410"/>
+      <c r="Q3" s="410"/>
+      <c r="R3" s="410"/>
+      <c r="S3" s="410"/>
+      <c r="T3" s="410"/>
+      <c r="U3" s="410"/>
+      <c r="V3" s="410"/>
+      <c r="W3" s="410"/>
+      <c r="X3" s="410"/>
+      <c r="Y3" s="410"/>
+      <c r="Z3" s="410"/>
+      <c r="AA3" s="410"/>
+      <c r="AB3" s="410"/>
+      <c r="AC3" s="410"/>
+      <c r="AD3" s="410"/>
+      <c r="AE3" s="410"/>
+      <c r="AF3" s="410"/>
+      <c r="AG3" s="410"/>
+      <c r="AH3" s="410"/>
+      <c r="AI3" s="410"/>
+      <c r="AJ3" s="410"/>
+      <c r="AK3" s="410"/>
+      <c r="AL3" s="410"/>
+      <c r="AM3" s="410"/>
+      <c r="AN3" s="410"/>
+      <c r="AO3" s="410"/>
+      <c r="AP3" s="410"/>
+      <c r="AQ3" s="410"/>
+      <c r="AR3" s="410"/>
+      <c r="AS3" s="410"/>
+      <c r="AT3" s="410"/>
+      <c r="AU3" s="410"/>
+      <c r="AV3" s="410"/>
+      <c r="AW3" s="410"/>
+      <c r="AX3" s="410"/>
+      <c r="AY3" s="410"/>
+      <c r="AZ3" s="410"/>
+      <c r="BA3" s="410"/>
+      <c r="BB3" s="410"/>
+      <c r="BC3" s="410"/>
+      <c r="BD3" s="410"/>
+      <c r="BE3" s="410"/>
+      <c r="BF3" s="410"/>
+      <c r="BG3" s="410"/>
+      <c r="BH3" s="410"/>
+      <c r="BI3" s="410"/>
+      <c r="BJ3" s="410"/>
+      <c r="BK3" s="410"/>
+      <c r="BL3" s="410"/>
+      <c r="BM3" s="410"/>
+      <c r="BN3" s="410"/>
+      <c r="BO3" s="410"/>
+      <c r="BP3" s="410"/>
+      <c r="BQ3" s="410"/>
+      <c r="BR3" s="410"/>
+      <c r="BS3" s="410"/>
+      <c r="BT3" s="410"/>
+      <c r="BU3" s="410"/>
+      <c r="BW3" s="409" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="396"/>
-      <c r="BY3" s="396"/>
-      <c r="BZ3" s="396"/>
-      <c r="CA3" s="396"/>
-      <c r="CB3" s="396"/>
+      <c r="BX3" s="410"/>
+      <c r="BY3" s="410"/>
+      <c r="BZ3" s="410"/>
+      <c r="CA3" s="410"/>
+      <c r="CB3" s="410"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11699,35 +11701,35 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="396"/>
-      <c r="BX4" s="396"/>
-      <c r="BY4" s="396"/>
-      <c r="BZ4" s="396"/>
-      <c r="CA4" s="396"/>
-      <c r="CB4" s="396"/>
+      <c r="BW4" s="410"/>
+      <c r="BX4" s="410"/>
+      <c r="BY4" s="410"/>
+      <c r="BZ4" s="410"/>
+      <c r="CA4" s="410"/>
+      <c r="CB4" s="410"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="422" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="394" t="s">
+      <c r="B5" s="421" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="382" t="s">
+      <c r="C5" s="395" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="389" t="s">
+      <c r="D5" s="420" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="389" t="s">
+      <c r="E5" s="420" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="382" t="s">
+      <c r="F5" s="395" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="382" t="s">
+      <c r="G5" s="395" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="338" t="s">
@@ -11736,184 +11738,184 @@
       <c r="I5" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="382" t="s">
+      <c r="J5" s="395" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="387" t="s">
+      <c r="K5" s="424" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="379"/>
-      <c r="M5" s="379"/>
-      <c r="N5" s="379"/>
-      <c r="O5" s="379"/>
-      <c r="P5" s="379"/>
-      <c r="Q5" s="379"/>
-      <c r="R5" s="379"/>
-      <c r="S5" s="379"/>
-      <c r="T5" s="379"/>
-      <c r="U5" s="379"/>
-      <c r="V5" s="379"/>
-      <c r="W5" s="379"/>
-      <c r="X5" s="379"/>
-      <c r="Y5" s="382" t="s">
+      <c r="L5" s="406"/>
+      <c r="M5" s="406"/>
+      <c r="N5" s="406"/>
+      <c r="O5" s="406"/>
+      <c r="P5" s="406"/>
+      <c r="Q5" s="406"/>
+      <c r="R5" s="406"/>
+      <c r="S5" s="406"/>
+      <c r="T5" s="406"/>
+      <c r="U5" s="406"/>
+      <c r="V5" s="406"/>
+      <c r="W5" s="406"/>
+      <c r="X5" s="406"/>
+      <c r="Y5" s="395" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="379"/>
-      <c r="AA5" s="379"/>
-      <c r="AB5" s="379"/>
-      <c r="AC5" s="379"/>
-      <c r="AD5" s="379"/>
-      <c r="AE5" s="379"/>
-      <c r="AF5" s="379"/>
-      <c r="AG5" s="379"/>
-      <c r="AH5" s="379"/>
-      <c r="AI5" s="379"/>
-      <c r="AJ5" s="379"/>
-      <c r="AK5" s="379"/>
-      <c r="AL5" s="379"/>
-      <c r="AM5" s="379"/>
-      <c r="AN5" s="379"/>
-      <c r="AO5" s="380"/>
-      <c r="AP5" s="382" t="s">
+      <c r="Z5" s="406"/>
+      <c r="AA5" s="406"/>
+      <c r="AB5" s="406"/>
+      <c r="AC5" s="406"/>
+      <c r="AD5" s="406"/>
+      <c r="AE5" s="406"/>
+      <c r="AF5" s="406"/>
+      <c r="AG5" s="406"/>
+      <c r="AH5" s="406"/>
+      <c r="AI5" s="406"/>
+      <c r="AJ5" s="406"/>
+      <c r="AK5" s="406"/>
+      <c r="AL5" s="406"/>
+      <c r="AM5" s="406"/>
+      <c r="AN5" s="406"/>
+      <c r="AO5" s="407"/>
+      <c r="AP5" s="395" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="382" t="s">
+      <c r="AQ5" s="395" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="382" t="s">
+      <c r="AR5" s="395" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="382" t="s">
+      <c r="AS5" s="395" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="382" t="s">
+      <c r="AT5" s="395" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="382" t="s">
+      <c r="AU5" s="395" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="382" t="s">
+      <c r="AV5" s="395" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="382" t="s">
+      <c r="AW5" s="395" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="382" t="s">
+      <c r="AX5" s="395" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="378" t="s">
+      <c r="AY5" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="379"/>
-      <c r="BA5" s="379"/>
-      <c r="BB5" s="379"/>
-      <c r="BC5" s="379"/>
-      <c r="BD5" s="379"/>
-      <c r="BE5" s="379"/>
-      <c r="BF5" s="379"/>
-      <c r="BG5" s="379"/>
-      <c r="BH5" s="379"/>
-      <c r="BI5" s="379"/>
-      <c r="BJ5" s="379"/>
-      <c r="BK5" s="379"/>
-      <c r="BL5" s="379"/>
-      <c r="BM5" s="379"/>
-      <c r="BN5" s="379"/>
-      <c r="BO5" s="379"/>
-      <c r="BP5" s="379"/>
-      <c r="BQ5" s="380"/>
-      <c r="BR5" s="399" t="s">
+      <c r="AZ5" s="406"/>
+      <c r="BA5" s="406"/>
+      <c r="BB5" s="406"/>
+      <c r="BC5" s="406"/>
+      <c r="BD5" s="406"/>
+      <c r="BE5" s="406"/>
+      <c r="BF5" s="406"/>
+      <c r="BG5" s="406"/>
+      <c r="BH5" s="406"/>
+      <c r="BI5" s="406"/>
+      <c r="BJ5" s="406"/>
+      <c r="BK5" s="406"/>
+      <c r="BL5" s="406"/>
+      <c r="BM5" s="406"/>
+      <c r="BN5" s="406"/>
+      <c r="BO5" s="406"/>
+      <c r="BP5" s="406"/>
+      <c r="BQ5" s="407"/>
+      <c r="BR5" s="411" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="392"/>
-      <c r="BT5" s="378" t="s">
+      <c r="BS5" s="412"/>
+      <c r="BT5" s="405" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="410" t="s">
+      <c r="BU5" s="399" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="411" t="s">
+      <c r="BW5" s="402" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="400" t="s">
+      <c r="BX5" s="413" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="401"/>
-      <c r="BZ5" s="401"/>
-      <c r="CA5" s="392"/>
-      <c r="CB5" s="412" t="s">
+      <c r="BY5" s="414"/>
+      <c r="BZ5" s="414"/>
+      <c r="CA5" s="412"/>
+      <c r="CB5" s="408" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="397" t="s">
+      <c r="CC5" s="390" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="397" t="s">
+      <c r="CD5" s="390" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="376"/>
-      <c r="B6" s="376"/>
-      <c r="C6" s="376"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="376"/>
-      <c r="G6" s="376"/>
-      <c r="H6" s="376"/>
-      <c r="I6" s="376"/>
-      <c r="J6" s="376"/>
-      <c r="K6" s="390" t="s">
+      <c r="A6" s="391"/>
+      <c r="B6" s="391"/>
+      <c r="C6" s="391"/>
+      <c r="D6" s="391"/>
+      <c r="E6" s="391"/>
+      <c r="F6" s="391"/>
+      <c r="G6" s="391"/>
+      <c r="H6" s="391"/>
+      <c r="I6" s="391"/>
+      <c r="J6" s="391"/>
+      <c r="K6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="390" t="s">
+      <c r="L6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="390" t="s">
+      <c r="M6" s="396" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="390" t="s">
+      <c r="N6" s="396" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="390" t="s">
+      <c r="O6" s="396" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="390" t="s">
+      <c r="P6" s="396" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="390" t="s">
+      <c r="Q6" s="396" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="390" t="s">
+      <c r="R6" s="396" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="390" t="s">
+      <c r="S6" s="396" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="390" t="s">
+      <c r="T6" s="396" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="390" t="s">
+      <c r="U6" s="396" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="391" t="s">
+      <c r="V6" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="392"/>
-      <c r="X6" s="390" t="s">
+      <c r="W6" s="412"/>
+      <c r="X6" s="396" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="382" t="s">
+      <c r="Y6" s="395" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="382" t="s">
+      <c r="Z6" s="395" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="382" t="s">
+      <c r="AA6" s="395" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="382" t="s">
+      <c r="AB6" s="395" t="s">
         <v>50</v>
       </c>
       <c r="AC6" s="338" t="s">
@@ -11928,7 +11930,7 @@
       <c r="AF6" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="382" t="s">
+      <c r="AG6" s="395" t="s">
         <v>55</v>
       </c>
       <c r="AH6" s="338" t="s">
@@ -11937,126 +11939,126 @@
       <c r="AI6" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="382" t="s">
+      <c r="AJ6" s="395" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="384" t="s">
+      <c r="AK6" s="423" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="382" t="s">
+      <c r="AL6" s="395" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="382" t="s">
+      <c r="AM6" s="395" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="388" t="s">
+      <c r="AN6" s="425" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="382" t="s">
+      <c r="AO6" s="395" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="376"/>
-      <c r="AQ6" s="376"/>
-      <c r="AR6" s="376"/>
-      <c r="AS6" s="376"/>
-      <c r="AT6" s="376"/>
-      <c r="AU6" s="376"/>
-      <c r="AV6" s="376"/>
-      <c r="AW6" s="376"/>
-      <c r="AX6" s="376"/>
-      <c r="AY6" s="378" t="s">
+      <c r="AP6" s="391"/>
+      <c r="AQ6" s="391"/>
+      <c r="AR6" s="391"/>
+      <c r="AS6" s="391"/>
+      <c r="AT6" s="391"/>
+      <c r="AU6" s="391"/>
+      <c r="AV6" s="391"/>
+      <c r="AW6" s="391"/>
+      <c r="AX6" s="391"/>
+      <c r="AY6" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="379"/>
-      <c r="BA6" s="379"/>
-      <c r="BB6" s="379"/>
-      <c r="BC6" s="379"/>
-      <c r="BD6" s="379"/>
-      <c r="BE6" s="379"/>
-      <c r="BF6" s="379"/>
-      <c r="BG6" s="379"/>
-      <c r="BH6" s="379"/>
-      <c r="BI6" s="379"/>
-      <c r="BJ6" s="379"/>
-      <c r="BK6" s="379"/>
-      <c r="BL6" s="380"/>
-      <c r="BM6" s="378" t="s">
+      <c r="AZ6" s="406"/>
+      <c r="BA6" s="406"/>
+      <c r="BB6" s="406"/>
+      <c r="BC6" s="406"/>
+      <c r="BD6" s="406"/>
+      <c r="BE6" s="406"/>
+      <c r="BF6" s="406"/>
+      <c r="BG6" s="406"/>
+      <c r="BH6" s="406"/>
+      <c r="BI6" s="406"/>
+      <c r="BJ6" s="406"/>
+      <c r="BK6" s="406"/>
+      <c r="BL6" s="407"/>
+      <c r="BM6" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="379"/>
-      <c r="BO6" s="379"/>
-      <c r="BP6" s="379"/>
-      <c r="BQ6" s="380"/>
-      <c r="BR6" s="375" t="s">
+      <c r="BN6" s="406"/>
+      <c r="BO6" s="406"/>
+      <c r="BP6" s="406"/>
+      <c r="BQ6" s="407"/>
+      <c r="BR6" s="393" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="375" t="s">
+      <c r="BS6" s="393" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="376"/>
-      <c r="BU6" s="385"/>
+      <c r="BT6" s="391"/>
+      <c r="BU6" s="400"/>
       <c r="BW6" s="403"/>
-      <c r="BX6" s="385"/>
-      <c r="BY6" s="402"/>
-      <c r="BZ6" s="402"/>
+      <c r="BX6" s="400"/>
+      <c r="BY6" s="415"/>
+      <c r="BZ6" s="415"/>
       <c r="CA6" s="403"/>
-      <c r="CB6" s="376"/>
-      <c r="CC6" s="376"/>
-      <c r="CD6" s="376"/>
+      <c r="CB6" s="391"/>
+      <c r="CC6" s="391"/>
+      <c r="CD6" s="391"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="376"/>
-      <c r="B7" s="376"/>
-      <c r="C7" s="376"/>
-      <c r="D7" s="376"/>
-      <c r="E7" s="376"/>
-      <c r="F7" s="376"/>
-      <c r="G7" s="376"/>
-      <c r="H7" s="376"/>
-      <c r="I7" s="376"/>
-      <c r="J7" s="376"/>
-      <c r="K7" s="376"/>
-      <c r="L7" s="376"/>
-      <c r="M7" s="376"/>
-      <c r="N7" s="376"/>
-      <c r="O7" s="376"/>
-      <c r="P7" s="376"/>
-      <c r="Q7" s="376"/>
-      <c r="R7" s="376"/>
-      <c r="S7" s="376"/>
-      <c r="T7" s="376"/>
-      <c r="U7" s="376"/>
-      <c r="V7" s="386"/>
-      <c r="W7" s="393"/>
-      <c r="X7" s="376"/>
-      <c r="Y7" s="376"/>
-      <c r="Z7" s="376"/>
-      <c r="AA7" s="376"/>
-      <c r="AB7" s="376"/>
-      <c r="AC7" s="376"/>
-      <c r="AD7" s="376"/>
-      <c r="AE7" s="376"/>
-      <c r="AF7" s="376"/>
-      <c r="AG7" s="376"/>
-      <c r="AH7" s="376"/>
-      <c r="AI7" s="376"/>
-      <c r="AJ7" s="376"/>
-      <c r="AK7" s="385"/>
-      <c r="AL7" s="376"/>
-      <c r="AM7" s="376"/>
-      <c r="AN7" s="376"/>
-      <c r="AO7" s="376"/>
-      <c r="AP7" s="376"/>
-      <c r="AQ7" s="376"/>
-      <c r="AR7" s="376"/>
-      <c r="AS7" s="376"/>
-      <c r="AT7" s="376"/>
-      <c r="AU7" s="376"/>
-      <c r="AV7" s="376"/>
-      <c r="AW7" s="376"/>
-      <c r="AX7" s="376"/>
+      <c r="A7" s="391"/>
+      <c r="B7" s="391"/>
+      <c r="C7" s="391"/>
+      <c r="D7" s="391"/>
+      <c r="E7" s="391"/>
+      <c r="F7" s="391"/>
+      <c r="G7" s="391"/>
+      <c r="H7" s="391"/>
+      <c r="I7" s="391"/>
+      <c r="J7" s="391"/>
+      <c r="K7" s="391"/>
+      <c r="L7" s="391"/>
+      <c r="M7" s="391"/>
+      <c r="N7" s="391"/>
+      <c r="O7" s="391"/>
+      <c r="P7" s="391"/>
+      <c r="Q7" s="391"/>
+      <c r="R7" s="391"/>
+      <c r="S7" s="391"/>
+      <c r="T7" s="391"/>
+      <c r="U7" s="391"/>
+      <c r="V7" s="401"/>
+      <c r="W7" s="427"/>
+      <c r="X7" s="391"/>
+      <c r="Y7" s="391"/>
+      <c r="Z7" s="391"/>
+      <c r="AA7" s="391"/>
+      <c r="AB7" s="391"/>
+      <c r="AC7" s="391"/>
+      <c r="AD7" s="391"/>
+      <c r="AE7" s="391"/>
+      <c r="AF7" s="391"/>
+      <c r="AG7" s="391"/>
+      <c r="AH7" s="391"/>
+      <c r="AI7" s="391"/>
+      <c r="AJ7" s="391"/>
+      <c r="AK7" s="400"/>
+      <c r="AL7" s="391"/>
+      <c r="AM7" s="391"/>
+      <c r="AN7" s="391"/>
+      <c r="AO7" s="391"/>
+      <c r="AP7" s="391"/>
+      <c r="AQ7" s="391"/>
+      <c r="AR7" s="391"/>
+      <c r="AS7" s="391"/>
+      <c r="AT7" s="391"/>
+      <c r="AU7" s="391"/>
+      <c r="AV7" s="391"/>
+      <c r="AW7" s="391"/>
+      <c r="AX7" s="391"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12066,124 +12068,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="378" t="s">
+      <c r="BB7" s="405" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="381" t="s">
+      <c r="BC7" s="397" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="381" t="s">
+      <c r="BD7" s="397" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="407" t="s">
+      <c r="BE7" s="418" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="381" t="s">
+      <c r="BF7" s="397" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="381" t="s">
+      <c r="BG7" s="397" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="381" t="s">
+      <c r="BH7" s="397" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="381" t="s">
+      <c r="BI7" s="397" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="381" t="s">
+      <c r="BJ7" s="397" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="381" t="s">
+      <c r="BK7" s="397" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="409" t="s">
+      <c r="BL7" s="398" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="381" t="s">
+      <c r="BM7" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="378" t="s">
+      <c r="BN7" s="405" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="381" t="s">
+      <c r="BO7" s="397" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="378" t="s">
+      <c r="BP7" s="405" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="378" t="s">
+      <c r="BQ7" s="405" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="376"/>
-      <c r="BS7" s="376"/>
-      <c r="BT7" s="376"/>
-      <c r="BU7" s="385"/>
+      <c r="BR7" s="391"/>
+      <c r="BS7" s="391"/>
+      <c r="BT7" s="391"/>
+      <c r="BU7" s="400"/>
       <c r="BW7" s="403"/>
-      <c r="BX7" s="404"/>
-      <c r="BY7" s="405"/>
-      <c r="BZ7" s="405"/>
-      <c r="CA7" s="406"/>
-      <c r="CB7" s="376"/>
-      <c r="CC7" s="376"/>
-      <c r="CD7" s="376"/>
+      <c r="BX7" s="416"/>
+      <c r="BY7" s="417"/>
+      <c r="BZ7" s="417"/>
+      <c r="CA7" s="404"/>
+      <c r="CB7" s="391"/>
+      <c r="CC7" s="391"/>
+      <c r="CD7" s="391"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="377"/>
-      <c r="B8" s="377"/>
-      <c r="C8" s="377"/>
-      <c r="D8" s="377"/>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
-      <c r="G8" s="377"/>
-      <c r="H8" s="377"/>
-      <c r="I8" s="377"/>
-      <c r="J8" s="377"/>
-      <c r="K8" s="377"/>
-      <c r="L8" s="377"/>
-      <c r="M8" s="377"/>
-      <c r="N8" s="377"/>
-      <c r="O8" s="377"/>
-      <c r="P8" s="377"/>
-      <c r="Q8" s="377"/>
-      <c r="R8" s="377"/>
-      <c r="S8" s="377"/>
-      <c r="T8" s="377"/>
-      <c r="U8" s="377"/>
+      <c r="A8" s="394"/>
+      <c r="B8" s="394"/>
+      <c r="C8" s="394"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="394"/>
+      <c r="H8" s="394"/>
+      <c r="I8" s="394"/>
+      <c r="J8" s="394"/>
+      <c r="K8" s="394"/>
+      <c r="L8" s="394"/>
+      <c r="M8" s="394"/>
+      <c r="N8" s="394"/>
+      <c r="O8" s="394"/>
+      <c r="P8" s="394"/>
+      <c r="Q8" s="394"/>
+      <c r="R8" s="394"/>
+      <c r="S8" s="394"/>
+      <c r="T8" s="394"/>
+      <c r="U8" s="394"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="377"/>
-      <c r="Y8" s="377"/>
-      <c r="Z8" s="377"/>
-      <c r="AA8" s="377"/>
-      <c r="AB8" s="377"/>
-      <c r="AC8" s="377"/>
-      <c r="AD8" s="377"/>
-      <c r="AE8" s="377"/>
-      <c r="AF8" s="377"/>
-      <c r="AG8" s="377"/>
-      <c r="AH8" s="377"/>
-      <c r="AI8" s="377"/>
-      <c r="AJ8" s="377"/>
-      <c r="AK8" s="386"/>
-      <c r="AL8" s="377"/>
-      <c r="AM8" s="377"/>
-      <c r="AN8" s="377"/>
-      <c r="AO8" s="377"/>
-      <c r="AP8" s="377"/>
-      <c r="AQ8" s="377"/>
-      <c r="AR8" s="377"/>
-      <c r="AS8" s="377"/>
-      <c r="AT8" s="377"/>
-      <c r="AU8" s="377"/>
-      <c r="AV8" s="377"/>
-      <c r="AW8" s="377"/>
-      <c r="AX8" s="377"/>
+      <c r="X8" s="394"/>
+      <c r="Y8" s="394"/>
+      <c r="Z8" s="394"/>
+      <c r="AA8" s="394"/>
+      <c r="AB8" s="394"/>
+      <c r="AC8" s="394"/>
+      <c r="AD8" s="394"/>
+      <c r="AE8" s="394"/>
+      <c r="AF8" s="394"/>
+      <c r="AG8" s="394"/>
+      <c r="AH8" s="394"/>
+      <c r="AI8" s="394"/>
+      <c r="AJ8" s="394"/>
+      <c r="AK8" s="401"/>
+      <c r="AL8" s="394"/>
+      <c r="AM8" s="394"/>
+      <c r="AN8" s="394"/>
+      <c r="AO8" s="394"/>
+      <c r="AP8" s="394"/>
+      <c r="AQ8" s="394"/>
+      <c r="AR8" s="394"/>
+      <c r="AS8" s="394"/>
+      <c r="AT8" s="394"/>
+      <c r="AU8" s="394"/>
+      <c r="AV8" s="394"/>
+      <c r="AW8" s="394"/>
+      <c r="AX8" s="394"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12193,27 +12195,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="377"/>
-      <c r="BC8" s="377"/>
-      <c r="BD8" s="377"/>
-      <c r="BE8" s="377"/>
-      <c r="BF8" s="377"/>
-      <c r="BG8" s="377"/>
-      <c r="BH8" s="377"/>
-      <c r="BI8" s="377"/>
-      <c r="BJ8" s="377"/>
-      <c r="BK8" s="377"/>
-      <c r="BL8" s="377"/>
-      <c r="BM8" s="377"/>
-      <c r="BN8" s="377"/>
-      <c r="BO8" s="377"/>
-      <c r="BP8" s="377"/>
-      <c r="BQ8" s="377"/>
-      <c r="BR8" s="377"/>
-      <c r="BS8" s="377"/>
-      <c r="BT8" s="377"/>
-      <c r="BU8" s="386"/>
-      <c r="BW8" s="406"/>
+      <c r="BB8" s="394"/>
+      <c r="BC8" s="394"/>
+      <c r="BD8" s="394"/>
+      <c r="BE8" s="394"/>
+      <c r="BF8" s="394"/>
+      <c r="BG8" s="394"/>
+      <c r="BH8" s="394"/>
+      <c r="BI8" s="394"/>
+      <c r="BJ8" s="394"/>
+      <c r="BK8" s="394"/>
+      <c r="BL8" s="394"/>
+      <c r="BM8" s="394"/>
+      <c r="BN8" s="394"/>
+      <c r="BO8" s="394"/>
+      <c r="BP8" s="394"/>
+      <c r="BQ8" s="394"/>
+      <c r="BR8" s="394"/>
+      <c r="BS8" s="394"/>
+      <c r="BT8" s="394"/>
+      <c r="BU8" s="401"/>
+      <c r="BW8" s="404"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12226,9 +12228,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="398"/>
-      <c r="CC8" s="398"/>
-      <c r="CD8" s="398"/>
+      <c r="CB8" s="392"/>
+      <c r="CC8" s="392"/>
+      <c r="CD8" s="392"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14686,6 +14688,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="CD5:CD8"/>
     <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="AT5:AT8"/>
@@ -14702,72 +14770,6 @@
     <mergeCell ref="AY5:BQ5"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -14803,7 +14805,7 @@
     <col min="2" max="2" width="8.5" style="66" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="67" customWidth="1"/>
     <col min="4" max="4" width="34" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="5.5" style="68" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="15.1640625" style="68" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="5.5" style="69" bestFit="1" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6640625" style="64" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="64" customWidth="1"/>
@@ -14995,88 +14997,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="423"/>
-      <c r="B3" s="422"/>
-      <c r="C3" s="422"/>
-      <c r="D3" s="422"/>
-      <c r="E3" s="422"/>
-      <c r="F3" s="422"/>
-      <c r="G3" s="422"/>
-      <c r="H3" s="422"/>
-      <c r="I3" s="422"/>
-      <c r="J3" s="422"/>
-      <c r="K3" s="422"/>
-      <c r="L3" s="422"/>
-      <c r="M3" s="422"/>
-      <c r="N3" s="422"/>
-      <c r="O3" s="422"/>
-      <c r="P3" s="422"/>
-      <c r="Q3" s="422"/>
-      <c r="R3" s="422"/>
-      <c r="S3" s="422"/>
-      <c r="T3" s="422"/>
-      <c r="U3" s="422"/>
-      <c r="V3" s="422"/>
-      <c r="W3" s="422"/>
-      <c r="X3" s="422"/>
-      <c r="Y3" s="422"/>
-      <c r="Z3" s="422"/>
-      <c r="AA3" s="422"/>
-      <c r="AB3" s="422"/>
-      <c r="AC3" s="422"/>
-      <c r="AD3" s="422"/>
-      <c r="AE3" s="422"/>
-      <c r="AF3" s="422"/>
-      <c r="AG3" s="422"/>
-      <c r="AH3" s="422"/>
-      <c r="AI3" s="422"/>
-      <c r="AJ3" s="422"/>
-      <c r="AK3" s="422"/>
-      <c r="AL3" s="422"/>
-      <c r="AM3" s="422"/>
-      <c r="AN3" s="422"/>
-      <c r="AO3" s="422"/>
-      <c r="AP3" s="422"/>
-      <c r="AQ3" s="422"/>
-      <c r="AR3" s="422"/>
-      <c r="AS3" s="422"/>
-      <c r="AT3" s="422"/>
-      <c r="AU3" s="422"/>
-      <c r="AV3" s="422"/>
-      <c r="AW3" s="422"/>
-      <c r="AX3" s="422"/>
-      <c r="AY3" s="422"/>
-      <c r="AZ3" s="422"/>
-      <c r="BA3" s="422"/>
-      <c r="BB3" s="422"/>
-      <c r="BC3" s="422"/>
-      <c r="BD3" s="422"/>
-      <c r="BE3" s="422"/>
-      <c r="BF3" s="422"/>
-      <c r="BG3" s="422"/>
-      <c r="BH3" s="422"/>
-      <c r="BI3" s="422"/>
-      <c r="BJ3" s="422"/>
-      <c r="BK3" s="422"/>
-      <c r="BL3" s="422"/>
-      <c r="BM3" s="422"/>
-      <c r="BN3" s="422"/>
-      <c r="BO3" s="422"/>
-      <c r="BP3" s="422"/>
-      <c r="BQ3" s="422"/>
-      <c r="BR3" s="422"/>
-      <c r="BS3" s="422"/>
-      <c r="BT3" s="422"/>
-      <c r="BU3" s="422"/>
+      <c r="A3" s="438"/>
+      <c r="B3" s="437"/>
+      <c r="C3" s="437"/>
+      <c r="D3" s="437"/>
+      <c r="E3" s="437"/>
+      <c r="F3" s="437"/>
+      <c r="G3" s="437"/>
+      <c r="H3" s="437"/>
+      <c r="I3" s="437"/>
+      <c r="J3" s="437"/>
+      <c r="K3" s="437"/>
+      <c r="L3" s="437"/>
+      <c r="M3" s="437"/>
+      <c r="N3" s="437"/>
+      <c r="O3" s="437"/>
+      <c r="P3" s="437"/>
+      <c r="Q3" s="437"/>
+      <c r="R3" s="437"/>
+      <c r="S3" s="437"/>
+      <c r="T3" s="437"/>
+      <c r="U3" s="437"/>
+      <c r="V3" s="437"/>
+      <c r="W3" s="437"/>
+      <c r="X3" s="437"/>
+      <c r="Y3" s="437"/>
+      <c r="Z3" s="437"/>
+      <c r="AA3" s="437"/>
+      <c r="AB3" s="437"/>
+      <c r="AC3" s="437"/>
+      <c r="AD3" s="437"/>
+      <c r="AE3" s="437"/>
+      <c r="AF3" s="437"/>
+      <c r="AG3" s="437"/>
+      <c r="AH3" s="437"/>
+      <c r="AI3" s="437"/>
+      <c r="AJ3" s="437"/>
+      <c r="AK3" s="437"/>
+      <c r="AL3" s="437"/>
+      <c r="AM3" s="437"/>
+      <c r="AN3" s="437"/>
+      <c r="AO3" s="437"/>
+      <c r="AP3" s="437"/>
+      <c r="AQ3" s="437"/>
+      <c r="AR3" s="437"/>
+      <c r="AS3" s="437"/>
+      <c r="AT3" s="437"/>
+      <c r="AU3" s="437"/>
+      <c r="AV3" s="437"/>
+      <c r="AW3" s="437"/>
+      <c r="AX3" s="437"/>
+      <c r="AY3" s="437"/>
+      <c r="AZ3" s="437"/>
+      <c r="BA3" s="437"/>
+      <c r="BB3" s="437"/>
+      <c r="BC3" s="437"/>
+      <c r="BD3" s="437"/>
+      <c r="BE3" s="437"/>
+      <c r="BF3" s="437"/>
+      <c r="BG3" s="437"/>
+      <c r="BH3" s="437"/>
+      <c r="BI3" s="437"/>
+      <c r="BJ3" s="437"/>
+      <c r="BK3" s="437"/>
+      <c r="BL3" s="437"/>
+      <c r="BM3" s="437"/>
+      <c r="BN3" s="437"/>
+      <c r="BO3" s="437"/>
+      <c r="BP3" s="437"/>
+      <c r="BQ3" s="437"/>
+      <c r="BR3" s="437"/>
+      <c r="BS3" s="437"/>
+      <c r="BT3" s="437"/>
+      <c r="BU3" s="437"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="421" t="s">
+      <c r="BW3" s="436" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="422"/>
-      <c r="BY3" s="422"/>
-      <c r="BZ3" s="422"/>
-      <c r="CA3" s="422"/>
-      <c r="CB3" s="422"/>
+      <c r="BX3" s="437"/>
+      <c r="BY3" s="437"/>
+      <c r="BZ3" s="437"/>
+      <c r="CA3" s="437"/>
+      <c r="CB3" s="437"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15160,12 +15162,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="422"/>
-      <c r="BX4" s="422"/>
-      <c r="BY4" s="422"/>
-      <c r="BZ4" s="422"/>
-      <c r="CA4" s="422"/>
-      <c r="CB4" s="422"/>
+      <c r="BW4" s="437"/>
+      <c r="BX4" s="437"/>
+      <c r="BY4" s="437"/>
+      <c r="BZ4" s="437"/>
+      <c r="CA4" s="437"/>
+      <c r="CB4" s="437"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15243,12 +15245,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="352"/>
-      <c r="BX5" s="352"/>
-      <c r="BY5" s="352"/>
-      <c r="BZ5" s="352"/>
-      <c r="CA5" s="352"/>
-      <c r="CB5" s="352"/>
+      <c r="BW5" s="373"/>
+      <c r="BX5" s="373"/>
+      <c r="BY5" s="373"/>
+      <c r="BZ5" s="373"/>
+      <c r="CA5" s="373"/>
+      <c r="CB5" s="373"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15326,12 +15328,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="352"/>
-      <c r="BX6" s="352"/>
-      <c r="BY6" s="352"/>
-      <c r="BZ6" s="352"/>
-      <c r="CA6" s="352"/>
-      <c r="CB6" s="352"/>
+      <c r="BW6" s="373"/>
+      <c r="BX6" s="373"/>
+      <c r="BY6" s="373"/>
+      <c r="BZ6" s="373"/>
+      <c r="CA6" s="373"/>
+      <c r="CB6" s="373"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15419,358 +15421,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="383" t="s">
+      <c r="A8" s="422" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="394" t="s">
+      <c r="B8" s="421" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="382" t="s">
+      <c r="C8" s="395" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="389" t="s">
+      <c r="D8" s="420" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="389" t="s">
+      <c r="E8" s="420" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="419" t="s">
+      <c r="F8" s="440" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="416" t="s">
+      <c r="G8" s="429" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="367" t="s">
+      <c r="H8" s="434" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="367" t="s">
+      <c r="I8" s="434" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="416" t="s">
+      <c r="J8" s="429" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="420" t="s">
+      <c r="K8" s="441" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="379"/>
-      <c r="M8" s="379"/>
-      <c r="N8" s="379"/>
-      <c r="O8" s="379"/>
-      <c r="P8" s="379"/>
-      <c r="Q8" s="379"/>
-      <c r="R8" s="379"/>
-      <c r="S8" s="379"/>
-      <c r="T8" s="379"/>
-      <c r="U8" s="379"/>
-      <c r="V8" s="379"/>
-      <c r="W8" s="379"/>
-      <c r="X8" s="379"/>
-      <c r="Y8" s="416" t="s">
+      <c r="L8" s="406"/>
+      <c r="M8" s="406"/>
+      <c r="N8" s="406"/>
+      <c r="O8" s="406"/>
+      <c r="P8" s="406"/>
+      <c r="Q8" s="406"/>
+      <c r="R8" s="406"/>
+      <c r="S8" s="406"/>
+      <c r="T8" s="406"/>
+      <c r="U8" s="406"/>
+      <c r="V8" s="406"/>
+      <c r="W8" s="406"/>
+      <c r="X8" s="406"/>
+      <c r="Y8" s="429" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="379"/>
-      <c r="AA8" s="379"/>
-      <c r="AB8" s="379"/>
-      <c r="AC8" s="379"/>
-      <c r="AD8" s="379"/>
-      <c r="AE8" s="379"/>
-      <c r="AF8" s="379"/>
-      <c r="AG8" s="379"/>
-      <c r="AH8" s="379"/>
-      <c r="AI8" s="379"/>
-      <c r="AJ8" s="379"/>
-      <c r="AK8" s="379"/>
-      <c r="AL8" s="379"/>
-      <c r="AM8" s="379"/>
-      <c r="AN8" s="379"/>
-      <c r="AO8" s="380"/>
-      <c r="AP8" s="416" t="s">
+      <c r="Z8" s="406"/>
+      <c r="AA8" s="406"/>
+      <c r="AB8" s="406"/>
+      <c r="AC8" s="406"/>
+      <c r="AD8" s="406"/>
+      <c r="AE8" s="406"/>
+      <c r="AF8" s="406"/>
+      <c r="AG8" s="406"/>
+      <c r="AH8" s="406"/>
+      <c r="AI8" s="406"/>
+      <c r="AJ8" s="406"/>
+      <c r="AK8" s="406"/>
+      <c r="AL8" s="406"/>
+      <c r="AM8" s="406"/>
+      <c r="AN8" s="406"/>
+      <c r="AO8" s="407"/>
+      <c r="AP8" s="429" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="416" t="s">
+      <c r="AQ8" s="429" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="416" t="s">
+      <c r="AR8" s="429" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="416" t="s">
+      <c r="AS8" s="429" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="416" t="s">
+      <c r="AT8" s="429" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="416" t="s">
+      <c r="AU8" s="429" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="382" t="s">
+      <c r="AV8" s="395" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="382" t="s">
+      <c r="AW8" s="395" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="382" t="s">
+      <c r="AX8" s="395" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="378" t="s">
+      <c r="AY8" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="379"/>
-      <c r="BA8" s="379"/>
-      <c r="BB8" s="379"/>
-      <c r="BC8" s="379"/>
-      <c r="BD8" s="379"/>
-      <c r="BE8" s="379"/>
-      <c r="BF8" s="379"/>
-      <c r="BG8" s="379"/>
-      <c r="BH8" s="379"/>
-      <c r="BI8" s="379"/>
-      <c r="BJ8" s="379"/>
-      <c r="BK8" s="379"/>
-      <c r="BL8" s="379"/>
-      <c r="BM8" s="379"/>
-      <c r="BN8" s="379"/>
-      <c r="BO8" s="379"/>
-      <c r="BP8" s="380"/>
-      <c r="BQ8" s="399" t="s">
+      <c r="AZ8" s="406"/>
+      <c r="BA8" s="406"/>
+      <c r="BB8" s="406"/>
+      <c r="BC8" s="406"/>
+      <c r="BD8" s="406"/>
+      <c r="BE8" s="406"/>
+      <c r="BF8" s="406"/>
+      <c r="BG8" s="406"/>
+      <c r="BH8" s="406"/>
+      <c r="BI8" s="406"/>
+      <c r="BJ8" s="406"/>
+      <c r="BK8" s="406"/>
+      <c r="BL8" s="406"/>
+      <c r="BM8" s="406"/>
+      <c r="BN8" s="406"/>
+      <c r="BO8" s="406"/>
+      <c r="BP8" s="407"/>
+      <c r="BQ8" s="411" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="392"/>
-      <c r="BS8" s="378" t="s">
+      <c r="BR8" s="412"/>
+      <c r="BS8" s="405" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="378" t="s">
+      <c r="BT8" s="405" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="410" t="s">
+      <c r="BU8" s="399" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="411" t="s">
+      <c r="BW8" s="402" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="400" t="s">
+      <c r="BX8" s="413" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="401"/>
-      <c r="BZ8" s="401"/>
-      <c r="CA8" s="392"/>
-      <c r="CB8" s="412" t="s">
+      <c r="BY8" s="414"/>
+      <c r="BZ8" s="414"/>
+      <c r="CA8" s="412"/>
+      <c r="CB8" s="408" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="397" t="s">
+      <c r="CC8" s="390" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="397" t="s">
+      <c r="CD8" s="390" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="376"/>
-      <c r="B9" s="376"/>
-      <c r="C9" s="376"/>
-      <c r="D9" s="376"/>
-      <c r="E9" s="376"/>
-      <c r="F9" s="376"/>
-      <c r="G9" s="376"/>
-      <c r="H9" s="376"/>
-      <c r="I9" s="376"/>
-      <c r="J9" s="376"/>
-      <c r="K9" s="413" t="s">
+      <c r="A9" s="391"/>
+      <c r="B9" s="391"/>
+      <c r="C9" s="391"/>
+      <c r="D9" s="391"/>
+      <c r="E9" s="391"/>
+      <c r="F9" s="391"/>
+      <c r="G9" s="391"/>
+      <c r="H9" s="391"/>
+      <c r="I9" s="391"/>
+      <c r="J9" s="391"/>
+      <c r="K9" s="431" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="413" t="s">
+      <c r="L9" s="431" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="413" t="s">
+      <c r="M9" s="431" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="413" t="s">
+      <c r="N9" s="431" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="413" t="s">
+      <c r="O9" s="431" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="413" t="s">
+      <c r="P9" s="431" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="413" t="s">
+      <c r="Q9" s="431" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="413" t="s">
+      <c r="R9" s="431" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="413" t="s">
+      <c r="S9" s="431" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="413" t="s">
+      <c r="T9" s="431" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="413" t="s">
+      <c r="U9" s="431" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="425" t="s">
+      <c r="V9" s="435" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="392"/>
-      <c r="X9" s="413" t="s">
+      <c r="W9" s="412"/>
+      <c r="X9" s="431" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="415" t="s">
+      <c r="Y9" s="428" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="415" t="s">
+      <c r="Z9" s="428" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="415" t="s">
+      <c r="AA9" s="428" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="415" t="s">
+      <c r="AB9" s="428" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="341" t="s">
+      <c r="AC9" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="341" t="s">
+      <c r="AD9" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="341" t="s">
+      <c r="AE9" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="341" t="s">
+      <c r="AF9" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="415" t="s">
+      <c r="AG9" s="428" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="341" t="s">
+      <c r="AH9" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="341" t="s">
+      <c r="AI9" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="415" t="s">
+      <c r="AJ9" s="428" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="384" t="s">
+      <c r="AK9" s="423" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="382" t="s">
+      <c r="AL9" s="395" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="415" t="s">
+      <c r="AM9" s="428" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="388" t="s">
+      <c r="AN9" s="425" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="382" t="s">
+      <c r="AO9" s="395" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="376"/>
-      <c r="AQ9" s="376"/>
-      <c r="AR9" s="376"/>
-      <c r="AS9" s="376"/>
-      <c r="AT9" s="376"/>
-      <c r="AU9" s="376"/>
-      <c r="AV9" s="376"/>
-      <c r="AW9" s="376"/>
-      <c r="AX9" s="376"/>
-      <c r="AY9" s="378" t="s">
+      <c r="AP9" s="391"/>
+      <c r="AQ9" s="391"/>
+      <c r="AR9" s="391"/>
+      <c r="AS9" s="391"/>
+      <c r="AT9" s="391"/>
+      <c r="AU9" s="391"/>
+      <c r="AV9" s="391"/>
+      <c r="AW9" s="391"/>
+      <c r="AX9" s="391"/>
+      <c r="AY9" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="379"/>
-      <c r="BA9" s="379"/>
-      <c r="BB9" s="379"/>
-      <c r="BC9" s="379"/>
-      <c r="BD9" s="379"/>
-      <c r="BE9" s="379"/>
-      <c r="BF9" s="379"/>
-      <c r="BG9" s="379"/>
-      <c r="BH9" s="379"/>
-      <c r="BI9" s="379"/>
-      <c r="BJ9" s="380"/>
-      <c r="BK9" s="378" t="s">
+      <c r="AZ9" s="406"/>
+      <c r="BA9" s="406"/>
+      <c r="BB9" s="406"/>
+      <c r="BC9" s="406"/>
+      <c r="BD9" s="406"/>
+      <c r="BE9" s="406"/>
+      <c r="BF9" s="406"/>
+      <c r="BG9" s="406"/>
+      <c r="BH9" s="406"/>
+      <c r="BI9" s="406"/>
+      <c r="BJ9" s="407"/>
+      <c r="BK9" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="379"/>
-      <c r="BM9" s="379"/>
-      <c r="BN9" s="379"/>
-      <c r="BO9" s="379"/>
-      <c r="BP9" s="380"/>
-      <c r="BQ9" s="375" t="s">
+      <c r="BL9" s="406"/>
+      <c r="BM9" s="406"/>
+      <c r="BN9" s="406"/>
+      <c r="BO9" s="406"/>
+      <c r="BP9" s="407"/>
+      <c r="BQ9" s="393" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="375" t="s">
+      <c r="BR9" s="393" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="376"/>
-      <c r="BT9" s="376"/>
-      <c r="BU9" s="385"/>
+      <c r="BS9" s="391"/>
+      <c r="BT9" s="391"/>
+      <c r="BU9" s="400"/>
       <c r="BV9" s="114"/>
       <c r="BW9" s="403"/>
-      <c r="BX9" s="385"/>
-      <c r="BY9" s="417"/>
-      <c r="BZ9" s="417"/>
+      <c r="BX9" s="400"/>
+      <c r="BY9" s="442"/>
+      <c r="BZ9" s="442"/>
       <c r="CA9" s="403"/>
-      <c r="CB9" s="376"/>
-      <c r="CC9" s="376"/>
-      <c r="CD9" s="376"/>
+      <c r="CB9" s="391"/>
+      <c r="CC9" s="391"/>
+      <c r="CD9" s="391"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="376"/>
-      <c r="B10" s="376"/>
-      <c r="C10" s="376"/>
-      <c r="D10" s="376"/>
-      <c r="E10" s="376"/>
-      <c r="F10" s="376"/>
-      <c r="G10" s="376"/>
-      <c r="H10" s="376"/>
-      <c r="I10" s="376"/>
-      <c r="J10" s="376"/>
-      <c r="K10" s="376"/>
-      <c r="L10" s="376"/>
-      <c r="M10" s="376"/>
-      <c r="N10" s="376"/>
-      <c r="O10" s="376"/>
-      <c r="P10" s="376"/>
-      <c r="Q10" s="376"/>
-      <c r="R10" s="376"/>
-      <c r="S10" s="376"/>
-      <c r="T10" s="376"/>
-      <c r="U10" s="376"/>
-      <c r="V10" s="386"/>
-      <c r="W10" s="393"/>
-      <c r="X10" s="376"/>
-      <c r="Y10" s="376"/>
-      <c r="Z10" s="376"/>
-      <c r="AA10" s="376"/>
-      <c r="AB10" s="376"/>
-      <c r="AC10" s="376"/>
-      <c r="AD10" s="376"/>
-      <c r="AE10" s="376"/>
-      <c r="AF10" s="376"/>
-      <c r="AG10" s="376"/>
-      <c r="AH10" s="376"/>
-      <c r="AI10" s="376"/>
-      <c r="AJ10" s="376"/>
-      <c r="AK10" s="385"/>
-      <c r="AL10" s="376"/>
-      <c r="AM10" s="376"/>
-      <c r="AN10" s="376"/>
-      <c r="AO10" s="376"/>
-      <c r="AP10" s="376"/>
-      <c r="AQ10" s="376"/>
-      <c r="AR10" s="376"/>
-      <c r="AS10" s="376"/>
-      <c r="AT10" s="376"/>
-      <c r="AU10" s="376"/>
-      <c r="AV10" s="376"/>
-      <c r="AW10" s="376"/>
-      <c r="AX10" s="376"/>
+      <c r="A10" s="391"/>
+      <c r="B10" s="391"/>
+      <c r="C10" s="391"/>
+      <c r="D10" s="391"/>
+      <c r="E10" s="391"/>
+      <c r="F10" s="391"/>
+      <c r="G10" s="391"/>
+      <c r="H10" s="391"/>
+      <c r="I10" s="391"/>
+      <c r="J10" s="391"/>
+      <c r="K10" s="391"/>
+      <c r="L10" s="391"/>
+      <c r="M10" s="391"/>
+      <c r="N10" s="391"/>
+      <c r="O10" s="391"/>
+      <c r="P10" s="391"/>
+      <c r="Q10" s="391"/>
+      <c r="R10" s="391"/>
+      <c r="S10" s="391"/>
+      <c r="T10" s="391"/>
+      <c r="U10" s="391"/>
+      <c r="V10" s="401"/>
+      <c r="W10" s="427"/>
+      <c r="X10" s="391"/>
+      <c r="Y10" s="391"/>
+      <c r="Z10" s="391"/>
+      <c r="AA10" s="391"/>
+      <c r="AB10" s="391"/>
+      <c r="AC10" s="391"/>
+      <c r="AD10" s="391"/>
+      <c r="AE10" s="391"/>
+      <c r="AF10" s="391"/>
+      <c r="AG10" s="391"/>
+      <c r="AH10" s="391"/>
+      <c r="AI10" s="391"/>
+      <c r="AJ10" s="391"/>
+      <c r="AK10" s="400"/>
+      <c r="AL10" s="391"/>
+      <c r="AM10" s="391"/>
+      <c r="AN10" s="391"/>
+      <c r="AO10" s="391"/>
+      <c r="AP10" s="391"/>
+      <c r="AQ10" s="391"/>
+      <c r="AR10" s="391"/>
+      <c r="AS10" s="391"/>
+      <c r="AT10" s="391"/>
+      <c r="AU10" s="391"/>
+      <c r="AV10" s="391"/>
+      <c r="AW10" s="391"/>
+      <c r="AX10" s="391"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15780,123 +15782,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="424" t="s">
+      <c r="BB10" s="439" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="414" t="s">
+      <c r="BC10" s="432" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="414" t="s">
+      <c r="BD10" s="432" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="414" t="s">
+      <c r="BE10" s="432" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="414" t="s">
+      <c r="BF10" s="432" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="414" t="s">
+      <c r="BG10" s="432" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="414" t="s">
+      <c r="BH10" s="432" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="414" t="s">
+      <c r="BI10" s="432" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="426" t="s">
+      <c r="BJ10" s="430" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="414" t="s">
+      <c r="BK10" s="432" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="418" t="s">
+      <c r="BL10" s="433" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="414" t="s">
+      <c r="BM10" s="432" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="418" t="s">
+      <c r="BN10" s="433" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="418" t="s">
+      <c r="BO10" s="433" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="378" t="s">
+      <c r="BP10" s="405" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="376"/>
-      <c r="BR10" s="376"/>
-      <c r="BS10" s="376"/>
-      <c r="BT10" s="376"/>
-      <c r="BU10" s="385"/>
+      <c r="BQ10" s="391"/>
+      <c r="BR10" s="391"/>
+      <c r="BS10" s="391"/>
+      <c r="BT10" s="391"/>
+      <c r="BU10" s="400"/>
       <c r="BV10" s="114"/>
       <c r="BW10" s="403"/>
-      <c r="BX10" s="404"/>
-      <c r="BY10" s="405"/>
-      <c r="BZ10" s="405"/>
-      <c r="CA10" s="406"/>
-      <c r="CB10" s="376"/>
-      <c r="CC10" s="376"/>
-      <c r="CD10" s="376"/>
+      <c r="BX10" s="416"/>
+      <c r="BY10" s="417"/>
+      <c r="BZ10" s="417"/>
+      <c r="CA10" s="404"/>
+      <c r="CB10" s="391"/>
+      <c r="CC10" s="391"/>
+      <c r="CD10" s="391"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="377"/>
-      <c r="B11" s="377"/>
-      <c r="C11" s="377"/>
-      <c r="D11" s="377"/>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
-      <c r="G11" s="377"/>
-      <c r="H11" s="377"/>
-      <c r="I11" s="377"/>
-      <c r="J11" s="377"/>
-      <c r="K11" s="377"/>
-      <c r="L11" s="377"/>
-      <c r="M11" s="377"/>
-      <c r="N11" s="377"/>
-      <c r="O11" s="377"/>
-      <c r="P11" s="377"/>
-      <c r="Q11" s="377"/>
-      <c r="R11" s="377"/>
-      <c r="S11" s="377"/>
-      <c r="T11" s="377"/>
-      <c r="U11" s="377"/>
+      <c r="A11" s="394"/>
+      <c r="B11" s="394"/>
+      <c r="C11" s="394"/>
+      <c r="D11" s="394"/>
+      <c r="E11" s="394"/>
+      <c r="F11" s="394"/>
+      <c r="G11" s="394"/>
+      <c r="H11" s="394"/>
+      <c r="I11" s="394"/>
+      <c r="J11" s="394"/>
+      <c r="K11" s="394"/>
+      <c r="L11" s="394"/>
+      <c r="M11" s="394"/>
+      <c r="N11" s="394"/>
+      <c r="O11" s="394"/>
+      <c r="P11" s="394"/>
+      <c r="Q11" s="394"/>
+      <c r="R11" s="394"/>
+      <c r="S11" s="394"/>
+      <c r="T11" s="394"/>
+      <c r="U11" s="394"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="377"/>
-      <c r="Y11" s="377"/>
-      <c r="Z11" s="377"/>
-      <c r="AA11" s="377"/>
-      <c r="AB11" s="377"/>
-      <c r="AC11" s="377"/>
-      <c r="AD11" s="377"/>
-      <c r="AE11" s="377"/>
-      <c r="AF11" s="377"/>
-      <c r="AG11" s="377"/>
-      <c r="AH11" s="377"/>
-      <c r="AI11" s="377"/>
-      <c r="AJ11" s="377"/>
-      <c r="AK11" s="386"/>
-      <c r="AL11" s="377"/>
-      <c r="AM11" s="377"/>
-      <c r="AN11" s="377"/>
-      <c r="AO11" s="377"/>
-      <c r="AP11" s="377"/>
-      <c r="AQ11" s="377"/>
-      <c r="AR11" s="377"/>
-      <c r="AS11" s="377"/>
-      <c r="AT11" s="377"/>
-      <c r="AU11" s="377"/>
-      <c r="AV11" s="377"/>
-      <c r="AW11" s="377"/>
-      <c r="AX11" s="377"/>
+      <c r="X11" s="394"/>
+      <c r="Y11" s="394"/>
+      <c r="Z11" s="394"/>
+      <c r="AA11" s="394"/>
+      <c r="AB11" s="394"/>
+      <c r="AC11" s="394"/>
+      <c r="AD11" s="394"/>
+      <c r="AE11" s="394"/>
+      <c r="AF11" s="394"/>
+      <c r="AG11" s="394"/>
+      <c r="AH11" s="394"/>
+      <c r="AI11" s="394"/>
+      <c r="AJ11" s="394"/>
+      <c r="AK11" s="401"/>
+      <c r="AL11" s="394"/>
+      <c r="AM11" s="394"/>
+      <c r="AN11" s="394"/>
+      <c r="AO11" s="394"/>
+      <c r="AP11" s="394"/>
+      <c r="AQ11" s="394"/>
+      <c r="AR11" s="394"/>
+      <c r="AS11" s="394"/>
+      <c r="AT11" s="394"/>
+      <c r="AU11" s="394"/>
+      <c r="AV11" s="394"/>
+      <c r="AW11" s="394"/>
+      <c r="AX11" s="394"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15906,28 +15908,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="377"/>
-      <c r="BC11" s="377"/>
-      <c r="BD11" s="377"/>
-      <c r="BE11" s="377"/>
-      <c r="BF11" s="377"/>
-      <c r="BG11" s="377"/>
-      <c r="BH11" s="377"/>
-      <c r="BI11" s="377"/>
-      <c r="BJ11" s="377"/>
-      <c r="BK11" s="377"/>
-      <c r="BL11" s="377"/>
-      <c r="BM11" s="377"/>
-      <c r="BN11" s="377"/>
-      <c r="BO11" s="377"/>
-      <c r="BP11" s="377"/>
-      <c r="BQ11" s="377"/>
-      <c r="BR11" s="377"/>
-      <c r="BS11" s="377"/>
-      <c r="BT11" s="377"/>
-      <c r="BU11" s="386"/>
+      <c r="BB11" s="394"/>
+      <c r="BC11" s="394"/>
+      <c r="BD11" s="394"/>
+      <c r="BE11" s="394"/>
+      <c r="BF11" s="394"/>
+      <c r="BG11" s="394"/>
+      <c r="BH11" s="394"/>
+      <c r="BI11" s="394"/>
+      <c r="BJ11" s="394"/>
+      <c r="BK11" s="394"/>
+      <c r="BL11" s="394"/>
+      <c r="BM11" s="394"/>
+      <c r="BN11" s="394"/>
+      <c r="BO11" s="394"/>
+      <c r="BP11" s="394"/>
+      <c r="BQ11" s="394"/>
+      <c r="BR11" s="394"/>
+      <c r="BS11" s="394"/>
+      <c r="BT11" s="394"/>
+      <c r="BU11" s="401"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="406"/>
+      <c r="BW11" s="404"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15940,9 +15942,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="398"/>
-      <c r="CC11" s="398"/>
-      <c r="CD11" s="398"/>
+      <c r="CB11" s="392"/>
+      <c r="CC11" s="392"/>
+      <c r="CD11" s="392"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18343,14 +18345,64 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="G8:G11"/>
     <mergeCell ref="BS8:BS11"/>
@@ -18367,64 +18419,14 @@
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18654,87 +18656,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="408"/>
-      <c r="B3" s="396"/>
-      <c r="C3" s="396"/>
-      <c r="D3" s="396"/>
-      <c r="E3" s="396"/>
-      <c r="F3" s="396"/>
-      <c r="G3" s="396"/>
-      <c r="H3" s="396"/>
-      <c r="I3" s="396"/>
-      <c r="J3" s="396"/>
-      <c r="K3" s="396"/>
-      <c r="L3" s="396"/>
-      <c r="M3" s="396"/>
-      <c r="N3" s="396"/>
-      <c r="O3" s="396"/>
-      <c r="P3" s="396"/>
-      <c r="Q3" s="396"/>
-      <c r="R3" s="396"/>
-      <c r="S3" s="396"/>
-      <c r="T3" s="396"/>
-      <c r="U3" s="396"/>
-      <c r="V3" s="396"/>
-      <c r="W3" s="396"/>
-      <c r="X3" s="396"/>
-      <c r="Y3" s="396"/>
-      <c r="Z3" s="396"/>
-      <c r="AA3" s="396"/>
-      <c r="AB3" s="396"/>
-      <c r="AC3" s="396"/>
-      <c r="AD3" s="396"/>
-      <c r="AE3" s="396"/>
-      <c r="AF3" s="396"/>
-      <c r="AG3" s="396"/>
-      <c r="AH3" s="396"/>
-      <c r="AI3" s="396"/>
-      <c r="AJ3" s="396"/>
-      <c r="AK3" s="396"/>
-      <c r="AL3" s="396"/>
-      <c r="AM3" s="396"/>
-      <c r="AN3" s="396"/>
-      <c r="AO3" s="396"/>
-      <c r="AP3" s="396"/>
-      <c r="AQ3" s="396"/>
-      <c r="AR3" s="396"/>
-      <c r="AS3" s="396"/>
-      <c r="AT3" s="396"/>
-      <c r="AU3" s="396"/>
-      <c r="AV3" s="396"/>
-      <c r="AW3" s="396"/>
-      <c r="AX3" s="396"/>
-      <c r="AY3" s="396"/>
-      <c r="AZ3" s="396"/>
-      <c r="BA3" s="396"/>
-      <c r="BB3" s="396"/>
-      <c r="BC3" s="396"/>
-      <c r="BD3" s="396"/>
-      <c r="BE3" s="396"/>
-      <c r="BF3" s="396"/>
-      <c r="BG3" s="396"/>
-      <c r="BH3" s="396"/>
-      <c r="BI3" s="396"/>
-      <c r="BJ3" s="396"/>
-      <c r="BK3" s="396"/>
-      <c r="BL3" s="396"/>
-      <c r="BM3" s="396"/>
-      <c r="BN3" s="396"/>
-      <c r="BO3" s="396"/>
-      <c r="BP3" s="396"/>
-      <c r="BQ3" s="396"/>
-      <c r="BR3" s="396"/>
-      <c r="BS3" s="396"/>
-      <c r="BT3" s="396"/>
-      <c r="BU3" s="396"/>
-      <c r="BW3" s="395" t="s">
+      <c r="A3" s="419"/>
+      <c r="B3" s="410"/>
+      <c r="C3" s="410"/>
+      <c r="D3" s="410"/>
+      <c r="E3" s="410"/>
+      <c r="F3" s="410"/>
+      <c r="G3" s="410"/>
+      <c r="H3" s="410"/>
+      <c r="I3" s="410"/>
+      <c r="J3" s="410"/>
+      <c r="K3" s="410"/>
+      <c r="L3" s="410"/>
+      <c r="M3" s="410"/>
+      <c r="N3" s="410"/>
+      <c r="O3" s="410"/>
+      <c r="P3" s="410"/>
+      <c r="Q3" s="410"/>
+      <c r="R3" s="410"/>
+      <c r="S3" s="410"/>
+      <c r="T3" s="410"/>
+      <c r="U3" s="410"/>
+      <c r="V3" s="410"/>
+      <c r="W3" s="410"/>
+      <c r="X3" s="410"/>
+      <c r="Y3" s="410"/>
+      <c r="Z3" s="410"/>
+      <c r="AA3" s="410"/>
+      <c r="AB3" s="410"/>
+      <c r="AC3" s="410"/>
+      <c r="AD3" s="410"/>
+      <c r="AE3" s="410"/>
+      <c r="AF3" s="410"/>
+      <c r="AG3" s="410"/>
+      <c r="AH3" s="410"/>
+      <c r="AI3" s="410"/>
+      <c r="AJ3" s="410"/>
+      <c r="AK3" s="410"/>
+      <c r="AL3" s="410"/>
+      <c r="AM3" s="410"/>
+      <c r="AN3" s="410"/>
+      <c r="AO3" s="410"/>
+      <c r="AP3" s="410"/>
+      <c r="AQ3" s="410"/>
+      <c r="AR3" s="410"/>
+      <c r="AS3" s="410"/>
+      <c r="AT3" s="410"/>
+      <c r="AU3" s="410"/>
+      <c r="AV3" s="410"/>
+      <c r="AW3" s="410"/>
+      <c r="AX3" s="410"/>
+      <c r="AY3" s="410"/>
+      <c r="AZ3" s="410"/>
+      <c r="BA3" s="410"/>
+      <c r="BB3" s="410"/>
+      <c r="BC3" s="410"/>
+      <c r="BD3" s="410"/>
+      <c r="BE3" s="410"/>
+      <c r="BF3" s="410"/>
+      <c r="BG3" s="410"/>
+      <c r="BH3" s="410"/>
+      <c r="BI3" s="410"/>
+      <c r="BJ3" s="410"/>
+      <c r="BK3" s="410"/>
+      <c r="BL3" s="410"/>
+      <c r="BM3" s="410"/>
+      <c r="BN3" s="410"/>
+      <c r="BO3" s="410"/>
+      <c r="BP3" s="410"/>
+      <c r="BQ3" s="410"/>
+      <c r="BR3" s="410"/>
+      <c r="BS3" s="410"/>
+      <c r="BT3" s="410"/>
+      <c r="BU3" s="410"/>
+      <c r="BW3" s="409" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="396"/>
-      <c r="BY3" s="396"/>
-      <c r="BZ3" s="396"/>
-      <c r="CA3" s="396"/>
-      <c r="CB3" s="396"/>
+      <c r="BX3" s="410"/>
+      <c r="BY3" s="410"/>
+      <c r="BZ3" s="410"/>
+      <c r="CA3" s="410"/>
+      <c r="CB3" s="410"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18817,35 +18819,35 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="396"/>
-      <c r="BX4" s="396"/>
-      <c r="BY4" s="396"/>
-      <c r="BZ4" s="396"/>
-      <c r="CA4" s="396"/>
-      <c r="CB4" s="396"/>
+      <c r="BW4" s="410"/>
+      <c r="BX4" s="410"/>
+      <c r="BY4" s="410"/>
+      <c r="BZ4" s="410"/>
+      <c r="CA4" s="410"/>
+      <c r="CB4" s="410"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="422" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="394" t="s">
+      <c r="B5" s="421" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="382" t="s">
+      <c r="C5" s="395" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="389" t="s">
+      <c r="D5" s="420" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="389" t="s">
+      <c r="E5" s="420" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="419" t="s">
+      <c r="F5" s="440" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="382" t="s">
+      <c r="G5" s="395" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="338" t="s">
@@ -18854,186 +18856,186 @@
       <c r="I5" s="338" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="382" t="s">
+      <c r="J5" s="395" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="387" t="s">
+      <c r="K5" s="424" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="379"/>
-      <c r="M5" s="379"/>
-      <c r="N5" s="379"/>
-      <c r="O5" s="379"/>
-      <c r="P5" s="379"/>
-      <c r="Q5" s="379"/>
-      <c r="R5" s="379"/>
-      <c r="S5" s="379"/>
-      <c r="T5" s="379"/>
-      <c r="U5" s="379"/>
-      <c r="V5" s="379"/>
-      <c r="W5" s="379"/>
-      <c r="X5" s="379"/>
-      <c r="Y5" s="382" t="s">
+      <c r="L5" s="406"/>
+      <c r="M5" s="406"/>
+      <c r="N5" s="406"/>
+      <c r="O5" s="406"/>
+      <c r="P5" s="406"/>
+      <c r="Q5" s="406"/>
+      <c r="R5" s="406"/>
+      <c r="S5" s="406"/>
+      <c r="T5" s="406"/>
+      <c r="U5" s="406"/>
+      <c r="V5" s="406"/>
+      <c r="W5" s="406"/>
+      <c r="X5" s="406"/>
+      <c r="Y5" s="395" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="379"/>
-      <c r="AA5" s="379"/>
-      <c r="AB5" s="379"/>
-      <c r="AC5" s="379"/>
-      <c r="AD5" s="379"/>
-      <c r="AE5" s="379"/>
-      <c r="AF5" s="379"/>
-      <c r="AG5" s="379"/>
-      <c r="AH5" s="379"/>
-      <c r="AI5" s="379"/>
-      <c r="AJ5" s="379"/>
-      <c r="AK5" s="379"/>
-      <c r="AL5" s="379"/>
-      <c r="AM5" s="379"/>
-      <c r="AN5" s="379"/>
-      <c r="AO5" s="380"/>
-      <c r="AP5" s="382" t="s">
+      <c r="Z5" s="406"/>
+      <c r="AA5" s="406"/>
+      <c r="AB5" s="406"/>
+      <c r="AC5" s="406"/>
+      <c r="AD5" s="406"/>
+      <c r="AE5" s="406"/>
+      <c r="AF5" s="406"/>
+      <c r="AG5" s="406"/>
+      <c r="AH5" s="406"/>
+      <c r="AI5" s="406"/>
+      <c r="AJ5" s="406"/>
+      <c r="AK5" s="406"/>
+      <c r="AL5" s="406"/>
+      <c r="AM5" s="406"/>
+      <c r="AN5" s="406"/>
+      <c r="AO5" s="407"/>
+      <c r="AP5" s="395" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="382" t="s">
+      <c r="AQ5" s="395" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="382" t="s">
+      <c r="AR5" s="395" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="382" t="s">
+      <c r="AS5" s="395" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="382" t="s">
+      <c r="AT5" s="395" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="382" t="s">
+      <c r="AU5" s="395" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="382" t="s">
+      <c r="AV5" s="395" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="382" t="s">
+      <c r="AW5" s="395" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="382" t="s">
+      <c r="AX5" s="395" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="378" t="s">
+      <c r="AY5" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="379"/>
-      <c r="BA5" s="379"/>
-      <c r="BB5" s="379"/>
-      <c r="BC5" s="379"/>
-      <c r="BD5" s="379"/>
-      <c r="BE5" s="379"/>
-      <c r="BF5" s="379"/>
-      <c r="BG5" s="379"/>
-      <c r="BH5" s="379"/>
-      <c r="BI5" s="379"/>
-      <c r="BJ5" s="379"/>
-      <c r="BK5" s="379"/>
-      <c r="BL5" s="379"/>
-      <c r="BM5" s="379"/>
-      <c r="BN5" s="379"/>
-      <c r="BO5" s="379"/>
-      <c r="BP5" s="380"/>
-      <c r="BQ5" s="399" t="s">
+      <c r="AZ5" s="406"/>
+      <c r="BA5" s="406"/>
+      <c r="BB5" s="406"/>
+      <c r="BC5" s="406"/>
+      <c r="BD5" s="406"/>
+      <c r="BE5" s="406"/>
+      <c r="BF5" s="406"/>
+      <c r="BG5" s="406"/>
+      <c r="BH5" s="406"/>
+      <c r="BI5" s="406"/>
+      <c r="BJ5" s="406"/>
+      <c r="BK5" s="406"/>
+      <c r="BL5" s="406"/>
+      <c r="BM5" s="406"/>
+      <c r="BN5" s="406"/>
+      <c r="BO5" s="406"/>
+      <c r="BP5" s="407"/>
+      <c r="BQ5" s="411" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="392"/>
-      <c r="BS5" s="378" t="s">
+      <c r="BR5" s="412"/>
+      <c r="BS5" s="405" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="378" t="s">
+      <c r="BT5" s="405" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="410" t="s">
+      <c r="BU5" s="399" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="411" t="s">
+      <c r="BW5" s="402" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="400" t="s">
+      <c r="BX5" s="413" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="401"/>
-      <c r="BZ5" s="401"/>
-      <c r="CA5" s="392"/>
-      <c r="CB5" s="412" t="s">
+      <c r="BY5" s="414"/>
+      <c r="BZ5" s="414"/>
+      <c r="CA5" s="412"/>
+      <c r="CB5" s="408" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="397" t="s">
+      <c r="CC5" s="390" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="397" t="s">
+      <c r="CD5" s="390" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="376"/>
-      <c r="B6" s="376"/>
-      <c r="C6" s="376"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="376"/>
-      <c r="F6" s="376"/>
-      <c r="G6" s="376"/>
-      <c r="H6" s="376"/>
-      <c r="I6" s="376"/>
-      <c r="J6" s="376"/>
-      <c r="K6" s="390" t="s">
+      <c r="A6" s="391"/>
+      <c r="B6" s="391"/>
+      <c r="C6" s="391"/>
+      <c r="D6" s="391"/>
+      <c r="E6" s="391"/>
+      <c r="F6" s="391"/>
+      <c r="G6" s="391"/>
+      <c r="H6" s="391"/>
+      <c r="I6" s="391"/>
+      <c r="J6" s="391"/>
+      <c r="K6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="390" t="s">
+      <c r="L6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="390" t="s">
+      <c r="M6" s="396" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="390" t="s">
+      <c r="N6" s="396" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="390" t="s">
+      <c r="O6" s="396" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="390" t="s">
+      <c r="P6" s="396" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="390" t="s">
+      <c r="Q6" s="396" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="390" t="s">
+      <c r="R6" s="396" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="390" t="s">
+      <c r="S6" s="396" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="390" t="s">
+      <c r="T6" s="396" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="390" t="s">
+      <c r="U6" s="396" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="391" t="s">
+      <c r="V6" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="392"/>
-      <c r="X6" s="390" t="s">
+      <c r="W6" s="412"/>
+      <c r="X6" s="396" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="382" t="s">
+      <c r="Y6" s="395" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="382" t="s">
+      <c r="Z6" s="395" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="382" t="s">
+      <c r="AA6" s="395" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="382" t="s">
+      <c r="AB6" s="395" t="s">
         <v>50</v>
       </c>
       <c r="AC6" s="338" t="s">
@@ -19048,7 +19050,7 @@
       <c r="AF6" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="382" t="s">
+      <c r="AG6" s="395" t="s">
         <v>55</v>
       </c>
       <c r="AH6" s="338" t="s">
@@ -19057,126 +19059,126 @@
       <c r="AI6" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="382" t="s">
+      <c r="AJ6" s="395" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="384" t="s">
+      <c r="AK6" s="423" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="382" t="s">
+      <c r="AL6" s="395" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="382" t="s">
+      <c r="AM6" s="395" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="388" t="s">
+      <c r="AN6" s="425" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="382" t="s">
+      <c r="AO6" s="395" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="376"/>
-      <c r="AQ6" s="376"/>
-      <c r="AR6" s="376"/>
-      <c r="AS6" s="376"/>
-      <c r="AT6" s="376"/>
-      <c r="AU6" s="376"/>
-      <c r="AV6" s="376"/>
-      <c r="AW6" s="376"/>
-      <c r="AX6" s="376"/>
-      <c r="AY6" s="378" t="s">
+      <c r="AP6" s="391"/>
+      <c r="AQ6" s="391"/>
+      <c r="AR6" s="391"/>
+      <c r="AS6" s="391"/>
+      <c r="AT6" s="391"/>
+      <c r="AU6" s="391"/>
+      <c r="AV6" s="391"/>
+      <c r="AW6" s="391"/>
+      <c r="AX6" s="391"/>
+      <c r="AY6" s="405" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="379"/>
-      <c r="BA6" s="379"/>
-      <c r="BB6" s="379"/>
-      <c r="BC6" s="379"/>
-      <c r="BD6" s="379"/>
-      <c r="BE6" s="379"/>
-      <c r="BF6" s="379"/>
-      <c r="BG6" s="379"/>
-      <c r="BH6" s="379"/>
-      <c r="BI6" s="379"/>
-      <c r="BJ6" s="380"/>
-      <c r="BK6" s="378" t="s">
+      <c r="AZ6" s="406"/>
+      <c r="BA6" s="406"/>
+      <c r="BB6" s="406"/>
+      <c r="BC6" s="406"/>
+      <c r="BD6" s="406"/>
+      <c r="BE6" s="406"/>
+      <c r="BF6" s="406"/>
+      <c r="BG6" s="406"/>
+      <c r="BH6" s="406"/>
+      <c r="BI6" s="406"/>
+      <c r="BJ6" s="407"/>
+      <c r="BK6" s="405" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="379"/>
-      <c r="BM6" s="379"/>
-      <c r="BN6" s="379"/>
-      <c r="BO6" s="379"/>
-      <c r="BP6" s="380"/>
-      <c r="BQ6" s="375" t="s">
+      <c r="BL6" s="406"/>
+      <c r="BM6" s="406"/>
+      <c r="BN6" s="406"/>
+      <c r="BO6" s="406"/>
+      <c r="BP6" s="407"/>
+      <c r="BQ6" s="393" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="375" t="s">
+      <c r="BR6" s="393" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="376"/>
-      <c r="BT6" s="376"/>
-      <c r="BU6" s="385"/>
+      <c r="BS6" s="391"/>
+      <c r="BT6" s="391"/>
+      <c r="BU6" s="400"/>
       <c r="BW6" s="403"/>
-      <c r="BX6" s="385"/>
-      <c r="BY6" s="402"/>
-      <c r="BZ6" s="402"/>
+      <c r="BX6" s="400"/>
+      <c r="BY6" s="415"/>
+      <c r="BZ6" s="415"/>
       <c r="CA6" s="403"/>
-      <c r="CB6" s="376"/>
-      <c r="CC6" s="376"/>
-      <c r="CD6" s="376"/>
+      <c r="CB6" s="391"/>
+      <c r="CC6" s="391"/>
+      <c r="CD6" s="391"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="376"/>
-      <c r="B7" s="376"/>
-      <c r="C7" s="376"/>
-      <c r="D7" s="376"/>
-      <c r="E7" s="376"/>
-      <c r="F7" s="376"/>
-      <c r="G7" s="376"/>
-      <c r="H7" s="376"/>
-      <c r="I7" s="376"/>
-      <c r="J7" s="376"/>
-      <c r="K7" s="376"/>
-      <c r="L7" s="376"/>
-      <c r="M7" s="376"/>
-      <c r="N7" s="376"/>
-      <c r="O7" s="376"/>
-      <c r="P7" s="376"/>
-      <c r="Q7" s="376"/>
-      <c r="R7" s="376"/>
-      <c r="S7" s="376"/>
-      <c r="T7" s="376"/>
-      <c r="U7" s="376"/>
-      <c r="V7" s="386"/>
-      <c r="W7" s="393"/>
-      <c r="X7" s="376"/>
-      <c r="Y7" s="376"/>
-      <c r="Z7" s="376"/>
-      <c r="AA7" s="376"/>
-      <c r="AB7" s="376"/>
-      <c r="AC7" s="376"/>
-      <c r="AD7" s="376"/>
-      <c r="AE7" s="376"/>
-      <c r="AF7" s="376"/>
-      <c r="AG7" s="376"/>
-      <c r="AH7" s="376"/>
-      <c r="AI7" s="376"/>
-      <c r="AJ7" s="376"/>
-      <c r="AK7" s="385"/>
-      <c r="AL7" s="376"/>
-      <c r="AM7" s="376"/>
-      <c r="AN7" s="376"/>
-      <c r="AO7" s="376"/>
-      <c r="AP7" s="376"/>
-      <c r="AQ7" s="376"/>
-      <c r="AR7" s="376"/>
-      <c r="AS7" s="376"/>
-      <c r="AT7" s="376"/>
-      <c r="AU7" s="376"/>
-      <c r="AV7" s="376"/>
-      <c r="AW7" s="376"/>
-      <c r="AX7" s="376"/>
+      <c r="A7" s="391"/>
+      <c r="B7" s="391"/>
+      <c r="C7" s="391"/>
+      <c r="D7" s="391"/>
+      <c r="E7" s="391"/>
+      <c r="F7" s="391"/>
+      <c r="G7" s="391"/>
+      <c r="H7" s="391"/>
+      <c r="I7" s="391"/>
+      <c r="J7" s="391"/>
+      <c r="K7" s="391"/>
+      <c r="L7" s="391"/>
+      <c r="M7" s="391"/>
+      <c r="N7" s="391"/>
+      <c r="O7" s="391"/>
+      <c r="P7" s="391"/>
+      <c r="Q7" s="391"/>
+      <c r="R7" s="391"/>
+      <c r="S7" s="391"/>
+      <c r="T7" s="391"/>
+      <c r="U7" s="391"/>
+      <c r="V7" s="401"/>
+      <c r="W7" s="427"/>
+      <c r="X7" s="391"/>
+      <c r="Y7" s="391"/>
+      <c r="Z7" s="391"/>
+      <c r="AA7" s="391"/>
+      <c r="AB7" s="391"/>
+      <c r="AC7" s="391"/>
+      <c r="AD7" s="391"/>
+      <c r="AE7" s="391"/>
+      <c r="AF7" s="391"/>
+      <c r="AG7" s="391"/>
+      <c r="AH7" s="391"/>
+      <c r="AI7" s="391"/>
+      <c r="AJ7" s="391"/>
+      <c r="AK7" s="400"/>
+      <c r="AL7" s="391"/>
+      <c r="AM7" s="391"/>
+      <c r="AN7" s="391"/>
+      <c r="AO7" s="391"/>
+      <c r="AP7" s="391"/>
+      <c r="AQ7" s="391"/>
+      <c r="AR7" s="391"/>
+      <c r="AS7" s="391"/>
+      <c r="AT7" s="391"/>
+      <c r="AU7" s="391"/>
+      <c r="AV7" s="391"/>
+      <c r="AW7" s="391"/>
+      <c r="AX7" s="391"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19186,122 +19188,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="378" t="s">
+      <c r="BB7" s="405" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="381" t="s">
+      <c r="BC7" s="397" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="381" t="s">
+      <c r="BD7" s="397" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="381" t="s">
+      <c r="BE7" s="397" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="381" t="s">
+      <c r="BF7" s="397" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="381" t="s">
+      <c r="BG7" s="397" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="381" t="s">
+      <c r="BH7" s="397" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="381" t="s">
+      <c r="BI7" s="397" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="409" t="s">
+      <c r="BJ7" s="398" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="381" t="s">
+      <c r="BK7" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="378" t="s">
+      <c r="BL7" s="405" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="381" t="s">
+      <c r="BM7" s="397" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="378" t="s">
+      <c r="BN7" s="405" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="378" t="s">
+      <c r="BO7" s="405" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="378" t="s">
+      <c r="BP7" s="405" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="376"/>
-      <c r="BR7" s="376"/>
-      <c r="BS7" s="376"/>
-      <c r="BT7" s="376"/>
-      <c r="BU7" s="385"/>
+      <c r="BQ7" s="391"/>
+      <c r="BR7" s="391"/>
+      <c r="BS7" s="391"/>
+      <c r="BT7" s="391"/>
+      <c r="BU7" s="400"/>
       <c r="BW7" s="403"/>
-      <c r="BX7" s="404"/>
-      <c r="BY7" s="405"/>
-      <c r="BZ7" s="405"/>
-      <c r="CA7" s="406"/>
-      <c r="CB7" s="376"/>
-      <c r="CC7" s="376"/>
-      <c r="CD7" s="376"/>
+      <c r="BX7" s="416"/>
+      <c r="BY7" s="417"/>
+      <c r="BZ7" s="417"/>
+      <c r="CA7" s="404"/>
+      <c r="CB7" s="391"/>
+      <c r="CC7" s="391"/>
+      <c r="CD7" s="391"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="377"/>
-      <c r="B8" s="377"/>
-      <c r="C8" s="377"/>
-      <c r="D8" s="377"/>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
-      <c r="G8" s="377"/>
-      <c r="H8" s="377"/>
-      <c r="I8" s="377"/>
-      <c r="J8" s="377"/>
-      <c r="K8" s="377"/>
-      <c r="L8" s="377"/>
-      <c r="M8" s="377"/>
-      <c r="N8" s="377"/>
-      <c r="O8" s="377"/>
-      <c r="P8" s="377"/>
-      <c r="Q8" s="377"/>
-      <c r="R8" s="377"/>
-      <c r="S8" s="377"/>
-      <c r="T8" s="377"/>
-      <c r="U8" s="377"/>
+      <c r="A8" s="394"/>
+      <c r="B8" s="394"/>
+      <c r="C8" s="394"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="394"/>
+      <c r="H8" s="394"/>
+      <c r="I8" s="394"/>
+      <c r="J8" s="394"/>
+      <c r="K8" s="394"/>
+      <c r="L8" s="394"/>
+      <c r="M8" s="394"/>
+      <c r="N8" s="394"/>
+      <c r="O8" s="394"/>
+      <c r="P8" s="394"/>
+      <c r="Q8" s="394"/>
+      <c r="R8" s="394"/>
+      <c r="S8" s="394"/>
+      <c r="T8" s="394"/>
+      <c r="U8" s="394"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="377"/>
-      <c r="Y8" s="377"/>
-      <c r="Z8" s="377"/>
-      <c r="AA8" s="377"/>
-      <c r="AB8" s="377"/>
-      <c r="AC8" s="377"/>
-      <c r="AD8" s="377"/>
-      <c r="AE8" s="377"/>
-      <c r="AF8" s="377"/>
-      <c r="AG8" s="377"/>
-      <c r="AH8" s="377"/>
-      <c r="AI8" s="377"/>
-      <c r="AJ8" s="377"/>
-      <c r="AK8" s="386"/>
-      <c r="AL8" s="377"/>
-      <c r="AM8" s="377"/>
-      <c r="AN8" s="377"/>
-      <c r="AO8" s="377"/>
-      <c r="AP8" s="377"/>
-      <c r="AQ8" s="377"/>
-      <c r="AR8" s="377"/>
-      <c r="AS8" s="377"/>
-      <c r="AT8" s="377"/>
-      <c r="AU8" s="377"/>
-      <c r="AV8" s="377"/>
-      <c r="AW8" s="377"/>
-      <c r="AX8" s="377"/>
+      <c r="X8" s="394"/>
+      <c r="Y8" s="394"/>
+      <c r="Z8" s="394"/>
+      <c r="AA8" s="394"/>
+      <c r="AB8" s="394"/>
+      <c r="AC8" s="394"/>
+      <c r="AD8" s="394"/>
+      <c r="AE8" s="394"/>
+      <c r="AF8" s="394"/>
+      <c r="AG8" s="394"/>
+      <c r="AH8" s="394"/>
+      <c r="AI8" s="394"/>
+      <c r="AJ8" s="394"/>
+      <c r="AK8" s="401"/>
+      <c r="AL8" s="394"/>
+      <c r="AM8" s="394"/>
+      <c r="AN8" s="394"/>
+      <c r="AO8" s="394"/>
+      <c r="AP8" s="394"/>
+      <c r="AQ8" s="394"/>
+      <c r="AR8" s="394"/>
+      <c r="AS8" s="394"/>
+      <c r="AT8" s="394"/>
+      <c r="AU8" s="394"/>
+      <c r="AV8" s="394"/>
+      <c r="AW8" s="394"/>
+      <c r="AX8" s="394"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19311,27 +19313,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="377"/>
-      <c r="BC8" s="377"/>
-      <c r="BD8" s="377"/>
-      <c r="BE8" s="377"/>
-      <c r="BF8" s="377"/>
-      <c r="BG8" s="377"/>
-      <c r="BH8" s="377"/>
-      <c r="BI8" s="377"/>
-      <c r="BJ8" s="377"/>
-      <c r="BK8" s="377"/>
-      <c r="BL8" s="377"/>
-      <c r="BM8" s="377"/>
-      <c r="BN8" s="377"/>
-      <c r="BO8" s="377"/>
-      <c r="BP8" s="377"/>
-      <c r="BQ8" s="377"/>
-      <c r="BR8" s="377"/>
-      <c r="BS8" s="377"/>
-      <c r="BT8" s="377"/>
-      <c r="BU8" s="386"/>
-      <c r="BW8" s="406"/>
+      <c r="BB8" s="394"/>
+      <c r="BC8" s="394"/>
+      <c r="BD8" s="394"/>
+      <c r="BE8" s="394"/>
+      <c r="BF8" s="394"/>
+      <c r="BG8" s="394"/>
+      <c r="BH8" s="394"/>
+      <c r="BI8" s="394"/>
+      <c r="BJ8" s="394"/>
+      <c r="BK8" s="394"/>
+      <c r="BL8" s="394"/>
+      <c r="BM8" s="394"/>
+      <c r="BN8" s="394"/>
+      <c r="BO8" s="394"/>
+      <c r="BP8" s="394"/>
+      <c r="BQ8" s="394"/>
+      <c r="BR8" s="394"/>
+      <c r="BS8" s="394"/>
+      <c r="BT8" s="394"/>
+      <c r="BU8" s="401"/>
+      <c r="BW8" s="404"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19344,9 +19346,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="398"/>
-      <c r="CC8" s="398"/>
-      <c r="CD8" s="398"/>
+      <c r="CB8" s="392"/>
+      <c r="CC8" s="392"/>
+      <c r="CD8" s="392"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21353,6 +21355,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
     <mergeCell ref="CD5:CD8"/>
     <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="AT5:AT8"/>
@@ -21369,72 +21437,6 @@
     <mergeCell ref="AY5:BP5"/>
     <mergeCell ref="AU5:AU8"/>
     <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46BFC66-376C-2D4E-82EA-624E9CAD1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1697A5-2187-404F-8B2F-E858923EE07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38540" yWindow="660" windowWidth="38100" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5062,7 +5062,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="78">
+  <fonts count="76">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5487,18 +5487,7 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="7"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF00B0F0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -5532,13 +5521,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="7.5"/>
       <color rgb="FFFF0000"/>
@@ -5552,6 +5534,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -5867,7 +5856,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="445">
+  <cellXfs count="439">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6597,9 +6586,6 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6741,22 +6727,19 @@
     <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="71" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="69" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6775,17 +6758,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6796,26 +6778,19 @@
     <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="68" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6824,28 +6799,16 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="76" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6893,11 +6856,8 @@
     <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7029,8 +6989,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="77" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -7632,989 +7607,989 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" s="240" customFormat="1" ht="23.25" customHeight="1" outlineLevel="1">
-      <c r="A1" s="283" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="I1" s="287"/>
-      <c r="K1" s="288"/>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="289"/>
-      <c r="Z1" s="289"/>
-      <c r="AA1" s="289"/>
-      <c r="AB1" s="289"/>
-      <c r="AC1" s="289"/>
-      <c r="AD1" s="289"/>
-      <c r="AE1" s="289"/>
-      <c r="AF1" s="289"/>
-      <c r="AG1" s="289"/>
-      <c r="AH1" s="289"/>
-      <c r="AI1" s="289"/>
-      <c r="AJ1" s="289"/>
-      <c r="AK1" s="289"/>
-      <c r="AL1" s="289"/>
-      <c r="AM1" s="289"/>
-      <c r="AN1" s="289"/>
-      <c r="AO1" s="289"/>
-      <c r="AP1" s="289"/>
-      <c r="AQ1" s="289"/>
-      <c r="AR1" s="289"/>
-      <c r="AS1" s="289"/>
-      <c r="AT1" s="289"/>
-      <c r="AU1" s="289"/>
-      <c r="AV1" s="289"/>
-      <c r="AW1" s="289"/>
-      <c r="AX1" s="289"/>
-      <c r="AY1" s="289"/>
-      <c r="AZ1" s="289"/>
-      <c r="BA1" s="289"/>
-      <c r="BB1" s="289"/>
-      <c r="BC1" s="289"/>
-      <c r="BD1" s="290"/>
-      <c r="BE1" s="289"/>
-      <c r="BF1" s="290"/>
-      <c r="BG1" s="289"/>
-      <c r="BH1" s="289"/>
-      <c r="BI1" s="289"/>
-      <c r="BJ1" s="289"/>
-      <c r="BK1" s="289"/>
-      <c r="BL1" s="289"/>
-      <c r="BM1" s="289"/>
-      <c r="BN1" s="289"/>
-      <c r="BO1" s="289"/>
-      <c r="BP1" s="291"/>
-      <c r="BQ1" s="289"/>
-      <c r="BR1" s="289"/>
-      <c r="BS1" s="289"/>
-      <c r="BU1" s="289"/>
-      <c r="BV1" s="289"/>
-      <c r="BW1" s="292"/>
-      <c r="BX1" s="292"/>
-      <c r="BY1" s="292"/>
-      <c r="BZ1" s="292"/>
-      <c r="CA1" s="292"/>
-      <c r="CB1" s="293"/>
-      <c r="CC1" s="293"/>
-      <c r="CD1" s="293"/>
+      <c r="A1" s="282" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="283"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="I1" s="286"/>
+      <c r="K1" s="287"/>
+      <c r="L1" s="287"/>
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="288"/>
+      <c r="AI1" s="288"/>
+      <c r="AJ1" s="288"/>
+      <c r="AK1" s="288"/>
+      <c r="AL1" s="288"/>
+      <c r="AM1" s="288"/>
+      <c r="AN1" s="288"/>
+      <c r="AO1" s="288"/>
+      <c r="AP1" s="288"/>
+      <c r="AQ1" s="288"/>
+      <c r="AR1" s="288"/>
+      <c r="AS1" s="288"/>
+      <c r="AT1" s="288"/>
+      <c r="AU1" s="288"/>
+      <c r="AV1" s="288"/>
+      <c r="AW1" s="288"/>
+      <c r="AX1" s="288"/>
+      <c r="AY1" s="288"/>
+      <c r="AZ1" s="288"/>
+      <c r="BA1" s="288"/>
+      <c r="BB1" s="288"/>
+      <c r="BC1" s="288"/>
+      <c r="BD1" s="289"/>
+      <c r="BE1" s="288"/>
+      <c r="BF1" s="289"/>
+      <c r="BG1" s="288"/>
+      <c r="BH1" s="288"/>
+      <c r="BI1" s="288"/>
+      <c r="BJ1" s="288"/>
+      <c r="BK1" s="288"/>
+      <c r="BL1" s="288"/>
+      <c r="BM1" s="288"/>
+      <c r="BN1" s="288"/>
+      <c r="BO1" s="288"/>
+      <c r="BP1" s="290"/>
+      <c r="BQ1" s="288"/>
+      <c r="BR1" s="288"/>
+      <c r="BS1" s="288"/>
+      <c r="BU1" s="288"/>
+      <c r="BV1" s="288"/>
+      <c r="BW1" s="291"/>
+      <c r="BX1" s="291"/>
+      <c r="BY1" s="291"/>
+      <c r="BZ1" s="291"/>
+      <c r="CA1" s="291"/>
+      <c r="CB1" s="292"/>
+      <c r="CC1" s="292"/>
+      <c r="CD1" s="292"/>
     </row>
     <row r="2" spans="1:87" s="240" customFormat="1" ht="19.25" customHeight="1" outlineLevel="1">
-      <c r="A2" s="294" t="s">
+      <c r="A2" s="293" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="284"/>
-      <c r="C2" s="295"/>
-      <c r="D2" s="286"/>
-      <c r="E2" s="286"/>
-      <c r="F2" s="286"/>
-      <c r="I2" s="287"/>
-      <c r="K2" s="288"/>
-      <c r="L2" s="288"/>
-      <c r="M2" s="288"/>
-      <c r="N2" s="288"/>
-      <c r="O2" s="288"/>
-      <c r="P2" s="288"/>
-      <c r="Q2" s="288"/>
-      <c r="R2" s="288"/>
-      <c r="S2" s="288"/>
-      <c r="T2" s="288"/>
-      <c r="U2" s="288"/>
-      <c r="V2" s="288"/>
-      <c r="W2" s="288"/>
-      <c r="X2" s="288"/>
-      <c r="Y2" s="289"/>
-      <c r="Z2" s="289"/>
-      <c r="AA2" s="289"/>
-      <c r="AB2" s="289"/>
-      <c r="AC2" s="289"/>
-      <c r="AD2" s="289"/>
-      <c r="AE2" s="289"/>
-      <c r="AF2" s="289"/>
-      <c r="AG2" s="289"/>
-      <c r="AH2" s="289"/>
-      <c r="AI2" s="289"/>
-      <c r="AJ2" s="289"/>
-      <c r="AK2" s="289"/>
-      <c r="AL2" s="289"/>
-      <c r="AM2" s="289"/>
-      <c r="AN2" s="289"/>
-      <c r="AO2" s="289"/>
-      <c r="AP2" s="289"/>
-      <c r="AQ2" s="289"/>
-      <c r="AR2" s="289"/>
-      <c r="AS2" s="289"/>
-      <c r="AT2" s="289"/>
-      <c r="AU2" s="289"/>
-      <c r="AV2" s="289"/>
-      <c r="AW2" s="289"/>
-      <c r="AX2" s="289"/>
-      <c r="AY2" s="289"/>
-      <c r="AZ2" s="289"/>
-      <c r="BA2" s="289"/>
-      <c r="BB2" s="289"/>
-      <c r="BC2" s="289"/>
-      <c r="BD2" s="290"/>
-      <c r="BE2" s="289"/>
-      <c r="BF2" s="289"/>
-      <c r="BG2" s="289"/>
-      <c r="BH2" s="289"/>
-      <c r="BI2" s="289"/>
-      <c r="BJ2" s="289"/>
-      <c r="BK2" s="289"/>
-      <c r="BL2" s="289"/>
-      <c r="BM2" s="289"/>
-      <c r="BN2" s="289"/>
-      <c r="BO2" s="289"/>
-      <c r="BP2" s="289"/>
-      <c r="BQ2" s="289"/>
-      <c r="BR2" s="289"/>
-      <c r="BS2" s="289"/>
-      <c r="BT2" s="289"/>
-      <c r="BU2" s="289"/>
-      <c r="BV2" s="289"/>
-      <c r="BW2" s="296"/>
-      <c r="BX2" s="296"/>
-      <c r="BY2" s="296"/>
-      <c r="BZ2" s="296"/>
-      <c r="CA2" s="296"/>
-      <c r="CB2" s="295"/>
-      <c r="CC2" s="295"/>
-      <c r="CD2" s="295"/>
+      <c r="B2" s="283"/>
+      <c r="C2" s="294"/>
+      <c r="D2" s="285"/>
+      <c r="E2" s="285"/>
+      <c r="F2" s="285"/>
+      <c r="I2" s="286"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
+      <c r="P2" s="287"/>
+      <c r="Q2" s="287"/>
+      <c r="R2" s="287"/>
+      <c r="S2" s="287"/>
+      <c r="T2" s="287"/>
+      <c r="U2" s="287"/>
+      <c r="V2" s="287"/>
+      <c r="W2" s="287"/>
+      <c r="X2" s="287"/>
+      <c r="Y2" s="288"/>
+      <c r="Z2" s="288"/>
+      <c r="AA2" s="288"/>
+      <c r="AB2" s="288"/>
+      <c r="AC2" s="288"/>
+      <c r="AD2" s="288"/>
+      <c r="AE2" s="288"/>
+      <c r="AF2" s="288"/>
+      <c r="AG2" s="288"/>
+      <c r="AH2" s="288"/>
+      <c r="AI2" s="288"/>
+      <c r="AJ2" s="288"/>
+      <c r="AK2" s="288"/>
+      <c r="AL2" s="288"/>
+      <c r="AM2" s="288"/>
+      <c r="AN2" s="288"/>
+      <c r="AO2" s="288"/>
+      <c r="AP2" s="288"/>
+      <c r="AQ2" s="288"/>
+      <c r="AR2" s="288"/>
+      <c r="AS2" s="288"/>
+      <c r="AT2" s="288"/>
+      <c r="AU2" s="288"/>
+      <c r="AV2" s="288"/>
+      <c r="AW2" s="288"/>
+      <c r="AX2" s="288"/>
+      <c r="AY2" s="288"/>
+      <c r="AZ2" s="288"/>
+      <c r="BA2" s="288"/>
+      <c r="BB2" s="288"/>
+      <c r="BC2" s="288"/>
+      <c r="BD2" s="289"/>
+      <c r="BE2" s="288"/>
+      <c r="BF2" s="288"/>
+      <c r="BG2" s="288"/>
+      <c r="BH2" s="288"/>
+      <c r="BI2" s="288"/>
+      <c r="BJ2" s="288"/>
+      <c r="BK2" s="288"/>
+      <c r="BL2" s="288"/>
+      <c r="BM2" s="288"/>
+      <c r="BN2" s="288"/>
+      <c r="BO2" s="288"/>
+      <c r="BP2" s="288"/>
+      <c r="BQ2" s="288"/>
+      <c r="BR2" s="288"/>
+      <c r="BS2" s="288"/>
+      <c r="BT2" s="288"/>
+      <c r="BU2" s="288"/>
+      <c r="BV2" s="288"/>
+      <c r="BW2" s="295"/>
+      <c r="BX2" s="295"/>
+      <c r="BY2" s="295"/>
+      <c r="BZ2" s="295"/>
+      <c r="CA2" s="295"/>
+      <c r="CB2" s="294"/>
+      <c r="CC2" s="294"/>
+      <c r="CD2" s="294"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="374"/>
-      <c r="B3" s="373"/>
-      <c r="C3" s="373"/>
-      <c r="D3" s="373"/>
-      <c r="E3" s="373"/>
-      <c r="F3" s="373"/>
-      <c r="G3" s="373"/>
-      <c r="H3" s="373"/>
-      <c r="I3" s="373"/>
-      <c r="J3" s="373"/>
-      <c r="K3" s="373"/>
-      <c r="L3" s="373"/>
-      <c r="M3" s="373"/>
-      <c r="N3" s="373"/>
-      <c r="O3" s="373"/>
-      <c r="P3" s="373"/>
-      <c r="Q3" s="373"/>
-      <c r="R3" s="373"/>
-      <c r="S3" s="373"/>
-      <c r="T3" s="373"/>
-      <c r="U3" s="373"/>
-      <c r="V3" s="373"/>
-      <c r="W3" s="373"/>
-      <c r="X3" s="373"/>
-      <c r="Y3" s="373"/>
-      <c r="Z3" s="373"/>
-      <c r="AA3" s="373"/>
-      <c r="AB3" s="373"/>
-      <c r="AC3" s="373"/>
-      <c r="AD3" s="373"/>
-      <c r="AE3" s="373"/>
-      <c r="AF3" s="373"/>
-      <c r="AG3" s="373"/>
-      <c r="AH3" s="373"/>
-      <c r="AI3" s="373"/>
-      <c r="AJ3" s="373"/>
-      <c r="AK3" s="373"/>
-      <c r="AL3" s="373"/>
-      <c r="AM3" s="373"/>
-      <c r="AN3" s="373"/>
-      <c r="AO3" s="373"/>
-      <c r="AP3" s="373"/>
-      <c r="AQ3" s="373"/>
-      <c r="AR3" s="373"/>
-      <c r="AS3" s="373"/>
-      <c r="AT3" s="373"/>
-      <c r="AU3" s="373"/>
-      <c r="AV3" s="373"/>
-      <c r="AW3" s="373"/>
-      <c r="AX3" s="373"/>
-      <c r="AY3" s="373"/>
-      <c r="AZ3" s="373"/>
-      <c r="BA3" s="373"/>
-      <c r="BB3" s="373"/>
-      <c r="BC3" s="373"/>
-      <c r="BD3" s="373"/>
-      <c r="BE3" s="373"/>
-      <c r="BF3" s="373"/>
-      <c r="BG3" s="373"/>
-      <c r="BH3" s="373"/>
-      <c r="BI3" s="373"/>
-      <c r="BJ3" s="373"/>
-      <c r="BK3" s="373"/>
-      <c r="BL3" s="373"/>
-      <c r="BM3" s="373"/>
-      <c r="BN3" s="373"/>
-      <c r="BO3" s="373"/>
-      <c r="BP3" s="373"/>
-      <c r="BQ3" s="373"/>
-      <c r="BR3" s="373"/>
-      <c r="BS3" s="373"/>
-      <c r="BT3" s="373"/>
-      <c r="BU3" s="373"/>
-      <c r="BV3" s="297"/>
-      <c r="BW3" s="372" t="s">
+      <c r="A3" s="364"/>
+      <c r="B3" s="363"/>
+      <c r="C3" s="363"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
+      <c r="F3" s="363"/>
+      <c r="G3" s="363"/>
+      <c r="H3" s="363"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="363"/>
+      <c r="K3" s="363"/>
+      <c r="L3" s="363"/>
+      <c r="M3" s="363"/>
+      <c r="N3" s="363"/>
+      <c r="O3" s="363"/>
+      <c r="P3" s="363"/>
+      <c r="Q3" s="363"/>
+      <c r="R3" s="363"/>
+      <c r="S3" s="363"/>
+      <c r="T3" s="363"/>
+      <c r="U3" s="363"/>
+      <c r="V3" s="363"/>
+      <c r="W3" s="363"/>
+      <c r="X3" s="363"/>
+      <c r="Y3" s="363"/>
+      <c r="Z3" s="363"/>
+      <c r="AA3" s="363"/>
+      <c r="AB3" s="363"/>
+      <c r="AC3" s="363"/>
+      <c r="AD3" s="363"/>
+      <c r="AE3" s="363"/>
+      <c r="AF3" s="363"/>
+      <c r="AG3" s="363"/>
+      <c r="AH3" s="363"/>
+      <c r="AI3" s="363"/>
+      <c r="AJ3" s="363"/>
+      <c r="AK3" s="363"/>
+      <c r="AL3" s="363"/>
+      <c r="AM3" s="363"/>
+      <c r="AN3" s="363"/>
+      <c r="AO3" s="363"/>
+      <c r="AP3" s="363"/>
+      <c r="AQ3" s="363"/>
+      <c r="AR3" s="363"/>
+      <c r="AS3" s="363"/>
+      <c r="AT3" s="363"/>
+      <c r="AU3" s="363"/>
+      <c r="AV3" s="363"/>
+      <c r="AW3" s="363"/>
+      <c r="AX3" s="363"/>
+      <c r="AY3" s="363"/>
+      <c r="AZ3" s="363"/>
+      <c r="BA3" s="363"/>
+      <c r="BB3" s="363"/>
+      <c r="BC3" s="363"/>
+      <c r="BD3" s="363"/>
+      <c r="BE3" s="363"/>
+      <c r="BF3" s="363"/>
+      <c r="BG3" s="363"/>
+      <c r="BH3" s="363"/>
+      <c r="BI3" s="363"/>
+      <c r="BJ3" s="363"/>
+      <c r="BK3" s="363"/>
+      <c r="BL3" s="363"/>
+      <c r="BM3" s="363"/>
+      <c r="BN3" s="363"/>
+      <c r="BO3" s="363"/>
+      <c r="BP3" s="363"/>
+      <c r="BQ3" s="363"/>
+      <c r="BR3" s="363"/>
+      <c r="BS3" s="363"/>
+      <c r="BT3" s="363"/>
+      <c r="BU3" s="363"/>
+      <c r="BV3" s="296"/>
+      <c r="BW3" s="362" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="373"/>
-      <c r="BY3" s="373"/>
-      <c r="BZ3" s="373"/>
-      <c r="CA3" s="373"/>
-      <c r="CB3" s="373"/>
-      <c r="CC3" s="299"/>
-      <c r="CD3" s="299"/>
+      <c r="BX3" s="363"/>
+      <c r="BY3" s="363"/>
+      <c r="BZ3" s="363"/>
+      <c r="CA3" s="363"/>
+      <c r="CB3" s="363"/>
+      <c r="CC3" s="298"/>
+      <c r="CD3" s="298"/>
     </row>
     <row r="4" spans="1:87" s="14" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
-      <c r="A4" s="300"/>
-      <c r="B4" s="300"/>
-      <c r="C4" s="300"/>
-      <c r="D4" s="300"/>
-      <c r="E4" s="300"/>
-      <c r="F4" s="300"/>
-      <c r="G4" s="300"/>
-      <c r="H4" s="300"/>
-      <c r="I4" s="287"/>
-      <c r="K4" s="300"/>
-      <c r="L4" s="300"/>
-      <c r="M4" s="300"/>
-      <c r="N4" s="300"/>
-      <c r="O4" s="300"/>
-      <c r="P4" s="300"/>
-      <c r="Q4" s="300"/>
-      <c r="R4" s="300"/>
-      <c r="S4" s="300"/>
-      <c r="T4" s="300"/>
-      <c r="U4" s="300"/>
-      <c r="V4" s="301"/>
-      <c r="W4" s="301"/>
-      <c r="X4" s="301"/>
-      <c r="Y4" s="301"/>
-      <c r="Z4" s="301"/>
-      <c r="AA4" s="301"/>
-      <c r="AB4" s="301"/>
-      <c r="AC4" s="301"/>
-      <c r="AD4" s="301"/>
-      <c r="AE4" s="301"/>
-      <c r="AF4" s="301"/>
-      <c r="AG4" s="301"/>
-      <c r="AH4" s="301"/>
-      <c r="AI4" s="301"/>
-      <c r="AJ4" s="301"/>
-      <c r="AK4" s="301"/>
-      <c r="AL4" s="301"/>
-      <c r="AM4" s="300"/>
-      <c r="AN4" s="300"/>
-      <c r="AO4" s="300"/>
-      <c r="AP4" s="300"/>
-      <c r="AQ4" s="300"/>
-      <c r="AR4" s="300"/>
-      <c r="AS4" s="300"/>
-      <c r="AT4" s="300"/>
-      <c r="AU4" s="300"/>
-      <c r="AV4" s="300"/>
-      <c r="AW4" s="300"/>
-      <c r="AX4" s="300"/>
-      <c r="AY4" s="300"/>
-      <c r="AZ4" s="300"/>
-      <c r="BA4" s="300"/>
-      <c r="BB4" s="300"/>
-      <c r="BC4" s="300"/>
-      <c r="BD4" s="300"/>
-      <c r="BE4" s="300"/>
-      <c r="BF4" s="300"/>
-      <c r="BG4" s="300"/>
-      <c r="BH4" s="300"/>
-      <c r="BI4" s="300"/>
-      <c r="BJ4" s="300"/>
-      <c r="BK4" s="300"/>
-      <c r="BL4" s="300"/>
-      <c r="BM4" s="300"/>
-      <c r="BN4" s="300"/>
-      <c r="BO4" s="300"/>
-      <c r="BP4" s="300"/>
-      <c r="BQ4" s="300"/>
-      <c r="BR4" s="300"/>
-      <c r="BS4" s="300"/>
-      <c r="BT4" s="300"/>
-      <c r="BU4" s="300"/>
-      <c r="BV4" s="300"/>
-      <c r="BW4" s="373"/>
-      <c r="BX4" s="373"/>
-      <c r="BY4" s="373"/>
-      <c r="BZ4" s="373"/>
-      <c r="CA4" s="373"/>
-      <c r="CB4" s="373"/>
-      <c r="CC4" s="299"/>
-      <c r="CD4" s="299"/>
+      <c r="A4" s="299"/>
+      <c r="B4" s="299"/>
+      <c r="C4" s="299"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
+      <c r="G4" s="299"/>
+      <c r="H4" s="299"/>
+      <c r="I4" s="286"/>
+      <c r="K4" s="299"/>
+      <c r="L4" s="299"/>
+      <c r="M4" s="299"/>
+      <c r="N4" s="299"/>
+      <c r="O4" s="299"/>
+      <c r="P4" s="299"/>
+      <c r="Q4" s="299"/>
+      <c r="R4" s="299"/>
+      <c r="S4" s="299"/>
+      <c r="T4" s="299"/>
+      <c r="U4" s="299"/>
+      <c r="V4" s="300"/>
+      <c r="W4" s="300"/>
+      <c r="X4" s="300"/>
+      <c r="Y4" s="300"/>
+      <c r="Z4" s="300"/>
+      <c r="AA4" s="300"/>
+      <c r="AB4" s="300"/>
+      <c r="AC4" s="300"/>
+      <c r="AD4" s="300"/>
+      <c r="AE4" s="300"/>
+      <c r="AF4" s="300"/>
+      <c r="AG4" s="300"/>
+      <c r="AH4" s="300"/>
+      <c r="AI4" s="300"/>
+      <c r="AJ4" s="300"/>
+      <c r="AK4" s="300"/>
+      <c r="AL4" s="300"/>
+      <c r="AM4" s="299"/>
+      <c r="AN4" s="299"/>
+      <c r="AO4" s="299"/>
+      <c r="AP4" s="299"/>
+      <c r="AQ4" s="299"/>
+      <c r="AR4" s="299"/>
+      <c r="AS4" s="299"/>
+      <c r="AT4" s="299"/>
+      <c r="AU4" s="299"/>
+      <c r="AV4" s="299"/>
+      <c r="AW4" s="299"/>
+      <c r="AX4" s="299"/>
+      <c r="AY4" s="299"/>
+      <c r="AZ4" s="299"/>
+      <c r="BA4" s="299"/>
+      <c r="BB4" s="299"/>
+      <c r="BC4" s="299"/>
+      <c r="BD4" s="299"/>
+      <c r="BE4" s="299"/>
+      <c r="BF4" s="299"/>
+      <c r="BG4" s="299"/>
+      <c r="BH4" s="299"/>
+      <c r="BI4" s="299"/>
+      <c r="BJ4" s="299"/>
+      <c r="BK4" s="299"/>
+      <c r="BL4" s="299"/>
+      <c r="BM4" s="299"/>
+      <c r="BN4" s="299"/>
+      <c r="BO4" s="299"/>
+      <c r="BP4" s="299"/>
+      <c r="BQ4" s="299"/>
+      <c r="BR4" s="299"/>
+      <c r="BS4" s="299"/>
+      <c r="BT4" s="299"/>
+      <c r="BU4" s="299"/>
+      <c r="BV4" s="299"/>
+      <c r="BW4" s="363"/>
+      <c r="BX4" s="363"/>
+      <c r="BY4" s="363"/>
+      <c r="BZ4" s="363"/>
+      <c r="CA4" s="363"/>
+      <c r="CB4" s="363"/>
+      <c r="CC4" s="298"/>
+      <c r="CD4" s="298"/>
     </row>
     <row r="5" spans="1:87" s="14" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
-      <c r="A5" s="300"/>
-      <c r="B5" s="300"/>
-      <c r="C5" s="300"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="300"/>
-      <c r="G5" s="300"/>
-      <c r="H5" s="300"/>
-      <c r="I5" s="287"/>
-      <c r="K5" s="300"/>
-      <c r="L5" s="300"/>
-      <c r="M5" s="300"/>
-      <c r="N5" s="300"/>
-      <c r="O5" s="300"/>
-      <c r="P5" s="300"/>
-      <c r="Q5" s="300"/>
-      <c r="R5" s="300"/>
-      <c r="S5" s="300"/>
-      <c r="T5" s="300"/>
-      <c r="U5" s="300"/>
-      <c r="V5" s="300"/>
-      <c r="W5" s="300"/>
-      <c r="X5" s="300"/>
-      <c r="Y5" s="300"/>
-      <c r="Z5" s="300"/>
-      <c r="AA5" s="300"/>
-      <c r="AB5" s="300"/>
-      <c r="AC5" s="300"/>
-      <c r="AD5" s="300"/>
-      <c r="AE5" s="300"/>
-      <c r="AF5" s="300"/>
-      <c r="AG5" s="300"/>
-      <c r="AH5" s="300"/>
-      <c r="AI5" s="300"/>
-      <c r="AJ5" s="300"/>
-      <c r="AK5" s="300"/>
-      <c r="AL5" s="300"/>
-      <c r="AM5" s="300"/>
-      <c r="AN5" s="300"/>
-      <c r="AO5" s="300"/>
-      <c r="AP5" s="300"/>
-      <c r="AQ5" s="300"/>
-      <c r="AR5" s="300"/>
-      <c r="AS5" s="300"/>
-      <c r="AT5" s="300"/>
-      <c r="AU5" s="300"/>
-      <c r="AV5" s="300"/>
-      <c r="AW5" s="300"/>
-      <c r="AX5" s="300"/>
-      <c r="AY5" s="300"/>
-      <c r="AZ5" s="300"/>
-      <c r="BA5" s="300"/>
-      <c r="BB5" s="300"/>
-      <c r="BC5" s="300"/>
-      <c r="BD5" s="300"/>
-      <c r="BE5" s="300"/>
-      <c r="BF5" s="300"/>
-      <c r="BG5" s="300"/>
-      <c r="BH5" s="300"/>
-      <c r="BI5" s="300"/>
-      <c r="BJ5" s="300"/>
-      <c r="BK5" s="300"/>
-      <c r="BL5" s="300"/>
-      <c r="BM5" s="300"/>
-      <c r="BN5" s="300"/>
-      <c r="BO5" s="300"/>
-      <c r="BP5" s="300"/>
-      <c r="BQ5" s="300"/>
-      <c r="BR5" s="300"/>
-      <c r="BS5" s="300"/>
-      <c r="BT5" s="300"/>
-      <c r="BU5" s="300"/>
-      <c r="BV5" s="300"/>
-      <c r="BW5" s="373"/>
-      <c r="BX5" s="373"/>
-      <c r="BY5" s="373"/>
-      <c r="BZ5" s="373"/>
-      <c r="CA5" s="373"/>
-      <c r="CB5" s="373"/>
-      <c r="CC5" s="299"/>
-      <c r="CD5" s="299"/>
+      <c r="A5" s="299"/>
+      <c r="B5" s="299"/>
+      <c r="C5" s="299"/>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
+      <c r="G5" s="299"/>
+      <c r="H5" s="299"/>
+      <c r="I5" s="286"/>
+      <c r="K5" s="299"/>
+      <c r="L5" s="299"/>
+      <c r="M5" s="299"/>
+      <c r="N5" s="299"/>
+      <c r="O5" s="299"/>
+      <c r="P5" s="299"/>
+      <c r="Q5" s="299"/>
+      <c r="R5" s="299"/>
+      <c r="S5" s="299"/>
+      <c r="T5" s="299"/>
+      <c r="U5" s="299"/>
+      <c r="V5" s="299"/>
+      <c r="W5" s="299"/>
+      <c r="X5" s="299"/>
+      <c r="Y5" s="299"/>
+      <c r="Z5" s="299"/>
+      <c r="AA5" s="299"/>
+      <c r="AB5" s="299"/>
+      <c r="AC5" s="299"/>
+      <c r="AD5" s="299"/>
+      <c r="AE5" s="299"/>
+      <c r="AF5" s="299"/>
+      <c r="AG5" s="299"/>
+      <c r="AH5" s="299"/>
+      <c r="AI5" s="299"/>
+      <c r="AJ5" s="299"/>
+      <c r="AK5" s="299"/>
+      <c r="AL5" s="299"/>
+      <c r="AM5" s="299"/>
+      <c r="AN5" s="299"/>
+      <c r="AO5" s="299"/>
+      <c r="AP5" s="299"/>
+      <c r="AQ5" s="299"/>
+      <c r="AR5" s="299"/>
+      <c r="AS5" s="299"/>
+      <c r="AT5" s="299"/>
+      <c r="AU5" s="299"/>
+      <c r="AV5" s="299"/>
+      <c r="AW5" s="299"/>
+      <c r="AX5" s="299"/>
+      <c r="AY5" s="299"/>
+      <c r="AZ5" s="299"/>
+      <c r="BA5" s="299"/>
+      <c r="BB5" s="299"/>
+      <c r="BC5" s="299"/>
+      <c r="BD5" s="299"/>
+      <c r="BE5" s="299"/>
+      <c r="BF5" s="299"/>
+      <c r="BG5" s="299"/>
+      <c r="BH5" s="299"/>
+      <c r="BI5" s="299"/>
+      <c r="BJ5" s="299"/>
+      <c r="BK5" s="299"/>
+      <c r="BL5" s="299"/>
+      <c r="BM5" s="299"/>
+      <c r="BN5" s="299"/>
+      <c r="BO5" s="299"/>
+      <c r="BP5" s="299"/>
+      <c r="BQ5" s="299"/>
+      <c r="BR5" s="299"/>
+      <c r="BS5" s="299"/>
+      <c r="BT5" s="299"/>
+      <c r="BU5" s="299"/>
+      <c r="BV5" s="299"/>
+      <c r="BW5" s="363"/>
+      <c r="BX5" s="363"/>
+      <c r="BY5" s="363"/>
+      <c r="BZ5" s="363"/>
+      <c r="CA5" s="363"/>
+      <c r="CB5" s="363"/>
+      <c r="CC5" s="298"/>
+      <c r="CD5" s="298"/>
     </row>
     <row r="6" spans="1:87" s="14" customFormat="1" ht="34" customHeight="1" outlineLevel="1">
-      <c r="A6" s="302"/>
-      <c r="D6" s="302"/>
-      <c r="E6" s="302"/>
-      <c r="F6" s="302"/>
-      <c r="G6" s="302"/>
-      <c r="H6" s="302"/>
-      <c r="I6" s="287"/>
-      <c r="K6" s="303"/>
-      <c r="L6" s="303"/>
-      <c r="M6" s="303"/>
-      <c r="N6" s="303"/>
-      <c r="O6" s="303"/>
-      <c r="P6" s="303"/>
-      <c r="Q6" s="303"/>
-      <c r="R6" s="303"/>
-      <c r="S6" s="303"/>
-      <c r="T6" s="303"/>
-      <c r="U6" s="303"/>
-      <c r="V6" s="303"/>
-      <c r="W6" s="303"/>
-      <c r="X6" s="303"/>
-      <c r="Y6" s="304"/>
-      <c r="Z6" s="304"/>
-      <c r="AA6" s="304"/>
-      <c r="AB6" s="304"/>
-      <c r="AC6" s="300"/>
-      <c r="AD6" s="302"/>
-      <c r="AE6" s="302"/>
-      <c r="AF6" s="302"/>
-      <c r="AG6" s="302"/>
-      <c r="AH6" s="302"/>
-      <c r="AI6" s="302"/>
-      <c r="AJ6" s="302"/>
-      <c r="AK6" s="302"/>
-      <c r="AL6" s="302"/>
-      <c r="AM6" s="302"/>
-      <c r="AN6" s="302"/>
-      <c r="AO6" s="302"/>
-      <c r="AP6" s="302"/>
-      <c r="AQ6" s="302"/>
-      <c r="AR6" s="302"/>
-      <c r="AS6" s="302"/>
-      <c r="AT6" s="302"/>
-      <c r="AU6" s="302"/>
-      <c r="AV6" s="302"/>
-      <c r="AW6" s="302"/>
-      <c r="AX6" s="302"/>
-      <c r="AY6" s="302"/>
-      <c r="AZ6" s="302"/>
-      <c r="BA6" s="302"/>
-      <c r="BB6" s="302"/>
-      <c r="BC6" s="302"/>
-      <c r="BD6" s="302"/>
-      <c r="BE6" s="302"/>
-      <c r="BF6" s="302"/>
-      <c r="BG6" s="302"/>
-      <c r="BH6" s="302"/>
-      <c r="BI6" s="302"/>
-      <c r="BJ6" s="302"/>
-      <c r="BK6" s="302"/>
-      <c r="BL6" s="302"/>
-      <c r="BM6" s="302"/>
-      <c r="BN6" s="302"/>
-      <c r="BO6" s="302"/>
-      <c r="BP6" s="302"/>
-      <c r="BQ6" s="302"/>
-      <c r="BR6" s="302"/>
-      <c r="BS6" s="302"/>
-      <c r="BT6" s="302"/>
-      <c r="BU6" s="302"/>
-      <c r="BV6" s="302"/>
-      <c r="BW6" s="373"/>
-      <c r="BX6" s="373"/>
-      <c r="BY6" s="373"/>
-      <c r="BZ6" s="373"/>
-      <c r="CA6" s="373"/>
-      <c r="CB6" s="373"/>
-      <c r="CC6" s="299"/>
-      <c r="CD6" s="299"/>
+      <c r="A6" s="301"/>
+      <c r="D6" s="301"/>
+      <c r="E6" s="301"/>
+      <c r="F6" s="301"/>
+      <c r="G6" s="301"/>
+      <c r="H6" s="301"/>
+      <c r="I6" s="286"/>
+      <c r="K6" s="302"/>
+      <c r="L6" s="302"/>
+      <c r="M6" s="302"/>
+      <c r="N6" s="302"/>
+      <c r="O6" s="302"/>
+      <c r="P6" s="302"/>
+      <c r="Q6" s="302"/>
+      <c r="R6" s="302"/>
+      <c r="S6" s="302"/>
+      <c r="T6" s="302"/>
+      <c r="U6" s="302"/>
+      <c r="V6" s="302"/>
+      <c r="W6" s="302"/>
+      <c r="X6" s="302"/>
+      <c r="Y6" s="303"/>
+      <c r="Z6" s="303"/>
+      <c r="AA6" s="303"/>
+      <c r="AB6" s="303"/>
+      <c r="AC6" s="299"/>
+      <c r="AD6" s="301"/>
+      <c r="AE6" s="301"/>
+      <c r="AF6" s="301"/>
+      <c r="AG6" s="301"/>
+      <c r="AH6" s="301"/>
+      <c r="AI6" s="301"/>
+      <c r="AJ6" s="301"/>
+      <c r="AK6" s="301"/>
+      <c r="AL6" s="301"/>
+      <c r="AM6" s="301"/>
+      <c r="AN6" s="301"/>
+      <c r="AO6" s="301"/>
+      <c r="AP6" s="301"/>
+      <c r="AQ6" s="301"/>
+      <c r="AR6" s="301"/>
+      <c r="AS6" s="301"/>
+      <c r="AT6" s="301"/>
+      <c r="AU6" s="301"/>
+      <c r="AV6" s="301"/>
+      <c r="AW6" s="301"/>
+      <c r="AX6" s="301"/>
+      <c r="AY6" s="301"/>
+      <c r="AZ6" s="301"/>
+      <c r="BA6" s="301"/>
+      <c r="BB6" s="301"/>
+      <c r="BC6" s="301"/>
+      <c r="BD6" s="301"/>
+      <c r="BE6" s="301"/>
+      <c r="BF6" s="301"/>
+      <c r="BG6" s="301"/>
+      <c r="BH6" s="301"/>
+      <c r="BI6" s="301"/>
+      <c r="BJ6" s="301"/>
+      <c r="BK6" s="301"/>
+      <c r="BL6" s="301"/>
+      <c r="BM6" s="301"/>
+      <c r="BN6" s="301"/>
+      <c r="BO6" s="301"/>
+      <c r="BP6" s="301"/>
+      <c r="BQ6" s="301"/>
+      <c r="BR6" s="301"/>
+      <c r="BS6" s="301"/>
+      <c r="BT6" s="301"/>
+      <c r="BU6" s="301"/>
+      <c r="BV6" s="301"/>
+      <c r="BW6" s="363"/>
+      <c r="BX6" s="363"/>
+      <c r="BY6" s="363"/>
+      <c r="BZ6" s="363"/>
+      <c r="CA6" s="363"/>
+      <c r="CB6" s="363"/>
+      <c r="CC6" s="298"/>
+      <c r="CD6" s="298"/>
     </row>
-    <row r="7" spans="1:87" s="322" customFormat="1" ht="31" outlineLevel="1">
-      <c r="B7" s="302" t="s">
+    <row r="7" spans="1:87" s="320" customFormat="1" ht="31" outlineLevel="1">
+      <c r="B7" s="301" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="302" t="s">
+      <c r="C7" s="301" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323" t="s">
+      <c r="D7" s="321"/>
+      <c r="E7" s="321" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="324"/>
-      <c r="G7" s="323" t="s">
+      <c r="F7" s="322"/>
+      <c r="G7" s="321" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="323"/>
-      <c r="I7" s="325" t="s">
+      <c r="H7" s="321"/>
+      <c r="I7" s="323" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="322" t="s">
+      <c r="J7" s="320" t="s">
         <v>157</v>
       </c>
-      <c r="K7" s="326"/>
-      <c r="L7" s="326"/>
-      <c r="M7" s="326"/>
-      <c r="N7" s="326"/>
-      <c r="O7" s="326"/>
-      <c r="Q7" s="326"/>
-      <c r="R7" s="326"/>
-      <c r="S7" s="326"/>
-      <c r="T7" s="326"/>
-      <c r="U7" s="327"/>
-      <c r="V7" s="326"/>
-      <c r="W7" s="326"/>
-      <c r="X7" s="326"/>
-      <c r="Y7" s="328" t="s">
+      <c r="K7" s="324"/>
+      <c r="L7" s="324"/>
+      <c r="M7" s="324"/>
+      <c r="N7" s="324"/>
+      <c r="O7" s="324"/>
+      <c r="Q7" s="324"/>
+      <c r="R7" s="324"/>
+      <c r="S7" s="324"/>
+      <c r="T7" s="324"/>
+      <c r="U7" s="325"/>
+      <c r="V7" s="324"/>
+      <c r="W7" s="324"/>
+      <c r="X7" s="324"/>
+      <c r="Y7" s="326" t="s">
         <v>158</v>
       </c>
-      <c r="Z7" s="328" t="s">
+      <c r="Z7" s="326" t="s">
         <v>158</v>
       </c>
-      <c r="AA7" s="328" t="s">
+      <c r="AA7" s="326" t="s">
         <v>158</v>
       </c>
-      <c r="AB7" s="328"/>
-      <c r="AC7" s="326" t="s">
+      <c r="AB7" s="326"/>
+      <c r="AC7" s="324" t="s">
         <v>158</v>
       </c>
-      <c r="AD7" s="302" t="s">
+      <c r="AD7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AE7" s="302" t="s">
+      <c r="AE7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AF7" s="302"/>
-      <c r="AG7" s="302"/>
-      <c r="AH7" s="302" t="s">
+      <c r="AF7" s="301"/>
+      <c r="AG7" s="301"/>
+      <c r="AH7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AI7" s="302" t="s">
+      <c r="AI7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AJ7" s="302"/>
-      <c r="AK7" s="302"/>
-      <c r="AL7" s="302" t="s">
+      <c r="AJ7" s="301"/>
+      <c r="AK7" s="301"/>
+      <c r="AL7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AM7" s="302" t="s">
+      <c r="AM7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AN7" s="302" t="s">
+      <c r="AN7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AO7" s="302" t="s">
+      <c r="AO7" s="301" t="s">
         <v>158</v>
       </c>
-      <c r="AP7" s="302" t="s">
+      <c r="AP7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AQ7" s="302"/>
-      <c r="AR7" s="302" t="s">
+      <c r="AQ7" s="301"/>
+      <c r="AR7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AS7" s="302" t="s">
+      <c r="AS7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AT7" s="302" t="s">
+      <c r="AT7" s="301" t="s">
         <v>156</v>
       </c>
-      <c r="AU7" s="302" t="s">
+      <c r="AU7" s="301" t="s">
         <v>159</v>
       </c>
-      <c r="AY7" s="323"/>
-      <c r="BA7" s="323"/>
-      <c r="BB7" s="323" t="s">
+      <c r="AY7" s="321"/>
+      <c r="BA7" s="321"/>
+      <c r="BB7" s="321" t="s">
         <v>160</v>
       </c>
-      <c r="BE7" s="323"/>
-      <c r="BF7" s="323"/>
-      <c r="BG7" s="323"/>
-      <c r="BH7" s="323"/>
-      <c r="BI7" s="323" t="s">
+      <c r="BE7" s="321"/>
+      <c r="BF7" s="321"/>
+      <c r="BG7" s="321"/>
+      <c r="BH7" s="321"/>
+      <c r="BI7" s="321" t="s">
         <v>160</v>
       </c>
-      <c r="BJ7" s="323"/>
-      <c r="BK7" s="323"/>
-      <c r="BL7" s="322" t="s">
+      <c r="BJ7" s="321"/>
+      <c r="BK7" s="321"/>
+      <c r="BL7" s="320" t="s">
         <v>160</v>
       </c>
-      <c r="BN7" s="323"/>
-      <c r="BP7" s="323"/>
-      <c r="BT7" s="323" t="s">
+      <c r="BN7" s="321"/>
+      <c r="BP7" s="321"/>
+      <c r="BT7" s="321" t="s">
         <v>161</v>
       </c>
-      <c r="BU7" s="322" t="s">
+      <c r="BU7" s="320" t="s">
         <v>161</v>
       </c>
-      <c r="BW7" s="298"/>
-      <c r="BX7" s="298" t="s">
+      <c r="BW7" s="297"/>
+      <c r="BX7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="BY7" s="298" t="s">
+      <c r="BY7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="BZ7" s="298"/>
-      <c r="CA7" s="298" t="s">
+      <c r="BZ7" s="297"/>
+      <c r="CA7" s="297" t="s">
         <v>156</v>
       </c>
-      <c r="CB7" s="327"/>
-      <c r="CC7" s="327"/>
-      <c r="CD7" s="327"/>
-      <c r="CE7" s="302" t="s">
+      <c r="CB7" s="325"/>
+      <c r="CC7" s="325"/>
+      <c r="CD7" s="325"/>
+      <c r="CE7" s="301" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="371" t="s">
+    <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A8" s="361" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="376" t="s">
+      <c r="B8" s="366" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="338" t="s">
+      <c r="C8" s="335" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="360" t="s">
+      <c r="D8" s="353" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="360" t="s">
+      <c r="E8" s="353" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="338" t="s">
+      <c r="F8" s="335" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="361" t="s">
+      <c r="G8" s="354" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="362" t="s">
+      <c r="H8" s="423" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="362" t="s">
+      <c r="I8" s="423" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="358" t="s">
+      <c r="J8" s="354" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="370" t="s">
+      <c r="K8" s="360" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="355"/>
-      <c r="M8" s="355"/>
-      <c r="N8" s="355"/>
-      <c r="O8" s="355"/>
-      <c r="P8" s="355"/>
-      <c r="Q8" s="355"/>
-      <c r="R8" s="355"/>
-      <c r="S8" s="355"/>
-      <c r="T8" s="355"/>
-      <c r="U8" s="355"/>
-      <c r="V8" s="355"/>
-      <c r="W8" s="355"/>
-      <c r="X8" s="355"/>
-      <c r="Y8" s="354" t="s">
+      <c r="L8" s="349"/>
+      <c r="M8" s="349"/>
+      <c r="N8" s="349"/>
+      <c r="O8" s="349"/>
+      <c r="P8" s="349"/>
+      <c r="Q8" s="349"/>
+      <c r="R8" s="349"/>
+      <c r="S8" s="349"/>
+      <c r="T8" s="349"/>
+      <c r="U8" s="349"/>
+      <c r="V8" s="349"/>
+      <c r="W8" s="349"/>
+      <c r="X8" s="349"/>
+      <c r="Y8" s="348" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="355"/>
-      <c r="AA8" s="355"/>
-      <c r="AB8" s="355"/>
-      <c r="AC8" s="355"/>
-      <c r="AD8" s="355"/>
-      <c r="AE8" s="355"/>
-      <c r="AF8" s="355"/>
-      <c r="AG8" s="355"/>
-      <c r="AH8" s="355"/>
-      <c r="AI8" s="355"/>
-      <c r="AJ8" s="355"/>
-      <c r="AK8" s="355"/>
-      <c r="AL8" s="355"/>
-      <c r="AM8" s="355"/>
-      <c r="AN8" s="355"/>
-      <c r="AO8" s="356"/>
-      <c r="AP8" s="358" t="s">
+      <c r="Z8" s="349"/>
+      <c r="AA8" s="349"/>
+      <c r="AB8" s="349"/>
+      <c r="AC8" s="349"/>
+      <c r="AD8" s="349"/>
+      <c r="AE8" s="349"/>
+      <c r="AF8" s="349"/>
+      <c r="AG8" s="349"/>
+      <c r="AH8" s="349"/>
+      <c r="AI8" s="349"/>
+      <c r="AJ8" s="349"/>
+      <c r="AK8" s="349"/>
+      <c r="AL8" s="349"/>
+      <c r="AM8" s="349"/>
+      <c r="AN8" s="349"/>
+      <c r="AO8" s="350"/>
+      <c r="AP8" s="354" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="358" t="s">
+      <c r="AQ8" s="354" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="358" t="s">
+      <c r="AR8" s="354" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="358" t="s">
+      <c r="AS8" s="354" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="358" t="s">
+      <c r="AT8" s="354" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="358" t="s">
+      <c r="AU8" s="354" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="338" t="s">
+      <c r="AV8" s="335" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="352" t="s">
+      <c r="AW8" s="340" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="338" t="s">
+      <c r="AX8" s="335" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="363" t="s">
+      <c r="AY8" s="355" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="355"/>
-      <c r="BA8" s="355"/>
-      <c r="BB8" s="355"/>
-      <c r="BC8" s="355"/>
-      <c r="BD8" s="355"/>
-      <c r="BE8" s="355"/>
-      <c r="BF8" s="355"/>
-      <c r="BG8" s="355"/>
-      <c r="BH8" s="355"/>
-      <c r="BI8" s="355"/>
-      <c r="BJ8" s="355"/>
-      <c r="BK8" s="355"/>
-      <c r="BL8" s="355"/>
-      <c r="BM8" s="355"/>
-      <c r="BN8" s="355"/>
-      <c r="BO8" s="355"/>
-      <c r="BP8" s="355"/>
-      <c r="BQ8" s="356"/>
-      <c r="BR8" s="339" t="s">
+      <c r="AZ8" s="349"/>
+      <c r="BA8" s="349"/>
+      <c r="BB8" s="349"/>
+      <c r="BC8" s="349"/>
+      <c r="BD8" s="349"/>
+      <c r="BE8" s="349"/>
+      <c r="BF8" s="349"/>
+      <c r="BG8" s="349"/>
+      <c r="BH8" s="349"/>
+      <c r="BI8" s="349"/>
+      <c r="BJ8" s="349"/>
+      <c r="BK8" s="349"/>
+      <c r="BL8" s="349"/>
+      <c r="BM8" s="349"/>
+      <c r="BN8" s="349"/>
+      <c r="BO8" s="349"/>
+      <c r="BP8" s="349"/>
+      <c r="BQ8" s="350"/>
+      <c r="BR8" s="336" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="340"/>
-      <c r="BT8" s="338" t="s">
+      <c r="BS8" s="337"/>
+      <c r="BT8" s="335" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="335" t="s">
+      <c r="BU8" s="332" t="s">
         <v>28</v>
       </c>
-      <c r="BV8" s="22"/>
-      <c r="BW8" s="386" t="s">
+      <c r="BV8" s="434"/>
+      <c r="BW8" s="376" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="377" t="s">
+      <c r="BX8" s="367" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="378"/>
-      <c r="BZ8" s="378"/>
-      <c r="CA8" s="379"/>
-      <c r="CB8" s="341" t="s">
+      <c r="BY8" s="368"/>
+      <c r="BZ8" s="368"/>
+      <c r="CA8" s="369"/>
+      <c r="CB8" s="338" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="390" t="s">
+      <c r="CC8" s="379" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="390" t="s">
+      <c r="CD8" s="379" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
-    <row r="9" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="350"/>
-      <c r="B9" s="333"/>
-      <c r="C9" s="333"/>
-      <c r="D9" s="333"/>
-      <c r="E9" s="333"/>
-      <c r="F9" s="333"/>
-      <c r="G9" s="344"/>
-      <c r="H9" s="350"/>
-      <c r="I9" s="350"/>
-      <c r="J9" s="331"/>
-      <c r="K9" s="349" t="s">
+    <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A9" s="346"/>
+      <c r="B9" s="330"/>
+      <c r="C9" s="330"/>
+      <c r="D9" s="330"/>
+      <c r="E9" s="330"/>
+      <c r="F9" s="330"/>
+      <c r="G9" s="341"/>
+      <c r="H9" s="330"/>
+      <c r="I9" s="330"/>
+      <c r="J9" s="341"/>
+      <c r="K9" s="435" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="349" t="s">
+      <c r="L9" s="435" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="349" t="s">
+      <c r="M9" s="435" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="349" t="s">
+      <c r="N9" s="435" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="349" t="s">
+      <c r="O9" s="435" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="349" t="s">
+      <c r="P9" s="435" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="349" t="s">
+      <c r="Q9" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="349" t="s">
+      <c r="R9" s="435" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="349" t="s">
+      <c r="S9" s="435" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="349" t="s">
+      <c r="T9" s="435" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="349" t="s">
+      <c r="U9" s="435" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="366" t="s">
+      <c r="V9" s="356" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="340"/>
-      <c r="X9" s="349" t="s">
+      <c r="W9" s="337"/>
+      <c r="X9" s="435" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="332" t="s">
+      <c r="Y9" s="329" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="332" t="s">
+      <c r="Z9" s="329" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="332" t="s">
+      <c r="AA9" s="329" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="332" t="s">
+      <c r="AB9" s="329" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="332" t="s">
+      <c r="AC9" s="329" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="332" t="s">
+      <c r="AD9" s="329" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="332" t="s">
+      <c r="AE9" s="329" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="332" t="s">
+      <c r="AF9" s="329" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="332" t="s">
+      <c r="AG9" s="329" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="332" t="s">
+      <c r="AH9" s="329" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="332" t="s">
+      <c r="AI9" s="329" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="359" t="s">
+      <c r="AJ9" s="352" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="335" t="s">
+      <c r="AK9" s="332" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="343" t="s">
+      <c r="AL9" s="340" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="332" t="s">
+      <c r="AM9" s="329" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="338" t="s">
+      <c r="AN9" s="335" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="338" t="s">
+      <c r="AO9" s="335" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="331"/>
-      <c r="AQ9" s="331"/>
-      <c r="AR9" s="331"/>
-      <c r="AS9" s="331"/>
-      <c r="AT9" s="331"/>
-      <c r="AU9" s="331"/>
-      <c r="AV9" s="333"/>
-      <c r="AW9" s="331"/>
-      <c r="AX9" s="333"/>
-      <c r="AY9" s="346" t="s">
+      <c r="AP9" s="341"/>
+      <c r="AQ9" s="341"/>
+      <c r="AR9" s="341"/>
+      <c r="AS9" s="341"/>
+      <c r="AT9" s="341"/>
+      <c r="AU9" s="341"/>
+      <c r="AV9" s="330"/>
+      <c r="AW9" s="341"/>
+      <c r="AX9" s="330"/>
+      <c r="AY9" s="343" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="347"/>
-      <c r="BA9" s="347"/>
-      <c r="BB9" s="347"/>
-      <c r="BC9" s="347"/>
-      <c r="BD9" s="347"/>
-      <c r="BE9" s="347"/>
-      <c r="BF9" s="347"/>
-      <c r="BG9" s="347"/>
-      <c r="BH9" s="347"/>
-      <c r="BI9" s="347"/>
-      <c r="BJ9" s="347"/>
-      <c r="BK9" s="347"/>
-      <c r="BL9" s="348"/>
-      <c r="BM9" s="346" t="s">
+      <c r="AZ9" s="344"/>
+      <c r="BA9" s="344"/>
+      <c r="BB9" s="344"/>
+      <c r="BC9" s="344"/>
+      <c r="BD9" s="344"/>
+      <c r="BE9" s="344"/>
+      <c r="BF9" s="344"/>
+      <c r="BG9" s="344"/>
+      <c r="BH9" s="344"/>
+      <c r="BI9" s="344"/>
+      <c r="BJ9" s="344"/>
+      <c r="BK9" s="344"/>
+      <c r="BL9" s="345"/>
+      <c r="BM9" s="343" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="347"/>
-      <c r="BO9" s="347"/>
-      <c r="BP9" s="347"/>
-      <c r="BQ9" s="348"/>
-      <c r="BR9" s="365" t="s">
+      <c r="BN9" s="344"/>
+      <c r="BO9" s="344"/>
+      <c r="BP9" s="344"/>
+      <c r="BQ9" s="345"/>
+      <c r="BR9" s="436" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="365" t="s">
+      <c r="BS9" s="436" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="333"/>
-      <c r="BU9" s="336"/>
-      <c r="BV9" s="22"/>
-      <c r="BW9" s="387"/>
-      <c r="BX9" s="380"/>
-      <c r="BY9" s="381"/>
-      <c r="BZ9" s="381"/>
-      <c r="CA9" s="382"/>
-      <c r="CB9" s="333"/>
-      <c r="CC9" s="443"/>
-      <c r="CD9" s="443"/>
+      <c r="BT9" s="330"/>
+      <c r="BU9" s="333"/>
+      <c r="BV9" s="434"/>
+      <c r="BW9" s="377"/>
+      <c r="BX9" s="370"/>
+      <c r="BY9" s="371"/>
+      <c r="BZ9" s="371"/>
+      <c r="CA9" s="372"/>
+      <c r="CB9" s="330"/>
+      <c r="CC9" s="432"/>
+      <c r="CD9" s="432"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
-    <row r="10" spans="1:87" s="306" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="350"/>
-      <c r="B10" s="333"/>
-      <c r="C10" s="333"/>
-      <c r="D10" s="333"/>
-      <c r="E10" s="333"/>
-      <c r="F10" s="333"/>
-      <c r="G10" s="344"/>
-      <c r="H10" s="350"/>
-      <c r="I10" s="350"/>
-      <c r="J10" s="331"/>
-      <c r="K10" s="350"/>
-      <c r="L10" s="350"/>
-      <c r="M10" s="350"/>
-      <c r="N10" s="350"/>
-      <c r="O10" s="350"/>
-      <c r="P10" s="350"/>
-      <c r="Q10" s="350"/>
-      <c r="R10" s="350"/>
-      <c r="S10" s="350"/>
-      <c r="T10" s="350"/>
-      <c r="U10" s="350"/>
-      <c r="V10" s="367"/>
-      <c r="W10" s="368"/>
-      <c r="X10" s="350"/>
-      <c r="Y10" s="333"/>
-      <c r="Z10" s="333"/>
-      <c r="AA10" s="333"/>
-      <c r="AB10" s="333"/>
-      <c r="AC10" s="333"/>
-      <c r="AD10" s="333"/>
-      <c r="AE10" s="333"/>
-      <c r="AF10" s="333"/>
-      <c r="AG10" s="333"/>
-      <c r="AH10" s="333"/>
-      <c r="AI10" s="333"/>
-      <c r="AJ10" s="344"/>
-      <c r="AK10" s="336"/>
-      <c r="AL10" s="344"/>
-      <c r="AM10" s="333"/>
-      <c r="AN10" s="333"/>
-      <c r="AO10" s="333"/>
-      <c r="AP10" s="331"/>
-      <c r="AQ10" s="331"/>
-      <c r="AR10" s="331"/>
-      <c r="AS10" s="331"/>
-      <c r="AT10" s="331"/>
-      <c r="AU10" s="331"/>
-      <c r="AV10" s="333"/>
-      <c r="AW10" s="331"/>
-      <c r="AX10" s="333"/>
+    <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A10" s="346"/>
+      <c r="B10" s="330"/>
+      <c r="C10" s="330"/>
+      <c r="D10" s="330"/>
+      <c r="E10" s="330"/>
+      <c r="F10" s="330"/>
+      <c r="G10" s="341"/>
+      <c r="H10" s="330"/>
+      <c r="I10" s="330"/>
+      <c r="J10" s="341"/>
+      <c r="K10" s="330"/>
+      <c r="L10" s="330"/>
+      <c r="M10" s="330"/>
+      <c r="N10" s="330"/>
+      <c r="O10" s="330"/>
+      <c r="P10" s="330"/>
+      <c r="Q10" s="330"/>
+      <c r="R10" s="330"/>
+      <c r="S10" s="330"/>
+      <c r="T10" s="330"/>
+      <c r="U10" s="330"/>
+      <c r="V10" s="357"/>
+      <c r="W10" s="358"/>
+      <c r="X10" s="330"/>
+      <c r="Y10" s="330"/>
+      <c r="Z10" s="330"/>
+      <c r="AA10" s="330"/>
+      <c r="AB10" s="330"/>
+      <c r="AC10" s="330"/>
+      <c r="AD10" s="330"/>
+      <c r="AE10" s="330"/>
+      <c r="AF10" s="330"/>
+      <c r="AG10" s="330"/>
+      <c r="AH10" s="330"/>
+      <c r="AI10" s="330"/>
+      <c r="AJ10" s="341"/>
+      <c r="AK10" s="333"/>
+      <c r="AL10" s="341"/>
+      <c r="AM10" s="330"/>
+      <c r="AN10" s="330"/>
+      <c r="AO10" s="330"/>
+      <c r="AP10" s="341"/>
+      <c r="AQ10" s="341"/>
+      <c r="AR10" s="341"/>
+      <c r="AS10" s="341"/>
+      <c r="AT10" s="341"/>
+      <c r="AU10" s="341"/>
+      <c r="AV10" s="330"/>
+      <c r="AW10" s="341"/>
+      <c r="AX10" s="330"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8624,578 +8599,578 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="375" t="s">
+      <c r="BB10" s="365" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="364" t="s">
+      <c r="BC10" s="359" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="364" t="s">
+      <c r="BD10" s="359" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="357" t="s">
+      <c r="BE10" s="351" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="357" t="s">
+      <c r="BF10" s="351" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="389" t="s">
+      <c r="BG10" s="351" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="364" t="s">
+      <c r="BH10" s="359" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="369" t="s">
+      <c r="BI10" s="359" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="357" t="s">
+      <c r="BJ10" s="351" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="357" t="s">
+      <c r="BK10" s="351" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="338" t="s">
+      <c r="BL10" s="335" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="364" t="s">
+      <c r="BM10" s="359" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="352" t="s">
+      <c r="BN10" s="340" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="364" t="s">
+      <c r="BO10" s="359" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="352" t="s">
+      <c r="BP10" s="340" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="352" t="s">
+      <c r="BQ10" s="340" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="350"/>
-      <c r="BS10" s="350"/>
-      <c r="BT10" s="333"/>
-      <c r="BU10" s="336"/>
-      <c r="BV10" s="22"/>
-      <c r="BW10" s="387"/>
-      <c r="BX10" s="383"/>
-      <c r="BY10" s="384"/>
-      <c r="BZ10" s="384"/>
-      <c r="CA10" s="385"/>
-      <c r="CB10" s="333"/>
-      <c r="CC10" s="443"/>
-      <c r="CD10" s="443"/>
-      <c r="CE10" s="320" t="s">
+      <c r="BR10" s="330"/>
+      <c r="BS10" s="330"/>
+      <c r="BT10" s="330"/>
+      <c r="BU10" s="333"/>
+      <c r="BV10" s="434"/>
+      <c r="BW10" s="377"/>
+      <c r="BX10" s="373"/>
+      <c r="BY10" s="374"/>
+      <c r="BZ10" s="374"/>
+      <c r="CA10" s="375"/>
+      <c r="CB10" s="330"/>
+      <c r="CC10" s="432"/>
+      <c r="CD10" s="432"/>
+      <c r="CE10" s="319" t="s">
         <v>3</v>
       </c>
       <c r="CH10" s="241"/>
       <c r="CI10" s="241"/>
     </row>
-    <row r="11" spans="1:87" s="306" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="351"/>
-      <c r="B11" s="334"/>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="345"/>
-      <c r="H11" s="351"/>
-      <c r="I11" s="351"/>
-      <c r="J11" s="353"/>
-      <c r="K11" s="351"/>
-      <c r="L11" s="351"/>
-      <c r="M11" s="351"/>
-      <c r="N11" s="351"/>
-      <c r="O11" s="351"/>
-      <c r="P11" s="351"/>
-      <c r="Q11" s="351"/>
-      <c r="R11" s="351"/>
-      <c r="S11" s="351"/>
-      <c r="T11" s="351"/>
-      <c r="U11" s="351"/>
-      <c r="V11" s="269" t="s">
+    <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A11" s="347"/>
+      <c r="B11" s="331"/>
+      <c r="C11" s="331"/>
+      <c r="D11" s="331"/>
+      <c r="E11" s="331"/>
+      <c r="F11" s="331"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="331"/>
+      <c r="I11" s="331"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="331"/>
+      <c r="L11" s="331"/>
+      <c r="M11" s="331"/>
+      <c r="N11" s="331"/>
+      <c r="O11" s="331"/>
+      <c r="P11" s="331"/>
+      <c r="Q11" s="331"/>
+      <c r="R11" s="331"/>
+      <c r="S11" s="331"/>
+      <c r="T11" s="331"/>
+      <c r="U11" s="331"/>
+      <c r="V11" s="437" t="s">
         <v>86</v>
       </c>
-      <c r="W11" s="269" t="s">
+      <c r="W11" s="437" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="351"/>
-      <c r="Y11" s="334"/>
-      <c r="Z11" s="334"/>
-      <c r="AA11" s="334"/>
-      <c r="AB11" s="334"/>
-      <c r="AC11" s="334"/>
-      <c r="AD11" s="334"/>
-      <c r="AE11" s="334"/>
-      <c r="AF11" s="334"/>
-      <c r="AG11" s="334"/>
-      <c r="AH11" s="334"/>
-      <c r="AI11" s="334"/>
-      <c r="AJ11" s="345"/>
-      <c r="AK11" s="337"/>
-      <c r="AL11" s="345"/>
-      <c r="AM11" s="334"/>
-      <c r="AN11" s="334"/>
-      <c r="AO11" s="334"/>
-      <c r="AP11" s="353"/>
-      <c r="AQ11" s="353"/>
-      <c r="AR11" s="353"/>
-      <c r="AS11" s="353"/>
-      <c r="AT11" s="353"/>
-      <c r="AU11" s="353"/>
-      <c r="AV11" s="334"/>
-      <c r="AW11" s="353"/>
-      <c r="AX11" s="334"/>
-      <c r="AY11" s="321" t="s">
+      <c r="X11" s="331"/>
+      <c r="Y11" s="331"/>
+      <c r="Z11" s="331"/>
+      <c r="AA11" s="331"/>
+      <c r="AB11" s="331"/>
+      <c r="AC11" s="331"/>
+      <c r="AD11" s="331"/>
+      <c r="AE11" s="331"/>
+      <c r="AF11" s="331"/>
+      <c r="AG11" s="331"/>
+      <c r="AH11" s="331"/>
+      <c r="AI11" s="331"/>
+      <c r="AJ11" s="342"/>
+      <c r="AK11" s="334"/>
+      <c r="AL11" s="342"/>
+      <c r="AM11" s="331"/>
+      <c r="AN11" s="331"/>
+      <c r="AO11" s="331"/>
+      <c r="AP11" s="342"/>
+      <c r="AQ11" s="342"/>
+      <c r="AR11" s="342"/>
+      <c r="AS11" s="342"/>
+      <c r="AT11" s="342"/>
+      <c r="AU11" s="342"/>
+      <c r="AV11" s="331"/>
+      <c r="AW11" s="342"/>
+      <c r="AX11" s="331"/>
+      <c r="AY11" s="438" t="s">
         <v>88</v>
       </c>
-      <c r="AZ11" s="321" t="s">
+      <c r="AZ11" s="438" t="s">
         <v>89</v>
       </c>
-      <c r="BA11" s="321" t="s">
+      <c r="BA11" s="438" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="334"/>
-      <c r="BC11" s="353"/>
-      <c r="BD11" s="353"/>
-      <c r="BE11" s="334"/>
-      <c r="BF11" s="334"/>
-      <c r="BG11" s="351"/>
-      <c r="BH11" s="353"/>
-      <c r="BI11" s="345"/>
-      <c r="BJ11" s="334"/>
-      <c r="BK11" s="334"/>
-      <c r="BL11" s="334"/>
-      <c r="BM11" s="353"/>
-      <c r="BN11" s="353"/>
-      <c r="BO11" s="353"/>
-      <c r="BP11" s="353"/>
-      <c r="BQ11" s="353"/>
-      <c r="BR11" s="351"/>
-      <c r="BS11" s="351"/>
-      <c r="BT11" s="334"/>
-      <c r="BU11" s="337"/>
-      <c r="BV11" s="22"/>
-      <c r="BW11" s="388"/>
-      <c r="BX11" s="329" t="s">
+      <c r="BB11" s="331"/>
+      <c r="BC11" s="342"/>
+      <c r="BD11" s="342"/>
+      <c r="BE11" s="331"/>
+      <c r="BF11" s="331"/>
+      <c r="BG11" s="331"/>
+      <c r="BH11" s="342"/>
+      <c r="BI11" s="342"/>
+      <c r="BJ11" s="331"/>
+      <c r="BK11" s="331"/>
+      <c r="BL11" s="331"/>
+      <c r="BM11" s="342"/>
+      <c r="BN11" s="342"/>
+      <c r="BO11" s="342"/>
+      <c r="BP11" s="342"/>
+      <c r="BQ11" s="342"/>
+      <c r="BR11" s="331"/>
+      <c r="BS11" s="331"/>
+      <c r="BT11" s="331"/>
+      <c r="BU11" s="334"/>
+      <c r="BV11" s="434"/>
+      <c r="BW11" s="378"/>
+      <c r="BX11" s="327" t="s">
         <v>91</v>
       </c>
-      <c r="BY11" s="329" t="s">
+      <c r="BY11" s="327" t="s">
         <v>92</v>
       </c>
-      <c r="BZ11" s="329" t="s">
+      <c r="BZ11" s="327" t="s">
         <v>93</v>
       </c>
-      <c r="CA11" s="270" t="s">
+      <c r="CA11" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="342"/>
-      <c r="CC11" s="444"/>
-      <c r="CD11" s="444"/>
-      <c r="CE11" s="319">
+      <c r="CB11" s="339"/>
+      <c r="CC11" s="433"/>
+      <c r="CD11" s="433"/>
+      <c r="CE11" s="318">
         <v>26</v>
       </c>
-      <c r="CF11" s="307"/>
+      <c r="CF11" s="306"/>
       <c r="CH11" s="241"/>
       <c r="CI11" s="241"/>
     </row>
-    <row r="12" spans="1:87" s="312" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="308">
+    <row r="12" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
+      <c r="A12" s="307">
         <v>1</v>
       </c>
-      <c r="B12" s="309">
+      <c r="B12" s="308">
         <f>A12+1</f>
         <v>2</v>
       </c>
-      <c r="C12" s="309">
+      <c r="C12" s="308">
         <f>B12+1</f>
         <v>3</v>
       </c>
-      <c r="D12" s="309">
+      <c r="D12" s="308">
         <f>C12+1</f>
         <v>4</v>
       </c>
-      <c r="E12" s="309"/>
-      <c r="F12" s="309">
+      <c r="E12" s="308"/>
+      <c r="F12" s="308">
         <f>D12+1</f>
         <v>5</v>
       </c>
-      <c r="G12" s="309">
+      <c r="G12" s="308">
         <f t="shared" ref="G12:AV12" si="0">F12+1</f>
         <v>6</v>
       </c>
-      <c r="H12" s="309">
+      <c r="H12" s="308">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I12" s="309">
+      <c r="I12" s="308">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J12" s="309">
+      <c r="J12" s="308">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K12" s="309">
+      <c r="K12" s="308">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="309">
+      <c r="L12" s="308">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="M12" s="309">
+      <c r="M12" s="308">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N12" s="309">
+      <c r="N12" s="308">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="O12" s="309">
+      <c r="O12" s="308">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="P12" s="309">
+      <c r="P12" s="308">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q12" s="309">
+      <c r="Q12" s="308">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="R12" s="309">
+      <c r="R12" s="308">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="S12" s="309">
+      <c r="S12" s="308">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="T12" s="309">
+      <c r="T12" s="308">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="U12" s="309">
+      <c r="U12" s="308">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="V12" s="309">
+      <c r="V12" s="308">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="W12" s="309">
+      <c r="W12" s="308">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X12" s="309">
+      <c r="X12" s="308">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="Y12" s="309">
+      <c r="Y12" s="308">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="Z12" s="309">
+      <c r="Z12" s="308">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AA12" s="309">
+      <c r="AA12" s="308">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AB12" s="309">
+      <c r="AB12" s="308">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AC12" s="309">
+      <c r="AC12" s="308">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="AD12" s="309">
+      <c r="AD12" s="308">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="AE12" s="309">
+      <c r="AE12" s="308">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="AF12" s="309">
+      <c r="AF12" s="308">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="AG12" s="309">
+      <c r="AG12" s="308">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="AH12" s="309">
+      <c r="AH12" s="308">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="AI12" s="309">
+      <c r="AI12" s="308">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="AJ12" s="309">
+      <c r="AJ12" s="308">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="AK12" s="309">
+      <c r="AK12" s="308">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="AL12" s="309">
+      <c r="AL12" s="308">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="AM12" s="309">
+      <c r="AM12" s="308">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="AN12" s="309">
+      <c r="AN12" s="308">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="AO12" s="309">
+      <c r="AO12" s="308">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="AP12" s="309">
+      <c r="AP12" s="308">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="AQ12" s="309">
+      <c r="AQ12" s="308">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="AR12" s="309">
+      <c r="AR12" s="308">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="AS12" s="309">
+      <c r="AS12" s="308">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="AT12" s="309">
+      <c r="AT12" s="308">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="AU12" s="309">
+      <c r="AU12" s="308">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="AV12" s="309">
+      <c r="AV12" s="308">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="AW12" s="309"/>
-      <c r="AX12" s="309"/>
-      <c r="AY12" s="309">
+      <c r="AW12" s="308"/>
+      <c r="AX12" s="308"/>
+      <c r="AY12" s="308">
         <f>AV12+1</f>
         <v>48</v>
       </c>
-      <c r="AZ12" s="309">
+      <c r="AZ12" s="308">
         <f t="shared" ref="AZ12:BE12" si="1">AY12+1</f>
         <v>49</v>
       </c>
-      <c r="BA12" s="309">
+      <c r="BA12" s="308">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="BB12" s="309">
+      <c r="BB12" s="308">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="BC12" s="309">
+      <c r="BC12" s="308">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="BD12" s="309">
+      <c r="BD12" s="308">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="BE12" s="309">
+      <c r="BE12" s="308">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="BF12" s="309"/>
-      <c r="BG12" s="309"/>
-      <c r="BH12" s="309"/>
-      <c r="BI12" s="309"/>
-      <c r="BJ12" s="309"/>
-      <c r="BK12" s="309"/>
-      <c r="BL12" s="309">
+      <c r="BF12" s="308"/>
+      <c r="BG12" s="308"/>
+      <c r="BH12" s="308"/>
+      <c r="BI12" s="308"/>
+      <c r="BJ12" s="308"/>
+      <c r="BK12" s="308"/>
+      <c r="BL12" s="308">
         <f>BE12+1</f>
         <v>55</v>
       </c>
-      <c r="BM12" s="309">
+      <c r="BM12" s="308">
         <f t="shared" ref="BM12:BU12" si="2">BL12+1</f>
         <v>56</v>
       </c>
-      <c r="BN12" s="309">
+      <c r="BN12" s="308">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="BO12" s="309">
+      <c r="BO12" s="308">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="BP12" s="309">
+      <c r="BP12" s="308">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="BQ12" s="309">
+      <c r="BQ12" s="308">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="BR12" s="309">
+      <c r="BR12" s="308">
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="BS12" s="309">
+      <c r="BS12" s="308">
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="BT12" s="309">
+      <c r="BT12" s="308">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="BU12" s="309">
+      <c r="BU12" s="308">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="BV12" s="310"/>
-      <c r="BW12" s="311" t="s">
+      <c r="BV12" s="309"/>
+      <c r="BW12" s="310" t="s">
         <v>95</v>
       </c>
-      <c r="BX12" s="309">
+      <c r="BX12" s="308">
         <f t="shared" ref="BX12:CD12" si="3">BW12+1</f>
         <v>66</v>
       </c>
-      <c r="BY12" s="309">
+      <c r="BY12" s="308">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="BZ12" s="309">
+      <c r="BZ12" s="308">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="CA12" s="309">
+      <c r="CA12" s="308">
         <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="CB12" s="309">
+      <c r="CB12" s="308">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="CC12" s="309">
+      <c r="CC12" s="308">
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
-      <c r="CD12" s="309">
+      <c r="CD12" s="308">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="CG12" s="306"/>
+      <c r="CG12" s="305"/>
       <c r="CH12" s="241"/>
       <c r="CI12" s="241"/>
     </row>
-    <row r="13" spans="1:87" s="312" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="308" t="s">
+    <row r="13" spans="1:87" s="311" customFormat="1" ht="15" customHeight="1">
+      <c r="A13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="308" t="s">
+      <c r="B13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="308" t="s">
+      <c r="C13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="309"/>
-      <c r="E13" s="309"/>
-      <c r="F13" s="309"/>
-      <c r="G13" s="308" t="s">
+      <c r="D13" s="308"/>
+      <c r="E13" s="308"/>
+      <c r="F13" s="308"/>
+      <c r="G13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="308" t="s">
+      <c r="H13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="308" t="s">
+      <c r="I13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="J13" s="309"/>
-      <c r="K13" s="309"/>
-      <c r="L13" s="309"/>
-      <c r="M13" s="309"/>
-      <c r="N13" s="309"/>
-      <c r="O13" s="309"/>
-      <c r="P13" s="309"/>
-      <c r="Q13" s="309"/>
-      <c r="R13" s="309"/>
-      <c r="S13" s="309"/>
-      <c r="T13" s="309"/>
-      <c r="U13" s="309"/>
-      <c r="V13" s="309"/>
-      <c r="W13" s="309"/>
-      <c r="X13" s="309"/>
-      <c r="Y13" s="309"/>
-      <c r="Z13" s="309"/>
-      <c r="AA13" s="309"/>
-      <c r="AB13" s="309"/>
-      <c r="AC13" s="309"/>
-      <c r="AD13" s="309"/>
-      <c r="AE13" s="309"/>
-      <c r="AF13" s="309"/>
-      <c r="AG13" s="309"/>
-      <c r="AH13" s="309"/>
-      <c r="AI13" s="309"/>
-      <c r="AJ13" s="309"/>
-      <c r="AK13" s="309"/>
-      <c r="AL13" s="309"/>
-      <c r="AM13" s="309"/>
-      <c r="AN13" s="309"/>
-      <c r="AO13" s="309"/>
-      <c r="AP13" s="309"/>
-      <c r="AQ13" s="309"/>
-      <c r="AR13" s="309"/>
-      <c r="AS13" s="309"/>
-      <c r="AT13" s="309"/>
-      <c r="AU13" s="309"/>
-      <c r="AV13" s="309"/>
-      <c r="AW13" s="309"/>
-      <c r="AX13" s="309"/>
-      <c r="AY13" s="309"/>
-      <c r="AZ13" s="309"/>
-      <c r="BA13" s="309"/>
-      <c r="BB13" s="309"/>
-      <c r="BC13" s="309"/>
-      <c r="BD13" s="309"/>
-      <c r="BE13" s="309"/>
-      <c r="BF13" s="309"/>
-      <c r="BG13" s="309"/>
-      <c r="BH13" s="309"/>
-      <c r="BI13" s="309"/>
-      <c r="BJ13" s="309"/>
-      <c r="BK13" s="309"/>
-      <c r="BL13" s="309"/>
-      <c r="BM13" s="309"/>
-      <c r="BN13" s="309"/>
-      <c r="BO13" s="309"/>
-      <c r="BP13" s="309"/>
-      <c r="BQ13" s="309"/>
-      <c r="BR13" s="309"/>
-      <c r="BS13" s="309"/>
-      <c r="BT13" s="309"/>
-      <c r="BU13" s="313"/>
-      <c r="BV13" s="310"/>
-      <c r="BW13" s="311"/>
-      <c r="BX13" s="309"/>
-      <c r="BY13" s="309"/>
-      <c r="BZ13" s="309"/>
-      <c r="CA13" s="309"/>
-      <c r="CB13" s="309"/>
-      <c r="CC13" s="309"/>
-      <c r="CD13" s="309"/>
-      <c r="CG13" s="306"/>
+      <c r="J13" s="308"/>
+      <c r="K13" s="308"/>
+      <c r="L13" s="308"/>
+      <c r="M13" s="308"/>
+      <c r="N13" s="308"/>
+      <c r="O13" s="308"/>
+      <c r="P13" s="308"/>
+      <c r="Q13" s="308"/>
+      <c r="R13" s="308"/>
+      <c r="S13" s="308"/>
+      <c r="T13" s="308"/>
+      <c r="U13" s="308"/>
+      <c r="V13" s="308"/>
+      <c r="W13" s="308"/>
+      <c r="X13" s="308"/>
+      <c r="Y13" s="308"/>
+      <c r="Z13" s="308"/>
+      <c r="AA13" s="308"/>
+      <c r="AB13" s="308"/>
+      <c r="AC13" s="308"/>
+      <c r="AD13" s="308"/>
+      <c r="AE13" s="308"/>
+      <c r="AF13" s="308"/>
+      <c r="AG13" s="308"/>
+      <c r="AH13" s="308"/>
+      <c r="AI13" s="308"/>
+      <c r="AJ13" s="308"/>
+      <c r="AK13" s="308"/>
+      <c r="AL13" s="308"/>
+      <c r="AM13" s="308"/>
+      <c r="AN13" s="308"/>
+      <c r="AO13" s="308"/>
+      <c r="AP13" s="308"/>
+      <c r="AQ13" s="308"/>
+      <c r="AR13" s="308"/>
+      <c r="AS13" s="308"/>
+      <c r="AT13" s="308"/>
+      <c r="AU13" s="308"/>
+      <c r="AV13" s="308"/>
+      <c r="AW13" s="308"/>
+      <c r="AX13" s="308"/>
+      <c r="AY13" s="308"/>
+      <c r="AZ13" s="308"/>
+      <c r="BA13" s="308"/>
+      <c r="BB13" s="308"/>
+      <c r="BC13" s="308"/>
+      <c r="BD13" s="308"/>
+      <c r="BE13" s="308"/>
+      <c r="BF13" s="308"/>
+      <c r="BG13" s="308"/>
+      <c r="BH13" s="308"/>
+      <c r="BI13" s="308"/>
+      <c r="BJ13" s="308"/>
+      <c r="BK13" s="308"/>
+      <c r="BL13" s="308"/>
+      <c r="BM13" s="308"/>
+      <c r="BN13" s="308"/>
+      <c r="BO13" s="308"/>
+      <c r="BP13" s="308"/>
+      <c r="BQ13" s="308"/>
+      <c r="BR13" s="308"/>
+      <c r="BS13" s="308"/>
+      <c r="BT13" s="308"/>
+      <c r="BU13" s="312"/>
+      <c r="BV13" s="309"/>
+      <c r="BW13" s="310"/>
+      <c r="BX13" s="308"/>
+      <c r="BY13" s="308"/>
+      <c r="BZ13" s="308"/>
+      <c r="CA13" s="308"/>
+      <c r="CB13" s="308"/>
+      <c r="CC13" s="308"/>
+      <c r="CD13" s="308"/>
+      <c r="CG13" s="305"/>
       <c r="CH13" s="241"/>
       <c r="CI13" s="241"/>
     </row>
@@ -9219,56 +9194,56 @@
         <v>183399990</v>
       </c>
       <c r="J14" s="94"/>
-      <c r="K14" s="314">
+      <c r="K14" s="313">
         <f t="shared" ref="K14:S14" si="4">SUM(K15:K21)</f>
         <v>166</v>
       </c>
-      <c r="L14" s="314">
+      <c r="L14" s="313">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="M14" s="314">
+      <c r="M14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N14" s="314">
+      <c r="N14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="O14" s="314">
+      <c r="O14" s="313">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P14" s="314">
+      <c r="P14" s="313">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="Q14" s="314">
+      <c r="Q14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="R14" s="314">
+      <c r="R14" s="313">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S14" s="314">
+      <c r="S14" s="313">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="T14" s="314"/>
-      <c r="U14" s="314">
+      <c r="T14" s="313"/>
+      <c r="U14" s="313">
         <f>SUM(U15:U21)</f>
         <v>2</v>
       </c>
-      <c r="V14" s="314">
+      <c r="V14" s="313">
         <f>SUM(V15:V21)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="314">
+      <c r="W14" s="313">
         <f>SUM(W15:W21)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="314">
+      <c r="X14" s="313">
         <f>SUM(X15:X21)</f>
         <v>0</v>
       </c>
@@ -9398,7 +9373,7 @@
       <c r="BR14" s="94"/>
       <c r="BS14" s="94"/>
       <c r="BT14" s="94"/>
-      <c r="BU14" s="315">
+      <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
         <v>226721558.59230769</v>
       </c>
@@ -9413,241 +9388,241 @@
       <c r="CD14" s="243"/>
     </row>
     <row r="15" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
-      <c r="A15" s="271">
+      <c r="A15" s="270">
         <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
-      <c r="B15" s="272">
+      <c r="B15" s="271">
         <v>2405236</v>
       </c>
-      <c r="C15" s="273" t="s">
+      <c r="C15" s="272" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="274" t="s">
+      <c r="D15" s="273" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="275" t="s">
+      <c r="E15" s="274" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="275" t="s">
+      <c r="F15" s="274" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="276">
+      <c r="G15" s="275">
         <v>9520000</v>
       </c>
-      <c r="H15" s="276">
+      <c r="H15" s="275">
         <f t="shared" ref="H15:H21" si="7">+IF(OR(CC15="ĐT PCCC",CC15="ĐP PCCC"),780000,IF(CC15="AT-VSV",300000,0))</f>
         <v>0</v>
       </c>
-      <c r="I15" s="276">
+      <c r="I15" s="275">
         <f t="shared" ref="I15:I21" si="8">CB15-BZ15-G15-H15</f>
         <v>53480000</v>
       </c>
-      <c r="J15" s="277">
+      <c r="J15" s="276">
         <v>1</v>
       </c>
-      <c r="K15" s="278">
+      <c r="K15" s="277">
         <v>26</v>
       </c>
-      <c r="L15" s="278">
-        <v>0</v>
-      </c>
-      <c r="M15" s="278">
-        <v>0</v>
-      </c>
-      <c r="N15" s="278">
-        <v>0</v>
-      </c>
-      <c r="O15" s="278">
-        <v>0</v>
-      </c>
-      <c r="P15" s="278">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="278">
-        <v>0</v>
-      </c>
-      <c r="R15" s="278">
-        <v>0</v>
-      </c>
-      <c r="S15" s="278">
-        <v>0</v>
-      </c>
-      <c r="T15" s="278"/>
-      <c r="U15" s="278">
-        <v>0</v>
-      </c>
-      <c r="V15" s="278">
-        <v>0</v>
-      </c>
-      <c r="W15" s="278">
-        <v>0</v>
-      </c>
-      <c r="X15" s="278">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="276">
+      <c r="L15" s="277">
+        <v>0</v>
+      </c>
+      <c r="M15" s="277">
+        <v>0</v>
+      </c>
+      <c r="N15" s="277">
+        <v>0</v>
+      </c>
+      <c r="O15" s="277">
+        <v>0</v>
+      </c>
+      <c r="P15" s="277">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="277">
+        <v>0</v>
+      </c>
+      <c r="R15" s="277">
+        <v>0</v>
+      </c>
+      <c r="S15" s="277">
+        <v>0</v>
+      </c>
+      <c r="T15" s="277"/>
+      <c r="U15" s="277">
+        <v>0</v>
+      </c>
+      <c r="V15" s="277">
+        <v>0</v>
+      </c>
+      <c r="W15" s="277">
+        <v>0</v>
+      </c>
+      <c r="X15" s="277">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="275">
         <f t="shared" ref="Y15:Y21" si="9">G15*(K15+L15)/26</f>
         <v>9520000</v>
       </c>
-      <c r="Z15" s="276">
+      <c r="Z15" s="275">
         <f t="shared" ref="Z15:Z21" si="10">M15*G15/26</f>
         <v>0</v>
       </c>
-      <c r="AA15" s="276">
+      <c r="AA15" s="275">
         <f t="shared" ref="AA15:AA21" si="11">G15*N15/26</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="276">
+      <c r="AB15" s="275">
         <f t="shared" ref="AB15:AB21" si="12">G15*O15/26</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="276">
+      <c r="AC15" s="275">
         <f t="shared" ref="AC15:AC21" si="13">G15*P15*150%/26</f>
         <v>0</v>
       </c>
-      <c r="AD15" s="276">
+      <c r="AD15" s="275">
         <f t="shared" ref="AD15:AD21" si="14">G15*Q15/26*200%</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="276">
+      <c r="AE15" s="275">
         <f t="shared" ref="AE15:AE21" si="15">G15*R15/26*300%</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="276">
+      <c r="AF15" s="275">
         <f>ROUND((G15+H15)/26*S15*30%,0)</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="276">
+      <c r="AG15" s="275">
         <f t="shared" ref="AG15:AG21" si="16">T15*G15/26/8</f>
         <v>0</v>
       </c>
-      <c r="AH15" s="276">
+      <c r="AH15" s="275">
         <f t="shared" ref="AH15:AH21" si="17">CB15/26*U15</f>
         <v>0</v>
       </c>
-      <c r="AI15" s="276">
+      <c r="AI15" s="275">
         <f t="shared" ref="AI15:AI21" si="18">G15*V15/26</f>
         <v>0</v>
       </c>
-      <c r="AJ15" s="276"/>
-      <c r="AK15" s="276">
+      <c r="AJ15" s="275"/>
+      <c r="AK15" s="275">
         <f t="shared" ref="AK15:AK21" si="19">BZ15*L15/26</f>
         <v>0</v>
       </c>
-      <c r="AL15" s="276"/>
-      <c r="AM15" s="276">
+      <c r="AL15" s="275"/>
+      <c r="AM15" s="275">
         <f t="shared" ref="AM15:AM21" si="20">X15*CD15</f>
         <v>0</v>
       </c>
-      <c r="AN15" s="276">
+      <c r="AN15" s="275">
         <f>H15/26*(K15+L15)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="276">
+      <c r="AO15" s="275">
         <f t="shared" ref="AO15:AO21" si="21">IF(F15="LN",I15*(K15+L15)/26+(H15+I15)*50%*M15/26+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15,I15-I15*($CE$11-K15-L15)/26+(H15+I15)*50%*M15/26+BW15*O15/26-AB15+MAX($G15*P15/26*150%,P15*$BW15/26)-AC15+MAX($G15*Q15/26*200%,Q15*$BW15/26)-AD15+MAX($G15*R15/26*300%,R15*$BW15/26)-AE15+BW15*S15/26-AF15+AH15-AG15+(G15-G15*($CE$11-K15-L15)/26-Y15)+(H15-H15*($CE$11-K15-L15)/26-AN15))</f>
         <v>53480000</v>
       </c>
-      <c r="AP15" s="276"/>
-      <c r="AQ15" s="276"/>
-      <c r="AR15" s="276">
+      <c r="AP15" s="275"/>
+      <c r="AQ15" s="275"/>
+      <c r="AR15" s="275">
         <v>1000000</v>
       </c>
-      <c r="AS15" s="276"/>
-      <c r="AT15" s="276"/>
-      <c r="AU15" s="276"/>
-      <c r="AV15" s="276">
+      <c r="AS15" s="275"/>
+      <c r="AT15" s="275"/>
+      <c r="AU15" s="275"/>
+      <c r="AV15" s="275">
         <f t="shared" ref="AV15:AV21" si="22">Y15+Z15+AA15+AB15+AC15+AD15+AE15+AF15+AG15+AI15+AJ15+AK15+AL15+AM15+AN15+AO15+AP15-AQ15+AR15+AS15+AT15+AU15</f>
         <v>64000000</v>
       </c>
-      <c r="AW15" s="276"/>
-      <c r="AX15" s="276" t="str">
+      <c r="AW15" s="275"/>
+      <c r="AX15" s="275" t="str">
         <f t="shared" ref="AX15:AX21" si="23">IF(E15="CT","x",0)</f>
         <v>x</v>
       </c>
-      <c r="AY15" s="279">
+      <c r="AY15" s="278">
         <f t="shared" ref="AY15:BA21" si="24">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
         <v>761600</v>
       </c>
-      <c r="AZ15" s="279">
+      <c r="AZ15" s="278">
         <f t="shared" si="24"/>
         <v>142800</v>
       </c>
-      <c r="BA15" s="279">
+      <c r="BA15" s="278">
         <f t="shared" si="24"/>
         <v>95200</v>
       </c>
-      <c r="BB15" s="279">
+      <c r="BB15" s="278">
         <f t="shared" ref="BB15:BB21" si="25">SUM(AY15:BA15)</f>
         <v>999600</v>
       </c>
-      <c r="BC15" s="279"/>
-      <c r="BD15" s="279"/>
-      <c r="BE15" s="279">
+      <c r="BC15" s="278"/>
+      <c r="BD15" s="278"/>
+      <c r="BE15" s="278">
         <f t="shared" ref="BE15:BE21" si="26">IF(G15*1%&gt;=234000,234000,G15*1%)</f>
         <v>95200</v>
       </c>
-      <c r="BF15" s="279">
+      <c r="BF15" s="278">
         <f>AM15+IF(E15="CT",IF(AR15&gt;=730000,730000,AR15),0)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
         <v>10220500</v>
       </c>
-      <c r="BG15" s="279">
+      <c r="BG15" s="278">
         <f t="shared" ref="BG15:BG21" si="27">AV15-BF15+AW15</f>
         <v>53779500</v>
       </c>
-      <c r="BH15" s="279">
+      <c r="BH15" s="278">
         <v>3</v>
       </c>
-      <c r="BI15" s="279">
+      <c r="BI15" s="278">
         <v>6200000</v>
       </c>
-      <c r="BJ15" s="279">
+      <c r="BJ15" s="278">
         <f>IF(E15="CT",15500000,0)</f>
         <v>15500000</v>
       </c>
-      <c r="BK15" s="279">
+      <c r="BK15" s="278">
         <f t="shared" ref="BK15:BK21" si="28">BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
         <v>18679900</v>
       </c>
-      <c r="BL15" s="280">
+      <c r="BL15" s="279">
         <f t="shared" ref="BL15:BL21" si="29">IF(E15="TV",BK15*10%,IF(BK15&gt;0,ROUND(IF(BK15&gt;=80000000,BK15*35%-9850000,IF(BK15&gt;=52000000,BK15*30%-5850000,IF(BK15&gt;=32000000,BK15*25%-3250000,IF(BK15&gt;=18000000,BK15*20%-1650000,IF(BK15&gt;=10000000,BK15*15%-750000,IF(BK15&gt;5000000,BK15*10%-250000,BK15*5%)))))),0),0))</f>
         <v>2085980</v>
       </c>
-      <c r="BM15" s="279"/>
-      <c r="BN15" s="279"/>
-      <c r="BO15" s="279">
-        <v>0</v>
-      </c>
-      <c r="BP15" s="279"/>
-      <c r="BQ15" s="279"/>
-      <c r="BR15" s="279"/>
-      <c r="BS15" s="279"/>
-      <c r="BT15" s="330"/>
-      <c r="BU15" s="281">
+      <c r="BM15" s="278"/>
+      <c r="BN15" s="278"/>
+      <c r="BO15" s="278">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="278"/>
+      <c r="BQ15" s="278"/>
+      <c r="BR15" s="278"/>
+      <c r="BS15" s="278"/>
+      <c r="BT15" s="328"/>
+      <c r="BU15" s="280">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
         <v>60819220</v>
       </c>
       <c r="BV15" s="252"/>
-      <c r="BW15" s="282">
+      <c r="BW15" s="281">
         <v>60000000</v>
       </c>
-      <c r="BX15" s="280">
-        <v>0</v>
-      </c>
-      <c r="BY15" s="280"/>
-      <c r="BZ15" s="280">
+      <c r="BX15" s="279">
+        <v>0</v>
+      </c>
+      <c r="BY15" s="279"/>
+      <c r="BZ15" s="279">
         <v>200000</v>
       </c>
-      <c r="CA15" s="280">
+      <c r="CA15" s="279">
         <f t="shared" ref="CA15:CA21" si="31">+BW15*5%</f>
         <v>3000000</v>
       </c>
-      <c r="CB15" s="280">
+      <c r="CB15" s="279">
         <f t="shared" ref="CB15:CB21" si="32">SUM(BW15:CA15)</f>
         <v>63200000</v>
       </c>
-      <c r="CC15" s="280"/>
-      <c r="CD15" s="280"/>
+      <c r="CC15" s="279"/>
+      <c r="CD15" s="279"/>
       <c r="CE15" s="253"/>
       <c r="CF15" s="254"/>
       <c r="CG15" s="254"/>
@@ -9838,7 +9813,7 @@
         <v>40832692.307692312</v>
       </c>
       <c r="BH16" s="250"/>
-      <c r="BI16" s="279">
+      <c r="BI16" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ16" s="250">
@@ -10080,7 +10055,7 @@
         <v>35713076.923076928</v>
       </c>
       <c r="BH17" s="250"/>
-      <c r="BI17" s="279">
+      <c r="BI17" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ17" s="250">
@@ -10322,7 +10297,7 @@
         <v>22247115.384615384</v>
       </c>
       <c r="BH18" s="250"/>
-      <c r="BI18" s="279">
+      <c r="BI18" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ18" s="250">
@@ -10564,7 +10539,7 @@
         <v>9879615.3846153859</v>
       </c>
       <c r="BH19" s="250"/>
-      <c r="BI19" s="279">
+      <c r="BI19" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ19" s="250">
@@ -10806,7 +10781,7 @@
         <v>21247500</v>
       </c>
       <c r="BH20" s="250"/>
-      <c r="BI20" s="279">
+      <c r="BI20" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ20" s="250">
@@ -11050,7 +11025,7 @@
         <v>19128270.53846154</v>
       </c>
       <c r="BH21" s="250"/>
-      <c r="BI21" s="279">
+      <c r="BI21" s="278">
         <v>6200000</v>
       </c>
       <c r="BJ21" s="250">
@@ -11126,9 +11101,9 @@
       <c r="T22" s="40"/>
       <c r="U22" s="41"/>
       <c r="V22" s="41"/>
-      <c r="W22" s="316"/>
-      <c r="X22" s="316"/>
-      <c r="AC22" s="317"/>
+      <c r="W22" s="315"/>
+      <c r="X22" s="315"/>
+      <c r="AC22" s="316"/>
       <c r="BL22" s="45"/>
       <c r="BP22" s="45"/>
       <c r="BQ22" s="45"/>
@@ -11221,8 +11196,8 @@
       <c r="R24" s="53"/>
       <c r="U24" s="54"/>
       <c r="V24" s="54"/>
-      <c r="W24" s="318"/>
-      <c r="X24" s="318"/>
+      <c r="W24" s="317"/>
+      <c r="X24" s="317"/>
       <c r="AN24" s="58"/>
       <c r="AV24" s="49"/>
       <c r="AW24" s="49"/>
@@ -11538,87 +11513,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="419"/>
-      <c r="B3" s="410"/>
-      <c r="C3" s="410"/>
-      <c r="D3" s="410"/>
-      <c r="E3" s="410"/>
-      <c r="F3" s="410"/>
-      <c r="G3" s="410"/>
-      <c r="H3" s="410"/>
-      <c r="I3" s="410"/>
-      <c r="J3" s="410"/>
-      <c r="K3" s="410"/>
-      <c r="L3" s="410"/>
-      <c r="M3" s="410"/>
-      <c r="N3" s="410"/>
-      <c r="O3" s="410"/>
-      <c r="P3" s="410"/>
-      <c r="Q3" s="410"/>
-      <c r="R3" s="410"/>
-      <c r="S3" s="410"/>
-      <c r="T3" s="410"/>
-      <c r="U3" s="410"/>
-      <c r="V3" s="410"/>
-      <c r="W3" s="410"/>
-      <c r="X3" s="410"/>
-      <c r="Y3" s="410"/>
-      <c r="Z3" s="410"/>
-      <c r="AA3" s="410"/>
-      <c r="AB3" s="410"/>
-      <c r="AC3" s="410"/>
-      <c r="AD3" s="410"/>
-      <c r="AE3" s="410"/>
-      <c r="AF3" s="410"/>
-      <c r="AG3" s="410"/>
-      <c r="AH3" s="410"/>
-      <c r="AI3" s="410"/>
-      <c r="AJ3" s="410"/>
-      <c r="AK3" s="410"/>
-      <c r="AL3" s="410"/>
-      <c r="AM3" s="410"/>
-      <c r="AN3" s="410"/>
-      <c r="AO3" s="410"/>
-      <c r="AP3" s="410"/>
-      <c r="AQ3" s="410"/>
-      <c r="AR3" s="410"/>
-      <c r="AS3" s="410"/>
-      <c r="AT3" s="410"/>
-      <c r="AU3" s="410"/>
-      <c r="AV3" s="410"/>
-      <c r="AW3" s="410"/>
-      <c r="AX3" s="410"/>
-      <c r="AY3" s="410"/>
-      <c r="AZ3" s="410"/>
-      <c r="BA3" s="410"/>
-      <c r="BB3" s="410"/>
-      <c r="BC3" s="410"/>
-      <c r="BD3" s="410"/>
-      <c r="BE3" s="410"/>
-      <c r="BF3" s="410"/>
-      <c r="BG3" s="410"/>
-      <c r="BH3" s="410"/>
-      <c r="BI3" s="410"/>
-      <c r="BJ3" s="410"/>
-      <c r="BK3" s="410"/>
-      <c r="BL3" s="410"/>
-      <c r="BM3" s="410"/>
-      <c r="BN3" s="410"/>
-      <c r="BO3" s="410"/>
-      <c r="BP3" s="410"/>
-      <c r="BQ3" s="410"/>
-      <c r="BR3" s="410"/>
-      <c r="BS3" s="410"/>
-      <c r="BT3" s="410"/>
-      <c r="BU3" s="410"/>
-      <c r="BW3" s="409" t="s">
+      <c r="A3" s="408"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="399"/>
+      <c r="I3" s="399"/>
+      <c r="J3" s="399"/>
+      <c r="K3" s="399"/>
+      <c r="L3" s="399"/>
+      <c r="M3" s="399"/>
+      <c r="N3" s="399"/>
+      <c r="O3" s="399"/>
+      <c r="P3" s="399"/>
+      <c r="Q3" s="399"/>
+      <c r="R3" s="399"/>
+      <c r="S3" s="399"/>
+      <c r="T3" s="399"/>
+      <c r="U3" s="399"/>
+      <c r="V3" s="399"/>
+      <c r="W3" s="399"/>
+      <c r="X3" s="399"/>
+      <c r="Y3" s="399"/>
+      <c r="Z3" s="399"/>
+      <c r="AA3" s="399"/>
+      <c r="AB3" s="399"/>
+      <c r="AC3" s="399"/>
+      <c r="AD3" s="399"/>
+      <c r="AE3" s="399"/>
+      <c r="AF3" s="399"/>
+      <c r="AG3" s="399"/>
+      <c r="AH3" s="399"/>
+      <c r="AI3" s="399"/>
+      <c r="AJ3" s="399"/>
+      <c r="AK3" s="399"/>
+      <c r="AL3" s="399"/>
+      <c r="AM3" s="399"/>
+      <c r="AN3" s="399"/>
+      <c r="AO3" s="399"/>
+      <c r="AP3" s="399"/>
+      <c r="AQ3" s="399"/>
+      <c r="AR3" s="399"/>
+      <c r="AS3" s="399"/>
+      <c r="AT3" s="399"/>
+      <c r="AU3" s="399"/>
+      <c r="AV3" s="399"/>
+      <c r="AW3" s="399"/>
+      <c r="AX3" s="399"/>
+      <c r="AY3" s="399"/>
+      <c r="AZ3" s="399"/>
+      <c r="BA3" s="399"/>
+      <c r="BB3" s="399"/>
+      <c r="BC3" s="399"/>
+      <c r="BD3" s="399"/>
+      <c r="BE3" s="399"/>
+      <c r="BF3" s="399"/>
+      <c r="BG3" s="399"/>
+      <c r="BH3" s="399"/>
+      <c r="BI3" s="399"/>
+      <c r="BJ3" s="399"/>
+      <c r="BK3" s="399"/>
+      <c r="BL3" s="399"/>
+      <c r="BM3" s="399"/>
+      <c r="BN3" s="399"/>
+      <c r="BO3" s="399"/>
+      <c r="BP3" s="399"/>
+      <c r="BQ3" s="399"/>
+      <c r="BR3" s="399"/>
+      <c r="BS3" s="399"/>
+      <c r="BT3" s="399"/>
+      <c r="BU3" s="399"/>
+      <c r="BW3" s="398" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="410"/>
-      <c r="BY3" s="410"/>
-      <c r="BZ3" s="410"/>
-      <c r="CA3" s="410"/>
-      <c r="CB3" s="410"/>
+      <c r="BX3" s="399"/>
+      <c r="BY3" s="399"/>
+      <c r="BZ3" s="399"/>
+      <c r="CA3" s="399"/>
+      <c r="CB3" s="399"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11701,364 +11676,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="410"/>
-      <c r="BX4" s="410"/>
-      <c r="BY4" s="410"/>
-      <c r="BZ4" s="410"/>
-      <c r="CA4" s="410"/>
-      <c r="CB4" s="410"/>
+      <c r="BW4" s="399"/>
+      <c r="BX4" s="399"/>
+      <c r="BY4" s="399"/>
+      <c r="BZ4" s="399"/>
+      <c r="CA4" s="399"/>
+      <c r="CB4" s="399"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="422" t="s">
+      <c r="A5" s="411" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="421" t="s">
+      <c r="B5" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="395" t="s">
+      <c r="C5" s="384" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="420" t="s">
+      <c r="D5" s="409" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="420" t="s">
+      <c r="E5" s="409" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="395" t="s">
+      <c r="F5" s="384" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="395" t="s">
+      <c r="G5" s="384" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="338" t="s">
+      <c r="H5" s="335" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="338" t="s">
+      <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="395" t="s">
+      <c r="J5" s="384" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="424" t="s">
+      <c r="K5" s="413" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="406"/>
-      <c r="M5" s="406"/>
-      <c r="N5" s="406"/>
-      <c r="O5" s="406"/>
-      <c r="P5" s="406"/>
-      <c r="Q5" s="406"/>
-      <c r="R5" s="406"/>
-      <c r="S5" s="406"/>
-      <c r="T5" s="406"/>
-      <c r="U5" s="406"/>
-      <c r="V5" s="406"/>
-      <c r="W5" s="406"/>
-      <c r="X5" s="406"/>
-      <c r="Y5" s="395" t="s">
+      <c r="L5" s="395"/>
+      <c r="M5" s="395"/>
+      <c r="N5" s="395"/>
+      <c r="O5" s="395"/>
+      <c r="P5" s="395"/>
+      <c r="Q5" s="395"/>
+      <c r="R5" s="395"/>
+      <c r="S5" s="395"/>
+      <c r="T5" s="395"/>
+      <c r="U5" s="395"/>
+      <c r="V5" s="395"/>
+      <c r="W5" s="395"/>
+      <c r="X5" s="395"/>
+      <c r="Y5" s="384" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="406"/>
-      <c r="AA5" s="406"/>
-      <c r="AB5" s="406"/>
-      <c r="AC5" s="406"/>
-      <c r="AD5" s="406"/>
-      <c r="AE5" s="406"/>
-      <c r="AF5" s="406"/>
-      <c r="AG5" s="406"/>
-      <c r="AH5" s="406"/>
-      <c r="AI5" s="406"/>
-      <c r="AJ5" s="406"/>
-      <c r="AK5" s="406"/>
-      <c r="AL5" s="406"/>
-      <c r="AM5" s="406"/>
-      <c r="AN5" s="406"/>
-      <c r="AO5" s="407"/>
-      <c r="AP5" s="395" t="s">
+      <c r="Z5" s="395"/>
+      <c r="AA5" s="395"/>
+      <c r="AB5" s="395"/>
+      <c r="AC5" s="395"/>
+      <c r="AD5" s="395"/>
+      <c r="AE5" s="395"/>
+      <c r="AF5" s="395"/>
+      <c r="AG5" s="395"/>
+      <c r="AH5" s="395"/>
+      <c r="AI5" s="395"/>
+      <c r="AJ5" s="395"/>
+      <c r="AK5" s="395"/>
+      <c r="AL5" s="395"/>
+      <c r="AM5" s="395"/>
+      <c r="AN5" s="395"/>
+      <c r="AO5" s="396"/>
+      <c r="AP5" s="384" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="395" t="s">
+      <c r="AQ5" s="384" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="395" t="s">
+      <c r="AR5" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="395" t="s">
+      <c r="AS5" s="384" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="395" t="s">
+      <c r="AT5" s="384" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="395" t="s">
+      <c r="AU5" s="384" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="395" t="s">
+      <c r="AV5" s="384" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="395" t="s">
+      <c r="AW5" s="384" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="395" t="s">
+      <c r="AX5" s="384" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="405" t="s">
+      <c r="AY5" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="406"/>
-      <c r="BA5" s="406"/>
-      <c r="BB5" s="406"/>
-      <c r="BC5" s="406"/>
-      <c r="BD5" s="406"/>
-      <c r="BE5" s="406"/>
-      <c r="BF5" s="406"/>
-      <c r="BG5" s="406"/>
-      <c r="BH5" s="406"/>
-      <c r="BI5" s="406"/>
-      <c r="BJ5" s="406"/>
-      <c r="BK5" s="406"/>
-      <c r="BL5" s="406"/>
-      <c r="BM5" s="406"/>
-      <c r="BN5" s="406"/>
-      <c r="BO5" s="406"/>
-      <c r="BP5" s="406"/>
-      <c r="BQ5" s="407"/>
-      <c r="BR5" s="411" t="s">
+      <c r="AZ5" s="395"/>
+      <c r="BA5" s="395"/>
+      <c r="BB5" s="395"/>
+      <c r="BC5" s="395"/>
+      <c r="BD5" s="395"/>
+      <c r="BE5" s="395"/>
+      <c r="BF5" s="395"/>
+      <c r="BG5" s="395"/>
+      <c r="BH5" s="395"/>
+      <c r="BI5" s="395"/>
+      <c r="BJ5" s="395"/>
+      <c r="BK5" s="395"/>
+      <c r="BL5" s="395"/>
+      <c r="BM5" s="395"/>
+      <c r="BN5" s="395"/>
+      <c r="BO5" s="395"/>
+      <c r="BP5" s="395"/>
+      <c r="BQ5" s="396"/>
+      <c r="BR5" s="400" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="412"/>
-      <c r="BT5" s="405" t="s">
+      <c r="BS5" s="401"/>
+      <c r="BT5" s="394" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="399" t="s">
+      <c r="BU5" s="388" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="402" t="s">
+      <c r="BW5" s="391" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="413" t="s">
+      <c r="BX5" s="402" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="414"/>
-      <c r="BZ5" s="414"/>
-      <c r="CA5" s="412"/>
-      <c r="CB5" s="408" t="s">
+      <c r="BY5" s="403"/>
+      <c r="BZ5" s="403"/>
+      <c r="CA5" s="401"/>
+      <c r="CB5" s="397" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="390" t="s">
+      <c r="CC5" s="379" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="390" t="s">
+      <c r="CD5" s="379" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="391"/>
-      <c r="B6" s="391"/>
-      <c r="C6" s="391"/>
-      <c r="D6" s="391"/>
-      <c r="E6" s="391"/>
-      <c r="F6" s="391"/>
-      <c r="G6" s="391"/>
-      <c r="H6" s="391"/>
-      <c r="I6" s="391"/>
-      <c r="J6" s="391"/>
-      <c r="K6" s="396" t="s">
+      <c r="A6" s="380"/>
+      <c r="B6" s="380"/>
+      <c r="C6" s="380"/>
+      <c r="D6" s="380"/>
+      <c r="E6" s="380"/>
+      <c r="F6" s="380"/>
+      <c r="G6" s="380"/>
+      <c r="H6" s="380"/>
+      <c r="I6" s="380"/>
+      <c r="J6" s="380"/>
+      <c r="K6" s="385" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="396" t="s">
+      <c r="L6" s="385" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="396" t="s">
+      <c r="M6" s="385" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="396" t="s">
+      <c r="N6" s="385" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="396" t="s">
+      <c r="O6" s="385" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="396" t="s">
+      <c r="P6" s="385" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="396" t="s">
+      <c r="Q6" s="385" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="396" t="s">
+      <c r="R6" s="385" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="396" t="s">
+      <c r="S6" s="385" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="396" t="s">
+      <c r="T6" s="385" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="396" t="s">
+      <c r="U6" s="385" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="426" t="s">
+      <c r="V6" s="415" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="412"/>
-      <c r="X6" s="396" t="s">
+      <c r="W6" s="401"/>
+      <c r="X6" s="385" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="395" t="s">
+      <c r="Y6" s="384" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="395" t="s">
+      <c r="Z6" s="384" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="395" t="s">
+      <c r="AA6" s="384" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="395" t="s">
+      <c r="AB6" s="384" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="338" t="s">
+      <c r="AC6" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="338" t="s">
+      <c r="AD6" s="335" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="338" t="s">
+      <c r="AE6" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="338" t="s">
+      <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="395" t="s">
+      <c r="AG6" s="384" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="338" t="s">
+      <c r="AH6" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="338" t="s">
+      <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="395" t="s">
+      <c r="AJ6" s="384" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="423" t="s">
+      <c r="AK6" s="412" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="395" t="s">
+      <c r="AL6" s="384" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="395" t="s">
+      <c r="AM6" s="384" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="425" t="s">
+      <c r="AN6" s="414" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="395" t="s">
+      <c r="AO6" s="384" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="391"/>
-      <c r="AQ6" s="391"/>
-      <c r="AR6" s="391"/>
-      <c r="AS6" s="391"/>
-      <c r="AT6" s="391"/>
-      <c r="AU6" s="391"/>
-      <c r="AV6" s="391"/>
-      <c r="AW6" s="391"/>
-      <c r="AX6" s="391"/>
-      <c r="AY6" s="405" t="s">
+      <c r="AP6" s="380"/>
+      <c r="AQ6" s="380"/>
+      <c r="AR6" s="380"/>
+      <c r="AS6" s="380"/>
+      <c r="AT6" s="380"/>
+      <c r="AU6" s="380"/>
+      <c r="AV6" s="380"/>
+      <c r="AW6" s="380"/>
+      <c r="AX6" s="380"/>
+      <c r="AY6" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="406"/>
-      <c r="BA6" s="406"/>
-      <c r="BB6" s="406"/>
-      <c r="BC6" s="406"/>
-      <c r="BD6" s="406"/>
-      <c r="BE6" s="406"/>
-      <c r="BF6" s="406"/>
-      <c r="BG6" s="406"/>
-      <c r="BH6" s="406"/>
-      <c r="BI6" s="406"/>
-      <c r="BJ6" s="406"/>
-      <c r="BK6" s="406"/>
-      <c r="BL6" s="407"/>
-      <c r="BM6" s="405" t="s">
+      <c r="AZ6" s="395"/>
+      <c r="BA6" s="395"/>
+      <c r="BB6" s="395"/>
+      <c r="BC6" s="395"/>
+      <c r="BD6" s="395"/>
+      <c r="BE6" s="395"/>
+      <c r="BF6" s="395"/>
+      <c r="BG6" s="395"/>
+      <c r="BH6" s="395"/>
+      <c r="BI6" s="395"/>
+      <c r="BJ6" s="395"/>
+      <c r="BK6" s="395"/>
+      <c r="BL6" s="396"/>
+      <c r="BM6" s="394" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="406"/>
-      <c r="BO6" s="406"/>
-      <c r="BP6" s="406"/>
-      <c r="BQ6" s="407"/>
-      <c r="BR6" s="393" t="s">
+      <c r="BN6" s="395"/>
+      <c r="BO6" s="395"/>
+      <c r="BP6" s="395"/>
+      <c r="BQ6" s="396"/>
+      <c r="BR6" s="382" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="393" t="s">
+      <c r="BS6" s="382" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="391"/>
-      <c r="BU6" s="400"/>
-      <c r="BW6" s="403"/>
-      <c r="BX6" s="400"/>
-      <c r="BY6" s="415"/>
-      <c r="BZ6" s="415"/>
-      <c r="CA6" s="403"/>
-      <c r="CB6" s="391"/>
-      <c r="CC6" s="391"/>
-      <c r="CD6" s="391"/>
+      <c r="BT6" s="380"/>
+      <c r="BU6" s="389"/>
+      <c r="BW6" s="392"/>
+      <c r="BX6" s="389"/>
+      <c r="BY6" s="404"/>
+      <c r="BZ6" s="404"/>
+      <c r="CA6" s="392"/>
+      <c r="CB6" s="380"/>
+      <c r="CC6" s="380"/>
+      <c r="CD6" s="380"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="391"/>
-      <c r="B7" s="391"/>
-      <c r="C7" s="391"/>
-      <c r="D7" s="391"/>
-      <c r="E7" s="391"/>
-      <c r="F7" s="391"/>
-      <c r="G7" s="391"/>
-      <c r="H7" s="391"/>
-      <c r="I7" s="391"/>
-      <c r="J7" s="391"/>
-      <c r="K7" s="391"/>
-      <c r="L7" s="391"/>
-      <c r="M7" s="391"/>
-      <c r="N7" s="391"/>
-      <c r="O7" s="391"/>
-      <c r="P7" s="391"/>
-      <c r="Q7" s="391"/>
-      <c r="R7" s="391"/>
-      <c r="S7" s="391"/>
-      <c r="T7" s="391"/>
-      <c r="U7" s="391"/>
-      <c r="V7" s="401"/>
-      <c r="W7" s="427"/>
-      <c r="X7" s="391"/>
-      <c r="Y7" s="391"/>
-      <c r="Z7" s="391"/>
-      <c r="AA7" s="391"/>
-      <c r="AB7" s="391"/>
-      <c r="AC7" s="391"/>
-      <c r="AD7" s="391"/>
-      <c r="AE7" s="391"/>
-      <c r="AF7" s="391"/>
-      <c r="AG7" s="391"/>
-      <c r="AH7" s="391"/>
-      <c r="AI7" s="391"/>
-      <c r="AJ7" s="391"/>
-      <c r="AK7" s="400"/>
-      <c r="AL7" s="391"/>
-      <c r="AM7" s="391"/>
-      <c r="AN7" s="391"/>
-      <c r="AO7" s="391"/>
-      <c r="AP7" s="391"/>
-      <c r="AQ7" s="391"/>
-      <c r="AR7" s="391"/>
-      <c r="AS7" s="391"/>
-      <c r="AT7" s="391"/>
-      <c r="AU7" s="391"/>
-      <c r="AV7" s="391"/>
-      <c r="AW7" s="391"/>
-      <c r="AX7" s="391"/>
+      <c r="A7" s="380"/>
+      <c r="B7" s="380"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
+      <c r="E7" s="380"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="380"/>
+      <c r="H7" s="380"/>
+      <c r="I7" s="380"/>
+      <c r="J7" s="380"/>
+      <c r="K7" s="380"/>
+      <c r="L7" s="380"/>
+      <c r="M7" s="380"/>
+      <c r="N7" s="380"/>
+      <c r="O7" s="380"/>
+      <c r="P7" s="380"/>
+      <c r="Q7" s="380"/>
+      <c r="R7" s="380"/>
+      <c r="S7" s="380"/>
+      <c r="T7" s="380"/>
+      <c r="U7" s="380"/>
+      <c r="V7" s="390"/>
+      <c r="W7" s="416"/>
+      <c r="X7" s="380"/>
+      <c r="Y7" s="380"/>
+      <c r="Z7" s="380"/>
+      <c r="AA7" s="380"/>
+      <c r="AB7" s="380"/>
+      <c r="AC7" s="380"/>
+      <c r="AD7" s="380"/>
+      <c r="AE7" s="380"/>
+      <c r="AF7" s="380"/>
+      <c r="AG7" s="380"/>
+      <c r="AH7" s="380"/>
+      <c r="AI7" s="380"/>
+      <c r="AJ7" s="380"/>
+      <c r="AK7" s="389"/>
+      <c r="AL7" s="380"/>
+      <c r="AM7" s="380"/>
+      <c r="AN7" s="380"/>
+      <c r="AO7" s="380"/>
+      <c r="AP7" s="380"/>
+      <c r="AQ7" s="380"/>
+      <c r="AR7" s="380"/>
+      <c r="AS7" s="380"/>
+      <c r="AT7" s="380"/>
+      <c r="AU7" s="380"/>
+      <c r="AV7" s="380"/>
+      <c r="AW7" s="380"/>
+      <c r="AX7" s="380"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12068,124 +12043,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="405" t="s">
+      <c r="BB7" s="394" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="397" t="s">
+      <c r="BC7" s="386" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="397" t="s">
+      <c r="BD7" s="386" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="418" t="s">
+      <c r="BE7" s="407" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="397" t="s">
+      <c r="BF7" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="397" t="s">
+      <c r="BG7" s="386" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="397" t="s">
+      <c r="BH7" s="386" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="397" t="s">
+      <c r="BI7" s="386" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="397" t="s">
+      <c r="BJ7" s="386" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="397" t="s">
+      <c r="BK7" s="386" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="398" t="s">
+      <c r="BL7" s="387" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="397" t="s">
+      <c r="BM7" s="386" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="405" t="s">
+      <c r="BN7" s="394" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="397" t="s">
+      <c r="BO7" s="386" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="405" t="s">
+      <c r="BP7" s="394" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="405" t="s">
+      <c r="BQ7" s="394" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="391"/>
-      <c r="BS7" s="391"/>
-      <c r="BT7" s="391"/>
-      <c r="BU7" s="400"/>
-      <c r="BW7" s="403"/>
-      <c r="BX7" s="416"/>
-      <c r="BY7" s="417"/>
-      <c r="BZ7" s="417"/>
-      <c r="CA7" s="404"/>
-      <c r="CB7" s="391"/>
-      <c r="CC7" s="391"/>
-      <c r="CD7" s="391"/>
+      <c r="BR7" s="380"/>
+      <c r="BS7" s="380"/>
+      <c r="BT7" s="380"/>
+      <c r="BU7" s="389"/>
+      <c r="BW7" s="392"/>
+      <c r="BX7" s="405"/>
+      <c r="BY7" s="406"/>
+      <c r="BZ7" s="406"/>
+      <c r="CA7" s="393"/>
+      <c r="CB7" s="380"/>
+      <c r="CC7" s="380"/>
+      <c r="CD7" s="380"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="394"/>
-      <c r="B8" s="394"/>
-      <c r="C8" s="394"/>
-      <c r="D8" s="394"/>
-      <c r="E8" s="394"/>
-      <c r="F8" s="394"/>
-      <c r="G8" s="394"/>
-      <c r="H8" s="394"/>
-      <c r="I8" s="394"/>
-      <c r="J8" s="394"/>
-      <c r="K8" s="394"/>
-      <c r="L8" s="394"/>
-      <c r="M8" s="394"/>
-      <c r="N8" s="394"/>
-      <c r="O8" s="394"/>
-      <c r="P8" s="394"/>
-      <c r="Q8" s="394"/>
-      <c r="R8" s="394"/>
-      <c r="S8" s="394"/>
-      <c r="T8" s="394"/>
-      <c r="U8" s="394"/>
+      <c r="A8" s="383"/>
+      <c r="B8" s="383"/>
+      <c r="C8" s="383"/>
+      <c r="D8" s="383"/>
+      <c r="E8" s="383"/>
+      <c r="F8" s="383"/>
+      <c r="G8" s="383"/>
+      <c r="H8" s="383"/>
+      <c r="I8" s="383"/>
+      <c r="J8" s="383"/>
+      <c r="K8" s="383"/>
+      <c r="L8" s="383"/>
+      <c r="M8" s="383"/>
+      <c r="N8" s="383"/>
+      <c r="O8" s="383"/>
+      <c r="P8" s="383"/>
+      <c r="Q8" s="383"/>
+      <c r="R8" s="383"/>
+      <c r="S8" s="383"/>
+      <c r="T8" s="383"/>
+      <c r="U8" s="383"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="394"/>
-      <c r="Y8" s="394"/>
-      <c r="Z8" s="394"/>
-      <c r="AA8" s="394"/>
-      <c r="AB8" s="394"/>
-      <c r="AC8" s="394"/>
-      <c r="AD8" s="394"/>
-      <c r="AE8" s="394"/>
-      <c r="AF8" s="394"/>
-      <c r="AG8" s="394"/>
-      <c r="AH8" s="394"/>
-      <c r="AI8" s="394"/>
-      <c r="AJ8" s="394"/>
-      <c r="AK8" s="401"/>
-      <c r="AL8" s="394"/>
-      <c r="AM8" s="394"/>
-      <c r="AN8" s="394"/>
-      <c r="AO8" s="394"/>
-      <c r="AP8" s="394"/>
-      <c r="AQ8" s="394"/>
-      <c r="AR8" s="394"/>
-      <c r="AS8" s="394"/>
-      <c r="AT8" s="394"/>
-      <c r="AU8" s="394"/>
-      <c r="AV8" s="394"/>
-      <c r="AW8" s="394"/>
-      <c r="AX8" s="394"/>
+      <c r="X8" s="383"/>
+      <c r="Y8" s="383"/>
+      <c r="Z8" s="383"/>
+      <c r="AA8" s="383"/>
+      <c r="AB8" s="383"/>
+      <c r="AC8" s="383"/>
+      <c r="AD8" s="383"/>
+      <c r="AE8" s="383"/>
+      <c r="AF8" s="383"/>
+      <c r="AG8" s="383"/>
+      <c r="AH8" s="383"/>
+      <c r="AI8" s="383"/>
+      <c r="AJ8" s="383"/>
+      <c r="AK8" s="390"/>
+      <c r="AL8" s="383"/>
+      <c r="AM8" s="383"/>
+      <c r="AN8" s="383"/>
+      <c r="AO8" s="383"/>
+      <c r="AP8" s="383"/>
+      <c r="AQ8" s="383"/>
+      <c r="AR8" s="383"/>
+      <c r="AS8" s="383"/>
+      <c r="AT8" s="383"/>
+      <c r="AU8" s="383"/>
+      <c r="AV8" s="383"/>
+      <c r="AW8" s="383"/>
+      <c r="AX8" s="383"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12195,27 +12170,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="394"/>
-      <c r="BC8" s="394"/>
-      <c r="BD8" s="394"/>
-      <c r="BE8" s="394"/>
-      <c r="BF8" s="394"/>
-      <c r="BG8" s="394"/>
-      <c r="BH8" s="394"/>
-      <c r="BI8" s="394"/>
-      <c r="BJ8" s="394"/>
-      <c r="BK8" s="394"/>
-      <c r="BL8" s="394"/>
-      <c r="BM8" s="394"/>
-      <c r="BN8" s="394"/>
-      <c r="BO8" s="394"/>
-      <c r="BP8" s="394"/>
-      <c r="BQ8" s="394"/>
-      <c r="BR8" s="394"/>
-      <c r="BS8" s="394"/>
-      <c r="BT8" s="394"/>
-      <c r="BU8" s="401"/>
-      <c r="BW8" s="404"/>
+      <c r="BB8" s="383"/>
+      <c r="BC8" s="383"/>
+      <c r="BD8" s="383"/>
+      <c r="BE8" s="383"/>
+      <c r="BF8" s="383"/>
+      <c r="BG8" s="383"/>
+      <c r="BH8" s="383"/>
+      <c r="BI8" s="383"/>
+      <c r="BJ8" s="383"/>
+      <c r="BK8" s="383"/>
+      <c r="BL8" s="383"/>
+      <c r="BM8" s="383"/>
+      <c r="BN8" s="383"/>
+      <c r="BO8" s="383"/>
+      <c r="BP8" s="383"/>
+      <c r="BQ8" s="383"/>
+      <c r="BR8" s="383"/>
+      <c r="BS8" s="383"/>
+      <c r="BT8" s="383"/>
+      <c r="BU8" s="390"/>
+      <c r="BW8" s="393"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12228,9 +12203,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="392"/>
-      <c r="CC8" s="392"/>
-      <c r="CD8" s="392"/>
+      <c r="CB8" s="381"/>
+      <c r="CC8" s="381"/>
+      <c r="CD8" s="381"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14997,88 +14972,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="438"/>
-      <c r="B3" s="437"/>
-      <c r="C3" s="437"/>
-      <c r="D3" s="437"/>
-      <c r="E3" s="437"/>
-      <c r="F3" s="437"/>
-      <c r="G3" s="437"/>
-      <c r="H3" s="437"/>
-      <c r="I3" s="437"/>
-      <c r="J3" s="437"/>
-      <c r="K3" s="437"/>
-      <c r="L3" s="437"/>
-      <c r="M3" s="437"/>
-      <c r="N3" s="437"/>
-      <c r="O3" s="437"/>
-      <c r="P3" s="437"/>
-      <c r="Q3" s="437"/>
-      <c r="R3" s="437"/>
-      <c r="S3" s="437"/>
-      <c r="T3" s="437"/>
-      <c r="U3" s="437"/>
-      <c r="V3" s="437"/>
-      <c r="W3" s="437"/>
-      <c r="X3" s="437"/>
-      <c r="Y3" s="437"/>
-      <c r="Z3" s="437"/>
-      <c r="AA3" s="437"/>
-      <c r="AB3" s="437"/>
-      <c r="AC3" s="437"/>
-      <c r="AD3" s="437"/>
-      <c r="AE3" s="437"/>
-      <c r="AF3" s="437"/>
-      <c r="AG3" s="437"/>
-      <c r="AH3" s="437"/>
-      <c r="AI3" s="437"/>
-      <c r="AJ3" s="437"/>
-      <c r="AK3" s="437"/>
-      <c r="AL3" s="437"/>
-      <c r="AM3" s="437"/>
-      <c r="AN3" s="437"/>
-      <c r="AO3" s="437"/>
-      <c r="AP3" s="437"/>
-      <c r="AQ3" s="437"/>
-      <c r="AR3" s="437"/>
-      <c r="AS3" s="437"/>
-      <c r="AT3" s="437"/>
-      <c r="AU3" s="437"/>
-      <c r="AV3" s="437"/>
-      <c r="AW3" s="437"/>
-      <c r="AX3" s="437"/>
-      <c r="AY3" s="437"/>
-      <c r="AZ3" s="437"/>
-      <c r="BA3" s="437"/>
-      <c r="BB3" s="437"/>
-      <c r="BC3" s="437"/>
-      <c r="BD3" s="437"/>
-      <c r="BE3" s="437"/>
-      <c r="BF3" s="437"/>
-      <c r="BG3" s="437"/>
-      <c r="BH3" s="437"/>
-      <c r="BI3" s="437"/>
-      <c r="BJ3" s="437"/>
-      <c r="BK3" s="437"/>
-      <c r="BL3" s="437"/>
-      <c r="BM3" s="437"/>
-      <c r="BN3" s="437"/>
-      <c r="BO3" s="437"/>
-      <c r="BP3" s="437"/>
-      <c r="BQ3" s="437"/>
-      <c r="BR3" s="437"/>
-      <c r="BS3" s="437"/>
-      <c r="BT3" s="437"/>
-      <c r="BU3" s="437"/>
+      <c r="A3" s="427"/>
+      <c r="B3" s="426"/>
+      <c r="C3" s="426"/>
+      <c r="D3" s="426"/>
+      <c r="E3" s="426"/>
+      <c r="F3" s="426"/>
+      <c r="G3" s="426"/>
+      <c r="H3" s="426"/>
+      <c r="I3" s="426"/>
+      <c r="J3" s="426"/>
+      <c r="K3" s="426"/>
+      <c r="L3" s="426"/>
+      <c r="M3" s="426"/>
+      <c r="N3" s="426"/>
+      <c r="O3" s="426"/>
+      <c r="P3" s="426"/>
+      <c r="Q3" s="426"/>
+      <c r="R3" s="426"/>
+      <c r="S3" s="426"/>
+      <c r="T3" s="426"/>
+      <c r="U3" s="426"/>
+      <c r="V3" s="426"/>
+      <c r="W3" s="426"/>
+      <c r="X3" s="426"/>
+      <c r="Y3" s="426"/>
+      <c r="Z3" s="426"/>
+      <c r="AA3" s="426"/>
+      <c r="AB3" s="426"/>
+      <c r="AC3" s="426"/>
+      <c r="AD3" s="426"/>
+      <c r="AE3" s="426"/>
+      <c r="AF3" s="426"/>
+      <c r="AG3" s="426"/>
+      <c r="AH3" s="426"/>
+      <c r="AI3" s="426"/>
+      <c r="AJ3" s="426"/>
+      <c r="AK3" s="426"/>
+      <c r="AL3" s="426"/>
+      <c r="AM3" s="426"/>
+      <c r="AN3" s="426"/>
+      <c r="AO3" s="426"/>
+      <c r="AP3" s="426"/>
+      <c r="AQ3" s="426"/>
+      <c r="AR3" s="426"/>
+      <c r="AS3" s="426"/>
+      <c r="AT3" s="426"/>
+      <c r="AU3" s="426"/>
+      <c r="AV3" s="426"/>
+      <c r="AW3" s="426"/>
+      <c r="AX3" s="426"/>
+      <c r="AY3" s="426"/>
+      <c r="AZ3" s="426"/>
+      <c r="BA3" s="426"/>
+      <c r="BB3" s="426"/>
+      <c r="BC3" s="426"/>
+      <c r="BD3" s="426"/>
+      <c r="BE3" s="426"/>
+      <c r="BF3" s="426"/>
+      <c r="BG3" s="426"/>
+      <c r="BH3" s="426"/>
+      <c r="BI3" s="426"/>
+      <c r="BJ3" s="426"/>
+      <c r="BK3" s="426"/>
+      <c r="BL3" s="426"/>
+      <c r="BM3" s="426"/>
+      <c r="BN3" s="426"/>
+      <c r="BO3" s="426"/>
+      <c r="BP3" s="426"/>
+      <c r="BQ3" s="426"/>
+      <c r="BR3" s="426"/>
+      <c r="BS3" s="426"/>
+      <c r="BT3" s="426"/>
+      <c r="BU3" s="426"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="436" t="s">
+      <c r="BW3" s="425" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="437"/>
-      <c r="BY3" s="437"/>
-      <c r="BZ3" s="437"/>
-      <c r="CA3" s="437"/>
-      <c r="CB3" s="437"/>
+      <c r="BX3" s="426"/>
+      <c r="BY3" s="426"/>
+      <c r="BZ3" s="426"/>
+      <c r="CA3" s="426"/>
+      <c r="CB3" s="426"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15162,12 +15137,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="437"/>
-      <c r="BX4" s="437"/>
-      <c r="BY4" s="437"/>
-      <c r="BZ4" s="437"/>
-      <c r="CA4" s="437"/>
-      <c r="CB4" s="437"/>
+      <c r="BW4" s="426"/>
+      <c r="BX4" s="426"/>
+      <c r="BY4" s="426"/>
+      <c r="BZ4" s="426"/>
+      <c r="CA4" s="426"/>
+      <c r="CB4" s="426"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15245,12 +15220,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="373"/>
-      <c r="BX5" s="373"/>
-      <c r="BY5" s="373"/>
-      <c r="BZ5" s="373"/>
-      <c r="CA5" s="373"/>
-      <c r="CB5" s="373"/>
+      <c r="BW5" s="363"/>
+      <c r="BX5" s="363"/>
+      <c r="BY5" s="363"/>
+      <c r="BZ5" s="363"/>
+      <c r="CA5" s="363"/>
+      <c r="CB5" s="363"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15328,12 +15303,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="373"/>
-      <c r="BX6" s="373"/>
-      <c r="BY6" s="373"/>
-      <c r="BZ6" s="373"/>
-      <c r="CA6" s="373"/>
-      <c r="CB6" s="373"/>
+      <c r="BW6" s="363"/>
+      <c r="BX6" s="363"/>
+      <c r="BY6" s="363"/>
+      <c r="BZ6" s="363"/>
+      <c r="CA6" s="363"/>
+      <c r="CB6" s="363"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15421,358 +15396,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="422" t="s">
+      <c r="A8" s="411" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="421" t="s">
+      <c r="B8" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="395" t="s">
+      <c r="C8" s="384" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="420" t="s">
+      <c r="D8" s="409" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="420" t="s">
+      <c r="E8" s="409" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="440" t="s">
+      <c r="F8" s="429" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="429" t="s">
+      <c r="G8" s="418" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="434" t="s">
+      <c r="H8" s="423" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="434" t="s">
+      <c r="I8" s="423" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="429" t="s">
+      <c r="J8" s="418" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="441" t="s">
+      <c r="K8" s="430" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="406"/>
-      <c r="M8" s="406"/>
-      <c r="N8" s="406"/>
-      <c r="O8" s="406"/>
-      <c r="P8" s="406"/>
-      <c r="Q8" s="406"/>
-      <c r="R8" s="406"/>
-      <c r="S8" s="406"/>
-      <c r="T8" s="406"/>
-      <c r="U8" s="406"/>
-      <c r="V8" s="406"/>
-      <c r="W8" s="406"/>
-      <c r="X8" s="406"/>
-      <c r="Y8" s="429" t="s">
+      <c r="L8" s="395"/>
+      <c r="M8" s="395"/>
+      <c r="N8" s="395"/>
+      <c r="O8" s="395"/>
+      <c r="P8" s="395"/>
+      <c r="Q8" s="395"/>
+      <c r="R8" s="395"/>
+      <c r="S8" s="395"/>
+      <c r="T8" s="395"/>
+      <c r="U8" s="395"/>
+      <c r="V8" s="395"/>
+      <c r="W8" s="395"/>
+      <c r="X8" s="395"/>
+      <c r="Y8" s="418" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="406"/>
-      <c r="AA8" s="406"/>
-      <c r="AB8" s="406"/>
-      <c r="AC8" s="406"/>
-      <c r="AD8" s="406"/>
-      <c r="AE8" s="406"/>
-      <c r="AF8" s="406"/>
-      <c r="AG8" s="406"/>
-      <c r="AH8" s="406"/>
-      <c r="AI8" s="406"/>
-      <c r="AJ8" s="406"/>
-      <c r="AK8" s="406"/>
-      <c r="AL8" s="406"/>
-      <c r="AM8" s="406"/>
-      <c r="AN8" s="406"/>
-      <c r="AO8" s="407"/>
-      <c r="AP8" s="429" t="s">
+      <c r="Z8" s="395"/>
+      <c r="AA8" s="395"/>
+      <c r="AB8" s="395"/>
+      <c r="AC8" s="395"/>
+      <c r="AD8" s="395"/>
+      <c r="AE8" s="395"/>
+      <c r="AF8" s="395"/>
+      <c r="AG8" s="395"/>
+      <c r="AH8" s="395"/>
+      <c r="AI8" s="395"/>
+      <c r="AJ8" s="395"/>
+      <c r="AK8" s="395"/>
+      <c r="AL8" s="395"/>
+      <c r="AM8" s="395"/>
+      <c r="AN8" s="395"/>
+      <c r="AO8" s="396"/>
+      <c r="AP8" s="418" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="429" t="s">
+      <c r="AQ8" s="418" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="429" t="s">
+      <c r="AR8" s="418" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="429" t="s">
+      <c r="AS8" s="418" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="429" t="s">
+      <c r="AT8" s="418" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="429" t="s">
+      <c r="AU8" s="418" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="395" t="s">
+      <c r="AV8" s="384" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="395" t="s">
+      <c r="AW8" s="384" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="395" t="s">
+      <c r="AX8" s="384" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="405" t="s">
+      <c r="AY8" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="406"/>
-      <c r="BA8" s="406"/>
-      <c r="BB8" s="406"/>
-      <c r="BC8" s="406"/>
-      <c r="BD8" s="406"/>
-      <c r="BE8" s="406"/>
-      <c r="BF8" s="406"/>
-      <c r="BG8" s="406"/>
-      <c r="BH8" s="406"/>
-      <c r="BI8" s="406"/>
-      <c r="BJ8" s="406"/>
-      <c r="BK8" s="406"/>
-      <c r="BL8" s="406"/>
-      <c r="BM8" s="406"/>
-      <c r="BN8" s="406"/>
-      <c r="BO8" s="406"/>
-      <c r="BP8" s="407"/>
-      <c r="BQ8" s="411" t="s">
+      <c r="AZ8" s="395"/>
+      <c r="BA8" s="395"/>
+      <c r="BB8" s="395"/>
+      <c r="BC8" s="395"/>
+      <c r="BD8" s="395"/>
+      <c r="BE8" s="395"/>
+      <c r="BF8" s="395"/>
+      <c r="BG8" s="395"/>
+      <c r="BH8" s="395"/>
+      <c r="BI8" s="395"/>
+      <c r="BJ8" s="395"/>
+      <c r="BK8" s="395"/>
+      <c r="BL8" s="395"/>
+      <c r="BM8" s="395"/>
+      <c r="BN8" s="395"/>
+      <c r="BO8" s="395"/>
+      <c r="BP8" s="396"/>
+      <c r="BQ8" s="400" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="412"/>
-      <c r="BS8" s="405" t="s">
+      <c r="BR8" s="401"/>
+      <c r="BS8" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="405" t="s">
+      <c r="BT8" s="394" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="399" t="s">
+      <c r="BU8" s="388" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="402" t="s">
+      <c r="BW8" s="391" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="413" t="s">
+      <c r="BX8" s="402" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="414"/>
-      <c r="BZ8" s="414"/>
-      <c r="CA8" s="412"/>
-      <c r="CB8" s="408" t="s">
+      <c r="BY8" s="403"/>
+      <c r="BZ8" s="403"/>
+      <c r="CA8" s="401"/>
+      <c r="CB8" s="397" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="390" t="s">
+      <c r="CC8" s="379" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="390" t="s">
+      <c r="CD8" s="379" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="391"/>
-      <c r="B9" s="391"/>
-      <c r="C9" s="391"/>
-      <c r="D9" s="391"/>
-      <c r="E9" s="391"/>
-      <c r="F9" s="391"/>
-      <c r="G9" s="391"/>
-      <c r="H9" s="391"/>
-      <c r="I9" s="391"/>
-      <c r="J9" s="391"/>
-      <c r="K9" s="431" t="s">
+      <c r="A9" s="380"/>
+      <c r="B9" s="380"/>
+      <c r="C9" s="380"/>
+      <c r="D9" s="380"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
+      <c r="G9" s="380"/>
+      <c r="H9" s="380"/>
+      <c r="I9" s="380"/>
+      <c r="J9" s="380"/>
+      <c r="K9" s="420" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="431" t="s">
+      <c r="L9" s="420" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="431" t="s">
+      <c r="M9" s="420" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="431" t="s">
+      <c r="N9" s="420" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="431" t="s">
+      <c r="O9" s="420" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="431" t="s">
+      <c r="P9" s="420" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="431" t="s">
+      <c r="Q9" s="420" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="431" t="s">
+      <c r="R9" s="420" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="431" t="s">
+      <c r="S9" s="420" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="431" t="s">
+      <c r="T9" s="420" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="431" t="s">
+      <c r="U9" s="420" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="435" t="s">
+      <c r="V9" s="424" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="412"/>
-      <c r="X9" s="431" t="s">
+      <c r="W9" s="401"/>
+      <c r="X9" s="420" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="428" t="s">
+      <c r="Y9" s="417" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="428" t="s">
+      <c r="Z9" s="417" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="428" t="s">
+      <c r="AA9" s="417" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="428" t="s">
+      <c r="AB9" s="417" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="332" t="s">
+      <c r="AC9" s="329" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="332" t="s">
+      <c r="AD9" s="329" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="332" t="s">
+      <c r="AE9" s="329" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="332" t="s">
+      <c r="AF9" s="329" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="428" t="s">
+      <c r="AG9" s="417" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="332" t="s">
+      <c r="AH9" s="329" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="332" t="s">
+      <c r="AI9" s="329" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="428" t="s">
+      <c r="AJ9" s="417" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="423" t="s">
+      <c r="AK9" s="412" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="395" t="s">
+      <c r="AL9" s="384" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="428" t="s">
+      <c r="AM9" s="417" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="425" t="s">
+      <c r="AN9" s="414" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="395" t="s">
+      <c r="AO9" s="384" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="391"/>
-      <c r="AQ9" s="391"/>
-      <c r="AR9" s="391"/>
-      <c r="AS9" s="391"/>
-      <c r="AT9" s="391"/>
-      <c r="AU9" s="391"/>
-      <c r="AV9" s="391"/>
-      <c r="AW9" s="391"/>
-      <c r="AX9" s="391"/>
-      <c r="AY9" s="405" t="s">
+      <c r="AP9" s="380"/>
+      <c r="AQ9" s="380"/>
+      <c r="AR9" s="380"/>
+      <c r="AS9" s="380"/>
+      <c r="AT9" s="380"/>
+      <c r="AU9" s="380"/>
+      <c r="AV9" s="380"/>
+      <c r="AW9" s="380"/>
+      <c r="AX9" s="380"/>
+      <c r="AY9" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="406"/>
-      <c r="BA9" s="406"/>
-      <c r="BB9" s="406"/>
-      <c r="BC9" s="406"/>
-      <c r="BD9" s="406"/>
-      <c r="BE9" s="406"/>
-      <c r="BF9" s="406"/>
-      <c r="BG9" s="406"/>
-      <c r="BH9" s="406"/>
-      <c r="BI9" s="406"/>
-      <c r="BJ9" s="407"/>
-      <c r="BK9" s="405" t="s">
+      <c r="AZ9" s="395"/>
+      <c r="BA9" s="395"/>
+      <c r="BB9" s="395"/>
+      <c r="BC9" s="395"/>
+      <c r="BD9" s="395"/>
+      <c r="BE9" s="395"/>
+      <c r="BF9" s="395"/>
+      <c r="BG9" s="395"/>
+      <c r="BH9" s="395"/>
+      <c r="BI9" s="395"/>
+      <c r="BJ9" s="396"/>
+      <c r="BK9" s="394" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="406"/>
-      <c r="BM9" s="406"/>
-      <c r="BN9" s="406"/>
-      <c r="BO9" s="406"/>
-      <c r="BP9" s="407"/>
-      <c r="BQ9" s="393" t="s">
+      <c r="BL9" s="395"/>
+      <c r="BM9" s="395"/>
+      <c r="BN9" s="395"/>
+      <c r="BO9" s="395"/>
+      <c r="BP9" s="396"/>
+      <c r="BQ9" s="382" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="393" t="s">
+      <c r="BR9" s="382" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="391"/>
-      <c r="BT9" s="391"/>
-      <c r="BU9" s="400"/>
+      <c r="BS9" s="380"/>
+      <c r="BT9" s="380"/>
+      <c r="BU9" s="389"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="403"/>
-      <c r="BX9" s="400"/>
-      <c r="BY9" s="442"/>
-      <c r="BZ9" s="442"/>
-      <c r="CA9" s="403"/>
-      <c r="CB9" s="391"/>
-      <c r="CC9" s="391"/>
-      <c r="CD9" s="391"/>
+      <c r="BW9" s="392"/>
+      <c r="BX9" s="389"/>
+      <c r="BY9" s="431"/>
+      <c r="BZ9" s="431"/>
+      <c r="CA9" s="392"/>
+      <c r="CB9" s="380"/>
+      <c r="CC9" s="380"/>
+      <c r="CD9" s="380"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="391"/>
-      <c r="B10" s="391"/>
-      <c r="C10" s="391"/>
-      <c r="D10" s="391"/>
-      <c r="E10" s="391"/>
-      <c r="F10" s="391"/>
-      <c r="G10" s="391"/>
-      <c r="H10" s="391"/>
-      <c r="I10" s="391"/>
-      <c r="J10" s="391"/>
-      <c r="K10" s="391"/>
-      <c r="L10" s="391"/>
-      <c r="M10" s="391"/>
-      <c r="N10" s="391"/>
-      <c r="O10" s="391"/>
-      <c r="P10" s="391"/>
-      <c r="Q10" s="391"/>
-      <c r="R10" s="391"/>
-      <c r="S10" s="391"/>
-      <c r="T10" s="391"/>
-      <c r="U10" s="391"/>
-      <c r="V10" s="401"/>
-      <c r="W10" s="427"/>
-      <c r="X10" s="391"/>
-      <c r="Y10" s="391"/>
-      <c r="Z10" s="391"/>
-      <c r="AA10" s="391"/>
-      <c r="AB10" s="391"/>
-      <c r="AC10" s="391"/>
-      <c r="AD10" s="391"/>
-      <c r="AE10" s="391"/>
-      <c r="AF10" s="391"/>
-      <c r="AG10" s="391"/>
-      <c r="AH10" s="391"/>
-      <c r="AI10" s="391"/>
-      <c r="AJ10" s="391"/>
-      <c r="AK10" s="400"/>
-      <c r="AL10" s="391"/>
-      <c r="AM10" s="391"/>
-      <c r="AN10" s="391"/>
-      <c r="AO10" s="391"/>
-      <c r="AP10" s="391"/>
-      <c r="AQ10" s="391"/>
-      <c r="AR10" s="391"/>
-      <c r="AS10" s="391"/>
-      <c r="AT10" s="391"/>
-      <c r="AU10" s="391"/>
-      <c r="AV10" s="391"/>
-      <c r="AW10" s="391"/>
-      <c r="AX10" s="391"/>
+      <c r="A10" s="380"/>
+      <c r="B10" s="380"/>
+      <c r="C10" s="380"/>
+      <c r="D10" s="380"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
+      <c r="G10" s="380"/>
+      <c r="H10" s="380"/>
+      <c r="I10" s="380"/>
+      <c r="J10" s="380"/>
+      <c r="K10" s="380"/>
+      <c r="L10" s="380"/>
+      <c r="M10" s="380"/>
+      <c r="N10" s="380"/>
+      <c r="O10" s="380"/>
+      <c r="P10" s="380"/>
+      <c r="Q10" s="380"/>
+      <c r="R10" s="380"/>
+      <c r="S10" s="380"/>
+      <c r="T10" s="380"/>
+      <c r="U10" s="380"/>
+      <c r="V10" s="390"/>
+      <c r="W10" s="416"/>
+      <c r="X10" s="380"/>
+      <c r="Y10" s="380"/>
+      <c r="Z10" s="380"/>
+      <c r="AA10" s="380"/>
+      <c r="AB10" s="380"/>
+      <c r="AC10" s="380"/>
+      <c r="AD10" s="380"/>
+      <c r="AE10" s="380"/>
+      <c r="AF10" s="380"/>
+      <c r="AG10" s="380"/>
+      <c r="AH10" s="380"/>
+      <c r="AI10" s="380"/>
+      <c r="AJ10" s="380"/>
+      <c r="AK10" s="389"/>
+      <c r="AL10" s="380"/>
+      <c r="AM10" s="380"/>
+      <c r="AN10" s="380"/>
+      <c r="AO10" s="380"/>
+      <c r="AP10" s="380"/>
+      <c r="AQ10" s="380"/>
+      <c r="AR10" s="380"/>
+      <c r="AS10" s="380"/>
+      <c r="AT10" s="380"/>
+      <c r="AU10" s="380"/>
+      <c r="AV10" s="380"/>
+      <c r="AW10" s="380"/>
+      <c r="AX10" s="380"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15782,123 +15757,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="439" t="s">
+      <c r="BB10" s="428" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="432" t="s">
+      <c r="BC10" s="421" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="432" t="s">
+      <c r="BD10" s="421" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="432" t="s">
+      <c r="BE10" s="421" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="432" t="s">
+      <c r="BF10" s="421" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="432" t="s">
+      <c r="BG10" s="421" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="432" t="s">
+      <c r="BH10" s="421" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="432" t="s">
+      <c r="BI10" s="421" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="430" t="s">
+      <c r="BJ10" s="419" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="432" t="s">
+      <c r="BK10" s="421" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="433" t="s">
+      <c r="BL10" s="422" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="432" t="s">
+      <c r="BM10" s="421" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="433" t="s">
+      <c r="BN10" s="422" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="433" t="s">
+      <c r="BO10" s="422" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="405" t="s">
+      <c r="BP10" s="394" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="391"/>
-      <c r="BR10" s="391"/>
-      <c r="BS10" s="391"/>
-      <c r="BT10" s="391"/>
-      <c r="BU10" s="400"/>
+      <c r="BQ10" s="380"/>
+      <c r="BR10" s="380"/>
+      <c r="BS10" s="380"/>
+      <c r="BT10" s="380"/>
+      <c r="BU10" s="389"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="403"/>
-      <c r="BX10" s="416"/>
-      <c r="BY10" s="417"/>
-      <c r="BZ10" s="417"/>
-      <c r="CA10" s="404"/>
-      <c r="CB10" s="391"/>
-      <c r="CC10" s="391"/>
-      <c r="CD10" s="391"/>
+      <c r="BW10" s="392"/>
+      <c r="BX10" s="405"/>
+      <c r="BY10" s="406"/>
+      <c r="BZ10" s="406"/>
+      <c r="CA10" s="393"/>
+      <c r="CB10" s="380"/>
+      <c r="CC10" s="380"/>
+      <c r="CD10" s="380"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="394"/>
-      <c r="B11" s="394"/>
-      <c r="C11" s="394"/>
-      <c r="D11" s="394"/>
-      <c r="E11" s="394"/>
-      <c r="F11" s="394"/>
-      <c r="G11" s="394"/>
-      <c r="H11" s="394"/>
-      <c r="I11" s="394"/>
-      <c r="J11" s="394"/>
-      <c r="K11" s="394"/>
-      <c r="L11" s="394"/>
-      <c r="M11" s="394"/>
-      <c r="N11" s="394"/>
-      <c r="O11" s="394"/>
-      <c r="P11" s="394"/>
-      <c r="Q11" s="394"/>
-      <c r="R11" s="394"/>
-      <c r="S11" s="394"/>
-      <c r="T11" s="394"/>
-      <c r="U11" s="394"/>
+      <c r="A11" s="383"/>
+      <c r="B11" s="383"/>
+      <c r="C11" s="383"/>
+      <c r="D11" s="383"/>
+      <c r="E11" s="383"/>
+      <c r="F11" s="383"/>
+      <c r="G11" s="383"/>
+      <c r="H11" s="383"/>
+      <c r="I11" s="383"/>
+      <c r="J11" s="383"/>
+      <c r="K11" s="383"/>
+      <c r="L11" s="383"/>
+      <c r="M11" s="383"/>
+      <c r="N11" s="383"/>
+      <c r="O11" s="383"/>
+      <c r="P11" s="383"/>
+      <c r="Q11" s="383"/>
+      <c r="R11" s="383"/>
+      <c r="S11" s="383"/>
+      <c r="T11" s="383"/>
+      <c r="U11" s="383"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="394"/>
-      <c r="Y11" s="394"/>
-      <c r="Z11" s="394"/>
-      <c r="AA11" s="394"/>
-      <c r="AB11" s="394"/>
-      <c r="AC11" s="394"/>
-      <c r="AD11" s="394"/>
-      <c r="AE11" s="394"/>
-      <c r="AF11" s="394"/>
-      <c r="AG11" s="394"/>
-      <c r="AH11" s="394"/>
-      <c r="AI11" s="394"/>
-      <c r="AJ11" s="394"/>
-      <c r="AK11" s="401"/>
-      <c r="AL11" s="394"/>
-      <c r="AM11" s="394"/>
-      <c r="AN11" s="394"/>
-      <c r="AO11" s="394"/>
-      <c r="AP11" s="394"/>
-      <c r="AQ11" s="394"/>
-      <c r="AR11" s="394"/>
-      <c r="AS11" s="394"/>
-      <c r="AT11" s="394"/>
-      <c r="AU11" s="394"/>
-      <c r="AV11" s="394"/>
-      <c r="AW11" s="394"/>
-      <c r="AX11" s="394"/>
+      <c r="X11" s="383"/>
+      <c r="Y11" s="383"/>
+      <c r="Z11" s="383"/>
+      <c r="AA11" s="383"/>
+      <c r="AB11" s="383"/>
+      <c r="AC11" s="383"/>
+      <c r="AD11" s="383"/>
+      <c r="AE11" s="383"/>
+      <c r="AF11" s="383"/>
+      <c r="AG11" s="383"/>
+      <c r="AH11" s="383"/>
+      <c r="AI11" s="383"/>
+      <c r="AJ11" s="383"/>
+      <c r="AK11" s="390"/>
+      <c r="AL11" s="383"/>
+      <c r="AM11" s="383"/>
+      <c r="AN11" s="383"/>
+      <c r="AO11" s="383"/>
+      <c r="AP11" s="383"/>
+      <c r="AQ11" s="383"/>
+      <c r="AR11" s="383"/>
+      <c r="AS11" s="383"/>
+      <c r="AT11" s="383"/>
+      <c r="AU11" s="383"/>
+      <c r="AV11" s="383"/>
+      <c r="AW11" s="383"/>
+      <c r="AX11" s="383"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15908,28 +15883,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="394"/>
-      <c r="BC11" s="394"/>
-      <c r="BD11" s="394"/>
-      <c r="BE11" s="394"/>
-      <c r="BF11" s="394"/>
-      <c r="BG11" s="394"/>
-      <c r="BH11" s="394"/>
-      <c r="BI11" s="394"/>
-      <c r="BJ11" s="394"/>
-      <c r="BK11" s="394"/>
-      <c r="BL11" s="394"/>
-      <c r="BM11" s="394"/>
-      <c r="BN11" s="394"/>
-      <c r="BO11" s="394"/>
-      <c r="BP11" s="394"/>
-      <c r="BQ11" s="394"/>
-      <c r="BR11" s="394"/>
-      <c r="BS11" s="394"/>
-      <c r="BT11" s="394"/>
-      <c r="BU11" s="401"/>
+      <c r="BB11" s="383"/>
+      <c r="BC11" s="383"/>
+      <c r="BD11" s="383"/>
+      <c r="BE11" s="383"/>
+      <c r="BF11" s="383"/>
+      <c r="BG11" s="383"/>
+      <c r="BH11" s="383"/>
+      <c r="BI11" s="383"/>
+      <c r="BJ11" s="383"/>
+      <c r="BK11" s="383"/>
+      <c r="BL11" s="383"/>
+      <c r="BM11" s="383"/>
+      <c r="BN11" s="383"/>
+      <c r="BO11" s="383"/>
+      <c r="BP11" s="383"/>
+      <c r="BQ11" s="383"/>
+      <c r="BR11" s="383"/>
+      <c r="BS11" s="383"/>
+      <c r="BT11" s="383"/>
+      <c r="BU11" s="390"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="404"/>
+      <c r="BW11" s="393"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15942,9 +15917,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="392"/>
-      <c r="CC11" s="392"/>
-      <c r="CD11" s="392"/>
+      <c r="CB11" s="381"/>
+      <c r="CC11" s="381"/>
+      <c r="CD11" s="381"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18656,87 +18631,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="419"/>
-      <c r="B3" s="410"/>
-      <c r="C3" s="410"/>
-      <c r="D3" s="410"/>
-      <c r="E3" s="410"/>
-      <c r="F3" s="410"/>
-      <c r="G3" s="410"/>
-      <c r="H3" s="410"/>
-      <c r="I3" s="410"/>
-      <c r="J3" s="410"/>
-      <c r="K3" s="410"/>
-      <c r="L3" s="410"/>
-      <c r="M3" s="410"/>
-      <c r="N3" s="410"/>
-      <c r="O3" s="410"/>
-      <c r="P3" s="410"/>
-      <c r="Q3" s="410"/>
-      <c r="R3" s="410"/>
-      <c r="S3" s="410"/>
-      <c r="T3" s="410"/>
-      <c r="U3" s="410"/>
-      <c r="V3" s="410"/>
-      <c r="W3" s="410"/>
-      <c r="X3" s="410"/>
-      <c r="Y3" s="410"/>
-      <c r="Z3" s="410"/>
-      <c r="AA3" s="410"/>
-      <c r="AB3" s="410"/>
-      <c r="AC3" s="410"/>
-      <c r="AD3" s="410"/>
-      <c r="AE3" s="410"/>
-      <c r="AF3" s="410"/>
-      <c r="AG3" s="410"/>
-      <c r="AH3" s="410"/>
-      <c r="AI3" s="410"/>
-      <c r="AJ3" s="410"/>
-      <c r="AK3" s="410"/>
-      <c r="AL3" s="410"/>
-      <c r="AM3" s="410"/>
-      <c r="AN3" s="410"/>
-      <c r="AO3" s="410"/>
-      <c r="AP3" s="410"/>
-      <c r="AQ3" s="410"/>
-      <c r="AR3" s="410"/>
-      <c r="AS3" s="410"/>
-      <c r="AT3" s="410"/>
-      <c r="AU3" s="410"/>
-      <c r="AV3" s="410"/>
-      <c r="AW3" s="410"/>
-      <c r="AX3" s="410"/>
-      <c r="AY3" s="410"/>
-      <c r="AZ3" s="410"/>
-      <c r="BA3" s="410"/>
-      <c r="BB3" s="410"/>
-      <c r="BC3" s="410"/>
-      <c r="BD3" s="410"/>
-      <c r="BE3" s="410"/>
-      <c r="BF3" s="410"/>
-      <c r="BG3" s="410"/>
-      <c r="BH3" s="410"/>
-      <c r="BI3" s="410"/>
-      <c r="BJ3" s="410"/>
-      <c r="BK3" s="410"/>
-      <c r="BL3" s="410"/>
-      <c r="BM3" s="410"/>
-      <c r="BN3" s="410"/>
-      <c r="BO3" s="410"/>
-      <c r="BP3" s="410"/>
-      <c r="BQ3" s="410"/>
-      <c r="BR3" s="410"/>
-      <c r="BS3" s="410"/>
-      <c r="BT3" s="410"/>
-      <c r="BU3" s="410"/>
-      <c r="BW3" s="409" t="s">
+      <c r="A3" s="408"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="399"/>
+      <c r="I3" s="399"/>
+      <c r="J3" s="399"/>
+      <c r="K3" s="399"/>
+      <c r="L3" s="399"/>
+      <c r="M3" s="399"/>
+      <c r="N3" s="399"/>
+      <c r="O3" s="399"/>
+      <c r="P3" s="399"/>
+      <c r="Q3" s="399"/>
+      <c r="R3" s="399"/>
+      <c r="S3" s="399"/>
+      <c r="T3" s="399"/>
+      <c r="U3" s="399"/>
+      <c r="V3" s="399"/>
+      <c r="W3" s="399"/>
+      <c r="X3" s="399"/>
+      <c r="Y3" s="399"/>
+      <c r="Z3" s="399"/>
+      <c r="AA3" s="399"/>
+      <c r="AB3" s="399"/>
+      <c r="AC3" s="399"/>
+      <c r="AD3" s="399"/>
+      <c r="AE3" s="399"/>
+      <c r="AF3" s="399"/>
+      <c r="AG3" s="399"/>
+      <c r="AH3" s="399"/>
+      <c r="AI3" s="399"/>
+      <c r="AJ3" s="399"/>
+      <c r="AK3" s="399"/>
+      <c r="AL3" s="399"/>
+      <c r="AM3" s="399"/>
+      <c r="AN3" s="399"/>
+      <c r="AO3" s="399"/>
+      <c r="AP3" s="399"/>
+      <c r="AQ3" s="399"/>
+      <c r="AR3" s="399"/>
+      <c r="AS3" s="399"/>
+      <c r="AT3" s="399"/>
+      <c r="AU3" s="399"/>
+      <c r="AV3" s="399"/>
+      <c r="AW3" s="399"/>
+      <c r="AX3" s="399"/>
+      <c r="AY3" s="399"/>
+      <c r="AZ3" s="399"/>
+      <c r="BA3" s="399"/>
+      <c r="BB3" s="399"/>
+      <c r="BC3" s="399"/>
+      <c r="BD3" s="399"/>
+      <c r="BE3" s="399"/>
+      <c r="BF3" s="399"/>
+      <c r="BG3" s="399"/>
+      <c r="BH3" s="399"/>
+      <c r="BI3" s="399"/>
+      <c r="BJ3" s="399"/>
+      <c r="BK3" s="399"/>
+      <c r="BL3" s="399"/>
+      <c r="BM3" s="399"/>
+      <c r="BN3" s="399"/>
+      <c r="BO3" s="399"/>
+      <c r="BP3" s="399"/>
+      <c r="BQ3" s="399"/>
+      <c r="BR3" s="399"/>
+      <c r="BS3" s="399"/>
+      <c r="BT3" s="399"/>
+      <c r="BU3" s="399"/>
+      <c r="BW3" s="398" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="410"/>
-      <c r="BY3" s="410"/>
-      <c r="BZ3" s="410"/>
-      <c r="CA3" s="410"/>
-      <c r="CB3" s="410"/>
+      <c r="BX3" s="399"/>
+      <c r="BY3" s="399"/>
+      <c r="BZ3" s="399"/>
+      <c r="CA3" s="399"/>
+      <c r="CB3" s="399"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18819,366 +18794,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="410"/>
-      <c r="BX4" s="410"/>
-      <c r="BY4" s="410"/>
-      <c r="BZ4" s="410"/>
-      <c r="CA4" s="410"/>
-      <c r="CB4" s="410"/>
+      <c r="BW4" s="399"/>
+      <c r="BX4" s="399"/>
+      <c r="BY4" s="399"/>
+      <c r="BZ4" s="399"/>
+      <c r="CA4" s="399"/>
+      <c r="CB4" s="399"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="422" t="s">
+      <c r="A5" s="411" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="421" t="s">
+      <c r="B5" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="395" t="s">
+      <c r="C5" s="384" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="420" t="s">
+      <c r="D5" s="409" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="420" t="s">
+      <c r="E5" s="409" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="440" t="s">
+      <c r="F5" s="429" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="395" t="s">
+      <c r="G5" s="384" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="338" t="s">
+      <c r="H5" s="335" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="338" t="s">
+      <c r="I5" s="335" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="395" t="s">
+      <c r="J5" s="384" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="424" t="s">
+      <c r="K5" s="413" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="406"/>
-      <c r="M5" s="406"/>
-      <c r="N5" s="406"/>
-      <c r="O5" s="406"/>
-      <c r="P5" s="406"/>
-      <c r="Q5" s="406"/>
-      <c r="R5" s="406"/>
-      <c r="S5" s="406"/>
-      <c r="T5" s="406"/>
-      <c r="U5" s="406"/>
-      <c r="V5" s="406"/>
-      <c r="W5" s="406"/>
-      <c r="X5" s="406"/>
-      <c r="Y5" s="395" t="s">
+      <c r="L5" s="395"/>
+      <c r="M5" s="395"/>
+      <c r="N5" s="395"/>
+      <c r="O5" s="395"/>
+      <c r="P5" s="395"/>
+      <c r="Q5" s="395"/>
+      <c r="R5" s="395"/>
+      <c r="S5" s="395"/>
+      <c r="T5" s="395"/>
+      <c r="U5" s="395"/>
+      <c r="V5" s="395"/>
+      <c r="W5" s="395"/>
+      <c r="X5" s="395"/>
+      <c r="Y5" s="384" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="406"/>
-      <c r="AA5" s="406"/>
-      <c r="AB5" s="406"/>
-      <c r="AC5" s="406"/>
-      <c r="AD5" s="406"/>
-      <c r="AE5" s="406"/>
-      <c r="AF5" s="406"/>
-      <c r="AG5" s="406"/>
-      <c r="AH5" s="406"/>
-      <c r="AI5" s="406"/>
-      <c r="AJ5" s="406"/>
-      <c r="AK5" s="406"/>
-      <c r="AL5" s="406"/>
-      <c r="AM5" s="406"/>
-      <c r="AN5" s="406"/>
-      <c r="AO5" s="407"/>
-      <c r="AP5" s="395" t="s">
+      <c r="Z5" s="395"/>
+      <c r="AA5" s="395"/>
+      <c r="AB5" s="395"/>
+      <c r="AC5" s="395"/>
+      <c r="AD5" s="395"/>
+      <c r="AE5" s="395"/>
+      <c r="AF5" s="395"/>
+      <c r="AG5" s="395"/>
+      <c r="AH5" s="395"/>
+      <c r="AI5" s="395"/>
+      <c r="AJ5" s="395"/>
+      <c r="AK5" s="395"/>
+      <c r="AL5" s="395"/>
+      <c r="AM5" s="395"/>
+      <c r="AN5" s="395"/>
+      <c r="AO5" s="396"/>
+      <c r="AP5" s="384" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="395" t="s">
+      <c r="AQ5" s="384" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="395" t="s">
+      <c r="AR5" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="395" t="s">
+      <c r="AS5" s="384" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="395" t="s">
+      <c r="AT5" s="384" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="395" t="s">
+      <c r="AU5" s="384" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="395" t="s">
+      <c r="AV5" s="384" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="395" t="s">
+      <c r="AW5" s="384" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="395" t="s">
+      <c r="AX5" s="384" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="405" t="s">
+      <c r="AY5" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="406"/>
-      <c r="BA5" s="406"/>
-      <c r="BB5" s="406"/>
-      <c r="BC5" s="406"/>
-      <c r="BD5" s="406"/>
-      <c r="BE5" s="406"/>
-      <c r="BF5" s="406"/>
-      <c r="BG5" s="406"/>
-      <c r="BH5" s="406"/>
-      <c r="BI5" s="406"/>
-      <c r="BJ5" s="406"/>
-      <c r="BK5" s="406"/>
-      <c r="BL5" s="406"/>
-      <c r="BM5" s="406"/>
-      <c r="BN5" s="406"/>
-      <c r="BO5" s="406"/>
-      <c r="BP5" s="407"/>
-      <c r="BQ5" s="411" t="s">
+      <c r="AZ5" s="395"/>
+      <c r="BA5" s="395"/>
+      <c r="BB5" s="395"/>
+      <c r="BC5" s="395"/>
+      <c r="BD5" s="395"/>
+      <c r="BE5" s="395"/>
+      <c r="BF5" s="395"/>
+      <c r="BG5" s="395"/>
+      <c r="BH5" s="395"/>
+      <c r="BI5" s="395"/>
+      <c r="BJ5" s="395"/>
+      <c r="BK5" s="395"/>
+      <c r="BL5" s="395"/>
+      <c r="BM5" s="395"/>
+      <c r="BN5" s="395"/>
+      <c r="BO5" s="395"/>
+      <c r="BP5" s="396"/>
+      <c r="BQ5" s="400" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="412"/>
-      <c r="BS5" s="405" t="s">
+      <c r="BR5" s="401"/>
+      <c r="BS5" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="405" t="s">
+      <c r="BT5" s="394" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="399" t="s">
+      <c r="BU5" s="388" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="402" t="s">
+      <c r="BW5" s="391" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="413" t="s">
+      <c r="BX5" s="402" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="414"/>
-      <c r="BZ5" s="414"/>
-      <c r="CA5" s="412"/>
-      <c r="CB5" s="408" t="s">
+      <c r="BY5" s="403"/>
+      <c r="BZ5" s="403"/>
+      <c r="CA5" s="401"/>
+      <c r="CB5" s="397" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="390" t="s">
+      <c r="CC5" s="379" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="390" t="s">
+      <c r="CD5" s="379" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="391"/>
-      <c r="B6" s="391"/>
-      <c r="C6" s="391"/>
-      <c r="D6" s="391"/>
-      <c r="E6" s="391"/>
-      <c r="F6" s="391"/>
-      <c r="G6" s="391"/>
-      <c r="H6" s="391"/>
-      <c r="I6" s="391"/>
-      <c r="J6" s="391"/>
-      <c r="K6" s="396" t="s">
+      <c r="A6" s="380"/>
+      <c r="B6" s="380"/>
+      <c r="C6" s="380"/>
+      <c r="D6" s="380"/>
+      <c r="E6" s="380"/>
+      <c r="F6" s="380"/>
+      <c r="G6" s="380"/>
+      <c r="H6" s="380"/>
+      <c r="I6" s="380"/>
+      <c r="J6" s="380"/>
+      <c r="K6" s="385" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="396" t="s">
+      <c r="L6" s="385" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="396" t="s">
+      <c r="M6" s="385" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="396" t="s">
+      <c r="N6" s="385" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="396" t="s">
+      <c r="O6" s="385" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="396" t="s">
+      <c r="P6" s="385" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="396" t="s">
+      <c r="Q6" s="385" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="396" t="s">
+      <c r="R6" s="385" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="396" t="s">
+      <c r="S6" s="385" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="396" t="s">
+      <c r="T6" s="385" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="396" t="s">
+      <c r="U6" s="385" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="426" t="s">
+      <c r="V6" s="415" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="412"/>
-      <c r="X6" s="396" t="s">
+      <c r="W6" s="401"/>
+      <c r="X6" s="385" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="395" t="s">
+      <c r="Y6" s="384" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="395" t="s">
+      <c r="Z6" s="384" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="395" t="s">
+      <c r="AA6" s="384" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="395" t="s">
+      <c r="AB6" s="384" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="338" t="s">
+      <c r="AC6" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="338" t="s">
+      <c r="AD6" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="338" t="s">
+      <c r="AE6" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="338" t="s">
+      <c r="AF6" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="395" t="s">
+      <c r="AG6" s="384" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="338" t="s">
+      <c r="AH6" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="338" t="s">
+      <c r="AI6" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="395" t="s">
+      <c r="AJ6" s="384" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="423" t="s">
+      <c r="AK6" s="412" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="395" t="s">
+      <c r="AL6" s="384" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="395" t="s">
+      <c r="AM6" s="384" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="425" t="s">
+      <c r="AN6" s="414" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="395" t="s">
+      <c r="AO6" s="384" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="391"/>
-      <c r="AQ6" s="391"/>
-      <c r="AR6" s="391"/>
-      <c r="AS6" s="391"/>
-      <c r="AT6" s="391"/>
-      <c r="AU6" s="391"/>
-      <c r="AV6" s="391"/>
-      <c r="AW6" s="391"/>
-      <c r="AX6" s="391"/>
-      <c r="AY6" s="405" t="s">
+      <c r="AP6" s="380"/>
+      <c r="AQ6" s="380"/>
+      <c r="AR6" s="380"/>
+      <c r="AS6" s="380"/>
+      <c r="AT6" s="380"/>
+      <c r="AU6" s="380"/>
+      <c r="AV6" s="380"/>
+      <c r="AW6" s="380"/>
+      <c r="AX6" s="380"/>
+      <c r="AY6" s="394" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="406"/>
-      <c r="BA6" s="406"/>
-      <c r="BB6" s="406"/>
-      <c r="BC6" s="406"/>
-      <c r="BD6" s="406"/>
-      <c r="BE6" s="406"/>
-      <c r="BF6" s="406"/>
-      <c r="BG6" s="406"/>
-      <c r="BH6" s="406"/>
-      <c r="BI6" s="406"/>
-      <c r="BJ6" s="407"/>
-      <c r="BK6" s="405" t="s">
+      <c r="AZ6" s="395"/>
+      <c r="BA6" s="395"/>
+      <c r="BB6" s="395"/>
+      <c r="BC6" s="395"/>
+      <c r="BD6" s="395"/>
+      <c r="BE6" s="395"/>
+      <c r="BF6" s="395"/>
+      <c r="BG6" s="395"/>
+      <c r="BH6" s="395"/>
+      <c r="BI6" s="395"/>
+      <c r="BJ6" s="396"/>
+      <c r="BK6" s="394" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="406"/>
-      <c r="BM6" s="406"/>
-      <c r="BN6" s="406"/>
-      <c r="BO6" s="406"/>
-      <c r="BP6" s="407"/>
-      <c r="BQ6" s="393" t="s">
+      <c r="BL6" s="395"/>
+      <c r="BM6" s="395"/>
+      <c r="BN6" s="395"/>
+      <c r="BO6" s="395"/>
+      <c r="BP6" s="396"/>
+      <c r="BQ6" s="382" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="393" t="s">
+      <c r="BR6" s="382" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="391"/>
-      <c r="BT6" s="391"/>
-      <c r="BU6" s="400"/>
-      <c r="BW6" s="403"/>
-      <c r="BX6" s="400"/>
-      <c r="BY6" s="415"/>
-      <c r="BZ6" s="415"/>
-      <c r="CA6" s="403"/>
-      <c r="CB6" s="391"/>
-      <c r="CC6" s="391"/>
-      <c r="CD6" s="391"/>
+      <c r="BS6" s="380"/>
+      <c r="BT6" s="380"/>
+      <c r="BU6" s="389"/>
+      <c r="BW6" s="392"/>
+      <c r="BX6" s="389"/>
+      <c r="BY6" s="404"/>
+      <c r="BZ6" s="404"/>
+      <c r="CA6" s="392"/>
+      <c r="CB6" s="380"/>
+      <c r="CC6" s="380"/>
+      <c r="CD6" s="380"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="391"/>
-      <c r="B7" s="391"/>
-      <c r="C7" s="391"/>
-      <c r="D7" s="391"/>
-      <c r="E7" s="391"/>
-      <c r="F7" s="391"/>
-      <c r="G7" s="391"/>
-      <c r="H7" s="391"/>
-      <c r="I7" s="391"/>
-      <c r="J7" s="391"/>
-      <c r="K7" s="391"/>
-      <c r="L7" s="391"/>
-      <c r="M7" s="391"/>
-      <c r="N7" s="391"/>
-      <c r="O7" s="391"/>
-      <c r="P7" s="391"/>
-      <c r="Q7" s="391"/>
-      <c r="R7" s="391"/>
-      <c r="S7" s="391"/>
-      <c r="T7" s="391"/>
-      <c r="U7" s="391"/>
-      <c r="V7" s="401"/>
-      <c r="W7" s="427"/>
-      <c r="X7" s="391"/>
-      <c r="Y7" s="391"/>
-      <c r="Z7" s="391"/>
-      <c r="AA7" s="391"/>
-      <c r="AB7" s="391"/>
-      <c r="AC7" s="391"/>
-      <c r="AD7" s="391"/>
-      <c r="AE7" s="391"/>
-      <c r="AF7" s="391"/>
-      <c r="AG7" s="391"/>
-      <c r="AH7" s="391"/>
-      <c r="AI7" s="391"/>
-      <c r="AJ7" s="391"/>
-      <c r="AK7" s="400"/>
-      <c r="AL7" s="391"/>
-      <c r="AM7" s="391"/>
-      <c r="AN7" s="391"/>
-      <c r="AO7" s="391"/>
-      <c r="AP7" s="391"/>
-      <c r="AQ7" s="391"/>
-      <c r="AR7" s="391"/>
-      <c r="AS7" s="391"/>
-      <c r="AT7" s="391"/>
-      <c r="AU7" s="391"/>
-      <c r="AV7" s="391"/>
-      <c r="AW7" s="391"/>
-      <c r="AX7" s="391"/>
+      <c r="A7" s="380"/>
+      <c r="B7" s="380"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
+      <c r="E7" s="380"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="380"/>
+      <c r="H7" s="380"/>
+      <c r="I7" s="380"/>
+      <c r="J7" s="380"/>
+      <c r="K7" s="380"/>
+      <c r="L7" s="380"/>
+      <c r="M7" s="380"/>
+      <c r="N7" s="380"/>
+      <c r="O7" s="380"/>
+      <c r="P7" s="380"/>
+      <c r="Q7" s="380"/>
+      <c r="R7" s="380"/>
+      <c r="S7" s="380"/>
+      <c r="T7" s="380"/>
+      <c r="U7" s="380"/>
+      <c r="V7" s="390"/>
+      <c r="W7" s="416"/>
+      <c r="X7" s="380"/>
+      <c r="Y7" s="380"/>
+      <c r="Z7" s="380"/>
+      <c r="AA7" s="380"/>
+      <c r="AB7" s="380"/>
+      <c r="AC7" s="380"/>
+      <c r="AD7" s="380"/>
+      <c r="AE7" s="380"/>
+      <c r="AF7" s="380"/>
+      <c r="AG7" s="380"/>
+      <c r="AH7" s="380"/>
+      <c r="AI7" s="380"/>
+      <c r="AJ7" s="380"/>
+      <c r="AK7" s="389"/>
+      <c r="AL7" s="380"/>
+      <c r="AM7" s="380"/>
+      <c r="AN7" s="380"/>
+      <c r="AO7" s="380"/>
+      <c r="AP7" s="380"/>
+      <c r="AQ7" s="380"/>
+      <c r="AR7" s="380"/>
+      <c r="AS7" s="380"/>
+      <c r="AT7" s="380"/>
+      <c r="AU7" s="380"/>
+      <c r="AV7" s="380"/>
+      <c r="AW7" s="380"/>
+      <c r="AX7" s="380"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19188,122 +19163,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="405" t="s">
+      <c r="BB7" s="394" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="397" t="s">
+      <c r="BC7" s="386" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="397" t="s">
+      <c r="BD7" s="386" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="397" t="s">
+      <c r="BE7" s="386" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="397" t="s">
+      <c r="BF7" s="386" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="397" t="s">
+      <c r="BG7" s="386" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="397" t="s">
+      <c r="BH7" s="386" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="397" t="s">
+      <c r="BI7" s="386" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="398" t="s">
+      <c r="BJ7" s="387" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="397" t="s">
+      <c r="BK7" s="386" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="405" t="s">
+      <c r="BL7" s="394" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="397" t="s">
+      <c r="BM7" s="386" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="405" t="s">
+      <c r="BN7" s="394" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="405" t="s">
+      <c r="BO7" s="394" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="405" t="s">
+      <c r="BP7" s="394" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="391"/>
-      <c r="BR7" s="391"/>
-      <c r="BS7" s="391"/>
-      <c r="BT7" s="391"/>
-      <c r="BU7" s="400"/>
-      <c r="BW7" s="403"/>
-      <c r="BX7" s="416"/>
-      <c r="BY7" s="417"/>
-      <c r="BZ7" s="417"/>
-      <c r="CA7" s="404"/>
-      <c r="CB7" s="391"/>
-      <c r="CC7" s="391"/>
-      <c r="CD7" s="391"/>
+      <c r="BQ7" s="380"/>
+      <c r="BR7" s="380"/>
+      <c r="BS7" s="380"/>
+      <c r="BT7" s="380"/>
+      <c r="BU7" s="389"/>
+      <c r="BW7" s="392"/>
+      <c r="BX7" s="405"/>
+      <c r="BY7" s="406"/>
+      <c r="BZ7" s="406"/>
+      <c r="CA7" s="393"/>
+      <c r="CB7" s="380"/>
+      <c r="CC7" s="380"/>
+      <c r="CD7" s="380"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="394"/>
-      <c r="B8" s="394"/>
-      <c r="C8" s="394"/>
-      <c r="D8" s="394"/>
-      <c r="E8" s="394"/>
-      <c r="F8" s="394"/>
-      <c r="G8" s="394"/>
-      <c r="H8" s="394"/>
-      <c r="I8" s="394"/>
-      <c r="J8" s="394"/>
-      <c r="K8" s="394"/>
-      <c r="L8" s="394"/>
-      <c r="M8" s="394"/>
-      <c r="N8" s="394"/>
-      <c r="O8" s="394"/>
-      <c r="P8" s="394"/>
-      <c r="Q8" s="394"/>
-      <c r="R8" s="394"/>
-      <c r="S8" s="394"/>
-      <c r="T8" s="394"/>
-      <c r="U8" s="394"/>
+      <c r="A8" s="383"/>
+      <c r="B8" s="383"/>
+      <c r="C8" s="383"/>
+      <c r="D8" s="383"/>
+      <c r="E8" s="383"/>
+      <c r="F8" s="383"/>
+      <c r="G8" s="383"/>
+      <c r="H8" s="383"/>
+      <c r="I8" s="383"/>
+      <c r="J8" s="383"/>
+      <c r="K8" s="383"/>
+      <c r="L8" s="383"/>
+      <c r="M8" s="383"/>
+      <c r="N8" s="383"/>
+      <c r="O8" s="383"/>
+      <c r="P8" s="383"/>
+      <c r="Q8" s="383"/>
+      <c r="R8" s="383"/>
+      <c r="S8" s="383"/>
+      <c r="T8" s="383"/>
+      <c r="U8" s="383"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="394"/>
-      <c r="Y8" s="394"/>
-      <c r="Z8" s="394"/>
-      <c r="AA8" s="394"/>
-      <c r="AB8" s="394"/>
-      <c r="AC8" s="394"/>
-      <c r="AD8" s="394"/>
-      <c r="AE8" s="394"/>
-      <c r="AF8" s="394"/>
-      <c r="AG8" s="394"/>
-      <c r="AH8" s="394"/>
-      <c r="AI8" s="394"/>
-      <c r="AJ8" s="394"/>
-      <c r="AK8" s="401"/>
-      <c r="AL8" s="394"/>
-      <c r="AM8" s="394"/>
-      <c r="AN8" s="394"/>
-      <c r="AO8" s="394"/>
-      <c r="AP8" s="394"/>
-      <c r="AQ8" s="394"/>
-      <c r="AR8" s="394"/>
-      <c r="AS8" s="394"/>
-      <c r="AT8" s="394"/>
-      <c r="AU8" s="394"/>
-      <c r="AV8" s="394"/>
-      <c r="AW8" s="394"/>
-      <c r="AX8" s="394"/>
+      <c r="X8" s="383"/>
+      <c r="Y8" s="383"/>
+      <c r="Z8" s="383"/>
+      <c r="AA8" s="383"/>
+      <c r="AB8" s="383"/>
+      <c r="AC8" s="383"/>
+      <c r="AD8" s="383"/>
+      <c r="AE8" s="383"/>
+      <c r="AF8" s="383"/>
+      <c r="AG8" s="383"/>
+      <c r="AH8" s="383"/>
+      <c r="AI8" s="383"/>
+      <c r="AJ8" s="383"/>
+      <c r="AK8" s="390"/>
+      <c r="AL8" s="383"/>
+      <c r="AM8" s="383"/>
+      <c r="AN8" s="383"/>
+      <c r="AO8" s="383"/>
+      <c r="AP8" s="383"/>
+      <c r="AQ8" s="383"/>
+      <c r="AR8" s="383"/>
+      <c r="AS8" s="383"/>
+      <c r="AT8" s="383"/>
+      <c r="AU8" s="383"/>
+      <c r="AV8" s="383"/>
+      <c r="AW8" s="383"/>
+      <c r="AX8" s="383"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19313,27 +19288,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="394"/>
-      <c r="BC8" s="394"/>
-      <c r="BD8" s="394"/>
-      <c r="BE8" s="394"/>
-      <c r="BF8" s="394"/>
-      <c r="BG8" s="394"/>
-      <c r="BH8" s="394"/>
-      <c r="BI8" s="394"/>
-      <c r="BJ8" s="394"/>
-      <c r="BK8" s="394"/>
-      <c r="BL8" s="394"/>
-      <c r="BM8" s="394"/>
-      <c r="BN8" s="394"/>
-      <c r="BO8" s="394"/>
-      <c r="BP8" s="394"/>
-      <c r="BQ8" s="394"/>
-      <c r="BR8" s="394"/>
-      <c r="BS8" s="394"/>
-      <c r="BT8" s="394"/>
-      <c r="BU8" s="401"/>
-      <c r="BW8" s="404"/>
+      <c r="BB8" s="383"/>
+      <c r="BC8" s="383"/>
+      <c r="BD8" s="383"/>
+      <c r="BE8" s="383"/>
+      <c r="BF8" s="383"/>
+      <c r="BG8" s="383"/>
+      <c r="BH8" s="383"/>
+      <c r="BI8" s="383"/>
+      <c r="BJ8" s="383"/>
+      <c r="BK8" s="383"/>
+      <c r="BL8" s="383"/>
+      <c r="BM8" s="383"/>
+      <c r="BN8" s="383"/>
+      <c r="BO8" s="383"/>
+      <c r="BP8" s="383"/>
+      <c r="BQ8" s="383"/>
+      <c r="BR8" s="383"/>
+      <c r="BS8" s="383"/>
+      <c r="BT8" s="383"/>
+      <c r="BU8" s="390"/>
+      <c r="BW8" s="393"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19346,9 +19321,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="392"/>
-      <c r="CC8" s="392"/>
-      <c r="CD8" s="392"/>
+      <c r="CB8" s="381"/>
+      <c r="CC8" s="381"/>
+      <c r="CD8" s="381"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1697A5-2187-404F-8B2F-E858923EE07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02E038B-839E-0D43-8BA8-C7C50AC15ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38540" yWindow="660" windowWidth="38100" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42000" yWindow="1360" windowWidth="33420" windowHeight="20240" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4546,7 +4546,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="162">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -9187,11 +9187,11 @@
       </c>
       <c r="H14" s="94">
         <f>SUM(H15:H21)</f>
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="I14" s="94">
         <f>SUM(I15:I21)</f>
-        <v>183399990</v>
+        <v>182799990</v>
       </c>
       <c r="J14" s="94"/>
       <c r="K14" s="313">
@@ -9265,7 +9265,7 @@
       <c r="AE14" s="94"/>
       <c r="AF14" s="94">
         <f t="shared" ref="AF14:AO14" si="5">SUM(AF15:AF21)</f>
-        <v>111923.07692307692</v>
+        <v>118846.15384615383</v>
       </c>
       <c r="AG14" s="94">
         <f t="shared" si="5"/>
@@ -9297,11 +9297,11 @@
       </c>
       <c r="AN14" s="94">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>830769.23076923075</v>
       </c>
       <c r="AO14" s="94">
         <f t="shared" si="5"/>
-        <v>181303448.65384617</v>
+        <v>180765756.34615386</v>
       </c>
       <c r="AP14" s="94"/>
       <c r="AQ14" s="94"/>
@@ -9317,19 +9317,19 @@
       <c r="AX14" s="94"/>
       <c r="AY14" s="94">
         <f>SUM(AY15:AY21)</f>
-        <v>3756801</v>
+        <v>3804801</v>
       </c>
       <c r="AZ14" s="94">
         <f>SUM(AZ15:AZ21)</f>
-        <v>704400</v>
+        <v>713400</v>
       </c>
       <c r="BA14" s="94">
         <f>SUM(BA15:BA21)</f>
-        <v>469600</v>
+        <v>475600</v>
       </c>
       <c r="BB14" s="94">
         <f>SUM(BB15:BB21)</f>
-        <v>4930801</v>
+        <v>4993801</v>
       </c>
       <c r="BC14" s="94">
         <f>SUM(BC15:BC21)</f>
@@ -9348,7 +9348,7 @@
       <c r="BK14" s="94"/>
       <c r="BL14" s="94">
         <f t="shared" ref="BL14:BQ14" si="6">SUM(BL15:BL21)</f>
-        <v>10161488</v>
+        <v>10155188</v>
       </c>
       <c r="BM14" s="94">
         <f t="shared" si="6"/>
@@ -9375,7 +9375,7 @@
       <c r="BT14" s="94"/>
       <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
-        <v>226721558.59230769</v>
+        <v>226664858.59230769</v>
       </c>
       <c r="BV14" s="252"/>
       <c r="BW14" s="242"/>
@@ -9621,7 +9621,9 @@
         <f t="shared" ref="CB15:CB21" si="32">SUM(BW15:CA15)</f>
         <v>63200000</v>
       </c>
-      <c r="CC15" s="279"/>
+      <c r="CC15" s="84" t="s">
+        <v>122</v>
+      </c>
       <c r="CD15" s="279"/>
       <c r="CE15" s="253"/>
       <c r="CF15" s="254"/>
@@ -9863,7 +9865,9 @@
         <f t="shared" si="32"/>
         <v>52200000</v>
       </c>
-      <c r="CC16" s="243"/>
+      <c r="CC16" s="84" t="s">
+        <v>114</v>
+      </c>
       <c r="CD16" s="243"/>
       <c r="CE16" s="253"/>
       <c r="CF16" s="254"/>
@@ -9896,11 +9900,11 @@
       </c>
       <c r="H17" s="94">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="I17" s="94">
         <f t="shared" si="8"/>
-        <v>34180000</v>
+        <v>33880000</v>
       </c>
       <c r="J17" s="92">
         <v>1</v>
@@ -10001,11 +10005,11 @@
       </c>
       <c r="AN17" s="94">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>276923.07692307694</v>
       </c>
       <c r="AO17" s="94">
         <f t="shared" si="21"/>
-        <v>34796923.07692308</v>
+        <v>34520000</v>
       </c>
       <c r="AP17" s="94"/>
       <c r="AQ17" s="94"/>
@@ -10026,19 +10030,19 @@
       </c>
       <c r="AY17" s="250">
         <f t="shared" si="24"/>
-        <v>625600</v>
+        <v>649600</v>
       </c>
       <c r="AZ17" s="250">
         <f t="shared" si="24"/>
-        <v>117300</v>
+        <v>121800</v>
       </c>
       <c r="BA17" s="250">
         <f t="shared" si="24"/>
-        <v>78200</v>
+        <v>81200</v>
       </c>
       <c r="BB17" s="250">
         <f t="shared" si="25"/>
-        <v>821100</v>
+        <v>852600</v>
       </c>
       <c r="BC17" s="250"/>
       <c r="BD17" s="250"/>
@@ -10064,11 +10068,11 @@
       </c>
       <c r="BK17" s="250">
         <f t="shared" si="28"/>
-        <v>19391976.923076928</v>
+        <v>19360476.923076928</v>
       </c>
       <c r="BL17" s="243">
         <f t="shared" si="29"/>
-        <v>2228395</v>
+        <v>2222095</v>
       </c>
       <c r="BM17" s="250"/>
       <c r="BN17" s="250"/>
@@ -10082,7 +10086,7 @@
       <c r="BT17" s="263"/>
       <c r="BU17" s="251">
         <f t="shared" si="30"/>
-        <v>39447689.615384616</v>
+        <v>39422489.615384616</v>
       </c>
       <c r="BV17" s="252"/>
       <c r="BW17" s="242">
@@ -10105,7 +10109,9 @@
         <f t="shared" si="32"/>
         <v>42200000</v>
       </c>
-      <c r="CC17" s="243"/>
+      <c r="CC17" s="84" t="s">
+        <v>118</v>
+      </c>
       <c r="CD17" s="243"/>
       <c r="CE17" s="253"/>
       <c r="CF17" s="254"/>
@@ -10347,7 +10353,9 @@
         <f t="shared" si="32"/>
         <v>26350000</v>
       </c>
-      <c r="CC18" s="243"/>
+      <c r="CC18" s="84" t="s">
+        <v>114</v>
+      </c>
       <c r="CD18" s="243"/>
       <c r="CE18" s="253"/>
       <c r="CF18" s="254"/>
@@ -10380,11 +10388,11 @@
       </c>
       <c r="H19" s="94">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="I19" s="94">
         <f t="shared" si="8"/>
-        <v>6700000</v>
+        <v>6400000</v>
       </c>
       <c r="J19" s="92">
         <v>1</v>
@@ -10459,7 +10467,7 @@
       </c>
       <c r="AF19" s="94">
         <f>IF(F19="LN",(G19+H19)/26*S19*30%,0)</f>
-        <v>111923.07692307692</v>
+        <v>118846.15384615383</v>
       </c>
       <c r="AG19" s="94">
         <f t="shared" si="16"/>
@@ -10485,11 +10493,11 @@
       </c>
       <c r="AN19" s="94">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>253846.15384615387</v>
       </c>
       <c r="AO19" s="94">
         <f t="shared" si="21"/>
-        <v>6661153.846153846</v>
+        <v>6400384.615384615</v>
       </c>
       <c r="AP19" s="94"/>
       <c r="AQ19" s="94"/>
@@ -10510,19 +10518,19 @@
       </c>
       <c r="AY19" s="250">
         <f t="shared" si="24"/>
-        <v>388000</v>
+        <v>412000</v>
       </c>
       <c r="AZ19" s="250">
         <f t="shared" si="24"/>
-        <v>72750</v>
+        <v>77250</v>
       </c>
       <c r="BA19" s="250">
         <f t="shared" si="24"/>
-        <v>48500</v>
+        <v>51500</v>
       </c>
       <c r="BB19" s="250">
         <f t="shared" si="25"/>
-        <v>509250</v>
+        <v>540750</v>
       </c>
       <c r="BC19" s="250"/>
       <c r="BD19" s="250"/>
@@ -10548,7 +10556,7 @@
       </c>
       <c r="BK19" s="250">
         <f t="shared" si="28"/>
-        <v>-6129634.6153846141</v>
+        <v>-6161134.6153846141</v>
       </c>
       <c r="BL19" s="243">
         <f t="shared" si="29"/>
@@ -10566,7 +10574,7 @@
       <c r="BT19" s="263"/>
       <c r="BU19" s="251">
         <f t="shared" si="30"/>
-        <v>11625326.923076924</v>
+        <v>11593826.923076924</v>
       </c>
       <c r="BV19" s="252"/>
       <c r="BW19" s="242">
@@ -10589,7 +10597,9 @@
         <f t="shared" si="32"/>
         <v>11750000</v>
       </c>
-      <c r="CC19" s="243"/>
+      <c r="CC19" s="84" t="s">
+        <v>118</v>
+      </c>
       <c r="CD19" s="243"/>
       <c r="CE19" s="253"/>
       <c r="CF19" s="254"/>
@@ -10831,7 +10841,7 @@
         <f t="shared" si="32"/>
         <v>24350000</v>
       </c>
-      <c r="CC20" s="243" t="s">
+      <c r="CC20" s="84" t="s">
         <v>114</v>
       </c>
       <c r="CD20" s="243"/>
@@ -11075,7 +11085,7 @@
         <f t="shared" si="32"/>
         <v>18050000</v>
       </c>
-      <c r="CC21" s="243" t="s">
+      <c r="CC21" s="84" t="s">
         <v>118</v>
       </c>
       <c r="CD21" s="243"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63319DB3-52B9-1C42-8481-FC96DB47FB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C46ADD5-E081-C144-9512-8FB783518F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38420" yWindow="500" windowWidth="33420" windowHeight="20240" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38920" yWindow="560" windowWidth="33440" windowHeight="14320" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4259,7 +4259,6 @@
     <definedName name="解_任_">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5856,7 +5855,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="45" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="439">
+  <cellXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6758,78 +6757,61 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6853,48 +6835,88 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6903,10 +6925,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6914,97 +6936,72 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7772,88 +7769,88 @@
       <c r="CD2" s="294"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="364"/>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="363"/>
-      <c r="K3" s="363"/>
-      <c r="L3" s="363"/>
-      <c r="M3" s="363"/>
-      <c r="N3" s="363"/>
-      <c r="O3" s="363"/>
-      <c r="P3" s="363"/>
-      <c r="Q3" s="363"/>
-      <c r="R3" s="363"/>
-      <c r="S3" s="363"/>
-      <c r="T3" s="363"/>
-      <c r="U3" s="363"/>
-      <c r="V3" s="363"/>
-      <c r="W3" s="363"/>
-      <c r="X3" s="363"/>
-      <c r="Y3" s="363"/>
-      <c r="Z3" s="363"/>
-      <c r="AA3" s="363"/>
-      <c r="AB3" s="363"/>
-      <c r="AC3" s="363"/>
-      <c r="AD3" s="363"/>
-      <c r="AE3" s="363"/>
-      <c r="AF3" s="363"/>
-      <c r="AG3" s="363"/>
-      <c r="AH3" s="363"/>
-      <c r="AI3" s="363"/>
-      <c r="AJ3" s="363"/>
-      <c r="AK3" s="363"/>
-      <c r="AL3" s="363"/>
-      <c r="AM3" s="363"/>
-      <c r="AN3" s="363"/>
-      <c r="AO3" s="363"/>
-      <c r="AP3" s="363"/>
-      <c r="AQ3" s="363"/>
-      <c r="AR3" s="363"/>
-      <c r="AS3" s="363"/>
-      <c r="AT3" s="363"/>
-      <c r="AU3" s="363"/>
-      <c r="AV3" s="363"/>
-      <c r="AW3" s="363"/>
-      <c r="AX3" s="363"/>
-      <c r="AY3" s="363"/>
-      <c r="AZ3" s="363"/>
-      <c r="BA3" s="363"/>
-      <c r="BB3" s="363"/>
-      <c r="BC3" s="363"/>
-      <c r="BD3" s="363"/>
-      <c r="BE3" s="363"/>
-      <c r="BF3" s="363"/>
-      <c r="BG3" s="363"/>
-      <c r="BH3" s="363"/>
-      <c r="BI3" s="363"/>
-      <c r="BJ3" s="363"/>
-      <c r="BK3" s="363"/>
-      <c r="BL3" s="363"/>
-      <c r="BM3" s="363"/>
-      <c r="BN3" s="363"/>
-      <c r="BO3" s="363"/>
-      <c r="BP3" s="363"/>
-      <c r="BQ3" s="363"/>
-      <c r="BR3" s="363"/>
-      <c r="BS3" s="363"/>
-      <c r="BT3" s="363"/>
-      <c r="BU3" s="363"/>
+      <c r="A3" s="353"/>
+      <c r="B3" s="348"/>
+      <c r="C3" s="348"/>
+      <c r="D3" s="348"/>
+      <c r="E3" s="348"/>
+      <c r="F3" s="348"/>
+      <c r="G3" s="348"/>
+      <c r="H3" s="348"/>
+      <c r="I3" s="348"/>
+      <c r="J3" s="348"/>
+      <c r="K3" s="348"/>
+      <c r="L3" s="348"/>
+      <c r="M3" s="348"/>
+      <c r="N3" s="348"/>
+      <c r="O3" s="348"/>
+      <c r="P3" s="348"/>
+      <c r="Q3" s="348"/>
+      <c r="R3" s="348"/>
+      <c r="S3" s="348"/>
+      <c r="T3" s="348"/>
+      <c r="U3" s="348"/>
+      <c r="V3" s="348"/>
+      <c r="W3" s="348"/>
+      <c r="X3" s="348"/>
+      <c r="Y3" s="348"/>
+      <c r="Z3" s="348"/>
+      <c r="AA3" s="348"/>
+      <c r="AB3" s="348"/>
+      <c r="AC3" s="348"/>
+      <c r="AD3" s="348"/>
+      <c r="AE3" s="348"/>
+      <c r="AF3" s="348"/>
+      <c r="AG3" s="348"/>
+      <c r="AH3" s="348"/>
+      <c r="AI3" s="348"/>
+      <c r="AJ3" s="348"/>
+      <c r="AK3" s="348"/>
+      <c r="AL3" s="348"/>
+      <c r="AM3" s="348"/>
+      <c r="AN3" s="348"/>
+      <c r="AO3" s="348"/>
+      <c r="AP3" s="348"/>
+      <c r="AQ3" s="348"/>
+      <c r="AR3" s="348"/>
+      <c r="AS3" s="348"/>
+      <c r="AT3" s="348"/>
+      <c r="AU3" s="348"/>
+      <c r="AV3" s="348"/>
+      <c r="AW3" s="348"/>
+      <c r="AX3" s="348"/>
+      <c r="AY3" s="348"/>
+      <c r="AZ3" s="348"/>
+      <c r="BA3" s="348"/>
+      <c r="BB3" s="348"/>
+      <c r="BC3" s="348"/>
+      <c r="BD3" s="348"/>
+      <c r="BE3" s="348"/>
+      <c r="BF3" s="348"/>
+      <c r="BG3" s="348"/>
+      <c r="BH3" s="348"/>
+      <c r="BI3" s="348"/>
+      <c r="BJ3" s="348"/>
+      <c r="BK3" s="348"/>
+      <c r="BL3" s="348"/>
+      <c r="BM3" s="348"/>
+      <c r="BN3" s="348"/>
+      <c r="BO3" s="348"/>
+      <c r="BP3" s="348"/>
+      <c r="BQ3" s="348"/>
+      <c r="BR3" s="348"/>
+      <c r="BS3" s="348"/>
+      <c r="BT3" s="348"/>
+      <c r="BU3" s="348"/>
       <c r="BV3" s="296"/>
-      <c r="BW3" s="362" t="s">
+      <c r="BW3" s="347" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="363"/>
-      <c r="BY3" s="363"/>
-      <c r="BZ3" s="363"/>
-      <c r="CA3" s="363"/>
-      <c r="CB3" s="363"/>
+      <c r="BX3" s="348"/>
+      <c r="BY3" s="348"/>
+      <c r="BZ3" s="348"/>
+      <c r="CA3" s="348"/>
+      <c r="CB3" s="348"/>
       <c r="CC3" s="298"/>
       <c r="CD3" s="298"/>
     </row>
@@ -7931,12 +7928,12 @@
       <c r="BT4" s="299"/>
       <c r="BU4" s="299"/>
       <c r="BV4" s="299"/>
-      <c r="BW4" s="363"/>
-      <c r="BX4" s="363"/>
-      <c r="BY4" s="363"/>
-      <c r="BZ4" s="363"/>
-      <c r="CA4" s="363"/>
-      <c r="CB4" s="363"/>
+      <c r="BW4" s="348"/>
+      <c r="BX4" s="348"/>
+      <c r="BY4" s="348"/>
+      <c r="BZ4" s="348"/>
+      <c r="CA4" s="348"/>
+      <c r="CB4" s="348"/>
       <c r="CC4" s="298"/>
       <c r="CD4" s="298"/>
     </row>
@@ -8014,12 +8011,12 @@
       <c r="BT5" s="299"/>
       <c r="BU5" s="299"/>
       <c r="BV5" s="299"/>
-      <c r="BW5" s="363"/>
-      <c r="BX5" s="363"/>
-      <c r="BY5" s="363"/>
-      <c r="BZ5" s="363"/>
-      <c r="CA5" s="363"/>
-      <c r="CB5" s="363"/>
+      <c r="BW5" s="348"/>
+      <c r="BX5" s="348"/>
+      <c r="BY5" s="348"/>
+      <c r="BZ5" s="348"/>
+      <c r="CA5" s="348"/>
+      <c r="CB5" s="348"/>
       <c r="CC5" s="298"/>
       <c r="CD5" s="298"/>
     </row>
@@ -8095,12 +8092,12 @@
       <c r="BT6" s="301"/>
       <c r="BU6" s="301"/>
       <c r="BV6" s="301"/>
-      <c r="BW6" s="363"/>
-      <c r="BX6" s="363"/>
-      <c r="BY6" s="363"/>
-      <c r="BZ6" s="363"/>
-      <c r="CA6" s="363"/>
-      <c r="CB6" s="363"/>
+      <c r="BW6" s="348"/>
+      <c r="BX6" s="348"/>
+      <c r="BY6" s="348"/>
+      <c r="BZ6" s="348"/>
+      <c r="CA6" s="348"/>
+      <c r="CB6" s="348"/>
       <c r="CC6" s="298"/>
       <c r="CD6" s="298"/>
     </row>
@@ -8240,356 +8237,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="361" t="s">
+      <c r="A8" s="436" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="366" t="s">
+      <c r="B8" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="335" t="s">
+      <c r="C8" s="332" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="353" t="s">
+      <c r="D8" s="339" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="353" t="s">
+      <c r="E8" s="339" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="335" t="s">
+      <c r="F8" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="354" t="s">
+      <c r="G8" s="345" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="423" t="s">
+      <c r="H8" s="371" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="423" t="s">
+      <c r="I8" s="371" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="354" t="s">
+      <c r="J8" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="360" t="s">
+      <c r="K8" s="369" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="349"/>
-      <c r="M8" s="349"/>
-      <c r="N8" s="349"/>
-      <c r="O8" s="349"/>
-      <c r="P8" s="349"/>
-      <c r="Q8" s="349"/>
-      <c r="R8" s="349"/>
-      <c r="S8" s="349"/>
-      <c r="T8" s="349"/>
-      <c r="U8" s="349"/>
-      <c r="V8" s="349"/>
-      <c r="W8" s="349"/>
-      <c r="X8" s="349"/>
-      <c r="Y8" s="348" t="s">
+      <c r="L8" s="370"/>
+      <c r="M8" s="370"/>
+      <c r="N8" s="370"/>
+      <c r="O8" s="370"/>
+      <c r="P8" s="370"/>
+      <c r="Q8" s="370"/>
+      <c r="R8" s="370"/>
+      <c r="S8" s="370"/>
+      <c r="T8" s="370"/>
+      <c r="U8" s="370"/>
+      <c r="V8" s="370"/>
+      <c r="W8" s="370"/>
+      <c r="X8" s="370"/>
+      <c r="Y8" s="372" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="349"/>
-      <c r="AA8" s="349"/>
-      <c r="AB8" s="349"/>
-      <c r="AC8" s="349"/>
-      <c r="AD8" s="349"/>
-      <c r="AE8" s="349"/>
-      <c r="AF8" s="349"/>
-      <c r="AG8" s="349"/>
-      <c r="AH8" s="349"/>
-      <c r="AI8" s="349"/>
-      <c r="AJ8" s="349"/>
-      <c r="AK8" s="349"/>
-      <c r="AL8" s="349"/>
-      <c r="AM8" s="349"/>
-      <c r="AN8" s="349"/>
-      <c r="AO8" s="350"/>
-      <c r="AP8" s="354" t="s">
+      <c r="Z8" s="370"/>
+      <c r="AA8" s="370"/>
+      <c r="AB8" s="370"/>
+      <c r="AC8" s="370"/>
+      <c r="AD8" s="370"/>
+      <c r="AE8" s="370"/>
+      <c r="AF8" s="370"/>
+      <c r="AG8" s="370"/>
+      <c r="AH8" s="370"/>
+      <c r="AI8" s="370"/>
+      <c r="AJ8" s="370"/>
+      <c r="AK8" s="370"/>
+      <c r="AL8" s="370"/>
+      <c r="AM8" s="370"/>
+      <c r="AN8" s="370"/>
+      <c r="AO8" s="373"/>
+      <c r="AP8" s="345" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="354" t="s">
+      <c r="AQ8" s="345" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="354" t="s">
+      <c r="AR8" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="354" t="s">
+      <c r="AS8" s="345" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="354" t="s">
+      <c r="AT8" s="345" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="354" t="s">
+      <c r="AU8" s="345" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="335" t="s">
+      <c r="AV8" s="332" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="340" t="s">
+      <c r="AW8" s="352" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="335" t="s">
+      <c r="AX8" s="332" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="355" t="s">
+      <c r="AY8" s="375" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="349"/>
-      <c r="BA8" s="349"/>
-      <c r="BB8" s="349"/>
-      <c r="BC8" s="349"/>
-      <c r="BD8" s="349"/>
-      <c r="BE8" s="349"/>
-      <c r="BF8" s="349"/>
-      <c r="BG8" s="349"/>
-      <c r="BH8" s="349"/>
-      <c r="BI8" s="349"/>
-      <c r="BJ8" s="349"/>
-      <c r="BK8" s="349"/>
-      <c r="BL8" s="349"/>
-      <c r="BM8" s="349"/>
-      <c r="BN8" s="349"/>
-      <c r="BO8" s="349"/>
-      <c r="BP8" s="349"/>
-      <c r="BQ8" s="350"/>
-      <c r="BR8" s="336" t="s">
+      <c r="AZ8" s="370"/>
+      <c r="BA8" s="370"/>
+      <c r="BB8" s="370"/>
+      <c r="BC8" s="370"/>
+      <c r="BD8" s="370"/>
+      <c r="BE8" s="370"/>
+      <c r="BF8" s="370"/>
+      <c r="BG8" s="370"/>
+      <c r="BH8" s="370"/>
+      <c r="BI8" s="370"/>
+      <c r="BJ8" s="370"/>
+      <c r="BK8" s="370"/>
+      <c r="BL8" s="370"/>
+      <c r="BM8" s="370"/>
+      <c r="BN8" s="370"/>
+      <c r="BO8" s="370"/>
+      <c r="BP8" s="370"/>
+      <c r="BQ8" s="373"/>
+      <c r="BR8" s="379" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="337"/>
-      <c r="BT8" s="335" t="s">
+      <c r="BS8" s="366"/>
+      <c r="BT8" s="332" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="332" t="s">
+      <c r="BU8" s="376" t="s">
         <v>28</v>
       </c>
-      <c r="BV8" s="434"/>
-      <c r="BW8" s="376" t="s">
+      <c r="BV8" s="329"/>
+      <c r="BW8" s="335" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="367" t="s">
+      <c r="BX8" s="356" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="368"/>
-      <c r="BZ8" s="368"/>
-      <c r="CA8" s="369"/>
-      <c r="CB8" s="338" t="s">
+      <c r="BY8" s="357"/>
+      <c r="BZ8" s="357"/>
+      <c r="CA8" s="358"/>
+      <c r="CB8" s="380" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="379" t="s">
+      <c r="CC8" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="379" t="s">
+      <c r="CD8" s="349" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="346"/>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="341"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="341"/>
-      <c r="K9" s="435" t="s">
+      <c r="A9" s="333"/>
+      <c r="B9" s="333"/>
+      <c r="C9" s="333"/>
+      <c r="D9" s="333"/>
+      <c r="E9" s="333"/>
+      <c r="F9" s="333"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="333"/>
+      <c r="I9" s="333"/>
+      <c r="J9" s="346"/>
+      <c r="K9" s="343" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="435" t="s">
+      <c r="L9" s="343" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="435" t="s">
+      <c r="M9" s="343" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="435" t="s">
+      <c r="N9" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="435" t="s">
+      <c r="O9" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="435" t="s">
+      <c r="P9" s="343" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="435" t="s">
+      <c r="Q9" s="343" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="435" t="s">
+      <c r="R9" s="343" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="435" t="s">
+      <c r="S9" s="343" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="435" t="s">
+      <c r="T9" s="343" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="435" t="s">
+      <c r="U9" s="343" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="356" t="s">
+      <c r="V9" s="365" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="337"/>
-      <c r="X9" s="435" t="s">
+      <c r="W9" s="366"/>
+      <c r="X9" s="343" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="329" t="s">
+      <c r="Y9" s="338" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="329" t="s">
+      <c r="Z9" s="338" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="329" t="s">
+      <c r="AA9" s="338" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="329" t="s">
+      <c r="AB9" s="338" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="329" t="s">
+      <c r="AC9" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="329" t="s">
+      <c r="AD9" s="338" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="329" t="s">
+      <c r="AE9" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="329" t="s">
+      <c r="AF9" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="329" t="s">
+      <c r="AG9" s="338" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="329" t="s">
+      <c r="AH9" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="329" t="s">
+      <c r="AI9" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="352" t="s">
+      <c r="AJ9" s="374" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="332" t="s">
+      <c r="AK9" s="376" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="340" t="s">
+      <c r="AL9" s="352" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="329" t="s">
+      <c r="AM9" s="338" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="335" t="s">
+      <c r="AN9" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="335" t="s">
+      <c r="AO9" s="332" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="341"/>
-      <c r="AQ9" s="341"/>
-      <c r="AR9" s="341"/>
-      <c r="AS9" s="341"/>
-      <c r="AT9" s="341"/>
-      <c r="AU9" s="341"/>
-      <c r="AV9" s="330"/>
-      <c r="AW9" s="341"/>
-      <c r="AX9" s="330"/>
-      <c r="AY9" s="343" t="s">
+      <c r="AP9" s="346"/>
+      <c r="AQ9" s="346"/>
+      <c r="AR9" s="346"/>
+      <c r="AS9" s="346"/>
+      <c r="AT9" s="346"/>
+      <c r="AU9" s="346"/>
+      <c r="AV9" s="333"/>
+      <c r="AW9" s="346"/>
+      <c r="AX9" s="333"/>
+      <c r="AY9" s="382" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="344"/>
-      <c r="BA9" s="344"/>
-      <c r="BB9" s="344"/>
-      <c r="BC9" s="344"/>
-      <c r="BD9" s="344"/>
-      <c r="BE9" s="344"/>
-      <c r="BF9" s="344"/>
-      <c r="BG9" s="344"/>
-      <c r="BH9" s="344"/>
-      <c r="BI9" s="344"/>
-      <c r="BJ9" s="344"/>
-      <c r="BK9" s="344"/>
-      <c r="BL9" s="345"/>
-      <c r="BM9" s="343" t="s">
+      <c r="AZ9" s="383"/>
+      <c r="BA9" s="383"/>
+      <c r="BB9" s="383"/>
+      <c r="BC9" s="383"/>
+      <c r="BD9" s="383"/>
+      <c r="BE9" s="383"/>
+      <c r="BF9" s="383"/>
+      <c r="BG9" s="383"/>
+      <c r="BH9" s="383"/>
+      <c r="BI9" s="383"/>
+      <c r="BJ9" s="383"/>
+      <c r="BK9" s="383"/>
+      <c r="BL9" s="384"/>
+      <c r="BM9" s="382" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="344"/>
-      <c r="BO9" s="344"/>
-      <c r="BP9" s="344"/>
-      <c r="BQ9" s="345"/>
-      <c r="BR9" s="436" t="s">
+      <c r="BN9" s="383"/>
+      <c r="BO9" s="383"/>
+      <c r="BP9" s="383"/>
+      <c r="BQ9" s="384"/>
+      <c r="BR9" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="436" t="s">
+      <c r="BS9" s="344" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="330"/>
-      <c r="BU9" s="333"/>
-      <c r="BV9" s="434"/>
-      <c r="BW9" s="377"/>
-      <c r="BX9" s="370"/>
-      <c r="BY9" s="371"/>
-      <c r="BZ9" s="371"/>
-      <c r="CA9" s="372"/>
-      <c r="CB9" s="330"/>
-      <c r="CC9" s="432"/>
-      <c r="CD9" s="432"/>
+      <c r="BT9" s="333"/>
+      <c r="BU9" s="377"/>
+      <c r="BV9" s="329"/>
+      <c r="BW9" s="336"/>
+      <c r="BX9" s="359"/>
+      <c r="BY9" s="360"/>
+      <c r="BZ9" s="360"/>
+      <c r="CA9" s="361"/>
+      <c r="CB9" s="333"/>
+      <c r="CC9" s="350"/>
+      <c r="CD9" s="350"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="346"/>
-      <c r="B10" s="330"/>
-      <c r="C10" s="330"/>
-      <c r="D10" s="330"/>
-      <c r="E10" s="330"/>
-      <c r="F10" s="330"/>
-      <c r="G10" s="341"/>
-      <c r="H10" s="330"/>
-      <c r="I10" s="330"/>
-      <c r="J10" s="341"/>
-      <c r="K10" s="330"/>
-      <c r="L10" s="330"/>
-      <c r="M10" s="330"/>
-      <c r="N10" s="330"/>
-      <c r="O10" s="330"/>
-      <c r="P10" s="330"/>
-      <c r="Q10" s="330"/>
-      <c r="R10" s="330"/>
-      <c r="S10" s="330"/>
-      <c r="T10" s="330"/>
-      <c r="U10" s="330"/>
-      <c r="V10" s="357"/>
-      <c r="W10" s="358"/>
-      <c r="X10" s="330"/>
-      <c r="Y10" s="330"/>
-      <c r="Z10" s="330"/>
-      <c r="AA10" s="330"/>
-      <c r="AB10" s="330"/>
-      <c r="AC10" s="330"/>
-      <c r="AD10" s="330"/>
-      <c r="AE10" s="330"/>
-      <c r="AF10" s="330"/>
-      <c r="AG10" s="330"/>
-      <c r="AH10" s="330"/>
-      <c r="AI10" s="330"/>
-      <c r="AJ10" s="341"/>
-      <c r="AK10" s="333"/>
-      <c r="AL10" s="341"/>
-      <c r="AM10" s="330"/>
-      <c r="AN10" s="330"/>
-      <c r="AO10" s="330"/>
-      <c r="AP10" s="341"/>
-      <c r="AQ10" s="341"/>
-      <c r="AR10" s="341"/>
-      <c r="AS10" s="341"/>
-      <c r="AT10" s="341"/>
-      <c r="AU10" s="341"/>
-      <c r="AV10" s="330"/>
-      <c r="AW10" s="341"/>
-      <c r="AX10" s="330"/>
+      <c r="A10" s="333"/>
+      <c r="B10" s="333"/>
+      <c r="C10" s="333"/>
+      <c r="D10" s="333"/>
+      <c r="E10" s="333"/>
+      <c r="F10" s="333"/>
+      <c r="G10" s="346"/>
+      <c r="H10" s="333"/>
+      <c r="I10" s="333"/>
+      <c r="J10" s="346"/>
+      <c r="K10" s="333"/>
+      <c r="L10" s="333"/>
+      <c r="M10" s="333"/>
+      <c r="N10" s="333"/>
+      <c r="O10" s="333"/>
+      <c r="P10" s="333"/>
+      <c r="Q10" s="333"/>
+      <c r="R10" s="333"/>
+      <c r="S10" s="333"/>
+      <c r="T10" s="333"/>
+      <c r="U10" s="333"/>
+      <c r="V10" s="367"/>
+      <c r="W10" s="368"/>
+      <c r="X10" s="333"/>
+      <c r="Y10" s="333"/>
+      <c r="Z10" s="333"/>
+      <c r="AA10" s="333"/>
+      <c r="AB10" s="333"/>
+      <c r="AC10" s="333"/>
+      <c r="AD10" s="333"/>
+      <c r="AE10" s="333"/>
+      <c r="AF10" s="333"/>
+      <c r="AG10" s="333"/>
+      <c r="AH10" s="333"/>
+      <c r="AI10" s="333"/>
+      <c r="AJ10" s="346"/>
+      <c r="AK10" s="377"/>
+      <c r="AL10" s="346"/>
+      <c r="AM10" s="333"/>
+      <c r="AN10" s="333"/>
+      <c r="AO10" s="333"/>
+      <c r="AP10" s="346"/>
+      <c r="AQ10" s="346"/>
+      <c r="AR10" s="346"/>
+      <c r="AS10" s="346"/>
+      <c r="AT10" s="346"/>
+      <c r="AU10" s="346"/>
+      <c r="AV10" s="333"/>
+      <c r="AW10" s="346"/>
+      <c r="AX10" s="333"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8599,67 +8596,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="365" t="s">
+      <c r="BB10" s="354" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="359" t="s">
+      <c r="BC10" s="341" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="359" t="s">
+      <c r="BD10" s="341" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="351" t="s">
+      <c r="BE10" s="340" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="351" t="s">
+      <c r="BF10" s="340" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="351" t="s">
+      <c r="BG10" s="340" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="359" t="s">
+      <c r="BH10" s="341" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="359" t="s">
+      <c r="BI10" s="341" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="351" t="s">
+      <c r="BJ10" s="340" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="351" t="s">
+      <c r="BK10" s="340" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="335" t="s">
+      <c r="BL10" s="332" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="359" t="s">
+      <c r="BM10" s="341" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="340" t="s">
+      <c r="BN10" s="352" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="359" t="s">
+      <c r="BO10" s="341" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="340" t="s">
+      <c r="BP10" s="352" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="340" t="s">
+      <c r="BQ10" s="352" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="330"/>
-      <c r="BS10" s="330"/>
-      <c r="BT10" s="330"/>
-      <c r="BU10" s="333"/>
-      <c r="BV10" s="434"/>
-      <c r="BW10" s="377"/>
-      <c r="BX10" s="373"/>
-      <c r="BY10" s="374"/>
-      <c r="BZ10" s="374"/>
-      <c r="CA10" s="375"/>
-      <c r="CB10" s="330"/>
-      <c r="CC10" s="432"/>
-      <c r="CD10" s="432"/>
+      <c r="BR10" s="333"/>
+      <c r="BS10" s="333"/>
+      <c r="BT10" s="333"/>
+      <c r="BU10" s="377"/>
+      <c r="BV10" s="329"/>
+      <c r="BW10" s="336"/>
+      <c r="BX10" s="362"/>
+      <c r="BY10" s="363"/>
+      <c r="BZ10" s="363"/>
+      <c r="CA10" s="364"/>
+      <c r="CB10" s="333"/>
+      <c r="CC10" s="350"/>
+      <c r="CD10" s="350"/>
       <c r="CE10" s="319" t="s">
         <v>3</v>
       </c>
@@ -8667,91 +8664,91 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="347"/>
-      <c r="B11" s="331"/>
-      <c r="C11" s="331"/>
-      <c r="D11" s="331"/>
-      <c r="E11" s="331"/>
-      <c r="F11" s="331"/>
+      <c r="A11" s="334"/>
+      <c r="B11" s="334"/>
+      <c r="C11" s="334"/>
+      <c r="D11" s="334"/>
+      <c r="E11" s="334"/>
+      <c r="F11" s="334"/>
       <c r="G11" s="342"/>
-      <c r="H11" s="331"/>
-      <c r="I11" s="331"/>
+      <c r="H11" s="334"/>
+      <c r="I11" s="334"/>
       <c r="J11" s="342"/>
-      <c r="K11" s="331"/>
-      <c r="L11" s="331"/>
-      <c r="M11" s="331"/>
-      <c r="N11" s="331"/>
-      <c r="O11" s="331"/>
-      <c r="P11" s="331"/>
-      <c r="Q11" s="331"/>
-      <c r="R11" s="331"/>
-      <c r="S11" s="331"/>
-      <c r="T11" s="331"/>
-      <c r="U11" s="331"/>
-      <c r="V11" s="437" t="s">
+      <c r="K11" s="334"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="334"/>
+      <c r="N11" s="334"/>
+      <c r="O11" s="334"/>
+      <c r="P11" s="334"/>
+      <c r="Q11" s="334"/>
+      <c r="R11" s="334"/>
+      <c r="S11" s="334"/>
+      <c r="T11" s="334"/>
+      <c r="U11" s="334"/>
+      <c r="V11" s="330" t="s">
         <v>86</v>
       </c>
-      <c r="W11" s="437" t="s">
+      <c r="W11" s="330" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="331"/>
-      <c r="Y11" s="331"/>
-      <c r="Z11" s="331"/>
-      <c r="AA11" s="331"/>
-      <c r="AB11" s="331"/>
-      <c r="AC11" s="331"/>
-      <c r="AD11" s="331"/>
-      <c r="AE11" s="331"/>
-      <c r="AF11" s="331"/>
-      <c r="AG11" s="331"/>
-      <c r="AH11" s="331"/>
-      <c r="AI11" s="331"/>
+      <c r="X11" s="334"/>
+      <c r="Y11" s="334"/>
+      <c r="Z11" s="334"/>
+      <c r="AA11" s="334"/>
+      <c r="AB11" s="334"/>
+      <c r="AC11" s="334"/>
+      <c r="AD11" s="334"/>
+      <c r="AE11" s="334"/>
+      <c r="AF11" s="334"/>
+      <c r="AG11" s="334"/>
+      <c r="AH11" s="334"/>
+      <c r="AI11" s="334"/>
       <c r="AJ11" s="342"/>
-      <c r="AK11" s="334"/>
+      <c r="AK11" s="378"/>
       <c r="AL11" s="342"/>
-      <c r="AM11" s="331"/>
-      <c r="AN11" s="331"/>
-      <c r="AO11" s="331"/>
+      <c r="AM11" s="334"/>
+      <c r="AN11" s="334"/>
+      <c r="AO11" s="334"/>
       <c r="AP11" s="342"/>
       <c r="AQ11" s="342"/>
       <c r="AR11" s="342"/>
       <c r="AS11" s="342"/>
       <c r="AT11" s="342"/>
       <c r="AU11" s="342"/>
-      <c r="AV11" s="331"/>
+      <c r="AV11" s="334"/>
       <c r="AW11" s="342"/>
-      <c r="AX11" s="331"/>
-      <c r="AY11" s="438" t="s">
+      <c r="AX11" s="334"/>
+      <c r="AY11" s="331" t="s">
         <v>88</v>
       </c>
-      <c r="AZ11" s="438" t="s">
+      <c r="AZ11" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="BA11" s="438" t="s">
+      <c r="BA11" s="331" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="331"/>
+      <c r="BB11" s="334"/>
       <c r="BC11" s="342"/>
       <c r="BD11" s="342"/>
-      <c r="BE11" s="331"/>
-      <c r="BF11" s="331"/>
-      <c r="BG11" s="331"/>
+      <c r="BE11" s="334"/>
+      <c r="BF11" s="334"/>
+      <c r="BG11" s="334"/>
       <c r="BH11" s="342"/>
       <c r="BI11" s="342"/>
-      <c r="BJ11" s="331"/>
-      <c r="BK11" s="331"/>
-      <c r="BL11" s="331"/>
+      <c r="BJ11" s="334"/>
+      <c r="BK11" s="334"/>
+      <c r="BL11" s="334"/>
       <c r="BM11" s="342"/>
       <c r="BN11" s="342"/>
       <c r="BO11" s="342"/>
       <c r="BP11" s="342"/>
       <c r="BQ11" s="342"/>
-      <c r="BR11" s="331"/>
-      <c r="BS11" s="331"/>
-      <c r="BT11" s="331"/>
-      <c r="BU11" s="334"/>
-      <c r="BV11" s="434"/>
-      <c r="BW11" s="378"/>
+      <c r="BR11" s="334"/>
+      <c r="BS11" s="334"/>
+      <c r="BT11" s="334"/>
+      <c r="BU11" s="378"/>
+      <c r="BV11" s="329"/>
+      <c r="BW11" s="337"/>
       <c r="BX11" s="327" t="s">
         <v>91</v>
       </c>
@@ -8764,9 +8761,9 @@
       <c r="CA11" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="339"/>
-      <c r="CC11" s="433"/>
-      <c r="CD11" s="433"/>
+      <c r="CB11" s="381"/>
+      <c r="CC11" s="351"/>
+      <c r="CD11" s="351"/>
       <c r="CE11" s="318">
         <v>26</v>
       </c>
@@ -9389,7 +9386,6 @@
     </row>
     <row r="15" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A15" s="270">
-        <f>IF(B15=0,"",COUNTA($B$15:(B15)))</f>
         <v>1</v>
       </c>
       <c r="B15" s="271">
@@ -9633,7 +9629,6 @@
     </row>
     <row r="16" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A16" s="244">
-        <f>IF(B16=0,"",COUNTA($B$15:(B16)))</f>
         <v>2</v>
       </c>
       <c r="B16" s="245">
@@ -9877,7 +9872,6 @@
     </row>
     <row r="17" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A17" s="244">
-        <f>IF(B17=0,"",COUNTA($B$15:(B17)))</f>
         <v>3</v>
       </c>
       <c r="B17" s="257" t="s">
@@ -10121,7 +10115,6 @@
     </row>
     <row r="18" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A18" s="244">
-        <f>IF(B18=0,"",COUNTA($B$15:(B18)))</f>
         <v>4</v>
       </c>
       <c r="B18" s="245">
@@ -10365,7 +10358,6 @@
     </row>
     <row r="19" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A19" s="244">
-        <f>IF(B19=0,"",COUNTA($B$15:(B19)))</f>
         <v>5</v>
       </c>
       <c r="B19" s="257" t="s">
@@ -10609,7 +10601,6 @@
     </row>
     <row r="20" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A20" s="244">
-        <f>IF(B20=0,"",COUNTA($B$15:(B20)))</f>
         <v>6</v>
       </c>
       <c r="B20" s="245">
@@ -10853,7 +10844,6 @@
     </row>
     <row r="21" spans="1:87" s="256" customFormat="1" ht="30.5" customHeight="1">
       <c r="A21" s="244">
-        <f>IF(B21=0,"",COUNTA($B$15:(B21)))</f>
         <v>7</v>
       </c>
       <c r="B21" s="257" t="s">
@@ -11233,21 +11223,56 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="T9:T11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="BW3:CB6"/>
     <mergeCell ref="CC8:CC11"/>
@@ -11264,57 +11289,22 @@
     <mergeCell ref="O9:O11"/>
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11523,87 +11513,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="408"/>
-      <c r="B3" s="399"/>
-      <c r="C3" s="399"/>
-      <c r="D3" s="399"/>
-      <c r="E3" s="399"/>
-      <c r="F3" s="399"/>
-      <c r="G3" s="399"/>
-      <c r="H3" s="399"/>
-      <c r="I3" s="399"/>
-      <c r="J3" s="399"/>
-      <c r="K3" s="399"/>
-      <c r="L3" s="399"/>
-      <c r="M3" s="399"/>
-      <c r="N3" s="399"/>
-      <c r="O3" s="399"/>
-      <c r="P3" s="399"/>
-      <c r="Q3" s="399"/>
-      <c r="R3" s="399"/>
-      <c r="S3" s="399"/>
-      <c r="T3" s="399"/>
-      <c r="U3" s="399"/>
-      <c r="V3" s="399"/>
-      <c r="W3" s="399"/>
-      <c r="X3" s="399"/>
-      <c r="Y3" s="399"/>
-      <c r="Z3" s="399"/>
-      <c r="AA3" s="399"/>
-      <c r="AB3" s="399"/>
-      <c r="AC3" s="399"/>
-      <c r="AD3" s="399"/>
-      <c r="AE3" s="399"/>
-      <c r="AF3" s="399"/>
-      <c r="AG3" s="399"/>
-      <c r="AH3" s="399"/>
-      <c r="AI3" s="399"/>
-      <c r="AJ3" s="399"/>
-      <c r="AK3" s="399"/>
-      <c r="AL3" s="399"/>
-      <c r="AM3" s="399"/>
-      <c r="AN3" s="399"/>
-      <c r="AO3" s="399"/>
-      <c r="AP3" s="399"/>
-      <c r="AQ3" s="399"/>
-      <c r="AR3" s="399"/>
-      <c r="AS3" s="399"/>
-      <c r="AT3" s="399"/>
-      <c r="AU3" s="399"/>
-      <c r="AV3" s="399"/>
-      <c r="AW3" s="399"/>
-      <c r="AX3" s="399"/>
-      <c r="AY3" s="399"/>
-      <c r="AZ3" s="399"/>
-      <c r="BA3" s="399"/>
-      <c r="BB3" s="399"/>
-      <c r="BC3" s="399"/>
-      <c r="BD3" s="399"/>
-      <c r="BE3" s="399"/>
-      <c r="BF3" s="399"/>
-      <c r="BG3" s="399"/>
-      <c r="BH3" s="399"/>
-      <c r="BI3" s="399"/>
-      <c r="BJ3" s="399"/>
-      <c r="BK3" s="399"/>
-      <c r="BL3" s="399"/>
-      <c r="BM3" s="399"/>
-      <c r="BN3" s="399"/>
-      <c r="BO3" s="399"/>
-      <c r="BP3" s="399"/>
-      <c r="BQ3" s="399"/>
-      <c r="BR3" s="399"/>
-      <c r="BS3" s="399"/>
-      <c r="BT3" s="399"/>
-      <c r="BU3" s="399"/>
-      <c r="BW3" s="398" t="s">
+      <c r="A3" s="417"/>
+      <c r="B3" s="406"/>
+      <c r="C3" s="406"/>
+      <c r="D3" s="406"/>
+      <c r="E3" s="406"/>
+      <c r="F3" s="406"/>
+      <c r="G3" s="406"/>
+      <c r="H3" s="406"/>
+      <c r="I3" s="406"/>
+      <c r="J3" s="406"/>
+      <c r="K3" s="406"/>
+      <c r="L3" s="406"/>
+      <c r="M3" s="406"/>
+      <c r="N3" s="406"/>
+      <c r="O3" s="406"/>
+      <c r="P3" s="406"/>
+      <c r="Q3" s="406"/>
+      <c r="R3" s="406"/>
+      <c r="S3" s="406"/>
+      <c r="T3" s="406"/>
+      <c r="U3" s="406"/>
+      <c r="V3" s="406"/>
+      <c r="W3" s="406"/>
+      <c r="X3" s="406"/>
+      <c r="Y3" s="406"/>
+      <c r="Z3" s="406"/>
+      <c r="AA3" s="406"/>
+      <c r="AB3" s="406"/>
+      <c r="AC3" s="406"/>
+      <c r="AD3" s="406"/>
+      <c r="AE3" s="406"/>
+      <c r="AF3" s="406"/>
+      <c r="AG3" s="406"/>
+      <c r="AH3" s="406"/>
+      <c r="AI3" s="406"/>
+      <c r="AJ3" s="406"/>
+      <c r="AK3" s="406"/>
+      <c r="AL3" s="406"/>
+      <c r="AM3" s="406"/>
+      <c r="AN3" s="406"/>
+      <c r="AO3" s="406"/>
+      <c r="AP3" s="406"/>
+      <c r="AQ3" s="406"/>
+      <c r="AR3" s="406"/>
+      <c r="AS3" s="406"/>
+      <c r="AT3" s="406"/>
+      <c r="AU3" s="406"/>
+      <c r="AV3" s="406"/>
+      <c r="AW3" s="406"/>
+      <c r="AX3" s="406"/>
+      <c r="AY3" s="406"/>
+      <c r="AZ3" s="406"/>
+      <c r="BA3" s="406"/>
+      <c r="BB3" s="406"/>
+      <c r="BC3" s="406"/>
+      <c r="BD3" s="406"/>
+      <c r="BE3" s="406"/>
+      <c r="BF3" s="406"/>
+      <c r="BG3" s="406"/>
+      <c r="BH3" s="406"/>
+      <c r="BI3" s="406"/>
+      <c r="BJ3" s="406"/>
+      <c r="BK3" s="406"/>
+      <c r="BL3" s="406"/>
+      <c r="BM3" s="406"/>
+      <c r="BN3" s="406"/>
+      <c r="BO3" s="406"/>
+      <c r="BP3" s="406"/>
+      <c r="BQ3" s="406"/>
+      <c r="BR3" s="406"/>
+      <c r="BS3" s="406"/>
+      <c r="BT3" s="406"/>
+      <c r="BU3" s="406"/>
+      <c r="BW3" s="405" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="399"/>
-      <c r="BY3" s="399"/>
-      <c r="BZ3" s="399"/>
-      <c r="CA3" s="399"/>
-      <c r="CB3" s="399"/>
+      <c r="BX3" s="406"/>
+      <c r="BY3" s="406"/>
+      <c r="BZ3" s="406"/>
+      <c r="CA3" s="406"/>
+      <c r="CB3" s="406"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11686,364 +11676,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="399"/>
-      <c r="BX4" s="399"/>
-      <c r="BY4" s="399"/>
-      <c r="BZ4" s="399"/>
-      <c r="CA4" s="399"/>
-      <c r="CB4" s="399"/>
+      <c r="BW4" s="406"/>
+      <c r="BX4" s="406"/>
+      <c r="BY4" s="406"/>
+      <c r="BZ4" s="406"/>
+      <c r="CA4" s="406"/>
+      <c r="CB4" s="406"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="411" t="s">
+      <c r="A5" s="393" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="410" t="s">
+      <c r="B5" s="404" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="384" t="s">
+      <c r="C5" s="392" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="409" t="s">
+      <c r="D5" s="399" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="409" t="s">
+      <c r="E5" s="399" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="384" t="s">
+      <c r="F5" s="392" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="384" t="s">
+      <c r="G5" s="392" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="335" t="s">
+      <c r="H5" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="335" t="s">
+      <c r="I5" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="384" t="s">
+      <c r="J5" s="392" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="413" t="s">
+      <c r="K5" s="397" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="395"/>
-      <c r="M5" s="395"/>
-      <c r="N5" s="395"/>
-      <c r="O5" s="395"/>
-      <c r="P5" s="395"/>
-      <c r="Q5" s="395"/>
-      <c r="R5" s="395"/>
-      <c r="S5" s="395"/>
-      <c r="T5" s="395"/>
-      <c r="U5" s="395"/>
-      <c r="V5" s="395"/>
-      <c r="W5" s="395"/>
-      <c r="X5" s="395"/>
-      <c r="Y5" s="384" t="s">
+      <c r="L5" s="389"/>
+      <c r="M5" s="389"/>
+      <c r="N5" s="389"/>
+      <c r="O5" s="389"/>
+      <c r="P5" s="389"/>
+      <c r="Q5" s="389"/>
+      <c r="R5" s="389"/>
+      <c r="S5" s="389"/>
+      <c r="T5" s="389"/>
+      <c r="U5" s="389"/>
+      <c r="V5" s="389"/>
+      <c r="W5" s="389"/>
+      <c r="X5" s="389"/>
+      <c r="Y5" s="392" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="395"/>
-      <c r="AA5" s="395"/>
-      <c r="AB5" s="395"/>
-      <c r="AC5" s="395"/>
-      <c r="AD5" s="395"/>
-      <c r="AE5" s="395"/>
-      <c r="AF5" s="395"/>
-      <c r="AG5" s="395"/>
-      <c r="AH5" s="395"/>
-      <c r="AI5" s="395"/>
-      <c r="AJ5" s="395"/>
-      <c r="AK5" s="395"/>
-      <c r="AL5" s="395"/>
-      <c r="AM5" s="395"/>
-      <c r="AN5" s="395"/>
-      <c r="AO5" s="396"/>
-      <c r="AP5" s="384" t="s">
+      <c r="Z5" s="389"/>
+      <c r="AA5" s="389"/>
+      <c r="AB5" s="389"/>
+      <c r="AC5" s="389"/>
+      <c r="AD5" s="389"/>
+      <c r="AE5" s="389"/>
+      <c r="AF5" s="389"/>
+      <c r="AG5" s="389"/>
+      <c r="AH5" s="389"/>
+      <c r="AI5" s="389"/>
+      <c r="AJ5" s="389"/>
+      <c r="AK5" s="389"/>
+      <c r="AL5" s="389"/>
+      <c r="AM5" s="389"/>
+      <c r="AN5" s="389"/>
+      <c r="AO5" s="390"/>
+      <c r="AP5" s="392" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="384" t="s">
+      <c r="AQ5" s="392" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="384" t="s">
+      <c r="AR5" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="384" t="s">
+      <c r="AS5" s="392" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="384" t="s">
+      <c r="AT5" s="392" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="384" t="s">
+      <c r="AU5" s="392" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="384" t="s">
+      <c r="AV5" s="392" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="384" t="s">
+      <c r="AW5" s="392" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="384" t="s">
+      <c r="AX5" s="392" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="394" t="s">
+      <c r="AY5" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="395"/>
-      <c r="BA5" s="395"/>
-      <c r="BB5" s="395"/>
-      <c r="BC5" s="395"/>
-      <c r="BD5" s="395"/>
-      <c r="BE5" s="395"/>
-      <c r="BF5" s="395"/>
-      <c r="BG5" s="395"/>
-      <c r="BH5" s="395"/>
-      <c r="BI5" s="395"/>
-      <c r="BJ5" s="395"/>
-      <c r="BK5" s="395"/>
-      <c r="BL5" s="395"/>
-      <c r="BM5" s="395"/>
-      <c r="BN5" s="395"/>
-      <c r="BO5" s="395"/>
-      <c r="BP5" s="395"/>
-      <c r="BQ5" s="396"/>
-      <c r="BR5" s="400" t="s">
+      <c r="AZ5" s="389"/>
+      <c r="BA5" s="389"/>
+      <c r="BB5" s="389"/>
+      <c r="BC5" s="389"/>
+      <c r="BD5" s="389"/>
+      <c r="BE5" s="389"/>
+      <c r="BF5" s="389"/>
+      <c r="BG5" s="389"/>
+      <c r="BH5" s="389"/>
+      <c r="BI5" s="389"/>
+      <c r="BJ5" s="389"/>
+      <c r="BK5" s="389"/>
+      <c r="BL5" s="389"/>
+      <c r="BM5" s="389"/>
+      <c r="BN5" s="389"/>
+      <c r="BO5" s="389"/>
+      <c r="BP5" s="389"/>
+      <c r="BQ5" s="390"/>
+      <c r="BR5" s="408" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="401"/>
-      <c r="BT5" s="394" t="s">
+      <c r="BS5" s="402"/>
+      <c r="BT5" s="388" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="388" t="s">
+      <c r="BU5" s="419" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="391" t="s">
+      <c r="BW5" s="420" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="402" t="s">
+      <c r="BX5" s="409" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="403"/>
-      <c r="BZ5" s="403"/>
-      <c r="CA5" s="401"/>
-      <c r="CB5" s="397" t="s">
+      <c r="BY5" s="410"/>
+      <c r="BZ5" s="410"/>
+      <c r="CA5" s="402"/>
+      <c r="CB5" s="421" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="379" t="s">
+      <c r="CC5" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="379" t="s">
+      <c r="CD5" s="349" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="380"/>
-      <c r="B6" s="380"/>
-      <c r="C6" s="380"/>
-      <c r="D6" s="380"/>
-      <c r="E6" s="380"/>
-      <c r="F6" s="380"/>
-      <c r="G6" s="380"/>
-      <c r="H6" s="380"/>
-      <c r="I6" s="380"/>
-      <c r="J6" s="380"/>
-      <c r="K6" s="385" t="s">
+      <c r="A6" s="386"/>
+      <c r="B6" s="386"/>
+      <c r="C6" s="386"/>
+      <c r="D6" s="386"/>
+      <c r="E6" s="386"/>
+      <c r="F6" s="386"/>
+      <c r="G6" s="386"/>
+      <c r="H6" s="386"/>
+      <c r="I6" s="386"/>
+      <c r="J6" s="386"/>
+      <c r="K6" s="400" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="385" t="s">
+      <c r="L6" s="400" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="385" t="s">
+      <c r="M6" s="400" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="385" t="s">
+      <c r="N6" s="400" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="385" t="s">
+      <c r="O6" s="400" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="385" t="s">
+      <c r="P6" s="400" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="385" t="s">
+      <c r="Q6" s="400" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="385" t="s">
+      <c r="R6" s="400" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="385" t="s">
+      <c r="S6" s="400" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="385" t="s">
+      <c r="T6" s="400" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="385" t="s">
+      <c r="U6" s="400" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="415" t="s">
+      <c r="V6" s="401" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="401"/>
-      <c r="X6" s="385" t="s">
+      <c r="W6" s="402"/>
+      <c r="X6" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="384" t="s">
+      <c r="Y6" s="392" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="384" t="s">
+      <c r="Z6" s="392" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="384" t="s">
+      <c r="AA6" s="392" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="384" t="s">
+      <c r="AB6" s="392" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="335" t="s">
+      <c r="AC6" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="335" t="s">
+      <c r="AD6" s="332" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="335" t="s">
+      <c r="AE6" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="335" t="s">
+      <c r="AF6" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="384" t="s">
+      <c r="AG6" s="392" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="335" t="s">
+      <c r="AH6" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="335" t="s">
+      <c r="AI6" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="384" t="s">
+      <c r="AJ6" s="392" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="412" t="s">
+      <c r="AK6" s="394" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="384" t="s">
+      <c r="AL6" s="392" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="384" t="s">
+      <c r="AM6" s="392" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="414" t="s">
+      <c r="AN6" s="398" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="384" t="s">
+      <c r="AO6" s="392" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="380"/>
-      <c r="AQ6" s="380"/>
-      <c r="AR6" s="380"/>
-      <c r="AS6" s="380"/>
-      <c r="AT6" s="380"/>
-      <c r="AU6" s="380"/>
-      <c r="AV6" s="380"/>
-      <c r="AW6" s="380"/>
-      <c r="AX6" s="380"/>
-      <c r="AY6" s="394" t="s">
+      <c r="AP6" s="386"/>
+      <c r="AQ6" s="386"/>
+      <c r="AR6" s="386"/>
+      <c r="AS6" s="386"/>
+      <c r="AT6" s="386"/>
+      <c r="AU6" s="386"/>
+      <c r="AV6" s="386"/>
+      <c r="AW6" s="386"/>
+      <c r="AX6" s="386"/>
+      <c r="AY6" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="395"/>
-      <c r="BA6" s="395"/>
-      <c r="BB6" s="395"/>
-      <c r="BC6" s="395"/>
-      <c r="BD6" s="395"/>
-      <c r="BE6" s="395"/>
-      <c r="BF6" s="395"/>
-      <c r="BG6" s="395"/>
-      <c r="BH6" s="395"/>
-      <c r="BI6" s="395"/>
-      <c r="BJ6" s="395"/>
-      <c r="BK6" s="395"/>
-      <c r="BL6" s="396"/>
-      <c r="BM6" s="394" t="s">
+      <c r="AZ6" s="389"/>
+      <c r="BA6" s="389"/>
+      <c r="BB6" s="389"/>
+      <c r="BC6" s="389"/>
+      <c r="BD6" s="389"/>
+      <c r="BE6" s="389"/>
+      <c r="BF6" s="389"/>
+      <c r="BG6" s="389"/>
+      <c r="BH6" s="389"/>
+      <c r="BI6" s="389"/>
+      <c r="BJ6" s="389"/>
+      <c r="BK6" s="389"/>
+      <c r="BL6" s="390"/>
+      <c r="BM6" s="388" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="395"/>
-      <c r="BO6" s="395"/>
-      <c r="BP6" s="395"/>
-      <c r="BQ6" s="396"/>
-      <c r="BR6" s="382" t="s">
+      <c r="BN6" s="389"/>
+      <c r="BO6" s="389"/>
+      <c r="BP6" s="389"/>
+      <c r="BQ6" s="390"/>
+      <c r="BR6" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="382" t="s">
+      <c r="BS6" s="385" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="380"/>
-      <c r="BU6" s="389"/>
-      <c r="BW6" s="392"/>
-      <c r="BX6" s="389"/>
-      <c r="BY6" s="404"/>
-      <c r="BZ6" s="404"/>
-      <c r="CA6" s="392"/>
-      <c r="CB6" s="380"/>
-      <c r="CC6" s="380"/>
-      <c r="CD6" s="380"/>
+      <c r="BT6" s="386"/>
+      <c r="BU6" s="395"/>
+      <c r="BW6" s="412"/>
+      <c r="BX6" s="395"/>
+      <c r="BY6" s="411"/>
+      <c r="BZ6" s="411"/>
+      <c r="CA6" s="412"/>
+      <c r="CB6" s="386"/>
+      <c r="CC6" s="386"/>
+      <c r="CD6" s="386"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="380"/>
-      <c r="B7" s="380"/>
-      <c r="C7" s="380"/>
-      <c r="D7" s="380"/>
-      <c r="E7" s="380"/>
-      <c r="F7" s="380"/>
-      <c r="G7" s="380"/>
-      <c r="H7" s="380"/>
-      <c r="I7" s="380"/>
-      <c r="J7" s="380"/>
-      <c r="K7" s="380"/>
-      <c r="L7" s="380"/>
-      <c r="M7" s="380"/>
-      <c r="N7" s="380"/>
-      <c r="O7" s="380"/>
-      <c r="P7" s="380"/>
-      <c r="Q7" s="380"/>
-      <c r="R7" s="380"/>
-      <c r="S7" s="380"/>
-      <c r="T7" s="380"/>
-      <c r="U7" s="380"/>
-      <c r="V7" s="390"/>
-      <c r="W7" s="416"/>
-      <c r="X7" s="380"/>
-      <c r="Y7" s="380"/>
-      <c r="Z7" s="380"/>
-      <c r="AA7" s="380"/>
-      <c r="AB7" s="380"/>
-      <c r="AC7" s="380"/>
-      <c r="AD7" s="380"/>
-      <c r="AE7" s="380"/>
-      <c r="AF7" s="380"/>
-      <c r="AG7" s="380"/>
-      <c r="AH7" s="380"/>
-      <c r="AI7" s="380"/>
-      <c r="AJ7" s="380"/>
-      <c r="AK7" s="389"/>
-      <c r="AL7" s="380"/>
-      <c r="AM7" s="380"/>
-      <c r="AN7" s="380"/>
-      <c r="AO7" s="380"/>
-      <c r="AP7" s="380"/>
-      <c r="AQ7" s="380"/>
-      <c r="AR7" s="380"/>
-      <c r="AS7" s="380"/>
-      <c r="AT7" s="380"/>
-      <c r="AU7" s="380"/>
-      <c r="AV7" s="380"/>
-      <c r="AW7" s="380"/>
-      <c r="AX7" s="380"/>
+      <c r="A7" s="386"/>
+      <c r="B7" s="386"/>
+      <c r="C7" s="386"/>
+      <c r="D7" s="386"/>
+      <c r="E7" s="386"/>
+      <c r="F7" s="386"/>
+      <c r="G7" s="386"/>
+      <c r="H7" s="386"/>
+      <c r="I7" s="386"/>
+      <c r="J7" s="386"/>
+      <c r="K7" s="386"/>
+      <c r="L7" s="386"/>
+      <c r="M7" s="386"/>
+      <c r="N7" s="386"/>
+      <c r="O7" s="386"/>
+      <c r="P7" s="386"/>
+      <c r="Q7" s="386"/>
+      <c r="R7" s="386"/>
+      <c r="S7" s="386"/>
+      <c r="T7" s="386"/>
+      <c r="U7" s="386"/>
+      <c r="V7" s="396"/>
+      <c r="W7" s="403"/>
+      <c r="X7" s="386"/>
+      <c r="Y7" s="386"/>
+      <c r="Z7" s="386"/>
+      <c r="AA7" s="386"/>
+      <c r="AB7" s="386"/>
+      <c r="AC7" s="386"/>
+      <c r="AD7" s="386"/>
+      <c r="AE7" s="386"/>
+      <c r="AF7" s="386"/>
+      <c r="AG7" s="386"/>
+      <c r="AH7" s="386"/>
+      <c r="AI7" s="386"/>
+      <c r="AJ7" s="386"/>
+      <c r="AK7" s="395"/>
+      <c r="AL7" s="386"/>
+      <c r="AM7" s="386"/>
+      <c r="AN7" s="386"/>
+      <c r="AO7" s="386"/>
+      <c r="AP7" s="386"/>
+      <c r="AQ7" s="386"/>
+      <c r="AR7" s="386"/>
+      <c r="AS7" s="386"/>
+      <c r="AT7" s="386"/>
+      <c r="AU7" s="386"/>
+      <c r="AV7" s="386"/>
+      <c r="AW7" s="386"/>
+      <c r="AX7" s="386"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12053,124 +12043,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="394" t="s">
+      <c r="BB7" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="386" t="s">
+      <c r="BC7" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="386" t="s">
+      <c r="BD7" s="391" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="407" t="s">
+      <c r="BE7" s="416" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="386" t="s">
+      <c r="BF7" s="391" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="386" t="s">
+      <c r="BG7" s="391" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="386" t="s">
+      <c r="BH7" s="391" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="386" t="s">
+      <c r="BI7" s="391" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="386" t="s">
+      <c r="BJ7" s="391" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="386" t="s">
+      <c r="BK7" s="391" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="387" t="s">
+      <c r="BL7" s="418" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="386" t="s">
+      <c r="BM7" s="391" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="394" t="s">
+      <c r="BN7" s="388" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="386" t="s">
+      <c r="BO7" s="391" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="394" t="s">
+      <c r="BP7" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="394" t="s">
+      <c r="BQ7" s="388" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="380"/>
-      <c r="BS7" s="380"/>
-      <c r="BT7" s="380"/>
-      <c r="BU7" s="389"/>
-      <c r="BW7" s="392"/>
-      <c r="BX7" s="405"/>
-      <c r="BY7" s="406"/>
-      <c r="BZ7" s="406"/>
-      <c r="CA7" s="393"/>
-      <c r="CB7" s="380"/>
-      <c r="CC7" s="380"/>
-      <c r="CD7" s="380"/>
+      <c r="BR7" s="386"/>
+      <c r="BS7" s="386"/>
+      <c r="BT7" s="386"/>
+      <c r="BU7" s="395"/>
+      <c r="BW7" s="412"/>
+      <c r="BX7" s="413"/>
+      <c r="BY7" s="414"/>
+      <c r="BZ7" s="414"/>
+      <c r="CA7" s="415"/>
+      <c r="CB7" s="386"/>
+      <c r="CC7" s="386"/>
+      <c r="CD7" s="386"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="383"/>
-      <c r="B8" s="383"/>
-      <c r="C8" s="383"/>
-      <c r="D8" s="383"/>
-      <c r="E8" s="383"/>
-      <c r="F8" s="383"/>
-      <c r="G8" s="383"/>
-      <c r="H8" s="383"/>
-      <c r="I8" s="383"/>
-      <c r="J8" s="383"/>
-      <c r="K8" s="383"/>
-      <c r="L8" s="383"/>
-      <c r="M8" s="383"/>
-      <c r="N8" s="383"/>
-      <c r="O8" s="383"/>
-      <c r="P8" s="383"/>
-      <c r="Q8" s="383"/>
-      <c r="R8" s="383"/>
-      <c r="S8" s="383"/>
-      <c r="T8" s="383"/>
-      <c r="U8" s="383"/>
+      <c r="A8" s="387"/>
+      <c r="B8" s="387"/>
+      <c r="C8" s="387"/>
+      <c r="D8" s="387"/>
+      <c r="E8" s="387"/>
+      <c r="F8" s="387"/>
+      <c r="G8" s="387"/>
+      <c r="H8" s="387"/>
+      <c r="I8" s="387"/>
+      <c r="J8" s="387"/>
+      <c r="K8" s="387"/>
+      <c r="L8" s="387"/>
+      <c r="M8" s="387"/>
+      <c r="N8" s="387"/>
+      <c r="O8" s="387"/>
+      <c r="P8" s="387"/>
+      <c r="Q8" s="387"/>
+      <c r="R8" s="387"/>
+      <c r="S8" s="387"/>
+      <c r="T8" s="387"/>
+      <c r="U8" s="387"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="383"/>
-      <c r="Y8" s="383"/>
-      <c r="Z8" s="383"/>
-      <c r="AA8" s="383"/>
-      <c r="AB8" s="383"/>
-      <c r="AC8" s="383"/>
-      <c r="AD8" s="383"/>
-      <c r="AE8" s="383"/>
-      <c r="AF8" s="383"/>
-      <c r="AG8" s="383"/>
-      <c r="AH8" s="383"/>
-      <c r="AI8" s="383"/>
-      <c r="AJ8" s="383"/>
-      <c r="AK8" s="390"/>
-      <c r="AL8" s="383"/>
-      <c r="AM8" s="383"/>
-      <c r="AN8" s="383"/>
-      <c r="AO8" s="383"/>
-      <c r="AP8" s="383"/>
-      <c r="AQ8" s="383"/>
-      <c r="AR8" s="383"/>
-      <c r="AS8" s="383"/>
-      <c r="AT8" s="383"/>
-      <c r="AU8" s="383"/>
-      <c r="AV8" s="383"/>
-      <c r="AW8" s="383"/>
-      <c r="AX8" s="383"/>
+      <c r="X8" s="387"/>
+      <c r="Y8" s="387"/>
+      <c r="Z8" s="387"/>
+      <c r="AA8" s="387"/>
+      <c r="AB8" s="387"/>
+      <c r="AC8" s="387"/>
+      <c r="AD8" s="387"/>
+      <c r="AE8" s="387"/>
+      <c r="AF8" s="387"/>
+      <c r="AG8" s="387"/>
+      <c r="AH8" s="387"/>
+      <c r="AI8" s="387"/>
+      <c r="AJ8" s="387"/>
+      <c r="AK8" s="396"/>
+      <c r="AL8" s="387"/>
+      <c r="AM8" s="387"/>
+      <c r="AN8" s="387"/>
+      <c r="AO8" s="387"/>
+      <c r="AP8" s="387"/>
+      <c r="AQ8" s="387"/>
+      <c r="AR8" s="387"/>
+      <c r="AS8" s="387"/>
+      <c r="AT8" s="387"/>
+      <c r="AU8" s="387"/>
+      <c r="AV8" s="387"/>
+      <c r="AW8" s="387"/>
+      <c r="AX8" s="387"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12180,27 +12170,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="383"/>
-      <c r="BC8" s="383"/>
-      <c r="BD8" s="383"/>
-      <c r="BE8" s="383"/>
-      <c r="BF8" s="383"/>
-      <c r="BG8" s="383"/>
-      <c r="BH8" s="383"/>
-      <c r="BI8" s="383"/>
-      <c r="BJ8" s="383"/>
-      <c r="BK8" s="383"/>
-      <c r="BL8" s="383"/>
-      <c r="BM8" s="383"/>
-      <c r="BN8" s="383"/>
-      <c r="BO8" s="383"/>
-      <c r="BP8" s="383"/>
-      <c r="BQ8" s="383"/>
-      <c r="BR8" s="383"/>
-      <c r="BS8" s="383"/>
-      <c r="BT8" s="383"/>
-      <c r="BU8" s="390"/>
-      <c r="BW8" s="393"/>
+      <c r="BB8" s="387"/>
+      <c r="BC8" s="387"/>
+      <c r="BD8" s="387"/>
+      <c r="BE8" s="387"/>
+      <c r="BF8" s="387"/>
+      <c r="BG8" s="387"/>
+      <c r="BH8" s="387"/>
+      <c r="BI8" s="387"/>
+      <c r="BJ8" s="387"/>
+      <c r="BK8" s="387"/>
+      <c r="BL8" s="387"/>
+      <c r="BM8" s="387"/>
+      <c r="BN8" s="387"/>
+      <c r="BO8" s="387"/>
+      <c r="BP8" s="387"/>
+      <c r="BQ8" s="387"/>
+      <c r="BR8" s="387"/>
+      <c r="BS8" s="387"/>
+      <c r="BT8" s="387"/>
+      <c r="BU8" s="396"/>
+      <c r="BW8" s="415"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12213,9 +12203,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="381"/>
-      <c r="CC8" s="381"/>
-      <c r="CD8" s="381"/>
+      <c r="CB8" s="407"/>
+      <c r="CC8" s="407"/>
+      <c r="CD8" s="407"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14673,6 +14663,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="BS6:BS8"/>
     <mergeCell ref="BM6:BQ6"/>
     <mergeCell ref="AC6:AC8"/>
@@ -14689,72 +14745,6 @@
     <mergeCell ref="BD7:BD8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -14982,88 +14972,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="427"/>
-      <c r="B3" s="426"/>
-      <c r="C3" s="426"/>
-      <c r="D3" s="426"/>
-      <c r="E3" s="426"/>
-      <c r="F3" s="426"/>
-      <c r="G3" s="426"/>
-      <c r="H3" s="426"/>
-      <c r="I3" s="426"/>
-      <c r="J3" s="426"/>
-      <c r="K3" s="426"/>
-      <c r="L3" s="426"/>
-      <c r="M3" s="426"/>
-      <c r="N3" s="426"/>
-      <c r="O3" s="426"/>
-      <c r="P3" s="426"/>
-      <c r="Q3" s="426"/>
-      <c r="R3" s="426"/>
-      <c r="S3" s="426"/>
-      <c r="T3" s="426"/>
-      <c r="U3" s="426"/>
-      <c r="V3" s="426"/>
-      <c r="W3" s="426"/>
-      <c r="X3" s="426"/>
-      <c r="Y3" s="426"/>
-      <c r="Z3" s="426"/>
-      <c r="AA3" s="426"/>
-      <c r="AB3" s="426"/>
-      <c r="AC3" s="426"/>
-      <c r="AD3" s="426"/>
-      <c r="AE3" s="426"/>
-      <c r="AF3" s="426"/>
-      <c r="AG3" s="426"/>
-      <c r="AH3" s="426"/>
-      <c r="AI3" s="426"/>
-      <c r="AJ3" s="426"/>
-      <c r="AK3" s="426"/>
-      <c r="AL3" s="426"/>
-      <c r="AM3" s="426"/>
-      <c r="AN3" s="426"/>
-      <c r="AO3" s="426"/>
-      <c r="AP3" s="426"/>
-      <c r="AQ3" s="426"/>
-      <c r="AR3" s="426"/>
-      <c r="AS3" s="426"/>
-      <c r="AT3" s="426"/>
-      <c r="AU3" s="426"/>
-      <c r="AV3" s="426"/>
-      <c r="AW3" s="426"/>
-      <c r="AX3" s="426"/>
-      <c r="AY3" s="426"/>
-      <c r="AZ3" s="426"/>
-      <c r="BA3" s="426"/>
-      <c r="BB3" s="426"/>
-      <c r="BC3" s="426"/>
-      <c r="BD3" s="426"/>
-      <c r="BE3" s="426"/>
-      <c r="BF3" s="426"/>
-      <c r="BG3" s="426"/>
-      <c r="BH3" s="426"/>
-      <c r="BI3" s="426"/>
-      <c r="BJ3" s="426"/>
-      <c r="BK3" s="426"/>
-      <c r="BL3" s="426"/>
-      <c r="BM3" s="426"/>
-      <c r="BN3" s="426"/>
-      <c r="BO3" s="426"/>
-      <c r="BP3" s="426"/>
-      <c r="BQ3" s="426"/>
-      <c r="BR3" s="426"/>
-      <c r="BS3" s="426"/>
-      <c r="BT3" s="426"/>
-      <c r="BU3" s="426"/>
+      <c r="A3" s="432"/>
+      <c r="B3" s="431"/>
+      <c r="C3" s="431"/>
+      <c r="D3" s="431"/>
+      <c r="E3" s="431"/>
+      <c r="F3" s="431"/>
+      <c r="G3" s="431"/>
+      <c r="H3" s="431"/>
+      <c r="I3" s="431"/>
+      <c r="J3" s="431"/>
+      <c r="K3" s="431"/>
+      <c r="L3" s="431"/>
+      <c r="M3" s="431"/>
+      <c r="N3" s="431"/>
+      <c r="O3" s="431"/>
+      <c r="P3" s="431"/>
+      <c r="Q3" s="431"/>
+      <c r="R3" s="431"/>
+      <c r="S3" s="431"/>
+      <c r="T3" s="431"/>
+      <c r="U3" s="431"/>
+      <c r="V3" s="431"/>
+      <c r="W3" s="431"/>
+      <c r="X3" s="431"/>
+      <c r="Y3" s="431"/>
+      <c r="Z3" s="431"/>
+      <c r="AA3" s="431"/>
+      <c r="AB3" s="431"/>
+      <c r="AC3" s="431"/>
+      <c r="AD3" s="431"/>
+      <c r="AE3" s="431"/>
+      <c r="AF3" s="431"/>
+      <c r="AG3" s="431"/>
+      <c r="AH3" s="431"/>
+      <c r="AI3" s="431"/>
+      <c r="AJ3" s="431"/>
+      <c r="AK3" s="431"/>
+      <c r="AL3" s="431"/>
+      <c r="AM3" s="431"/>
+      <c r="AN3" s="431"/>
+      <c r="AO3" s="431"/>
+      <c r="AP3" s="431"/>
+      <c r="AQ3" s="431"/>
+      <c r="AR3" s="431"/>
+      <c r="AS3" s="431"/>
+      <c r="AT3" s="431"/>
+      <c r="AU3" s="431"/>
+      <c r="AV3" s="431"/>
+      <c r="AW3" s="431"/>
+      <c r="AX3" s="431"/>
+      <c r="AY3" s="431"/>
+      <c r="AZ3" s="431"/>
+      <c r="BA3" s="431"/>
+      <c r="BB3" s="431"/>
+      <c r="BC3" s="431"/>
+      <c r="BD3" s="431"/>
+      <c r="BE3" s="431"/>
+      <c r="BF3" s="431"/>
+      <c r="BG3" s="431"/>
+      <c r="BH3" s="431"/>
+      <c r="BI3" s="431"/>
+      <c r="BJ3" s="431"/>
+      <c r="BK3" s="431"/>
+      <c r="BL3" s="431"/>
+      <c r="BM3" s="431"/>
+      <c r="BN3" s="431"/>
+      <c r="BO3" s="431"/>
+      <c r="BP3" s="431"/>
+      <c r="BQ3" s="431"/>
+      <c r="BR3" s="431"/>
+      <c r="BS3" s="431"/>
+      <c r="BT3" s="431"/>
+      <c r="BU3" s="431"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="425" t="s">
+      <c r="BW3" s="430" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="426"/>
-      <c r="BY3" s="426"/>
-      <c r="BZ3" s="426"/>
-      <c r="CA3" s="426"/>
-      <c r="CB3" s="426"/>
+      <c r="BX3" s="431"/>
+      <c r="BY3" s="431"/>
+      <c r="BZ3" s="431"/>
+      <c r="CA3" s="431"/>
+      <c r="CB3" s="431"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15147,12 +15137,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="426"/>
-      <c r="BX4" s="426"/>
-      <c r="BY4" s="426"/>
-      <c r="BZ4" s="426"/>
-      <c r="CA4" s="426"/>
-      <c r="CB4" s="426"/>
+      <c r="BW4" s="431"/>
+      <c r="BX4" s="431"/>
+      <c r="BY4" s="431"/>
+      <c r="BZ4" s="431"/>
+      <c r="CA4" s="431"/>
+      <c r="CB4" s="431"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15230,12 +15220,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="363"/>
-      <c r="BX5" s="363"/>
-      <c r="BY5" s="363"/>
-      <c r="BZ5" s="363"/>
-      <c r="CA5" s="363"/>
-      <c r="CB5" s="363"/>
+      <c r="BW5" s="348"/>
+      <c r="BX5" s="348"/>
+      <c r="BY5" s="348"/>
+      <c r="BZ5" s="348"/>
+      <c r="CA5" s="348"/>
+      <c r="CB5" s="348"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15313,12 +15303,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="363"/>
-      <c r="BX6" s="363"/>
-      <c r="BY6" s="363"/>
-      <c r="BZ6" s="363"/>
-      <c r="CA6" s="363"/>
-      <c r="CB6" s="363"/>
+      <c r="BW6" s="348"/>
+      <c r="BX6" s="348"/>
+      <c r="BY6" s="348"/>
+      <c r="BZ6" s="348"/>
+      <c r="CA6" s="348"/>
+      <c r="CB6" s="348"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15406,358 +15396,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="411" t="s">
+      <c r="A8" s="393" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="410" t="s">
+      <c r="B8" s="404" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="384" t="s">
+      <c r="C8" s="392" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="409" t="s">
+      <c r="D8" s="399" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="409" t="s">
+      <c r="E8" s="399" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="429" t="s">
+      <c r="F8" s="428" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="418" t="s">
+      <c r="G8" s="425" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="423" t="s">
+      <c r="H8" s="371" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="423" t="s">
+      <c r="I8" s="371" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="418" t="s">
+      <c r="J8" s="425" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="430" t="s">
+      <c r="K8" s="429" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="395"/>
-      <c r="M8" s="395"/>
-      <c r="N8" s="395"/>
-      <c r="O8" s="395"/>
-      <c r="P8" s="395"/>
-      <c r="Q8" s="395"/>
-      <c r="R8" s="395"/>
-      <c r="S8" s="395"/>
-      <c r="T8" s="395"/>
-      <c r="U8" s="395"/>
-      <c r="V8" s="395"/>
-      <c r="W8" s="395"/>
-      <c r="X8" s="395"/>
-      <c r="Y8" s="418" t="s">
+      <c r="L8" s="389"/>
+      <c r="M8" s="389"/>
+      <c r="N8" s="389"/>
+      <c r="O8" s="389"/>
+      <c r="P8" s="389"/>
+      <c r="Q8" s="389"/>
+      <c r="R8" s="389"/>
+      <c r="S8" s="389"/>
+      <c r="T8" s="389"/>
+      <c r="U8" s="389"/>
+      <c r="V8" s="389"/>
+      <c r="W8" s="389"/>
+      <c r="X8" s="389"/>
+      <c r="Y8" s="425" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="395"/>
-      <c r="AA8" s="395"/>
-      <c r="AB8" s="395"/>
-      <c r="AC8" s="395"/>
-      <c r="AD8" s="395"/>
-      <c r="AE8" s="395"/>
-      <c r="AF8" s="395"/>
-      <c r="AG8" s="395"/>
-      <c r="AH8" s="395"/>
-      <c r="AI8" s="395"/>
-      <c r="AJ8" s="395"/>
-      <c r="AK8" s="395"/>
-      <c r="AL8" s="395"/>
-      <c r="AM8" s="395"/>
-      <c r="AN8" s="395"/>
-      <c r="AO8" s="396"/>
-      <c r="AP8" s="418" t="s">
+      <c r="Z8" s="389"/>
+      <c r="AA8" s="389"/>
+      <c r="AB8" s="389"/>
+      <c r="AC8" s="389"/>
+      <c r="AD8" s="389"/>
+      <c r="AE8" s="389"/>
+      <c r="AF8" s="389"/>
+      <c r="AG8" s="389"/>
+      <c r="AH8" s="389"/>
+      <c r="AI8" s="389"/>
+      <c r="AJ8" s="389"/>
+      <c r="AK8" s="389"/>
+      <c r="AL8" s="389"/>
+      <c r="AM8" s="389"/>
+      <c r="AN8" s="389"/>
+      <c r="AO8" s="390"/>
+      <c r="AP8" s="425" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="418" t="s">
+      <c r="AQ8" s="425" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="418" t="s">
+      <c r="AR8" s="425" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="418" t="s">
+      <c r="AS8" s="425" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="418" t="s">
+      <c r="AT8" s="425" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="418" t="s">
+      <c r="AU8" s="425" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="384" t="s">
+      <c r="AV8" s="392" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="384" t="s">
+      <c r="AW8" s="392" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="384" t="s">
+      <c r="AX8" s="392" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="394" t="s">
+      <c r="AY8" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="395"/>
-      <c r="BA8" s="395"/>
-      <c r="BB8" s="395"/>
-      <c r="BC8" s="395"/>
-      <c r="BD8" s="395"/>
-      <c r="BE8" s="395"/>
-      <c r="BF8" s="395"/>
-      <c r="BG8" s="395"/>
-      <c r="BH8" s="395"/>
-      <c r="BI8" s="395"/>
-      <c r="BJ8" s="395"/>
-      <c r="BK8" s="395"/>
-      <c r="BL8" s="395"/>
-      <c r="BM8" s="395"/>
-      <c r="BN8" s="395"/>
-      <c r="BO8" s="395"/>
-      <c r="BP8" s="396"/>
-      <c r="BQ8" s="400" t="s">
+      <c r="AZ8" s="389"/>
+      <c r="BA8" s="389"/>
+      <c r="BB8" s="389"/>
+      <c r="BC8" s="389"/>
+      <c r="BD8" s="389"/>
+      <c r="BE8" s="389"/>
+      <c r="BF8" s="389"/>
+      <c r="BG8" s="389"/>
+      <c r="BH8" s="389"/>
+      <c r="BI8" s="389"/>
+      <c r="BJ8" s="389"/>
+      <c r="BK8" s="389"/>
+      <c r="BL8" s="389"/>
+      <c r="BM8" s="389"/>
+      <c r="BN8" s="389"/>
+      <c r="BO8" s="389"/>
+      <c r="BP8" s="390"/>
+      <c r="BQ8" s="408" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="401"/>
-      <c r="BS8" s="394" t="s">
+      <c r="BR8" s="402"/>
+      <c r="BS8" s="388" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="394" t="s">
+      <c r="BT8" s="388" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="388" t="s">
+      <c r="BU8" s="419" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="391" t="s">
+      <c r="BW8" s="420" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="402" t="s">
+      <c r="BX8" s="409" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="403"/>
-      <c r="BZ8" s="403"/>
-      <c r="CA8" s="401"/>
-      <c r="CB8" s="397" t="s">
+      <c r="BY8" s="410"/>
+      <c r="BZ8" s="410"/>
+      <c r="CA8" s="402"/>
+      <c r="CB8" s="421" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="379" t="s">
+      <c r="CC8" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="379" t="s">
+      <c r="CD8" s="349" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="380"/>
-      <c r="B9" s="380"/>
-      <c r="C9" s="380"/>
-      <c r="D9" s="380"/>
-      <c r="E9" s="380"/>
-      <c r="F9" s="380"/>
-      <c r="G9" s="380"/>
-      <c r="H9" s="380"/>
-      <c r="I9" s="380"/>
-      <c r="J9" s="380"/>
-      <c r="K9" s="420" t="s">
+      <c r="A9" s="386"/>
+      <c r="B9" s="386"/>
+      <c r="C9" s="386"/>
+      <c r="D9" s="386"/>
+      <c r="E9" s="386"/>
+      <c r="F9" s="386"/>
+      <c r="G9" s="386"/>
+      <c r="H9" s="386"/>
+      <c r="I9" s="386"/>
+      <c r="J9" s="386"/>
+      <c r="K9" s="422" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="420" t="s">
+      <c r="L9" s="422" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="420" t="s">
+      <c r="M9" s="422" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="420" t="s">
+      <c r="N9" s="422" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="420" t="s">
+      <c r="O9" s="422" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="420" t="s">
+      <c r="P9" s="422" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="420" t="s">
+      <c r="Q9" s="422" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="420" t="s">
+      <c r="R9" s="422" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="420" t="s">
+      <c r="S9" s="422" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="420" t="s">
+      <c r="T9" s="422" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="420" t="s">
+      <c r="U9" s="422" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="424" t="s">
+      <c r="V9" s="434" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="401"/>
-      <c r="X9" s="420" t="s">
+      <c r="W9" s="402"/>
+      <c r="X9" s="422" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="417" t="s">
+      <c r="Y9" s="424" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="417" t="s">
+      <c r="Z9" s="424" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="417" t="s">
+      <c r="AA9" s="424" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="417" t="s">
+      <c r="AB9" s="424" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="329" t="s">
+      <c r="AC9" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="329" t="s">
+      <c r="AD9" s="338" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="329" t="s">
+      <c r="AE9" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="329" t="s">
+      <c r="AF9" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="417" t="s">
+      <c r="AG9" s="424" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="329" t="s">
+      <c r="AH9" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="329" t="s">
+      <c r="AI9" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="417" t="s">
+      <c r="AJ9" s="424" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="412" t="s">
+      <c r="AK9" s="394" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="384" t="s">
+      <c r="AL9" s="392" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="417" t="s">
+      <c r="AM9" s="424" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="414" t="s">
+      <c r="AN9" s="398" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="384" t="s">
+      <c r="AO9" s="392" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="380"/>
-      <c r="AQ9" s="380"/>
-      <c r="AR9" s="380"/>
-      <c r="AS9" s="380"/>
-      <c r="AT9" s="380"/>
-      <c r="AU9" s="380"/>
-      <c r="AV9" s="380"/>
-      <c r="AW9" s="380"/>
-      <c r="AX9" s="380"/>
-      <c r="AY9" s="394" t="s">
+      <c r="AP9" s="386"/>
+      <c r="AQ9" s="386"/>
+      <c r="AR9" s="386"/>
+      <c r="AS9" s="386"/>
+      <c r="AT9" s="386"/>
+      <c r="AU9" s="386"/>
+      <c r="AV9" s="386"/>
+      <c r="AW9" s="386"/>
+      <c r="AX9" s="386"/>
+      <c r="AY9" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="395"/>
-      <c r="BA9" s="395"/>
-      <c r="BB9" s="395"/>
-      <c r="BC9" s="395"/>
-      <c r="BD9" s="395"/>
-      <c r="BE9" s="395"/>
-      <c r="BF9" s="395"/>
-      <c r="BG9" s="395"/>
-      <c r="BH9" s="395"/>
-      <c r="BI9" s="395"/>
-      <c r="BJ9" s="396"/>
-      <c r="BK9" s="394" t="s">
+      <c r="AZ9" s="389"/>
+      <c r="BA9" s="389"/>
+      <c r="BB9" s="389"/>
+      <c r="BC9" s="389"/>
+      <c r="BD9" s="389"/>
+      <c r="BE9" s="389"/>
+      <c r="BF9" s="389"/>
+      <c r="BG9" s="389"/>
+      <c r="BH9" s="389"/>
+      <c r="BI9" s="389"/>
+      <c r="BJ9" s="390"/>
+      <c r="BK9" s="388" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="395"/>
-      <c r="BM9" s="395"/>
-      <c r="BN9" s="395"/>
-      <c r="BO9" s="395"/>
-      <c r="BP9" s="396"/>
-      <c r="BQ9" s="382" t="s">
+      <c r="BL9" s="389"/>
+      <c r="BM9" s="389"/>
+      <c r="BN9" s="389"/>
+      <c r="BO9" s="389"/>
+      <c r="BP9" s="390"/>
+      <c r="BQ9" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="382" t="s">
+      <c r="BR9" s="385" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="380"/>
-      <c r="BT9" s="380"/>
-      <c r="BU9" s="389"/>
+      <c r="BS9" s="386"/>
+      <c r="BT9" s="386"/>
+      <c r="BU9" s="395"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="392"/>
-      <c r="BX9" s="389"/>
-      <c r="BY9" s="431"/>
-      <c r="BZ9" s="431"/>
-      <c r="CA9" s="392"/>
-      <c r="CB9" s="380"/>
-      <c r="CC9" s="380"/>
-      <c r="CD9" s="380"/>
+      <c r="BW9" s="412"/>
+      <c r="BX9" s="395"/>
+      <c r="BY9" s="426"/>
+      <c r="BZ9" s="426"/>
+      <c r="CA9" s="412"/>
+      <c r="CB9" s="386"/>
+      <c r="CC9" s="386"/>
+      <c r="CD9" s="386"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="380"/>
-      <c r="B10" s="380"/>
-      <c r="C10" s="380"/>
-      <c r="D10" s="380"/>
-      <c r="E10" s="380"/>
-      <c r="F10" s="380"/>
-      <c r="G10" s="380"/>
-      <c r="H10" s="380"/>
-      <c r="I10" s="380"/>
-      <c r="J10" s="380"/>
-      <c r="K10" s="380"/>
-      <c r="L10" s="380"/>
-      <c r="M10" s="380"/>
-      <c r="N10" s="380"/>
-      <c r="O10" s="380"/>
-      <c r="P10" s="380"/>
-      <c r="Q10" s="380"/>
-      <c r="R10" s="380"/>
-      <c r="S10" s="380"/>
-      <c r="T10" s="380"/>
-      <c r="U10" s="380"/>
-      <c r="V10" s="390"/>
-      <c r="W10" s="416"/>
-      <c r="X10" s="380"/>
-      <c r="Y10" s="380"/>
-      <c r="Z10" s="380"/>
-      <c r="AA10" s="380"/>
-      <c r="AB10" s="380"/>
-      <c r="AC10" s="380"/>
-      <c r="AD10" s="380"/>
-      <c r="AE10" s="380"/>
-      <c r="AF10" s="380"/>
-      <c r="AG10" s="380"/>
-      <c r="AH10" s="380"/>
-      <c r="AI10" s="380"/>
-      <c r="AJ10" s="380"/>
-      <c r="AK10" s="389"/>
-      <c r="AL10" s="380"/>
-      <c r="AM10" s="380"/>
-      <c r="AN10" s="380"/>
-      <c r="AO10" s="380"/>
-      <c r="AP10" s="380"/>
-      <c r="AQ10" s="380"/>
-      <c r="AR10" s="380"/>
-      <c r="AS10" s="380"/>
-      <c r="AT10" s="380"/>
-      <c r="AU10" s="380"/>
-      <c r="AV10" s="380"/>
-      <c r="AW10" s="380"/>
-      <c r="AX10" s="380"/>
+      <c r="A10" s="386"/>
+      <c r="B10" s="386"/>
+      <c r="C10" s="386"/>
+      <c r="D10" s="386"/>
+      <c r="E10" s="386"/>
+      <c r="F10" s="386"/>
+      <c r="G10" s="386"/>
+      <c r="H10" s="386"/>
+      <c r="I10" s="386"/>
+      <c r="J10" s="386"/>
+      <c r="K10" s="386"/>
+      <c r="L10" s="386"/>
+      <c r="M10" s="386"/>
+      <c r="N10" s="386"/>
+      <c r="O10" s="386"/>
+      <c r="P10" s="386"/>
+      <c r="Q10" s="386"/>
+      <c r="R10" s="386"/>
+      <c r="S10" s="386"/>
+      <c r="T10" s="386"/>
+      <c r="U10" s="386"/>
+      <c r="V10" s="396"/>
+      <c r="W10" s="403"/>
+      <c r="X10" s="386"/>
+      <c r="Y10" s="386"/>
+      <c r="Z10" s="386"/>
+      <c r="AA10" s="386"/>
+      <c r="AB10" s="386"/>
+      <c r="AC10" s="386"/>
+      <c r="AD10" s="386"/>
+      <c r="AE10" s="386"/>
+      <c r="AF10" s="386"/>
+      <c r="AG10" s="386"/>
+      <c r="AH10" s="386"/>
+      <c r="AI10" s="386"/>
+      <c r="AJ10" s="386"/>
+      <c r="AK10" s="395"/>
+      <c r="AL10" s="386"/>
+      <c r="AM10" s="386"/>
+      <c r="AN10" s="386"/>
+      <c r="AO10" s="386"/>
+      <c r="AP10" s="386"/>
+      <c r="AQ10" s="386"/>
+      <c r="AR10" s="386"/>
+      <c r="AS10" s="386"/>
+      <c r="AT10" s="386"/>
+      <c r="AU10" s="386"/>
+      <c r="AV10" s="386"/>
+      <c r="AW10" s="386"/>
+      <c r="AX10" s="386"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15767,123 +15757,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="428" t="s">
+      <c r="BB10" s="433" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="421" t="s">
+      <c r="BC10" s="423" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="421" t="s">
+      <c r="BD10" s="423" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="421" t="s">
+      <c r="BE10" s="423" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="421" t="s">
+      <c r="BF10" s="423" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="421" t="s">
+      <c r="BG10" s="423" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="421" t="s">
+      <c r="BH10" s="423" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="421" t="s">
+      <c r="BI10" s="423" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="419" t="s">
+      <c r="BJ10" s="435" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="421" t="s">
+      <c r="BK10" s="423" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="422" t="s">
+      <c r="BL10" s="427" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="421" t="s">
+      <c r="BM10" s="423" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="422" t="s">
+      <c r="BN10" s="427" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="422" t="s">
+      <c r="BO10" s="427" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="394" t="s">
+      <c r="BP10" s="388" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="380"/>
-      <c r="BR10" s="380"/>
-      <c r="BS10" s="380"/>
-      <c r="BT10" s="380"/>
-      <c r="BU10" s="389"/>
+      <c r="BQ10" s="386"/>
+      <c r="BR10" s="386"/>
+      <c r="BS10" s="386"/>
+      <c r="BT10" s="386"/>
+      <c r="BU10" s="395"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="392"/>
-      <c r="BX10" s="405"/>
-      <c r="BY10" s="406"/>
-      <c r="BZ10" s="406"/>
-      <c r="CA10" s="393"/>
-      <c r="CB10" s="380"/>
-      <c r="CC10" s="380"/>
-      <c r="CD10" s="380"/>
+      <c r="BW10" s="412"/>
+      <c r="BX10" s="413"/>
+      <c r="BY10" s="414"/>
+      <c r="BZ10" s="414"/>
+      <c r="CA10" s="415"/>
+      <c r="CB10" s="386"/>
+      <c r="CC10" s="386"/>
+      <c r="CD10" s="386"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="383"/>
-      <c r="B11" s="383"/>
-      <c r="C11" s="383"/>
-      <c r="D11" s="383"/>
-      <c r="E11" s="383"/>
-      <c r="F11" s="383"/>
-      <c r="G11" s="383"/>
-      <c r="H11" s="383"/>
-      <c r="I11" s="383"/>
-      <c r="J11" s="383"/>
-      <c r="K11" s="383"/>
-      <c r="L11" s="383"/>
-      <c r="M11" s="383"/>
-      <c r="N11" s="383"/>
-      <c r="O11" s="383"/>
-      <c r="P11" s="383"/>
-      <c r="Q11" s="383"/>
-      <c r="R11" s="383"/>
-      <c r="S11" s="383"/>
-      <c r="T11" s="383"/>
-      <c r="U11" s="383"/>
+      <c r="A11" s="387"/>
+      <c r="B11" s="387"/>
+      <c r="C11" s="387"/>
+      <c r="D11" s="387"/>
+      <c r="E11" s="387"/>
+      <c r="F11" s="387"/>
+      <c r="G11" s="387"/>
+      <c r="H11" s="387"/>
+      <c r="I11" s="387"/>
+      <c r="J11" s="387"/>
+      <c r="K11" s="387"/>
+      <c r="L11" s="387"/>
+      <c r="M11" s="387"/>
+      <c r="N11" s="387"/>
+      <c r="O11" s="387"/>
+      <c r="P11" s="387"/>
+      <c r="Q11" s="387"/>
+      <c r="R11" s="387"/>
+      <c r="S11" s="387"/>
+      <c r="T11" s="387"/>
+      <c r="U11" s="387"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="383"/>
-      <c r="Y11" s="383"/>
-      <c r="Z11" s="383"/>
-      <c r="AA11" s="383"/>
-      <c r="AB11" s="383"/>
-      <c r="AC11" s="383"/>
-      <c r="AD11" s="383"/>
-      <c r="AE11" s="383"/>
-      <c r="AF11" s="383"/>
-      <c r="AG11" s="383"/>
-      <c r="AH11" s="383"/>
-      <c r="AI11" s="383"/>
-      <c r="AJ11" s="383"/>
-      <c r="AK11" s="390"/>
-      <c r="AL11" s="383"/>
-      <c r="AM11" s="383"/>
-      <c r="AN11" s="383"/>
-      <c r="AO11" s="383"/>
-      <c r="AP11" s="383"/>
-      <c r="AQ11" s="383"/>
-      <c r="AR11" s="383"/>
-      <c r="AS11" s="383"/>
-      <c r="AT11" s="383"/>
-      <c r="AU11" s="383"/>
-      <c r="AV11" s="383"/>
-      <c r="AW11" s="383"/>
-      <c r="AX11" s="383"/>
+      <c r="X11" s="387"/>
+      <c r="Y11" s="387"/>
+      <c r="Z11" s="387"/>
+      <c r="AA11" s="387"/>
+      <c r="AB11" s="387"/>
+      <c r="AC11" s="387"/>
+      <c r="AD11" s="387"/>
+      <c r="AE11" s="387"/>
+      <c r="AF11" s="387"/>
+      <c r="AG11" s="387"/>
+      <c r="AH11" s="387"/>
+      <c r="AI11" s="387"/>
+      <c r="AJ11" s="387"/>
+      <c r="AK11" s="396"/>
+      <c r="AL11" s="387"/>
+      <c r="AM11" s="387"/>
+      <c r="AN11" s="387"/>
+      <c r="AO11" s="387"/>
+      <c r="AP11" s="387"/>
+      <c r="AQ11" s="387"/>
+      <c r="AR11" s="387"/>
+      <c r="AS11" s="387"/>
+      <c r="AT11" s="387"/>
+      <c r="AU11" s="387"/>
+      <c r="AV11" s="387"/>
+      <c r="AW11" s="387"/>
+      <c r="AX11" s="387"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15893,28 +15883,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="383"/>
-      <c r="BC11" s="383"/>
-      <c r="BD11" s="383"/>
-      <c r="BE11" s="383"/>
-      <c r="BF11" s="383"/>
-      <c r="BG11" s="383"/>
-      <c r="BH11" s="383"/>
-      <c r="BI11" s="383"/>
-      <c r="BJ11" s="383"/>
-      <c r="BK11" s="383"/>
-      <c r="BL11" s="383"/>
-      <c r="BM11" s="383"/>
-      <c r="BN11" s="383"/>
-      <c r="BO11" s="383"/>
-      <c r="BP11" s="383"/>
-      <c r="BQ11" s="383"/>
-      <c r="BR11" s="383"/>
-      <c r="BS11" s="383"/>
-      <c r="BT11" s="383"/>
-      <c r="BU11" s="390"/>
+      <c r="BB11" s="387"/>
+      <c r="BC11" s="387"/>
+      <c r="BD11" s="387"/>
+      <c r="BE11" s="387"/>
+      <c r="BF11" s="387"/>
+      <c r="BG11" s="387"/>
+      <c r="BH11" s="387"/>
+      <c r="BI11" s="387"/>
+      <c r="BJ11" s="387"/>
+      <c r="BK11" s="387"/>
+      <c r="BL11" s="387"/>
+      <c r="BM11" s="387"/>
+      <c r="BN11" s="387"/>
+      <c r="BO11" s="387"/>
+      <c r="BP11" s="387"/>
+      <c r="BQ11" s="387"/>
+      <c r="BR11" s="387"/>
+      <c r="BS11" s="387"/>
+      <c r="BT11" s="387"/>
+      <c r="BU11" s="396"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="393"/>
+      <c r="BW11" s="415"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15927,9 +15917,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="381"/>
-      <c r="CC11" s="381"/>
-      <c r="CD11" s="381"/>
+      <c r="CB11" s="407"/>
+      <c r="CC11" s="407"/>
+      <c r="CD11" s="407"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18330,16 +18320,62 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="BX8:CA10"/>
@@ -18356,62 +18392,16 @@
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18641,87 +18631,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="408"/>
-      <c r="B3" s="399"/>
-      <c r="C3" s="399"/>
-      <c r="D3" s="399"/>
-      <c r="E3" s="399"/>
-      <c r="F3" s="399"/>
-      <c r="G3" s="399"/>
-      <c r="H3" s="399"/>
-      <c r="I3" s="399"/>
-      <c r="J3" s="399"/>
-      <c r="K3" s="399"/>
-      <c r="L3" s="399"/>
-      <c r="M3" s="399"/>
-      <c r="N3" s="399"/>
-      <c r="O3" s="399"/>
-      <c r="P3" s="399"/>
-      <c r="Q3" s="399"/>
-      <c r="R3" s="399"/>
-      <c r="S3" s="399"/>
-      <c r="T3" s="399"/>
-      <c r="U3" s="399"/>
-      <c r="V3" s="399"/>
-      <c r="W3" s="399"/>
-      <c r="X3" s="399"/>
-      <c r="Y3" s="399"/>
-      <c r="Z3" s="399"/>
-      <c r="AA3" s="399"/>
-      <c r="AB3" s="399"/>
-      <c r="AC3" s="399"/>
-      <c r="AD3" s="399"/>
-      <c r="AE3" s="399"/>
-      <c r="AF3" s="399"/>
-      <c r="AG3" s="399"/>
-      <c r="AH3" s="399"/>
-      <c r="AI3" s="399"/>
-      <c r="AJ3" s="399"/>
-      <c r="AK3" s="399"/>
-      <c r="AL3" s="399"/>
-      <c r="AM3" s="399"/>
-      <c r="AN3" s="399"/>
-      <c r="AO3" s="399"/>
-      <c r="AP3" s="399"/>
-      <c r="AQ3" s="399"/>
-      <c r="AR3" s="399"/>
-      <c r="AS3" s="399"/>
-      <c r="AT3" s="399"/>
-      <c r="AU3" s="399"/>
-      <c r="AV3" s="399"/>
-      <c r="AW3" s="399"/>
-      <c r="AX3" s="399"/>
-      <c r="AY3" s="399"/>
-      <c r="AZ3" s="399"/>
-      <c r="BA3" s="399"/>
-      <c r="BB3" s="399"/>
-      <c r="BC3" s="399"/>
-      <c r="BD3" s="399"/>
-      <c r="BE3" s="399"/>
-      <c r="BF3" s="399"/>
-      <c r="BG3" s="399"/>
-      <c r="BH3" s="399"/>
-      <c r="BI3" s="399"/>
-      <c r="BJ3" s="399"/>
-      <c r="BK3" s="399"/>
-      <c r="BL3" s="399"/>
-      <c r="BM3" s="399"/>
-      <c r="BN3" s="399"/>
-      <c r="BO3" s="399"/>
-      <c r="BP3" s="399"/>
-      <c r="BQ3" s="399"/>
-      <c r="BR3" s="399"/>
-      <c r="BS3" s="399"/>
-      <c r="BT3" s="399"/>
-      <c r="BU3" s="399"/>
-      <c r="BW3" s="398" t="s">
+      <c r="A3" s="417"/>
+      <c r="B3" s="406"/>
+      <c r="C3" s="406"/>
+      <c r="D3" s="406"/>
+      <c r="E3" s="406"/>
+      <c r="F3" s="406"/>
+      <c r="G3" s="406"/>
+      <c r="H3" s="406"/>
+      <c r="I3" s="406"/>
+      <c r="J3" s="406"/>
+      <c r="K3" s="406"/>
+      <c r="L3" s="406"/>
+      <c r="M3" s="406"/>
+      <c r="N3" s="406"/>
+      <c r="O3" s="406"/>
+      <c r="P3" s="406"/>
+      <c r="Q3" s="406"/>
+      <c r="R3" s="406"/>
+      <c r="S3" s="406"/>
+      <c r="T3" s="406"/>
+      <c r="U3" s="406"/>
+      <c r="V3" s="406"/>
+      <c r="W3" s="406"/>
+      <c r="X3" s="406"/>
+      <c r="Y3" s="406"/>
+      <c r="Z3" s="406"/>
+      <c r="AA3" s="406"/>
+      <c r="AB3" s="406"/>
+      <c r="AC3" s="406"/>
+      <c r="AD3" s="406"/>
+      <c r="AE3" s="406"/>
+      <c r="AF3" s="406"/>
+      <c r="AG3" s="406"/>
+      <c r="AH3" s="406"/>
+      <c r="AI3" s="406"/>
+      <c r="AJ3" s="406"/>
+      <c r="AK3" s="406"/>
+      <c r="AL3" s="406"/>
+      <c r="AM3" s="406"/>
+      <c r="AN3" s="406"/>
+      <c r="AO3" s="406"/>
+      <c r="AP3" s="406"/>
+      <c r="AQ3" s="406"/>
+      <c r="AR3" s="406"/>
+      <c r="AS3" s="406"/>
+      <c r="AT3" s="406"/>
+      <c r="AU3" s="406"/>
+      <c r="AV3" s="406"/>
+      <c r="AW3" s="406"/>
+      <c r="AX3" s="406"/>
+      <c r="AY3" s="406"/>
+      <c r="AZ3" s="406"/>
+      <c r="BA3" s="406"/>
+      <c r="BB3" s="406"/>
+      <c r="BC3" s="406"/>
+      <c r="BD3" s="406"/>
+      <c r="BE3" s="406"/>
+      <c r="BF3" s="406"/>
+      <c r="BG3" s="406"/>
+      <c r="BH3" s="406"/>
+      <c r="BI3" s="406"/>
+      <c r="BJ3" s="406"/>
+      <c r="BK3" s="406"/>
+      <c r="BL3" s="406"/>
+      <c r="BM3" s="406"/>
+      <c r="BN3" s="406"/>
+      <c r="BO3" s="406"/>
+      <c r="BP3" s="406"/>
+      <c r="BQ3" s="406"/>
+      <c r="BR3" s="406"/>
+      <c r="BS3" s="406"/>
+      <c r="BT3" s="406"/>
+      <c r="BU3" s="406"/>
+      <c r="BW3" s="405" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="399"/>
-      <c r="BY3" s="399"/>
-      <c r="BZ3" s="399"/>
-      <c r="CA3" s="399"/>
-      <c r="CB3" s="399"/>
+      <c r="BX3" s="406"/>
+      <c r="BY3" s="406"/>
+      <c r="BZ3" s="406"/>
+      <c r="CA3" s="406"/>
+      <c r="CB3" s="406"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18804,366 +18794,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="399"/>
-      <c r="BX4" s="399"/>
-      <c r="BY4" s="399"/>
-      <c r="BZ4" s="399"/>
-      <c r="CA4" s="399"/>
-      <c r="CB4" s="399"/>
+      <c r="BW4" s="406"/>
+      <c r="BX4" s="406"/>
+      <c r="BY4" s="406"/>
+      <c r="BZ4" s="406"/>
+      <c r="CA4" s="406"/>
+      <c r="CB4" s="406"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="411" t="s">
+      <c r="A5" s="393" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="410" t="s">
+      <c r="B5" s="404" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="384" t="s">
+      <c r="C5" s="392" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="409" t="s">
+      <c r="D5" s="399" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="409" t="s">
+      <c r="E5" s="399" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="429" t="s">
+      <c r="F5" s="428" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="384" t="s">
+      <c r="G5" s="392" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="335" t="s">
+      <c r="H5" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="335" t="s">
+      <c r="I5" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="384" t="s">
+      <c r="J5" s="392" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="413" t="s">
+      <c r="K5" s="397" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="395"/>
-      <c r="M5" s="395"/>
-      <c r="N5" s="395"/>
-      <c r="O5" s="395"/>
-      <c r="P5" s="395"/>
-      <c r="Q5" s="395"/>
-      <c r="R5" s="395"/>
-      <c r="S5" s="395"/>
-      <c r="T5" s="395"/>
-      <c r="U5" s="395"/>
-      <c r="V5" s="395"/>
-      <c r="W5" s="395"/>
-      <c r="X5" s="395"/>
-      <c r="Y5" s="384" t="s">
+      <c r="L5" s="389"/>
+      <c r="M5" s="389"/>
+      <c r="N5" s="389"/>
+      <c r="O5" s="389"/>
+      <c r="P5" s="389"/>
+      <c r="Q5" s="389"/>
+      <c r="R5" s="389"/>
+      <c r="S5" s="389"/>
+      <c r="T5" s="389"/>
+      <c r="U5" s="389"/>
+      <c r="V5" s="389"/>
+      <c r="W5" s="389"/>
+      <c r="X5" s="389"/>
+      <c r="Y5" s="392" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="395"/>
-      <c r="AA5" s="395"/>
-      <c r="AB5" s="395"/>
-      <c r="AC5" s="395"/>
-      <c r="AD5" s="395"/>
-      <c r="AE5" s="395"/>
-      <c r="AF5" s="395"/>
-      <c r="AG5" s="395"/>
-      <c r="AH5" s="395"/>
-      <c r="AI5" s="395"/>
-      <c r="AJ5" s="395"/>
-      <c r="AK5" s="395"/>
-      <c r="AL5" s="395"/>
-      <c r="AM5" s="395"/>
-      <c r="AN5" s="395"/>
-      <c r="AO5" s="396"/>
-      <c r="AP5" s="384" t="s">
+      <c r="Z5" s="389"/>
+      <c r="AA5" s="389"/>
+      <c r="AB5" s="389"/>
+      <c r="AC5" s="389"/>
+      <c r="AD5" s="389"/>
+      <c r="AE5" s="389"/>
+      <c r="AF5" s="389"/>
+      <c r="AG5" s="389"/>
+      <c r="AH5" s="389"/>
+      <c r="AI5" s="389"/>
+      <c r="AJ5" s="389"/>
+      <c r="AK5" s="389"/>
+      <c r="AL5" s="389"/>
+      <c r="AM5" s="389"/>
+      <c r="AN5" s="389"/>
+      <c r="AO5" s="390"/>
+      <c r="AP5" s="392" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="384" t="s">
+      <c r="AQ5" s="392" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="384" t="s">
+      <c r="AR5" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="384" t="s">
+      <c r="AS5" s="392" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="384" t="s">
+      <c r="AT5" s="392" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="384" t="s">
+      <c r="AU5" s="392" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="384" t="s">
+      <c r="AV5" s="392" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="384" t="s">
+      <c r="AW5" s="392" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="384" t="s">
+      <c r="AX5" s="392" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="394" t="s">
+      <c r="AY5" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="395"/>
-      <c r="BA5" s="395"/>
-      <c r="BB5" s="395"/>
-      <c r="BC5" s="395"/>
-      <c r="BD5" s="395"/>
-      <c r="BE5" s="395"/>
-      <c r="BF5" s="395"/>
-      <c r="BG5" s="395"/>
-      <c r="BH5" s="395"/>
-      <c r="BI5" s="395"/>
-      <c r="BJ5" s="395"/>
-      <c r="BK5" s="395"/>
-      <c r="BL5" s="395"/>
-      <c r="BM5" s="395"/>
-      <c r="BN5" s="395"/>
-      <c r="BO5" s="395"/>
-      <c r="BP5" s="396"/>
-      <c r="BQ5" s="400" t="s">
+      <c r="AZ5" s="389"/>
+      <c r="BA5" s="389"/>
+      <c r="BB5" s="389"/>
+      <c r="BC5" s="389"/>
+      <c r="BD5" s="389"/>
+      <c r="BE5" s="389"/>
+      <c r="BF5" s="389"/>
+      <c r="BG5" s="389"/>
+      <c r="BH5" s="389"/>
+      <c r="BI5" s="389"/>
+      <c r="BJ5" s="389"/>
+      <c r="BK5" s="389"/>
+      <c r="BL5" s="389"/>
+      <c r="BM5" s="389"/>
+      <c r="BN5" s="389"/>
+      <c r="BO5" s="389"/>
+      <c r="BP5" s="390"/>
+      <c r="BQ5" s="408" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="401"/>
-      <c r="BS5" s="394" t="s">
+      <c r="BR5" s="402"/>
+      <c r="BS5" s="388" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="394" t="s">
+      <c r="BT5" s="388" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="388" t="s">
+      <c r="BU5" s="419" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="391" t="s">
+      <c r="BW5" s="420" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="402" t="s">
+      <c r="BX5" s="409" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="403"/>
-      <c r="BZ5" s="403"/>
-      <c r="CA5" s="401"/>
-      <c r="CB5" s="397" t="s">
+      <c r="BY5" s="410"/>
+      <c r="BZ5" s="410"/>
+      <c r="CA5" s="402"/>
+      <c r="CB5" s="421" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="379" t="s">
+      <c r="CC5" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="379" t="s">
+      <c r="CD5" s="349" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="380"/>
-      <c r="B6" s="380"/>
-      <c r="C6" s="380"/>
-      <c r="D6" s="380"/>
-      <c r="E6" s="380"/>
-      <c r="F6" s="380"/>
-      <c r="G6" s="380"/>
-      <c r="H6" s="380"/>
-      <c r="I6" s="380"/>
-      <c r="J6" s="380"/>
-      <c r="K6" s="385" t="s">
+      <c r="A6" s="386"/>
+      <c r="B6" s="386"/>
+      <c r="C6" s="386"/>
+      <c r="D6" s="386"/>
+      <c r="E6" s="386"/>
+      <c r="F6" s="386"/>
+      <c r="G6" s="386"/>
+      <c r="H6" s="386"/>
+      <c r="I6" s="386"/>
+      <c r="J6" s="386"/>
+      <c r="K6" s="400" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="385" t="s">
+      <c r="L6" s="400" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="385" t="s">
+      <c r="M6" s="400" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="385" t="s">
+      <c r="N6" s="400" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="385" t="s">
+      <c r="O6" s="400" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="385" t="s">
+      <c r="P6" s="400" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="385" t="s">
+      <c r="Q6" s="400" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="385" t="s">
+      <c r="R6" s="400" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="385" t="s">
+      <c r="S6" s="400" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="385" t="s">
+      <c r="T6" s="400" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="385" t="s">
+      <c r="U6" s="400" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="415" t="s">
+      <c r="V6" s="401" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="401"/>
-      <c r="X6" s="385" t="s">
+      <c r="W6" s="402"/>
+      <c r="X6" s="400" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="384" t="s">
+      <c r="Y6" s="392" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="384" t="s">
+      <c r="Z6" s="392" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="384" t="s">
+      <c r="AA6" s="392" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="384" t="s">
+      <c r="AB6" s="392" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="335" t="s">
+      <c r="AC6" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="335" t="s">
+      <c r="AD6" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="335" t="s">
+      <c r="AE6" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="335" t="s">
+      <c r="AF6" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="384" t="s">
+      <c r="AG6" s="392" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="335" t="s">
+      <c r="AH6" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="335" t="s">
+      <c r="AI6" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="384" t="s">
+      <c r="AJ6" s="392" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="412" t="s">
+      <c r="AK6" s="394" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="384" t="s">
+      <c r="AL6" s="392" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="384" t="s">
+      <c r="AM6" s="392" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="414" t="s">
+      <c r="AN6" s="398" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="384" t="s">
+      <c r="AO6" s="392" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="380"/>
-      <c r="AQ6" s="380"/>
-      <c r="AR6" s="380"/>
-      <c r="AS6" s="380"/>
-      <c r="AT6" s="380"/>
-      <c r="AU6" s="380"/>
-      <c r="AV6" s="380"/>
-      <c r="AW6" s="380"/>
-      <c r="AX6" s="380"/>
-      <c r="AY6" s="394" t="s">
+      <c r="AP6" s="386"/>
+      <c r="AQ6" s="386"/>
+      <c r="AR6" s="386"/>
+      <c r="AS6" s="386"/>
+      <c r="AT6" s="386"/>
+      <c r="AU6" s="386"/>
+      <c r="AV6" s="386"/>
+      <c r="AW6" s="386"/>
+      <c r="AX6" s="386"/>
+      <c r="AY6" s="388" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="395"/>
-      <c r="BA6" s="395"/>
-      <c r="BB6" s="395"/>
-      <c r="BC6" s="395"/>
-      <c r="BD6" s="395"/>
-      <c r="BE6" s="395"/>
-      <c r="BF6" s="395"/>
-      <c r="BG6" s="395"/>
-      <c r="BH6" s="395"/>
-      <c r="BI6" s="395"/>
-      <c r="BJ6" s="396"/>
-      <c r="BK6" s="394" t="s">
+      <c r="AZ6" s="389"/>
+      <c r="BA6" s="389"/>
+      <c r="BB6" s="389"/>
+      <c r="BC6" s="389"/>
+      <c r="BD6" s="389"/>
+      <c r="BE6" s="389"/>
+      <c r="BF6" s="389"/>
+      <c r="BG6" s="389"/>
+      <c r="BH6" s="389"/>
+      <c r="BI6" s="389"/>
+      <c r="BJ6" s="390"/>
+      <c r="BK6" s="388" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="395"/>
-      <c r="BM6" s="395"/>
-      <c r="BN6" s="395"/>
-      <c r="BO6" s="395"/>
-      <c r="BP6" s="396"/>
-      <c r="BQ6" s="382" t="s">
+      <c r="BL6" s="389"/>
+      <c r="BM6" s="389"/>
+      <c r="BN6" s="389"/>
+      <c r="BO6" s="389"/>
+      <c r="BP6" s="390"/>
+      <c r="BQ6" s="385" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="382" t="s">
+      <c r="BR6" s="385" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="380"/>
-      <c r="BT6" s="380"/>
-      <c r="BU6" s="389"/>
-      <c r="BW6" s="392"/>
-      <c r="BX6" s="389"/>
-      <c r="BY6" s="404"/>
-      <c r="BZ6" s="404"/>
-      <c r="CA6" s="392"/>
-      <c r="CB6" s="380"/>
-      <c r="CC6" s="380"/>
-      <c r="CD6" s="380"/>
+      <c r="BS6" s="386"/>
+      <c r="BT6" s="386"/>
+      <c r="BU6" s="395"/>
+      <c r="BW6" s="412"/>
+      <c r="BX6" s="395"/>
+      <c r="BY6" s="411"/>
+      <c r="BZ6" s="411"/>
+      <c r="CA6" s="412"/>
+      <c r="CB6" s="386"/>
+      <c r="CC6" s="386"/>
+      <c r="CD6" s="386"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="380"/>
-      <c r="B7" s="380"/>
-      <c r="C7" s="380"/>
-      <c r="D7" s="380"/>
-      <c r="E7" s="380"/>
-      <c r="F7" s="380"/>
-      <c r="G7" s="380"/>
-      <c r="H7" s="380"/>
-      <c r="I7" s="380"/>
-      <c r="J7" s="380"/>
-      <c r="K7" s="380"/>
-      <c r="L7" s="380"/>
-      <c r="M7" s="380"/>
-      <c r="N7" s="380"/>
-      <c r="O7" s="380"/>
-      <c r="P7" s="380"/>
-      <c r="Q7" s="380"/>
-      <c r="R7" s="380"/>
-      <c r="S7" s="380"/>
-      <c r="T7" s="380"/>
-      <c r="U7" s="380"/>
-      <c r="V7" s="390"/>
-      <c r="W7" s="416"/>
-      <c r="X7" s="380"/>
-      <c r="Y7" s="380"/>
-      <c r="Z7" s="380"/>
-      <c r="AA7" s="380"/>
-      <c r="AB7" s="380"/>
-      <c r="AC7" s="380"/>
-      <c r="AD7" s="380"/>
-      <c r="AE7" s="380"/>
-      <c r="AF7" s="380"/>
-      <c r="AG7" s="380"/>
-      <c r="AH7" s="380"/>
-      <c r="AI7" s="380"/>
-      <c r="AJ7" s="380"/>
-      <c r="AK7" s="389"/>
-      <c r="AL7" s="380"/>
-      <c r="AM7" s="380"/>
-      <c r="AN7" s="380"/>
-      <c r="AO7" s="380"/>
-      <c r="AP7" s="380"/>
-      <c r="AQ7" s="380"/>
-      <c r="AR7" s="380"/>
-      <c r="AS7" s="380"/>
-      <c r="AT7" s="380"/>
-      <c r="AU7" s="380"/>
-      <c r="AV7" s="380"/>
-      <c r="AW7" s="380"/>
-      <c r="AX7" s="380"/>
+      <c r="A7" s="386"/>
+      <c r="B7" s="386"/>
+      <c r="C7" s="386"/>
+      <c r="D7" s="386"/>
+      <c r="E7" s="386"/>
+      <c r="F7" s="386"/>
+      <c r="G7" s="386"/>
+      <c r="H7" s="386"/>
+      <c r="I7" s="386"/>
+      <c r="J7" s="386"/>
+      <c r="K7" s="386"/>
+      <c r="L7" s="386"/>
+      <c r="M7" s="386"/>
+      <c r="N7" s="386"/>
+      <c r="O7" s="386"/>
+      <c r="P7" s="386"/>
+      <c r="Q7" s="386"/>
+      <c r="R7" s="386"/>
+      <c r="S7" s="386"/>
+      <c r="T7" s="386"/>
+      <c r="U7" s="386"/>
+      <c r="V7" s="396"/>
+      <c r="W7" s="403"/>
+      <c r="X7" s="386"/>
+      <c r="Y7" s="386"/>
+      <c r="Z7" s="386"/>
+      <c r="AA7" s="386"/>
+      <c r="AB7" s="386"/>
+      <c r="AC7" s="386"/>
+      <c r="AD7" s="386"/>
+      <c r="AE7" s="386"/>
+      <c r="AF7" s="386"/>
+      <c r="AG7" s="386"/>
+      <c r="AH7" s="386"/>
+      <c r="AI7" s="386"/>
+      <c r="AJ7" s="386"/>
+      <c r="AK7" s="395"/>
+      <c r="AL7" s="386"/>
+      <c r="AM7" s="386"/>
+      <c r="AN7" s="386"/>
+      <c r="AO7" s="386"/>
+      <c r="AP7" s="386"/>
+      <c r="AQ7" s="386"/>
+      <c r="AR7" s="386"/>
+      <c r="AS7" s="386"/>
+      <c r="AT7" s="386"/>
+      <c r="AU7" s="386"/>
+      <c r="AV7" s="386"/>
+      <c r="AW7" s="386"/>
+      <c r="AX7" s="386"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19173,122 +19163,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="394" t="s">
+      <c r="BB7" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="386" t="s">
+      <c r="BC7" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="386" t="s">
+      <c r="BD7" s="391" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="386" t="s">
+      <c r="BE7" s="391" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="386" t="s">
+      <c r="BF7" s="391" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="386" t="s">
+      <c r="BG7" s="391" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="386" t="s">
+      <c r="BH7" s="391" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="386" t="s">
+      <c r="BI7" s="391" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="387" t="s">
+      <c r="BJ7" s="418" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="386" t="s">
+      <c r="BK7" s="391" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="394" t="s">
+      <c r="BL7" s="388" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="386" t="s">
+      <c r="BM7" s="391" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="394" t="s">
+      <c r="BN7" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="394" t="s">
+      <c r="BO7" s="388" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="394" t="s">
+      <c r="BP7" s="388" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="380"/>
-      <c r="BR7" s="380"/>
-      <c r="BS7" s="380"/>
-      <c r="BT7" s="380"/>
-      <c r="BU7" s="389"/>
-      <c r="BW7" s="392"/>
-      <c r="BX7" s="405"/>
-      <c r="BY7" s="406"/>
-      <c r="BZ7" s="406"/>
-      <c r="CA7" s="393"/>
-      <c r="CB7" s="380"/>
-      <c r="CC7" s="380"/>
-      <c r="CD7" s="380"/>
+      <c r="BQ7" s="386"/>
+      <c r="BR7" s="386"/>
+      <c r="BS7" s="386"/>
+      <c r="BT7" s="386"/>
+      <c r="BU7" s="395"/>
+      <c r="BW7" s="412"/>
+      <c r="BX7" s="413"/>
+      <c r="BY7" s="414"/>
+      <c r="BZ7" s="414"/>
+      <c r="CA7" s="415"/>
+      <c r="CB7" s="386"/>
+      <c r="CC7" s="386"/>
+      <c r="CD7" s="386"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="383"/>
-      <c r="B8" s="383"/>
-      <c r="C8" s="383"/>
-      <c r="D8" s="383"/>
-      <c r="E8" s="383"/>
-      <c r="F8" s="383"/>
-      <c r="G8" s="383"/>
-      <c r="H8" s="383"/>
-      <c r="I8" s="383"/>
-      <c r="J8" s="383"/>
-      <c r="K8" s="383"/>
-      <c r="L8" s="383"/>
-      <c r="M8" s="383"/>
-      <c r="N8" s="383"/>
-      <c r="O8" s="383"/>
-      <c r="P8" s="383"/>
-      <c r="Q8" s="383"/>
-      <c r="R8" s="383"/>
-      <c r="S8" s="383"/>
-      <c r="T8" s="383"/>
-      <c r="U8" s="383"/>
+      <c r="A8" s="387"/>
+      <c r="B8" s="387"/>
+      <c r="C8" s="387"/>
+      <c r="D8" s="387"/>
+      <c r="E8" s="387"/>
+      <c r="F8" s="387"/>
+      <c r="G8" s="387"/>
+      <c r="H8" s="387"/>
+      <c r="I8" s="387"/>
+      <c r="J8" s="387"/>
+      <c r="K8" s="387"/>
+      <c r="L8" s="387"/>
+      <c r="M8" s="387"/>
+      <c r="N8" s="387"/>
+      <c r="O8" s="387"/>
+      <c r="P8" s="387"/>
+      <c r="Q8" s="387"/>
+      <c r="R8" s="387"/>
+      <c r="S8" s="387"/>
+      <c r="T8" s="387"/>
+      <c r="U8" s="387"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="383"/>
-      <c r="Y8" s="383"/>
-      <c r="Z8" s="383"/>
-      <c r="AA8" s="383"/>
-      <c r="AB8" s="383"/>
-      <c r="AC8" s="383"/>
-      <c r="AD8" s="383"/>
-      <c r="AE8" s="383"/>
-      <c r="AF8" s="383"/>
-      <c r="AG8" s="383"/>
-      <c r="AH8" s="383"/>
-      <c r="AI8" s="383"/>
-      <c r="AJ8" s="383"/>
-      <c r="AK8" s="390"/>
-      <c r="AL8" s="383"/>
-      <c r="AM8" s="383"/>
-      <c r="AN8" s="383"/>
-      <c r="AO8" s="383"/>
-      <c r="AP8" s="383"/>
-      <c r="AQ8" s="383"/>
-      <c r="AR8" s="383"/>
-      <c r="AS8" s="383"/>
-      <c r="AT8" s="383"/>
-      <c r="AU8" s="383"/>
-      <c r="AV8" s="383"/>
-      <c r="AW8" s="383"/>
-      <c r="AX8" s="383"/>
+      <c r="X8" s="387"/>
+      <c r="Y8" s="387"/>
+      <c r="Z8" s="387"/>
+      <c r="AA8" s="387"/>
+      <c r="AB8" s="387"/>
+      <c r="AC8" s="387"/>
+      <c r="AD8" s="387"/>
+      <c r="AE8" s="387"/>
+      <c r="AF8" s="387"/>
+      <c r="AG8" s="387"/>
+      <c r="AH8" s="387"/>
+      <c r="AI8" s="387"/>
+      <c r="AJ8" s="387"/>
+      <c r="AK8" s="396"/>
+      <c r="AL8" s="387"/>
+      <c r="AM8" s="387"/>
+      <c r="AN8" s="387"/>
+      <c r="AO8" s="387"/>
+      <c r="AP8" s="387"/>
+      <c r="AQ8" s="387"/>
+      <c r="AR8" s="387"/>
+      <c r="AS8" s="387"/>
+      <c r="AT8" s="387"/>
+      <c r="AU8" s="387"/>
+      <c r="AV8" s="387"/>
+      <c r="AW8" s="387"/>
+      <c r="AX8" s="387"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19298,27 +19288,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="383"/>
-      <c r="BC8" s="383"/>
-      <c r="BD8" s="383"/>
-      <c r="BE8" s="383"/>
-      <c r="BF8" s="383"/>
-      <c r="BG8" s="383"/>
-      <c r="BH8" s="383"/>
-      <c r="BI8" s="383"/>
-      <c r="BJ8" s="383"/>
-      <c r="BK8" s="383"/>
-      <c r="BL8" s="383"/>
-      <c r="BM8" s="383"/>
-      <c r="BN8" s="383"/>
-      <c r="BO8" s="383"/>
-      <c r="BP8" s="383"/>
-      <c r="BQ8" s="383"/>
-      <c r="BR8" s="383"/>
-      <c r="BS8" s="383"/>
-      <c r="BT8" s="383"/>
-      <c r="BU8" s="390"/>
-      <c r="BW8" s="393"/>
+      <c r="BB8" s="387"/>
+      <c r="BC8" s="387"/>
+      <c r="BD8" s="387"/>
+      <c r="BE8" s="387"/>
+      <c r="BF8" s="387"/>
+      <c r="BG8" s="387"/>
+      <c r="BH8" s="387"/>
+      <c r="BI8" s="387"/>
+      <c r="BJ8" s="387"/>
+      <c r="BK8" s="387"/>
+      <c r="BL8" s="387"/>
+      <c r="BM8" s="387"/>
+      <c r="BN8" s="387"/>
+      <c r="BO8" s="387"/>
+      <c r="BP8" s="387"/>
+      <c r="BQ8" s="387"/>
+      <c r="BR8" s="387"/>
+      <c r="BS8" s="387"/>
+      <c r="BT8" s="387"/>
+      <c r="BU8" s="396"/>
+      <c r="BW8" s="415"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19331,9 +19321,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="381"/>
-      <c r="CC8" s="381"/>
-      <c r="CD8" s="381"/>
+      <c r="CB8" s="407"/>
+      <c r="CC8" s="407"/>
+      <c r="CD8" s="407"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21340,6 +21330,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
     <mergeCell ref="BI7:BI8"/>
@@ -21356,72 +21412,6 @@
     <mergeCell ref="BQ6:BQ8"/>
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AK6:AK8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C46ADD5-E081-C144-9512-8FB783518F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB52E758-EA33-4246-88D8-2D6D676EBBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38920" yWindow="560" windowWidth="33440" windowHeight="14320" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39900" yWindow="500" windowWidth="37160" windowHeight="21040" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -6766,52 +6766,90 @@
     <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6835,88 +6873,45 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6925,10 +6920,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6936,27 +6931,44 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6964,43 +6976,31 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7769,88 +7769,88 @@
       <c r="CD2" s="294"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="353"/>
-      <c r="B3" s="348"/>
-      <c r="C3" s="348"/>
-      <c r="D3" s="348"/>
-      <c r="E3" s="348"/>
-      <c r="F3" s="348"/>
-      <c r="G3" s="348"/>
-      <c r="H3" s="348"/>
-      <c r="I3" s="348"/>
-      <c r="J3" s="348"/>
-      <c r="K3" s="348"/>
-      <c r="L3" s="348"/>
-      <c r="M3" s="348"/>
-      <c r="N3" s="348"/>
-      <c r="O3" s="348"/>
-      <c r="P3" s="348"/>
-      <c r="Q3" s="348"/>
-      <c r="R3" s="348"/>
-      <c r="S3" s="348"/>
-      <c r="T3" s="348"/>
-      <c r="U3" s="348"/>
-      <c r="V3" s="348"/>
-      <c r="W3" s="348"/>
-      <c r="X3" s="348"/>
-      <c r="Y3" s="348"/>
-      <c r="Z3" s="348"/>
-      <c r="AA3" s="348"/>
-      <c r="AB3" s="348"/>
-      <c r="AC3" s="348"/>
-      <c r="AD3" s="348"/>
-      <c r="AE3" s="348"/>
-      <c r="AF3" s="348"/>
-      <c r="AG3" s="348"/>
-      <c r="AH3" s="348"/>
-      <c r="AI3" s="348"/>
-      <c r="AJ3" s="348"/>
-      <c r="AK3" s="348"/>
-      <c r="AL3" s="348"/>
-      <c r="AM3" s="348"/>
-      <c r="AN3" s="348"/>
-      <c r="AO3" s="348"/>
-      <c r="AP3" s="348"/>
-      <c r="AQ3" s="348"/>
-      <c r="AR3" s="348"/>
-      <c r="AS3" s="348"/>
-      <c r="AT3" s="348"/>
-      <c r="AU3" s="348"/>
-      <c r="AV3" s="348"/>
-      <c r="AW3" s="348"/>
-      <c r="AX3" s="348"/>
-      <c r="AY3" s="348"/>
-      <c r="AZ3" s="348"/>
-      <c r="BA3" s="348"/>
-      <c r="BB3" s="348"/>
-      <c r="BC3" s="348"/>
-      <c r="BD3" s="348"/>
-      <c r="BE3" s="348"/>
-      <c r="BF3" s="348"/>
-      <c r="BG3" s="348"/>
-      <c r="BH3" s="348"/>
-      <c r="BI3" s="348"/>
-      <c r="BJ3" s="348"/>
-      <c r="BK3" s="348"/>
-      <c r="BL3" s="348"/>
-      <c r="BM3" s="348"/>
-      <c r="BN3" s="348"/>
-      <c r="BO3" s="348"/>
-      <c r="BP3" s="348"/>
-      <c r="BQ3" s="348"/>
-      <c r="BR3" s="348"/>
-      <c r="BS3" s="348"/>
-      <c r="BT3" s="348"/>
-      <c r="BU3" s="348"/>
+      <c r="A3" s="371"/>
+      <c r="B3" s="370"/>
+      <c r="C3" s="370"/>
+      <c r="D3" s="370"/>
+      <c r="E3" s="370"/>
+      <c r="F3" s="370"/>
+      <c r="G3" s="370"/>
+      <c r="H3" s="370"/>
+      <c r="I3" s="370"/>
+      <c r="J3" s="370"/>
+      <c r="K3" s="370"/>
+      <c r="L3" s="370"/>
+      <c r="M3" s="370"/>
+      <c r="N3" s="370"/>
+      <c r="O3" s="370"/>
+      <c r="P3" s="370"/>
+      <c r="Q3" s="370"/>
+      <c r="R3" s="370"/>
+      <c r="S3" s="370"/>
+      <c r="T3" s="370"/>
+      <c r="U3" s="370"/>
+      <c r="V3" s="370"/>
+      <c r="W3" s="370"/>
+      <c r="X3" s="370"/>
+      <c r="Y3" s="370"/>
+      <c r="Z3" s="370"/>
+      <c r="AA3" s="370"/>
+      <c r="AB3" s="370"/>
+      <c r="AC3" s="370"/>
+      <c r="AD3" s="370"/>
+      <c r="AE3" s="370"/>
+      <c r="AF3" s="370"/>
+      <c r="AG3" s="370"/>
+      <c r="AH3" s="370"/>
+      <c r="AI3" s="370"/>
+      <c r="AJ3" s="370"/>
+      <c r="AK3" s="370"/>
+      <c r="AL3" s="370"/>
+      <c r="AM3" s="370"/>
+      <c r="AN3" s="370"/>
+      <c r="AO3" s="370"/>
+      <c r="AP3" s="370"/>
+      <c r="AQ3" s="370"/>
+      <c r="AR3" s="370"/>
+      <c r="AS3" s="370"/>
+      <c r="AT3" s="370"/>
+      <c r="AU3" s="370"/>
+      <c r="AV3" s="370"/>
+      <c r="AW3" s="370"/>
+      <c r="AX3" s="370"/>
+      <c r="AY3" s="370"/>
+      <c r="AZ3" s="370"/>
+      <c r="BA3" s="370"/>
+      <c r="BB3" s="370"/>
+      <c r="BC3" s="370"/>
+      <c r="BD3" s="370"/>
+      <c r="BE3" s="370"/>
+      <c r="BF3" s="370"/>
+      <c r="BG3" s="370"/>
+      <c r="BH3" s="370"/>
+      <c r="BI3" s="370"/>
+      <c r="BJ3" s="370"/>
+      <c r="BK3" s="370"/>
+      <c r="BL3" s="370"/>
+      <c r="BM3" s="370"/>
+      <c r="BN3" s="370"/>
+      <c r="BO3" s="370"/>
+      <c r="BP3" s="370"/>
+      <c r="BQ3" s="370"/>
+      <c r="BR3" s="370"/>
+      <c r="BS3" s="370"/>
+      <c r="BT3" s="370"/>
+      <c r="BU3" s="370"/>
       <c r="BV3" s="296"/>
-      <c r="BW3" s="347" t="s">
+      <c r="BW3" s="369" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="348"/>
-      <c r="BY3" s="348"/>
-      <c r="BZ3" s="348"/>
-      <c r="CA3" s="348"/>
-      <c r="CB3" s="348"/>
+      <c r="BX3" s="370"/>
+      <c r="BY3" s="370"/>
+      <c r="BZ3" s="370"/>
+      <c r="CA3" s="370"/>
+      <c r="CB3" s="370"/>
       <c r="CC3" s="298"/>
       <c r="CD3" s="298"/>
     </row>
@@ -7928,12 +7928,12 @@
       <c r="BT4" s="299"/>
       <c r="BU4" s="299"/>
       <c r="BV4" s="299"/>
-      <c r="BW4" s="348"/>
-      <c r="BX4" s="348"/>
-      <c r="BY4" s="348"/>
-      <c r="BZ4" s="348"/>
-      <c r="CA4" s="348"/>
-      <c r="CB4" s="348"/>
+      <c r="BW4" s="370"/>
+      <c r="BX4" s="370"/>
+      <c r="BY4" s="370"/>
+      <c r="BZ4" s="370"/>
+      <c r="CA4" s="370"/>
+      <c r="CB4" s="370"/>
       <c r="CC4" s="298"/>
       <c r="CD4" s="298"/>
     </row>
@@ -8011,12 +8011,12 @@
       <c r="BT5" s="299"/>
       <c r="BU5" s="299"/>
       <c r="BV5" s="299"/>
-      <c r="BW5" s="348"/>
-      <c r="BX5" s="348"/>
-      <c r="BY5" s="348"/>
-      <c r="BZ5" s="348"/>
-      <c r="CA5" s="348"/>
-      <c r="CB5" s="348"/>
+      <c r="BW5" s="370"/>
+      <c r="BX5" s="370"/>
+      <c r="BY5" s="370"/>
+      <c r="BZ5" s="370"/>
+      <c r="CA5" s="370"/>
+      <c r="CB5" s="370"/>
       <c r="CC5" s="298"/>
       <c r="CD5" s="298"/>
     </row>
@@ -8092,12 +8092,12 @@
       <c r="BT6" s="301"/>
       <c r="BU6" s="301"/>
       <c r="BV6" s="301"/>
-      <c r="BW6" s="348"/>
-      <c r="BX6" s="348"/>
-      <c r="BY6" s="348"/>
-      <c r="BZ6" s="348"/>
-      <c r="CA6" s="348"/>
-      <c r="CB6" s="348"/>
+      <c r="BW6" s="370"/>
+      <c r="BX6" s="370"/>
+      <c r="BY6" s="370"/>
+      <c r="BZ6" s="370"/>
+      <c r="CA6" s="370"/>
+      <c r="CB6" s="370"/>
       <c r="CC6" s="298"/>
       <c r="CD6" s="298"/>
     </row>
@@ -8237,356 +8237,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="436" t="s">
+      <c r="A8" s="368" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="355" t="s">
+      <c r="B8" s="373" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="332" t="s">
+      <c r="C8" s="341" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="339" t="s">
+      <c r="D8" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="339" t="s">
+      <c r="E8" s="360" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="332" t="s">
+      <c r="F8" s="341" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="345" t="s">
+      <c r="G8" s="356" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="371" t="s">
+      <c r="H8" s="361" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="371" t="s">
+      <c r="I8" s="361" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="345" t="s">
+      <c r="J8" s="356" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="369" t="s">
+      <c r="K8" s="367" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="370"/>
-      <c r="M8" s="370"/>
-      <c r="N8" s="370"/>
-      <c r="O8" s="370"/>
-      <c r="P8" s="370"/>
-      <c r="Q8" s="370"/>
-      <c r="R8" s="370"/>
-      <c r="S8" s="370"/>
-      <c r="T8" s="370"/>
-      <c r="U8" s="370"/>
-      <c r="V8" s="370"/>
-      <c r="W8" s="370"/>
-      <c r="X8" s="370"/>
-      <c r="Y8" s="372" t="s">
+      <c r="L8" s="353"/>
+      <c r="M8" s="353"/>
+      <c r="N8" s="353"/>
+      <c r="O8" s="353"/>
+      <c r="P8" s="353"/>
+      <c r="Q8" s="353"/>
+      <c r="R8" s="353"/>
+      <c r="S8" s="353"/>
+      <c r="T8" s="353"/>
+      <c r="U8" s="353"/>
+      <c r="V8" s="353"/>
+      <c r="W8" s="353"/>
+      <c r="X8" s="353"/>
+      <c r="Y8" s="352" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="370"/>
-      <c r="AA8" s="370"/>
-      <c r="AB8" s="370"/>
-      <c r="AC8" s="370"/>
-      <c r="AD8" s="370"/>
-      <c r="AE8" s="370"/>
-      <c r="AF8" s="370"/>
-      <c r="AG8" s="370"/>
-      <c r="AH8" s="370"/>
-      <c r="AI8" s="370"/>
-      <c r="AJ8" s="370"/>
-      <c r="AK8" s="370"/>
-      <c r="AL8" s="370"/>
-      <c r="AM8" s="370"/>
-      <c r="AN8" s="370"/>
-      <c r="AO8" s="373"/>
-      <c r="AP8" s="345" t="s">
+      <c r="Z8" s="353"/>
+      <c r="AA8" s="353"/>
+      <c r="AB8" s="353"/>
+      <c r="AC8" s="353"/>
+      <c r="AD8" s="353"/>
+      <c r="AE8" s="353"/>
+      <c r="AF8" s="353"/>
+      <c r="AG8" s="353"/>
+      <c r="AH8" s="353"/>
+      <c r="AI8" s="353"/>
+      <c r="AJ8" s="353"/>
+      <c r="AK8" s="353"/>
+      <c r="AL8" s="353"/>
+      <c r="AM8" s="353"/>
+      <c r="AN8" s="353"/>
+      <c r="AO8" s="354"/>
+      <c r="AP8" s="356" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="345" t="s">
+      <c r="AQ8" s="356" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="345" t="s">
+      <c r="AR8" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="345" t="s">
+      <c r="AS8" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="345" t="s">
+      <c r="AT8" s="356" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="345" t="s">
+      <c r="AU8" s="356" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="332" t="s">
+      <c r="AV8" s="341" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="352" t="s">
+      <c r="AW8" s="346" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="332" t="s">
+      <c r="AX8" s="341" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="375" t="s">
+      <c r="AY8" s="358" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="370"/>
-      <c r="BA8" s="370"/>
-      <c r="BB8" s="370"/>
-      <c r="BC8" s="370"/>
-      <c r="BD8" s="370"/>
-      <c r="BE8" s="370"/>
-      <c r="BF8" s="370"/>
-      <c r="BG8" s="370"/>
-      <c r="BH8" s="370"/>
-      <c r="BI8" s="370"/>
-      <c r="BJ8" s="370"/>
-      <c r="BK8" s="370"/>
-      <c r="BL8" s="370"/>
-      <c r="BM8" s="370"/>
-      <c r="BN8" s="370"/>
-      <c r="BO8" s="370"/>
-      <c r="BP8" s="370"/>
-      <c r="BQ8" s="373"/>
-      <c r="BR8" s="379" t="s">
+      <c r="AZ8" s="353"/>
+      <c r="BA8" s="353"/>
+      <c r="BB8" s="353"/>
+      <c r="BC8" s="353"/>
+      <c r="BD8" s="353"/>
+      <c r="BE8" s="353"/>
+      <c r="BF8" s="353"/>
+      <c r="BG8" s="353"/>
+      <c r="BH8" s="353"/>
+      <c r="BI8" s="353"/>
+      <c r="BJ8" s="353"/>
+      <c r="BK8" s="353"/>
+      <c r="BL8" s="353"/>
+      <c r="BM8" s="353"/>
+      <c r="BN8" s="353"/>
+      <c r="BO8" s="353"/>
+      <c r="BP8" s="353"/>
+      <c r="BQ8" s="354"/>
+      <c r="BR8" s="342" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="366"/>
-      <c r="BT8" s="332" t="s">
+      <c r="BS8" s="343"/>
+      <c r="BT8" s="341" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="376" t="s">
+      <c r="BU8" s="338" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="329"/>
-      <c r="BW8" s="335" t="s">
+      <c r="BW8" s="383" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="356" t="s">
+      <c r="BX8" s="374" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="357"/>
-      <c r="BZ8" s="357"/>
-      <c r="CA8" s="358"/>
-      <c r="CB8" s="380" t="s">
+      <c r="BY8" s="375"/>
+      <c r="BZ8" s="375"/>
+      <c r="CA8" s="376"/>
+      <c r="CB8" s="344" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="349" t="s">
+      <c r="CC8" s="332" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="349" t="s">
+      <c r="CD8" s="332" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="333"/>
-      <c r="B9" s="333"/>
-      <c r="C9" s="333"/>
-      <c r="D9" s="333"/>
-      <c r="E9" s="333"/>
-      <c r="F9" s="333"/>
-      <c r="G9" s="346"/>
-      <c r="H9" s="333"/>
-      <c r="I9" s="333"/>
-      <c r="J9" s="346"/>
-      <c r="K9" s="343" t="s">
+      <c r="A9" s="336"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="347"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="347"/>
+      <c r="K9" s="363" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="343" t="s">
+      <c r="L9" s="363" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="343" t="s">
+      <c r="M9" s="363" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="343" t="s">
+      <c r="N9" s="363" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="343" t="s">
+      <c r="O9" s="363" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="343" t="s">
+      <c r="P9" s="363" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="343" t="s">
+      <c r="Q9" s="363" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="343" t="s">
+      <c r="R9" s="363" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="343" t="s">
+      <c r="S9" s="363" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="343" t="s">
+      <c r="T9" s="363" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="343" t="s">
+      <c r="U9" s="363" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="365" t="s">
+      <c r="V9" s="364" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="366"/>
-      <c r="X9" s="343" t="s">
+      <c r="W9" s="343"/>
+      <c r="X9" s="363" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="338" t="s">
+      <c r="Y9" s="335" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="338" t="s">
+      <c r="Z9" s="335" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="338" t="s">
+      <c r="AA9" s="335" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="338" t="s">
+      <c r="AB9" s="335" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="338" t="s">
+      <c r="AC9" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="338" t="s">
+      <c r="AD9" s="335" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="338" t="s">
+      <c r="AE9" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="338" t="s">
+      <c r="AF9" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="338" t="s">
+      <c r="AG9" s="335" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="338" t="s">
+      <c r="AH9" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="338" t="s">
+      <c r="AI9" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="374" t="s">
+      <c r="AJ9" s="357" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="376" t="s">
+      <c r="AK9" s="338" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="352" t="s">
+      <c r="AL9" s="346" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="338" t="s">
+      <c r="AM9" s="335" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="332" t="s">
+      <c r="AN9" s="341" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="332" t="s">
+      <c r="AO9" s="341" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="346"/>
-      <c r="AQ9" s="346"/>
-      <c r="AR9" s="346"/>
-      <c r="AS9" s="346"/>
-      <c r="AT9" s="346"/>
-      <c r="AU9" s="346"/>
-      <c r="AV9" s="333"/>
-      <c r="AW9" s="346"/>
-      <c r="AX9" s="333"/>
-      <c r="AY9" s="382" t="s">
+      <c r="AP9" s="347"/>
+      <c r="AQ9" s="347"/>
+      <c r="AR9" s="347"/>
+      <c r="AS9" s="347"/>
+      <c r="AT9" s="347"/>
+      <c r="AU9" s="347"/>
+      <c r="AV9" s="336"/>
+      <c r="AW9" s="347"/>
+      <c r="AX9" s="336"/>
+      <c r="AY9" s="349" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="383"/>
-      <c r="BA9" s="383"/>
-      <c r="BB9" s="383"/>
-      <c r="BC9" s="383"/>
-      <c r="BD9" s="383"/>
-      <c r="BE9" s="383"/>
-      <c r="BF9" s="383"/>
-      <c r="BG9" s="383"/>
-      <c r="BH9" s="383"/>
-      <c r="BI9" s="383"/>
-      <c r="BJ9" s="383"/>
-      <c r="BK9" s="383"/>
-      <c r="BL9" s="384"/>
-      <c r="BM9" s="382" t="s">
+      <c r="AZ9" s="350"/>
+      <c r="BA9" s="350"/>
+      <c r="BB9" s="350"/>
+      <c r="BC9" s="350"/>
+      <c r="BD9" s="350"/>
+      <c r="BE9" s="350"/>
+      <c r="BF9" s="350"/>
+      <c r="BG9" s="350"/>
+      <c r="BH9" s="350"/>
+      <c r="BI9" s="350"/>
+      <c r="BJ9" s="350"/>
+      <c r="BK9" s="350"/>
+      <c r="BL9" s="351"/>
+      <c r="BM9" s="349" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="383"/>
-      <c r="BO9" s="383"/>
-      <c r="BP9" s="383"/>
-      <c r="BQ9" s="384"/>
-      <c r="BR9" s="344" t="s">
+      <c r="BN9" s="350"/>
+      <c r="BO9" s="350"/>
+      <c r="BP9" s="350"/>
+      <c r="BQ9" s="351"/>
+      <c r="BR9" s="362" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="344" t="s">
+      <c r="BS9" s="362" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="333"/>
-      <c r="BU9" s="377"/>
+      <c r="BT9" s="336"/>
+      <c r="BU9" s="339"/>
       <c r="BV9" s="329"/>
-      <c r="BW9" s="336"/>
-      <c r="BX9" s="359"/>
-      <c r="BY9" s="360"/>
-      <c r="BZ9" s="360"/>
-      <c r="CA9" s="361"/>
-      <c r="CB9" s="333"/>
-      <c r="CC9" s="350"/>
-      <c r="CD9" s="350"/>
+      <c r="BW9" s="384"/>
+      <c r="BX9" s="377"/>
+      <c r="BY9" s="378"/>
+      <c r="BZ9" s="378"/>
+      <c r="CA9" s="379"/>
+      <c r="CB9" s="336"/>
+      <c r="CC9" s="333"/>
+      <c r="CD9" s="333"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="333"/>
-      <c r="B10" s="333"/>
-      <c r="C10" s="333"/>
-      <c r="D10" s="333"/>
-      <c r="E10" s="333"/>
-      <c r="F10" s="333"/>
-      <c r="G10" s="346"/>
-      <c r="H10" s="333"/>
-      <c r="I10" s="333"/>
-      <c r="J10" s="346"/>
-      <c r="K10" s="333"/>
-      <c r="L10" s="333"/>
-      <c r="M10" s="333"/>
-      <c r="N10" s="333"/>
-      <c r="O10" s="333"/>
-      <c r="P10" s="333"/>
-      <c r="Q10" s="333"/>
-      <c r="R10" s="333"/>
-      <c r="S10" s="333"/>
-      <c r="T10" s="333"/>
-      <c r="U10" s="333"/>
-      <c r="V10" s="367"/>
-      <c r="W10" s="368"/>
-      <c r="X10" s="333"/>
-      <c r="Y10" s="333"/>
-      <c r="Z10" s="333"/>
-      <c r="AA10" s="333"/>
-      <c r="AB10" s="333"/>
-      <c r="AC10" s="333"/>
-      <c r="AD10" s="333"/>
-      <c r="AE10" s="333"/>
-      <c r="AF10" s="333"/>
-      <c r="AG10" s="333"/>
-      <c r="AH10" s="333"/>
-      <c r="AI10" s="333"/>
-      <c r="AJ10" s="346"/>
-      <c r="AK10" s="377"/>
-      <c r="AL10" s="346"/>
-      <c r="AM10" s="333"/>
-      <c r="AN10" s="333"/>
-      <c r="AO10" s="333"/>
-      <c r="AP10" s="346"/>
-      <c r="AQ10" s="346"/>
-      <c r="AR10" s="346"/>
-      <c r="AS10" s="346"/>
-      <c r="AT10" s="346"/>
-      <c r="AU10" s="346"/>
-      <c r="AV10" s="333"/>
-      <c r="AW10" s="346"/>
-      <c r="AX10" s="333"/>
+      <c r="A10" s="336"/>
+      <c r="B10" s="336"/>
+      <c r="C10" s="336"/>
+      <c r="D10" s="336"/>
+      <c r="E10" s="336"/>
+      <c r="F10" s="336"/>
+      <c r="G10" s="347"/>
+      <c r="H10" s="336"/>
+      <c r="I10" s="336"/>
+      <c r="J10" s="347"/>
+      <c r="K10" s="336"/>
+      <c r="L10" s="336"/>
+      <c r="M10" s="336"/>
+      <c r="N10" s="336"/>
+      <c r="O10" s="336"/>
+      <c r="P10" s="336"/>
+      <c r="Q10" s="336"/>
+      <c r="R10" s="336"/>
+      <c r="S10" s="336"/>
+      <c r="T10" s="336"/>
+      <c r="U10" s="336"/>
+      <c r="V10" s="365"/>
+      <c r="W10" s="366"/>
+      <c r="X10" s="336"/>
+      <c r="Y10" s="336"/>
+      <c r="Z10" s="336"/>
+      <c r="AA10" s="336"/>
+      <c r="AB10" s="336"/>
+      <c r="AC10" s="336"/>
+      <c r="AD10" s="336"/>
+      <c r="AE10" s="336"/>
+      <c r="AF10" s="336"/>
+      <c r="AG10" s="336"/>
+      <c r="AH10" s="336"/>
+      <c r="AI10" s="336"/>
+      <c r="AJ10" s="347"/>
+      <c r="AK10" s="339"/>
+      <c r="AL10" s="347"/>
+      <c r="AM10" s="336"/>
+      <c r="AN10" s="336"/>
+      <c r="AO10" s="336"/>
+      <c r="AP10" s="347"/>
+      <c r="AQ10" s="347"/>
+      <c r="AR10" s="347"/>
+      <c r="AS10" s="347"/>
+      <c r="AT10" s="347"/>
+      <c r="AU10" s="347"/>
+      <c r="AV10" s="336"/>
+      <c r="AW10" s="347"/>
+      <c r="AX10" s="336"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8596,67 +8596,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="354" t="s">
+      <c r="BB10" s="372" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="341" t="s">
+      <c r="BC10" s="359" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="341" t="s">
+      <c r="BD10" s="359" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="340" t="s">
+      <c r="BE10" s="355" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="340" t="s">
+      <c r="BF10" s="355" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="340" t="s">
+      <c r="BG10" s="355" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="341" t="s">
+      <c r="BH10" s="359" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="341" t="s">
+      <c r="BI10" s="359" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="340" t="s">
+      <c r="BJ10" s="355" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="340" t="s">
+      <c r="BK10" s="355" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="332" t="s">
+      <c r="BL10" s="341" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="341" t="s">
+      <c r="BM10" s="359" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="352" t="s">
+      <c r="BN10" s="346" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="341" t="s">
+      <c r="BO10" s="359" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="352" t="s">
+      <c r="BP10" s="346" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="352" t="s">
+      <c r="BQ10" s="346" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="333"/>
-      <c r="BS10" s="333"/>
-      <c r="BT10" s="333"/>
-      <c r="BU10" s="377"/>
+      <c r="BR10" s="336"/>
+      <c r="BS10" s="336"/>
+      <c r="BT10" s="336"/>
+      <c r="BU10" s="339"/>
       <c r="BV10" s="329"/>
-      <c r="BW10" s="336"/>
-      <c r="BX10" s="362"/>
-      <c r="BY10" s="363"/>
-      <c r="BZ10" s="363"/>
-      <c r="CA10" s="364"/>
-      <c r="CB10" s="333"/>
-      <c r="CC10" s="350"/>
-      <c r="CD10" s="350"/>
+      <c r="BW10" s="384"/>
+      <c r="BX10" s="380"/>
+      <c r="BY10" s="381"/>
+      <c r="BZ10" s="381"/>
+      <c r="CA10" s="382"/>
+      <c r="CB10" s="336"/>
+      <c r="CC10" s="333"/>
+      <c r="CD10" s="333"/>
       <c r="CE10" s="319" t="s">
         <v>3</v>
       </c>
@@ -8664,60 +8664,60 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="334"/>
-      <c r="B11" s="334"/>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="342"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="342"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
-      <c r="N11" s="334"/>
-      <c r="O11" s="334"/>
-      <c r="P11" s="334"/>
-      <c r="Q11" s="334"/>
-      <c r="R11" s="334"/>
-      <c r="S11" s="334"/>
-      <c r="T11" s="334"/>
-      <c r="U11" s="334"/>
+      <c r="A11" s="337"/>
+      <c r="B11" s="337"/>
+      <c r="C11" s="337"/>
+      <c r="D11" s="337"/>
+      <c r="E11" s="337"/>
+      <c r="F11" s="337"/>
+      <c r="G11" s="348"/>
+      <c r="H11" s="337"/>
+      <c r="I11" s="337"/>
+      <c r="J11" s="348"/>
+      <c r="K11" s="337"/>
+      <c r="L11" s="337"/>
+      <c r="M11" s="337"/>
+      <c r="N11" s="337"/>
+      <c r="O11" s="337"/>
+      <c r="P11" s="337"/>
+      <c r="Q11" s="337"/>
+      <c r="R11" s="337"/>
+      <c r="S11" s="337"/>
+      <c r="T11" s="337"/>
+      <c r="U11" s="337"/>
       <c r="V11" s="330" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="330" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="334"/>
-      <c r="Y11" s="334"/>
-      <c r="Z11" s="334"/>
-      <c r="AA11" s="334"/>
-      <c r="AB11" s="334"/>
-      <c r="AC11" s="334"/>
-      <c r="AD11" s="334"/>
-      <c r="AE11" s="334"/>
-      <c r="AF11" s="334"/>
-      <c r="AG11" s="334"/>
-      <c r="AH11" s="334"/>
-      <c r="AI11" s="334"/>
-      <c r="AJ11" s="342"/>
-      <c r="AK11" s="378"/>
-      <c r="AL11" s="342"/>
-      <c r="AM11" s="334"/>
-      <c r="AN11" s="334"/>
-      <c r="AO11" s="334"/>
-      <c r="AP11" s="342"/>
-      <c r="AQ11" s="342"/>
-      <c r="AR11" s="342"/>
-      <c r="AS11" s="342"/>
-      <c r="AT11" s="342"/>
-      <c r="AU11" s="342"/>
-      <c r="AV11" s="334"/>
-      <c r="AW11" s="342"/>
-      <c r="AX11" s="334"/>
+      <c r="X11" s="337"/>
+      <c r="Y11" s="337"/>
+      <c r="Z11" s="337"/>
+      <c r="AA11" s="337"/>
+      <c r="AB11" s="337"/>
+      <c r="AC11" s="337"/>
+      <c r="AD11" s="337"/>
+      <c r="AE11" s="337"/>
+      <c r="AF11" s="337"/>
+      <c r="AG11" s="337"/>
+      <c r="AH11" s="337"/>
+      <c r="AI11" s="337"/>
+      <c r="AJ11" s="348"/>
+      <c r="AK11" s="340"/>
+      <c r="AL11" s="348"/>
+      <c r="AM11" s="337"/>
+      <c r="AN11" s="337"/>
+      <c r="AO11" s="337"/>
+      <c r="AP11" s="348"/>
+      <c r="AQ11" s="348"/>
+      <c r="AR11" s="348"/>
+      <c r="AS11" s="348"/>
+      <c r="AT11" s="348"/>
+      <c r="AU11" s="348"/>
+      <c r="AV11" s="337"/>
+      <c r="AW11" s="348"/>
+      <c r="AX11" s="337"/>
       <c r="AY11" s="331" t="s">
         <v>88</v>
       </c>
@@ -8727,28 +8727,28 @@
       <c r="BA11" s="331" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="334"/>
-      <c r="BC11" s="342"/>
-      <c r="BD11" s="342"/>
-      <c r="BE11" s="334"/>
-      <c r="BF11" s="334"/>
-      <c r="BG11" s="334"/>
-      <c r="BH11" s="342"/>
-      <c r="BI11" s="342"/>
-      <c r="BJ11" s="334"/>
-      <c r="BK11" s="334"/>
-      <c r="BL11" s="334"/>
-      <c r="BM11" s="342"/>
-      <c r="BN11" s="342"/>
-      <c r="BO11" s="342"/>
-      <c r="BP11" s="342"/>
-      <c r="BQ11" s="342"/>
-      <c r="BR11" s="334"/>
-      <c r="BS11" s="334"/>
-      <c r="BT11" s="334"/>
-      <c r="BU11" s="378"/>
+      <c r="BB11" s="337"/>
+      <c r="BC11" s="348"/>
+      <c r="BD11" s="348"/>
+      <c r="BE11" s="337"/>
+      <c r="BF11" s="337"/>
+      <c r="BG11" s="337"/>
+      <c r="BH11" s="348"/>
+      <c r="BI11" s="348"/>
+      <c r="BJ11" s="337"/>
+      <c r="BK11" s="337"/>
+      <c r="BL11" s="337"/>
+      <c r="BM11" s="348"/>
+      <c r="BN11" s="348"/>
+      <c r="BO11" s="348"/>
+      <c r="BP11" s="348"/>
+      <c r="BQ11" s="348"/>
+      <c r="BR11" s="337"/>
+      <c r="BS11" s="337"/>
+      <c r="BT11" s="337"/>
+      <c r="BU11" s="340"/>
       <c r="BV11" s="329"/>
-      <c r="BW11" s="337"/>
+      <c r="BW11" s="385"/>
       <c r="BX11" s="327" t="s">
         <v>91</v>
       </c>
@@ -8761,9 +8761,9 @@
       <c r="CA11" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="381"/>
-      <c r="CC11" s="351"/>
-      <c r="CD11" s="351"/>
+      <c r="CB11" s="345"/>
+      <c r="CC11" s="334"/>
+      <c r="CD11" s="334"/>
       <c r="CE11" s="318">
         <v>26</v>
       </c>
@@ -9314,19 +9314,19 @@
       <c r="AX14" s="94"/>
       <c r="AY14" s="94">
         <f>SUM(AY15:AY21)</f>
-        <v>3804801</v>
+        <v>3550401</v>
       </c>
       <c r="AZ14" s="94">
         <f>SUM(AZ15:AZ21)</f>
-        <v>713400</v>
+        <v>665700</v>
       </c>
       <c r="BA14" s="94">
         <f>SUM(BA15:BA21)</f>
-        <v>475600</v>
+        <v>443800</v>
       </c>
       <c r="BB14" s="94">
         <f>SUM(BB15:BB21)</f>
-        <v>4993801</v>
+        <v>4659901</v>
       </c>
       <c r="BC14" s="94">
         <f>SUM(BC15:BC21)</f>
@@ -9345,7 +9345,7 @@
       <c r="BK14" s="94"/>
       <c r="BL14" s="94">
         <f t="shared" ref="BL14:BQ14" si="6">SUM(BL15:BL21)</f>
-        <v>10155188</v>
+        <v>9753498</v>
       </c>
       <c r="BM14" s="94">
         <f t="shared" si="6"/>
@@ -9372,7 +9372,7 @@
       <c r="BT14" s="94"/>
       <c r="BU14" s="314">
         <f>SUM(BU15:BU21)</f>
-        <v>226664858.59230769</v>
+        <v>227400448.59230769</v>
       </c>
       <c r="BV14" s="252"/>
       <c r="BW14" s="242"/>
@@ -9398,7 +9398,7 @@
         <v>98</v>
       </c>
       <c r="E15" s="274" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F15" s="274" t="s">
         <v>100</v>
@@ -9532,25 +9532,25 @@
         <v>64000000</v>
       </c>
       <c r="AW15" s="275"/>
-      <c r="AX15" s="275" t="str">
+      <c r="AX15" s="275">
         <f t="shared" ref="AX15:AX21" si="23">IF(E15="CT","x",0)</f>
-        <v>x</v>
+        <v>0</v>
       </c>
       <c r="AY15" s="278">
         <f t="shared" ref="AY15:BA21" si="24">ROUND(IF($AX15="x",($G15+$H15)*AY$11,0),0)</f>
-        <v>761600</v>
+        <v>0</v>
       </c>
       <c r="AZ15" s="278">
         <f t="shared" si="24"/>
-        <v>142800</v>
+        <v>0</v>
       </c>
       <c r="BA15" s="278">
         <f t="shared" si="24"/>
-        <v>95200</v>
+        <v>0</v>
       </c>
       <c r="BB15" s="278">
         <f t="shared" ref="BB15:BB21" si="25">SUM(AY15:BA15)</f>
-        <v>999600</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="278"/>
       <c r="BD15" s="278"/>
@@ -9560,11 +9560,11 @@
       </c>
       <c r="BF15" s="278">
         <f>AM15+IF(E15="CT",IF(AR15&gt;=730000,730000,AR15),0)+IF(((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15)&gt;0,((AV15-AM15-IF(AR15&gt;=730000,730000,AR15)-AS15)*15%-AS15),0)</f>
-        <v>10220500</v>
+        <v>9490500</v>
       </c>
       <c r="BG15" s="278">
         <f t="shared" ref="BG15:BG21" si="27">AV15-BF15+AW15</f>
-        <v>53779500</v>
+        <v>54509500</v>
       </c>
       <c r="BH15" s="278">
         <v>3</v>
@@ -9574,15 +9574,15 @@
       </c>
       <c r="BJ15" s="278">
         <f>IF(E15="CT",15500000,0)</f>
-        <v>15500000</v>
+        <v>0</v>
       </c>
       <c r="BK15" s="278">
         <f t="shared" ref="BK15:BK21" si="28">BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
-        <v>18679900</v>
+        <v>35909500</v>
       </c>
       <c r="BL15" s="279">
         <f t="shared" ref="BL15:BL21" si="29">IF(E15="TV",BK15*10%,IF(BK15&gt;0,ROUND(IF(BK15&gt;=80000000,BK15*35%-9850000,IF(BK15&gt;=52000000,BK15*30%-5850000,IF(BK15&gt;=32000000,BK15*25%-3250000,IF(BK15&gt;=18000000,BK15*20%-1650000,IF(BK15&gt;=10000000,BK15*15%-750000,IF(BK15&gt;5000000,BK15*10%-250000,BK15*5%)))))),0),0))</f>
-        <v>2085980</v>
+        <v>3590950</v>
       </c>
       <c r="BM15" s="278"/>
       <c r="BN15" s="278"/>
@@ -9596,7 +9596,7 @@
       <c r="BT15" s="328"/>
       <c r="BU15" s="280">
         <f t="shared" ref="BU15:BU21" si="30">AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
-        <v>60819220</v>
+        <v>60313850</v>
       </c>
       <c r="BV15" s="252"/>
       <c r="BW15" s="281">
@@ -10613,7 +10613,7 @@
         <v>103</v>
       </c>
       <c r="E20" s="248" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F20" s="248" t="s">
         <v>100</v>
@@ -10747,25 +10747,25 @@
         <v>24870000</v>
       </c>
       <c r="AW20" s="94"/>
-      <c r="AX20" s="94">
+      <c r="AX20" s="94" t="str">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="AY20" s="250">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>507200</v>
       </c>
       <c r="AZ20" s="250">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>95100</v>
       </c>
       <c r="BA20" s="250">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>63400</v>
       </c>
       <c r="BB20" s="250">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>665700</v>
       </c>
       <c r="BC20" s="250"/>
       <c r="BD20" s="250"/>
@@ -10775,11 +10775,11 @@
       </c>
       <c r="BF20" s="250">
         <f t="shared" si="34"/>
-        <v>3622500</v>
+        <v>4342500</v>
       </c>
       <c r="BG20" s="250">
         <f t="shared" si="27"/>
-        <v>21247500</v>
+        <v>20527500</v>
       </c>
       <c r="BH20" s="250"/>
       <c r="BI20" s="278">
@@ -10787,15 +10787,15 @@
       </c>
       <c r="BJ20" s="250">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>15500000</v>
       </c>
       <c r="BK20" s="250">
         <f t="shared" si="28"/>
-        <v>21247500</v>
+        <v>4361800</v>
       </c>
       <c r="BL20" s="243">
         <f t="shared" si="29"/>
-        <v>2124750</v>
+        <v>218090</v>
       </c>
       <c r="BM20" s="250"/>
       <c r="BN20" s="250"/>
@@ -10809,7 +10809,7 @@
       <c r="BT20" s="263"/>
       <c r="BU20" s="251">
         <f t="shared" si="30"/>
-        <v>22681850</v>
+        <v>23922810</v>
       </c>
       <c r="BV20" s="252"/>
       <c r="BW20" s="242">
@@ -11223,6 +11223,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
     <mergeCell ref="CD8:CD11"/>
     <mergeCell ref="Y9:Y11"/>
     <mergeCell ref="AA9:AA11"/>
@@ -11239,72 +11305,6 @@
     <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BS9:BS11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="R9:R11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11513,87 +11513,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="417"/>
-      <c r="B3" s="406"/>
-      <c r="C3" s="406"/>
-      <c r="D3" s="406"/>
-      <c r="E3" s="406"/>
-      <c r="F3" s="406"/>
-      <c r="G3" s="406"/>
-      <c r="H3" s="406"/>
-      <c r="I3" s="406"/>
-      <c r="J3" s="406"/>
-      <c r="K3" s="406"/>
-      <c r="L3" s="406"/>
-      <c r="M3" s="406"/>
-      <c r="N3" s="406"/>
-      <c r="O3" s="406"/>
-      <c r="P3" s="406"/>
-      <c r="Q3" s="406"/>
-      <c r="R3" s="406"/>
-      <c r="S3" s="406"/>
-      <c r="T3" s="406"/>
-      <c r="U3" s="406"/>
-      <c r="V3" s="406"/>
-      <c r="W3" s="406"/>
-      <c r="X3" s="406"/>
-      <c r="Y3" s="406"/>
-      <c r="Z3" s="406"/>
-      <c r="AA3" s="406"/>
-      <c r="AB3" s="406"/>
-      <c r="AC3" s="406"/>
-      <c r="AD3" s="406"/>
-      <c r="AE3" s="406"/>
-      <c r="AF3" s="406"/>
-      <c r="AG3" s="406"/>
-      <c r="AH3" s="406"/>
-      <c r="AI3" s="406"/>
-      <c r="AJ3" s="406"/>
-      <c r="AK3" s="406"/>
-      <c r="AL3" s="406"/>
-      <c r="AM3" s="406"/>
-      <c r="AN3" s="406"/>
-      <c r="AO3" s="406"/>
-      <c r="AP3" s="406"/>
-      <c r="AQ3" s="406"/>
-      <c r="AR3" s="406"/>
-      <c r="AS3" s="406"/>
-      <c r="AT3" s="406"/>
-      <c r="AU3" s="406"/>
-      <c r="AV3" s="406"/>
-      <c r="AW3" s="406"/>
-      <c r="AX3" s="406"/>
-      <c r="AY3" s="406"/>
-      <c r="AZ3" s="406"/>
-      <c r="BA3" s="406"/>
-      <c r="BB3" s="406"/>
-      <c r="BC3" s="406"/>
-      <c r="BD3" s="406"/>
-      <c r="BE3" s="406"/>
-      <c r="BF3" s="406"/>
-      <c r="BG3" s="406"/>
-      <c r="BH3" s="406"/>
-      <c r="BI3" s="406"/>
-      <c r="BJ3" s="406"/>
-      <c r="BK3" s="406"/>
-      <c r="BL3" s="406"/>
-      <c r="BM3" s="406"/>
-      <c r="BN3" s="406"/>
-      <c r="BO3" s="406"/>
-      <c r="BP3" s="406"/>
-      <c r="BQ3" s="406"/>
-      <c r="BR3" s="406"/>
-      <c r="BS3" s="406"/>
-      <c r="BT3" s="406"/>
-      <c r="BU3" s="406"/>
-      <c r="BW3" s="405" t="s">
+      <c r="A3" s="414"/>
+      <c r="B3" s="405"/>
+      <c r="C3" s="405"/>
+      <c r="D3" s="405"/>
+      <c r="E3" s="405"/>
+      <c r="F3" s="405"/>
+      <c r="G3" s="405"/>
+      <c r="H3" s="405"/>
+      <c r="I3" s="405"/>
+      <c r="J3" s="405"/>
+      <c r="K3" s="405"/>
+      <c r="L3" s="405"/>
+      <c r="M3" s="405"/>
+      <c r="N3" s="405"/>
+      <c r="O3" s="405"/>
+      <c r="P3" s="405"/>
+      <c r="Q3" s="405"/>
+      <c r="R3" s="405"/>
+      <c r="S3" s="405"/>
+      <c r="T3" s="405"/>
+      <c r="U3" s="405"/>
+      <c r="V3" s="405"/>
+      <c r="W3" s="405"/>
+      <c r="X3" s="405"/>
+      <c r="Y3" s="405"/>
+      <c r="Z3" s="405"/>
+      <c r="AA3" s="405"/>
+      <c r="AB3" s="405"/>
+      <c r="AC3" s="405"/>
+      <c r="AD3" s="405"/>
+      <c r="AE3" s="405"/>
+      <c r="AF3" s="405"/>
+      <c r="AG3" s="405"/>
+      <c r="AH3" s="405"/>
+      <c r="AI3" s="405"/>
+      <c r="AJ3" s="405"/>
+      <c r="AK3" s="405"/>
+      <c r="AL3" s="405"/>
+      <c r="AM3" s="405"/>
+      <c r="AN3" s="405"/>
+      <c r="AO3" s="405"/>
+      <c r="AP3" s="405"/>
+      <c r="AQ3" s="405"/>
+      <c r="AR3" s="405"/>
+      <c r="AS3" s="405"/>
+      <c r="AT3" s="405"/>
+      <c r="AU3" s="405"/>
+      <c r="AV3" s="405"/>
+      <c r="AW3" s="405"/>
+      <c r="AX3" s="405"/>
+      <c r="AY3" s="405"/>
+      <c r="AZ3" s="405"/>
+      <c r="BA3" s="405"/>
+      <c r="BB3" s="405"/>
+      <c r="BC3" s="405"/>
+      <c r="BD3" s="405"/>
+      <c r="BE3" s="405"/>
+      <c r="BF3" s="405"/>
+      <c r="BG3" s="405"/>
+      <c r="BH3" s="405"/>
+      <c r="BI3" s="405"/>
+      <c r="BJ3" s="405"/>
+      <c r="BK3" s="405"/>
+      <c r="BL3" s="405"/>
+      <c r="BM3" s="405"/>
+      <c r="BN3" s="405"/>
+      <c r="BO3" s="405"/>
+      <c r="BP3" s="405"/>
+      <c r="BQ3" s="405"/>
+      <c r="BR3" s="405"/>
+      <c r="BS3" s="405"/>
+      <c r="BT3" s="405"/>
+      <c r="BU3" s="405"/>
+      <c r="BW3" s="404" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="406"/>
-      <c r="BY3" s="406"/>
-      <c r="BZ3" s="406"/>
-      <c r="CA3" s="406"/>
-      <c r="CB3" s="406"/>
+      <c r="BX3" s="405"/>
+      <c r="BY3" s="405"/>
+      <c r="BZ3" s="405"/>
+      <c r="CA3" s="405"/>
+      <c r="CB3" s="405"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11676,155 +11676,155 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="406"/>
-      <c r="BX4" s="406"/>
-      <c r="BY4" s="406"/>
-      <c r="BZ4" s="406"/>
-      <c r="CA4" s="406"/>
-      <c r="CB4" s="406"/>
+      <c r="BW4" s="405"/>
+      <c r="BX4" s="405"/>
+      <c r="BY4" s="405"/>
+      <c r="BZ4" s="405"/>
+      <c r="CA4" s="405"/>
+      <c r="CB4" s="405"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="393" t="s">
+      <c r="A5" s="417" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="404" t="s">
+      <c r="B5" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="392" t="s">
+      <c r="C5" s="390" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="399" t="s">
+      <c r="D5" s="415" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="399" t="s">
+      <c r="E5" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="392" t="s">
+      <c r="F5" s="390" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="392" t="s">
+      <c r="G5" s="390" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="332" t="s">
+      <c r="H5" s="341" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="332" t="s">
+      <c r="I5" s="341" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="392" t="s">
+      <c r="J5" s="390" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="397" t="s">
+      <c r="K5" s="419" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="389"/>
-      <c r="M5" s="389"/>
-      <c r="N5" s="389"/>
-      <c r="O5" s="389"/>
-      <c r="P5" s="389"/>
-      <c r="Q5" s="389"/>
-      <c r="R5" s="389"/>
-      <c r="S5" s="389"/>
-      <c r="T5" s="389"/>
-      <c r="U5" s="389"/>
-      <c r="V5" s="389"/>
-      <c r="W5" s="389"/>
-      <c r="X5" s="389"/>
-      <c r="Y5" s="392" t="s">
+      <c r="L5" s="401"/>
+      <c r="M5" s="401"/>
+      <c r="N5" s="401"/>
+      <c r="O5" s="401"/>
+      <c r="P5" s="401"/>
+      <c r="Q5" s="401"/>
+      <c r="R5" s="401"/>
+      <c r="S5" s="401"/>
+      <c r="T5" s="401"/>
+      <c r="U5" s="401"/>
+      <c r="V5" s="401"/>
+      <c r="W5" s="401"/>
+      <c r="X5" s="401"/>
+      <c r="Y5" s="390" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="389"/>
-      <c r="AA5" s="389"/>
-      <c r="AB5" s="389"/>
-      <c r="AC5" s="389"/>
-      <c r="AD5" s="389"/>
-      <c r="AE5" s="389"/>
-      <c r="AF5" s="389"/>
-      <c r="AG5" s="389"/>
-      <c r="AH5" s="389"/>
-      <c r="AI5" s="389"/>
-      <c r="AJ5" s="389"/>
-      <c r="AK5" s="389"/>
-      <c r="AL5" s="389"/>
-      <c r="AM5" s="389"/>
-      <c r="AN5" s="389"/>
-      <c r="AO5" s="390"/>
-      <c r="AP5" s="392" t="s">
+      <c r="Z5" s="401"/>
+      <c r="AA5" s="401"/>
+      <c r="AB5" s="401"/>
+      <c r="AC5" s="401"/>
+      <c r="AD5" s="401"/>
+      <c r="AE5" s="401"/>
+      <c r="AF5" s="401"/>
+      <c r="AG5" s="401"/>
+      <c r="AH5" s="401"/>
+      <c r="AI5" s="401"/>
+      <c r="AJ5" s="401"/>
+      <c r="AK5" s="401"/>
+      <c r="AL5" s="401"/>
+      <c r="AM5" s="401"/>
+      <c r="AN5" s="401"/>
+      <c r="AO5" s="402"/>
+      <c r="AP5" s="390" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="392" t="s">
+      <c r="AQ5" s="390" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="392" t="s">
+      <c r="AR5" s="390" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="392" t="s">
+      <c r="AS5" s="390" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="392" t="s">
+      <c r="AT5" s="390" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="392" t="s">
+      <c r="AU5" s="390" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="392" t="s">
+      <c r="AV5" s="390" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="392" t="s">
+      <c r="AW5" s="390" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="392" t="s">
+      <c r="AX5" s="390" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="388" t="s">
+      <c r="AY5" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="389"/>
-      <c r="BA5" s="389"/>
-      <c r="BB5" s="389"/>
-      <c r="BC5" s="389"/>
-      <c r="BD5" s="389"/>
-      <c r="BE5" s="389"/>
-      <c r="BF5" s="389"/>
-      <c r="BG5" s="389"/>
-      <c r="BH5" s="389"/>
-      <c r="BI5" s="389"/>
-      <c r="BJ5" s="389"/>
-      <c r="BK5" s="389"/>
-      <c r="BL5" s="389"/>
-      <c r="BM5" s="389"/>
-      <c r="BN5" s="389"/>
-      <c r="BO5" s="389"/>
-      <c r="BP5" s="389"/>
-      <c r="BQ5" s="390"/>
-      <c r="BR5" s="408" t="s">
+      <c r="AZ5" s="401"/>
+      <c r="BA5" s="401"/>
+      <c r="BB5" s="401"/>
+      <c r="BC5" s="401"/>
+      <c r="BD5" s="401"/>
+      <c r="BE5" s="401"/>
+      <c r="BF5" s="401"/>
+      <c r="BG5" s="401"/>
+      <c r="BH5" s="401"/>
+      <c r="BI5" s="401"/>
+      <c r="BJ5" s="401"/>
+      <c r="BK5" s="401"/>
+      <c r="BL5" s="401"/>
+      <c r="BM5" s="401"/>
+      <c r="BN5" s="401"/>
+      <c r="BO5" s="401"/>
+      <c r="BP5" s="401"/>
+      <c r="BQ5" s="402"/>
+      <c r="BR5" s="406" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="402"/>
-      <c r="BT5" s="388" t="s">
+      <c r="BS5" s="407"/>
+      <c r="BT5" s="400" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="419" t="s">
+      <c r="BU5" s="394" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="420" t="s">
+      <c r="BW5" s="397" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="409" t="s">
+      <c r="BX5" s="408" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="410"/>
-      <c r="BZ5" s="410"/>
-      <c r="CA5" s="402"/>
-      <c r="CB5" s="421" t="s">
+      <c r="BY5" s="409"/>
+      <c r="BZ5" s="409"/>
+      <c r="CA5" s="407"/>
+      <c r="CB5" s="403" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="349" t="s">
+      <c r="CC5" s="332" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="349" t="s">
+      <c r="CD5" s="332" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
@@ -11841,95 +11841,95 @@
       <c r="H6" s="386"/>
       <c r="I6" s="386"/>
       <c r="J6" s="386"/>
-      <c r="K6" s="400" t="s">
+      <c r="K6" s="391" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="400" t="s">
+      <c r="L6" s="391" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="400" t="s">
+      <c r="M6" s="391" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="400" t="s">
+      <c r="N6" s="391" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="400" t="s">
+      <c r="O6" s="391" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="400" t="s">
+      <c r="P6" s="391" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="400" t="s">
+      <c r="Q6" s="391" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="400" t="s">
+      <c r="R6" s="391" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="400" t="s">
+      <c r="S6" s="391" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="400" t="s">
+      <c r="T6" s="391" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="400" t="s">
+      <c r="U6" s="391" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="401" t="s">
+      <c r="V6" s="421" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="402"/>
-      <c r="X6" s="400" t="s">
+      <c r="W6" s="407"/>
+      <c r="X6" s="391" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="392" t="s">
+      <c r="Y6" s="390" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="392" t="s">
+      <c r="Z6" s="390" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="392" t="s">
+      <c r="AA6" s="390" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="392" t="s">
+      <c r="AB6" s="390" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="332" t="s">
+      <c r="AC6" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="332" t="s">
+      <c r="AD6" s="341" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="332" t="s">
+      <c r="AE6" s="341" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="332" t="s">
+      <c r="AF6" s="341" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="392" t="s">
+      <c r="AG6" s="390" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="332" t="s">
+      <c r="AH6" s="341" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="332" t="s">
+      <c r="AI6" s="341" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="392" t="s">
+      <c r="AJ6" s="390" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="394" t="s">
+      <c r="AK6" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="392" t="s">
+      <c r="AL6" s="390" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="392" t="s">
+      <c r="AM6" s="390" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="398" t="s">
+      <c r="AN6" s="420" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="392" t="s">
+      <c r="AO6" s="390" t="s">
         <v>63</v>
       </c>
       <c r="AP6" s="386"/>
@@ -11941,42 +11941,42 @@
       <c r="AV6" s="386"/>
       <c r="AW6" s="386"/>
       <c r="AX6" s="386"/>
-      <c r="AY6" s="388" t="s">
+      <c r="AY6" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="389"/>
-      <c r="BA6" s="389"/>
-      <c r="BB6" s="389"/>
-      <c r="BC6" s="389"/>
-      <c r="BD6" s="389"/>
-      <c r="BE6" s="389"/>
-      <c r="BF6" s="389"/>
-      <c r="BG6" s="389"/>
-      <c r="BH6" s="389"/>
-      <c r="BI6" s="389"/>
-      <c r="BJ6" s="389"/>
-      <c r="BK6" s="389"/>
-      <c r="BL6" s="390"/>
-      <c r="BM6" s="388" t="s">
+      <c r="AZ6" s="401"/>
+      <c r="BA6" s="401"/>
+      <c r="BB6" s="401"/>
+      <c r="BC6" s="401"/>
+      <c r="BD6" s="401"/>
+      <c r="BE6" s="401"/>
+      <c r="BF6" s="401"/>
+      <c r="BG6" s="401"/>
+      <c r="BH6" s="401"/>
+      <c r="BI6" s="401"/>
+      <c r="BJ6" s="401"/>
+      <c r="BK6" s="401"/>
+      <c r="BL6" s="402"/>
+      <c r="BM6" s="400" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="389"/>
-      <c r="BO6" s="389"/>
-      <c r="BP6" s="389"/>
-      <c r="BQ6" s="390"/>
-      <c r="BR6" s="385" t="s">
+      <c r="BN6" s="401"/>
+      <c r="BO6" s="401"/>
+      <c r="BP6" s="401"/>
+      <c r="BQ6" s="402"/>
+      <c r="BR6" s="388" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="385" t="s">
+      <c r="BS6" s="388" t="s">
         <v>66</v>
       </c>
       <c r="BT6" s="386"/>
       <c r="BU6" s="395"/>
-      <c r="BW6" s="412"/>
+      <c r="BW6" s="398"/>
       <c r="BX6" s="395"/>
-      <c r="BY6" s="411"/>
-      <c r="BZ6" s="411"/>
-      <c r="CA6" s="412"/>
+      <c r="BY6" s="410"/>
+      <c r="BZ6" s="410"/>
+      <c r="CA6" s="398"/>
       <c r="CB6" s="386"/>
       <c r="CC6" s="386"/>
       <c r="CD6" s="386"/>
@@ -12006,7 +12006,7 @@
       <c r="T7" s="386"/>
       <c r="U7" s="386"/>
       <c r="V7" s="396"/>
-      <c r="W7" s="403"/>
+      <c r="W7" s="422"/>
       <c r="X7" s="386"/>
       <c r="Y7" s="386"/>
       <c r="Z7" s="386"/>
@@ -12043,63 +12043,63 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="388" t="s">
+      <c r="BB7" s="400" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="391" t="s">
+      <c r="BC7" s="392" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="391" t="s">
+      <c r="BD7" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="416" t="s">
+      <c r="BE7" s="413" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="391" t="s">
+      <c r="BF7" s="392" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="391" t="s">
+      <c r="BG7" s="392" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="391" t="s">
+      <c r="BH7" s="392" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="391" t="s">
+      <c r="BI7" s="392" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="391" t="s">
+      <c r="BJ7" s="392" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="391" t="s">
+      <c r="BK7" s="392" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="418" t="s">
+      <c r="BL7" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="391" t="s">
+      <c r="BM7" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="388" t="s">
+      <c r="BN7" s="400" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="391" t="s">
+      <c r="BO7" s="392" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="388" t="s">
+      <c r="BP7" s="400" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="388" t="s">
+      <c r="BQ7" s="400" t="s">
         <v>85</v>
       </c>
       <c r="BR7" s="386"/>
       <c r="BS7" s="386"/>
       <c r="BT7" s="386"/>
       <c r="BU7" s="395"/>
-      <c r="BW7" s="412"/>
-      <c r="BX7" s="413"/>
-      <c r="BY7" s="414"/>
-      <c r="BZ7" s="414"/>
-      <c r="CA7" s="415"/>
+      <c r="BW7" s="398"/>
+      <c r="BX7" s="411"/>
+      <c r="BY7" s="412"/>
+      <c r="BZ7" s="412"/>
+      <c r="CA7" s="399"/>
       <c r="CB7" s="386"/>
       <c r="CC7" s="386"/>
       <c r="CD7" s="386"/>
@@ -12107,60 +12107,60 @@
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="387"/>
-      <c r="B8" s="387"/>
-      <c r="C8" s="387"/>
-      <c r="D8" s="387"/>
-      <c r="E8" s="387"/>
-      <c r="F8" s="387"/>
-      <c r="G8" s="387"/>
-      <c r="H8" s="387"/>
-      <c r="I8" s="387"/>
-      <c r="J8" s="387"/>
-      <c r="K8" s="387"/>
-      <c r="L8" s="387"/>
-      <c r="M8" s="387"/>
-      <c r="N8" s="387"/>
-      <c r="O8" s="387"/>
-      <c r="P8" s="387"/>
-      <c r="Q8" s="387"/>
-      <c r="R8" s="387"/>
-      <c r="S8" s="387"/>
-      <c r="T8" s="387"/>
-      <c r="U8" s="387"/>
+      <c r="A8" s="389"/>
+      <c r="B8" s="389"/>
+      <c r="C8" s="389"/>
+      <c r="D8" s="389"/>
+      <c r="E8" s="389"/>
+      <c r="F8" s="389"/>
+      <c r="G8" s="389"/>
+      <c r="H8" s="389"/>
+      <c r="I8" s="389"/>
+      <c r="J8" s="389"/>
+      <c r="K8" s="389"/>
+      <c r="L8" s="389"/>
+      <c r="M8" s="389"/>
+      <c r="N8" s="389"/>
+      <c r="O8" s="389"/>
+      <c r="P8" s="389"/>
+      <c r="Q8" s="389"/>
+      <c r="R8" s="389"/>
+      <c r="S8" s="389"/>
+      <c r="T8" s="389"/>
+      <c r="U8" s="389"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="387"/>
-      <c r="Y8" s="387"/>
-      <c r="Z8" s="387"/>
-      <c r="AA8" s="387"/>
-      <c r="AB8" s="387"/>
-      <c r="AC8" s="387"/>
-      <c r="AD8" s="387"/>
-      <c r="AE8" s="387"/>
-      <c r="AF8" s="387"/>
-      <c r="AG8" s="387"/>
-      <c r="AH8" s="387"/>
-      <c r="AI8" s="387"/>
-      <c r="AJ8" s="387"/>
+      <c r="X8" s="389"/>
+      <c r="Y8" s="389"/>
+      <c r="Z8" s="389"/>
+      <c r="AA8" s="389"/>
+      <c r="AB8" s="389"/>
+      <c r="AC8" s="389"/>
+      <c r="AD8" s="389"/>
+      <c r="AE8" s="389"/>
+      <c r="AF8" s="389"/>
+      <c r="AG8" s="389"/>
+      <c r="AH8" s="389"/>
+      <c r="AI8" s="389"/>
+      <c r="AJ8" s="389"/>
       <c r="AK8" s="396"/>
-      <c r="AL8" s="387"/>
-      <c r="AM8" s="387"/>
-      <c r="AN8" s="387"/>
-      <c r="AO8" s="387"/>
-      <c r="AP8" s="387"/>
-      <c r="AQ8" s="387"/>
-      <c r="AR8" s="387"/>
-      <c r="AS8" s="387"/>
-      <c r="AT8" s="387"/>
-      <c r="AU8" s="387"/>
-      <c r="AV8" s="387"/>
-      <c r="AW8" s="387"/>
-      <c r="AX8" s="387"/>
+      <c r="AL8" s="389"/>
+      <c r="AM8" s="389"/>
+      <c r="AN8" s="389"/>
+      <c r="AO8" s="389"/>
+      <c r="AP8" s="389"/>
+      <c r="AQ8" s="389"/>
+      <c r="AR8" s="389"/>
+      <c r="AS8" s="389"/>
+      <c r="AT8" s="389"/>
+      <c r="AU8" s="389"/>
+      <c r="AV8" s="389"/>
+      <c r="AW8" s="389"/>
+      <c r="AX8" s="389"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12170,27 +12170,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="387"/>
-      <c r="BC8" s="387"/>
-      <c r="BD8" s="387"/>
-      <c r="BE8" s="387"/>
-      <c r="BF8" s="387"/>
-      <c r="BG8" s="387"/>
-      <c r="BH8" s="387"/>
-      <c r="BI8" s="387"/>
-      <c r="BJ8" s="387"/>
-      <c r="BK8" s="387"/>
-      <c r="BL8" s="387"/>
-      <c r="BM8" s="387"/>
-      <c r="BN8" s="387"/>
-      <c r="BO8" s="387"/>
-      <c r="BP8" s="387"/>
-      <c r="BQ8" s="387"/>
-      <c r="BR8" s="387"/>
-      <c r="BS8" s="387"/>
-      <c r="BT8" s="387"/>
+      <c r="BB8" s="389"/>
+      <c r="BC8" s="389"/>
+      <c r="BD8" s="389"/>
+      <c r="BE8" s="389"/>
+      <c r="BF8" s="389"/>
+      <c r="BG8" s="389"/>
+      <c r="BH8" s="389"/>
+      <c r="BI8" s="389"/>
+      <c r="BJ8" s="389"/>
+      <c r="BK8" s="389"/>
+      <c r="BL8" s="389"/>
+      <c r="BM8" s="389"/>
+      <c r="BN8" s="389"/>
+      <c r="BO8" s="389"/>
+      <c r="BP8" s="389"/>
+      <c r="BQ8" s="389"/>
+      <c r="BR8" s="389"/>
+      <c r="BS8" s="389"/>
+      <c r="BT8" s="389"/>
       <c r="BU8" s="396"/>
-      <c r="BW8" s="415"/>
+      <c r="BW8" s="399"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12203,9 +12203,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="407"/>
-      <c r="CC8" s="407"/>
-      <c r="CD8" s="407"/>
+      <c r="CB8" s="387"/>
+      <c r="CC8" s="387"/>
+      <c r="CD8" s="387"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14663,6 +14663,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="CD5:CD8"/>
     <mergeCell ref="BR6:BR8"/>
     <mergeCell ref="AT5:AT8"/>
@@ -14679,72 +14745,6 @@
     <mergeCell ref="AY5:BQ5"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -15220,12 +15220,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="348"/>
-      <c r="BX5" s="348"/>
-      <c r="BY5" s="348"/>
-      <c r="BZ5" s="348"/>
-      <c r="CA5" s="348"/>
-      <c r="CB5" s="348"/>
+      <c r="BW5" s="370"/>
+      <c r="BX5" s="370"/>
+      <c r="BY5" s="370"/>
+      <c r="BZ5" s="370"/>
+      <c r="CA5" s="370"/>
+      <c r="CB5" s="370"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15303,12 +15303,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="348"/>
-      <c r="BX6" s="348"/>
-      <c r="BY6" s="348"/>
-      <c r="BZ6" s="348"/>
-      <c r="CA6" s="348"/>
-      <c r="CB6" s="348"/>
+      <c r="BW6" s="370"/>
+      <c r="BX6" s="370"/>
+      <c r="BY6" s="370"/>
+      <c r="BZ6" s="370"/>
+      <c r="CA6" s="370"/>
+      <c r="CB6" s="370"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15396,148 +15396,148 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="393" t="s">
+      <c r="A8" s="417" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="404" t="s">
+      <c r="B8" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="392" t="s">
+      <c r="C8" s="390" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="399" t="s">
+      <c r="D8" s="415" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="399" t="s">
+      <c r="E8" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="428" t="s">
+      <c r="F8" s="434" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="425" t="s">
+      <c r="G8" s="424" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="371" t="s">
+      <c r="H8" s="361" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="371" t="s">
+      <c r="I8" s="361" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="425" t="s">
+      <c r="J8" s="424" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="429" t="s">
+      <c r="K8" s="435" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="389"/>
-      <c r="M8" s="389"/>
-      <c r="N8" s="389"/>
-      <c r="O8" s="389"/>
-      <c r="P8" s="389"/>
-      <c r="Q8" s="389"/>
-      <c r="R8" s="389"/>
-      <c r="S8" s="389"/>
-      <c r="T8" s="389"/>
-      <c r="U8" s="389"/>
-      <c r="V8" s="389"/>
-      <c r="W8" s="389"/>
-      <c r="X8" s="389"/>
-      <c r="Y8" s="425" t="s">
+      <c r="L8" s="401"/>
+      <c r="M8" s="401"/>
+      <c r="N8" s="401"/>
+      <c r="O8" s="401"/>
+      <c r="P8" s="401"/>
+      <c r="Q8" s="401"/>
+      <c r="R8" s="401"/>
+      <c r="S8" s="401"/>
+      <c r="T8" s="401"/>
+      <c r="U8" s="401"/>
+      <c r="V8" s="401"/>
+      <c r="W8" s="401"/>
+      <c r="X8" s="401"/>
+      <c r="Y8" s="424" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="389"/>
-      <c r="AA8" s="389"/>
-      <c r="AB8" s="389"/>
-      <c r="AC8" s="389"/>
-      <c r="AD8" s="389"/>
-      <c r="AE8" s="389"/>
-      <c r="AF8" s="389"/>
-      <c r="AG8" s="389"/>
-      <c r="AH8" s="389"/>
-      <c r="AI8" s="389"/>
-      <c r="AJ8" s="389"/>
-      <c r="AK8" s="389"/>
-      <c r="AL8" s="389"/>
-      <c r="AM8" s="389"/>
-      <c r="AN8" s="389"/>
-      <c r="AO8" s="390"/>
-      <c r="AP8" s="425" t="s">
+      <c r="Z8" s="401"/>
+      <c r="AA8" s="401"/>
+      <c r="AB8" s="401"/>
+      <c r="AC8" s="401"/>
+      <c r="AD8" s="401"/>
+      <c r="AE8" s="401"/>
+      <c r="AF8" s="401"/>
+      <c r="AG8" s="401"/>
+      <c r="AH8" s="401"/>
+      <c r="AI8" s="401"/>
+      <c r="AJ8" s="401"/>
+      <c r="AK8" s="401"/>
+      <c r="AL8" s="401"/>
+      <c r="AM8" s="401"/>
+      <c r="AN8" s="401"/>
+      <c r="AO8" s="402"/>
+      <c r="AP8" s="424" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="425" t="s">
+      <c r="AQ8" s="424" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="425" t="s">
+      <c r="AR8" s="424" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="425" t="s">
+      <c r="AS8" s="424" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="425" t="s">
+      <c r="AT8" s="424" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="425" t="s">
+      <c r="AU8" s="424" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="392" t="s">
+      <c r="AV8" s="390" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="392" t="s">
+      <c r="AW8" s="390" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="392" t="s">
+      <c r="AX8" s="390" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="388" t="s">
+      <c r="AY8" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="389"/>
-      <c r="BA8" s="389"/>
-      <c r="BB8" s="389"/>
-      <c r="BC8" s="389"/>
-      <c r="BD8" s="389"/>
-      <c r="BE8" s="389"/>
-      <c r="BF8" s="389"/>
-      <c r="BG8" s="389"/>
-      <c r="BH8" s="389"/>
-      <c r="BI8" s="389"/>
-      <c r="BJ8" s="389"/>
-      <c r="BK8" s="389"/>
-      <c r="BL8" s="389"/>
-      <c r="BM8" s="389"/>
-      <c r="BN8" s="389"/>
-      <c r="BO8" s="389"/>
-      <c r="BP8" s="390"/>
-      <c r="BQ8" s="408" t="s">
+      <c r="AZ8" s="401"/>
+      <c r="BA8" s="401"/>
+      <c r="BB8" s="401"/>
+      <c r="BC8" s="401"/>
+      <c r="BD8" s="401"/>
+      <c r="BE8" s="401"/>
+      <c r="BF8" s="401"/>
+      <c r="BG8" s="401"/>
+      <c r="BH8" s="401"/>
+      <c r="BI8" s="401"/>
+      <c r="BJ8" s="401"/>
+      <c r="BK8" s="401"/>
+      <c r="BL8" s="401"/>
+      <c r="BM8" s="401"/>
+      <c r="BN8" s="401"/>
+      <c r="BO8" s="401"/>
+      <c r="BP8" s="402"/>
+      <c r="BQ8" s="406" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="402"/>
-      <c r="BS8" s="388" t="s">
+      <c r="BR8" s="407"/>
+      <c r="BS8" s="400" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="388" t="s">
+      <c r="BT8" s="400" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="419" t="s">
+      <c r="BU8" s="394" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="420" t="s">
+      <c r="BW8" s="397" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="409" t="s">
+      <c r="BX8" s="408" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="410"/>
-      <c r="BZ8" s="410"/>
-      <c r="CA8" s="402"/>
-      <c r="CB8" s="421" t="s">
+      <c r="BY8" s="409"/>
+      <c r="BZ8" s="409"/>
+      <c r="CA8" s="407"/>
+      <c r="CB8" s="403" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="349" t="s">
+      <c r="CC8" s="332" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="349" t="s">
+      <c r="CD8" s="332" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
@@ -15554,95 +15554,95 @@
       <c r="H9" s="386"/>
       <c r="I9" s="386"/>
       <c r="J9" s="386"/>
-      <c r="K9" s="422" t="s">
+      <c r="K9" s="426" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="422" t="s">
+      <c r="L9" s="426" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="422" t="s">
+      <c r="M9" s="426" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="422" t="s">
+      <c r="N9" s="426" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="422" t="s">
+      <c r="O9" s="426" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="422" t="s">
+      <c r="P9" s="426" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="422" t="s">
+      <c r="Q9" s="426" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="422" t="s">
+      <c r="R9" s="426" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="422" t="s">
+      <c r="S9" s="426" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="422" t="s">
+      <c r="T9" s="426" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="422" t="s">
+      <c r="U9" s="426" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="434" t="s">
+      <c r="V9" s="429" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="402"/>
-      <c r="X9" s="422" t="s">
+      <c r="W9" s="407"/>
+      <c r="X9" s="426" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="424" t="s">
+      <c r="Y9" s="423" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="424" t="s">
+      <c r="Z9" s="423" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="424" t="s">
+      <c r="AA9" s="423" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="424" t="s">
+      <c r="AB9" s="423" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="338" t="s">
+      <c r="AC9" s="335" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="338" t="s">
+      <c r="AD9" s="335" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="338" t="s">
+      <c r="AE9" s="335" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="338" t="s">
+      <c r="AF9" s="335" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="424" t="s">
+      <c r="AG9" s="423" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="338" t="s">
+      <c r="AH9" s="335" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="338" t="s">
+      <c r="AI9" s="335" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="424" t="s">
+      <c r="AJ9" s="423" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="394" t="s">
+      <c r="AK9" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="392" t="s">
+      <c r="AL9" s="390" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="424" t="s">
+      <c r="AM9" s="423" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="398" t="s">
+      <c r="AN9" s="420" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="392" t="s">
+      <c r="AO9" s="390" t="s">
         <v>63</v>
       </c>
       <c r="AP9" s="386"/>
@@ -15654,43 +15654,43 @@
       <c r="AV9" s="386"/>
       <c r="AW9" s="386"/>
       <c r="AX9" s="386"/>
-      <c r="AY9" s="388" t="s">
+      <c r="AY9" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="389"/>
-      <c r="BA9" s="389"/>
-      <c r="BB9" s="389"/>
-      <c r="BC9" s="389"/>
-      <c r="BD9" s="389"/>
-      <c r="BE9" s="389"/>
-      <c r="BF9" s="389"/>
-      <c r="BG9" s="389"/>
-      <c r="BH9" s="389"/>
-      <c r="BI9" s="389"/>
-      <c r="BJ9" s="390"/>
-      <c r="BK9" s="388" t="s">
+      <c r="AZ9" s="401"/>
+      <c r="BA9" s="401"/>
+      <c r="BB9" s="401"/>
+      <c r="BC9" s="401"/>
+      <c r="BD9" s="401"/>
+      <c r="BE9" s="401"/>
+      <c r="BF9" s="401"/>
+      <c r="BG9" s="401"/>
+      <c r="BH9" s="401"/>
+      <c r="BI9" s="401"/>
+      <c r="BJ9" s="402"/>
+      <c r="BK9" s="400" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="389"/>
-      <c r="BM9" s="389"/>
-      <c r="BN9" s="389"/>
-      <c r="BO9" s="389"/>
-      <c r="BP9" s="390"/>
-      <c r="BQ9" s="385" t="s">
+      <c r="BL9" s="401"/>
+      <c r="BM9" s="401"/>
+      <c r="BN9" s="401"/>
+      <c r="BO9" s="401"/>
+      <c r="BP9" s="402"/>
+      <c r="BQ9" s="388" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="385" t="s">
+      <c r="BR9" s="388" t="s">
         <v>66</v>
       </c>
       <c r="BS9" s="386"/>
       <c r="BT9" s="386"/>
       <c r="BU9" s="395"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="412"/>
+      <c r="BW9" s="398"/>
       <c r="BX9" s="395"/>
-      <c r="BY9" s="426"/>
-      <c r="BZ9" s="426"/>
-      <c r="CA9" s="412"/>
+      <c r="BY9" s="436"/>
+      <c r="BZ9" s="436"/>
+      <c r="CA9" s="398"/>
       <c r="CB9" s="386"/>
       <c r="CC9" s="386"/>
       <c r="CD9" s="386"/>
@@ -15720,7 +15720,7 @@
       <c r="T10" s="386"/>
       <c r="U10" s="386"/>
       <c r="V10" s="396"/>
-      <c r="W10" s="403"/>
+      <c r="W10" s="422"/>
       <c r="X10" s="386"/>
       <c r="Y10" s="386"/>
       <c r="Z10" s="386"/>
@@ -15760,46 +15760,46 @@
       <c r="BB10" s="433" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="423" t="s">
+      <c r="BC10" s="427" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="423" t="s">
+      <c r="BD10" s="427" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="423" t="s">
+      <c r="BE10" s="427" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="423" t="s">
+      <c r="BF10" s="427" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="423" t="s">
+      <c r="BG10" s="427" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="423" t="s">
+      <c r="BH10" s="427" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="423" t="s">
+      <c r="BI10" s="427" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="435" t="s">
+      <c r="BJ10" s="425" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="423" t="s">
+      <c r="BK10" s="427" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="427" t="s">
+      <c r="BL10" s="428" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="423" t="s">
+      <c r="BM10" s="427" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="427" t="s">
+      <c r="BN10" s="428" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="427" t="s">
+      <c r="BO10" s="428" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="388" t="s">
+      <c r="BP10" s="400" t="s">
         <v>85</v>
       </c>
       <c r="BQ10" s="386"/>
@@ -15808,11 +15808,11 @@
       <c r="BT10" s="386"/>
       <c r="BU10" s="395"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="412"/>
-      <c r="BX10" s="413"/>
-      <c r="BY10" s="414"/>
-      <c r="BZ10" s="414"/>
-      <c r="CA10" s="415"/>
+      <c r="BW10" s="398"/>
+      <c r="BX10" s="411"/>
+      <c r="BY10" s="412"/>
+      <c r="BZ10" s="412"/>
+      <c r="CA10" s="399"/>
       <c r="CB10" s="386"/>
       <c r="CC10" s="386"/>
       <c r="CD10" s="386"/>
@@ -15820,60 +15820,60 @@
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="387"/>
-      <c r="B11" s="387"/>
-      <c r="C11" s="387"/>
-      <c r="D11" s="387"/>
-      <c r="E11" s="387"/>
-      <c r="F11" s="387"/>
-      <c r="G11" s="387"/>
-      <c r="H11" s="387"/>
-      <c r="I11" s="387"/>
-      <c r="J11" s="387"/>
-      <c r="K11" s="387"/>
-      <c r="L11" s="387"/>
-      <c r="M11" s="387"/>
-      <c r="N11" s="387"/>
-      <c r="O11" s="387"/>
-      <c r="P11" s="387"/>
-      <c r="Q11" s="387"/>
-      <c r="R11" s="387"/>
-      <c r="S11" s="387"/>
-      <c r="T11" s="387"/>
-      <c r="U11" s="387"/>
+      <c r="A11" s="389"/>
+      <c r="B11" s="389"/>
+      <c r="C11" s="389"/>
+      <c r="D11" s="389"/>
+      <c r="E11" s="389"/>
+      <c r="F11" s="389"/>
+      <c r="G11" s="389"/>
+      <c r="H11" s="389"/>
+      <c r="I11" s="389"/>
+      <c r="J11" s="389"/>
+      <c r="K11" s="389"/>
+      <c r="L11" s="389"/>
+      <c r="M11" s="389"/>
+      <c r="N11" s="389"/>
+      <c r="O11" s="389"/>
+      <c r="P11" s="389"/>
+      <c r="Q11" s="389"/>
+      <c r="R11" s="389"/>
+      <c r="S11" s="389"/>
+      <c r="T11" s="389"/>
+      <c r="U11" s="389"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="387"/>
-      <c r="Y11" s="387"/>
-      <c r="Z11" s="387"/>
-      <c r="AA11" s="387"/>
-      <c r="AB11" s="387"/>
-      <c r="AC11" s="387"/>
-      <c r="AD11" s="387"/>
-      <c r="AE11" s="387"/>
-      <c r="AF11" s="387"/>
-      <c r="AG11" s="387"/>
-      <c r="AH11" s="387"/>
-      <c r="AI11" s="387"/>
-      <c r="AJ11" s="387"/>
+      <c r="X11" s="389"/>
+      <c r="Y11" s="389"/>
+      <c r="Z11" s="389"/>
+      <c r="AA11" s="389"/>
+      <c r="AB11" s="389"/>
+      <c r="AC11" s="389"/>
+      <c r="AD11" s="389"/>
+      <c r="AE11" s="389"/>
+      <c r="AF11" s="389"/>
+      <c r="AG11" s="389"/>
+      <c r="AH11" s="389"/>
+      <c r="AI11" s="389"/>
+      <c r="AJ11" s="389"/>
       <c r="AK11" s="396"/>
-      <c r="AL11" s="387"/>
-      <c r="AM11" s="387"/>
-      <c r="AN11" s="387"/>
-      <c r="AO11" s="387"/>
-      <c r="AP11" s="387"/>
-      <c r="AQ11" s="387"/>
-      <c r="AR11" s="387"/>
-      <c r="AS11" s="387"/>
-      <c r="AT11" s="387"/>
-      <c r="AU11" s="387"/>
-      <c r="AV11" s="387"/>
-      <c r="AW11" s="387"/>
-      <c r="AX11" s="387"/>
+      <c r="AL11" s="389"/>
+      <c r="AM11" s="389"/>
+      <c r="AN11" s="389"/>
+      <c r="AO11" s="389"/>
+      <c r="AP11" s="389"/>
+      <c r="AQ11" s="389"/>
+      <c r="AR11" s="389"/>
+      <c r="AS11" s="389"/>
+      <c r="AT11" s="389"/>
+      <c r="AU11" s="389"/>
+      <c r="AV11" s="389"/>
+      <c r="AW11" s="389"/>
+      <c r="AX11" s="389"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15883,28 +15883,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="387"/>
-      <c r="BC11" s="387"/>
-      <c r="BD11" s="387"/>
-      <c r="BE11" s="387"/>
-      <c r="BF11" s="387"/>
-      <c r="BG11" s="387"/>
-      <c r="BH11" s="387"/>
-      <c r="BI11" s="387"/>
-      <c r="BJ11" s="387"/>
-      <c r="BK11" s="387"/>
-      <c r="BL11" s="387"/>
-      <c r="BM11" s="387"/>
-      <c r="BN11" s="387"/>
-      <c r="BO11" s="387"/>
-      <c r="BP11" s="387"/>
-      <c r="BQ11" s="387"/>
-      <c r="BR11" s="387"/>
-      <c r="BS11" s="387"/>
-      <c r="BT11" s="387"/>
+      <c r="BB11" s="389"/>
+      <c r="BC11" s="389"/>
+      <c r="BD11" s="389"/>
+      <c r="BE11" s="389"/>
+      <c r="BF11" s="389"/>
+      <c r="BG11" s="389"/>
+      <c r="BH11" s="389"/>
+      <c r="BI11" s="389"/>
+      <c r="BJ11" s="389"/>
+      <c r="BK11" s="389"/>
+      <c r="BL11" s="389"/>
+      <c r="BM11" s="389"/>
+      <c r="BN11" s="389"/>
+      <c r="BO11" s="389"/>
+      <c r="BP11" s="389"/>
+      <c r="BQ11" s="389"/>
+      <c r="BR11" s="389"/>
+      <c r="BS11" s="389"/>
+      <c r="BT11" s="389"/>
       <c r="BU11" s="396"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="415"/>
+      <c r="BW11" s="399"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15917,9 +15917,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="407"/>
-      <c r="CC11" s="407"/>
-      <c r="CD11" s="407"/>
+      <c r="CB11" s="387"/>
+      <c r="CC11" s="387"/>
+      <c r="CD11" s="387"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18320,14 +18320,64 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="BQ8:BR8"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="G8:G11"/>
     <mergeCell ref="BS8:BS11"/>
@@ -18344,64 +18394,14 @@
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="BQ8:BR8"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18631,87 +18631,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="417"/>
-      <c r="B3" s="406"/>
-      <c r="C3" s="406"/>
-      <c r="D3" s="406"/>
-      <c r="E3" s="406"/>
-      <c r="F3" s="406"/>
-      <c r="G3" s="406"/>
-      <c r="H3" s="406"/>
-      <c r="I3" s="406"/>
-      <c r="J3" s="406"/>
-      <c r="K3" s="406"/>
-      <c r="L3" s="406"/>
-      <c r="M3" s="406"/>
-      <c r="N3" s="406"/>
-      <c r="O3" s="406"/>
-      <c r="P3" s="406"/>
-      <c r="Q3" s="406"/>
-      <c r="R3" s="406"/>
-      <c r="S3" s="406"/>
-      <c r="T3" s="406"/>
-      <c r="U3" s="406"/>
-      <c r="V3" s="406"/>
-      <c r="W3" s="406"/>
-      <c r="X3" s="406"/>
-      <c r="Y3" s="406"/>
-      <c r="Z3" s="406"/>
-      <c r="AA3" s="406"/>
-      <c r="AB3" s="406"/>
-      <c r="AC3" s="406"/>
-      <c r="AD3" s="406"/>
-      <c r="AE3" s="406"/>
-      <c r="AF3" s="406"/>
-      <c r="AG3" s="406"/>
-      <c r="AH3" s="406"/>
-      <c r="AI3" s="406"/>
-      <c r="AJ3" s="406"/>
-      <c r="AK3" s="406"/>
-      <c r="AL3" s="406"/>
-      <c r="AM3" s="406"/>
-      <c r="AN3" s="406"/>
-      <c r="AO3" s="406"/>
-      <c r="AP3" s="406"/>
-      <c r="AQ3" s="406"/>
-      <c r="AR3" s="406"/>
-      <c r="AS3" s="406"/>
-      <c r="AT3" s="406"/>
-      <c r="AU3" s="406"/>
-      <c r="AV3" s="406"/>
-      <c r="AW3" s="406"/>
-      <c r="AX3" s="406"/>
-      <c r="AY3" s="406"/>
-      <c r="AZ3" s="406"/>
-      <c r="BA3" s="406"/>
-      <c r="BB3" s="406"/>
-      <c r="BC3" s="406"/>
-      <c r="BD3" s="406"/>
-      <c r="BE3" s="406"/>
-      <c r="BF3" s="406"/>
-      <c r="BG3" s="406"/>
-      <c r="BH3" s="406"/>
-      <c r="BI3" s="406"/>
-      <c r="BJ3" s="406"/>
-      <c r="BK3" s="406"/>
-      <c r="BL3" s="406"/>
-      <c r="BM3" s="406"/>
-      <c r="BN3" s="406"/>
-      <c r="BO3" s="406"/>
-      <c r="BP3" s="406"/>
-      <c r="BQ3" s="406"/>
-      <c r="BR3" s="406"/>
-      <c r="BS3" s="406"/>
-      <c r="BT3" s="406"/>
-      <c r="BU3" s="406"/>
-      <c r="BW3" s="405" t="s">
+      <c r="A3" s="414"/>
+      <c r="B3" s="405"/>
+      <c r="C3" s="405"/>
+      <c r="D3" s="405"/>
+      <c r="E3" s="405"/>
+      <c r="F3" s="405"/>
+      <c r="G3" s="405"/>
+      <c r="H3" s="405"/>
+      <c r="I3" s="405"/>
+      <c r="J3" s="405"/>
+      <c r="K3" s="405"/>
+      <c r="L3" s="405"/>
+      <c r="M3" s="405"/>
+      <c r="N3" s="405"/>
+      <c r="O3" s="405"/>
+      <c r="P3" s="405"/>
+      <c r="Q3" s="405"/>
+      <c r="R3" s="405"/>
+      <c r="S3" s="405"/>
+      <c r="T3" s="405"/>
+      <c r="U3" s="405"/>
+      <c r="V3" s="405"/>
+      <c r="W3" s="405"/>
+      <c r="X3" s="405"/>
+      <c r="Y3" s="405"/>
+      <c r="Z3" s="405"/>
+      <c r="AA3" s="405"/>
+      <c r="AB3" s="405"/>
+      <c r="AC3" s="405"/>
+      <c r="AD3" s="405"/>
+      <c r="AE3" s="405"/>
+      <c r="AF3" s="405"/>
+      <c r="AG3" s="405"/>
+      <c r="AH3" s="405"/>
+      <c r="AI3" s="405"/>
+      <c r="AJ3" s="405"/>
+      <c r="AK3" s="405"/>
+      <c r="AL3" s="405"/>
+      <c r="AM3" s="405"/>
+      <c r="AN3" s="405"/>
+      <c r="AO3" s="405"/>
+      <c r="AP3" s="405"/>
+      <c r="AQ3" s="405"/>
+      <c r="AR3" s="405"/>
+      <c r="AS3" s="405"/>
+      <c r="AT3" s="405"/>
+      <c r="AU3" s="405"/>
+      <c r="AV3" s="405"/>
+      <c r="AW3" s="405"/>
+      <c r="AX3" s="405"/>
+      <c r="AY3" s="405"/>
+      <c r="AZ3" s="405"/>
+      <c r="BA3" s="405"/>
+      <c r="BB3" s="405"/>
+      <c r="BC3" s="405"/>
+      <c r="BD3" s="405"/>
+      <c r="BE3" s="405"/>
+      <c r="BF3" s="405"/>
+      <c r="BG3" s="405"/>
+      <c r="BH3" s="405"/>
+      <c r="BI3" s="405"/>
+      <c r="BJ3" s="405"/>
+      <c r="BK3" s="405"/>
+      <c r="BL3" s="405"/>
+      <c r="BM3" s="405"/>
+      <c r="BN3" s="405"/>
+      <c r="BO3" s="405"/>
+      <c r="BP3" s="405"/>
+      <c r="BQ3" s="405"/>
+      <c r="BR3" s="405"/>
+      <c r="BS3" s="405"/>
+      <c r="BT3" s="405"/>
+      <c r="BU3" s="405"/>
+      <c r="BW3" s="404" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="406"/>
-      <c r="BY3" s="406"/>
-      <c r="BZ3" s="406"/>
-      <c r="CA3" s="406"/>
-      <c r="CB3" s="406"/>
+      <c r="BX3" s="405"/>
+      <c r="BY3" s="405"/>
+      <c r="BZ3" s="405"/>
+      <c r="CA3" s="405"/>
+      <c r="CB3" s="405"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18794,157 +18794,157 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="406"/>
-      <c r="BX4" s="406"/>
-      <c r="BY4" s="406"/>
-      <c r="BZ4" s="406"/>
-      <c r="CA4" s="406"/>
-      <c r="CB4" s="406"/>
+      <c r="BW4" s="405"/>
+      <c r="BX4" s="405"/>
+      <c r="BY4" s="405"/>
+      <c r="BZ4" s="405"/>
+      <c r="CA4" s="405"/>
+      <c r="CB4" s="405"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="393" t="s">
+      <c r="A5" s="417" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="404" t="s">
+      <c r="B5" s="416" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="392" t="s">
+      <c r="C5" s="390" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="399" t="s">
+      <c r="D5" s="415" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="399" t="s">
+      <c r="E5" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="428" t="s">
+      <c r="F5" s="434" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="392" t="s">
+      <c r="G5" s="390" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="332" t="s">
+      <c r="H5" s="341" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="332" t="s">
+      <c r="I5" s="341" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="392" t="s">
+      <c r="J5" s="390" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="397" t="s">
+      <c r="K5" s="419" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="389"/>
-      <c r="M5" s="389"/>
-      <c r="N5" s="389"/>
-      <c r="O5" s="389"/>
-      <c r="P5" s="389"/>
-      <c r="Q5" s="389"/>
-      <c r="R5" s="389"/>
-      <c r="S5" s="389"/>
-      <c r="T5" s="389"/>
-      <c r="U5" s="389"/>
-      <c r="V5" s="389"/>
-      <c r="W5" s="389"/>
-      <c r="X5" s="389"/>
-      <c r="Y5" s="392" t="s">
+      <c r="L5" s="401"/>
+      <c r="M5" s="401"/>
+      <c r="N5" s="401"/>
+      <c r="O5" s="401"/>
+      <c r="P5" s="401"/>
+      <c r="Q5" s="401"/>
+      <c r="R5" s="401"/>
+      <c r="S5" s="401"/>
+      <c r="T5" s="401"/>
+      <c r="U5" s="401"/>
+      <c r="V5" s="401"/>
+      <c r="W5" s="401"/>
+      <c r="X5" s="401"/>
+      <c r="Y5" s="390" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="389"/>
-      <c r="AA5" s="389"/>
-      <c r="AB5" s="389"/>
-      <c r="AC5" s="389"/>
-      <c r="AD5" s="389"/>
-      <c r="AE5" s="389"/>
-      <c r="AF5" s="389"/>
-      <c r="AG5" s="389"/>
-      <c r="AH5" s="389"/>
-      <c r="AI5" s="389"/>
-      <c r="AJ5" s="389"/>
-      <c r="AK5" s="389"/>
-      <c r="AL5" s="389"/>
-      <c r="AM5" s="389"/>
-      <c r="AN5" s="389"/>
-      <c r="AO5" s="390"/>
-      <c r="AP5" s="392" t="s">
+      <c r="Z5" s="401"/>
+      <c r="AA5" s="401"/>
+      <c r="AB5" s="401"/>
+      <c r="AC5" s="401"/>
+      <c r="AD5" s="401"/>
+      <c r="AE5" s="401"/>
+      <c r="AF5" s="401"/>
+      <c r="AG5" s="401"/>
+      <c r="AH5" s="401"/>
+      <c r="AI5" s="401"/>
+      <c r="AJ5" s="401"/>
+      <c r="AK5" s="401"/>
+      <c r="AL5" s="401"/>
+      <c r="AM5" s="401"/>
+      <c r="AN5" s="401"/>
+      <c r="AO5" s="402"/>
+      <c r="AP5" s="390" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="392" t="s">
+      <c r="AQ5" s="390" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="392" t="s">
+      <c r="AR5" s="390" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="392" t="s">
+      <c r="AS5" s="390" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="392" t="s">
+      <c r="AT5" s="390" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="392" t="s">
+      <c r="AU5" s="390" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="392" t="s">
+      <c r="AV5" s="390" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="392" t="s">
+      <c r="AW5" s="390" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="392" t="s">
+      <c r="AX5" s="390" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="388" t="s">
+      <c r="AY5" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="389"/>
-      <c r="BA5" s="389"/>
-      <c r="BB5" s="389"/>
-      <c r="BC5" s="389"/>
-      <c r="BD5" s="389"/>
-      <c r="BE5" s="389"/>
-      <c r="BF5" s="389"/>
-      <c r="BG5" s="389"/>
-      <c r="BH5" s="389"/>
-      <c r="BI5" s="389"/>
-      <c r="BJ5" s="389"/>
-      <c r="BK5" s="389"/>
-      <c r="BL5" s="389"/>
-      <c r="BM5" s="389"/>
-      <c r="BN5" s="389"/>
-      <c r="BO5" s="389"/>
-      <c r="BP5" s="390"/>
-      <c r="BQ5" s="408" t="s">
+      <c r="AZ5" s="401"/>
+      <c r="BA5" s="401"/>
+      <c r="BB5" s="401"/>
+      <c r="BC5" s="401"/>
+      <c r="BD5" s="401"/>
+      <c r="BE5" s="401"/>
+      <c r="BF5" s="401"/>
+      <c r="BG5" s="401"/>
+      <c r="BH5" s="401"/>
+      <c r="BI5" s="401"/>
+      <c r="BJ5" s="401"/>
+      <c r="BK5" s="401"/>
+      <c r="BL5" s="401"/>
+      <c r="BM5" s="401"/>
+      <c r="BN5" s="401"/>
+      <c r="BO5" s="401"/>
+      <c r="BP5" s="402"/>
+      <c r="BQ5" s="406" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="402"/>
-      <c r="BS5" s="388" t="s">
+      <c r="BR5" s="407"/>
+      <c r="BS5" s="400" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="388" t="s">
+      <c r="BT5" s="400" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="419" t="s">
+      <c r="BU5" s="394" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="420" t="s">
+      <c r="BW5" s="397" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="409" t="s">
+      <c r="BX5" s="408" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="410"/>
-      <c r="BZ5" s="410"/>
-      <c r="CA5" s="402"/>
-      <c r="CB5" s="421" t="s">
+      <c r="BY5" s="409"/>
+      <c r="BZ5" s="409"/>
+      <c r="CA5" s="407"/>
+      <c r="CB5" s="403" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="349" t="s">
+      <c r="CC5" s="332" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="349" t="s">
+      <c r="CD5" s="332" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
@@ -18961,95 +18961,95 @@
       <c r="H6" s="386"/>
       <c r="I6" s="386"/>
       <c r="J6" s="386"/>
-      <c r="K6" s="400" t="s">
+      <c r="K6" s="391" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="400" t="s">
+      <c r="L6" s="391" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="400" t="s">
+      <c r="M6" s="391" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="400" t="s">
+      <c r="N6" s="391" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="400" t="s">
+      <c r="O6" s="391" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="400" t="s">
+      <c r="P6" s="391" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="400" t="s">
+      <c r="Q6" s="391" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="400" t="s">
+      <c r="R6" s="391" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="400" t="s">
+      <c r="S6" s="391" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="400" t="s">
+      <c r="T6" s="391" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="400" t="s">
+      <c r="U6" s="391" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="401" t="s">
+      <c r="V6" s="421" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="402"/>
-      <c r="X6" s="400" t="s">
+      <c r="W6" s="407"/>
+      <c r="X6" s="391" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="392" t="s">
+      <c r="Y6" s="390" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="392" t="s">
+      <c r="Z6" s="390" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="392" t="s">
+      <c r="AA6" s="390" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="392" t="s">
+      <c r="AB6" s="390" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="332" t="s">
+      <c r="AC6" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="332" t="s">
+      <c r="AD6" s="341" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="332" t="s">
+      <c r="AE6" s="341" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="332" t="s">
+      <c r="AF6" s="341" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="392" t="s">
+      <c r="AG6" s="390" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="332" t="s">
+      <c r="AH6" s="341" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="332" t="s">
+      <c r="AI6" s="341" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="392" t="s">
+      <c r="AJ6" s="390" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="394" t="s">
+      <c r="AK6" s="418" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="392" t="s">
+      <c r="AL6" s="390" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="392" t="s">
+      <c r="AM6" s="390" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="398" t="s">
+      <c r="AN6" s="420" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="392" t="s">
+      <c r="AO6" s="390" t="s">
         <v>63</v>
       </c>
       <c r="AP6" s="386"/>
@@ -19061,42 +19061,42 @@
       <c r="AV6" s="386"/>
       <c r="AW6" s="386"/>
       <c r="AX6" s="386"/>
-      <c r="AY6" s="388" t="s">
+      <c r="AY6" s="400" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="389"/>
-      <c r="BA6" s="389"/>
-      <c r="BB6" s="389"/>
-      <c r="BC6" s="389"/>
-      <c r="BD6" s="389"/>
-      <c r="BE6" s="389"/>
-      <c r="BF6" s="389"/>
-      <c r="BG6" s="389"/>
-      <c r="BH6" s="389"/>
-      <c r="BI6" s="389"/>
-      <c r="BJ6" s="390"/>
-      <c r="BK6" s="388" t="s">
+      <c r="AZ6" s="401"/>
+      <c r="BA6" s="401"/>
+      <c r="BB6" s="401"/>
+      <c r="BC6" s="401"/>
+      <c r="BD6" s="401"/>
+      <c r="BE6" s="401"/>
+      <c r="BF6" s="401"/>
+      <c r="BG6" s="401"/>
+      <c r="BH6" s="401"/>
+      <c r="BI6" s="401"/>
+      <c r="BJ6" s="402"/>
+      <c r="BK6" s="400" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="389"/>
-      <c r="BM6" s="389"/>
-      <c r="BN6" s="389"/>
-      <c r="BO6" s="389"/>
-      <c r="BP6" s="390"/>
-      <c r="BQ6" s="385" t="s">
+      <c r="BL6" s="401"/>
+      <c r="BM6" s="401"/>
+      <c r="BN6" s="401"/>
+      <c r="BO6" s="401"/>
+      <c r="BP6" s="402"/>
+      <c r="BQ6" s="388" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="385" t="s">
+      <c r="BR6" s="388" t="s">
         <v>66</v>
       </c>
       <c r="BS6" s="386"/>
       <c r="BT6" s="386"/>
       <c r="BU6" s="395"/>
-      <c r="BW6" s="412"/>
+      <c r="BW6" s="398"/>
       <c r="BX6" s="395"/>
-      <c r="BY6" s="411"/>
-      <c r="BZ6" s="411"/>
-      <c r="CA6" s="412"/>
+      <c r="BY6" s="410"/>
+      <c r="BZ6" s="410"/>
+      <c r="CA6" s="398"/>
       <c r="CB6" s="386"/>
       <c r="CC6" s="386"/>
       <c r="CD6" s="386"/>
@@ -19126,7 +19126,7 @@
       <c r="T7" s="386"/>
       <c r="U7" s="386"/>
       <c r="V7" s="396"/>
-      <c r="W7" s="403"/>
+      <c r="W7" s="422"/>
       <c r="X7" s="386"/>
       <c r="Y7" s="386"/>
       <c r="Z7" s="386"/>
@@ -19163,49 +19163,49 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="388" t="s">
+      <c r="BB7" s="400" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="391" t="s">
+      <c r="BC7" s="392" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="391" t="s">
+      <c r="BD7" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="391" t="s">
+      <c r="BE7" s="392" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="391" t="s">
+      <c r="BF7" s="392" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="391" t="s">
+      <c r="BG7" s="392" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="391" t="s">
+      <c r="BH7" s="392" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="391" t="s">
+      <c r="BI7" s="392" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="418" t="s">
+      <c r="BJ7" s="393" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="391" t="s">
+      <c r="BK7" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="388" t="s">
+      <c r="BL7" s="400" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="391" t="s">
+      <c r="BM7" s="392" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="388" t="s">
+      <c r="BN7" s="400" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="388" t="s">
+      <c r="BO7" s="400" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="388" t="s">
+      <c r="BP7" s="400" t="s">
         <v>85</v>
       </c>
       <c r="BQ7" s="386"/>
@@ -19213,11 +19213,11 @@
       <c r="BS7" s="386"/>
       <c r="BT7" s="386"/>
       <c r="BU7" s="395"/>
-      <c r="BW7" s="412"/>
-      <c r="BX7" s="413"/>
-      <c r="BY7" s="414"/>
-      <c r="BZ7" s="414"/>
-      <c r="CA7" s="415"/>
+      <c r="BW7" s="398"/>
+      <c r="BX7" s="411"/>
+      <c r="BY7" s="412"/>
+      <c r="BZ7" s="412"/>
+      <c r="CA7" s="399"/>
       <c r="CB7" s="386"/>
       <c r="CC7" s="386"/>
       <c r="CD7" s="386"/>
@@ -19225,60 +19225,60 @@
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="387"/>
-      <c r="B8" s="387"/>
-      <c r="C8" s="387"/>
-      <c r="D8" s="387"/>
-      <c r="E8" s="387"/>
-      <c r="F8" s="387"/>
-      <c r="G8" s="387"/>
-      <c r="H8" s="387"/>
-      <c r="I8" s="387"/>
-      <c r="J8" s="387"/>
-      <c r="K8" s="387"/>
-      <c r="L8" s="387"/>
-      <c r="M8" s="387"/>
-      <c r="N8" s="387"/>
-      <c r="O8" s="387"/>
-      <c r="P8" s="387"/>
-      <c r="Q8" s="387"/>
-      <c r="R8" s="387"/>
-      <c r="S8" s="387"/>
-      <c r="T8" s="387"/>
-      <c r="U8" s="387"/>
+      <c r="A8" s="389"/>
+      <c r="B8" s="389"/>
+      <c r="C8" s="389"/>
+      <c r="D8" s="389"/>
+      <c r="E8" s="389"/>
+      <c r="F8" s="389"/>
+      <c r="G8" s="389"/>
+      <c r="H8" s="389"/>
+      <c r="I8" s="389"/>
+      <c r="J8" s="389"/>
+      <c r="K8" s="389"/>
+      <c r="L8" s="389"/>
+      <c r="M8" s="389"/>
+      <c r="N8" s="389"/>
+      <c r="O8" s="389"/>
+      <c r="P8" s="389"/>
+      <c r="Q8" s="389"/>
+      <c r="R8" s="389"/>
+      <c r="S8" s="389"/>
+      <c r="T8" s="389"/>
+      <c r="U8" s="389"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="387"/>
-      <c r="Y8" s="387"/>
-      <c r="Z8" s="387"/>
-      <c r="AA8" s="387"/>
-      <c r="AB8" s="387"/>
-      <c r="AC8" s="387"/>
-      <c r="AD8" s="387"/>
-      <c r="AE8" s="387"/>
-      <c r="AF8" s="387"/>
-      <c r="AG8" s="387"/>
-      <c r="AH8" s="387"/>
-      <c r="AI8" s="387"/>
-      <c r="AJ8" s="387"/>
+      <c r="X8" s="389"/>
+      <c r="Y8" s="389"/>
+      <c r="Z8" s="389"/>
+      <c r="AA8" s="389"/>
+      <c r="AB8" s="389"/>
+      <c r="AC8" s="389"/>
+      <c r="AD8" s="389"/>
+      <c r="AE8" s="389"/>
+      <c r="AF8" s="389"/>
+      <c r="AG8" s="389"/>
+      <c r="AH8" s="389"/>
+      <c r="AI8" s="389"/>
+      <c r="AJ8" s="389"/>
       <c r="AK8" s="396"/>
-      <c r="AL8" s="387"/>
-      <c r="AM8" s="387"/>
-      <c r="AN8" s="387"/>
-      <c r="AO8" s="387"/>
-      <c r="AP8" s="387"/>
-      <c r="AQ8" s="387"/>
-      <c r="AR8" s="387"/>
-      <c r="AS8" s="387"/>
-      <c r="AT8" s="387"/>
-      <c r="AU8" s="387"/>
-      <c r="AV8" s="387"/>
-      <c r="AW8" s="387"/>
-      <c r="AX8" s="387"/>
+      <c r="AL8" s="389"/>
+      <c r="AM8" s="389"/>
+      <c r="AN8" s="389"/>
+      <c r="AO8" s="389"/>
+      <c r="AP8" s="389"/>
+      <c r="AQ8" s="389"/>
+      <c r="AR8" s="389"/>
+      <c r="AS8" s="389"/>
+      <c r="AT8" s="389"/>
+      <c r="AU8" s="389"/>
+      <c r="AV8" s="389"/>
+      <c r="AW8" s="389"/>
+      <c r="AX8" s="389"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19288,27 +19288,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="387"/>
-      <c r="BC8" s="387"/>
-      <c r="BD8" s="387"/>
-      <c r="BE8" s="387"/>
-      <c r="BF8" s="387"/>
-      <c r="BG8" s="387"/>
-      <c r="BH8" s="387"/>
-      <c r="BI8" s="387"/>
-      <c r="BJ8" s="387"/>
-      <c r="BK8" s="387"/>
-      <c r="BL8" s="387"/>
-      <c r="BM8" s="387"/>
-      <c r="BN8" s="387"/>
-      <c r="BO8" s="387"/>
-      <c r="BP8" s="387"/>
-      <c r="BQ8" s="387"/>
-      <c r="BR8" s="387"/>
-      <c r="BS8" s="387"/>
-      <c r="BT8" s="387"/>
+      <c r="BB8" s="389"/>
+      <c r="BC8" s="389"/>
+      <c r="BD8" s="389"/>
+      <c r="BE8" s="389"/>
+      <c r="BF8" s="389"/>
+      <c r="BG8" s="389"/>
+      <c r="BH8" s="389"/>
+      <c r="BI8" s="389"/>
+      <c r="BJ8" s="389"/>
+      <c r="BK8" s="389"/>
+      <c r="BL8" s="389"/>
+      <c r="BM8" s="389"/>
+      <c r="BN8" s="389"/>
+      <c r="BO8" s="389"/>
+      <c r="BP8" s="389"/>
+      <c r="BQ8" s="389"/>
+      <c r="BR8" s="389"/>
+      <c r="BS8" s="389"/>
+      <c r="BT8" s="389"/>
       <c r="BU8" s="396"/>
-      <c r="BW8" s="415"/>
+      <c r="BW8" s="399"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19321,9 +19321,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="407"/>
-      <c r="CC8" s="407"/>
-      <c r="CD8" s="407"/>
+      <c r="CB8" s="387"/>
+      <c r="CC8" s="387"/>
+      <c r="CD8" s="387"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21330,6 +21330,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BE7:BE8"/>
     <mergeCell ref="AU5:AU8"/>
     <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="A5:A8"/>
@@ -21346,72 +21412,6 @@
     <mergeCell ref="AI6:AI8"/>
     <mergeCell ref="BU5:BU8"/>
     <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>

--- a/thaco/color/1_Office_color.xlsx
+++ b/thaco/color/1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB52E758-EA33-4246-88D8-2D6D676EBBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974E8750-93BA-534D-B323-F3F0640C665D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39900" yWindow="500" windowWidth="37160" windowHeight="21040" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4545,7 +4545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="162">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -6766,90 +6766,55 @@
     <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="74" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="71" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6873,45 +6838,88 @@
     <xf numFmtId="0" fontId="57" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="57" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="65" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="42" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="73" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6920,10 +6928,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6931,77 +6939,69 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7769,88 +7769,88 @@
       <c r="CD2" s="294"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="371"/>
-      <c r="B3" s="370"/>
-      <c r="C3" s="370"/>
-      <c r="D3" s="370"/>
-      <c r="E3" s="370"/>
-      <c r="F3" s="370"/>
-      <c r="G3" s="370"/>
-      <c r="H3" s="370"/>
-      <c r="I3" s="370"/>
-      <c r="J3" s="370"/>
-      <c r="K3" s="370"/>
-      <c r="L3" s="370"/>
-      <c r="M3" s="370"/>
-      <c r="N3" s="370"/>
-      <c r="O3" s="370"/>
-      <c r="P3" s="370"/>
-      <c r="Q3" s="370"/>
-      <c r="R3" s="370"/>
-      <c r="S3" s="370"/>
-      <c r="T3" s="370"/>
-      <c r="U3" s="370"/>
-      <c r="V3" s="370"/>
-      <c r="W3" s="370"/>
-      <c r="X3" s="370"/>
-      <c r="Y3" s="370"/>
-      <c r="Z3" s="370"/>
-      <c r="AA3" s="370"/>
-      <c r="AB3" s="370"/>
-      <c r="AC3" s="370"/>
-      <c r="AD3" s="370"/>
-      <c r="AE3" s="370"/>
-      <c r="AF3" s="370"/>
-      <c r="AG3" s="370"/>
-      <c r="AH3" s="370"/>
-      <c r="AI3" s="370"/>
-      <c r="AJ3" s="370"/>
-      <c r="AK3" s="370"/>
-      <c r="AL3" s="370"/>
-      <c r="AM3" s="370"/>
-      <c r="AN3" s="370"/>
-      <c r="AO3" s="370"/>
-      <c r="AP3" s="370"/>
-      <c r="AQ3" s="370"/>
-      <c r="AR3" s="370"/>
-      <c r="AS3" s="370"/>
-      <c r="AT3" s="370"/>
-      <c r="AU3" s="370"/>
-      <c r="AV3" s="370"/>
-      <c r="AW3" s="370"/>
-      <c r="AX3" s="370"/>
-      <c r="AY3" s="370"/>
-      <c r="AZ3" s="370"/>
-      <c r="BA3" s="370"/>
-      <c r="BB3" s="370"/>
-      <c r="BC3" s="370"/>
-      <c r="BD3" s="370"/>
-      <c r="BE3" s="370"/>
-      <c r="BF3" s="370"/>
-      <c r="BG3" s="370"/>
-      <c r="BH3" s="370"/>
-      <c r="BI3" s="370"/>
-      <c r="BJ3" s="370"/>
-      <c r="BK3" s="370"/>
-      <c r="BL3" s="370"/>
-      <c r="BM3" s="370"/>
-      <c r="BN3" s="370"/>
-      <c r="BO3" s="370"/>
-      <c r="BP3" s="370"/>
-      <c r="BQ3" s="370"/>
-      <c r="BR3" s="370"/>
-      <c r="BS3" s="370"/>
-      <c r="BT3" s="370"/>
-      <c r="BU3" s="370"/>
+      <c r="A3" s="354"/>
+      <c r="B3" s="349"/>
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="349"/>
+      <c r="F3" s="349"/>
+      <c r="G3" s="349"/>
+      <c r="H3" s="349"/>
+      <c r="I3" s="349"/>
+      <c r="J3" s="349"/>
+      <c r="K3" s="349"/>
+      <c r="L3" s="349"/>
+      <c r="M3" s="349"/>
+      <c r="N3" s="349"/>
+      <c r="O3" s="349"/>
+      <c r="P3" s="349"/>
+      <c r="Q3" s="349"/>
+      <c r="R3" s="349"/>
+      <c r="S3" s="349"/>
+      <c r="T3" s="349"/>
+      <c r="U3" s="349"/>
+      <c r="V3" s="349"/>
+      <c r="W3" s="349"/>
+      <c r="X3" s="349"/>
+      <c r="Y3" s="349"/>
+      <c r="Z3" s="349"/>
+      <c r="AA3" s="349"/>
+      <c r="AB3" s="349"/>
+      <c r="AC3" s="349"/>
+      <c r="AD3" s="349"/>
+      <c r="AE3" s="349"/>
+      <c r="AF3" s="349"/>
+      <c r="AG3" s="349"/>
+      <c r="AH3" s="349"/>
+      <c r="AI3" s="349"/>
+      <c r="AJ3" s="349"/>
+      <c r="AK3" s="349"/>
+      <c r="AL3" s="349"/>
+      <c r="AM3" s="349"/>
+      <c r="AN3" s="349"/>
+      <c r="AO3" s="349"/>
+      <c r="AP3" s="349"/>
+      <c r="AQ3" s="349"/>
+      <c r="AR3" s="349"/>
+      <c r="AS3" s="349"/>
+      <c r="AT3" s="349"/>
+      <c r="AU3" s="349"/>
+      <c r="AV3" s="349"/>
+      <c r="AW3" s="349"/>
+      <c r="AX3" s="349"/>
+      <c r="AY3" s="349"/>
+      <c r="AZ3" s="349"/>
+      <c r="BA3" s="349"/>
+      <c r="BB3" s="349"/>
+      <c r="BC3" s="349"/>
+      <c r="BD3" s="349"/>
+      <c r="BE3" s="349"/>
+      <c r="BF3" s="349"/>
+      <c r="BG3" s="349"/>
+      <c r="BH3" s="349"/>
+      <c r="BI3" s="349"/>
+      <c r="BJ3" s="349"/>
+      <c r="BK3" s="349"/>
+      <c r="BL3" s="349"/>
+      <c r="BM3" s="349"/>
+      <c r="BN3" s="349"/>
+      <c r="BO3" s="349"/>
+      <c r="BP3" s="349"/>
+      <c r="BQ3" s="349"/>
+      <c r="BR3" s="349"/>
+      <c r="BS3" s="349"/>
+      <c r="BT3" s="349"/>
+      <c r="BU3" s="349"/>
       <c r="BV3" s="296"/>
-      <c r="BW3" s="369" t="s">
+      <c r="BW3" s="348" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="370"/>
-      <c r="BY3" s="370"/>
-      <c r="BZ3" s="370"/>
-      <c r="CA3" s="370"/>
-      <c r="CB3" s="370"/>
+      <c r="BX3" s="349"/>
+      <c r="BY3" s="349"/>
+      <c r="BZ3" s="349"/>
+      <c r="CA3" s="349"/>
+      <c r="CB3" s="349"/>
       <c r="CC3" s="298"/>
       <c r="CD3" s="298"/>
     </row>
@@ -7928,12 +7928,12 @@
       <c r="BT4" s="299"/>
       <c r="BU4" s="299"/>
       <c r="BV4" s="299"/>
-      <c r="BW4" s="370"/>
-      <c r="BX4" s="370"/>
-      <c r="BY4" s="370"/>
-      <c r="BZ4" s="370"/>
-      <c r="CA4" s="370"/>
-      <c r="CB4" s="370"/>
+      <c r="BW4" s="349"/>
+      <c r="BX4" s="349"/>
+      <c r="BY4" s="349"/>
+      <c r="BZ4" s="349"/>
+      <c r="CA4" s="349"/>
+      <c r="CB4" s="349"/>
       <c r="CC4" s="298"/>
       <c r="CD4" s="298"/>
     </row>
@@ -8011,12 +8011,12 @@
       <c r="BT5" s="299"/>
       <c r="BU5" s="299"/>
       <c r="BV5" s="299"/>
-      <c r="BW5" s="370"/>
-      <c r="BX5" s="370"/>
-      <c r="BY5" s="370"/>
-      <c r="BZ5" s="370"/>
-      <c r="CA5" s="370"/>
-      <c r="CB5" s="370"/>
+      <c r="BW5" s="349"/>
+      <c r="BX5" s="349"/>
+      <c r="BY5" s="349"/>
+      <c r="BZ5" s="349"/>
+      <c r="CA5" s="349"/>
+      <c r="CB5" s="349"/>
       <c r="CC5" s="298"/>
       <c r="CD5" s="298"/>
     </row>
@@ -8092,22 +8092,18 @@
       <c r="BT6" s="301"/>
       <c r="BU6" s="301"/>
       <c r="BV6" s="301"/>
-      <c r="BW6" s="370"/>
-      <c r="BX6" s="370"/>
-      <c r="BY6" s="370"/>
-      <c r="BZ6" s="370"/>
-      <c r="CA6" s="370"/>
-      <c r="CB6" s="370"/>
+      <c r="BW6" s="349"/>
+      <c r="BX6" s="349"/>
+      <c r="BY6" s="349"/>
+      <c r="BZ6" s="349"/>
+      <c r="CA6" s="349"/>
+      <c r="CB6" s="349"/>
       <c r="CC6" s="298"/>
       <c r="CD6" s="298"/>
     </row>
     <row r="7" spans="1:87" s="320" customFormat="1" ht="31" outlineLevel="1">
-      <c r="B7" s="301" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="301" t="s">
-        <v>155</v>
-      </c>
+      <c r="B7" s="301"/>
+      <c r="C7" s="301"/>
       <c r="D7" s="321"/>
       <c r="E7" s="321" t="s">
         <v>156</v>
@@ -8237,356 +8233,356 @@
       </c>
     </row>
     <row r="8" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="368" t="s">
+      <c r="A8" s="347" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="373" t="s">
+      <c r="B8" s="356" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="341" t="s">
+      <c r="C8" s="332" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="360" t="s">
+      <c r="D8" s="339" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="360" t="s">
+      <c r="E8" s="339" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="341" t="s">
+      <c r="F8" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="356" t="s">
+      <c r="G8" s="345" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="361" t="s">
+      <c r="H8" s="372" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="361" t="s">
+      <c r="I8" s="372" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="356" t="s">
+      <c r="J8" s="345" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="367" t="s">
+      <c r="K8" s="370" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="353"/>
-      <c r="M8" s="353"/>
-      <c r="N8" s="353"/>
-      <c r="O8" s="353"/>
-      <c r="P8" s="353"/>
-      <c r="Q8" s="353"/>
-      <c r="R8" s="353"/>
-      <c r="S8" s="353"/>
-      <c r="T8" s="353"/>
-      <c r="U8" s="353"/>
-      <c r="V8" s="353"/>
-      <c r="W8" s="353"/>
-      <c r="X8" s="353"/>
-      <c r="Y8" s="352" t="s">
+      <c r="L8" s="371"/>
+      <c r="M8" s="371"/>
+      <c r="N8" s="371"/>
+      <c r="O8" s="371"/>
+      <c r="P8" s="371"/>
+      <c r="Q8" s="371"/>
+      <c r="R8" s="371"/>
+      <c r="S8" s="371"/>
+      <c r="T8" s="371"/>
+      <c r="U8" s="371"/>
+      <c r="V8" s="371"/>
+      <c r="W8" s="371"/>
+      <c r="X8" s="371"/>
+      <c r="Y8" s="373" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="353"/>
-      <c r="AA8" s="353"/>
-      <c r="AB8" s="353"/>
-      <c r="AC8" s="353"/>
-      <c r="AD8" s="353"/>
-      <c r="AE8" s="353"/>
-      <c r="AF8" s="353"/>
-      <c r="AG8" s="353"/>
-      <c r="AH8" s="353"/>
-      <c r="AI8" s="353"/>
-      <c r="AJ8" s="353"/>
-      <c r="AK8" s="353"/>
-      <c r="AL8" s="353"/>
-      <c r="AM8" s="353"/>
-      <c r="AN8" s="353"/>
-      <c r="AO8" s="354"/>
-      <c r="AP8" s="356" t="s">
+      <c r="Z8" s="371"/>
+      <c r="AA8" s="371"/>
+      <c r="AB8" s="371"/>
+      <c r="AC8" s="371"/>
+      <c r="AD8" s="371"/>
+      <c r="AE8" s="371"/>
+      <c r="AF8" s="371"/>
+      <c r="AG8" s="371"/>
+      <c r="AH8" s="371"/>
+      <c r="AI8" s="371"/>
+      <c r="AJ8" s="371"/>
+      <c r="AK8" s="371"/>
+      <c r="AL8" s="371"/>
+      <c r="AM8" s="371"/>
+      <c r="AN8" s="371"/>
+      <c r="AO8" s="374"/>
+      <c r="AP8" s="345" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="356" t="s">
+      <c r="AQ8" s="345" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="356" t="s">
+      <c r="AR8" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="356" t="s">
+      <c r="AS8" s="345" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="356" t="s">
+      <c r="AT8" s="345" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="356" t="s">
+      <c r="AU8" s="345" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="341" t="s">
+      <c r="AV8" s="332" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="346" t="s">
+      <c r="AW8" s="353" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="341" t="s">
+      <c r="AX8" s="332" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="358" t="s">
+      <c r="AY8" s="376" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="353"/>
-      <c r="BA8" s="353"/>
-      <c r="BB8" s="353"/>
-      <c r="BC8" s="353"/>
-      <c r="BD8" s="353"/>
-      <c r="BE8" s="353"/>
-      <c r="BF8" s="353"/>
-      <c r="BG8" s="353"/>
-      <c r="BH8" s="353"/>
-      <c r="BI8" s="353"/>
-      <c r="BJ8" s="353"/>
-      <c r="BK8" s="353"/>
-      <c r="BL8" s="353"/>
-      <c r="BM8" s="353"/>
-      <c r="BN8" s="353"/>
-      <c r="BO8" s="353"/>
-      <c r="BP8" s="353"/>
-      <c r="BQ8" s="354"/>
-      <c r="BR8" s="342" t="s">
+      <c r="AZ8" s="371"/>
+      <c r="BA8" s="371"/>
+      <c r="BB8" s="371"/>
+      <c r="BC8" s="371"/>
+      <c r="BD8" s="371"/>
+      <c r="BE8" s="371"/>
+      <c r="BF8" s="371"/>
+      <c r="BG8" s="371"/>
+      <c r="BH8" s="371"/>
+      <c r="BI8" s="371"/>
+      <c r="BJ8" s="371"/>
+      <c r="BK8" s="371"/>
+      <c r="BL8" s="371"/>
+      <c r="BM8" s="371"/>
+      <c r="BN8" s="371"/>
+      <c r="BO8" s="371"/>
+      <c r="BP8" s="371"/>
+      <c r="BQ8" s="374"/>
+      <c r="BR8" s="380" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="343"/>
-      <c r="BT8" s="341" t="s">
+      <c r="BS8" s="367"/>
+      <c r="BT8" s="332" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="338" t="s">
+      <c r="BU8" s="377" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="329"/>
-      <c r="BW8" s="383" t="s">
+      <c r="BW8" s="335" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="374" t="s">
+      <c r="BX8" s="357" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="375"/>
-      <c r="BZ8" s="375"/>
-      <c r="CA8" s="376"/>
-      <c r="CB8" s="344" t="s">
+      <c r="BY8" s="358"/>
+      <c r="BZ8" s="358"/>
+      <c r="CA8" s="359"/>
+      <c r="CB8" s="381" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="332" t="s">
+      <c r="CC8" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="332" t="s">
+      <c r="CD8" s="350" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="336"/>
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-      <c r="D9" s="336"/>
-      <c r="E9" s="336"/>
-      <c r="F9" s="336"/>
-      <c r="G9" s="347"/>
-      <c r="H9" s="336"/>
-      <c r="I9" s="336"/>
-      <c r="J9" s="347"/>
-      <c r="K9" s="363" t="s">
+      <c r="A9" s="333"/>
+      <c r="B9" s="333"/>
+      <c r="C9" s="333"/>
+      <c r="D9" s="333"/>
+      <c r="E9" s="333"/>
+      <c r="F9" s="333"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="333"/>
+      <c r="I9" s="333"/>
+      <c r="J9" s="346"/>
+      <c r="K9" s="343" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="363" t="s">
+      <c r="L9" s="343" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="363" t="s">
+      <c r="M9" s="343" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="363" t="s">
+      <c r="N9" s="343" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="363" t="s">
+      <c r="O9" s="343" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="363" t="s">
+      <c r="P9" s="343" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="363" t="s">
+      <c r="Q9" s="343" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="363" t="s">
+      <c r="R9" s="343" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="363" t="s">
+      <c r="S9" s="343" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="363" t="s">
+      <c r="T9" s="343" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="363" t="s">
+      <c r="U9" s="343" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="364" t="s">
+      <c r="V9" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="343"/>
-      <c r="X9" s="363" t="s">
+      <c r="W9" s="367"/>
+      <c r="X9" s="343" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="335" t="s">
+      <c r="Y9" s="338" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="335" t="s">
+      <c r="Z9" s="338" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="335" t="s">
+      <c r="AA9" s="338" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="335" t="s">
+      <c r="AB9" s="338" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="335" t="s">
+      <c r="AC9" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="335" t="s">
+      <c r="AD9" s="338" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="335" t="s">
+      <c r="AE9" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="335" t="s">
+      <c r="AF9" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="335" t="s">
+      <c r="AG9" s="338" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="335" t="s">
+      <c r="AH9" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="335" t="s">
+      <c r="AI9" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="357" t="s">
+      <c r="AJ9" s="375" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="338" t="s">
+      <c r="AK9" s="377" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="346" t="s">
+      <c r="AL9" s="353" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="335" t="s">
+      <c r="AM9" s="338" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="341" t="s">
+      <c r="AN9" s="332" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="341" t="s">
+      <c r="AO9" s="332" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="347"/>
-      <c r="AQ9" s="347"/>
-      <c r="AR9" s="347"/>
-      <c r="AS9" s="347"/>
-      <c r="AT9" s="347"/>
-      <c r="AU9" s="347"/>
-      <c r="AV9" s="336"/>
-      <c r="AW9" s="347"/>
-      <c r="AX9" s="336"/>
-      <c r="AY9" s="349" t="s">
+      <c r="AP9" s="346"/>
+      <c r="AQ9" s="346"/>
+      <c r="AR9" s="346"/>
+      <c r="AS9" s="346"/>
+      <c r="AT9" s="346"/>
+      <c r="AU9" s="346"/>
+      <c r="AV9" s="333"/>
+      <c r="AW9" s="346"/>
+      <c r="AX9" s="333"/>
+      <c r="AY9" s="383" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="350"/>
-      <c r="BA9" s="350"/>
-      <c r="BB9" s="350"/>
-      <c r="BC9" s="350"/>
-      <c r="BD9" s="350"/>
-      <c r="BE9" s="350"/>
-      <c r="BF9" s="350"/>
-      <c r="BG9" s="350"/>
-      <c r="BH9" s="350"/>
-      <c r="BI9" s="350"/>
-      <c r="BJ9" s="350"/>
-      <c r="BK9" s="350"/>
-      <c r="BL9" s="351"/>
-      <c r="BM9" s="349" t="s">
+      <c r="AZ9" s="384"/>
+      <c r="BA9" s="384"/>
+      <c r="BB9" s="384"/>
+      <c r="BC9" s="384"/>
+      <c r="BD9" s="384"/>
+      <c r="BE9" s="384"/>
+      <c r="BF9" s="384"/>
+      <c r="BG9" s="384"/>
+      <c r="BH9" s="384"/>
+      <c r="BI9" s="384"/>
+      <c r="BJ9" s="384"/>
+      <c r="BK9" s="384"/>
+      <c r="BL9" s="385"/>
+      <c r="BM9" s="383" t="s">
         <v>64</v>
       </c>
-      <c r="BN9" s="350"/>
-      <c r="BO9" s="350"/>
-      <c r="BP9" s="350"/>
-      <c r="BQ9" s="351"/>
-      <c r="BR9" s="362" t="s">
+      <c r="BN9" s="384"/>
+      <c r="BO9" s="384"/>
+      <c r="BP9" s="384"/>
+      <c r="BQ9" s="385"/>
+      <c r="BR9" s="344" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="362" t="s">
+      <c r="BS9" s="344" t="s">
         <v>66</v>
       </c>
-      <c r="BT9" s="336"/>
-      <c r="BU9" s="339"/>
+      <c r="BT9" s="333"/>
+      <c r="BU9" s="378"/>
       <c r="BV9" s="329"/>
-      <c r="BW9" s="384"/>
-      <c r="BX9" s="377"/>
-      <c r="BY9" s="378"/>
-      <c r="BZ9" s="378"/>
-      <c r="CA9" s="379"/>
-      <c r="CB9" s="336"/>
-      <c r="CC9" s="333"/>
-      <c r="CD9" s="333"/>
+      <c r="BW9" s="336"/>
+      <c r="BX9" s="360"/>
+      <c r="BY9" s="361"/>
+      <c r="BZ9" s="361"/>
+      <c r="CA9" s="362"/>
+      <c r="CB9" s="333"/>
+      <c r="CC9" s="351"/>
+      <c r="CD9" s="351"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="305" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="336"/>
-      <c r="B10" s="336"/>
-      <c r="C10" s="336"/>
-      <c r="D10" s="336"/>
-      <c r="E10" s="336"/>
-      <c r="F10" s="336"/>
-      <c r="G10" s="347"/>
-      <c r="H10" s="336"/>
-      <c r="I10" s="336"/>
-      <c r="J10" s="347"/>
-      <c r="K10" s="336"/>
-      <c r="L10" s="336"/>
-      <c r="M10" s="336"/>
-      <c r="N10" s="336"/>
-      <c r="O10" s="336"/>
-      <c r="P10" s="336"/>
-      <c r="Q10" s="336"/>
-      <c r="R10" s="336"/>
-      <c r="S10" s="336"/>
-      <c r="T10" s="336"/>
-      <c r="U10" s="336"/>
-      <c r="V10" s="365"/>
-      <c r="W10" s="366"/>
-      <c r="X10" s="336"/>
-      <c r="Y10" s="336"/>
-      <c r="Z10" s="336"/>
-      <c r="AA10" s="336"/>
-      <c r="AB10" s="336"/>
-      <c r="AC10" s="336"/>
-      <c r="AD10" s="336"/>
-      <c r="AE10" s="336"/>
-      <c r="AF10" s="336"/>
-      <c r="AG10" s="336"/>
-      <c r="AH10" s="336"/>
-      <c r="AI10" s="336"/>
-      <c r="AJ10" s="347"/>
-      <c r="AK10" s="339"/>
-      <c r="AL10" s="347"/>
-      <c r="AM10" s="336"/>
-      <c r="AN10" s="336"/>
-      <c r="AO10" s="336"/>
-      <c r="AP10" s="347"/>
-      <c r="AQ10" s="347"/>
-      <c r="AR10" s="347"/>
-      <c r="AS10" s="347"/>
-      <c r="AT10" s="347"/>
-      <c r="AU10" s="347"/>
-      <c r="AV10" s="336"/>
-      <c r="AW10" s="347"/>
-      <c r="AX10" s="336"/>
+      <c r="A10" s="333"/>
+      <c r="B10" s="333"/>
+      <c r="C10" s="333"/>
+      <c r="D10" s="333"/>
+      <c r="E10" s="333"/>
+      <c r="F10" s="333"/>
+      <c r="G10" s="346"/>
+      <c r="H10" s="333"/>
+      <c r="I10" s="333"/>
+      <c r="J10" s="346"/>
+      <c r="K10" s="333"/>
+      <c r="L10" s="333"/>
+      <c r="M10" s="333"/>
+      <c r="N10" s="333"/>
+      <c r="O10" s="333"/>
+      <c r="P10" s="333"/>
+      <c r="Q10" s="333"/>
+      <c r="R10" s="333"/>
+      <c r="S10" s="333"/>
+      <c r="T10" s="333"/>
+      <c r="U10" s="333"/>
+      <c r="V10" s="368"/>
+      <c r="W10" s="369"/>
+      <c r="X10" s="333"/>
+      <c r="Y10" s="333"/>
+      <c r="Z10" s="333"/>
+      <c r="AA10" s="333"/>
+      <c r="AB10" s="333"/>
+      <c r="AC10" s="333"/>
+      <c r="AD10" s="333"/>
+      <c r="AE10" s="333"/>
+      <c r="AF10" s="333"/>
+      <c r="AG10" s="333"/>
+      <c r="AH10" s="333"/>
+      <c r="AI10" s="333"/>
+      <c r="AJ10" s="346"/>
+      <c r="AK10" s="378"/>
+      <c r="AL10" s="346"/>
+      <c r="AM10" s="333"/>
+      <c r="AN10" s="333"/>
+      <c r="AO10" s="333"/>
+      <c r="AP10" s="346"/>
+      <c r="AQ10" s="346"/>
+      <c r="AR10" s="346"/>
+      <c r="AS10" s="346"/>
+      <c r="AT10" s="346"/>
+      <c r="AU10" s="346"/>
+      <c r="AV10" s="333"/>
+      <c r="AW10" s="346"/>
+      <c r="AX10" s="333"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -8596,67 +8592,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="372" t="s">
+      <c r="BB10" s="355" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="359" t="s">
+      <c r="BC10" s="341" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="359" t="s">
+      <c r="BD10" s="341" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="355" t="s">
+      <c r="BE10" s="340" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="355" t="s">
+      <c r="BF10" s="340" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="355" t="s">
+      <c r="BG10" s="340" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="359" t="s">
+      <c r="BH10" s="341" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="359" t="s">
+      <c r="BI10" s="341" t="s">
         <v>77</v>
       </c>
-      <c r="BJ10" s="355" t="s">
+      <c r="BJ10" s="340" t="s">
         <v>78</v>
       </c>
-      <c r="BK10" s="355" t="s">
+      <c r="BK10" s="340" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="341" t="s">
+      <c r="BL10" s="332" t="s">
         <v>80</v>
       </c>
-      <c r="BM10" s="359" t="s">
+      <c r="BM10" s="341" t="s">
         <v>81</v>
       </c>
-      <c r="BN10" s="346" t="s">
+      <c r="BN10" s="353" t="s">
         <v>82</v>
       </c>
-      <c r="BO10" s="359" t="s">
+      <c r="BO10" s="341" t="s">
         <v>83</v>
       </c>
-      <c r="BP10" s="346" t="s">
+      <c r="BP10" s="353" t="s">
         <v>84</v>
       </c>
-      <c r="BQ10" s="346" t="s">
+      <c r="BQ10" s="353" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="336"/>
-      <c r="BS10" s="336"/>
-      <c r="BT10" s="336"/>
-      <c r="BU10" s="339"/>
+      <c r="BR10" s="333"/>
+      <c r="BS10" s="333"/>
+      <c r="BT10" s="333"/>
+      <c r="BU10" s="378"/>
       <c r="BV10" s="329"/>
-      <c r="BW10" s="384"/>
-      <c r="BX10" s="380"/>
-      <c r="BY10" s="381"/>
-      <c r="BZ10" s="381"/>
-      <c r="CA10" s="382"/>
-      <c r="CB10" s="336"/>
-      <c r="CC10" s="333"/>
-      <c r="CD10" s="333"/>
+      <c r="BW10" s="336"/>
+      <c r="BX10" s="363"/>
+      <c r="BY10" s="364"/>
+      <c r="BZ10" s="364"/>
+      <c r="CA10" s="365"/>
+      <c r="CB10" s="333"/>
+      <c r="CC10" s="351"/>
+      <c r="CD10" s="351"/>
       <c r="CE10" s="319" t="s">
         <v>3</v>
       </c>
@@ -8664,60 +8660,60 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="305" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="337"/>
-      <c r="B11" s="337"/>
-      <c r="C11" s="337"/>
-      <c r="D11" s="337"/>
-      <c r="E11" s="337"/>
-      <c r="F11" s="337"/>
-      <c r="G11" s="348"/>
-      <c r="H11" s="337"/>
-      <c r="I11" s="337"/>
-      <c r="J11" s="348"/>
-      <c r="K11" s="337"/>
-      <c r="L11" s="337"/>
-      <c r="M11" s="337"/>
-      <c r="N11" s="337"/>
-      <c r="O11" s="337"/>
-      <c r="P11" s="337"/>
-      <c r="Q11" s="337"/>
-      <c r="R11" s="337"/>
-      <c r="S11" s="337"/>
-      <c r="T11" s="337"/>
-      <c r="U11" s="337"/>
+      <c r="A11" s="334"/>
+      <c r="B11" s="334"/>
+      <c r="C11" s="334"/>
+      <c r="D11" s="334"/>
+      <c r="E11" s="334"/>
+      <c r="F11" s="334"/>
+      <c r="G11" s="342"/>
+      <c r="H11" s="334"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="342"/>
+      <c r="K11" s="334"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="334"/>
+      <c r="N11" s="334"/>
+      <c r="O11" s="334"/>
+      <c r="P11" s="334"/>
+      <c r="Q11" s="334"/>
+      <c r="R11" s="334"/>
+      <c r="S11" s="334"/>
+      <c r="T11" s="334"/>
+      <c r="U11" s="334"/>
       <c r="V11" s="330" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="330" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="337"/>
-      <c r="Y11" s="337"/>
-      <c r="Z11" s="337"/>
-      <c r="AA11" s="337"/>
-      <c r="AB11" s="337"/>
-      <c r="AC11" s="337"/>
-      <c r="AD11" s="337"/>
-      <c r="AE11" s="337"/>
-      <c r="AF11" s="337"/>
-      <c r="AG11" s="337"/>
-      <c r="AH11" s="337"/>
-      <c r="AI11" s="337"/>
-      <c r="AJ11" s="348"/>
-      <c r="AK11" s="340"/>
-      <c r="AL11" s="348"/>
-      <c r="AM11" s="337"/>
-      <c r="AN11" s="337"/>
-      <c r="AO11" s="337"/>
-      <c r="AP11" s="348"/>
-      <c r="AQ11" s="348"/>
-      <c r="AR11" s="348"/>
-      <c r="AS11" s="348"/>
-      <c r="AT11" s="348"/>
-      <c r="AU11" s="348"/>
-      <c r="AV11" s="337"/>
-      <c r="AW11" s="348"/>
-      <c r="AX11" s="337"/>
+      <c r="X11" s="334"/>
+      <c r="Y11" s="334"/>
+      <c r="Z11" s="334"/>
+      <c r="AA11" s="334"/>
+      <c r="AB11" s="334"/>
+      <c r="AC11" s="334"/>
+      <c r="AD11" s="334"/>
+      <c r="AE11" s="334"/>
+      <c r="AF11" s="334"/>
+      <c r="AG11" s="334"/>
+      <c r="AH11" s="334"/>
+      <c r="AI11" s="334"/>
+      <c r="AJ11" s="342"/>
+      <c r="AK11" s="379"/>
+      <c r="AL11" s="342"/>
+      <c r="AM11" s="334"/>
+      <c r="AN11" s="334"/>
+      <c r="AO11" s="334"/>
+      <c r="AP11" s="342"/>
+      <c r="AQ11" s="342"/>
+      <c r="AR11" s="342"/>
+      <c r="AS11" s="342"/>
+      <c r="AT11" s="342"/>
+      <c r="AU11" s="342"/>
+      <c r="AV11" s="334"/>
+      <c r="AW11" s="342"/>
+      <c r="AX11" s="334"/>
       <c r="AY11" s="331" t="s">
         <v>88</v>
       </c>
@@ -8727,28 +8723,28 @@
       <c r="BA11" s="331" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="337"/>
-      <c r="BC11" s="348"/>
-      <c r="BD11" s="348"/>
-      <c r="BE11" s="337"/>
-      <c r="BF11" s="337"/>
-      <c r="BG11" s="337"/>
-      <c r="BH11" s="348"/>
-      <c r="BI11" s="348"/>
-      <c r="BJ11" s="337"/>
-      <c r="BK11" s="337"/>
-      <c r="BL11" s="337"/>
-      <c r="BM11" s="348"/>
-      <c r="BN11" s="348"/>
-      <c r="BO11" s="348"/>
-      <c r="BP11" s="348"/>
-      <c r="BQ11" s="348"/>
-      <c r="BR11" s="337"/>
-      <c r="BS11" s="337"/>
-      <c r="BT11" s="337"/>
-      <c r="BU11" s="340"/>
+      <c r="BB11" s="334"/>
+      <c r="BC11" s="342"/>
+      <c r="BD11" s="342"/>
+      <c r="BE11" s="334"/>
+      <c r="BF11" s="334"/>
+      <c r="BG11" s="334"/>
+      <c r="BH11" s="342"/>
+      <c r="BI11" s="342"/>
+      <c r="BJ11" s="334"/>
+      <c r="BK11" s="334"/>
+      <c r="BL11" s="334"/>
+      <c r="BM11" s="342"/>
+      <c r="BN11" s="342"/>
+      <c r="BO11" s="342"/>
+      <c r="BP11" s="342"/>
+      <c r="BQ11" s="342"/>
+      <c r="BR11" s="334"/>
+      <c r="BS11" s="334"/>
+      <c r="BT11" s="334"/>
+      <c r="BU11" s="379"/>
       <c r="BV11" s="329"/>
-      <c r="BW11" s="385"/>
+      <c r="BW11" s="337"/>
       <c r="BX11" s="327" t="s">
         <v>91</v>
       </c>
@@ -8761,9 +8757,9 @@
       <c r="CA11" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="345"/>
-      <c r="CC11" s="334"/>
-      <c r="CD11" s="334"/>
+      <c r="CB11" s="382"/>
+      <c r="CC11" s="352"/>
+      <c r="CD11" s="352"/>
       <c r="CE11" s="318">
         <v>26</v>
       </c>
@@ -11223,6 +11219,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="BW8:BW11"/>
     <mergeCell ref="AI9:AI11"/>
@@ -11239,72 +11301,6 @@
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="R9:R11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7:B12 B15:B25 C12:BU12 B37:B1048576 B27:B35">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
@@ -11513,87 +11509,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="414"/>
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
-      <c r="L3" s="405"/>
-      <c r="M3" s="405"/>
-      <c r="N3" s="405"/>
-      <c r="O3" s="405"/>
-      <c r="P3" s="405"/>
-      <c r="Q3" s="405"/>
-      <c r="R3" s="405"/>
-      <c r="S3" s="405"/>
-      <c r="T3" s="405"/>
-      <c r="U3" s="405"/>
-      <c r="V3" s="405"/>
-      <c r="W3" s="405"/>
-      <c r="X3" s="405"/>
-      <c r="Y3" s="405"/>
-      <c r="Z3" s="405"/>
-      <c r="AA3" s="405"/>
-      <c r="AB3" s="405"/>
-      <c r="AC3" s="405"/>
-      <c r="AD3" s="405"/>
-      <c r="AE3" s="405"/>
-      <c r="AF3" s="405"/>
-      <c r="AG3" s="405"/>
-      <c r="AH3" s="405"/>
-      <c r="AI3" s="405"/>
-      <c r="AJ3" s="405"/>
-      <c r="AK3" s="405"/>
-      <c r="AL3" s="405"/>
-      <c r="AM3" s="405"/>
-      <c r="AN3" s="405"/>
-      <c r="AO3" s="405"/>
-      <c r="AP3" s="405"/>
-      <c r="AQ3" s="405"/>
-      <c r="AR3" s="405"/>
-      <c r="AS3" s="405"/>
-      <c r="AT3" s="405"/>
-      <c r="AU3" s="405"/>
-      <c r="AV3" s="405"/>
-      <c r="AW3" s="405"/>
-      <c r="AX3" s="405"/>
-      <c r="AY3" s="405"/>
-      <c r="AZ3" s="405"/>
-      <c r="BA3" s="405"/>
-      <c r="BB3" s="405"/>
-      <c r="BC3" s="405"/>
-      <c r="BD3" s="405"/>
-      <c r="BE3" s="405"/>
-      <c r="BF3" s="405"/>
-      <c r="BG3" s="405"/>
-      <c r="BH3" s="405"/>
-      <c r="BI3" s="405"/>
-      <c r="BJ3" s="405"/>
-      <c r="BK3" s="405"/>
-      <c r="BL3" s="405"/>
-      <c r="BM3" s="405"/>
-      <c r="BN3" s="405"/>
-      <c r="BO3" s="405"/>
-      <c r="BP3" s="405"/>
-      <c r="BQ3" s="405"/>
-      <c r="BR3" s="405"/>
-      <c r="BS3" s="405"/>
-      <c r="BT3" s="405"/>
-      <c r="BU3" s="405"/>
-      <c r="BW3" s="404" t="s">
+      <c r="A3" s="418"/>
+      <c r="B3" s="407"/>
+      <c r="C3" s="407"/>
+      <c r="D3" s="407"/>
+      <c r="E3" s="407"/>
+      <c r="F3" s="407"/>
+      <c r="G3" s="407"/>
+      <c r="H3" s="407"/>
+      <c r="I3" s="407"/>
+      <c r="J3" s="407"/>
+      <c r="K3" s="407"/>
+      <c r="L3" s="407"/>
+      <c r="M3" s="407"/>
+      <c r="N3" s="407"/>
+      <c r="O3" s="407"/>
+      <c r="P3" s="407"/>
+      <c r="Q3" s="407"/>
+      <c r="R3" s="407"/>
+      <c r="S3" s="407"/>
+      <c r="T3" s="407"/>
+      <c r="U3" s="407"/>
+      <c r="V3" s="407"/>
+      <c r="W3" s="407"/>
+      <c r="X3" s="407"/>
+      <c r="Y3" s="407"/>
+      <c r="Z3" s="407"/>
+      <c r="AA3" s="407"/>
+      <c r="AB3" s="407"/>
+      <c r="AC3" s="407"/>
+      <c r="AD3" s="407"/>
+      <c r="AE3" s="407"/>
+      <c r="AF3" s="407"/>
+      <c r="AG3" s="407"/>
+      <c r="AH3" s="407"/>
+      <c r="AI3" s="407"/>
+      <c r="AJ3" s="407"/>
+      <c r="AK3" s="407"/>
+      <c r="AL3" s="407"/>
+      <c r="AM3" s="407"/>
+      <c r="AN3" s="407"/>
+      <c r="AO3" s="407"/>
+      <c r="AP3" s="407"/>
+      <c r="AQ3" s="407"/>
+      <c r="AR3" s="407"/>
+      <c r="AS3" s="407"/>
+      <c r="AT3" s="407"/>
+      <c r="AU3" s="407"/>
+      <c r="AV3" s="407"/>
+      <c r="AW3" s="407"/>
+      <c r="AX3" s="407"/>
+      <c r="AY3" s="407"/>
+      <c r="AZ3" s="407"/>
+      <c r="BA3" s="407"/>
+      <c r="BB3" s="407"/>
+      <c r="BC3" s="407"/>
+      <c r="BD3" s="407"/>
+      <c r="BE3" s="407"/>
+      <c r="BF3" s="407"/>
+      <c r="BG3" s="407"/>
+      <c r="BH3" s="407"/>
+      <c r="BI3" s="407"/>
+      <c r="BJ3" s="407"/>
+      <c r="BK3" s="407"/>
+      <c r="BL3" s="407"/>
+      <c r="BM3" s="407"/>
+      <c r="BN3" s="407"/>
+      <c r="BO3" s="407"/>
+      <c r="BP3" s="407"/>
+      <c r="BQ3" s="407"/>
+      <c r="BR3" s="407"/>
+      <c r="BS3" s="407"/>
+      <c r="BT3" s="407"/>
+      <c r="BU3" s="407"/>
+      <c r="BW3" s="406" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="405"/>
-      <c r="BY3" s="405"/>
-      <c r="BZ3" s="405"/>
-      <c r="CA3" s="405"/>
-      <c r="CB3" s="405"/>
+      <c r="BX3" s="407"/>
+      <c r="BY3" s="407"/>
+      <c r="BZ3" s="407"/>
+      <c r="CA3" s="407"/>
+      <c r="CB3" s="407"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -11676,364 +11672,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="405"/>
-      <c r="BX4" s="405"/>
-      <c r="BY4" s="405"/>
-      <c r="BZ4" s="405"/>
-      <c r="CA4" s="405"/>
-      <c r="CB4" s="405"/>
+      <c r="BW4" s="407"/>
+      <c r="BX4" s="407"/>
+      <c r="BY4" s="407"/>
+      <c r="BZ4" s="407"/>
+      <c r="CA4" s="407"/>
+      <c r="CB4" s="407"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="417" t="s">
+      <c r="A5" s="394" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="405" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="390" t="s">
+      <c r="C5" s="393" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="415" t="s">
+      <c r="D5" s="400" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="415" t="s">
+      <c r="E5" s="400" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="390" t="s">
+      <c r="F5" s="393" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="390" t="s">
+      <c r="G5" s="393" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="341" t="s">
+      <c r="H5" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="341" t="s">
+      <c r="I5" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="390" t="s">
+      <c r="J5" s="393" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="419" t="s">
+      <c r="K5" s="398" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="401"/>
-      <c r="M5" s="401"/>
-      <c r="N5" s="401"/>
-      <c r="O5" s="401"/>
-      <c r="P5" s="401"/>
-      <c r="Q5" s="401"/>
-      <c r="R5" s="401"/>
-      <c r="S5" s="401"/>
-      <c r="T5" s="401"/>
-      <c r="U5" s="401"/>
-      <c r="V5" s="401"/>
-      <c r="W5" s="401"/>
-      <c r="X5" s="401"/>
-      <c r="Y5" s="390" t="s">
+      <c r="L5" s="390"/>
+      <c r="M5" s="390"/>
+      <c r="N5" s="390"/>
+      <c r="O5" s="390"/>
+      <c r="P5" s="390"/>
+      <c r="Q5" s="390"/>
+      <c r="R5" s="390"/>
+      <c r="S5" s="390"/>
+      <c r="T5" s="390"/>
+      <c r="U5" s="390"/>
+      <c r="V5" s="390"/>
+      <c r="W5" s="390"/>
+      <c r="X5" s="390"/>
+      <c r="Y5" s="393" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="401"/>
-      <c r="AA5" s="401"/>
-      <c r="AB5" s="401"/>
-      <c r="AC5" s="401"/>
-      <c r="AD5" s="401"/>
-      <c r="AE5" s="401"/>
-      <c r="AF5" s="401"/>
-      <c r="AG5" s="401"/>
-      <c r="AH5" s="401"/>
-      <c r="AI5" s="401"/>
-      <c r="AJ5" s="401"/>
-      <c r="AK5" s="401"/>
-      <c r="AL5" s="401"/>
-      <c r="AM5" s="401"/>
-      <c r="AN5" s="401"/>
-      <c r="AO5" s="402"/>
-      <c r="AP5" s="390" t="s">
+      <c r="Z5" s="390"/>
+      <c r="AA5" s="390"/>
+      <c r="AB5" s="390"/>
+      <c r="AC5" s="390"/>
+      <c r="AD5" s="390"/>
+      <c r="AE5" s="390"/>
+      <c r="AF5" s="390"/>
+      <c r="AG5" s="390"/>
+      <c r="AH5" s="390"/>
+      <c r="AI5" s="390"/>
+      <c r="AJ5" s="390"/>
+      <c r="AK5" s="390"/>
+      <c r="AL5" s="390"/>
+      <c r="AM5" s="390"/>
+      <c r="AN5" s="390"/>
+      <c r="AO5" s="391"/>
+      <c r="AP5" s="393" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="390" t="s">
+      <c r="AQ5" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="390" t="s">
+      <c r="AR5" s="393" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="390" t="s">
+      <c r="AS5" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="390" t="s">
+      <c r="AT5" s="393" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="390" t="s">
+      <c r="AU5" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="390" t="s">
+      <c r="AV5" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="390" t="s">
+      <c r="AW5" s="393" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="390" t="s">
+      <c r="AX5" s="393" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="400" t="s">
+      <c r="AY5" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="401"/>
-      <c r="BA5" s="401"/>
-      <c r="BB5" s="401"/>
-      <c r="BC5" s="401"/>
-      <c r="BD5" s="401"/>
-      <c r="BE5" s="401"/>
-      <c r="BF5" s="401"/>
-      <c r="BG5" s="401"/>
-      <c r="BH5" s="401"/>
-      <c r="BI5" s="401"/>
-      <c r="BJ5" s="401"/>
-      <c r="BK5" s="401"/>
-      <c r="BL5" s="401"/>
-      <c r="BM5" s="401"/>
-      <c r="BN5" s="401"/>
-      <c r="BO5" s="401"/>
-      <c r="BP5" s="401"/>
-      <c r="BQ5" s="402"/>
-      <c r="BR5" s="406" t="s">
+      <c r="AZ5" s="390"/>
+      <c r="BA5" s="390"/>
+      <c r="BB5" s="390"/>
+      <c r="BC5" s="390"/>
+      <c r="BD5" s="390"/>
+      <c r="BE5" s="390"/>
+      <c r="BF5" s="390"/>
+      <c r="BG5" s="390"/>
+      <c r="BH5" s="390"/>
+      <c r="BI5" s="390"/>
+      <c r="BJ5" s="390"/>
+      <c r="BK5" s="390"/>
+      <c r="BL5" s="390"/>
+      <c r="BM5" s="390"/>
+      <c r="BN5" s="390"/>
+      <c r="BO5" s="390"/>
+      <c r="BP5" s="390"/>
+      <c r="BQ5" s="391"/>
+      <c r="BR5" s="409" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="407"/>
-      <c r="BT5" s="400" t="s">
+      <c r="BS5" s="403"/>
+      <c r="BT5" s="389" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="394" t="s">
+      <c r="BU5" s="420" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="397" t="s">
+      <c r="BW5" s="421" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="408" t="s">
+      <c r="BX5" s="410" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="409"/>
-      <c r="BZ5" s="409"/>
-      <c r="CA5" s="407"/>
-      <c r="CB5" s="403" t="s">
+      <c r="BY5" s="411"/>
+      <c r="BZ5" s="411"/>
+      <c r="CA5" s="403"/>
+      <c r="CB5" s="422" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="332" t="s">
+      <c r="CC5" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="332" t="s">
+      <c r="CD5" s="350" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="386"/>
-      <c r="B6" s="386"/>
-      <c r="C6" s="386"/>
-      <c r="D6" s="386"/>
-      <c r="E6" s="386"/>
-      <c r="F6" s="386"/>
-      <c r="G6" s="386"/>
-      <c r="H6" s="386"/>
-      <c r="I6" s="386"/>
-      <c r="J6" s="386"/>
-      <c r="K6" s="391" t="s">
+      <c r="A6" s="387"/>
+      <c r="B6" s="387"/>
+      <c r="C6" s="387"/>
+      <c r="D6" s="387"/>
+      <c r="E6" s="387"/>
+      <c r="F6" s="387"/>
+      <c r="G6" s="387"/>
+      <c r="H6" s="387"/>
+      <c r="I6" s="387"/>
+      <c r="J6" s="387"/>
+      <c r="K6" s="401" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="391" t="s">
+      <c r="L6" s="401" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="391" t="s">
+      <c r="M6" s="401" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="391" t="s">
+      <c r="N6" s="401" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="391" t="s">
+      <c r="O6" s="401" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="391" t="s">
+      <c r="P6" s="401" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="391" t="s">
+      <c r="Q6" s="401" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="391" t="s">
+      <c r="R6" s="401" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="391" t="s">
+      <c r="S6" s="401" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="391" t="s">
+      <c r="T6" s="401" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="391" t="s">
+      <c r="U6" s="401" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="421" t="s">
+      <c r="V6" s="402" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="407"/>
-      <c r="X6" s="391" t="s">
+      <c r="W6" s="403"/>
+      <c r="X6" s="401" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="390" t="s">
+      <c r="Y6" s="393" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="390" t="s">
+      <c r="Z6" s="393" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="390" t="s">
+      <c r="AA6" s="393" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="390" t="s">
+      <c r="AB6" s="393" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="341" t="s">
+      <c r="AC6" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="341" t="s">
+      <c r="AD6" s="332" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="341" t="s">
+      <c r="AE6" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="341" t="s">
+      <c r="AF6" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="390" t="s">
+      <c r="AG6" s="393" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="341" t="s">
+      <c r="AH6" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="341" t="s">
+      <c r="AI6" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="390" t="s">
+      <c r="AJ6" s="393" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="418" t="s">
+      <c r="AK6" s="395" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="390" t="s">
+      <c r="AL6" s="393" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="390" t="s">
+      <c r="AM6" s="393" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="420" t="s">
+      <c r="AN6" s="399" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="390" t="s">
+      <c r="AO6" s="393" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="386"/>
-      <c r="AQ6" s="386"/>
-      <c r="AR6" s="386"/>
-      <c r="AS6" s="386"/>
-      <c r="AT6" s="386"/>
-      <c r="AU6" s="386"/>
-      <c r="AV6" s="386"/>
-      <c r="AW6" s="386"/>
-      <c r="AX6" s="386"/>
-      <c r="AY6" s="400" t="s">
+      <c r="AP6" s="387"/>
+      <c r="AQ6" s="387"/>
+      <c r="AR6" s="387"/>
+      <c r="AS6" s="387"/>
+      <c r="AT6" s="387"/>
+      <c r="AU6" s="387"/>
+      <c r="AV6" s="387"/>
+      <c r="AW6" s="387"/>
+      <c r="AX6" s="387"/>
+      <c r="AY6" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="401"/>
-      <c r="BA6" s="401"/>
-      <c r="BB6" s="401"/>
-      <c r="BC6" s="401"/>
-      <c r="BD6" s="401"/>
-      <c r="BE6" s="401"/>
-      <c r="BF6" s="401"/>
-      <c r="BG6" s="401"/>
-      <c r="BH6" s="401"/>
-      <c r="BI6" s="401"/>
-      <c r="BJ6" s="401"/>
-      <c r="BK6" s="401"/>
-      <c r="BL6" s="402"/>
-      <c r="BM6" s="400" t="s">
+      <c r="AZ6" s="390"/>
+      <c r="BA6" s="390"/>
+      <c r="BB6" s="390"/>
+      <c r="BC6" s="390"/>
+      <c r="BD6" s="390"/>
+      <c r="BE6" s="390"/>
+      <c r="BF6" s="390"/>
+      <c r="BG6" s="390"/>
+      <c r="BH6" s="390"/>
+      <c r="BI6" s="390"/>
+      <c r="BJ6" s="390"/>
+      <c r="BK6" s="390"/>
+      <c r="BL6" s="391"/>
+      <c r="BM6" s="389" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="401"/>
-      <c r="BO6" s="401"/>
-      <c r="BP6" s="401"/>
-      <c r="BQ6" s="402"/>
-      <c r="BR6" s="388" t="s">
+      <c r="BN6" s="390"/>
+      <c r="BO6" s="390"/>
+      <c r="BP6" s="390"/>
+      <c r="BQ6" s="391"/>
+      <c r="BR6" s="386" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="388" t="s">
+      <c r="BS6" s="386" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="386"/>
-      <c r="BU6" s="395"/>
-      <c r="BW6" s="398"/>
-      <c r="BX6" s="395"/>
-      <c r="BY6" s="410"/>
-      <c r="BZ6" s="410"/>
-      <c r="CA6" s="398"/>
-      <c r="CB6" s="386"/>
-      <c r="CC6" s="386"/>
-      <c r="CD6" s="386"/>
+      <c r="BT6" s="387"/>
+      <c r="BU6" s="396"/>
+      <c r="BW6" s="413"/>
+      <c r="BX6" s="396"/>
+      <c r="BY6" s="412"/>
+      <c r="BZ6" s="412"/>
+      <c r="CA6" s="413"/>
+      <c r="CB6" s="387"/>
+      <c r="CC6" s="387"/>
+      <c r="CD6" s="387"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="386"/>
-      <c r="B7" s="386"/>
-      <c r="C7" s="386"/>
-      <c r="D7" s="386"/>
-      <c r="E7" s="386"/>
-      <c r="F7" s="386"/>
-      <c r="G7" s="386"/>
-      <c r="H7" s="386"/>
-      <c r="I7" s="386"/>
-      <c r="J7" s="386"/>
-      <c r="K7" s="386"/>
-      <c r="L7" s="386"/>
-      <c r="M7" s="386"/>
-      <c r="N7" s="386"/>
-      <c r="O7" s="386"/>
-      <c r="P7" s="386"/>
-      <c r="Q7" s="386"/>
-      <c r="R7" s="386"/>
-      <c r="S7" s="386"/>
-      <c r="T7" s="386"/>
-      <c r="U7" s="386"/>
-      <c r="V7" s="396"/>
-      <c r="W7" s="422"/>
-      <c r="X7" s="386"/>
-      <c r="Y7" s="386"/>
-      <c r="Z7" s="386"/>
-      <c r="AA7" s="386"/>
-      <c r="AB7" s="386"/>
-      <c r="AC7" s="386"/>
-      <c r="AD7" s="386"/>
-      <c r="AE7" s="386"/>
-      <c r="AF7" s="386"/>
-      <c r="AG7" s="386"/>
-      <c r="AH7" s="386"/>
-      <c r="AI7" s="386"/>
-      <c r="AJ7" s="386"/>
-      <c r="AK7" s="395"/>
-      <c r="AL7" s="386"/>
-      <c r="AM7" s="386"/>
-      <c r="AN7" s="386"/>
-      <c r="AO7" s="386"/>
-      <c r="AP7" s="386"/>
-      <c r="AQ7" s="386"/>
-      <c r="AR7" s="386"/>
-      <c r="AS7" s="386"/>
-      <c r="AT7" s="386"/>
-      <c r="AU7" s="386"/>
-      <c r="AV7" s="386"/>
-      <c r="AW7" s="386"/>
-      <c r="AX7" s="386"/>
+      <c r="A7" s="387"/>
+      <c r="B7" s="387"/>
+      <c r="C7" s="387"/>
+      <c r="D7" s="387"/>
+      <c r="E7" s="387"/>
+      <c r="F7" s="387"/>
+      <c r="G7" s="387"/>
+      <c r="H7" s="387"/>
+      <c r="I7" s="387"/>
+      <c r="J7" s="387"/>
+      <c r="K7" s="387"/>
+      <c r="L7" s="387"/>
+      <c r="M7" s="387"/>
+      <c r="N7" s="387"/>
+      <c r="O7" s="387"/>
+      <c r="P7" s="387"/>
+      <c r="Q7" s="387"/>
+      <c r="R7" s="387"/>
+      <c r="S7" s="387"/>
+      <c r="T7" s="387"/>
+      <c r="U7" s="387"/>
+      <c r="V7" s="397"/>
+      <c r="W7" s="404"/>
+      <c r="X7" s="387"/>
+      <c r="Y7" s="387"/>
+      <c r="Z7" s="387"/>
+      <c r="AA7" s="387"/>
+      <c r="AB7" s="387"/>
+      <c r="AC7" s="387"/>
+      <c r="AD7" s="387"/>
+      <c r="AE7" s="387"/>
+      <c r="AF7" s="387"/>
+      <c r="AG7" s="387"/>
+      <c r="AH7" s="387"/>
+      <c r="AI7" s="387"/>
+      <c r="AJ7" s="387"/>
+      <c r="AK7" s="396"/>
+      <c r="AL7" s="387"/>
+      <c r="AM7" s="387"/>
+      <c r="AN7" s="387"/>
+      <c r="AO7" s="387"/>
+      <c r="AP7" s="387"/>
+      <c r="AQ7" s="387"/>
+      <c r="AR7" s="387"/>
+      <c r="AS7" s="387"/>
+      <c r="AT7" s="387"/>
+      <c r="AU7" s="387"/>
+      <c r="AV7" s="387"/>
+      <c r="AW7" s="387"/>
+      <c r="AX7" s="387"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12043,7 +12039,7 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="400" t="s">
+      <c r="BB7" s="389" t="s">
         <v>70</v>
       </c>
       <c r="BC7" s="392" t="s">
@@ -12052,7 +12048,7 @@
       <c r="BD7" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="413" t="s">
+      <c r="BE7" s="417" t="s">
         <v>73</v>
       </c>
       <c r="BF7" s="392" t="s">
@@ -12073,94 +12069,94 @@
       <c r="BK7" s="392" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="393" t="s">
+      <c r="BL7" s="419" t="s">
         <v>80</v>
       </c>
       <c r="BM7" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="400" t="s">
+      <c r="BN7" s="389" t="s">
         <v>82</v>
       </c>
       <c r="BO7" s="392" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="400" t="s">
+      <c r="BP7" s="389" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="400" t="s">
+      <c r="BQ7" s="389" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="386"/>
-      <c r="BS7" s="386"/>
-      <c r="BT7" s="386"/>
-      <c r="BU7" s="395"/>
-      <c r="BW7" s="398"/>
-      <c r="BX7" s="411"/>
-      <c r="BY7" s="412"/>
-      <c r="BZ7" s="412"/>
-      <c r="CA7" s="399"/>
-      <c r="CB7" s="386"/>
-      <c r="CC7" s="386"/>
-      <c r="CD7" s="386"/>
+      <c r="BR7" s="387"/>
+      <c r="BS7" s="387"/>
+      <c r="BT7" s="387"/>
+      <c r="BU7" s="396"/>
+      <c r="BW7" s="413"/>
+      <c r="BX7" s="414"/>
+      <c r="BY7" s="415"/>
+      <c r="BZ7" s="415"/>
+      <c r="CA7" s="416"/>
+      <c r="CB7" s="387"/>
+      <c r="CC7" s="387"/>
+      <c r="CD7" s="387"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="389"/>
-      <c r="B8" s="389"/>
-      <c r="C8" s="389"/>
-      <c r="D8" s="389"/>
-      <c r="E8" s="389"/>
-      <c r="F8" s="389"/>
-      <c r="G8" s="389"/>
-      <c r="H8" s="389"/>
-      <c r="I8" s="389"/>
-      <c r="J8" s="389"/>
-      <c r="K8" s="389"/>
-      <c r="L8" s="389"/>
-      <c r="M8" s="389"/>
-      <c r="N8" s="389"/>
-      <c r="O8" s="389"/>
-      <c r="P8" s="389"/>
-      <c r="Q8" s="389"/>
-      <c r="R8" s="389"/>
-      <c r="S8" s="389"/>
-      <c r="T8" s="389"/>
-      <c r="U8" s="389"/>
+      <c r="A8" s="388"/>
+      <c r="B8" s="388"/>
+      <c r="C8" s="388"/>
+      <c r="D8" s="388"/>
+      <c r="E8" s="388"/>
+      <c r="F8" s="388"/>
+      <c r="G8" s="388"/>
+      <c r="H8" s="388"/>
+      <c r="I8" s="388"/>
+      <c r="J8" s="388"/>
+      <c r="K8" s="388"/>
+      <c r="L8" s="388"/>
+      <c r="M8" s="388"/>
+      <c r="N8" s="388"/>
+      <c r="O8" s="388"/>
+      <c r="P8" s="388"/>
+      <c r="Q8" s="388"/>
+      <c r="R8" s="388"/>
+      <c r="S8" s="388"/>
+      <c r="T8" s="388"/>
+      <c r="U8" s="388"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="389"/>
-      <c r="Y8" s="389"/>
-      <c r="Z8" s="389"/>
-      <c r="AA8" s="389"/>
-      <c r="AB8" s="389"/>
-      <c r="AC8" s="389"/>
-      <c r="AD8" s="389"/>
-      <c r="AE8" s="389"/>
-      <c r="AF8" s="389"/>
-      <c r="AG8" s="389"/>
-      <c r="AH8" s="389"/>
-      <c r="AI8" s="389"/>
-      <c r="AJ8" s="389"/>
-      <c r="AK8" s="396"/>
-      <c r="AL8" s="389"/>
-      <c r="AM8" s="389"/>
-      <c r="AN8" s="389"/>
-      <c r="AO8" s="389"/>
-      <c r="AP8" s="389"/>
-      <c r="AQ8" s="389"/>
-      <c r="AR8" s="389"/>
-      <c r="AS8" s="389"/>
-      <c r="AT8" s="389"/>
-      <c r="AU8" s="389"/>
-      <c r="AV8" s="389"/>
-      <c r="AW8" s="389"/>
-      <c r="AX8" s="389"/>
+      <c r="X8" s="388"/>
+      <c r="Y8" s="388"/>
+      <c r="Z8" s="388"/>
+      <c r="AA8" s="388"/>
+      <c r="AB8" s="388"/>
+      <c r="AC8" s="388"/>
+      <c r="AD8" s="388"/>
+      <c r="AE8" s="388"/>
+      <c r="AF8" s="388"/>
+      <c r="AG8" s="388"/>
+      <c r="AH8" s="388"/>
+      <c r="AI8" s="388"/>
+      <c r="AJ8" s="388"/>
+      <c r="AK8" s="397"/>
+      <c r="AL8" s="388"/>
+      <c r="AM8" s="388"/>
+      <c r="AN8" s="388"/>
+      <c r="AO8" s="388"/>
+      <c r="AP8" s="388"/>
+      <c r="AQ8" s="388"/>
+      <c r="AR8" s="388"/>
+      <c r="AS8" s="388"/>
+      <c r="AT8" s="388"/>
+      <c r="AU8" s="388"/>
+      <c r="AV8" s="388"/>
+      <c r="AW8" s="388"/>
+      <c r="AX8" s="388"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12170,27 +12166,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="389"/>
-      <c r="BC8" s="389"/>
-      <c r="BD8" s="389"/>
-      <c r="BE8" s="389"/>
-      <c r="BF8" s="389"/>
-      <c r="BG8" s="389"/>
-      <c r="BH8" s="389"/>
-      <c r="BI8" s="389"/>
-      <c r="BJ8" s="389"/>
-      <c r="BK8" s="389"/>
-      <c r="BL8" s="389"/>
-      <c r="BM8" s="389"/>
-      <c r="BN8" s="389"/>
-      <c r="BO8" s="389"/>
-      <c r="BP8" s="389"/>
-      <c r="BQ8" s="389"/>
-      <c r="BR8" s="389"/>
-      <c r="BS8" s="389"/>
-      <c r="BT8" s="389"/>
-      <c r="BU8" s="396"/>
-      <c r="BW8" s="399"/>
+      <c r="BB8" s="388"/>
+      <c r="BC8" s="388"/>
+      <c r="BD8" s="388"/>
+      <c r="BE8" s="388"/>
+      <c r="BF8" s="388"/>
+      <c r="BG8" s="388"/>
+      <c r="BH8" s="388"/>
+      <c r="BI8" s="388"/>
+      <c r="BJ8" s="388"/>
+      <c r="BK8" s="388"/>
+      <c r="BL8" s="388"/>
+      <c r="BM8" s="388"/>
+      <c r="BN8" s="388"/>
+      <c r="BO8" s="388"/>
+      <c r="BP8" s="388"/>
+      <c r="BQ8" s="388"/>
+      <c r="BR8" s="388"/>
+      <c r="BS8" s="388"/>
+      <c r="BT8" s="388"/>
+      <c r="BU8" s="397"/>
+      <c r="BW8" s="416"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12203,9 +12199,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="387"/>
-      <c r="CC8" s="387"/>
-      <c r="CD8" s="387"/>
+      <c r="CB8" s="408"/>
+      <c r="CC8" s="408"/>
+      <c r="CD8" s="408"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -14663,6 +14659,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="BS6:BS8"/>
     <mergeCell ref="BM6:BQ6"/>
     <mergeCell ref="AC6:AC8"/>
@@ -14679,72 +14741,6 @@
     <mergeCell ref="BD7:BD8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -14972,88 +14968,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="432"/>
-      <c r="B3" s="431"/>
-      <c r="C3" s="431"/>
-      <c r="D3" s="431"/>
-      <c r="E3" s="431"/>
-      <c r="F3" s="431"/>
-      <c r="G3" s="431"/>
-      <c r="H3" s="431"/>
-      <c r="I3" s="431"/>
-      <c r="J3" s="431"/>
-      <c r="K3" s="431"/>
-      <c r="L3" s="431"/>
-      <c r="M3" s="431"/>
-      <c r="N3" s="431"/>
-      <c r="O3" s="431"/>
-      <c r="P3" s="431"/>
-      <c r="Q3" s="431"/>
-      <c r="R3" s="431"/>
-      <c r="S3" s="431"/>
-      <c r="T3" s="431"/>
-      <c r="U3" s="431"/>
-      <c r="V3" s="431"/>
-      <c r="W3" s="431"/>
-      <c r="X3" s="431"/>
-      <c r="Y3" s="431"/>
-      <c r="Z3" s="431"/>
-      <c r="AA3" s="431"/>
-      <c r="AB3" s="431"/>
-      <c r="AC3" s="431"/>
-      <c r="AD3" s="431"/>
-      <c r="AE3" s="431"/>
-      <c r="AF3" s="431"/>
-      <c r="AG3" s="431"/>
-      <c r="AH3" s="431"/>
-      <c r="AI3" s="431"/>
-      <c r="AJ3" s="431"/>
-      <c r="AK3" s="431"/>
-      <c r="AL3" s="431"/>
-      <c r="AM3" s="431"/>
-      <c r="AN3" s="431"/>
-      <c r="AO3" s="431"/>
-      <c r="AP3" s="431"/>
-      <c r="AQ3" s="431"/>
-      <c r="AR3" s="431"/>
-      <c r="AS3" s="431"/>
-      <c r="AT3" s="431"/>
-      <c r="AU3" s="431"/>
-      <c r="AV3" s="431"/>
-      <c r="AW3" s="431"/>
-      <c r="AX3" s="431"/>
-      <c r="AY3" s="431"/>
-      <c r="AZ3" s="431"/>
-      <c r="BA3" s="431"/>
-      <c r="BB3" s="431"/>
-      <c r="BC3" s="431"/>
-      <c r="BD3" s="431"/>
-      <c r="BE3" s="431"/>
-      <c r="BF3" s="431"/>
-      <c r="BG3" s="431"/>
-      <c r="BH3" s="431"/>
-      <c r="BI3" s="431"/>
-      <c r="BJ3" s="431"/>
-      <c r="BK3" s="431"/>
-      <c r="BL3" s="431"/>
-      <c r="BM3" s="431"/>
-      <c r="BN3" s="431"/>
-      <c r="BO3" s="431"/>
-      <c r="BP3" s="431"/>
-      <c r="BQ3" s="431"/>
-      <c r="BR3" s="431"/>
-      <c r="BS3" s="431"/>
-      <c r="BT3" s="431"/>
-      <c r="BU3" s="431"/>
+      <c r="A3" s="433"/>
+      <c r="B3" s="432"/>
+      <c r="C3" s="432"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
+      <c r="F3" s="432"/>
+      <c r="G3" s="432"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
+      <c r="J3" s="432"/>
+      <c r="K3" s="432"/>
+      <c r="L3" s="432"/>
+      <c r="M3" s="432"/>
+      <c r="N3" s="432"/>
+      <c r="O3" s="432"/>
+      <c r="P3" s="432"/>
+      <c r="Q3" s="432"/>
+      <c r="R3" s="432"/>
+      <c r="S3" s="432"/>
+      <c r="T3" s="432"/>
+      <c r="U3" s="432"/>
+      <c r="V3" s="432"/>
+      <c r="W3" s="432"/>
+      <c r="X3" s="432"/>
+      <c r="Y3" s="432"/>
+      <c r="Z3" s="432"/>
+      <c r="AA3" s="432"/>
+      <c r="AB3" s="432"/>
+      <c r="AC3" s="432"/>
+      <c r="AD3" s="432"/>
+      <c r="AE3" s="432"/>
+      <c r="AF3" s="432"/>
+      <c r="AG3" s="432"/>
+      <c r="AH3" s="432"/>
+      <c r="AI3" s="432"/>
+      <c r="AJ3" s="432"/>
+      <c r="AK3" s="432"/>
+      <c r="AL3" s="432"/>
+      <c r="AM3" s="432"/>
+      <c r="AN3" s="432"/>
+      <c r="AO3" s="432"/>
+      <c r="AP3" s="432"/>
+      <c r="AQ3" s="432"/>
+      <c r="AR3" s="432"/>
+      <c r="AS3" s="432"/>
+      <c r="AT3" s="432"/>
+      <c r="AU3" s="432"/>
+      <c r="AV3" s="432"/>
+      <c r="AW3" s="432"/>
+      <c r="AX3" s="432"/>
+      <c r="AY3" s="432"/>
+      <c r="AZ3" s="432"/>
+      <c r="BA3" s="432"/>
+      <c r="BB3" s="432"/>
+      <c r="BC3" s="432"/>
+      <c r="BD3" s="432"/>
+      <c r="BE3" s="432"/>
+      <c r="BF3" s="432"/>
+      <c r="BG3" s="432"/>
+      <c r="BH3" s="432"/>
+      <c r="BI3" s="432"/>
+      <c r="BJ3" s="432"/>
+      <c r="BK3" s="432"/>
+      <c r="BL3" s="432"/>
+      <c r="BM3" s="432"/>
+      <c r="BN3" s="432"/>
+      <c r="BO3" s="432"/>
+      <c r="BP3" s="432"/>
+      <c r="BQ3" s="432"/>
+      <c r="BR3" s="432"/>
+      <c r="BS3" s="432"/>
+      <c r="BT3" s="432"/>
+      <c r="BU3" s="432"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="430" t="s">
+      <c r="BW3" s="431" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="431"/>
-      <c r="BY3" s="431"/>
-      <c r="BZ3" s="431"/>
-      <c r="CA3" s="431"/>
-      <c r="CB3" s="431"/>
+      <c r="BX3" s="432"/>
+      <c r="BY3" s="432"/>
+      <c r="BZ3" s="432"/>
+      <c r="CA3" s="432"/>
+      <c r="CB3" s="432"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15137,12 +15133,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="431"/>
-      <c r="BX4" s="431"/>
-      <c r="BY4" s="431"/>
-      <c r="BZ4" s="431"/>
-      <c r="CA4" s="431"/>
-      <c r="CB4" s="431"/>
+      <c r="BW4" s="432"/>
+      <c r="BX4" s="432"/>
+      <c r="BY4" s="432"/>
+      <c r="BZ4" s="432"/>
+      <c r="CA4" s="432"/>
+      <c r="CB4" s="432"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15220,12 +15216,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="370"/>
-      <c r="BX5" s="370"/>
-      <c r="BY5" s="370"/>
-      <c r="BZ5" s="370"/>
-      <c r="CA5" s="370"/>
-      <c r="CB5" s="370"/>
+      <c r="BW5" s="349"/>
+      <c r="BX5" s="349"/>
+      <c r="BY5" s="349"/>
+      <c r="BZ5" s="349"/>
+      <c r="CA5" s="349"/>
+      <c r="CB5" s="349"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15303,12 +15299,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="370"/>
-      <c r="BX6" s="370"/>
-      <c r="BY6" s="370"/>
-      <c r="BZ6" s="370"/>
-      <c r="CA6" s="370"/>
-      <c r="CB6" s="370"/>
+      <c r="BW6" s="349"/>
+      <c r="BX6" s="349"/>
+      <c r="BY6" s="349"/>
+      <c r="BZ6" s="349"/>
+      <c r="CA6" s="349"/>
+      <c r="CB6" s="349"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15396,358 +15392,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="417" t="s">
+      <c r="A8" s="394" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="416" t="s">
+      <c r="B8" s="405" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="390" t="s">
+      <c r="C8" s="393" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="415" t="s">
+      <c r="D8" s="400" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="415" t="s">
+      <c r="E8" s="400" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="434" t="s">
+      <c r="F8" s="429" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="424" t="s">
+      <c r="G8" s="426" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="361" t="s">
+      <c r="H8" s="372" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="361" t="s">
+      <c r="I8" s="372" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="424" t="s">
+      <c r="J8" s="426" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="435" t="s">
+      <c r="K8" s="430" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="401"/>
-      <c r="M8" s="401"/>
-      <c r="N8" s="401"/>
-      <c r="O8" s="401"/>
-      <c r="P8" s="401"/>
-      <c r="Q8" s="401"/>
-      <c r="R8" s="401"/>
-      <c r="S8" s="401"/>
-      <c r="T8" s="401"/>
-      <c r="U8" s="401"/>
-      <c r="V8" s="401"/>
-      <c r="W8" s="401"/>
-      <c r="X8" s="401"/>
-      <c r="Y8" s="424" t="s">
+      <c r="L8" s="390"/>
+      <c r="M8" s="390"/>
+      <c r="N8" s="390"/>
+      <c r="O8" s="390"/>
+      <c r="P8" s="390"/>
+      <c r="Q8" s="390"/>
+      <c r="R8" s="390"/>
+      <c r="S8" s="390"/>
+      <c r="T8" s="390"/>
+      <c r="U8" s="390"/>
+      <c r="V8" s="390"/>
+      <c r="W8" s="390"/>
+      <c r="X8" s="390"/>
+      <c r="Y8" s="426" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="401"/>
-      <c r="AA8" s="401"/>
-      <c r="AB8" s="401"/>
-      <c r="AC8" s="401"/>
-      <c r="AD8" s="401"/>
-      <c r="AE8" s="401"/>
-      <c r="AF8" s="401"/>
-      <c r="AG8" s="401"/>
-      <c r="AH8" s="401"/>
-      <c r="AI8" s="401"/>
-      <c r="AJ8" s="401"/>
-      <c r="AK8" s="401"/>
-      <c r="AL8" s="401"/>
-      <c r="AM8" s="401"/>
-      <c r="AN8" s="401"/>
-      <c r="AO8" s="402"/>
-      <c r="AP8" s="424" t="s">
+      <c r="Z8" s="390"/>
+      <c r="AA8" s="390"/>
+      <c r="AB8" s="390"/>
+      <c r="AC8" s="390"/>
+      <c r="AD8" s="390"/>
+      <c r="AE8" s="390"/>
+      <c r="AF8" s="390"/>
+      <c r="AG8" s="390"/>
+      <c r="AH8" s="390"/>
+      <c r="AI8" s="390"/>
+      <c r="AJ8" s="390"/>
+      <c r="AK8" s="390"/>
+      <c r="AL8" s="390"/>
+      <c r="AM8" s="390"/>
+      <c r="AN8" s="390"/>
+      <c r="AO8" s="391"/>
+      <c r="AP8" s="426" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="424" t="s">
+      <c r="AQ8" s="426" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="424" t="s">
+      <c r="AR8" s="426" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="424" t="s">
+      <c r="AS8" s="426" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="424" t="s">
+      <c r="AT8" s="426" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="424" t="s">
+      <c r="AU8" s="426" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="390" t="s">
+      <c r="AV8" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="390" t="s">
+      <c r="AW8" s="393" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="390" t="s">
+      <c r="AX8" s="393" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="400" t="s">
+      <c r="AY8" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="401"/>
-      <c r="BA8" s="401"/>
-      <c r="BB8" s="401"/>
-      <c r="BC8" s="401"/>
-      <c r="BD8" s="401"/>
-      <c r="BE8" s="401"/>
-      <c r="BF8" s="401"/>
-      <c r="BG8" s="401"/>
-      <c r="BH8" s="401"/>
-      <c r="BI8" s="401"/>
-      <c r="BJ8" s="401"/>
-      <c r="BK8" s="401"/>
-      <c r="BL8" s="401"/>
-      <c r="BM8" s="401"/>
-      <c r="BN8" s="401"/>
-      <c r="BO8" s="401"/>
-      <c r="BP8" s="402"/>
-      <c r="BQ8" s="406" t="s">
+      <c r="AZ8" s="390"/>
+      <c r="BA8" s="390"/>
+      <c r="BB8" s="390"/>
+      <c r="BC8" s="390"/>
+      <c r="BD8" s="390"/>
+      <c r="BE8" s="390"/>
+      <c r="BF8" s="390"/>
+      <c r="BG8" s="390"/>
+      <c r="BH8" s="390"/>
+      <c r="BI8" s="390"/>
+      <c r="BJ8" s="390"/>
+      <c r="BK8" s="390"/>
+      <c r="BL8" s="390"/>
+      <c r="BM8" s="390"/>
+      <c r="BN8" s="390"/>
+      <c r="BO8" s="390"/>
+      <c r="BP8" s="391"/>
+      <c r="BQ8" s="409" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="407"/>
-      <c r="BS8" s="400" t="s">
+      <c r="BR8" s="403"/>
+      <c r="BS8" s="389" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="400" t="s">
+      <c r="BT8" s="389" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="394" t="s">
+      <c r="BU8" s="420" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="397" t="s">
+      <c r="BW8" s="421" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="408" t="s">
+      <c r="BX8" s="410" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="409"/>
-      <c r="BZ8" s="409"/>
-      <c r="CA8" s="407"/>
-      <c r="CB8" s="403" t="s">
+      <c r="BY8" s="411"/>
+      <c r="BZ8" s="411"/>
+      <c r="CA8" s="403"/>
+      <c r="CB8" s="422" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="332" t="s">
+      <c r="CC8" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="332" t="s">
+      <c r="CD8" s="350" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="386"/>
-      <c r="B9" s="386"/>
-      <c r="C9" s="386"/>
-      <c r="D9" s="386"/>
-      <c r="E9" s="386"/>
-      <c r="F9" s="386"/>
-      <c r="G9" s="386"/>
-      <c r="H9" s="386"/>
-      <c r="I9" s="386"/>
-      <c r="J9" s="386"/>
-      <c r="K9" s="426" t="s">
+      <c r="A9" s="387"/>
+      <c r="B9" s="387"/>
+      <c r="C9" s="387"/>
+      <c r="D9" s="387"/>
+      <c r="E9" s="387"/>
+      <c r="F9" s="387"/>
+      <c r="G9" s="387"/>
+      <c r="H9" s="387"/>
+      <c r="I9" s="387"/>
+      <c r="J9" s="387"/>
+      <c r="K9" s="423" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="426" t="s">
+      <c r="L9" s="423" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="426" t="s">
+      <c r="M9" s="423" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="426" t="s">
+      <c r="N9" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="426" t="s">
+      <c r="O9" s="423" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="426" t="s">
+      <c r="P9" s="423" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="426" t="s">
+      <c r="Q9" s="423" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="426" t="s">
+      <c r="R9" s="423" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="426" t="s">
+      <c r="S9" s="423" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="426" t="s">
+      <c r="T9" s="423" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="426" t="s">
+      <c r="U9" s="423" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="429" t="s">
+      <c r="V9" s="435" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="407"/>
-      <c r="X9" s="426" t="s">
+      <c r="W9" s="403"/>
+      <c r="X9" s="423" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="423" t="s">
+      <c r="Y9" s="425" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="423" t="s">
+      <c r="Z9" s="425" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="423" t="s">
+      <c r="AA9" s="425" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="423" t="s">
+      <c r="AB9" s="425" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="335" t="s">
+      <c r="AC9" s="338" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="335" t="s">
+      <c r="AD9" s="338" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="335" t="s">
+      <c r="AE9" s="338" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="335" t="s">
+      <c r="AF9" s="338" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="423" t="s">
+      <c r="AG9" s="425" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="335" t="s">
+      <c r="AH9" s="338" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="335" t="s">
+      <c r="AI9" s="338" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="423" t="s">
+      <c r="AJ9" s="425" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="418" t="s">
+      <c r="AK9" s="395" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="390" t="s">
+      <c r="AL9" s="393" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="423" t="s">
+      <c r="AM9" s="425" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="420" t="s">
+      <c r="AN9" s="399" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="390" t="s">
+      <c r="AO9" s="393" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="386"/>
-      <c r="AQ9" s="386"/>
-      <c r="AR9" s="386"/>
-      <c r="AS9" s="386"/>
-      <c r="AT9" s="386"/>
-      <c r="AU9" s="386"/>
-      <c r="AV9" s="386"/>
-      <c r="AW9" s="386"/>
-      <c r="AX9" s="386"/>
-      <c r="AY9" s="400" t="s">
+      <c r="AP9" s="387"/>
+      <c r="AQ9" s="387"/>
+      <c r="AR9" s="387"/>
+      <c r="AS9" s="387"/>
+      <c r="AT9" s="387"/>
+      <c r="AU9" s="387"/>
+      <c r="AV9" s="387"/>
+      <c r="AW9" s="387"/>
+      <c r="AX9" s="387"/>
+      <c r="AY9" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="401"/>
-      <c r="BA9" s="401"/>
-      <c r="BB9" s="401"/>
-      <c r="BC9" s="401"/>
-      <c r="BD9" s="401"/>
-      <c r="BE9" s="401"/>
-      <c r="BF9" s="401"/>
-      <c r="BG9" s="401"/>
-      <c r="BH9" s="401"/>
-      <c r="BI9" s="401"/>
-      <c r="BJ9" s="402"/>
-      <c r="BK9" s="400" t="s">
+      <c r="AZ9" s="390"/>
+      <c r="BA9" s="390"/>
+      <c r="BB9" s="390"/>
+      <c r="BC9" s="390"/>
+      <c r="BD9" s="390"/>
+      <c r="BE9" s="390"/>
+      <c r="BF9" s="390"/>
+      <c r="BG9" s="390"/>
+      <c r="BH9" s="390"/>
+      <c r="BI9" s="390"/>
+      <c r="BJ9" s="391"/>
+      <c r="BK9" s="389" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="401"/>
-      <c r="BM9" s="401"/>
-      <c r="BN9" s="401"/>
-      <c r="BO9" s="401"/>
-      <c r="BP9" s="402"/>
-      <c r="BQ9" s="388" t="s">
+      <c r="BL9" s="390"/>
+      <c r="BM9" s="390"/>
+      <c r="BN9" s="390"/>
+      <c r="BO9" s="390"/>
+      <c r="BP9" s="391"/>
+      <c r="BQ9" s="386" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="388" t="s">
+      <c r="BR9" s="386" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="386"/>
-      <c r="BT9" s="386"/>
-      <c r="BU9" s="395"/>
+      <c r="BS9" s="387"/>
+      <c r="BT9" s="387"/>
+      <c r="BU9" s="396"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="398"/>
-      <c r="BX9" s="395"/>
-      <c r="BY9" s="436"/>
-      <c r="BZ9" s="436"/>
-      <c r="CA9" s="398"/>
-      <c r="CB9" s="386"/>
-      <c r="CC9" s="386"/>
-      <c r="CD9" s="386"/>
+      <c r="BW9" s="413"/>
+      <c r="BX9" s="396"/>
+      <c r="BY9" s="427"/>
+      <c r="BZ9" s="427"/>
+      <c r="CA9" s="413"/>
+      <c r="CB9" s="387"/>
+      <c r="CC9" s="387"/>
+      <c r="CD9" s="387"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="386"/>
-      <c r="B10" s="386"/>
-      <c r="C10" s="386"/>
-      <c r="D10" s="386"/>
-      <c r="E10" s="386"/>
-      <c r="F10" s="386"/>
-      <c r="G10" s="386"/>
-      <c r="H10" s="386"/>
-      <c r="I10" s="386"/>
-      <c r="J10" s="386"/>
-      <c r="K10" s="386"/>
-      <c r="L10" s="386"/>
-      <c r="M10" s="386"/>
-      <c r="N10" s="386"/>
-      <c r="O10" s="386"/>
-      <c r="P10" s="386"/>
-      <c r="Q10" s="386"/>
-      <c r="R10" s="386"/>
-      <c r="S10" s="386"/>
-      <c r="T10" s="386"/>
-      <c r="U10" s="386"/>
-      <c r="V10" s="396"/>
-      <c r="W10" s="422"/>
-      <c r="X10" s="386"/>
-      <c r="Y10" s="386"/>
-      <c r="Z10" s="386"/>
-      <c r="AA10" s="386"/>
-      <c r="AB10" s="386"/>
-      <c r="AC10" s="386"/>
-      <c r="AD10" s="386"/>
-      <c r="AE10" s="386"/>
-      <c r="AF10" s="386"/>
-      <c r="AG10" s="386"/>
-      <c r="AH10" s="386"/>
-      <c r="AI10" s="386"/>
-      <c r="AJ10" s="386"/>
-      <c r="AK10" s="395"/>
-      <c r="AL10" s="386"/>
-      <c r="AM10" s="386"/>
-      <c r="AN10" s="386"/>
-      <c r="AO10" s="386"/>
-      <c r="AP10" s="386"/>
-      <c r="AQ10" s="386"/>
-      <c r="AR10" s="386"/>
-      <c r="AS10" s="386"/>
-      <c r="AT10" s="386"/>
-      <c r="AU10" s="386"/>
-      <c r="AV10" s="386"/>
-      <c r="AW10" s="386"/>
-      <c r="AX10" s="386"/>
+      <c r="A10" s="387"/>
+      <c r="B10" s="387"/>
+      <c r="C10" s="387"/>
+      <c r="D10" s="387"/>
+      <c r="E10" s="387"/>
+      <c r="F10" s="387"/>
+      <c r="G10" s="387"/>
+      <c r="H10" s="387"/>
+      <c r="I10" s="387"/>
+      <c r="J10" s="387"/>
+      <c r="K10" s="387"/>
+      <c r="L10" s="387"/>
+      <c r="M10" s="387"/>
+      <c r="N10" s="387"/>
+      <c r="O10" s="387"/>
+      <c r="P10" s="387"/>
+      <c r="Q10" s="387"/>
+      <c r="R10" s="387"/>
+      <c r="S10" s="387"/>
+      <c r="T10" s="387"/>
+      <c r="U10" s="387"/>
+      <c r="V10" s="397"/>
+      <c r="W10" s="404"/>
+      <c r="X10" s="387"/>
+      <c r="Y10" s="387"/>
+      <c r="Z10" s="387"/>
+      <c r="AA10" s="387"/>
+      <c r="AB10" s="387"/>
+      <c r="AC10" s="387"/>
+      <c r="AD10" s="387"/>
+      <c r="AE10" s="387"/>
+      <c r="AF10" s="387"/>
+      <c r="AG10" s="387"/>
+      <c r="AH10" s="387"/>
+      <c r="AI10" s="387"/>
+      <c r="AJ10" s="387"/>
+      <c r="AK10" s="396"/>
+      <c r="AL10" s="387"/>
+      <c r="AM10" s="387"/>
+      <c r="AN10" s="387"/>
+      <c r="AO10" s="387"/>
+      <c r="AP10" s="387"/>
+      <c r="AQ10" s="387"/>
+      <c r="AR10" s="387"/>
+      <c r="AS10" s="387"/>
+      <c r="AT10" s="387"/>
+      <c r="AU10" s="387"/>
+      <c r="AV10" s="387"/>
+      <c r="AW10" s="387"/>
+      <c r="AX10" s="387"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -15757,40 +15753,40 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="433" t="s">
+      <c r="BB10" s="434" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="427" t="s">
+      <c r="BC10" s="424" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="427" t="s">
+      <c r="BD10" s="424" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="427" t="s">
+      <c r="BE10" s="424" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="427" t="s">
+      <c r="BF10" s="424" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="427" t="s">
+      <c r="BG10" s="424" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="427" t="s">
+      <c r="BH10" s="424" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="427" t="s">
+      <c r="BI10" s="424" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="425" t="s">
+      <c r="BJ10" s="436" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="427" t="s">
+      <c r="BK10" s="424" t="s">
         <v>81</v>
       </c>
       <c r="BL10" s="428" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="427" t="s">
+      <c r="BM10" s="424" t="s">
         <v>83</v>
       </c>
       <c r="BN10" s="428" t="s">
@@ -15799,81 +15795,81 @@
       <c r="BO10" s="428" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="400" t="s">
+      <c r="BP10" s="389" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="386"/>
-      <c r="BR10" s="386"/>
-      <c r="BS10" s="386"/>
-      <c r="BT10" s="386"/>
-      <c r="BU10" s="395"/>
+      <c r="BQ10" s="387"/>
+      <c r="BR10" s="387"/>
+      <c r="BS10" s="387"/>
+      <c r="BT10" s="387"/>
+      <c r="BU10" s="396"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="398"/>
-      <c r="BX10" s="411"/>
-      <c r="BY10" s="412"/>
-      <c r="BZ10" s="412"/>
-      <c r="CA10" s="399"/>
-      <c r="CB10" s="386"/>
-      <c r="CC10" s="386"/>
-      <c r="CD10" s="386"/>
+      <c r="BW10" s="413"/>
+      <c r="BX10" s="414"/>
+      <c r="BY10" s="415"/>
+      <c r="BZ10" s="415"/>
+      <c r="CA10" s="416"/>
+      <c r="CB10" s="387"/>
+      <c r="CC10" s="387"/>
+      <c r="CD10" s="387"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="389"/>
-      <c r="B11" s="389"/>
-      <c r="C11" s="389"/>
-      <c r="D11" s="389"/>
-      <c r="E11" s="389"/>
-      <c r="F11" s="389"/>
-      <c r="G11" s="389"/>
-      <c r="H11" s="389"/>
-      <c r="I11" s="389"/>
-      <c r="J11" s="389"/>
-      <c r="K11" s="389"/>
-      <c r="L11" s="389"/>
-      <c r="M11" s="389"/>
-      <c r="N11" s="389"/>
-      <c r="O11" s="389"/>
-      <c r="P11" s="389"/>
-      <c r="Q11" s="389"/>
-      <c r="R11" s="389"/>
-      <c r="S11" s="389"/>
-      <c r="T11" s="389"/>
-      <c r="U11" s="389"/>
+      <c r="A11" s="388"/>
+      <c r="B11" s="388"/>
+      <c r="C11" s="388"/>
+      <c r="D11" s="388"/>
+      <c r="E11" s="388"/>
+      <c r="F11" s="388"/>
+      <c r="G11" s="388"/>
+      <c r="H11" s="388"/>
+      <c r="I11" s="388"/>
+      <c r="J11" s="388"/>
+      <c r="K11" s="388"/>
+      <c r="L11" s="388"/>
+      <c r="M11" s="388"/>
+      <c r="N11" s="388"/>
+      <c r="O11" s="388"/>
+      <c r="P11" s="388"/>
+      <c r="Q11" s="388"/>
+      <c r="R11" s="388"/>
+      <c r="S11" s="388"/>
+      <c r="T11" s="388"/>
+      <c r="U11" s="388"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="389"/>
-      <c r="Y11" s="389"/>
-      <c r="Z11" s="389"/>
-      <c r="AA11" s="389"/>
-      <c r="AB11" s="389"/>
-      <c r="AC11" s="389"/>
-      <c r="AD11" s="389"/>
-      <c r="AE11" s="389"/>
-      <c r="AF11" s="389"/>
-      <c r="AG11" s="389"/>
-      <c r="AH11" s="389"/>
-      <c r="AI11" s="389"/>
-      <c r="AJ11" s="389"/>
-      <c r="AK11" s="396"/>
-      <c r="AL11" s="389"/>
-      <c r="AM11" s="389"/>
-      <c r="AN11" s="389"/>
-      <c r="AO11" s="389"/>
-      <c r="AP11" s="389"/>
-      <c r="AQ11" s="389"/>
-      <c r="AR11" s="389"/>
-      <c r="AS11" s="389"/>
-      <c r="AT11" s="389"/>
-      <c r="AU11" s="389"/>
-      <c r="AV11" s="389"/>
-      <c r="AW11" s="389"/>
-      <c r="AX11" s="389"/>
+      <c r="X11" s="388"/>
+      <c r="Y11" s="388"/>
+      <c r="Z11" s="388"/>
+      <c r="AA11" s="388"/>
+      <c r="AB11" s="388"/>
+      <c r="AC11" s="388"/>
+      <c r="AD11" s="388"/>
+      <c r="AE11" s="388"/>
+      <c r="AF11" s="388"/>
+      <c r="AG11" s="388"/>
+      <c r="AH11" s="388"/>
+      <c r="AI11" s="388"/>
+      <c r="AJ11" s="388"/>
+      <c r="AK11" s="397"/>
+      <c r="AL11" s="388"/>
+      <c r="AM11" s="388"/>
+      <c r="AN11" s="388"/>
+      <c r="AO11" s="388"/>
+      <c r="AP11" s="388"/>
+      <c r="AQ11" s="388"/>
+      <c r="AR11" s="388"/>
+      <c r="AS11" s="388"/>
+      <c r="AT11" s="388"/>
+      <c r="AU11" s="388"/>
+      <c r="AV11" s="388"/>
+      <c r="AW11" s="388"/>
+      <c r="AX11" s="388"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -15883,28 +15879,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="389"/>
-      <c r="BC11" s="389"/>
-      <c r="BD11" s="389"/>
-      <c r="BE11" s="389"/>
-      <c r="BF11" s="389"/>
-      <c r="BG11" s="389"/>
-      <c r="BH11" s="389"/>
-      <c r="BI11" s="389"/>
-      <c r="BJ11" s="389"/>
-      <c r="BK11" s="389"/>
-      <c r="BL11" s="389"/>
-      <c r="BM11" s="389"/>
-      <c r="BN11" s="389"/>
-      <c r="BO11" s="389"/>
-      <c r="BP11" s="389"/>
-      <c r="BQ11" s="389"/>
-      <c r="BR11" s="389"/>
-      <c r="BS11" s="389"/>
-      <c r="BT11" s="389"/>
-      <c r="BU11" s="396"/>
+      <c r="BB11" s="388"/>
+      <c r="BC11" s="388"/>
+      <c r="BD11" s="388"/>
+      <c r="BE11" s="388"/>
+      <c r="BF11" s="388"/>
+      <c r="BG11" s="388"/>
+      <c r="BH11" s="388"/>
+      <c r="BI11" s="388"/>
+      <c r="BJ11" s="388"/>
+      <c r="BK11" s="388"/>
+      <c r="BL11" s="388"/>
+      <c r="BM11" s="388"/>
+      <c r="BN11" s="388"/>
+      <c r="BO11" s="388"/>
+      <c r="BP11" s="388"/>
+      <c r="BQ11" s="388"/>
+      <c r="BR11" s="388"/>
+      <c r="BS11" s="388"/>
+      <c r="BT11" s="388"/>
+      <c r="BU11" s="397"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="399"/>
+      <c r="BW11" s="416"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -15917,9 +15913,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="387"/>
-      <c r="CC11" s="387"/>
-      <c r="CD11" s="387"/>
+      <c r="CB11" s="408"/>
+      <c r="CC11" s="408"/>
+      <c r="CD11" s="408"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18320,16 +18316,62 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="BX8:CA10"/>
@@ -18346,62 +18388,16 @@
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18631,87 +18627,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="414"/>
-      <c r="B3" s="405"/>
-      <c r="C3" s="405"/>
-      <c r="D3" s="405"/>
-      <c r="E3" s="405"/>
-      <c r="F3" s="405"/>
-      <c r="G3" s="405"/>
-      <c r="H3" s="405"/>
-      <c r="I3" s="405"/>
-      <c r="J3" s="405"/>
-      <c r="K3" s="405"/>
-      <c r="L3" s="405"/>
-      <c r="M3" s="405"/>
-      <c r="N3" s="405"/>
-      <c r="O3" s="405"/>
-      <c r="P3" s="405"/>
-      <c r="Q3" s="405"/>
-      <c r="R3" s="405"/>
-      <c r="S3" s="405"/>
-      <c r="T3" s="405"/>
-      <c r="U3" s="405"/>
-      <c r="V3" s="405"/>
-      <c r="W3" s="405"/>
-      <c r="X3" s="405"/>
-      <c r="Y3" s="405"/>
-      <c r="Z3" s="405"/>
-      <c r="AA3" s="405"/>
-      <c r="AB3" s="405"/>
-      <c r="AC3" s="405"/>
-      <c r="AD3" s="405"/>
-      <c r="AE3" s="405"/>
-      <c r="AF3" s="405"/>
-      <c r="AG3" s="405"/>
-      <c r="AH3" s="405"/>
-      <c r="AI3" s="405"/>
-      <c r="AJ3" s="405"/>
-      <c r="AK3" s="405"/>
-      <c r="AL3" s="405"/>
-      <c r="AM3" s="405"/>
-      <c r="AN3" s="405"/>
-      <c r="AO3" s="405"/>
-      <c r="AP3" s="405"/>
-      <c r="AQ3" s="405"/>
-      <c r="AR3" s="405"/>
-      <c r="AS3" s="405"/>
-      <c r="AT3" s="405"/>
-      <c r="AU3" s="405"/>
-      <c r="AV3" s="405"/>
-      <c r="AW3" s="405"/>
-      <c r="AX3" s="405"/>
-      <c r="AY3" s="405"/>
-      <c r="AZ3" s="405"/>
-      <c r="BA3" s="405"/>
-      <c r="BB3" s="405"/>
-      <c r="BC3" s="405"/>
-      <c r="BD3" s="405"/>
-      <c r="BE3" s="405"/>
-      <c r="BF3" s="405"/>
-      <c r="BG3" s="405"/>
-      <c r="BH3" s="405"/>
-      <c r="BI3" s="405"/>
-      <c r="BJ3" s="405"/>
-      <c r="BK3" s="405"/>
-      <c r="BL3" s="405"/>
-      <c r="BM3" s="405"/>
-      <c r="BN3" s="405"/>
-      <c r="BO3" s="405"/>
-      <c r="BP3" s="405"/>
-      <c r="BQ3" s="405"/>
-      <c r="BR3" s="405"/>
-      <c r="BS3" s="405"/>
-      <c r="BT3" s="405"/>
-      <c r="BU3" s="405"/>
-      <c r="BW3" s="404" t="s">
+      <c r="A3" s="418"/>
+      <c r="B3" s="407"/>
+      <c r="C3" s="407"/>
+      <c r="D3" s="407"/>
+      <c r="E3" s="407"/>
+      <c r="F3" s="407"/>
+      <c r="G3" s="407"/>
+      <c r="H3" s="407"/>
+      <c r="I3" s="407"/>
+      <c r="J3" s="407"/>
+      <c r="K3" s="407"/>
+      <c r="L3" s="407"/>
+      <c r="M3" s="407"/>
+      <c r="N3" s="407"/>
+      <c r="O3" s="407"/>
+      <c r="P3" s="407"/>
+      <c r="Q3" s="407"/>
+      <c r="R3" s="407"/>
+      <c r="S3" s="407"/>
+      <c r="T3" s="407"/>
+      <c r="U3" s="407"/>
+      <c r="V3" s="407"/>
+      <c r="W3" s="407"/>
+      <c r="X3" s="407"/>
+      <c r="Y3" s="407"/>
+      <c r="Z3" s="407"/>
+      <c r="AA3" s="407"/>
+      <c r="AB3" s="407"/>
+      <c r="AC3" s="407"/>
+      <c r="AD3" s="407"/>
+      <c r="AE3" s="407"/>
+      <c r="AF3" s="407"/>
+      <c r="AG3" s="407"/>
+      <c r="AH3" s="407"/>
+      <c r="AI3" s="407"/>
+      <c r="AJ3" s="407"/>
+      <c r="AK3" s="407"/>
+      <c r="AL3" s="407"/>
+      <c r="AM3" s="407"/>
+      <c r="AN3" s="407"/>
+      <c r="AO3" s="407"/>
+      <c r="AP3" s="407"/>
+      <c r="AQ3" s="407"/>
+      <c r="AR3" s="407"/>
+      <c r="AS3" s="407"/>
+      <c r="AT3" s="407"/>
+      <c r="AU3" s="407"/>
+      <c r="AV3" s="407"/>
+      <c r="AW3" s="407"/>
+      <c r="AX3" s="407"/>
+      <c r="AY3" s="407"/>
+      <c r="AZ3" s="407"/>
+      <c r="BA3" s="407"/>
+      <c r="BB3" s="407"/>
+      <c r="BC3" s="407"/>
+      <c r="BD3" s="407"/>
+      <c r="BE3" s="407"/>
+      <c r="BF3" s="407"/>
+      <c r="BG3" s="407"/>
+      <c r="BH3" s="407"/>
+      <c r="BI3" s="407"/>
+      <c r="BJ3" s="407"/>
+      <c r="BK3" s="407"/>
+      <c r="BL3" s="407"/>
+      <c r="BM3" s="407"/>
+      <c r="BN3" s="407"/>
+      <c r="BO3" s="407"/>
+      <c r="BP3" s="407"/>
+      <c r="BQ3" s="407"/>
+      <c r="BR3" s="407"/>
+      <c r="BS3" s="407"/>
+      <c r="BT3" s="407"/>
+      <c r="BU3" s="407"/>
+      <c r="BW3" s="406" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="405"/>
-      <c r="BY3" s="405"/>
-      <c r="BZ3" s="405"/>
-      <c r="CA3" s="405"/>
-      <c r="CB3" s="405"/>
+      <c r="BX3" s="407"/>
+      <c r="BY3" s="407"/>
+      <c r="BZ3" s="407"/>
+      <c r="CA3" s="407"/>
+      <c r="CB3" s="407"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -18794,366 +18790,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="405"/>
-      <c r="BX4" s="405"/>
-      <c r="BY4" s="405"/>
-      <c r="BZ4" s="405"/>
-      <c r="CA4" s="405"/>
-      <c r="CB4" s="405"/>
+      <c r="BW4" s="407"/>
+      <c r="BX4" s="407"/>
+      <c r="BY4" s="407"/>
+      <c r="BZ4" s="407"/>
+      <c r="CA4" s="407"/>
+      <c r="CB4" s="407"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="417" t="s">
+      <c r="A5" s="394" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" s="405" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="390" t="s">
+      <c r="C5" s="393" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="415" t="s">
+      <c r="D5" s="400" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="415" t="s">
+      <c r="E5" s="400" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="434" t="s">
+      <c r="F5" s="429" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="390" t="s">
+      <c r="G5" s="393" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="341" t="s">
+      <c r="H5" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="341" t="s">
+      <c r="I5" s="332" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="390" t="s">
+      <c r="J5" s="393" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="419" t="s">
+      <c r="K5" s="398" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="401"/>
-      <c r="M5" s="401"/>
-      <c r="N5" s="401"/>
-      <c r="O5" s="401"/>
-      <c r="P5" s="401"/>
-      <c r="Q5" s="401"/>
-      <c r="R5" s="401"/>
-      <c r="S5" s="401"/>
-      <c r="T5" s="401"/>
-      <c r="U5" s="401"/>
-      <c r="V5" s="401"/>
-      <c r="W5" s="401"/>
-      <c r="X5" s="401"/>
-      <c r="Y5" s="390" t="s">
+      <c r="L5" s="390"/>
+      <c r="M5" s="390"/>
+      <c r="N5" s="390"/>
+      <c r="O5" s="390"/>
+      <c r="P5" s="390"/>
+      <c r="Q5" s="390"/>
+      <c r="R5" s="390"/>
+      <c r="S5" s="390"/>
+      <c r="T5" s="390"/>
+      <c r="U5" s="390"/>
+      <c r="V5" s="390"/>
+      <c r="W5" s="390"/>
+      <c r="X5" s="390"/>
+      <c r="Y5" s="393" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="401"/>
-      <c r="AA5" s="401"/>
-      <c r="AB5" s="401"/>
-      <c r="AC5" s="401"/>
-      <c r="AD5" s="401"/>
-      <c r="AE5" s="401"/>
-      <c r="AF5" s="401"/>
-      <c r="AG5" s="401"/>
-      <c r="AH5" s="401"/>
-      <c r="AI5" s="401"/>
-      <c r="AJ5" s="401"/>
-      <c r="AK5" s="401"/>
-      <c r="AL5" s="401"/>
-      <c r="AM5" s="401"/>
-      <c r="AN5" s="401"/>
-      <c r="AO5" s="402"/>
-      <c r="AP5" s="390" t="s">
+      <c r="Z5" s="390"/>
+      <c r="AA5" s="390"/>
+      <c r="AB5" s="390"/>
+      <c r="AC5" s="390"/>
+      <c r="AD5" s="390"/>
+      <c r="AE5" s="390"/>
+      <c r="AF5" s="390"/>
+      <c r="AG5" s="390"/>
+      <c r="AH5" s="390"/>
+      <c r="AI5" s="390"/>
+      <c r="AJ5" s="390"/>
+      <c r="AK5" s="390"/>
+      <c r="AL5" s="390"/>
+      <c r="AM5" s="390"/>
+      <c r="AN5" s="390"/>
+      <c r="AO5" s="391"/>
+      <c r="AP5" s="393" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="390" t="s">
+      <c r="AQ5" s="393" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="390" t="s">
+      <c r="AR5" s="393" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="390" t="s">
+      <c r="AS5" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="390" t="s">
+      <c r="AT5" s="393" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="390" t="s">
+      <c r="AU5" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="390" t="s">
+      <c r="AV5" s="393" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="390" t="s">
+      <c r="AW5" s="393" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="390" t="s">
+      <c r="AX5" s="393" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="400" t="s">
+      <c r="AY5" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="401"/>
-      <c r="BA5" s="401"/>
-      <c r="BB5" s="401"/>
-      <c r="BC5" s="401"/>
-      <c r="BD5" s="401"/>
-      <c r="BE5" s="401"/>
-      <c r="BF5" s="401"/>
-      <c r="BG5" s="401"/>
-      <c r="BH5" s="401"/>
-      <c r="BI5" s="401"/>
-      <c r="BJ5" s="401"/>
-      <c r="BK5" s="401"/>
-      <c r="BL5" s="401"/>
-      <c r="BM5" s="401"/>
-      <c r="BN5" s="401"/>
-      <c r="BO5" s="401"/>
-      <c r="BP5" s="402"/>
-      <c r="BQ5" s="406" t="s">
+      <c r="AZ5" s="390"/>
+      <c r="BA5" s="390"/>
+      <c r="BB5" s="390"/>
+      <c r="BC5" s="390"/>
+      <c r="BD5" s="390"/>
+      <c r="BE5" s="390"/>
+      <c r="BF5" s="390"/>
+      <c r="BG5" s="390"/>
+      <c r="BH5" s="390"/>
+      <c r="BI5" s="390"/>
+      <c r="BJ5" s="390"/>
+      <c r="BK5" s="390"/>
+      <c r="BL5" s="390"/>
+      <c r="BM5" s="390"/>
+      <c r="BN5" s="390"/>
+      <c r="BO5" s="390"/>
+      <c r="BP5" s="391"/>
+      <c r="BQ5" s="409" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="407"/>
-      <c r="BS5" s="400" t="s">
+      <c r="BR5" s="403"/>
+      <c r="BS5" s="389" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="400" t="s">
+      <c r="BT5" s="389" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="394" t="s">
+      <c r="BU5" s="420" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="397" t="s">
+      <c r="BW5" s="421" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="408" t="s">
+      <c r="BX5" s="410" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="409"/>
-      <c r="BZ5" s="409"/>
-      <c r="CA5" s="407"/>
-      <c r="CB5" s="403" t="s">
+      <c r="BY5" s="411"/>
+      <c r="BZ5" s="411"/>
+      <c r="CA5" s="403"/>
+      <c r="CB5" s="422" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="332" t="s">
+      <c r="CC5" s="350" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="332" t="s">
+      <c r="CD5" s="350" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="386"/>
-      <c r="B6" s="386"/>
-      <c r="C6" s="386"/>
-      <c r="D6" s="386"/>
-      <c r="E6" s="386"/>
-      <c r="F6" s="386"/>
-      <c r="G6" s="386"/>
-      <c r="H6" s="386"/>
-      <c r="I6" s="386"/>
-      <c r="J6" s="386"/>
-      <c r="K6" s="391" t="s">
+      <c r="A6" s="387"/>
+      <c r="B6" s="387"/>
+      <c r="C6" s="387"/>
+      <c r="D6" s="387"/>
+      <c r="E6" s="387"/>
+      <c r="F6" s="387"/>
+      <c r="G6" s="387"/>
+      <c r="H6" s="387"/>
+      <c r="I6" s="387"/>
+      <c r="J6" s="387"/>
+      <c r="K6" s="401" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="391" t="s">
+      <c r="L6" s="401" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="391" t="s">
+      <c r="M6" s="401" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="391" t="s">
+      <c r="N6" s="401" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="391" t="s">
+      <c r="O6" s="401" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="391" t="s">
+      <c r="P6" s="401" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="391" t="s">
+      <c r="Q6" s="401" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="391" t="s">
+      <c r="R6" s="401" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="391" t="s">
+      <c r="S6" s="401" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="391" t="s">
+      <c r="T6" s="401" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="391" t="s">
+      <c r="U6" s="401" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="421" t="s">
+      <c r="V6" s="402" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="407"/>
-      <c r="X6" s="391" t="s">
+      <c r="W6" s="403"/>
+      <c r="X6" s="401" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="390" t="s">
+      <c r="Y6" s="393" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="390" t="s">
+      <c r="Z6" s="393" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="390" t="s">
+      <c r="AA6" s="393" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="390" t="s">
+      <c r="AB6" s="393" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="341" t="s">
+      <c r="AC6" s="332" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="341" t="s">
+      <c r="AD6" s="332" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="341" t="s">
+      <c r="AE6" s="332" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="341" t="s">
+      <c r="AF6" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="390" t="s">
+      <c r="AG6" s="393" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="341" t="s">
+      <c r="AH6" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="341" t="s">
+      <c r="AI6" s="332" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="390" t="s">
+      <c r="AJ6" s="393" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="418" t="s">
+      <c r="AK6" s="395" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="390" t="s">
+      <c r="AL6" s="393" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="390" t="s">
+      <c r="AM6" s="393" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="420" t="s">
+      <c r="AN6" s="399" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="390" t="s">
+      <c r="AO6" s="393" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="386"/>
-      <c r="AQ6" s="386"/>
-      <c r="AR6" s="386"/>
-      <c r="AS6" s="386"/>
-      <c r="AT6" s="386"/>
-      <c r="AU6" s="386"/>
-      <c r="AV6" s="386"/>
-      <c r="AW6" s="386"/>
-      <c r="AX6" s="386"/>
-      <c r="AY6" s="400" t="s">
+      <c r="AP6" s="387"/>
+      <c r="AQ6" s="387"/>
+      <c r="AR6" s="387"/>
+      <c r="AS6" s="387"/>
+      <c r="AT6" s="387"/>
+      <c r="AU6" s="387"/>
+      <c r="AV6" s="387"/>
+      <c r="AW6" s="387"/>
+      <c r="AX6" s="387"/>
+      <c r="AY6" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="401"/>
-      <c r="BA6" s="401"/>
-      <c r="BB6" s="401"/>
-      <c r="BC6" s="401"/>
-      <c r="BD6" s="401"/>
-      <c r="BE6" s="401"/>
-      <c r="BF6" s="401"/>
-      <c r="BG6" s="401"/>
-      <c r="BH6" s="401"/>
-      <c r="BI6" s="401"/>
-      <c r="BJ6" s="402"/>
-      <c r="BK6" s="400" t="s">
+      <c r="AZ6" s="390"/>
+      <c r="BA6" s="390"/>
+      <c r="BB6" s="390"/>
+      <c r="BC6" s="390"/>
+      <c r="BD6" s="390"/>
+      <c r="BE6" s="390"/>
+      <c r="BF6" s="390"/>
+      <c r="BG6" s="390"/>
+      <c r="BH6" s="390"/>
+      <c r="BI6" s="390"/>
+      <c r="BJ6" s="391"/>
+      <c r="BK6" s="389" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="401"/>
-      <c r="BM6" s="401"/>
-      <c r="BN6" s="401"/>
-      <c r="BO6" s="401"/>
-      <c r="BP6" s="402"/>
-      <c r="BQ6" s="388" t="s">
+      <c r="BL6" s="390"/>
+      <c r="BM6" s="390"/>
+      <c r="BN6" s="390"/>
+      <c r="BO6" s="390"/>
+      <c r="BP6" s="391"/>
+      <c r="BQ6" s="386" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="388" t="s">
+      <c r="BR6" s="386" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="386"/>
-      <c r="BT6" s="386"/>
-      <c r="BU6" s="395"/>
-      <c r="BW6" s="398"/>
-      <c r="BX6" s="395"/>
-      <c r="BY6" s="410"/>
-      <c r="BZ6" s="410"/>
-      <c r="CA6" s="398"/>
-      <c r="CB6" s="386"/>
-      <c r="CC6" s="386"/>
-      <c r="CD6" s="386"/>
+      <c r="BS6" s="387"/>
+      <c r="BT6" s="387"/>
+      <c r="BU6" s="396"/>
+      <c r="BW6" s="413"/>
+      <c r="BX6" s="396"/>
+      <c r="BY6" s="412"/>
+      <c r="BZ6" s="412"/>
+      <c r="CA6" s="413"/>
+      <c r="CB6" s="387"/>
+      <c r="CC6" s="387"/>
+      <c r="CD6" s="387"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="386"/>
-      <c r="B7" s="386"/>
-      <c r="C7" s="386"/>
-      <c r="D7" s="386"/>
-      <c r="E7" s="386"/>
-      <c r="F7" s="386"/>
-      <c r="G7" s="386"/>
-      <c r="H7" s="386"/>
-      <c r="I7" s="386"/>
-      <c r="J7" s="386"/>
-      <c r="K7" s="386"/>
-      <c r="L7" s="386"/>
-      <c r="M7" s="386"/>
-      <c r="N7" s="386"/>
-      <c r="O7" s="386"/>
-      <c r="P7" s="386"/>
-      <c r="Q7" s="386"/>
-      <c r="R7" s="386"/>
-      <c r="S7" s="386"/>
-      <c r="T7" s="386"/>
-      <c r="U7" s="386"/>
-      <c r="V7" s="396"/>
-      <c r="W7" s="422"/>
-      <c r="X7" s="386"/>
-      <c r="Y7" s="386"/>
-      <c r="Z7" s="386"/>
-      <c r="AA7" s="386"/>
-      <c r="AB7" s="386"/>
-      <c r="AC7" s="386"/>
-      <c r="AD7" s="386"/>
-      <c r="AE7" s="386"/>
-      <c r="AF7" s="386"/>
-      <c r="AG7" s="386"/>
-      <c r="AH7" s="386"/>
-      <c r="AI7" s="386"/>
-      <c r="AJ7" s="386"/>
-      <c r="AK7" s="395"/>
-      <c r="AL7" s="386"/>
-      <c r="AM7" s="386"/>
-      <c r="AN7" s="386"/>
-      <c r="AO7" s="386"/>
-      <c r="AP7" s="386"/>
-      <c r="AQ7" s="386"/>
-      <c r="AR7" s="386"/>
-      <c r="AS7" s="386"/>
-      <c r="AT7" s="386"/>
-      <c r="AU7" s="386"/>
-      <c r="AV7" s="386"/>
-      <c r="AW7" s="386"/>
-      <c r="AX7" s="386"/>
+      <c r="A7" s="387"/>
+      <c r="B7" s="387"/>
+      <c r="C7" s="387"/>
+      <c r="D7" s="387"/>
+      <c r="E7" s="387"/>
+      <c r="F7" s="387"/>
+      <c r="G7" s="387"/>
+      <c r="H7" s="387"/>
+      <c r="I7" s="387"/>
+      <c r="J7" s="387"/>
+      <c r="K7" s="387"/>
+      <c r="L7" s="387"/>
+      <c r="M7" s="387"/>
+      <c r="N7" s="387"/>
+      <c r="O7" s="387"/>
+      <c r="P7" s="387"/>
+      <c r="Q7" s="387"/>
+      <c r="R7" s="387"/>
+      <c r="S7" s="387"/>
+      <c r="T7" s="387"/>
+      <c r="U7" s="387"/>
+      <c r="V7" s="397"/>
+      <c r="W7" s="404"/>
+      <c r="X7" s="387"/>
+      <c r="Y7" s="387"/>
+      <c r="Z7" s="387"/>
+      <c r="AA7" s="387"/>
+      <c r="AB7" s="387"/>
+      <c r="AC7" s="387"/>
+      <c r="AD7" s="387"/>
+      <c r="AE7" s="387"/>
+      <c r="AF7" s="387"/>
+      <c r="AG7" s="387"/>
+      <c r="AH7" s="387"/>
+      <c r="AI7" s="387"/>
+      <c r="AJ7" s="387"/>
+      <c r="AK7" s="396"/>
+      <c r="AL7" s="387"/>
+      <c r="AM7" s="387"/>
+      <c r="AN7" s="387"/>
+      <c r="AO7" s="387"/>
+      <c r="AP7" s="387"/>
+      <c r="AQ7" s="387"/>
+      <c r="AR7" s="387"/>
+      <c r="AS7" s="387"/>
+      <c r="AT7" s="387"/>
+      <c r="AU7" s="387"/>
+      <c r="AV7" s="387"/>
+      <c r="AW7" s="387"/>
+      <c r="AX7" s="387"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19163,7 +19159,7 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="400" t="s">
+      <c r="BB7" s="389" t="s">
         <v>70</v>
       </c>
       <c r="BC7" s="392" t="s">
@@ -19187,98 +19183,98 @@
       <c r="BI7" s="392" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="393" t="s">
+      <c r="BJ7" s="419" t="s">
         <v>80</v>
       </c>
       <c r="BK7" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="400" t="s">
+      <c r="BL7" s="389" t="s">
         <v>82</v>
       </c>
       <c r="BM7" s="392" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="400" t="s">
+      <c r="BN7" s="389" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="400" t="s">
+      <c r="BO7" s="389" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="400" t="s">
+      <c r="BP7" s="389" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="386"/>
-      <c r="BR7" s="386"/>
-      <c r="BS7" s="386"/>
-      <c r="BT7" s="386"/>
-      <c r="BU7" s="395"/>
-      <c r="BW7" s="398"/>
-      <c r="BX7" s="411"/>
-      <c r="BY7" s="412"/>
-      <c r="BZ7" s="412"/>
-      <c r="CA7" s="399"/>
-      <c r="CB7" s="386"/>
-      <c r="CC7" s="386"/>
-      <c r="CD7" s="386"/>
+      <c r="BQ7" s="387"/>
+      <c r="BR7" s="387"/>
+      <c r="BS7" s="387"/>
+      <c r="BT7" s="387"/>
+      <c r="BU7" s="396"/>
+      <c r="BW7" s="413"/>
+      <c r="BX7" s="414"/>
+      <c r="BY7" s="415"/>
+      <c r="BZ7" s="415"/>
+      <c r="CA7" s="416"/>
+      <c r="CB7" s="387"/>
+      <c r="CC7" s="387"/>
+      <c r="CD7" s="387"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="389"/>
-      <c r="B8" s="389"/>
-      <c r="C8" s="389"/>
-      <c r="D8" s="389"/>
-      <c r="E8" s="389"/>
-      <c r="F8" s="389"/>
-      <c r="G8" s="389"/>
-      <c r="H8" s="389"/>
-      <c r="I8" s="389"/>
-      <c r="J8" s="389"/>
-      <c r="K8" s="389"/>
-      <c r="L8" s="389"/>
-      <c r="M8" s="389"/>
-      <c r="N8" s="389"/>
-      <c r="O8" s="389"/>
-      <c r="P8" s="389"/>
-      <c r="Q8" s="389"/>
-      <c r="R8" s="389"/>
-      <c r="S8" s="389"/>
-      <c r="T8" s="389"/>
-      <c r="U8" s="389"/>
+      <c r="A8" s="388"/>
+      <c r="B8" s="388"/>
+      <c r="C8" s="388"/>
+      <c r="D8" s="388"/>
+      <c r="E8" s="388"/>
+      <c r="F8" s="388"/>
+      <c r="G8" s="388"/>
+      <c r="H8" s="388"/>
+      <c r="I8" s="388"/>
+      <c r="J8" s="388"/>
+      <c r="K8" s="388"/>
+      <c r="L8" s="388"/>
+      <c r="M8" s="388"/>
+      <c r="N8" s="388"/>
+      <c r="O8" s="388"/>
+      <c r="P8" s="388"/>
+      <c r="Q8" s="388"/>
+      <c r="R8" s="388"/>
+      <c r="S8" s="388"/>
+      <c r="T8" s="388"/>
+      <c r="U8" s="388"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="389"/>
-      <c r="Y8" s="389"/>
-      <c r="Z8" s="389"/>
-      <c r="AA8" s="389"/>
-      <c r="AB8" s="389"/>
-      <c r="AC8" s="389"/>
-      <c r="AD8" s="389"/>
-      <c r="AE8" s="389"/>
-      <c r="AF8" s="389"/>
-      <c r="AG8" s="389"/>
-      <c r="AH8" s="389"/>
-      <c r="AI8" s="389"/>
-      <c r="AJ8" s="389"/>
-      <c r="AK8" s="396"/>
-      <c r="AL8" s="389"/>
-      <c r="AM8" s="389"/>
-      <c r="AN8" s="389"/>
-      <c r="AO8" s="389"/>
-      <c r="AP8" s="389"/>
-      <c r="AQ8" s="389"/>
-      <c r="AR8" s="389"/>
-      <c r="AS8" s="389"/>
-      <c r="AT8" s="389"/>
-      <c r="AU8" s="389"/>
-      <c r="AV8" s="389"/>
-      <c r="AW8" s="389"/>
-      <c r="AX8" s="389"/>
+      <c r="X8" s="388"/>
+      <c r="Y8" s="388"/>
+      <c r="Z8" s="388"/>
+      <c r="AA8" s="388"/>
+      <c r="AB8" s="388"/>
+      <c r="AC8" s="388"/>
+      <c r="AD8" s="388"/>
+      <c r="AE8" s="388"/>
+      <c r="AF8" s="388"/>
+      <c r="AG8" s="388"/>
+      <c r="AH8" s="388"/>
+      <c r="AI8" s="388"/>
+      <c r="AJ8" s="388"/>
+      <c r="AK8" s="397"/>
+      <c r="AL8" s="388"/>
+      <c r="AM8" s="388"/>
+      <c r="AN8" s="388"/>
+      <c r="AO8" s="388"/>
+      <c r="AP8" s="388"/>
+      <c r="AQ8" s="388"/>
+      <c r="AR8" s="388"/>
+      <c r="AS8" s="388"/>
+      <c r="AT8" s="388"/>
+      <c r="AU8" s="388"/>
+      <c r="AV8" s="388"/>
+      <c r="AW8" s="388"/>
+      <c r="AX8" s="388"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19288,27 +19284,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="389"/>
-      <c r="BC8" s="389"/>
-      <c r="BD8" s="389"/>
-      <c r="BE8" s="389"/>
-      <c r="BF8" s="389"/>
-      <c r="BG8" s="389"/>
-      <c r="BH8" s="389"/>
-      <c r="BI8" s="389"/>
-      <c r="BJ8" s="389"/>
-      <c r="BK8" s="389"/>
-      <c r="BL8" s="389"/>
-      <c r="BM8" s="389"/>
-      <c r="BN8" s="389"/>
-      <c r="BO8" s="389"/>
-      <c r="BP8" s="389"/>
-      <c r="BQ8" s="389"/>
-      <c r="BR8" s="389"/>
-      <c r="BS8" s="389"/>
-      <c r="BT8" s="389"/>
-      <c r="BU8" s="396"/>
-      <c r="BW8" s="399"/>
+      <c r="BB8" s="388"/>
+      <c r="BC8" s="388"/>
+      <c r="BD8" s="388"/>
+      <c r="BE8" s="388"/>
+      <c r="BF8" s="388"/>
+      <c r="BG8" s="388"/>
+      <c r="BH8" s="388"/>
+      <c r="BI8" s="388"/>
+      <c r="BJ8" s="388"/>
+      <c r="BK8" s="388"/>
+      <c r="BL8" s="388"/>
+      <c r="BM8" s="388"/>
+      <c r="BN8" s="388"/>
+      <c r="BO8" s="388"/>
+      <c r="BP8" s="388"/>
+      <c r="BQ8" s="388"/>
+      <c r="BR8" s="388"/>
+      <c r="BS8" s="388"/>
+      <c r="BT8" s="388"/>
+      <c r="BU8" s="397"/>
+      <c r="BW8" s="416"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19321,9 +19317,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="387"/>
-      <c r="CC8" s="387"/>
-      <c r="CD8" s="387"/>
+      <c r="CB8" s="408"/>
+      <c r="CC8" s="408"/>
+      <c r="CD8" s="408"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21330,6 +21326,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="AU5:AU8"/>
     <mergeCell ref="BH7:BH8"/>
     <mergeCell ref="BI7:BI8"/>
     <mergeCell ref="K5:X5"/>
@@ -21346,72 +21408,6 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AN6:AN8"/>
     <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>
